--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/hp12384_bristol_ac_uk/Documents/Projects/APEX/APEX_WP2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_2299CC05A0D764E4975C3285521D731F78C745D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E2DEC22-EE13-C54C-80F9-92A0711F95E1}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_36C5A469B1942586A8DAF0BA92C89005C29E96B8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0620DFDC-26A5-E646-B488-99B69FC79DA3}"/>
   <bookViews>
-    <workbookView xWindow="-29500" yWindow="-860" windowWidth="28500" windowHeight="19700" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COD date time index" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -66,6 +66,93 @@
   </si>
   <si>
     <t>12) 20*30 -3</t>
+  </si>
+  <si>
+    <t>24/07/2024</t>
+  </si>
+  <si>
+    <t>29/07/2024</t>
+  </si>
+  <si>
+    <t>02/08/2024</t>
+  </si>
+  <si>
+    <t>06/08/2024</t>
+  </si>
+  <si>
+    <t>08/08/2024</t>
+  </si>
+  <si>
+    <t>16/09/2024</t>
+  </si>
+  <si>
+    <t>24/09/2024</t>
+  </si>
+  <si>
+    <t>02/10/2024</t>
+  </si>
+  <si>
+    <t>10/10/2024</t>
+  </si>
+  <si>
+    <t>12/10/2024</t>
+  </si>
+  <si>
+    <t>16/10/2024</t>
+  </si>
+  <si>
+    <t>25/10/2024</t>
+  </si>
+  <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
+    <t>07/02/2025</t>
+  </si>
+  <si>
+    <t>11/02/2025</t>
+  </si>
+  <si>
+    <t>14/02/2025</t>
+  </si>
+  <si>
+    <t>21/02/2025</t>
+  </si>
+  <si>
+    <t>24/02/2025</t>
+  </si>
+  <si>
+    <t>02/04/2025</t>
+  </si>
+  <si>
+    <t>03/04/2025</t>
+  </si>
+  <si>
+    <t>04/04/2025</t>
+  </si>
+  <si>
+    <t>28/04/2025</t>
+  </si>
+  <si>
+    <t>30/04/2025</t>
+  </si>
+  <si>
+    <t>07/05/2025</t>
+  </si>
+  <si>
+    <t>08/05/2025</t>
+  </si>
+  <si>
+    <t>09/05/2025</t>
+  </si>
+  <si>
+    <t>12/05/2025</t>
+  </si>
+  <si>
+    <t>13/05/2025</t>
+  </si>
+  <si>
+    <t>18/05/2025</t>
   </si>
 </sst>
 </file>
@@ -411,6 +498,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -454,8 +544,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2" s="1">
         <v>45497.444166666668</v>
@@ -495,8 +585,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>45502.557013888887</v>
@@ -536,8 +626,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <v>45506.421377314808</v>
@@ -577,8 +667,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>45510.420578703714</v>
@@ -618,8 +708,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6" s="1">
         <v>45512.460555555554</v>
@@ -659,8 +749,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7" s="1">
         <v>45551.427384259259</v>
@@ -700,8 +790,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8" s="1">
         <v>45559.396516203713</v>
@@ -741,8 +831,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9" s="1">
         <v>45567.475219907406</v>
@@ -782,8 +872,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10" s="1">
         <v>45575.417071759257</v>
@@ -823,8 +913,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11" s="1">
         <v>45577.504918981482</v>
@@ -864,8 +954,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>45581.4221412037</v>
@@ -905,8 +995,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13" s="1">
         <v>45590.509282407409</v>
@@ -946,8 +1036,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14" s="1">
         <v>45636.417743055557</v>
@@ -987,8 +1077,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15" s="1">
         <v>45695.426319444443</v>
@@ -1028,8 +1118,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16" s="1">
         <v>45699.422881944447</v>
@@ -1069,8 +1159,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17" s="1">
         <v>45702.557650462957</v>
@@ -1110,8 +1200,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18" s="1">
         <v>45709.429502314822</v>
@@ -1151,8 +1241,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19" s="1">
         <v>45712.416400462957</v>
@@ -1192,8 +1282,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20" s="1">
         <v>45749.671550925923</v>
@@ -1233,8 +1323,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21" s="1">
         <v>45750.442800925928</v>
@@ -1274,8 +1364,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22" s="1">
         <v>45751.450590277767</v>
@@ -1315,8 +1405,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23" s="1">
         <v>45775.6487037037</v>
@@ -1356,8 +1446,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24" s="1">
         <v>45777.661747685182</v>
@@ -1397,8 +1487,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25" s="1">
         <v>45784.671226851853</v>
@@ -1438,8 +1528,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26" s="1">
         <v>45785.601956018523</v>
@@ -1479,8 +1569,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27" s="1">
         <v>45786.596226851849</v>
@@ -1520,8 +1610,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28" s="1">
         <v>45789.474861111114</v>
@@ -1561,8 +1651,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29" s="1">
         <v>45790.520335648151</v>
@@ -1602,8 +1692,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30" s="1">
         <v>45795.63422453704</v>
@@ -1694,8 +1784,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>839</v>
@@ -1735,8 +1825,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>180</v>
@@ -1776,8 +1866,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>101</v>
@@ -1817,8 +1907,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>47</v>
@@ -1858,8 +1948,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>360</v>
@@ -1899,8 +1989,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>900</v>
@@ -1940,8 +2030,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>101</v>
@@ -1981,8 +2071,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>360</v>
@@ -2022,8 +2112,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>185</v>
@@ -2063,8 +2153,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>79</v>
@@ -2104,8 +2194,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>30</v>
@@ -2145,8 +2235,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>270</v>
@@ -2186,8 +2276,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>900</v>
@@ -2227,8 +2317,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>801</v>
@@ -2268,8 +2358,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>785</v>
@@ -2309,8 +2399,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>312</v>
@@ -2350,8 +2440,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>180</v>
@@ -2391,8 +2481,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>76</v>
@@ -2432,8 +2522,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>33</v>
@@ -2473,8 +2563,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>162</v>
@@ -2514,8 +2604,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>810</v>
@@ -2555,8 +2645,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>844</v>
@@ -2596,8 +2686,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>376</v>
@@ -2637,8 +2727,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>198</v>
@@ -2678,8 +2768,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>70</v>
@@ -2719,8 +2809,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>817</v>
@@ -2760,8 +2850,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>45</v>
@@ -2801,8 +2891,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>182</v>
@@ -2842,8 +2932,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>180</v>
@@ -2934,8 +3024,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2975,8 +3065,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3016,8 +3106,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -3057,8 +3147,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3098,8 +3188,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -3139,8 +3229,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -3180,8 +3270,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3221,8 +3311,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -3262,8 +3352,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -3303,8 +3393,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -3344,8 +3434,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -3385,8 +3475,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -3426,8 +3516,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -3467,8 +3557,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -3508,8 +3598,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -3549,8 +3639,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>3</v>
@@ -3590,8 +3680,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>3</v>
@@ -3631,8 +3721,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -3672,8 +3762,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3713,8 +3803,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>3</v>
@@ -3754,8 +3844,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -3795,8 +3885,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>0.1</v>
@@ -3836,8 +3926,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>0.1</v>
@@ -3877,8 +3967,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>0.1</v>
@@ -3918,8 +4008,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>0.1</v>
@@ -3959,8 +4049,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0.1</v>
@@ -4000,8 +4090,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>0.1</v>
@@ -4041,8 +4131,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>0.1</v>
@@ -4082,8 +4172,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>0.1</v>
@@ -4174,8 +4264,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>162.982</v>
@@ -4215,8 +4305,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>78.113</v>
@@ -4256,8 +4346,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>42.896000000000001</v>
@@ -4297,8 +4387,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>20.974</v>
@@ -4335,8 +4425,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>100.102</v>
@@ -4376,8 +4466,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>275.97899999999998</v>
@@ -4417,8 +4507,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>9.1549999999999994</v>
@@ -4458,8 +4548,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>84.486999999999995</v>
@@ -4499,8 +4589,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>3.7010000000000001</v>
@@ -4540,8 +4630,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>-5.4050000000000002</v>
@@ -4581,8 +4671,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>-9.532</v>
@@ -4622,8 +4712,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>41.942</v>
@@ -4663,8 +4753,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>87.986999999999995</v>
@@ -4704,8 +4794,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>226.852</v>
@@ -4742,8 +4832,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>330.64600000000002</v>
@@ -4783,8 +4873,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>224.16800000000001</v>
@@ -4824,8 +4914,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>49.49</v>
@@ -4865,8 +4955,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>27.222999999999999</v>
@@ -4906,8 +4996,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>135.59100000000001</v>
@@ -4947,8 +5037,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>158.90600000000001</v>
@@ -4988,8 +5078,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>329.71300000000002</v>
@@ -5029,8 +5119,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>68.546999999999997</v>
@@ -5070,8 +5160,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>16.163</v>
@@ -5111,8 +5201,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>13.675000000000001</v>
@@ -5152,8 +5242,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>8.202</v>
@@ -5193,8 +5283,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>23.042999999999999</v>
@@ -5234,8 +5324,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>2.5590000000000002</v>
@@ -5275,8 +5365,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>4.5090000000000003</v>
@@ -5316,8 +5406,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>-0.42899999999999999</v>
@@ -5408,8 +5498,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>2.6563132324E-5</v>
@@ -5449,8 +5539,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>6.1016407690000001E-6</v>
@@ -5490,8 +5580,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>1.8400668160000001E-6</v>
@@ -5531,8 +5621,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>4.3990867599999999E-7</v>
@@ -5569,8 +5659,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>1.0020410404E-5</v>
@@ -5610,8 +5700,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>2.5388136147E-5</v>
@@ -5651,8 +5741,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>8.3814024999999997E-8</v>
@@ -5692,8 +5782,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>2.3793510563333328E-6</v>
@@ -5733,8 +5823,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>4.5658003333333333E-9</v>
@@ -5774,8 +5864,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>9.7380083333333341E-9</v>
@@ -5815,8 +5905,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>3.0286341333333342E-8</v>
@@ -5856,8 +5946,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>5.8637712133333332E-7</v>
@@ -5897,8 +5987,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>2.5805707230000001E-6</v>
@@ -5938,8 +6028,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>5.1461829904000001E-5</v>
@@ -5976,8 +6066,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>3.6442259105333327E-5</v>
@@ -6017,8 +6107,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>1.6750430741333339E-5</v>
@@ -6058,8 +6148,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>8.1642003333333337E-7</v>
@@ -6099,8 +6189,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>2.4703057633333328E-7</v>
@@ -6140,8 +6230,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>6.1283064270000017E-6</v>
@@ -6181,8 +6271,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>8.4170389453333348E-6</v>
@@ -6222,8 +6312,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>3.6236887456333338E-5</v>
@@ -6263,8 +6353,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>4.698691208999999E-5</v>
@@ -6304,8 +6394,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>2.61242569E-6</v>
@@ -6345,8 +6435,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>1.87005625E-6</v>
@@ -6386,8 +6476,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>6.7272803999999989E-7</v>
@@ -6427,8 +6517,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>5.3097984900000006E-6</v>
@@ -6468,8 +6558,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>6.5484810000000006E-8</v>
@@ -6509,8 +6599,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>2.0331081000000001E-7</v>
@@ -6550,8 +6640,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>1.8404100000000001E-9</v>
@@ -6642,8 +6732,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.33993099999999998</v>
@@ -6683,8 +6773,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0.18506900000000001</v>
@@ -6724,8 +6814,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>0.27326400000000001</v>
@@ -6765,8 +6855,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>0.30208299999999999</v>
@@ -6803,8 +6893,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>0.35486099999999998</v>
@@ -6844,8 +6934,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0.61493100000000001</v>
@@ -6885,8 +6975,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0.16666700000000001</v>
@@ -6926,8 +7016,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0.46041700000000002</v>
@@ -6967,8 +7057,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>0.33541700000000002</v>
@@ -7008,8 +7098,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0.39756900000000001</v>
@@ -7049,8 +7139,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0.51597199999999999</v>
@@ -7090,8 +7180,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.48888900000000002</v>
@@ -7131,8 +7221,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>1.3819440000000001</v>
@@ -7172,8 +7262,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0.286111</v>
@@ -7210,8 +7300,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0.39687499999999998</v>
@@ -7251,8 +7341,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0.27013900000000002</v>
@@ -7292,8 +7382,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>0.137847</v>
@@ -7333,8 +7423,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>0.26597199999999999</v>
@@ -7374,8 +7464,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>6.9399999999999996E-4</v>
@@ -7415,8 +7505,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>0.19722200000000001</v>
@@ -7456,8 +7546,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>0.31979200000000002</v>
@@ -7497,8 +7587,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>2.8819000000000001E-2</v>
@@ -7538,8 +7628,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>0.19062499999999999</v>
@@ -7579,8 +7669,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>0.16493099999999999</v>
@@ -7620,8 +7710,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>1.042E-3</v>
@@ -7661,8 +7751,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0.202431</v>
@@ -7702,8 +7792,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>5.2430999999999998E-2</v>
@@ -7743,8 +7833,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>0.157639</v>
@@ -7784,8 +7874,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -7876,8 +7966,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>-1.2300000000000001E-4</v>
@@ -7917,8 +8007,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>-3.19E-4</v>
@@ -7958,8 +8048,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>-7.7000000000000001E-5</v>
@@ -7996,8 +8086,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>-3.4999999999999997E-5</v>
@@ -8034,8 +8124,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>-3.1300000000000002E-4</v>
@@ -8075,8 +8165,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>-2.1800000000000001E-4</v>
@@ -8116,8 +8206,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>-2.9E-5</v>
@@ -8154,8 +8244,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>-2.22E-4</v>
@@ -8195,8 +8285,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>-2.0999999999999999E-5</v>
@@ -8236,8 +8326,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>-2.8E-5</v>
@@ -8277,8 +8367,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>-4.0000000000000003E-5</v>
@@ -8318,8 +8408,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>-1.11E-4</v>
@@ -8359,8 +8449,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>-1.8200000000000001E-4</v>
@@ -8400,8 +8490,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>-2.4899999999999998E-4</v>
@@ -8438,8 +8528,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>-1.2899999999999999E-4</v>
@@ -8479,8 +8569,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>-3.3399999999999999E-4</v>
@@ -8520,8 +8610,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>-1.54E-4</v>
@@ -8561,8 +8651,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>-6.0999999999999999E-5</v>
@@ -8602,8 +8692,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>-1.8309999999999999E-3</v>
@@ -8643,8 +8733,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>-3.4200000000000002E-4</v>
@@ -8684,8 +8774,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>-1.95E-4</v>
@@ -8725,8 +8815,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>-1.4069999999999999E-2</v>
@@ -8766,8 +8856,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>-6.2000000000000003E-5</v>
@@ -8807,8 +8897,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>-3.0000000000000001E-5</v>
@@ -8848,8 +8938,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>-1.63E-4</v>
@@ -8889,8 +8979,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>-4.3000000000000002E-5</v>
@@ -8930,8 +9020,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>-1.5E-5</v>
@@ -8968,8 +9058,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>-2.0999999999999999E-5</v>
@@ -9009,8 +9099,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>-3.9999999999999998E-6</v>
@@ -9058,10 +9148,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -9105,8 +9191,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>45497.456319444442</v>
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <v>3.891</v>
@@ -9146,8 +9232,8 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>45502.568819444437</v>
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0.58499999999999996</v>
@@ -9187,8 +9273,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>45506.432141203702</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
         <v>0.26100000000000001</v>
@@ -9228,8 +9314,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>45510.431689814817</v>
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>4.9000000000000002E-2</v>
@@ -9269,8 +9355,8 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>45512.469583333332</v>
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
         <v>1.046</v>
@@ -9310,8 +9396,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>45551.438842592594</v>
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
         <v>2.665</v>
@@ -9351,8 +9437,8 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>45559.396516203713</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1.2E-2</v>
@@ -9392,8 +9478,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>45567.486678240741</v>
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0.161</v>
@@ -9433,8 +9519,8 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>45575.428530092591</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
       <c r="B10">
         <v>4.0000000000000001E-3</v>
@@ -9474,8 +9560,8 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>45577.514988425923</v>
+      <c r="A11" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
         <v>2.1000000000000001E-2</v>
@@ -9515,8 +9601,8 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>45581.431863425933</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>5.1999999999999998E-2</v>
@@ -9556,8 +9642,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>45590.521087962959</v>
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0.27400000000000002</v>
@@ -9597,8 +9683,8 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>45636.426770833343</v>
+      <c r="A14" t="s">
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0.34899999999999998</v>
@@ -9638,8 +9724,8 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>45695.437777777777</v>
+      <c r="A15" t="s">
+        <v>26</v>
       </c>
       <c r="B15">
         <v>7.524</v>
@@ -9679,8 +9765,8 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>45699.435034722221</v>
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
         <v>5.2910000000000004</v>
@@ -9720,8 +9806,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>45702.570150462961</v>
+      <c r="A17" t="s">
+        <v>28</v>
       </c>
       <c r="B17">
         <v>1.58</v>
@@ -9761,8 +9847,8 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>45709.443043981482</v>
+      <c r="A18" t="s">
+        <v>29</v>
       </c>
       <c r="B18">
         <v>8.8999999999999996E-2</v>
@@ -9802,8 +9888,8 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>45712.429942129631</v>
+      <c r="A19" t="s">
+        <v>30</v>
       </c>
       <c r="B19">
         <v>4.3999999999999997E-2</v>
@@ -9843,8 +9929,8 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>45749.684745370367</v>
+      <c r="A20" t="s">
+        <v>31</v>
       </c>
       <c r="B20">
         <v>0.26900000000000002</v>
@@ -9884,8 +9970,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>45750.456342592603</v>
+      <c r="A21" t="s">
+        <v>32</v>
       </c>
       <c r="B21">
         <v>0.48099999999999998</v>
@@ -9925,8 +10011,8 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>45751.463090277779</v>
+      <c r="A22" t="s">
+        <v>33</v>
       </c>
       <c r="B22">
         <v>4.2439999999999998</v>
@@ -9966,8 +10052,8 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>45775.660162037027</v>
+      <c r="A23" t="s">
+        <v>34</v>
       </c>
       <c r="B23">
         <v>0.58799999999999997</v>
@@ -10007,8 +10093,8 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>45777.673206018517</v>
+      <c r="A24" t="s">
+        <v>35</v>
       </c>
       <c r="B24">
         <v>0.13800000000000001</v>
@@ -10048,8 +10134,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>45784.682685185187</v>
+      <c r="A25" t="s">
+        <v>36</v>
       </c>
       <c r="B25">
         <v>9.9000000000000005E-2</v>
@@ -10089,8 +10175,8 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>45785.61341435185</v>
+      <c r="A26" t="s">
+        <v>37</v>
       </c>
       <c r="B26">
         <v>0.03</v>
@@ -10130,8 +10216,8 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>45786.607685185183</v>
+      <c r="A27" t="s">
+        <v>38</v>
       </c>
       <c r="B27">
         <v>0.39200000000000002</v>
@@ -10171,8 +10257,8 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>45789.486319444448</v>
+      <c r="A28" t="s">
+        <v>39</v>
       </c>
       <c r="B28">
         <v>3.0000000000000001E-3</v>
@@ -10212,8 +10298,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>45790.532141203701</v>
+      <c r="A29" t="s">
+        <v>40</v>
       </c>
       <c r="B29">
         <v>8.0000000000000002E-3</v>
@@ -10253,8 +10339,8 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>45795.64603009259</v>
+      <c r="A30" t="s">
+        <v>41</v>
       </c>
       <c r="B30">
         <v>0</v>

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.109</v>
+        <v>0.272</v>
       </c>
       <c r="C2" t="n">
-        <v>0.096</v>
+        <v>0.319</v>
       </c>
       <c r="D2" t="n">
-        <v>0.254</v>
+        <v>0.58</v>
       </c>
       <c r="E2" t="n">
-        <v>0.608</v>
+        <v>1.085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.124</v>
+        <v>0.211</v>
       </c>
       <c r="G2" t="n">
-        <v>0.253</v>
+        <v>0.463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.146</v>
+        <v>0.417</v>
       </c>
       <c r="I2" t="n">
-        <v>0.185</v>
+        <v>0.527</v>
       </c>
       <c r="J2" t="n">
-        <v>0.293</v>
+        <v>0.755</v>
       </c>
       <c r="K2" t="n">
-        <v>0.151</v>
+        <v>0.487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.138</v>
+        <v>0.422</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039</v>
+        <v>0.082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08</v>
+        <v>0.175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.511</v>
+        <v>0.865</v>
       </c>
       <c r="F3" t="n">
-        <v>0.062</v>
+        <v>0.104</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="H3" t="n">
-        <v>0.059</v>
+        <v>0.219</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.209</v>
       </c>
       <c r="J3" t="n">
-        <v>0.041</v>
+        <v>0.141</v>
       </c>
       <c r="K3" t="n">
-        <v>0.046</v>
+        <v>0.224</v>
       </c>
       <c r="L3" t="n">
-        <v>0.054</v>
+        <v>0.176</v>
       </c>
       <c r="M3" t="n">
-        <v>0.012</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1917,40 +1917,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.011</v>
+        <v>0.023</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>0.022</v>
+        <v>0.041</v>
       </c>
       <c r="E4" t="n">
-        <v>0.423</v>
+        <v>0.717</v>
       </c>
       <c r="F4" t="n">
-        <v>0.058</v>
+        <v>0.098</v>
       </c>
       <c r="G4" t="n">
-        <v>0.041</v>
+        <v>0.073</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.001</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="5">
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E5" t="n">
-        <v>0.41</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.096</v>
+        <v>0.159</v>
       </c>
       <c r="G5" t="n">
-        <v>0.065</v>
+        <v>0.107</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.019</v>
+        <v>0.059</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="D6" t="n">
-        <v>0.011</v>
+        <v>0.041</v>
       </c>
       <c r="E6" t="n">
-        <v>0.336</v>
+        <v>0.583</v>
       </c>
       <c r="F6" t="n">
-        <v>0.082</v>
+        <v>0.142</v>
       </c>
       <c r="G6" t="n">
-        <v>0.028</v>
+        <v>0.055</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.014</v>
+        <v>0.083</v>
       </c>
       <c r="K6" t="n">
-        <v>0.031</v>
+        <v>0.137</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008</v>
+        <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.011</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.015</v>
+        <v>0.063</v>
       </c>
       <c r="C7" t="n">
-        <v>0.013</v>
+        <v>0.074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007</v>
+        <v>0.038</v>
       </c>
       <c r="E7" t="n">
-        <v>0.029</v>
+        <v>0.063</v>
       </c>
       <c r="F7" t="n">
-        <v>0.094</v>
+        <v>0.169</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.646</v>
+        <v>1.117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.369</v>
+        <v>0.617</v>
       </c>
       <c r="J7" t="n">
-        <v>0.416</v>
+        <v>0.743</v>
       </c>
       <c r="K7" t="n">
-        <v>0.457</v>
+        <v>0.773</v>
       </c>
       <c r="L7" t="n">
-        <v>0.284</v>
+        <v>0.553</v>
       </c>
       <c r="M7" t="n">
-        <v>0.364</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="8">
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.059</v>
+        <v>0.099</v>
       </c>
       <c r="F8" t="n">
-        <v>0.203</v>
+        <v>0.349</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.063</v>
+        <v>0.082</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2132,37 +2132,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03</v>
+        <v>0.055</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.015</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="F10" t="n">
-        <v>0.019</v>
+        <v>0.032</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.014</v>
+        <v>0.024</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,25 +2316,25 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.003</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.263</v>
+        <v>0.584</v>
       </c>
       <c r="C15" t="n">
-        <v>0.177</v>
+        <v>0.497</v>
       </c>
       <c r="D15" t="n">
-        <v>0.246</v>
+        <v>0.607</v>
       </c>
       <c r="E15" t="n">
-        <v>0.536</v>
+        <v>0.948</v>
       </c>
       <c r="F15" t="n">
-        <v>0.103</v>
+        <v>0.172</v>
       </c>
       <c r="G15" t="n">
-        <v>0.594</v>
+        <v>1.029</v>
       </c>
       <c r="H15" t="n">
-        <v>0.174</v>
+        <v>0.311</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.185</v>
+        <v>0.464</v>
       </c>
       <c r="K15" t="n">
-        <v>0.356</v>
+        <v>0.672</v>
       </c>
       <c r="L15" t="n">
-        <v>0.502</v>
+        <v>0.919</v>
       </c>
       <c r="M15" t="n">
-        <v>0.49</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.167</v>
+        <v>0.392</v>
       </c>
       <c r="C16" t="n">
-        <v>0.136</v>
+        <v>0.386</v>
       </c>
       <c r="D16" t="n">
-        <v>0.262</v>
+        <v>0.571</v>
       </c>
       <c r="E16" t="n">
-        <v>0.502</v>
+        <v>0.863</v>
       </c>
       <c r="F16" t="n">
-        <v>0.148</v>
+        <v>0.252</v>
       </c>
       <c r="G16" t="n">
-        <v>0.643</v>
+        <v>1.081</v>
       </c>
       <c r="H16" t="n">
-        <v>0.373</v>
+        <v>0.671</v>
       </c>
       <c r="I16" t="n">
-        <v>0.075</v>
+        <v>0.13</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="K16" t="n">
-        <v>0.37</v>
+        <v>0.711</v>
       </c>
       <c r="L16" t="n">
-        <v>0.401</v>
+        <v>0.728</v>
       </c>
       <c r="M16" t="n">
-        <v>0.403</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.077</v>
+        <v>0.179</v>
       </c>
       <c r="C17" t="n">
-        <v>0.064</v>
+        <v>0.154</v>
       </c>
       <c r="D17" t="n">
-        <v>0.218</v>
+        <v>0.436</v>
       </c>
       <c r="E17" t="n">
-        <v>0.623</v>
+        <v>1.045</v>
       </c>
       <c r="F17" t="n">
-        <v>0.113</v>
+        <v>0.189</v>
       </c>
       <c r="G17" t="n">
-        <v>0.379</v>
+        <v>0.64</v>
       </c>
       <c r="H17" t="n">
-        <v>0.265</v>
+        <v>0.526</v>
       </c>
       <c r="I17" t="n">
-        <v>0.029</v>
+        <v>0.074</v>
       </c>
       <c r="J17" t="n">
-        <v>0.475</v>
+        <v>0.888</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>0.385</v>
       </c>
       <c r="L17" t="n">
-        <v>0.341</v>
+        <v>0.677</v>
       </c>
       <c r="M17" t="n">
-        <v>0.24</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="C18" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.002</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.001</v>
-      </c>
       <c r="K18" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="L18" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="M18" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.53</v>
+        <v>0.888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.141</v>
       </c>
       <c r="G19" t="n">
-        <v>0.053</v>
+        <v>0.09</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.058</v>
+        <v>0.091</v>
       </c>
       <c r="C20" t="n">
-        <v>0.061</v>
+        <v>0.096</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.176</v>
+        <v>0.291</v>
       </c>
       <c r="F20" t="n">
-        <v>0.034</v>
+        <v>0.056</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H20" t="n">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.056</v>
+        <v>0.116</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06</v>
+        <v>0.121</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>0.155</v>
+        <v>0.264</v>
       </c>
       <c r="F21" t="n">
-        <v>0.026</v>
+        <v>0.043</v>
       </c>
       <c r="G21" t="n">
-        <v>0.026</v>
+        <v>0.045</v>
       </c>
       <c r="H21" t="n">
-        <v>0.202</v>
+        <v>0.425</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="J21" t="n">
-        <v>0.161</v>
+        <v>0.291</v>
       </c>
       <c r="K21" t="n">
-        <v>0.117</v>
+        <v>0.228</v>
       </c>
       <c r="L21" t="n">
-        <v>0.044</v>
+        <v>0.108</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.171</v>
+        <v>0.398</v>
       </c>
       <c r="C22" t="n">
-        <v>0.194</v>
+        <v>0.454</v>
       </c>
       <c r="D22" t="n">
-        <v>0.065</v>
+        <v>0.228</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0.315</v>
       </c>
       <c r="F22" t="n">
-        <v>0.025</v>
+        <v>0.048</v>
       </c>
       <c r="G22" t="n">
-        <v>0.025</v>
+        <v>0.057</v>
       </c>
       <c r="H22" t="n">
-        <v>0.394</v>
+        <v>0.66</v>
       </c>
       <c r="I22" t="n">
-        <v>0.137</v>
+        <v>0.223</v>
       </c>
       <c r="J22" t="n">
-        <v>0.609</v>
+        <v>1.049</v>
       </c>
       <c r="K22" t="n">
-        <v>0.183</v>
+        <v>0.325</v>
       </c>
       <c r="L22" t="n">
-        <v>0.352</v>
+        <v>0.654</v>
       </c>
       <c r="M22" t="n">
-        <v>0.222</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.064</v>
+        <v>0.111</v>
       </c>
       <c r="C23" t="n">
-        <v>0.058</v>
+        <v>0.127</v>
       </c>
       <c r="D23" t="n">
-        <v>0.056</v>
+        <v>0.134</v>
       </c>
       <c r="E23" t="n">
-        <v>0.056</v>
+        <v>0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="G23" t="n">
-        <v>0.127</v>
+        <v>0.239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.035</v>
+        <v>0.054</v>
       </c>
       <c r="I23" t="n">
-        <v>0.059</v>
+        <v>0.091</v>
       </c>
       <c r="J23" t="n">
-        <v>0.231</v>
+        <v>0.441</v>
       </c>
       <c r="K23" t="n">
-        <v>0.033</v>
+        <v>0.051</v>
       </c>
       <c r="L23" t="n">
-        <v>0.097</v>
+        <v>0.158</v>
       </c>
       <c r="M23" t="n">
-        <v>0.101</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.016</v>
+        <v>0.035</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04</v>
+        <v>0.089</v>
       </c>
       <c r="D24" t="n">
-        <v>0.027</v>
+        <v>0.064</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="F24" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="G24" t="n">
-        <v>0.164</v>
+        <v>0.278</v>
       </c>
       <c r="H24" t="n">
-        <v>0.033</v>
+        <v>0.051</v>
       </c>
       <c r="I24" t="n">
-        <v>0.054</v>
+        <v>0.081</v>
       </c>
       <c r="J24" t="n">
-        <v>0.191</v>
+        <v>0.322</v>
       </c>
       <c r="K24" t="n">
-        <v>0.032</v>
+        <v>0.048</v>
       </c>
       <c r="L24" t="n">
-        <v>0.083</v>
+        <v>0.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0.081</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.018</v>
+        <v>0.031</v>
       </c>
       <c r="C25" t="n">
-        <v>0.022</v>
+        <v>0.045</v>
       </c>
       <c r="D25" t="n">
-        <v>0.014</v>
+        <v>0.029</v>
       </c>
       <c r="E25" t="n">
-        <v>0.077</v>
+        <v>0.127</v>
       </c>
       <c r="F25" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.015</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.008</v>
-      </c>
       <c r="J25" t="n">
-        <v>0.044</v>
+        <v>0.058</v>
       </c>
       <c r="K25" t="n">
-        <v>0.038</v>
+        <v>0.054</v>
       </c>
       <c r="L25" t="n">
-        <v>0.047</v>
+        <v>0.094</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="C26" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E26" t="n">
-        <v>0.055</v>
+        <v>0.091</v>
       </c>
       <c r="F26" t="n">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="G26" t="n">
-        <v>0.097</v>
+        <v>0.164</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.027</v>
+        <v>0.064</v>
       </c>
       <c r="C27" t="n">
-        <v>0.045</v>
+        <v>0.139</v>
       </c>
       <c r="D27" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.033</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.022</v>
-      </c>
       <c r="J27" t="n">
-        <v>0.317</v>
+        <v>0.524</v>
       </c>
       <c r="K27" t="n">
-        <v>0.115</v>
+        <v>0.192</v>
       </c>
       <c r="L27" t="n">
-        <v>0.159</v>
+        <v>0.257</v>
       </c>
       <c r="M27" t="n">
-        <v>0.111</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="28">
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.053</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="G28" t="n">
-        <v>0.031</v>
+        <v>0.06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.001</v>
       </c>
-      <c r="C29" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
       <c r="E29" t="n">
-        <v>0.052</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="G29" t="n">
-        <v>0.048</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>0.002</v>
       </c>
       <c r="I29" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="J29" t="n">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="K29" t="n">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="M29" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.289</v>
+        <v>158.073</v>
       </c>
       <c r="C2" t="n">
-        <v>144.547</v>
+        <v>202.561</v>
       </c>
       <c r="D2" t="n">
-        <v>199.349</v>
+        <v>219.349</v>
       </c>
       <c r="E2" t="n">
-        <v>250.146</v>
+        <v>263.611</v>
       </c>
       <c r="F2" t="n">
-        <v>109.167</v>
+        <v>111.185</v>
       </c>
       <c r="G2" t="n">
-        <v>164.082</v>
+        <v>176.826</v>
       </c>
       <c r="H2" t="n">
-        <v>170.619</v>
+        <v>217.607</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4</v>
+        <v>222.177</v>
       </c>
       <c r="J2" t="n">
-        <v>248.485</v>
+        <v>265.208</v>
       </c>
       <c r="K2" t="n">
-        <v>186.89</v>
+        <v>228.197</v>
       </c>
       <c r="L2" t="n">
-        <v>174.557</v>
+        <v>224.486</v>
       </c>
       <c r="M2" t="n">
-        <v>230.517</v>
+        <v>299.262</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.538</v>
+        <v>78.113</v>
       </c>
       <c r="C3" t="n">
-        <v>76.78400000000001</v>
+        <v>82.932</v>
       </c>
       <c r="D3" t="n">
-        <v>108.727</v>
+        <v>118.555</v>
       </c>
       <c r="E3" t="n">
-        <v>220.451</v>
+        <v>222.981</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>86.02</v>
+        <v>88.104</v>
       </c>
       <c r="H3" t="n">
-        <v>136.496</v>
+        <v>154.766</v>
       </c>
       <c r="I3" t="n">
-        <v>135.516</v>
+        <v>143.15</v>
       </c>
       <c r="J3" t="n">
-        <v>108.492</v>
+        <v>124.705</v>
       </c>
       <c r="K3" t="n">
-        <v>138.241</v>
+        <v>161.81</v>
       </c>
       <c r="L3" t="n">
-        <v>127.499</v>
+        <v>132.332</v>
       </c>
       <c r="M3" t="n">
-        <v>78.70699999999999</v>
+        <v>95.678</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.016</v>
+        <v>41.88</v>
       </c>
       <c r="C4" t="n">
-        <v>27.104</v>
+        <v>29.478</v>
       </c>
       <c r="D4" t="n">
-        <v>49.399</v>
+        <v>53.194</v>
       </c>
       <c r="E4" t="n">
-        <v>200.76</v>
+        <v>203.011</v>
       </c>
       <c r="F4" t="n">
-        <v>74.05</v>
+        <v>74.467</v>
       </c>
       <c r="G4" t="n">
-        <v>65.21299999999999</v>
+        <v>67.461</v>
       </c>
       <c r="H4" t="n">
-        <v>9.351000000000001</v>
+        <v>10.24</v>
       </c>
       <c r="I4" t="n">
         <v>5.348</v>
       </c>
       <c r="J4" t="n">
-        <v>15.704</v>
+        <v>21.785</v>
       </c>
       <c r="K4" t="n">
-        <v>28.691</v>
+        <v>43.669</v>
       </c>
       <c r="L4" t="n">
-        <v>8.858000000000001</v>
+        <v>11.359</v>
       </c>
       <c r="M4" t="n">
-        <v>12.6</v>
+        <v>21.458</v>
       </c>
     </row>
     <row r="5">
@@ -7272,13 +7272,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.895</v>
+        <v>20.606</v>
       </c>
       <c r="C5" t="n">
-        <v>6.652</v>
+        <v>7.36</v>
       </c>
       <c r="D5" t="n">
-        <v>18.59</v>
+        <v>18.859</v>
       </c>
       <c r="E5" t="n">
         <v>196.449</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.335</v>
+        <v>83.803</v>
       </c>
       <c r="C6" t="n">
-        <v>33.024</v>
+        <v>51.545</v>
       </c>
       <c r="D6" t="n">
-        <v>51.429</v>
+        <v>76.074</v>
       </c>
       <c r="E6" t="n">
-        <v>181.879</v>
+        <v>188.479</v>
       </c>
       <c r="F6" t="n">
-        <v>89.614</v>
+        <v>92.52800000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>57.795</v>
+        <v>63.225</v>
       </c>
       <c r="H6" t="n">
-        <v>4.262</v>
+        <v>18.695</v>
       </c>
       <c r="I6" t="n">
-        <v>22.08</v>
+        <v>39.965</v>
       </c>
       <c r="J6" t="n">
-        <v>72.655</v>
+        <v>113.373</v>
       </c>
       <c r="K6" t="n">
-        <v>100.951</v>
+        <v>134.824</v>
       </c>
       <c r="L6" t="n">
-        <v>53.361</v>
+        <v>92.22499999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>64.032</v>
+        <v>107.489</v>
       </c>
     </row>
     <row r="7">
@@ -7356,22 +7356,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.645</v>
+        <v>168.635</v>
       </c>
       <c r="C7" t="n">
-        <v>116.566</v>
+        <v>193.065</v>
       </c>
       <c r="D7" t="n">
-        <v>83.959</v>
+        <v>138.086</v>
       </c>
       <c r="E7" t="n">
-        <v>107.365</v>
+        <v>129.949</v>
       </c>
       <c r="F7" t="n">
-        <v>171.397</v>
+        <v>182.741</v>
       </c>
       <c r="G7" t="n">
-        <v>68.69799999999999</v>
+        <v>92.735</v>
       </c>
       <c r="H7" t="n">
         <v>448.705</v>
@@ -7389,7 +7389,7 @@
         <v>345.876</v>
       </c>
       <c r="M7" t="n">
-        <v>409.27</v>
+        <v>417.21</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.999000000000001</v>
+        <v>9.154999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7411,10 +7411,10 @@
         <v>75.474</v>
       </c>
       <c r="F8" t="n">
-        <v>141.702</v>
+        <v>142.34</v>
       </c>
       <c r="G8" t="n">
-        <v>26.707</v>
+        <v>27.36</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -7442,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.174</v>
+        <v>44.97</v>
       </c>
       <c r="C9" t="n">
-        <v>0.329</v>
+        <v>25.829</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285</v>
+        <v>24.985</v>
       </c>
       <c r="E9" t="n">
-        <v>49.127</v>
+        <v>59.359</v>
       </c>
       <c r="F9" t="n">
-        <v>98.14100000000001</v>
+        <v>104.804</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37</v>
+        <v>20.287</v>
       </c>
       <c r="H9" t="n">
-        <v>9.68</v>
+        <v>20.83</v>
       </c>
       <c r="I9" t="n">
-        <v>29.345</v>
+        <v>89.836</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625</v>
+        <v>42.446</v>
       </c>
       <c r="K9" t="n">
-        <v>133.562</v>
+        <v>162.634</v>
       </c>
       <c r="L9" t="n">
-        <v>21.648</v>
+        <v>77.07599999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>5.757</v>
+        <v>21.573</v>
       </c>
     </row>
     <row r="10">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.093</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -7494,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>38.165</v>
+        <v>42.028</v>
       </c>
       <c r="F10" t="n">
-        <v>74.45</v>
+        <v>75.90600000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>4.057</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>2.029</v>
       </c>
       <c r="I10" t="n">
         <v>11.198</v>
       </c>
       <c r="J10" t="n">
-        <v>7.096</v>
+        <v>7.128</v>
       </c>
       <c r="K10" t="n">
-        <v>5.148</v>
+        <v>29.861</v>
       </c>
       <c r="L10" t="n">
-        <v>2.843</v>
+        <v>3.333</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7537,19 +7537,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36.519</v>
+        <v>37.906</v>
       </c>
       <c r="F11" t="n">
-        <v>63.697</v>
+        <v>64.315</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>1.867</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="I11" t="n">
-        <v>2.891</v>
+        <v>2.904</v>
       </c>
       <c r="J11" t="n">
         <v>3.736</v>
@@ -7580,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.796</v>
+        <v>22.804</v>
       </c>
       <c r="F12" t="n">
-        <v>48.502</v>
+        <v>49.017</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>13.059</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4.394</v>
       </c>
       <c r="E13" t="n">
-        <v>8.673999999999999</v>
+        <v>16.173</v>
       </c>
       <c r="F13" t="n">
-        <v>34.177</v>
+        <v>39.507</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.201</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>7.612</v>
       </c>
       <c r="I13" t="n">
-        <v>3.807</v>
+        <v>15.358</v>
       </c>
       <c r="J13" t="n">
-        <v>13.525</v>
+        <v>25.682</v>
       </c>
       <c r="K13" t="n">
-        <v>16.795</v>
+        <v>43.799</v>
       </c>
       <c r="L13" t="n">
-        <v>7.407</v>
+        <v>23.107</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7675,13 +7675,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.028</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4.396</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4.847</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198.422</v>
+        <v>219.074</v>
       </c>
       <c r="C15" t="n">
-        <v>182.077</v>
+        <v>230.359</v>
       </c>
       <c r="D15" t="n">
-        <v>205.629</v>
+        <v>240.287</v>
       </c>
       <c r="E15" t="n">
-        <v>234.016</v>
+        <v>243.71</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>242.281</v>
+        <v>249.007</v>
       </c>
       <c r="H15" t="n">
         <v>150.226</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>168.641</v>
+        <v>207.203</v>
       </c>
       <c r="K15" t="n">
-        <v>210.788</v>
+        <v>211.01</v>
       </c>
       <c r="L15" t="n">
-        <v>240.008</v>
+        <v>242.19</v>
       </c>
       <c r="M15" t="n">
-        <v>246.087</v>
+        <v>249.169</v>
       </c>
     </row>
     <row r="16">
@@ -7741,19 +7741,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.941</v>
+        <v>321.082</v>
       </c>
       <c r="C16" t="n">
-        <v>285.944</v>
+        <v>353.164</v>
       </c>
       <c r="D16" t="n">
-        <v>337.826</v>
+        <v>368.998</v>
       </c>
       <c r="E16" t="n">
-        <v>380.599</v>
+        <v>392.77</v>
       </c>
       <c r="F16" t="n">
-        <v>206.405</v>
+        <v>209.35</v>
       </c>
       <c r="G16" t="n">
         <v>437.584</v>
@@ -7768,13 +7768,13 @@
         <v>429.552</v>
       </c>
       <c r="K16" t="n">
-        <v>376.299</v>
+        <v>377.352</v>
       </c>
       <c r="L16" t="n">
-        <v>369.467</v>
+        <v>369.762</v>
       </c>
       <c r="M16" t="n">
-        <v>383.219</v>
+        <v>383.425</v>
       </c>
     </row>
     <row r="17">
@@ -7784,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>190.162</v>
+        <v>218.493</v>
       </c>
       <c r="C17" t="n">
-        <v>176.974</v>
+        <v>203.199</v>
       </c>
       <c r="D17" t="n">
-        <v>287.615</v>
+        <v>311.59</v>
       </c>
       <c r="E17" t="n">
-        <v>418.938</v>
+        <v>420.37</v>
       </c>
       <c r="F17" t="n">
         <v>178.899</v>
       </c>
       <c r="G17" t="n">
-        <v>328.324</v>
+        <v>330.48</v>
       </c>
       <c r="H17" t="n">
-        <v>334.933</v>
+        <v>335.315</v>
       </c>
       <c r="I17" t="n">
-        <v>122.944</v>
+        <v>140.185</v>
       </c>
       <c r="J17" t="n">
         <v>426.081</v>
       </c>
       <c r="K17" t="n">
-        <v>280.581</v>
+        <v>282.23</v>
       </c>
       <c r="L17" t="n">
-        <v>364.881</v>
+        <v>376.867</v>
       </c>
       <c r="M17" t="n">
-        <v>329.791</v>
+        <v>346.912</v>
       </c>
     </row>
     <row r="18">
@@ -7827,22 +7827,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.284</v>
+        <v>49.49</v>
       </c>
       <c r="C18" t="n">
-        <v>29.031</v>
+        <v>30.17</v>
       </c>
       <c r="D18" t="n">
-        <v>47.026</v>
+        <v>48.345</v>
       </c>
       <c r="E18" t="n">
-        <v>398.401</v>
+        <v>398.884</v>
       </c>
       <c r="F18" t="n">
-        <v>162.221</v>
+        <v>162.699</v>
       </c>
       <c r="G18" t="n">
-        <v>140.396</v>
+        <v>141.915</v>
       </c>
       <c r="H18" t="n">
         <v>32.366</v>
@@ -7870,22 +7870,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.853</v>
+        <v>26.515</v>
       </c>
       <c r="C19" t="n">
-        <v>10.437</v>
+        <v>11.697</v>
       </c>
       <c r="D19" t="n">
-        <v>29.286</v>
+        <v>29.897</v>
       </c>
       <c r="E19" t="n">
-        <v>385.916</v>
+        <v>386.918</v>
       </c>
       <c r="F19" t="n">
         <v>154.628</v>
       </c>
       <c r="G19" t="n">
-        <v>122.902</v>
+        <v>124.163</v>
       </c>
       <c r="H19" t="n">
         <v>3.76</v>
@@ -7940,7 +7940,7 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>70.63</v>
+        <v>79.911</v>
       </c>
       <c r="L20" t="n">
         <v>7.176</v>
@@ -7956,28 +7956,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151.843</v>
+        <v>158.906</v>
       </c>
       <c r="C21" t="n">
-        <v>155.286</v>
+        <v>161.693</v>
       </c>
       <c r="D21" t="n">
-        <v>44.554</v>
+        <v>53.392</v>
       </c>
       <c r="E21" t="n">
-        <v>211.495</v>
+        <v>214.245</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84699999999999</v>
+        <v>84.849</v>
       </c>
       <c r="G21" t="n">
-        <v>86.437</v>
+        <v>87.849</v>
       </c>
       <c r="H21" t="n">
-        <v>315.454</v>
+        <v>315.967</v>
       </c>
       <c r="I21" t="n">
-        <v>67.90000000000001</v>
+        <v>84.494</v>
       </c>
       <c r="J21" t="n">
         <v>312.499</v>
@@ -7986,7 +7986,7 @@
         <v>218.524</v>
       </c>
       <c r="L21" t="n">
-        <v>181.643</v>
+        <v>181.771</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,22 +7999,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285.401</v>
+        <v>321.763</v>
       </c>
       <c r="C22" t="n">
-        <v>308.21</v>
+        <v>341.681</v>
       </c>
       <c r="D22" t="n">
-        <v>213.229</v>
+        <v>296.783</v>
       </c>
       <c r="E22" t="n">
-        <v>235.775</v>
+        <v>259.053</v>
       </c>
       <c r="F22" t="n">
-        <v>93.426</v>
+        <v>104.325</v>
       </c>
       <c r="G22" t="n">
-        <v>102.116</v>
+        <v>126.244</v>
       </c>
       <c r="H22" t="n">
         <v>351.305</v>
@@ -8029,10 +8029,10 @@
         <v>245.673</v>
       </c>
       <c r="L22" t="n">
-        <v>351.869</v>
+        <v>356.592</v>
       </c>
       <c r="M22" t="n">
-        <v>345.778</v>
+        <v>372.582</v>
       </c>
     </row>
     <row r="23">
@@ -8045,19 +8045,19 @@
         <v>68.547</v>
       </c>
       <c r="C23" t="n">
-        <v>30.674</v>
+        <v>31.235</v>
       </c>
       <c r="D23" t="n">
-        <v>31.352</v>
+        <v>33.844</v>
       </c>
       <c r="E23" t="n">
-        <v>24.121</v>
+        <v>25.379</v>
       </c>
       <c r="F23" t="n">
-        <v>9.519</v>
+        <v>9.702</v>
       </c>
       <c r="G23" t="n">
-        <v>119.489</v>
+        <v>129.662</v>
       </c>
       <c r="H23" t="n">
         <v>21.522</v>
@@ -8085,22 +8085,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.531</v>
+        <v>16.163</v>
       </c>
       <c r="C24" t="n">
-        <v>25.396</v>
+        <v>26.155</v>
       </c>
       <c r="D24" t="n">
-        <v>21.851</v>
+        <v>22.878</v>
       </c>
       <c r="E24" t="n">
-        <v>25.831</v>
+        <v>26.181</v>
       </c>
       <c r="F24" t="n">
         <v>10.472</v>
       </c>
       <c r="G24" t="n">
-        <v>125.227</v>
+        <v>126.35</v>
       </c>
       <c r="H24" t="n">
         <v>20.425</v>
@@ -8128,13 +8128,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.563</v>
+        <v>13.675</v>
       </c>
       <c r="C25" t="n">
-        <v>17.647</v>
+        <v>17.848</v>
       </c>
       <c r="D25" t="n">
-        <v>14.358</v>
+        <v>14.61</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
@@ -8143,7 +8143,7 @@
         <v>12.027</v>
       </c>
       <c r="G25" t="n">
-        <v>86.818</v>
+        <v>93.524</v>
       </c>
       <c r="H25" t="n">
         <v>19.045</v>
@@ -8174,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.235</v>
+        <v>11.272</v>
       </c>
       <c r="D26" t="n">
-        <v>4.172</v>
+        <v>4.246</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8186,13 +8186,13 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>96.301</v>
+        <v>96.486</v>
       </c>
       <c r="H26" t="n">
         <v>1.428</v>
       </c>
       <c r="I26" t="n">
-        <v>1.551</v>
+        <v>1.559</v>
       </c>
       <c r="J26" t="n">
         <v>0.967</v>
@@ -8214,22 +8214,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.634</v>
+        <v>23.043</v>
       </c>
       <c r="C27" t="n">
-        <v>31.771</v>
+        <v>39.001</v>
       </c>
       <c r="D27" t="n">
-        <v>27.277</v>
+        <v>33.84</v>
       </c>
       <c r="E27" t="n">
-        <v>24.271</v>
+        <v>25.578</v>
       </c>
       <c r="F27" t="n">
-        <v>12.223</v>
+        <v>12.639</v>
       </c>
       <c r="G27" t="n">
-        <v>109.659</v>
+        <v>123.905</v>
       </c>
       <c r="H27" t="n">
         <v>33.252</v>
@@ -8272,7 +8272,7 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>61.175</v>
+        <v>65.71599999999999</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -8300,22 +8300,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.367</v>
+        <v>4.509</v>
       </c>
       <c r="C29" t="n">
-        <v>5.664</v>
+        <v>5.785</v>
       </c>
       <c r="D29" t="n">
-        <v>3.613</v>
+        <v>3.696</v>
       </c>
       <c r="E29" t="n">
-        <v>22.205</v>
+        <v>22.439</v>
       </c>
       <c r="F29" t="n">
-        <v>10.799</v>
+        <v>10.923</v>
       </c>
       <c r="G29" t="n">
-        <v>71.66200000000001</v>
+        <v>74.367</v>
       </c>
       <c r="H29" t="n">
         <v>5.992</v>
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9401425521e-05</v>
+        <v>2.498707332900001e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0893835209e-05</v>
+        <v>4.103095872100001e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9740023801e-05</v>
+        <v>4.811398380099999e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2573021316e-05</v>
+        <v>6.949075932099998e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1917433889e-05</v>
+        <v>1.2362104225e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6922902724e-05</v>
+        <v>3.1267434276e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9110843161e-05</v>
+        <v>4.7352806449e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857296000000001e-05</v>
+        <v>4.936261932899999e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1744795225e-05</v>
+        <v>7.033528326399999e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.49278721e-05</v>
+        <v>5.207387080900001e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0470146249e-05</v>
+        <v>5.0393964196e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3138087289e-05</v>
+        <v>8.955774464400001e-05</v>
       </c>
     </row>
     <row r="3">
@@ -8510,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.555913443999999e-06</v>
+        <v>6.101640769e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.895782656e-06</v>
+        <v>6.877716624000001e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1821560529e-05</v>
+        <v>1.4055288025e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8598643401e-05</v>
+        <v>4.9720526361e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3994404e-06</v>
+        <v>7.762314816e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8631158016e-05</v>
+        <v>2.3952514756e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8364586256e-05</v>
+        <v>2.04919225e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1770514064e-05</v>
+        <v>1.5551337025e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9110574081e-05</v>
+        <v>2.61824761e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6255995001e-05</v>
+        <v>1.7511758224e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>6.194791848999999e-06</v>
+        <v>9.154279684e-06</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.445216256e-06</v>
+        <v>1.7539344e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>7.346268159999999e-07</v>
+        <v>8.68952484e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.440261201e-06</v>
+        <v>2.829601636000001e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.030457759999999e-05</v>
+        <v>4.1213466121e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.483402499999999e-06</v>
+        <v>5.545334089e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.252735369e-06</v>
+        <v>4.550986520999999e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.744120100000002e-08</v>
+        <v>1.048576e-07</v>
       </c>
       <c r="I4" t="n">
         <v>2.860110399999999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.46615616e-07</v>
+        <v>4.745862249999999e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.231734809999998e-07</v>
+        <v>1.906981561e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>7.846416400000002e-08</v>
+        <v>1.29026881e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5876e-07</v>
+        <v>4.604457639999999e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8596,13 +8596,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95811025e-07</v>
+        <v>4.246072360000001e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4249104e-08</v>
+        <v>5.416960000000001e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.455880999999999e-07</v>
+        <v>3.55661881e-07</v>
       </c>
       <c r="E5" t="n">
         <v>3.8592209601e-05</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011322225000001e-06</v>
+        <v>7.022942809000001e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.090584576e-06</v>
+        <v>2.656887025e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644942041e-06</v>
+        <v>5.787253476000001e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3079970641e-05</v>
+        <v>3.5524333441e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.030668996000001e-06</v>
+        <v>8.561430784000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.340262025e-06</v>
+        <v>3.997400625e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816464399999999e-08</v>
+        <v>3.49503025e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875263999999999e-07</v>
+        <v>1.597201225e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.278749024999999e-06</v>
+        <v>1.2853437129e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0191104401e-05</v>
+        <v>1.8177510976e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.847396321e-06</v>
+        <v>8.505450624999998e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>4.100097023999998e-06</v>
+        <v>1.1553885121e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8680,22 +8680,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.080772008333333e-06</v>
+        <v>9.47925440833333e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>4.529210785333334e-06</v>
+        <v>1.2424698075e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349704560333334e-06</v>
+        <v>6.355914465333335e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>3.842414408333332e-06</v>
+        <v>5.628914200333334e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792310536333332e-06</v>
+        <v>1.113142436033334e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.573138401333333e-06</v>
+        <v>2.866593408333333e-06</v>
       </c>
       <c r="H7" t="n">
         <v>6.711205900833333e-05</v>
@@ -8713,7 +8713,7 @@
         <v>3.987673579199999e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.583397763333333e-05</v>
+        <v>5.802139469999999e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.098200100000001e-08</v>
+        <v>8.3814025e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8735,10 +8735,10 @@
         <v>5.696324676e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0079456804e-05</v>
+        <v>2.02606756e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.132638490000001e-07</v>
+        <v>7.485696e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.356634253333333e-07</v>
+        <v>6.741003e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>3.608033333333334e-11</v>
+        <v>2.223790803333334e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>6.120408333333333e-09</v>
+        <v>2.080834083333333e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>8.044873763333334e-07</v>
+        <v>1.174496960333333e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210551960333334e-06</v>
+        <v>3.661292805333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>5.100563333333332e-08</v>
+        <v>1.371874563333333e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.123413333333333e-08</v>
+        <v>1.446296333333333e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>2.870430083333333e-07</v>
+        <v>2.690168965333333e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.283802083333333e-07</v>
+        <v>6.005543053333333e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.946269281333335e-06</v>
+        <v>8.816605985333331e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56211968e-07</v>
+        <v>1.980236591999999e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1047683e-08</v>
+        <v>1.55131443e-07</v>
       </c>
     </row>
     <row r="10">
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3.982163333333333e-10</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.855224083333332e-07</v>
+        <v>5.887842613333331e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847600833333333e-06</v>
+        <v>1.920573612e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.136333333333333e-10</v>
+        <v>5.486416333333336e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>7.301333333333332e-10</v>
+        <v>1.372280333333333e-09</v>
       </c>
       <c r="I10" t="n">
         <v>4.179840133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.678440533333333e-08</v>
+        <v>1.6936128e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>8.833968e-09</v>
+        <v>2.972264403333334e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>2.694216333333333e-09</v>
+        <v>3.702963e-09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8861,19 +8861,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.445457869999999e-07</v>
+        <v>4.789549453333333e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352435936333333e-06</v>
+        <v>1.378806408333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93548e-10</v>
+        <v>1.161896333333333e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5.125333333333334e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>2.785960333333333e-09</v>
+        <v>2.811072e-09</v>
       </c>
       <c r="J11" t="n">
         <v>4.652565333333334e-09</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.732192053333333e-07</v>
+        <v>1.733408053333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.841480013333335e-07</v>
+        <v>8.008887630000001e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8938,37 +8938,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5.684582699999999e-08</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>6.435745333333334e-09</v>
       </c>
       <c r="E13" t="n">
-        <v>2.507942533333333e-08</v>
+        <v>8.718864299999999e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>3.893557763333333e-07</v>
+        <v>5.20267683e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4.808003333333333e-10</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.931418133333333e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>4.831083e-09</v>
+        <v>7.862272133333333e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>6.097520833333334e-08</v>
+        <v>2.198550413333333e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>9.402400833333334e-08</v>
+        <v>6.394508003333333e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8287883e-08</v>
+        <v>1.779778163333333e-07</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -8999,13 +8999,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.408261333333332e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>6.441605333333333e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>7.831136333333335e-09</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9371290084e-05</v>
+        <v>4.7993417476e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3152033929e-05</v>
+        <v>5.3065268881e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.228328564099999e-05</v>
+        <v>5.7737842369e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4763488256e-05</v>
+        <v>5.93945641e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8700082961e-05</v>
+        <v>6.200448604900001e-05</v>
       </c>
       <c r="H15" t="n">
         <v>2.2567851076e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.843978688099999e-05</v>
+        <v>4.2933083209e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4431580944e-05</v>
+        <v>4.45252201e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7603840064e-05</v>
+        <v>5.86559961e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0558811569e-05</v>
+        <v>6.2085190561e-05</v>
       </c>
     </row>
     <row r="16">
@@ -9065,19 +9065,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6874163827e-05</v>
+        <v>3.436455024133332e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>2.725465704533334e-05</v>
+        <v>4.157493696533333e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>3.804213542533334e-05</v>
+        <v>4.538650800133333e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.828519960033332e-05</v>
+        <v>5.142275763333333e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.420100800833334e-05</v>
+        <v>1.460914083333333e-05</v>
       </c>
       <c r="G16" t="n">
         <v>6.382658568533334e-05</v>
@@ -9092,13 +9092,13 @@
         <v>6.150497356800002e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7200312467e-05</v>
+        <v>4.746484396799999e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.550195469633334e-05</v>
+        <v>4.557464554799999e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.895226732033333e-05</v>
+        <v>4.900491020833333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -9108,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.205386208133333e-05</v>
+        <v>1.5913063683e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>1.043993222533333e-05</v>
+        <v>1.3763277867e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>2.757412940833333e-05</v>
+        <v>3.236277603333333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.850301594799999e-05</v>
+        <v>5.890364563333334e-05</v>
       </c>
       <c r="F17" t="n">
         <v>1.0668284067e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.593221632533333e-05</v>
+        <v>3.64056768e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.739337149633333e-05</v>
+        <v>3.747871640833333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>5.038409045333333e-06</v>
+        <v>6.550611408333334e-06</v>
       </c>
       <c r="J17" t="n">
         <v>6.051500618700001e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6241899187e-05</v>
+        <v>2.655125763333334e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4.437938138699999e-05</v>
+        <v>4.734291189633333e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.625403456033334e-05</v>
+        <v>4.011597858133333e-05</v>
       </c>
     </row>
     <row r="18">
@@ -9151,22 +9151,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.09637552e-07</v>
+        <v>8.164200333333334e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>2.80932987e-07</v>
+        <v>3.034096333333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.371482253333335e-07</v>
+        <v>7.790796749999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.290778560033334e-05</v>
+        <v>5.303614848533333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.771884280333334e-06</v>
+        <v>8.823654867000001e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.570345605333333e-06</v>
+        <v>6.713289074999999e-06</v>
       </c>
       <c r="H18" t="n">
         <v>3.491859853333333e-07</v>
@@ -9194,22 +9194,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.89655203e-07</v>
+        <v>2.343484083333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6310323e-08</v>
+        <v>4.5606603e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85889932e-07</v>
+        <v>2.979435363333333e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.964371968533333e-05</v>
+        <v>4.990184624133333e-05</v>
       </c>
       <c r="F19" t="n">
         <v>7.969939461333333e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.034967201333333e-06</v>
+        <v>5.138816856333333e-06</v>
       </c>
       <c r="H19" t="n">
         <v>4.712533333333333e-09</v>
@@ -9264,7 +9264,7 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>1.662865633333333e-06</v>
+        <v>2.128589307e-06</v>
       </c>
       <c r="L20" t="n">
         <v>1.7164992e-08</v>
@@ -9280,28 +9280,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.685432216333331e-06</v>
+        <v>8.417038945333335e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.037913932000002e-06</v>
+        <v>8.714875416333335e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>6.616863053333334e-07</v>
+        <v>9.502352213333334e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491004500833333e-05</v>
+        <v>1.5300306675e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399671136333333e-06</v>
+        <v>2.399784267000001e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.490451656333333e-06</v>
+        <v>2.572482267000001e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317040870533334e-05</v>
+        <v>3.327838169633334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>1.536803333333333e-06</v>
+        <v>2.379745345333333e-06</v>
       </c>
       <c r="J21" t="n">
         <v>3.255187500033334e-05</v>
@@ -9310,7 +9310,7 @@
         <v>1.591757952533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.099805981633333e-05</v>
+        <v>1.101356548033333e-05</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,22 +9323,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.715124360033333e-05</v>
+        <v>3.451047605633332e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.166446803333333e-05</v>
+        <v>3.891530192033332e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.515553548033333e-05</v>
+        <v>2.936004969633334e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.852995020833333e-05</v>
+        <v>2.2369485603e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.909472492e-06</v>
+        <v>3.627901875e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>3.475892485333333e-06</v>
+        <v>5.312515845333332e-06</v>
       </c>
       <c r="H22" t="n">
         <v>4.113840100833334e-05</v>
@@ -9353,10 +9353,10 @@
         <v>2.0118407643e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.127059772033335e-05</v>
+        <v>4.238595148799999e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.985414176133334e-05</v>
+        <v>4.627244890799999e-05</v>
       </c>
     </row>
     <row r="23">
@@ -9369,19 +9369,19 @@
         <v>4.698691208999999e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>9.408942760000001e-06</v>
+        <v>9.756252249999999e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82947904e-06</v>
+        <v>1.145416336e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>5.81822641e-06</v>
+        <v>6.440936410000001e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.0611361e-07</v>
+        <v>9.412880400000001e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4277621121e-05</v>
+        <v>1.6812234244e-05</v>
       </c>
       <c r="H23" t="n">
         <v>4.63196484e-06</v>
@@ -9409,22 +9409,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.41211961e-06</v>
+        <v>2.61242569e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>6.449568160000001e-06</v>
+        <v>6.840840250000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>4.774662009999999e-06</v>
+        <v>5.23402884e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.67240561e-06</v>
+        <v>6.85444761e-06</v>
       </c>
       <c r="F24" t="n">
         <v>1.09662784e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5681801529e-05</v>
+        <v>1.59643225e-05</v>
       </c>
       <c r="H24" t="n">
         <v>4.171806250000001e-06</v>
@@ -9452,13 +9452,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.83954969e-06</v>
+        <v>1.87005625e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.11416609e-06</v>
+        <v>3.18551104e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.06152164e-06</v>
+        <v>2.134521e-06</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
@@ -9467,7 +9467,7 @@
         <v>1.44648729e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>7.537365123999998e-06</v>
+        <v>8.746738576e-06</v>
       </c>
       <c r="H25" t="n">
         <v>3.627120250000001e-06</v>
@@ -9498,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26225225e-06</v>
+        <v>1.27057984e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7405584e-07</v>
+        <v>1.802851600000001e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9510,13 +9510,13 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.273882601e-06</v>
+        <v>9.309548195999999e-06</v>
       </c>
       <c r="H26" t="n">
         <v>2.039184e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>2.405601e-08</v>
+        <v>2.430480999999999e-08</v>
       </c>
       <c r="J26" t="n">
         <v>9.35089e-09</v>
@@ -9538,22 +9538,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.680299560000001e-06</v>
+        <v>5.309798490000001e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.009396441e-05</v>
+        <v>1.521078001e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>7.440347290000001e-06</v>
+        <v>1.1451456e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>5.890814410000001e-06</v>
+        <v>6.542340840000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49401729e-06</v>
+        <v>1.59744321e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2025096281e-05</v>
+        <v>1.5352449025e-05</v>
       </c>
       <c r="H27" t="n">
         <v>1.105695504e-05</v>
@@ -9596,7 +9596,7 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>3.742380625e-06</v>
+        <v>4.318592655999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -9624,22 +9624,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9070689e-07</v>
+        <v>2.0331081e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2080896e-07</v>
+        <v>3.3466225e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3053769e-07</v>
+        <v>1.3660416e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.930620249999999e-06</v>
+        <v>5.03508721e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16618401e-06</v>
+        <v>1.19311929e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.135442244e-06</v>
+        <v>5.530450689e-06</v>
       </c>
       <c r="H29" t="n">
         <v>3.5904064e-07</v>
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.289</v>
+        <v>158.073</v>
       </c>
       <c r="C2" t="n">
-        <v>144.547</v>
+        <v>202.561</v>
       </c>
       <c r="D2" t="n">
-        <v>199.349</v>
+        <v>219.349</v>
       </c>
       <c r="E2" t="n">
-        <v>250.146</v>
+        <v>263.611</v>
       </c>
       <c r="F2" t="n">
-        <v>109.167</v>
+        <v>111.17</v>
       </c>
       <c r="G2" t="n">
-        <v>164.082</v>
+        <v>176.826</v>
       </c>
       <c r="H2" t="n">
-        <v>170.619</v>
+        <v>217.607</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4</v>
+        <v>222.177</v>
       </c>
       <c r="J2" t="n">
-        <v>248.469</v>
+        <v>265.208</v>
       </c>
       <c r="K2" t="n">
-        <v>186.89</v>
+        <v>228.197</v>
       </c>
       <c r="L2" t="n">
-        <v>174.557</v>
+        <v>224.486</v>
       </c>
       <c r="M2" t="n">
-        <v>230.517</v>
+        <v>299.262</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.538</v>
+        <v>77.851</v>
       </c>
       <c r="C3" t="n">
-        <v>76.78400000000001</v>
+        <v>82.753</v>
       </c>
       <c r="D3" t="n">
-        <v>108.727</v>
+        <v>118.555</v>
       </c>
       <c r="E3" t="n">
-        <v>220.451</v>
+        <v>222.981</v>
       </c>
       <c r="F3" t="n">
-        <v>76.491</v>
+        <v>75.026</v>
       </c>
       <c r="G3" t="n">
-        <v>86.02</v>
+        <v>88.104</v>
       </c>
       <c r="H3" t="n">
-        <v>136.496</v>
+        <v>139.997</v>
       </c>
       <c r="I3" t="n">
-        <v>135.516</v>
+        <v>132.312</v>
       </c>
       <c r="J3" t="n">
-        <v>108.463</v>
+        <v>119.451</v>
       </c>
       <c r="K3" t="n">
-        <v>138.241</v>
+        <v>160.115</v>
       </c>
       <c r="L3" t="n">
-        <v>127.499</v>
+        <v>125.661</v>
       </c>
       <c r="M3" t="n">
-        <v>78.70699999999999</v>
+        <v>80.411</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.016</v>
+        <v>41.88</v>
       </c>
       <c r="C4" t="n">
-        <v>27.104</v>
+        <v>29.478</v>
       </c>
       <c r="D4" t="n">
-        <v>49.399</v>
+        <v>53.194</v>
       </c>
       <c r="E4" t="n">
-        <v>200.76</v>
+        <v>203.011</v>
       </c>
       <c r="F4" t="n">
-        <v>74.05</v>
+        <v>74.467</v>
       </c>
       <c r="G4" t="n">
-        <v>65.21299999999999</v>
+        <v>67.461</v>
       </c>
       <c r="H4" t="n">
-        <v>9.351000000000001</v>
+        <v>7.607</v>
       </c>
       <c r="I4" t="n">
-        <v>3.563</v>
+        <v>2.039</v>
       </c>
       <c r="J4" t="n">
-        <v>15.704</v>
+        <v>21.629</v>
       </c>
       <c r="K4" t="n">
-        <v>28.691</v>
+        <v>43.669</v>
       </c>
       <c r="L4" t="n">
-        <v>8.858000000000001</v>
+        <v>11.329</v>
       </c>
       <c r="M4" t="n">
-        <v>12.6</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.895</v>
+        <v>20.606</v>
       </c>
       <c r="C5" t="n">
-        <v>6.652</v>
+        <v>7.36</v>
       </c>
       <c r="D5" t="n">
-        <v>18.554</v>
+        <v>18.859</v>
       </c>
       <c r="E5" t="n">
-        <v>195.073</v>
+        <v>195.469</v>
       </c>
       <c r="F5" t="n">
-        <v>93.86199999999999</v>
+        <v>93.045</v>
       </c>
       <c r="G5" t="n">
-        <v>76.872</v>
+        <v>75.919</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.335</v>
+        <v>83.803</v>
       </c>
       <c r="C6" t="n">
-        <v>33.024</v>
+        <v>51.545</v>
       </c>
       <c r="D6" t="n">
-        <v>51.429</v>
+        <v>76.074</v>
       </c>
       <c r="E6" t="n">
-        <v>181.879</v>
+        <v>188.479</v>
       </c>
       <c r="F6" t="n">
-        <v>89.614</v>
+        <v>92.52800000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>57.795</v>
+        <v>63.225</v>
       </c>
       <c r="H6" t="n">
-        <v>4.262</v>
+        <v>18.695</v>
       </c>
       <c r="I6" t="n">
-        <v>22.08</v>
+        <v>39.965</v>
       </c>
       <c r="J6" t="n">
-        <v>72.655</v>
+        <v>113.373</v>
       </c>
       <c r="K6" t="n">
-        <v>100.951</v>
+        <v>134.824</v>
       </c>
       <c r="L6" t="n">
-        <v>53.361</v>
+        <v>92.22499999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>64.032</v>
+        <v>107.489</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.645</v>
+        <v>168.635</v>
       </c>
       <c r="C7" t="n">
-        <v>116.566</v>
+        <v>193.065</v>
       </c>
       <c r="D7" t="n">
-        <v>83.959</v>
+        <v>138.086</v>
       </c>
       <c r="E7" t="n">
-        <v>107.365</v>
+        <v>129.949</v>
       </c>
       <c r="F7" t="n">
-        <v>171.397</v>
+        <v>182.741</v>
       </c>
       <c r="G7" t="n">
-        <v>68.69799999999999</v>
+        <v>92.735</v>
       </c>
       <c r="H7" t="n">
-        <v>444.155</v>
+        <v>442.342</v>
       </c>
       <c r="I7" t="n">
-        <v>322.767</v>
+        <v>320.36</v>
       </c>
       <c r="J7" t="n">
-        <v>374.397</v>
+        <v>374.811</v>
       </c>
       <c r="K7" t="n">
-        <v>365.191</v>
+        <v>362.219</v>
       </c>
       <c r="L7" t="n">
-        <v>341.074</v>
+        <v>330.656</v>
       </c>
       <c r="M7" t="n">
-        <v>408.096</v>
+        <v>417.21</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.999000000000001</v>
+        <v>9.052</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.462</v>
+        <v>75.123</v>
       </c>
       <c r="F8" t="n">
-        <v>141.702</v>
+        <v>142.34</v>
       </c>
       <c r="G8" t="n">
-        <v>26.707</v>
+        <v>27.36</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.796</v>
+        <v>1.574</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>62.415</v>
+        <v>45.21</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10090,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.174</v>
+        <v>44.97</v>
       </c>
       <c r="C9" t="n">
-        <v>0.329</v>
+        <v>25.829</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285</v>
+        <v>24.985</v>
       </c>
       <c r="E9" t="n">
-        <v>49.127</v>
+        <v>59.359</v>
       </c>
       <c r="F9" t="n">
-        <v>98.14100000000001</v>
+        <v>104.804</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37</v>
+        <v>20.287</v>
       </c>
       <c r="H9" t="n">
-        <v>9.68</v>
+        <v>20.83</v>
       </c>
       <c r="I9" t="n">
-        <v>29.345</v>
+        <v>89.836</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625</v>
+        <v>42.446</v>
       </c>
       <c r="K9" t="n">
-        <v>133.562</v>
+        <v>162.634</v>
       </c>
       <c r="L9" t="n">
-        <v>21.648</v>
+        <v>77.07599999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>5.757</v>
+        <v>21.573</v>
       </c>
     </row>
     <row r="10">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.093</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>38.165</v>
+        <v>42.028</v>
       </c>
       <c r="F10" t="n">
-        <v>74.45</v>
+        <v>75.90600000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>4.057</v>
       </c>
       <c r="H10" t="n">
-        <v>1.476</v>
+        <v>2.029</v>
       </c>
       <c r="I10" t="n">
-        <v>10.515</v>
+        <v>6.542</v>
       </c>
       <c r="J10" t="n">
-        <v>7.096</v>
+        <v>6.602</v>
       </c>
       <c r="K10" t="n">
-        <v>5.148</v>
+        <v>29.861</v>
       </c>
       <c r="L10" t="n">
-        <v>2.843</v>
+        <v>0.092</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -10185,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36.519</v>
+        <v>37.906</v>
       </c>
       <c r="F11" t="n">
-        <v>63.697</v>
+        <v>64.315</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>1.867</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.891</v>
+        <v>0.611</v>
       </c>
       <c r="J11" t="n">
-        <v>3.736</v>
+        <v>2.067</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.796</v>
+        <v>22.722</v>
       </c>
       <c r="F12" t="n">
-        <v>48.502</v>
+        <v>49.017</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10262,37 +10262,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>13.059</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4.394</v>
       </c>
       <c r="E13" t="n">
-        <v>8.673999999999999</v>
+        <v>16.173</v>
       </c>
       <c r="F13" t="n">
-        <v>34.177</v>
+        <v>39.507</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.201</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>7.612</v>
       </c>
       <c r="I13" t="n">
-        <v>3.807</v>
+        <v>15.358</v>
       </c>
       <c r="J13" t="n">
-        <v>13.525</v>
+        <v>25.682</v>
       </c>
       <c r="K13" t="n">
-        <v>16.795</v>
+        <v>43.799</v>
       </c>
       <c r="L13" t="n">
-        <v>7.407</v>
+        <v>23.107</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10323,13 +10323,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.028</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4.396</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4.847</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198.422</v>
+        <v>219.074</v>
       </c>
       <c r="C15" t="n">
-        <v>182.077</v>
+        <v>230.359</v>
       </c>
       <c r="D15" t="n">
-        <v>205.629</v>
+        <v>240.287</v>
       </c>
       <c r="E15" t="n">
-        <v>234.016</v>
+        <v>243.71</v>
       </c>
       <c r="F15" t="n">
-        <v>98.13800000000001</v>
+        <v>98.771</v>
       </c>
       <c r="G15" t="n">
-        <v>242.281</v>
+        <v>248.523</v>
       </c>
       <c r="H15" t="n">
-        <v>144.372</v>
+        <v>132.569</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>168.641</v>
+        <v>207.203</v>
       </c>
       <c r="K15" t="n">
-        <v>210.788</v>
+        <v>207.056</v>
       </c>
       <c r="L15" t="n">
-        <v>240.008</v>
+        <v>238.67</v>
       </c>
       <c r="M15" t="n">
-        <v>246.087</v>
+        <v>245.778</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.941</v>
+        <v>321.082</v>
       </c>
       <c r="C16" t="n">
-        <v>285.944</v>
+        <v>353.164</v>
       </c>
       <c r="D16" t="n">
-        <v>337.826</v>
+        <v>368.998</v>
       </c>
       <c r="E16" t="n">
-        <v>380.599</v>
+        <v>392.77</v>
       </c>
       <c r="F16" t="n">
-        <v>206.405</v>
+        <v>209.35</v>
       </c>
       <c r="G16" t="n">
-        <v>424.195</v>
+        <v>429.31</v>
       </c>
       <c r="H16" t="n">
-        <v>356.476</v>
+        <v>349.255</v>
       </c>
       <c r="I16" t="n">
-        <v>160.309</v>
+        <v>143.898</v>
       </c>
       <c r="J16" t="n">
-        <v>422.299</v>
+        <v>414.826</v>
       </c>
       <c r="K16" t="n">
-        <v>376.299</v>
+        <v>374.933</v>
       </c>
       <c r="L16" t="n">
-        <v>369.467</v>
+        <v>367.486</v>
       </c>
       <c r="M16" t="n">
-        <v>383.219</v>
+        <v>379.669</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>190.162</v>
+        <v>218.493</v>
       </c>
       <c r="C17" t="n">
-        <v>176.974</v>
+        <v>203.199</v>
       </c>
       <c r="D17" t="n">
-        <v>287.615</v>
+        <v>311.59</v>
       </c>
       <c r="E17" t="n">
-        <v>418.938</v>
+        <v>420.37</v>
       </c>
       <c r="F17" t="n">
-        <v>178.14</v>
+        <v>177.211</v>
       </c>
       <c r="G17" t="n">
-        <v>328.324</v>
+        <v>330.48</v>
       </c>
       <c r="H17" t="n">
-        <v>334.933</v>
+        <v>323.196</v>
       </c>
       <c r="I17" t="n">
-        <v>122.944</v>
+        <v>140.132</v>
       </c>
       <c r="J17" t="n">
-        <v>421.894</v>
+        <v>409.132</v>
       </c>
       <c r="K17" t="n">
-        <v>280.581</v>
+        <v>269.857</v>
       </c>
       <c r="L17" t="n">
-        <v>364.881</v>
+        <v>374.777</v>
       </c>
       <c r="M17" t="n">
-        <v>329.791</v>
+        <v>345.761</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.284</v>
+        <v>48.431</v>
       </c>
       <c r="C18" t="n">
-        <v>29.031</v>
+        <v>30.17</v>
       </c>
       <c r="D18" t="n">
-        <v>47.026</v>
+        <v>48.344</v>
       </c>
       <c r="E18" t="n">
-        <v>398.401</v>
+        <v>398.36</v>
       </c>
       <c r="F18" t="n">
-        <v>162.221</v>
+        <v>160.957</v>
       </c>
       <c r="G18" t="n">
-        <v>140.396</v>
+        <v>141.915</v>
       </c>
       <c r="H18" t="n">
-        <v>29.584</v>
+        <v>17.359</v>
       </c>
       <c r="I18" t="n">
-        <v>8.759</v>
+        <v>5.294</v>
       </c>
       <c r="J18" t="n">
-        <v>18.803</v>
+        <v>13.452</v>
       </c>
       <c r="K18" t="n">
-        <v>32.529</v>
+        <v>22.613</v>
       </c>
       <c r="L18" t="n">
-        <v>52.306</v>
+        <v>28.373</v>
       </c>
       <c r="M18" t="n">
-        <v>27.016</v>
+        <v>18.225</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.853</v>
+        <v>26.515</v>
       </c>
       <c r="C19" t="n">
-        <v>10.437</v>
+        <v>11.697</v>
       </c>
       <c r="D19" t="n">
-        <v>29.286</v>
+        <v>29.897</v>
       </c>
       <c r="E19" t="n">
-        <v>385.916</v>
+        <v>386.918</v>
       </c>
       <c r="F19" t="n">
-        <v>153.59</v>
+        <v>153.969</v>
       </c>
       <c r="G19" t="n">
-        <v>122.902</v>
+        <v>124.163</v>
       </c>
       <c r="H19" t="n">
-        <v>3.177</v>
+        <v>0.659</v>
       </c>
       <c r="I19" t="n">
-        <v>3.101</v>
+        <v>1.381</v>
       </c>
       <c r="J19" t="n">
-        <v>1.914</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6.987</v>
+        <v>3.67</v>
       </c>
       <c r="L19" t="n">
-        <v>6.497</v>
+        <v>2.373</v>
       </c>
       <c r="M19" t="n">
-        <v>4.883</v>
+        <v>1.898</v>
       </c>
     </row>
     <row r="20">
@@ -10561,37 +10561,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>120.83</v>
+        <v>115.312</v>
       </c>
       <c r="C20" t="n">
-        <v>124.046</v>
+        <v>118.863</v>
       </c>
       <c r="D20" t="n">
-        <v>35.092</v>
+        <v>30.751</v>
       </c>
       <c r="E20" t="n">
-        <v>219.31</v>
+        <v>217.542</v>
       </c>
       <c r="F20" t="n">
-        <v>95.608</v>
+        <v>93.946</v>
       </c>
       <c r="G20" t="n">
-        <v>112.855</v>
+        <v>107.506</v>
       </c>
       <c r="H20" t="n">
-        <v>42.608</v>
+        <v>51.99</v>
       </c>
       <c r="I20" t="n">
-        <v>3.029</v>
+        <v>2.44</v>
       </c>
       <c r="J20" t="n">
-        <v>2.275</v>
+        <v>3.211</v>
       </c>
       <c r="K20" t="n">
-        <v>70.63</v>
+        <v>79.911</v>
       </c>
       <c r="L20" t="n">
-        <v>3.369</v>
+        <v>1.948</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151.843</v>
+        <v>158.751</v>
       </c>
       <c r="C21" t="n">
-        <v>155.286</v>
+        <v>161.577</v>
       </c>
       <c r="D21" t="n">
-        <v>44.554</v>
+        <v>53.392</v>
       </c>
       <c r="E21" t="n">
-        <v>211.495</v>
+        <v>214.245</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84699999999999</v>
+        <v>84.553</v>
       </c>
       <c r="G21" t="n">
-        <v>86.437</v>
+        <v>87.849</v>
       </c>
       <c r="H21" t="n">
-        <v>315.454</v>
+        <v>278.821</v>
       </c>
       <c r="I21" t="n">
-        <v>67.90000000000001</v>
+        <v>68.127</v>
       </c>
       <c r="J21" t="n">
-        <v>282.613</v>
+        <v>166.365</v>
       </c>
       <c r="K21" t="n">
-        <v>217.762</v>
+        <v>209.034</v>
       </c>
       <c r="L21" t="n">
-        <v>181.643</v>
+        <v>139.418</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285.401</v>
+        <v>321.763</v>
       </c>
       <c r="C22" t="n">
-        <v>308.21</v>
+        <v>341.681</v>
       </c>
       <c r="D22" t="n">
-        <v>213.229</v>
+        <v>296.783</v>
       </c>
       <c r="E22" t="n">
-        <v>235.775</v>
+        <v>259.053</v>
       </c>
       <c r="F22" t="n">
-        <v>93.426</v>
+        <v>104.325</v>
       </c>
       <c r="G22" t="n">
-        <v>102.116</v>
+        <v>126.244</v>
       </c>
       <c r="H22" t="n">
-        <v>337.765</v>
+        <v>328.273</v>
       </c>
       <c r="I22" t="n">
-        <v>194.998</v>
+        <v>184.461</v>
       </c>
       <c r="J22" t="n">
-        <v>436.149</v>
+        <v>421.585</v>
       </c>
       <c r="K22" t="n">
-        <v>245.437</v>
+        <v>241.759</v>
       </c>
       <c r="L22" t="n">
-        <v>351.869</v>
+        <v>352.97</v>
       </c>
       <c r="M22" t="n">
-        <v>345.778</v>
+        <v>372.582</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.674</v>
+        <v>26.268</v>
       </c>
       <c r="C23" t="n">
-        <v>30.674</v>
+        <v>30.528</v>
       </c>
       <c r="D23" t="n">
-        <v>31.352</v>
+        <v>33.844</v>
       </c>
       <c r="E23" t="n">
-        <v>24.121</v>
+        <v>25.379</v>
       </c>
       <c r="F23" t="n">
-        <v>9.516999999999999</v>
+        <v>9.701000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>119.489</v>
+        <v>129.662</v>
       </c>
       <c r="H23" t="n">
-        <v>17.539</v>
+        <v>15.243</v>
       </c>
       <c r="I23" t="n">
-        <v>22.228</v>
+        <v>20.435</v>
       </c>
       <c r="J23" t="n">
-        <v>56.305</v>
+        <v>51.615</v>
       </c>
       <c r="K23" t="n">
-        <v>16.719</v>
+        <v>14.596</v>
       </c>
       <c r="L23" t="n">
-        <v>30.828</v>
+        <v>27.396</v>
       </c>
       <c r="M23" t="n">
-        <v>32.793</v>
+        <v>29.432</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.531</v>
+        <v>16.116</v>
       </c>
       <c r="C24" t="n">
-        <v>25.396</v>
+        <v>25.788</v>
       </c>
       <c r="D24" t="n">
-        <v>21.851</v>
+        <v>22.745</v>
       </c>
       <c r="E24" t="n">
-        <v>25.831</v>
+        <v>26.181</v>
       </c>
       <c r="F24" t="n">
-        <v>10.456</v>
+        <v>10.387</v>
       </c>
       <c r="G24" t="n">
-        <v>125.227</v>
+        <v>126.35</v>
       </c>
       <c r="H24" t="n">
-        <v>16.58</v>
+        <v>14.744</v>
       </c>
       <c r="I24" t="n">
-        <v>20.535</v>
+        <v>18.473</v>
       </c>
       <c r="J24" t="n">
-        <v>46.069</v>
+        <v>38.897</v>
       </c>
       <c r="K24" t="n">
-        <v>16.215</v>
+        <v>14.115</v>
       </c>
       <c r="L24" t="n">
-        <v>27.037</v>
+        <v>23.955</v>
       </c>
       <c r="M24" t="n">
-        <v>28.073</v>
+        <v>24.889</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.563</v>
+        <v>13.56</v>
       </c>
       <c r="C25" t="n">
-        <v>17.647</v>
+        <v>17.151</v>
       </c>
       <c r="D25" t="n">
-        <v>14.358</v>
+        <v>14.13</v>
       </c>
       <c r="E25" t="n">
-        <v>26.681</v>
+        <v>25.997</v>
       </c>
       <c r="F25" t="n">
-        <v>12.021</v>
+        <v>11.906</v>
       </c>
       <c r="G25" t="n">
-        <v>86.818</v>
+        <v>93.524</v>
       </c>
       <c r="H25" t="n">
-        <v>16.527</v>
+        <v>7.184</v>
       </c>
       <c r="I25" t="n">
-        <v>11.087</v>
+        <v>7.864</v>
       </c>
       <c r="J25" t="n">
-        <v>18.461</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>21.149</v>
+        <v>9.253</v>
       </c>
       <c r="L25" t="n">
-        <v>27.456</v>
+        <v>22.892</v>
       </c>
       <c r="M25" t="n">
-        <v>18.094</v>
+        <v>9.379</v>
       </c>
     </row>
     <row r="26">
@@ -10819,37 +10819,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.778</v>
+        <v>7.491</v>
       </c>
       <c r="C26" t="n">
-        <v>11.235</v>
+        <v>10.872</v>
       </c>
       <c r="D26" t="n">
-        <v>4.172</v>
+        <v>3.965</v>
       </c>
       <c r="E26" t="n">
-        <v>22.438</v>
+        <v>22.31</v>
       </c>
       <c r="F26" t="n">
-        <v>11.269</v>
+        <v>11.251</v>
       </c>
       <c r="G26" t="n">
-        <v>96.301</v>
+        <v>96.38500000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>1.006</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.551</v>
+        <v>1.242</v>
       </c>
       <c r="J26" t="n">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>5.061</v>
+        <v>2.128</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.634</v>
+        <v>23.037</v>
       </c>
       <c r="C27" t="n">
-        <v>31.771</v>
+        <v>39.001</v>
       </c>
       <c r="D27" t="n">
-        <v>27.277</v>
+        <v>33.84</v>
       </c>
       <c r="E27" t="n">
-        <v>24.271</v>
+        <v>25.578</v>
       </c>
       <c r="F27" t="n">
-        <v>12.223</v>
+        <v>12.639</v>
       </c>
       <c r="G27" t="n">
-        <v>109.659</v>
+        <v>123.905</v>
       </c>
       <c r="H27" t="n">
-        <v>30.772</v>
+        <v>27.211</v>
       </c>
       <c r="I27" t="n">
-        <v>12.796</v>
+        <v>11.931</v>
       </c>
       <c r="J27" t="n">
-        <v>55.912</v>
+        <v>51.501</v>
       </c>
       <c r="K27" t="n">
-        <v>34.4</v>
+        <v>31</v>
       </c>
       <c r="L27" t="n">
-        <v>38.12</v>
+        <v>34.933</v>
       </c>
       <c r="M27" t="n">
-        <v>35.866</v>
+        <v>33.009</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.447</v>
+        <v>2.287</v>
       </c>
       <c r="C28" t="n">
-        <v>0.793</v>
+        <v>0.802</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.019</v>
+        <v>21.981</v>
       </c>
       <c r="F28" t="n">
-        <v>11.078</v>
+        <v>11.094</v>
       </c>
       <c r="G28" t="n">
-        <v>61.175</v>
+        <v>65.71599999999999</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.512</v>
+        <v>0.498</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.367</v>
+        <v>4.402</v>
       </c>
       <c r="C29" t="n">
-        <v>5.664</v>
+        <v>5.049</v>
       </c>
       <c r="D29" t="n">
-        <v>3.613</v>
+        <v>3.277</v>
       </c>
       <c r="E29" t="n">
-        <v>22.205</v>
+        <v>22.439</v>
       </c>
       <c r="F29" t="n">
-        <v>10.799</v>
+        <v>10.922</v>
       </c>
       <c r="G29" t="n">
-        <v>71.66200000000001</v>
+        <v>74.367</v>
       </c>
       <c r="H29" t="n">
-        <v>4.842</v>
+        <v>1.195</v>
       </c>
       <c r="I29" t="n">
-        <v>6.896</v>
+        <v>4.249</v>
       </c>
       <c r="J29" t="n">
-        <v>11.724</v>
+        <v>6.333</v>
       </c>
       <c r="K29" t="n">
-        <v>9.029</v>
+        <v>3.292</v>
       </c>
       <c r="L29" t="n">
-        <v>17.681</v>
+        <v>8.693</v>
       </c>
       <c r="M29" t="n">
-        <v>5.29</v>
+        <v>1.826</v>
       </c>
     </row>
     <row r="30">
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.548</v>
+        <v>13.295</v>
       </c>
       <c r="F30" t="n">
-        <v>5.748</v>
+        <v>5.599</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9401425521e-05</v>
+        <v>2.498707332900001e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0893835209e-05</v>
+        <v>4.103095872100001e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9740023801e-05</v>
+        <v>4.811398380099999e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2573021316e-05</v>
+        <v>6.949075932099998e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1917433889e-05</v>
+        <v>1.23587689e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6922902724e-05</v>
+        <v>3.1267434276e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9110843161e-05</v>
+        <v>4.7352806449e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857296000000001e-05</v>
+        <v>4.936261932899999e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1736843961e-05</v>
+        <v>7.033528326399999e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.49278721e-05</v>
+        <v>5.207387080900001e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0470146249e-05</v>
+        <v>5.0393964196e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3138087289e-05</v>
+        <v>8.955774464400001e-05</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.555913443999999e-06</v>
+        <v>6.060778201000001e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.895782656e-06</v>
+        <v>6.848059008999999e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1821560529e-05</v>
+        <v>1.4055288025e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8598643401e-05</v>
+        <v>4.9720526361e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.850873081e-06</v>
+        <v>5.628900675999999e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3994404e-06</v>
+        <v>7.762314816e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8631158016e-05</v>
+        <v>1.9599160009e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8364586256e-05</v>
+        <v>1.750646534400001e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1764222369e-05</v>
+        <v>1.4268541401e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9110574081e-05</v>
+        <v>2.5636813225e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6255995001e-05</v>
+        <v>1.5790686921e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>6.194791848999999e-06</v>
+        <v>6.465928921e-06</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.445216256e-06</v>
+        <v>1.7539344e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>7.346268159999999e-07</v>
+        <v>8.68952484e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.440261201e-06</v>
+        <v>2.829601636000001e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.030457759999999e-05</v>
+        <v>4.1213466121e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.483402499999999e-06</v>
+        <v>5.545334089e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.252735369e-06</v>
+        <v>4.550986520999999e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.744120100000002e-08</v>
+        <v>5.7866449e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2694969e-08</v>
+        <v>4.157521e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.46615616e-07</v>
+        <v>4.678136410000001e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.231734809999998e-07</v>
+        <v>1.906981561e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>7.846416400000002e-08</v>
+        <v>1.28346241e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5876e-07</v>
+        <v>4.431025e-07</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95811025e-07</v>
+        <v>4.246072360000001e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4249104e-08</v>
+        <v>5.416960000000001e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.442509159999999e-07</v>
+        <v>3.55661881e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8053475329e-05</v>
+        <v>3.8208129961e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.810075044000001e-06</v>
+        <v>8.657372025000001e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.909304383999999e-06</v>
+        <v>5.763694561e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011322225000001e-06</v>
+        <v>7.022942809000001e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.090584576e-06</v>
+        <v>2.656887025e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644942041e-06</v>
+        <v>5.787253476000001e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3079970641e-05</v>
+        <v>3.5524333441e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.030668996000001e-06</v>
+        <v>8.561430784000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.340262025e-06</v>
+        <v>3.997400625e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816464399999999e-08</v>
+        <v>3.49503025e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875263999999999e-07</v>
+        <v>1.597201225e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>5.278749024999999e-06</v>
+        <v>1.2853437129e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0191104401e-05</v>
+        <v>1.8177510976e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.847396321e-06</v>
+        <v>8.505450624999998e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>4.100097023999998e-06</v>
+        <v>1.1553885121e-05</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.080772008333333e-06</v>
+        <v>9.47925440833333e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>4.529210785333334e-06</v>
+        <v>1.2424698075e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349704560333334e-06</v>
+        <v>6.355914465333335e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>3.842414408333332e-06</v>
+        <v>5.628914200333334e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792310536333332e-06</v>
+        <v>1.113142436033334e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>1.573138401333333e-06</v>
+        <v>2.866593408333333e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>6.575788800833332e-05</v>
+        <v>6.522214832133332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.472617876299999e-05</v>
+        <v>3.421017653333334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.672437120299999e-05</v>
+        <v>4.6827761907e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.445482216033334e-05</v>
+        <v>4.373420132033333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.877715782533333e-05</v>
+        <v>3.644446344533334e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5514115072e-05</v>
+        <v>5.802139469999999e-05</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.098200100000001e-08</v>
+        <v>8.193870399999999e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.694513444e-06</v>
+        <v>5.643465129000001e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0079456804e-05</v>
+        <v>2.02606756e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.132638490000001e-07</v>
+        <v>7.485696e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.225616e-09</v>
+        <v>2.477476e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.895632225e-06</v>
+        <v>2.0439441e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11414,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.356634253333333e-07</v>
+        <v>6.741003e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>3.608033333333334e-11</v>
+        <v>2.223790803333334e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>6.120408333333333e-09</v>
+        <v>2.080834083333333e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>8.044873763333334e-07</v>
+        <v>1.174496960333333e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210551960333334e-06</v>
+        <v>3.661292805333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>5.100563333333332e-08</v>
+        <v>1.371874563333333e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>3.123413333333333e-08</v>
+        <v>1.446296333333333e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>2.870430083333333e-07</v>
+        <v>2.690168965333333e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>1.283802083333333e-07</v>
+        <v>6.005543053333333e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.946269281333335e-06</v>
+        <v>8.816605985333331e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56211968e-07</v>
+        <v>1.980236591999999e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1047683e-08</v>
+        <v>1.55131443e-07</v>
       </c>
     </row>
     <row r="10">
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3.982163333333333e-10</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -11466,28 +11466,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.855224083333332e-07</v>
+        <v>5.887842613333331e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847600833333333e-06</v>
+        <v>1.920573612e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.136333333333333e-10</v>
+        <v>5.486416333333336e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>7.261919999999999e-10</v>
+        <v>1.372280333333333e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6855075e-08</v>
+        <v>1.426592133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.678440533333333e-08</v>
+        <v>1.452880133333333e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>8.833968e-09</v>
+        <v>2.972264403333334e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>2.694216333333333e-09</v>
+        <v>2.821333333333334e-12</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -11509,22 +11509,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.445457869999999e-07</v>
+        <v>4.789549453333333e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352435936333333e-06</v>
+        <v>1.378806408333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93548e-10</v>
+        <v>1.161896333333333e-09</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.785960333333333e-09</v>
+        <v>1.244403333333333e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652565333333334e-09</v>
+        <v>1.424163e-09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.732192053333333e-07</v>
+        <v>1.720964280000001e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.841480013333335e-07</v>
+        <v>8.008887630000001e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11586,37 +11586,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>5.684582699999999e-08</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>6.435745333333334e-09</v>
       </c>
       <c r="E13" t="n">
-        <v>2.507942533333333e-08</v>
+        <v>8.718864299999999e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>3.893557763333333e-07</v>
+        <v>5.20267683e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4.808003333333333e-10</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.931418133333333e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>4.831083e-09</v>
+        <v>7.862272133333333e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>6.097520833333334e-08</v>
+        <v>2.198550413333333e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>9.402400833333334e-08</v>
+        <v>6.394508003333333e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8287883e-08</v>
+        <v>1.779778163333333e-07</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11647,13 +11647,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.408261333333332e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>6.441605333333333e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>7.831136333333335e-09</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9371290084e-05</v>
+        <v>4.7993417476e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3152033929e-05</v>
+        <v>5.3065268881e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.228328564099999e-05</v>
+        <v>5.7737842369e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4763488256e-05</v>
+        <v>5.93945641e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.631067044e-06</v>
+        <v>9.755710440999999e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8700082961e-05</v>
+        <v>6.176368152899999e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0843274384e-05</v>
+        <v>1.7574539761e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.843978688099999e-05</v>
+        <v>4.2933083209e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4431580944e-05</v>
+        <v>4.287218713600001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7603840064e-05</v>
+        <v>5.69633689e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0558811569e-05</v>
+        <v>6.0406825284e-05</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6874163827e-05</v>
+        <v>3.436455024133332e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>2.725465704533334e-05</v>
+        <v>4.157493696533333e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>3.804213542533334e-05</v>
+        <v>4.538650800133333e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.828519960033332e-05</v>
+        <v>5.142275763333333e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.420100800833334e-05</v>
+        <v>1.460914083333333e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>5.998046600833333e-05</v>
+        <v>6.143569203333335e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.235837952533334e-05</v>
+        <v>4.065968500833333e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>8.566325160333335e-06</v>
+        <v>6.902211467999999e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.944548180033333e-05</v>
+        <v>5.736020342533334e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7200312467e-05</v>
+        <v>4.685825149633333e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.550195469633334e-05</v>
+        <v>4.501532006533333e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.895226732033333e-05</v>
+        <v>4.804951652033333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.205386208133333e-05</v>
+        <v>1.5913063683e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>1.043993222533333e-05</v>
+        <v>1.3763277867e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>2.757412940833333e-05</v>
+        <v>3.236277603333333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.850301594799999e-05</v>
+        <v>5.890364563333334e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.05779532e-05</v>
+        <v>1.046791284033333e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.593221632533333e-05</v>
+        <v>3.64056768e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.739337149633333e-05</v>
+        <v>3.481855147200001e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>5.038409045333333e-06</v>
+        <v>6.545659141333333e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.933151574533333e-05</v>
+        <v>5.579633114133333e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6241899187e-05</v>
+        <v>2.427426681633334e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4.437938138699999e-05</v>
+        <v>4.681926657633332e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.625403456033334e-05</v>
+        <v>3.985022304033334e-05</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.09637552e-07</v>
+        <v>7.818539203333332e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>2.80932987e-07</v>
+        <v>3.034096333333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.371482253333335e-07</v>
+        <v>7.790474453333333e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.290778560033334e-05</v>
+        <v>5.289689653333333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.771884280333334e-06</v>
+        <v>8.635718616333333e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.570345605333333e-06</v>
+        <v>6.713289074999999e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>2.917376853333333e-07</v>
+        <v>1.004449603333334e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>2.557336033333334e-08</v>
+        <v>9.342145333333331e-09</v>
       </c>
       <c r="J18" t="n">
-        <v>1.178509363333333e-07</v>
+        <v>6.0318768e-08</v>
       </c>
       <c r="K18" t="n">
-        <v>3.52711947e-07</v>
+        <v>1.704492563333333e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>9.119725453333332e-07</v>
+        <v>2.683423763333334e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>2.432880853333333e-07</v>
+        <v>1.10716875e-07</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.89655203e-07</v>
+        <v>2.343484083333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6310323e-08</v>
+        <v>4.5606603e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85889932e-07</v>
+        <v>2.979435363333333e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.964371968533333e-05</v>
+        <v>4.990184624133333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.863296033333334e-06</v>
+        <v>7.902150986999999e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.034967201333333e-06</v>
+        <v>5.138816856333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>3.364443000000001e-09</v>
+        <v>1.447603333333334e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>3.205400333333334e-09</v>
+        <v>6.357203333333333e-10</v>
       </c>
       <c r="J19" t="n">
-        <v>1.221132e-09</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6272723e-08</v>
+        <v>4.489633333333334e-09</v>
       </c>
       <c r="L19" t="n">
-        <v>1.407033633333333e-08</v>
+        <v>1.877043e-09</v>
       </c>
       <c r="M19" t="n">
-        <v>7.947896333333335e-09</v>
+        <v>1.200801333333333e-09</v>
       </c>
     </row>
     <row r="20">
@@ -11885,37 +11885,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.866629633333332e-06</v>
+        <v>4.432285781333333e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>5.129136705333333e-06</v>
+        <v>4.709470923e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>4.104828213333333e-07</v>
+        <v>3.152080003333333e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.603229203333334e-05</v>
+        <v>1.5774840588e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.046963221333333e-06</v>
+        <v>2.941950305333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>4.245417008333334e-06</v>
+        <v>3.852513345333334e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>6.051472213333333e-07</v>
+        <v>9.009867e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>3.058280333333333e-09</v>
+        <v>1.984533333333333e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>1.725208333333333e-09</v>
+        <v>3.436840333333333e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>1.662865633333333e-06</v>
+        <v>2.128589307e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>3.783387e-09</v>
+        <v>1.264901333333333e-09</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.685432216333331e-06</v>
+        <v>8.400626667000001e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.037913932000002e-06</v>
+        <v>8.702375643e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>6.616863053333334e-07</v>
+        <v>9.502352213333334e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491004500833333e-05</v>
+        <v>1.5300306675e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399671136333333e-06</v>
+        <v>2.383069936333334e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.490451656333333e-06</v>
+        <v>2.572482267000001e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317040870533334e-05</v>
+        <v>2.591371668033334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>1.536803333333333e-06</v>
+        <v>1.547096043e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>2.662336925633333e-05</v>
+        <v>9.225771075000002e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>1.580676288133333e-05</v>
+        <v>1.4565071052e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.099805981633333e-05</v>
+        <v>6.479126241333335e-06</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.715124360033333e-05</v>
+        <v>3.451047605633332e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.166446803333333e-05</v>
+        <v>3.891530192033332e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.515553548033333e-05</v>
+        <v>2.936004969633334e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.852995020833333e-05</v>
+        <v>2.2369485603e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.909472492e-06</v>
+        <v>3.627901875e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>3.475892485333333e-06</v>
+        <v>5.312515845333332e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.802839840833333e-05</v>
+        <v>3.592105417633334e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.267474000133333e-05</v>
+        <v>1.1341953507e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>6.3408650067e-05</v>
+        <v>5.924463740833333e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.007977365633334e-05</v>
+        <v>1.948247136033333e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.127059772033335e-05</v>
+        <v>4.152927363333333e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.985414176133334e-05</v>
+        <v>4.627244890799999e-05</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.60458276e-06</v>
+        <v>6.90007824e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>9.408942760000001e-06</v>
+        <v>9.31958784e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82947904e-06</v>
+        <v>1.145416336e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>5.81822641e-06</v>
+        <v>6.440936410000001e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.057328899999998e-07</v>
+        <v>9.410940100000003e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4277621121e-05</v>
+        <v>1.6812234244e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>3.076165210000001e-06</v>
+        <v>2.32349049e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.940839840000001e-06</v>
+        <v>4.175892249999999e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>3.170253025e-05</v>
+        <v>2.664108225e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>2.79524961e-06</v>
+        <v>2.13043216e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>9.503655839999998e-06</v>
+        <v>7.50540816e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.075380849e-05</v>
+        <v>8.662426240000001e-06</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.41211961e-06</v>
+        <v>2.59725456e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>6.449568160000001e-06</v>
+        <v>6.650209440000002e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>4.774662009999999e-06</v>
+        <v>5.173350250000001e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.67240561e-06</v>
+        <v>6.85444761e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09327936e-06</v>
+        <v>1.07889769e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5681801529e-05</v>
+        <v>1.59643225e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.748963999999999e-06</v>
+        <v>2.17385536e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>4.21686225e-06</v>
+        <v>3.41251729e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.122352761e-05</v>
+        <v>1.512976609e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>2.62926225e-06</v>
+        <v>1.99233225e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>7.309993689999999e-06</v>
+        <v>5.738420249999999e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>7.88093329e-06</v>
+        <v>6.194623209999999e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.83954969e-06</v>
+        <v>1.838736e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.11416609e-06</v>
+        <v>2.94156801e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.06152164e-06</v>
+        <v>1.996569e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>7.118757610000001e-06</v>
+        <v>6.75844009e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44504441e-06</v>
+        <v>1.41752836e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>7.537365123999998e-06</v>
+        <v>8.746738576e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>2.73141729e-06</v>
+        <v>5.1609856e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>1.22921569e-06</v>
+        <v>6.184249599999999e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>3.408085209999999e-06</v>
+        <v>8.464000000000001e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>4.472802010000001e-06</v>
+        <v>8.561800900000001e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>7.538319360000001e-06</v>
+        <v>5.240436639999999e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>3.273928360000001e-06</v>
+        <v>8.7965641e-07</v>
       </c>
     </row>
     <row r="26">
@@ -12143,37 +12143,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.049728399999999e-07</v>
+        <v>5.611508099999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26225225e-06</v>
+        <v>1.18200384e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7405584e-07</v>
+        <v>1.5721225e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.03463844e-06</v>
+        <v>4.977361e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.26990361e-06</v>
+        <v>1.26585001e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.273882601e-06</v>
+        <v>9.290068225e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>1.012036e-08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.405601e-08</v>
+        <v>1.542564e-08</v>
       </c>
       <c r="J26" t="n">
-        <v>5.715360000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2.53009e-09</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.5613721e-07</v>
+        <v>4.528384e-08</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.680299560000001e-06</v>
+        <v>5.307033689999999e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.009396441e-05</v>
+        <v>1.521078001e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>7.440347290000001e-06</v>
+        <v>1.1451456e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>5.890814410000001e-06</v>
+        <v>6.542340840000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49401729e-06</v>
+        <v>1.59744321e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2025096281e-05</v>
+        <v>1.5352449025e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>9.469159839999999e-06</v>
+        <v>7.404385209999999e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>1.63737616e-06</v>
+        <v>1.42348761e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.126151743999999e-05</v>
+        <v>2.652353001e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.18336e-05</v>
+        <v>9.609999999999999e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>1.453134399999999e-05</v>
+        <v>1.220314489e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.286369956e-05</v>
+        <v>1.089594081e-05</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.987809e-08</v>
+        <v>5.230369e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>6.288490000000001e-09</v>
+        <v>6.432040000000001e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.848363609999998e-06</v>
+        <v>4.83164361e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.22722084e-06</v>
+        <v>1.23076836e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>3.742380625e-06</v>
+        <v>4.318592655999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.62144e-09</v>
+        <v>2.48004e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9070689e-07</v>
+        <v>1.9377604e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2080896e-07</v>
+        <v>2.5492401e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3053769e-07</v>
+        <v>1.0738729e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.930620249999999e-06</v>
+        <v>5.03508721e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16618401e-06</v>
+        <v>1.19290084e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.135442244e-06</v>
+        <v>5.530450689e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3444964e-07</v>
+        <v>1.428025e-08</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7554816e-07</v>
+        <v>1.805400099999999e-07</v>
       </c>
       <c r="J29" t="n">
-        <v>1.37452176e-06</v>
+        <v>4.0106889e-07</v>
       </c>
       <c r="K29" t="n">
-        <v>8.152284100000001e-07</v>
+        <v>1.0837264e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>3.126177610000001e-06</v>
+        <v>7.556824899999998e-07</v>
       </c>
       <c r="M29" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>3.334276000000001e-08</v>
       </c>
     </row>
     <row r="30">
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.83548304e-06</v>
+        <v>1.76757025e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.303950400000001e-07</v>
+        <v>3.1348801e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F2" t="n">
-        <v>0.124653</v>
+        <v>0.206944</v>
       </c>
       <c r="G2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="I2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="J2" t="n">
-        <v>0.123958</v>
+        <v>0.207986</v>
       </c>
       <c r="K2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="M2" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
     </row>
     <row r="3">
@@ -12482,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.124653</v>
+        <v>0.185069</v>
       </c>
       <c r="C3" t="n">
-        <v>0.124653</v>
+        <v>0.19375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E3" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H3" t="n">
-        <v>0.124653</v>
+        <v>0.165972</v>
       </c>
       <c r="I3" t="n">
-        <v>0.124653</v>
+        <v>0.160417</v>
       </c>
       <c r="J3" t="n">
-        <v>0.122569</v>
+        <v>0.181597</v>
       </c>
       <c r="K3" t="n">
-        <v>0.124653</v>
+        <v>0.192014</v>
       </c>
       <c r="L3" t="n">
-        <v>0.124653</v>
+        <v>0.166667</v>
       </c>
       <c r="M3" t="n">
-        <v>0.124653</v>
+        <v>0.160764</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C4" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E4" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.124653</v>
+        <v>0.207639</v>
       </c>
       <c r="G4" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H4" t="n">
-        <v>0.124653</v>
+        <v>0.148264</v>
       </c>
       <c r="I4" t="n">
         <v>0.051042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.124653</v>
+        <v>0.19375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L4" t="n">
-        <v>0.124653</v>
+        <v>0.204514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.124653</v>
+        <v>0.202083</v>
       </c>
     </row>
     <row r="5">
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000694</v>
+        <v>0.196181</v>
       </c>
       <c r="E5" t="n">
         <v>0.000694</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="I6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="J6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="K6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="M6" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
     </row>
     <row r="7">
@@ -12652,22 +12652,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C7" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D7" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E7" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F7" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G7" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H7" t="n">
         <v>0.080556</v>
@@ -12685,7 +12685,7 @@
         <v>0.08784699999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.103472</v>
+        <v>0.207986</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.121528</v>
+        <v>0.166667</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12707,10 +12707,10 @@
         <v>0.111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.121528</v>
+        <v>0.204861</v>
       </c>
       <c r="G8" t="n">
-        <v>0.121528</v>
+        <v>0.204861</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
@@ -12738,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="I9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="J9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="K9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="M9" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
     </row>
     <row r="10">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="C10" t="n">
         <v>0.000347</v>
@@ -12790,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F10" t="n">
-        <v>0.124653</v>
+        <v>0.207639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H10" t="n">
-        <v>0.123958</v>
+        <v>0.207986</v>
       </c>
       <c r="I10" t="n">
         <v>0.08437500000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.124653</v>
+        <v>0.127083</v>
       </c>
       <c r="K10" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L10" t="n">
-        <v>0.124653</v>
+        <v>0.13125</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12833,19 +12833,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F11" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G11" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.170833</v>
       </c>
       <c r="I11" t="n">
-        <v>0.124653</v>
+        <v>0.125694</v>
       </c>
       <c r="J11" t="n">
         <v>0.124653</v>
@@ -12876,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.124653</v>
+        <v>0.133681</v>
       </c>
       <c r="F12" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12910,37 +12910,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="C13" t="n">
         <v>0.000347</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="E13" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F13" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="H13" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="I13" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="J13" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="K13" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L13" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12971,13 +12971,13 @@
         <v>0.000347</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000347</v>
+        <v>0.207986</v>
       </c>
       <c r="K14" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C15" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D15" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E15" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.124653</v>
+        <v>0.205903</v>
       </c>
       <c r="H15" t="n">
         <v>0.046528</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="K15" t="n">
-        <v>0.124653</v>
+        <v>0.133333</v>
       </c>
       <c r="L15" t="n">
-        <v>0.124653</v>
+        <v>0.150347</v>
       </c>
       <c r="M15" t="n">
-        <v>0.124653</v>
+        <v>0.156597</v>
       </c>
     </row>
     <row r="16">
@@ -13037,19 +13037,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C16" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D16" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E16" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F16" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G16" t="n">
         <v>0.021875</v>
@@ -13064,13 +13064,13 @@
         <v>0.07256899999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.124653</v>
+        <v>0.154514</v>
       </c>
       <c r="L16" t="n">
-        <v>0.124653</v>
+        <v>0.139236</v>
       </c>
       <c r="M16" t="n">
-        <v>0.124653</v>
+        <v>0.132986</v>
       </c>
     </row>
     <row r="17">
@@ -13080,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C17" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D17" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E17" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F17" t="n">
         <v>0.101042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H17" t="n">
-        <v>0.124653</v>
+        <v>0.130556</v>
       </c>
       <c r="I17" t="n">
-        <v>0.124653</v>
+        <v>0.205208</v>
       </c>
       <c r="J17" t="n">
         <v>0.100694</v>
       </c>
       <c r="K17" t="n">
-        <v>0.124653</v>
+        <v>0.144444</v>
       </c>
       <c r="L17" t="n">
-        <v>0.124653</v>
+        <v>0.174306</v>
       </c>
       <c r="M17" t="n">
-        <v>0.124653</v>
+        <v>0.198611</v>
       </c>
     </row>
     <row r="18">
@@ -13123,22 +13123,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.124653</v>
+        <v>0.137847</v>
       </c>
       <c r="C18" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D18" t="n">
-        <v>0.124653</v>
+        <v>0.207292</v>
       </c>
       <c r="E18" t="n">
-        <v>0.124653</v>
+        <v>0.141319</v>
       </c>
       <c r="F18" t="n">
-        <v>0.124653</v>
+        <v>0.132986</v>
       </c>
       <c r="G18" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H18" t="n">
         <v>0.092361</v>
@@ -13166,22 +13166,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C19" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D19" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E19" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F19" t="n">
         <v>0.044792</v>
       </c>
       <c r="G19" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H19" t="n">
         <v>0.092014</v>
@@ -13236,7 +13236,7 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="L20" t="n">
         <v>0.026736</v>
@@ -13252,28 +13252,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.124653</v>
+        <v>0.197222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.124653</v>
+        <v>0.197917</v>
       </c>
       <c r="D21" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E21" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F21" t="n">
-        <v>0.124653</v>
+        <v>0.139236</v>
       </c>
       <c r="G21" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H21" t="n">
-        <v>0.124653</v>
+        <v>0.146875</v>
       </c>
       <c r="I21" t="n">
-        <v>0.124653</v>
+        <v>0.169444</v>
       </c>
       <c r="J21" t="n">
         <v>0.08749999999999999</v>
@@ -13282,7 +13282,7 @@
         <v>0.101042</v>
       </c>
       <c r="L21" t="n">
-        <v>0.124653</v>
+        <v>0.126736</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,22 +13295,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="C22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H22" t="n">
         <v>0.052431</v>
@@ -13325,10 +13325,10 @@
         <v>0.118403</v>
       </c>
       <c r="L22" t="n">
-        <v>0.124653</v>
+        <v>0.164931</v>
       </c>
       <c r="M22" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
     </row>
     <row r="23">
@@ -13341,19 +13341,19 @@
         <v>0.028819</v>
       </c>
       <c r="C23" t="n">
-        <v>0.124653</v>
+        <v>0.163194</v>
       </c>
       <c r="D23" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E23" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F23" t="n">
-        <v>0.123958</v>
+        <v>0.207292</v>
       </c>
       <c r="G23" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H23" t="n">
         <v>0.033681</v>
@@ -13381,22 +13381,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.124653</v>
+        <v>0.190625</v>
       </c>
       <c r="C24" t="n">
-        <v>0.124653</v>
+        <v>0.169097</v>
       </c>
       <c r="D24" t="n">
-        <v>0.124653</v>
+        <v>0.185764</v>
       </c>
       <c r="E24" t="n">
-        <v>0.124653</v>
+        <v>0.207292</v>
       </c>
       <c r="F24" t="n">
         <v>0.080208</v>
       </c>
       <c r="G24" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H24" t="n">
         <v>0.024306</v>
@@ -13424,13 +13424,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.124653</v>
+        <v>0.164931</v>
       </c>
       <c r="C25" t="n">
-        <v>0.124653</v>
+        <v>0.147569</v>
       </c>
       <c r="D25" t="n">
-        <v>0.124653</v>
+        <v>0.151736</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
@@ -13439,7 +13439,7 @@
         <v>0.106597</v>
       </c>
       <c r="G25" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H25" t="n">
         <v>0.043403</v>
@@ -13470,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.124653</v>
+        <v>0.132292</v>
       </c>
       <c r="D26" t="n">
-        <v>0.124653</v>
+        <v>0.154167</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13482,13 +13482,13 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.124653</v>
+        <v>0.160417</v>
       </c>
       <c r="H26" t="n">
         <v>0.08472200000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.124653</v>
+        <v>0.130903</v>
       </c>
       <c r="J26" t="n">
         <v>0.104167</v>
@@ -13510,22 +13510,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.124653</v>
+        <v>0.202431</v>
       </c>
       <c r="C27" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="D27" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="E27" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="F27" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="G27" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H27" t="n">
         <v>0.07083299999999999</v>
@@ -13568,7 +13568,7 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
@@ -13596,22 +13596,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.124653</v>
+        <v>0.157639</v>
       </c>
       <c r="C29" t="n">
-        <v>0.124306</v>
+        <v>0.144792</v>
       </c>
       <c r="D29" t="n">
-        <v>0.124653</v>
+        <v>0.139583</v>
       </c>
       <c r="E29" t="n">
-        <v>0.123958</v>
+        <v>0.203125</v>
       </c>
       <c r="F29" t="n">
-        <v>0.124653</v>
+        <v>0.199306</v>
       </c>
       <c r="G29" t="n">
-        <v>0.124653</v>
+        <v>0.207986</v>
       </c>
       <c r="H29" t="n">
         <v>0.092708</v>

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.272</v>
+        <v>0.014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.319</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.58</v>
+        <v>0.037</v>
       </c>
       <c r="E2" t="n">
-        <v>1.085</v>
+        <v>0.187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.211</v>
+        <v>0.04</v>
       </c>
       <c r="G2" t="n">
-        <v>0.463</v>
+        <v>0.076</v>
       </c>
       <c r="H2" t="n">
-        <v>0.417</v>
+        <v>0.007</v>
       </c>
       <c r="I2" t="n">
-        <v>0.527</v>
+        <v>0.012</v>
       </c>
       <c r="J2" t="n">
-        <v>0.755</v>
+        <v>0.006</v>
       </c>
       <c r="K2" t="n">
-        <v>0.487</v>
+        <v>0.003</v>
       </c>
       <c r="L2" t="n">
-        <v>0.422</v>
+        <v>0.003</v>
       </c>
       <c r="M2" t="n">
-        <v>0.776</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.082</v>
+        <v>0.007</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="D3" t="n">
-        <v>0.175</v>
+        <v>0.016</v>
       </c>
       <c r="E3" t="n">
-        <v>0.865</v>
+        <v>0.168</v>
       </c>
       <c r="F3" t="n">
-        <v>0.104</v>
+        <v>0.021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.126</v>
+        <v>0.021</v>
       </c>
       <c r="H3" t="n">
-        <v>0.219</v>
+        <v>0.001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.209</v>
+        <v>0.001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.141</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.224</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1917,40 +1917,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="E4" t="n">
-        <v>0.717</v>
+        <v>0.138</v>
       </c>
       <c r="F4" t="n">
-        <v>0.098</v>
+        <v>0.019</v>
       </c>
       <c r="G4" t="n">
-        <v>0.073</v>
+        <v>0.013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.001</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.006</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.159</v>
+        <v>0.032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.107</v>
+        <v>0.022</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.059</v>
+        <v>0.002</v>
       </c>
       <c r="C6" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.041</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.583</v>
+        <v>0.107</v>
       </c>
       <c r="F6" t="n">
-        <v>0.142</v>
+        <v>0.026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.055</v>
+        <v>0.008</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.063</v>
+        <v>0.007</v>
       </c>
       <c r="F7" t="n">
-        <v>0.169</v>
+        <v>0.028</v>
       </c>
       <c r="G7" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.025</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.553</v>
-      </c>
       <c r="M7" t="n">
-        <v>0.767</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.099</v>
+        <v>0.018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.349</v>
+        <v>0.06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.082</v>
+        <v>0.022</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2132,37 +2132,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.055</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.003</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.014</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.584</v>
+        <v>0.043</v>
       </c>
       <c r="C15" t="n">
-        <v>0.497</v>
+        <v>0.019</v>
       </c>
       <c r="D15" t="n">
-        <v>0.607</v>
+        <v>0.035</v>
       </c>
       <c r="E15" t="n">
-        <v>0.948</v>
+        <v>0.163</v>
       </c>
       <c r="F15" t="n">
-        <v>0.172</v>
+        <v>0.033</v>
       </c>
       <c r="G15" t="n">
-        <v>1.029</v>
+        <v>0.186</v>
       </c>
       <c r="H15" t="n">
-        <v>0.311</v>
+        <v>0.022</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.464</v>
+        <v>0.023</v>
       </c>
       <c r="K15" t="n">
-        <v>0.672</v>
+        <v>0.058</v>
       </c>
       <c r="L15" t="n">
-        <v>0.919</v>
+        <v>0.102</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.392</v>
+        <v>0.023</v>
       </c>
       <c r="C16" t="n">
-        <v>0.386</v>
+        <v>0.014</v>
       </c>
       <c r="D16" t="n">
-        <v>0.571</v>
+        <v>0.045</v>
       </c>
       <c r="E16" t="n">
-        <v>0.863</v>
+        <v>0.166</v>
       </c>
       <c r="F16" t="n">
-        <v>0.252</v>
+        <v>0.047</v>
       </c>
       <c r="G16" t="n">
-        <v>1.081</v>
+        <v>0.217</v>
       </c>
       <c r="H16" t="n">
-        <v>0.671</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.13</v>
       </c>
-      <c r="J16" t="n">
-        <v>0.981</v>
-      </c>
       <c r="K16" t="n">
-        <v>0.711</v>
+        <v>0.055</v>
       </c>
       <c r="L16" t="n">
-        <v>0.728</v>
+        <v>0.092</v>
       </c>
       <c r="M16" t="n">
-        <v>0.753</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.179</v>
+        <v>0.013</v>
       </c>
       <c r="C17" t="n">
-        <v>0.154</v>
+        <v>0.011</v>
       </c>
       <c r="D17" t="n">
-        <v>0.436</v>
+        <v>0.052</v>
       </c>
       <c r="E17" t="n">
-        <v>1.045</v>
+        <v>0.205</v>
       </c>
       <c r="F17" t="n">
-        <v>0.189</v>
+        <v>0.037</v>
       </c>
       <c r="G17" t="n">
-        <v>0.64</v>
+        <v>0.124</v>
       </c>
       <c r="H17" t="n">
-        <v>0.526</v>
+        <v>0.047</v>
       </c>
       <c r="I17" t="n">
-        <v>0.074</v>
+        <v>0.005</v>
       </c>
       <c r="J17" t="n">
-        <v>0.888</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.385</v>
+        <v>0.029</v>
       </c>
       <c r="L17" t="n">
-        <v>0.677</v>
+        <v>0.054</v>
       </c>
       <c r="M17" t="n">
-        <v>0.518</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.013</v>
+        <v>0.002</v>
       </c>
       <c r="C18" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.184</v>
       </c>
       <c r="F18" t="n">
-        <v>0.155</v>
+        <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>0.118</v>
+        <v>0.023</v>
       </c>
       <c r="H18" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.002</v>
       </c>
-      <c r="K18" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.018</v>
-      </c>
       <c r="M18" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.001</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.005</v>
-      </c>
       <c r="E19" t="n">
-        <v>0.888</v>
+        <v>0.174</v>
       </c>
       <c r="F19" t="n">
-        <v>0.141</v>
+        <v>0.028</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09</v>
+        <v>0.017</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.091</v>
+        <v>0.02</v>
       </c>
       <c r="C20" t="n">
-        <v>0.096</v>
+        <v>0.022</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="E20" t="n">
-        <v>0.291</v>
+        <v>0.059</v>
       </c>
       <c r="F20" t="n">
-        <v>0.056</v>
+        <v>0.012</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08</v>
+        <v>0.018</v>
       </c>
       <c r="H20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.023</v>
+        <v>0.001</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.116</v>
+        <v>0.012</v>
       </c>
       <c r="C21" t="n">
-        <v>0.121</v>
+        <v>0.013</v>
       </c>
       <c r="D21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.01</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.228</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.398</v>
+        <v>0.023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.454</v>
+        <v>0.025</v>
       </c>
       <c r="D22" t="n">
-        <v>0.228</v>
+        <v>0.004</v>
       </c>
       <c r="E22" t="n">
-        <v>0.315</v>
+        <v>0.049</v>
       </c>
       <c r="F22" t="n">
-        <v>0.048</v>
+        <v>0.007</v>
       </c>
       <c r="G22" t="n">
-        <v>0.057</v>
+        <v>0.006</v>
       </c>
       <c r="H22" t="n">
-        <v>0.66</v>
+        <v>0.108</v>
       </c>
       <c r="I22" t="n">
-        <v>0.223</v>
+        <v>0.036</v>
       </c>
       <c r="J22" t="n">
-        <v>1.049</v>
+        <v>0.144</v>
       </c>
       <c r="K22" t="n">
-        <v>0.325</v>
+        <v>0.042</v>
       </c>
       <c r="L22" t="n">
-        <v>0.654</v>
+        <v>0.068</v>
       </c>
       <c r="M22" t="n">
-        <v>0.524</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.111</v>
+        <v>0.038</v>
       </c>
       <c r="C23" t="n">
-        <v>0.127</v>
+        <v>0.005</v>
       </c>
       <c r="D23" t="n">
-        <v>0.134</v>
+        <v>0.004</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1</v>
+        <v>0.017</v>
       </c>
       <c r="F23" t="n">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.239</v>
+        <v>0.036</v>
       </c>
       <c r="H23" t="n">
-        <v>0.054</v>
+        <v>0.008</v>
       </c>
       <c r="I23" t="n">
-        <v>0.091</v>
+        <v>0.017</v>
       </c>
       <c r="J23" t="n">
-        <v>0.441</v>
+        <v>0.029</v>
       </c>
       <c r="K23" t="n">
-        <v>0.051</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.158</v>
+        <v>0.024</v>
       </c>
       <c r="M23" t="n">
-        <v>0.171</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.035</v>
+        <v>0.002</v>
       </c>
       <c r="C24" t="n">
-        <v>0.089</v>
+        <v>0.005</v>
       </c>
       <c r="D24" t="n">
-        <v>0.064</v>
+        <v>0.002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.118</v>
+        <v>0.022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.019</v>
+        <v>0.004</v>
       </c>
       <c r="G24" t="n">
-        <v>0.278</v>
+        <v>0.053</v>
       </c>
       <c r="H24" t="n">
-        <v>0.051</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.081</v>
+        <v>0.017</v>
       </c>
       <c r="J24" t="n">
-        <v>0.322</v>
+        <v>0.032</v>
       </c>
       <c r="K24" t="n">
-        <v>0.048</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.13</v>
+        <v>0.025</v>
       </c>
       <c r="M24" t="n">
-        <v>0.132</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.031</v>
+        <v>0.005</v>
       </c>
       <c r="C25" t="n">
-        <v>0.045</v>
+        <v>0.004</v>
       </c>
       <c r="D25" t="n">
-        <v>0.029</v>
+        <v>0.002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.127</v>
+        <v>0.025</v>
       </c>
       <c r="F25" t="n">
-        <v>0.026</v>
+        <v>0.005</v>
       </c>
       <c r="G25" t="n">
-        <v>0.122</v>
+        <v>0.016</v>
       </c>
       <c r="H25" t="n">
-        <v>0.041</v>
+        <v>0.006</v>
       </c>
       <c r="I25" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.058</v>
+        <v>0.006</v>
       </c>
       <c r="K25" t="n">
-        <v>0.054</v>
+        <v>0.002</v>
       </c>
       <c r="L25" t="n">
-        <v>0.094</v>
+        <v>0.002</v>
       </c>
       <c r="M25" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02</v>
+        <v>0.003</v>
       </c>
       <c r="D26" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.091</v>
+        <v>0.018</v>
       </c>
       <c r="F26" t="n">
-        <v>0.023</v>
+        <v>0.005</v>
       </c>
       <c r="G26" t="n">
-        <v>0.164</v>
+        <v>0.031</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.064</v>
+        <v>0.002</v>
       </c>
       <c r="C27" t="n">
-        <v>0.139</v>
+        <v>0.002</v>
       </c>
       <c r="D27" t="n">
-        <v>0.103</v>
+        <v>0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.102</v>
+        <v>0.018</v>
       </c>
       <c r="F27" t="n">
-        <v>0.026</v>
+        <v>0.004</v>
       </c>
       <c r="G27" t="n">
-        <v>0.197</v>
+        <v>0.025</v>
       </c>
       <c r="H27" t="n">
-        <v>0.157</v>
+        <v>0.022</v>
       </c>
       <c r="I27" t="n">
-        <v>0.033</v>
+        <v>0.008</v>
       </c>
       <c r="J27" t="n">
-        <v>0.524</v>
+        <v>0.079</v>
       </c>
       <c r="K27" t="n">
-        <v>0.192</v>
+        <v>0.021</v>
       </c>
       <c r="L27" t="n">
-        <v>0.257</v>
+        <v>0.042</v>
       </c>
       <c r="M27" t="n">
-        <v>0.197</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="28">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.018</v>
       </c>
       <c r="F28" t="n">
-        <v>0.022</v>
+        <v>0.004</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06</v>
+        <v>0.007</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.002</v>
       </c>
-      <c r="C29" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>0.002</v>
       </c>
-      <c r="I29" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.043</v>
-      </c>
       <c r="M29" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.033</v>
+        <v>0.007</v>
       </c>
       <c r="F30" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>158.073</v>
+        <v>82.55800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>202.561</v>
+        <v>68.876</v>
       </c>
       <c r="D2" t="n">
-        <v>219.349</v>
+        <v>130.078</v>
       </c>
       <c r="E2" t="n">
-        <v>263.611</v>
+        <v>233.056</v>
       </c>
       <c r="F2" t="n">
-        <v>111.185</v>
+        <v>106.766</v>
       </c>
       <c r="G2" t="n">
-        <v>176.826</v>
+        <v>149.325</v>
       </c>
       <c r="H2" t="n">
-        <v>217.607</v>
+        <v>83.10599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>222.177</v>
+        <v>97.759</v>
       </c>
       <c r="J2" t="n">
-        <v>265.208</v>
+        <v>87.083</v>
       </c>
       <c r="K2" t="n">
-        <v>228.197</v>
+        <v>62.736</v>
       </c>
       <c r="L2" t="n">
-        <v>224.486</v>
+        <v>58.879</v>
       </c>
       <c r="M2" t="n">
-        <v>299.262</v>
+        <v>59.529</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.113</v>
+        <v>53.215</v>
       </c>
       <c r="C3" t="n">
-        <v>82.932</v>
+        <v>48.462</v>
       </c>
       <c r="D3" t="n">
-        <v>118.555</v>
+        <v>75.45699999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>222.981</v>
+        <v>217.978</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>88.104</v>
+        <v>79.178</v>
       </c>
       <c r="H3" t="n">
-        <v>154.766</v>
+        <v>29.12</v>
       </c>
       <c r="I3" t="n">
-        <v>143.15</v>
+        <v>32.289</v>
       </c>
       <c r="J3" t="n">
-        <v>124.705</v>
+        <v>17.858</v>
       </c>
       <c r="K3" t="n">
-        <v>161.81</v>
+        <v>19.38</v>
       </c>
       <c r="L3" t="n">
-        <v>132.332</v>
+        <v>24.407</v>
       </c>
       <c r="M3" t="n">
-        <v>95.678</v>
+        <v>14.292</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.88</v>
+        <v>30.296</v>
       </c>
       <c r="C4" t="n">
-        <v>29.478</v>
+        <v>22.142</v>
       </c>
       <c r="D4" t="n">
-        <v>53.194</v>
+        <v>44.219</v>
       </c>
       <c r="E4" t="n">
-        <v>203.011</v>
+        <v>197.439</v>
       </c>
       <c r="F4" t="n">
-        <v>74.467</v>
+        <v>73.631</v>
       </c>
       <c r="G4" t="n">
-        <v>67.461</v>
+        <v>61.09</v>
       </c>
       <c r="H4" t="n">
-        <v>10.24</v>
+        <v>1.941</v>
       </c>
       <c r="I4" t="n">
-        <v>5.348</v>
+        <v>5.146</v>
       </c>
       <c r="J4" t="n">
-        <v>21.785</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>43.669</v>
+        <v>6.277</v>
       </c>
       <c r="L4" t="n">
-        <v>11.359</v>
+        <v>3.213</v>
       </c>
       <c r="M4" t="n">
-        <v>21.458</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="5">
@@ -7272,13 +7272,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.606</v>
+        <v>18.813</v>
       </c>
       <c r="C5" t="n">
-        <v>7.36</v>
+        <v>5.454</v>
       </c>
       <c r="D5" t="n">
-        <v>18.859</v>
+        <v>18.59</v>
       </c>
       <c r="E5" t="n">
         <v>196.449</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.803</v>
+        <v>30.072</v>
       </c>
       <c r="C6" t="n">
-        <v>51.545</v>
+        <v>9.172000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>76.074</v>
+        <v>20.748</v>
       </c>
       <c r="E6" t="n">
-        <v>188.479</v>
+        <v>174.943</v>
       </c>
       <c r="F6" t="n">
-        <v>92.52800000000001</v>
+        <v>86.857</v>
       </c>
       <c r="G6" t="n">
-        <v>63.225</v>
+        <v>48.683</v>
       </c>
       <c r="H6" t="n">
-        <v>18.695</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>39.965</v>
+        <v>5.742</v>
       </c>
       <c r="J6" t="n">
-        <v>113.373</v>
+        <v>12.105</v>
       </c>
       <c r="K6" t="n">
-        <v>134.824</v>
+        <v>11.65</v>
       </c>
       <c r="L6" t="n">
-        <v>92.22499999999999</v>
+        <v>8.004</v>
       </c>
       <c r="M6" t="n">
-        <v>107.489</v>
+        <v>9.208</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168.635</v>
+        <v>35.768</v>
       </c>
       <c r="C7" t="n">
-        <v>193.065</v>
+        <v>17.029</v>
       </c>
       <c r="D7" t="n">
-        <v>138.086</v>
+        <v>16.804</v>
       </c>
       <c r="E7" t="n">
-        <v>129.949</v>
+        <v>83.729</v>
       </c>
       <c r="F7" t="n">
-        <v>182.741</v>
+        <v>159.108</v>
       </c>
       <c r="G7" t="n">
-        <v>92.735</v>
+        <v>42.475</v>
       </c>
       <c r="H7" t="n">
-        <v>448.705</v>
+        <v>433.844</v>
       </c>
       <c r="I7" t="n">
-        <v>328.085</v>
+        <v>327.903</v>
       </c>
       <c r="J7" t="n">
-        <v>406.981</v>
+        <v>350.872</v>
       </c>
       <c r="K7" t="n">
-        <v>369.421</v>
+        <v>367.528</v>
       </c>
       <c r="L7" t="n">
-        <v>345.876</v>
+        <v>259.606</v>
       </c>
       <c r="M7" t="n">
-        <v>417.21</v>
+        <v>263.175</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.154999999999999</v>
+        <v>8.714</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7408,19 +7408,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.474</v>
+        <v>75.10899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>142.34</v>
+        <v>139.739</v>
       </c>
       <c r="G8" t="n">
-        <v>27.36</v>
+        <v>25.086</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.15</v>
+        <v>1.001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7442,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.97</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>25.829</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>24.985</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>59.359</v>
+        <v>38.32</v>
       </c>
       <c r="F9" t="n">
-        <v>104.804</v>
+        <v>89.896</v>
       </c>
       <c r="G9" t="n">
-        <v>20.287</v>
+        <v>4.764</v>
       </c>
       <c r="H9" t="n">
-        <v>20.83</v>
+        <v>4.508</v>
       </c>
       <c r="I9" t="n">
-        <v>89.836</v>
+        <v>11.693</v>
       </c>
       <c r="J9" t="n">
-        <v>42.446</v>
+        <v>7.54</v>
       </c>
       <c r="K9" t="n">
-        <v>162.634</v>
+        <v>13.177</v>
       </c>
       <c r="L9" t="n">
-        <v>77.07599999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>21.573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.093</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -7494,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>42.028</v>
+        <v>32.784</v>
       </c>
       <c r="F10" t="n">
-        <v>75.90600000000001</v>
+        <v>70.959</v>
       </c>
       <c r="G10" t="n">
-        <v>4.057</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.029</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11.198</v>
+        <v>6.068</v>
       </c>
       <c r="J10" t="n">
-        <v>7.128</v>
+        <v>2.512</v>
       </c>
       <c r="K10" t="n">
-        <v>29.861</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.333</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>37.906</v>
+        <v>34.551</v>
       </c>
       <c r="F11" t="n">
-        <v>64.315</v>
+        <v>62.546</v>
       </c>
       <c r="G11" t="n">
-        <v>1.867</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.904</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.736</v>
+        <v>0.263</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7580,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.804</v>
+        <v>22.546</v>
       </c>
       <c r="F12" t="n">
-        <v>49.017</v>
+        <v>47.975</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7614,37 +7614,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13.059</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4.394</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>16.173</v>
+        <v>1.892</v>
       </c>
       <c r="F13" t="n">
-        <v>39.507</v>
+        <v>28.268</v>
       </c>
       <c r="G13" t="n">
-        <v>1.201</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7.612</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>15.358</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>25.682</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>43.799</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>23.107</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7675,13 +7675,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.028</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4.396</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4.847</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>219.074</v>
+        <v>137.287</v>
       </c>
       <c r="C15" t="n">
-        <v>230.359</v>
+        <v>102.307</v>
       </c>
       <c r="D15" t="n">
-        <v>240.287</v>
+        <v>127.891</v>
       </c>
       <c r="E15" t="n">
-        <v>243.71</v>
+        <v>219.577</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>249.007</v>
+        <v>232.365</v>
       </c>
       <c r="H15" t="n">
-        <v>150.226</v>
+        <v>137.658</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>207.203</v>
+        <v>122.922</v>
       </c>
       <c r="K15" t="n">
-        <v>211.01</v>
+        <v>187.929</v>
       </c>
       <c r="L15" t="n">
-        <v>242.19</v>
+        <v>231.721</v>
       </c>
       <c r="M15" t="n">
-        <v>249.169</v>
+        <v>223.887</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>321.082</v>
+        <v>183.488</v>
       </c>
       <c r="C16" t="n">
-        <v>353.164</v>
+        <v>150.023</v>
       </c>
       <c r="D16" t="n">
-        <v>368.998</v>
+        <v>238.461</v>
       </c>
       <c r="E16" t="n">
-        <v>392.77</v>
+        <v>377.251</v>
       </c>
       <c r="F16" t="n">
-        <v>209.35</v>
+        <v>201.858</v>
       </c>
       <c r="G16" t="n">
         <v>437.584</v>
       </c>
       <c r="H16" t="n">
-        <v>361.504</v>
+        <v>332.719</v>
       </c>
       <c r="I16" t="n">
-        <v>171.377</v>
+        <v>145.556</v>
       </c>
       <c r="J16" t="n">
-        <v>429.552</v>
+        <v>406.512</v>
       </c>
       <c r="K16" t="n">
-        <v>377.352</v>
+        <v>334.722</v>
       </c>
       <c r="L16" t="n">
-        <v>369.762</v>
+        <v>344.066</v>
       </c>
       <c r="M16" t="n">
-        <v>383.425</v>
+        <v>360.896</v>
       </c>
     </row>
     <row r="17">
@@ -7784,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>218.493</v>
+        <v>125.077</v>
       </c>
       <c r="C17" t="n">
-        <v>203.199</v>
+        <v>112.356</v>
       </c>
       <c r="D17" t="n">
-        <v>311.59</v>
+        <v>228.485</v>
       </c>
       <c r="E17" t="n">
-        <v>420.37</v>
+        <v>416.187</v>
       </c>
       <c r="F17" t="n">
-        <v>178.899</v>
+        <v>177.486</v>
       </c>
       <c r="G17" t="n">
-        <v>330.48</v>
+        <v>323.78</v>
       </c>
       <c r="H17" t="n">
-        <v>335.315</v>
+        <v>247.612</v>
       </c>
       <c r="I17" t="n">
-        <v>140.185</v>
+        <v>88.39100000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>426.081</v>
+        <v>391.954</v>
       </c>
       <c r="K17" t="n">
-        <v>282.23</v>
+        <v>222.787</v>
       </c>
       <c r="L17" t="n">
-        <v>376.867</v>
+        <v>285.061</v>
       </c>
       <c r="M17" t="n">
-        <v>346.912</v>
+        <v>233.434</v>
       </c>
     </row>
     <row r="18">
@@ -7827,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.49</v>
+        <v>45.091</v>
       </c>
       <c r="C18" t="n">
-        <v>30.17</v>
+        <v>23.916</v>
       </c>
       <c r="D18" t="n">
-        <v>48.345</v>
+        <v>43.104</v>
       </c>
       <c r="E18" t="n">
-        <v>398.884</v>
+        <v>394.945</v>
       </c>
       <c r="F18" t="n">
-        <v>162.699</v>
+        <v>160.31</v>
       </c>
       <c r="G18" t="n">
-        <v>141.915</v>
+        <v>140.235</v>
       </c>
       <c r="H18" t="n">
-        <v>32.366</v>
+        <v>11.161</v>
       </c>
       <c r="I18" t="n">
-        <v>10.028</v>
+        <v>7.853</v>
       </c>
       <c r="J18" t="n">
-        <v>20.694</v>
+        <v>17.997</v>
       </c>
       <c r="K18" t="n">
-        <v>35.773</v>
+        <v>15.091</v>
       </c>
       <c r="L18" t="n">
-        <v>80.483</v>
+        <v>75.95</v>
       </c>
       <c r="M18" t="n">
-        <v>36.838</v>
+        <v>31.267</v>
       </c>
     </row>
     <row r="19">
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.515</v>
+        <v>20.448</v>
       </c>
       <c r="C19" t="n">
-        <v>11.697</v>
+        <v>6.977</v>
       </c>
       <c r="D19" t="n">
-        <v>29.897</v>
+        <v>26.126</v>
       </c>
       <c r="E19" t="n">
-        <v>386.918</v>
+        <v>383.979</v>
       </c>
       <c r="F19" t="n">
-        <v>154.628</v>
+        <v>154.366</v>
       </c>
       <c r="G19" t="n">
-        <v>124.163</v>
+        <v>121.046</v>
       </c>
       <c r="H19" t="n">
-        <v>3.76</v>
+        <v>0.65</v>
       </c>
       <c r="I19" t="n">
-        <v>3.267</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.56</v>
+        <v>1.539</v>
       </c>
       <c r="K19" t="n">
-        <v>7.721</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.242</v>
+        <v>8.343</v>
       </c>
       <c r="M19" t="n">
-        <v>7.12</v>
+        <v>3.769</v>
       </c>
     </row>
     <row r="20">
@@ -7940,7 +7940,7 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>79.911</v>
+        <v>37.744</v>
       </c>
       <c r="L20" t="n">
         <v>7.176</v>
@@ -7956,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>158.906</v>
+        <v>111.631</v>
       </c>
       <c r="C21" t="n">
-        <v>161.693</v>
+        <v>115.156</v>
       </c>
       <c r="D21" t="n">
-        <v>53.392</v>
+        <v>24.665</v>
       </c>
       <c r="E21" t="n">
-        <v>214.245</v>
+        <v>206.255</v>
       </c>
       <c r="F21" t="n">
-        <v>84.849</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>87.849</v>
+        <v>86.164</v>
       </c>
       <c r="H21" t="n">
-        <v>315.967</v>
+        <v>142.754</v>
       </c>
       <c r="I21" t="n">
-        <v>84.494</v>
+        <v>6.613</v>
       </c>
       <c r="J21" t="n">
-        <v>312.499</v>
+        <v>76.325</v>
       </c>
       <c r="K21" t="n">
-        <v>218.524</v>
+        <v>177.424</v>
       </c>
       <c r="L21" t="n">
-        <v>181.771</v>
+        <v>26.604</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>321.763</v>
+        <v>186.79</v>
       </c>
       <c r="C22" t="n">
-        <v>341.681</v>
+        <v>195.41</v>
       </c>
       <c r="D22" t="n">
-        <v>296.783</v>
+        <v>92.122</v>
       </c>
       <c r="E22" t="n">
-        <v>259.053</v>
+        <v>208.171</v>
       </c>
       <c r="F22" t="n">
-        <v>104.325</v>
+        <v>78.798</v>
       </c>
       <c r="G22" t="n">
-        <v>126.244</v>
+        <v>76.247</v>
       </c>
       <c r="H22" t="n">
-        <v>351.305</v>
+        <v>348.007</v>
       </c>
       <c r="I22" t="n">
         <v>218.601</v>
       </c>
       <c r="J22" t="n">
-        <v>447.263</v>
+        <v>424.852</v>
       </c>
       <c r="K22" t="n">
-        <v>245.673</v>
+        <v>236.359</v>
       </c>
       <c r="L22" t="n">
-        <v>356.592</v>
+        <v>337.703</v>
       </c>
       <c r="M22" t="n">
-        <v>372.582</v>
+        <v>191.242</v>
       </c>
     </row>
     <row r="23">
@@ -8045,19 +8045,19 @@
         <v>68.547</v>
       </c>
       <c r="C23" t="n">
-        <v>31.235</v>
+        <v>19.376</v>
       </c>
       <c r="D23" t="n">
-        <v>33.844</v>
+        <v>18.182</v>
       </c>
       <c r="E23" t="n">
-        <v>25.379</v>
+        <v>22.371</v>
       </c>
       <c r="F23" t="n">
-        <v>9.702</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>129.662</v>
+        <v>104.572</v>
       </c>
       <c r="H23" t="n">
         <v>21.522</v>
@@ -8066,16 +8066,16 @@
         <v>26.488</v>
       </c>
       <c r="J23" t="n">
-        <v>56.446</v>
+        <v>41.032</v>
       </c>
       <c r="K23" t="n">
         <v>20.712</v>
       </c>
       <c r="L23" t="n">
-        <v>32.653</v>
+        <v>32.652</v>
       </c>
       <c r="M23" t="n">
-        <v>35.369</v>
+        <v>35.127</v>
       </c>
     </row>
     <row r="24">
@@ -8085,22 +8085,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.163</v>
+        <v>10.954</v>
       </c>
       <c r="C24" t="n">
-        <v>26.155</v>
+        <v>16.375</v>
       </c>
       <c r="D24" t="n">
-        <v>22.878</v>
+        <v>12.773</v>
       </c>
       <c r="E24" t="n">
-        <v>26.181</v>
+        <v>25.242</v>
       </c>
       <c r="F24" t="n">
-        <v>10.472</v>
+        <v>10.442</v>
       </c>
       <c r="G24" t="n">
-        <v>126.35</v>
+        <v>123.314</v>
       </c>
       <c r="H24" t="n">
         <v>20.425</v>
@@ -8109,7 +8109,7 @@
         <v>25.756</v>
       </c>
       <c r="J24" t="n">
-        <v>47.703</v>
+        <v>45.773</v>
       </c>
       <c r="K24" t="n">
         <v>20.024</v>
@@ -8128,40 +8128,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.675</v>
+        <v>12.981</v>
       </c>
       <c r="C25" t="n">
-        <v>17.848</v>
+        <v>12.953</v>
       </c>
       <c r="D25" t="n">
-        <v>14.61</v>
+        <v>9.634</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>12.027</v>
+        <v>12.001</v>
       </c>
       <c r="G25" t="n">
-        <v>93.524</v>
+        <v>72.93600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>19.045</v>
+        <v>18.957</v>
       </c>
       <c r="I25" t="n">
-        <v>11.804</v>
+        <v>4.237</v>
       </c>
       <c r="J25" t="n">
-        <v>25.778</v>
+        <v>22.559</v>
       </c>
       <c r="K25" t="n">
-        <v>23.603</v>
+        <v>16.936</v>
       </c>
       <c r="L25" t="n">
-        <v>27.658</v>
+        <v>16.135</v>
       </c>
       <c r="M25" t="n">
-        <v>18.936</v>
+        <v>7.419</v>
       </c>
     </row>
     <row r="26">
@@ -8174,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.272</v>
+        <v>11.094</v>
       </c>
       <c r="D26" t="n">
-        <v>4.246</v>
+        <v>3.837</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8186,22 +8186,22 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>96.486</v>
+        <v>94.541</v>
       </c>
       <c r="H26" t="n">
-        <v>1.428</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.559</v>
+        <v>0.706</v>
       </c>
       <c r="J26" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.274</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>6.246</v>
+        <v>0.322</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8214,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23.043</v>
+        <v>12.649</v>
       </c>
       <c r="C27" t="n">
-        <v>39.001</v>
+        <v>13.973</v>
       </c>
       <c r="D27" t="n">
-        <v>33.84</v>
+        <v>11.88</v>
       </c>
       <c r="E27" t="n">
-        <v>25.578</v>
+        <v>22.689</v>
       </c>
       <c r="F27" t="n">
-        <v>12.639</v>
+        <v>11.417</v>
       </c>
       <c r="G27" t="n">
-        <v>123.905</v>
+        <v>89.908</v>
       </c>
       <c r="H27" t="n">
-        <v>33.252</v>
+        <v>32.159</v>
       </c>
       <c r="I27" t="n">
         <v>18.642</v>
       </c>
       <c r="J27" t="n">
-        <v>58.309</v>
+        <v>56.969</v>
       </c>
       <c r="K27" t="n">
-        <v>37.326</v>
+        <v>36.332</v>
       </c>
       <c r="L27" t="n">
-        <v>43.613</v>
+        <v>43.193</v>
       </c>
       <c r="M27" t="n">
-        <v>36.754</v>
+        <v>34.777</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.559</v>
+        <v>2.543</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,7 +8272,7 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>65.71599999999999</v>
+        <v>51.413</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -8300,40 +8300,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.509</v>
+        <v>2.112</v>
       </c>
       <c r="C29" t="n">
-        <v>5.785</v>
+        <v>1.371</v>
       </c>
       <c r="D29" t="n">
-        <v>3.696</v>
+        <v>0.36</v>
       </c>
       <c r="E29" t="n">
-        <v>22.439</v>
+        <v>21.824</v>
       </c>
       <c r="F29" t="n">
-        <v>10.923</v>
+        <v>10.523</v>
       </c>
       <c r="G29" t="n">
-        <v>74.367</v>
+        <v>65.325</v>
       </c>
       <c r="H29" t="n">
-        <v>5.992</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>7.339</v>
+        <v>1.949</v>
       </c>
       <c r="J29" t="n">
-        <v>16.438</v>
+        <v>14.104</v>
       </c>
       <c r="K29" t="n">
-        <v>11.718</v>
+        <v>6.626</v>
       </c>
       <c r="L29" t="n">
-        <v>21.617</v>
+        <v>13.898</v>
       </c>
       <c r="M29" t="n">
-        <v>5.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.498707332900001e-05</v>
+        <v>6.815823364000001e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.103095872100001e-05</v>
+        <v>4.743903376000001e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.811398380099999e-05</v>
+        <v>1.6920286084e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.949075932099998e-05</v>
+        <v>5.431509913600001e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2362104225e-05</v>
+        <v>1.1398978756e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1267434276e-05</v>
+        <v>2.229795562499999e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7352806449e-05</v>
+        <v>6.906607236e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.936261932899999e-05</v>
+        <v>9.556822080999999e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.033528326399999e-05</v>
+        <v>7.583448888999999e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.207387080900001e-05</v>
+        <v>3.935805696e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.0393964196e-05</v>
+        <v>3.466736641e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>8.955774464400001e-05</v>
+        <v>3.543701841000001e-06</v>
       </c>
     </row>
     <row r="3">
@@ -8510,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.101640769e-06</v>
+        <v>2.831836225000001e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.877716624000001e-06</v>
+        <v>2.348565444e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4055288025e-05</v>
+        <v>5.693758849e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9720526361e-05</v>
+        <v>4.7514408484e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.762314816e-06</v>
+        <v>6.269155684e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3952514756e-05</v>
+        <v>8.479744e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>2.04919225e-05</v>
+        <v>1.042579521e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5551337025e-05</v>
+        <v>3.189081639999999e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.61824761e-05</v>
+        <v>3.755843999999999e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7511758224e-05</v>
+        <v>5.95701649e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>9.154279684e-06</v>
+        <v>2.04261264e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7539344e-06</v>
+        <v>9.17847616e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>8.68952484e-07</v>
+        <v>4.90268164e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.829601636000001e-06</v>
+        <v>1.955319961e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1213466121e-05</v>
+        <v>3.8982158721e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.545334089e-06</v>
+        <v>5.421524161e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.550986520999999e-06</v>
+        <v>3.731988100000001e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.048576e-07</v>
+        <v>3.767481e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.860110399999999e-08</v>
+        <v>2.648131599999999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.745862249999999e-07</v>
+        <v>1.156e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.906981561e-06</v>
+        <v>3.940072900000001e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29026881e-07</v>
+        <v>1.0323369e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.604457639999999e-07</v>
+        <v>1.0640644e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8596,13 +8596,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.246072360000001e-07</v>
+        <v>3.53928969e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>5.416960000000001e-08</v>
+        <v>2.9746116e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.55661881e-07</v>
+        <v>3.455880999999999e-07</v>
       </c>
       <c r="E5" t="n">
         <v>3.8592209601e-05</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.022942809000001e-06</v>
+        <v>9.043251839999999e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.656887025e-06</v>
+        <v>8.412558400000002e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.787253476000001e-06</v>
+        <v>4.304795040000001e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5524333441e-05</v>
+        <v>3.060505324900001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.561430784000001e-06</v>
+        <v>7.544138449000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.997400625e-06</v>
+        <v>2.370034489e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>3.49503025e-07</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.597201225e-06</v>
+        <v>3.297056399999999e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2853437129e-05</v>
+        <v>1.46531025e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8177510976e-05</v>
+        <v>1.357225e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>8.505450624999998e-06</v>
+        <v>6.406401599999998e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1553885121e-05</v>
+        <v>8.478726400000002e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8680,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.47925440833333e-06</v>
+        <v>4.264499413333334e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2424698075e-05</v>
+        <v>9.666228033333332e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.355914465333335e-06</v>
+        <v>9.412480533333332e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.628914200333334e-06</v>
+        <v>2.336848480333333e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.113142436033334e-05</v>
+        <v>8.438451887999999e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.866593408333333e-06</v>
+        <v>6.013752083333332e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.711205900833333e-05</v>
+        <v>6.274020544533334e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.587992240833332e-05</v>
+        <v>3.5840125803e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.521117812033333e-05</v>
+        <v>4.103705346133334e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.549062508033333e-05</v>
+        <v>4.502561026133334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.987673579199999e-05</v>
+        <v>2.246509174533333e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.802139469999999e-05</v>
+        <v>2.3087026875e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.3814025e-08</v>
+        <v>7.593379600000002e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8732,19 +8732,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.696324676e-06</v>
+        <v>5.641361881e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.02606756e-05</v>
+        <v>1.9526988121e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.485696e-07</v>
+        <v>6.293073959999999e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.622500000000001e-09</v>
+        <v>1.002001e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.741003e-07</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.223790803333334e-07</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.080834083333333e-07</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.174496960333333e-06</v>
+        <v>4.894741333333333e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.661292805333334e-06</v>
+        <v>2.693763605333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>1.371874563333333e-07</v>
+        <v>7.565232e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.446296333333333e-07</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>2.690168965333333e-06</v>
+        <v>4.557541633333334e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.005543053333333e-07</v>
+        <v>1.895053333333333e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.816605985333331e-06</v>
+        <v>5.787777633333332e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.980236591999999e-06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.55131443e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.982163333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>5.887842613333331e-07</v>
+        <v>3.582635520000001e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.920573612e-06</v>
+        <v>1.678393227e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>5.486416333333336e-09</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.372280333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.179840133333333e-08</v>
+        <v>1.227354133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6936128e-08</v>
+        <v>2.103381333333333e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>2.972264403333334e-07</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.702963e-09</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8861,22 +8861,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.789549453333333e-07</v>
+        <v>3.979238670000001e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.378806408333333e-06</v>
+        <v>1.304000705333334e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.161896333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.125333333333334e-12</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.811072e-09</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652565333333334e-09</v>
+        <v>2.305633333333334e-11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.733408053333333e-07</v>
+        <v>1.694407053333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>8.008887630000001e-07</v>
+        <v>7.672002083333336e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8938,37 +8938,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.684582699999999e-08</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6.435745333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.718864299999999e-08</v>
+        <v>1.193221333333333e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>5.20267683e-07</v>
+        <v>2.663599413333334e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>4.808003333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.931418133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7.862272133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.198550413333333e-07</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>6.394508003333333e-07</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.779778163333333e-07</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -8999,13 +8999,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.408261333333332e-09</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>6.441605333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.831136333333335e-09</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.7993417476e-05</v>
+        <v>1.8847720369e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>5.3065268881e-05</v>
+        <v>1.0466722249e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7737842369e-05</v>
+        <v>1.6356107881e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>5.93945641e-05</v>
+        <v>4.8214058929e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>6.200448604900001e-05</v>
+        <v>5.399349322500001e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2567851076e-05</v>
+        <v>1.894972496399999e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>4.2933083209e-05</v>
+        <v>1.5109818084e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.45252201e-05</v>
+        <v>3.531730904100001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.86559961e-05</v>
+        <v>5.3694621841e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.2085190561e-05</v>
+        <v>5.0125388769e-05</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.436455024133332e-05</v>
+        <v>1.122261538133334e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>4.157493696533333e-05</v>
+        <v>7.502300176333332e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>4.538650800133333e-05</v>
+        <v>1.8954549507e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>5.142275763333333e-05</v>
+        <v>4.743943900033334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.460914083333333e-05</v>
+        <v>1.3582217388e-05</v>
       </c>
       <c r="G16" t="n">
         <v>6.382658568533334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.356171400533333e-05</v>
+        <v>3.690064432033333e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>9.790025376333333e-06</v>
+        <v>7.062183045333335e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>6.150497356800002e-05</v>
+        <v>5.5084002048e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.746484396799999e-05</v>
+        <v>3.734627242799999e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.557464554799999e-05</v>
+        <v>3.946047078533333e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.900491020833333e-05</v>
+        <v>4.341530760533333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -9108,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5913063683e-05</v>
+        <v>5.214751976333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3763277867e-05</v>
+        <v>4.207956912e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>3.236277603333333e-05</v>
+        <v>1.740179840833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.890364563333334e-05</v>
+        <v>5.773720632300001e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0668284067e-05</v>
+        <v>1.0500426732e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.64056768e-05</v>
+        <v>3.494449613333332e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.747871640833333e-05</v>
+        <v>2.043723418133333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>6.550611408333334e-06</v>
+        <v>2.604322960333334e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>6.051500618700001e-05</v>
+        <v>5.120931270533334e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.655125763333334e-05</v>
+        <v>1.654468245633333e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4.734291189633333e-05</v>
+        <v>2.708659124033332e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.011597858133333e-05</v>
+        <v>1.816381078533333e-05</v>
       </c>
     </row>
     <row r="18">
@@ -9151,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.164200333333334e-07</v>
+        <v>6.777327603333333e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>3.034096333333334e-07</v>
+        <v>1.90658352e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.790796749999999e-07</v>
+        <v>6.193182719999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.303614848533333e-05</v>
+        <v>5.199385100833333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.823654867000001e-06</v>
+        <v>8.566432033333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.713289074999999e-06</v>
+        <v>6.555285075000002e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>3.491859853333333e-07</v>
+        <v>4.152264033333332e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>3.352026133333334e-08</v>
+        <v>2.055653633333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.42747212e-07</v>
+        <v>1.07964003e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>4.265691763333335e-07</v>
+        <v>7.591276033333333e-08</v>
       </c>
       <c r="L18" t="n">
-        <v>2.159171096333333e-06</v>
+        <v>1.922800833333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>4.523460813333334e-07</v>
+        <v>3.258750963333332e-07</v>
       </c>
     </row>
     <row r="19">
@@ -9194,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.343484083333333e-07</v>
+        <v>1.39373568e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>4.5606603e-08</v>
+        <v>1.622617633333334e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.979435363333333e-07</v>
+        <v>2.275226253333333e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.990184624133333e-05</v>
+        <v>4.914662414699999e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.969939461333333e-06</v>
+        <v>7.942953985333334e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.138816856333333e-06</v>
+        <v>4.884044705333334e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>4.712533333333333e-09</v>
+        <v>1.408333333333333e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>3.557763e-09</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.224533333333334e-09</v>
+        <v>7.895070000000001e-10</v>
       </c>
       <c r="K19" t="n">
-        <v>1.987128033333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4966188e-08</v>
+        <v>2.3201883e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>1.689813333333334e-08</v>
+        <v>4.735120333333334e-09</v>
       </c>
     </row>
     <row r="20">
@@ -9264,7 +9264,7 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>2.128589307e-06</v>
+        <v>4.748698453333333e-07</v>
       </c>
       <c r="L20" t="n">
         <v>1.7164992e-08</v>
@@ -9280,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.417038945333335e-06</v>
+        <v>4.153826720333333e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.714875416333335e-06</v>
+        <v>4.420301445333334e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>9.502352213333334e-07</v>
+        <v>2.027874083333333e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5300306675e-05</v>
+        <v>1.418037500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399784267000001e-06</v>
+        <v>2.367256661333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.572482267000001e-06</v>
+        <v>2.474744965333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.327838169633334e-05</v>
+        <v>6.792901505333333e-06</v>
       </c>
       <c r="I21" t="n">
-        <v>2.379745345333333e-06</v>
+        <v>1.457725633333334e-08</v>
       </c>
       <c r="J21" t="n">
-        <v>3.255187500033334e-05</v>
+        <v>1.941835208333333e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>1.591757952533333e-05</v>
+        <v>1.049309192533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.101356548033333e-05</v>
+        <v>2.35924272e-07</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.451047605633332e-05</v>
+        <v>1.163016803333333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.891530192033332e-05</v>
+        <v>1.272835603333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>2.936004969633334e-05</v>
+        <v>2.828820961333333e-06</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2369485603e-05</v>
+        <v>1.444505508033333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>3.627901875e-06</v>
+        <v>2.069708268e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>5.312515845333332e-06</v>
+        <v>1.937868336333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.113840100833334e-05</v>
+        <v>4.036962401633334e-05</v>
       </c>
       <c r="I22" t="n">
         <v>1.5928799067e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>6.668139705633332e-05</v>
+        <v>6.016640730133331e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0118407643e-05</v>
+        <v>1.862185896033334e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.238595148799999e-05</v>
+        <v>3.801443873633333e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>4.627244890799999e-05</v>
+        <v>1.219116752133333e-05</v>
       </c>
     </row>
     <row r="23">
@@ -9369,19 +9369,19 @@
         <v>4.698691208999999e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>9.756252249999999e-06</v>
+        <v>3.75429376e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>1.145416336e-05</v>
+        <v>3.30585124e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>6.440936410000001e-06</v>
+        <v>5.00461641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.412880400000001e-07</v>
+        <v>8.184820900000002e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6812234244e-05</v>
+        <v>1.0935303184e-05</v>
       </c>
       <c r="H23" t="n">
         <v>4.63196484e-06</v>
@@ -9390,16 +9390,16 @@
         <v>7.016141440000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>3.186150915999999e-05</v>
+        <v>1.683625024e-05</v>
       </c>
       <c r="K23" t="n">
         <v>4.28986944e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066218409e-05</v>
+        <v>1.066153104e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>1.250966161e-05</v>
+        <v>1.233906129000001e-05</v>
       </c>
     </row>
     <row r="24">
@@ -9409,22 +9409,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.61242569e-06</v>
+        <v>1.19990116e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>6.840840250000001e-06</v>
+        <v>2.68140625e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>5.23402884e-06</v>
+        <v>1.63149529e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.85444761e-06</v>
+        <v>6.37158564e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09662784e-06</v>
+        <v>1.09035364e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.59643225e-05</v>
+        <v>1.5206342596e-05</v>
       </c>
       <c r="H24" t="n">
         <v>4.171806250000001e-06</v>
@@ -9433,7 +9433,7 @@
         <v>6.633715360000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.275576209e-05</v>
+        <v>2.095167529e-05</v>
       </c>
       <c r="K24" t="n">
         <v>4.00960576e-06</v>
@@ -9452,40 +9452,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.87005625e-06</v>
+        <v>1.68506361e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.18551104e-06</v>
+        <v>1.67780209e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.134521e-06</v>
+        <v>9.281395600000001e-07</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44648729e-06</v>
+        <v>1.44024001e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>8.746738576e-06</v>
+        <v>5.319660096e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.627120250000001e-06</v>
+        <v>3.593678490000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.39334416e-06</v>
+        <v>1.7952169e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>6.645052839999999e-06</v>
+        <v>5.089084810000001e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>5.571016090000001e-06</v>
+        <v>2.86828096e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>7.64964964e-06</v>
+        <v>2.60338225e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>3.58572096e-06</v>
+        <v>5.504156099999999e-07</v>
       </c>
     </row>
     <row r="26">
@@ -9498,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.27057984e-06</v>
+        <v>1.23076836e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.802851600000001e-07</v>
+        <v>1.4722569e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9510,22 +9510,22 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.309548195999999e-06</v>
+        <v>8.938000681e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>2.039184e-08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.430480999999999e-08</v>
+        <v>4.984359999999999e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>9.35089e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.623076e-08</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3.901251600000001e-07</v>
+        <v>1.03684e-09</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9538,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.309798490000001e-06</v>
+        <v>1.59997201e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.521078001e-05</v>
+        <v>1.95244729e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1451456e-05</v>
+        <v>1.411344e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>6.542340840000001e-06</v>
+        <v>5.147907210000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.59744321e-06</v>
+        <v>1.30347889e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5352449025e-05</v>
+        <v>8.083448463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>1.105695504e-05</v>
+        <v>1.034201281e-05</v>
       </c>
       <c r="I27" t="n">
         <v>3.47524164e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.399939481e-05</v>
+        <v>3.245466961e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.393230276e-05</v>
+        <v>1.320014224e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.902093769e-05</v>
+        <v>1.865635249e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.350856516e-05</v>
+        <v>1.209439729e-05</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.548481000000001e-08</v>
+        <v>6.466849e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,7 +9596,7 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>4.318592655999999e-06</v>
+        <v>2.643296568999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -9624,40 +9624,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.0331081e-07</v>
+        <v>4.460544e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>3.3466225e-07</v>
+        <v>1.879641e-08</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3660416e-07</v>
+        <v>1.296e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>5.03508721e-06</v>
+        <v>4.762869760000001e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.19311929e-06</v>
+        <v>1.10733529e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.530450689e-06</v>
+        <v>4.267355625000001e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5904064e-07</v>
+        <v>6.577210000000002e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>5.3860921e-07</v>
+        <v>3.798601e-08</v>
       </c>
       <c r="J29" t="n">
-        <v>2.70207844e-06</v>
+        <v>1.98922816e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>1.37311524e-06</v>
+        <v>4.3903876e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>4.67294689e-06</v>
+        <v>1.93154404e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>2.946318399999999e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>158.073</v>
+        <v>82.55800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>202.561</v>
+        <v>68.876</v>
       </c>
       <c r="D2" t="n">
-        <v>219.349</v>
+        <v>130.078</v>
       </c>
       <c r="E2" t="n">
-        <v>263.611</v>
+        <v>233.056</v>
       </c>
       <c r="F2" t="n">
-        <v>111.17</v>
+        <v>106.766</v>
       </c>
       <c r="G2" t="n">
-        <v>176.826</v>
+        <v>149.325</v>
       </c>
       <c r="H2" t="n">
-        <v>217.607</v>
+        <v>83.10599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>222.177</v>
+        <v>97.759</v>
       </c>
       <c r="J2" t="n">
-        <v>265.208</v>
+        <v>87.083</v>
       </c>
       <c r="K2" t="n">
-        <v>228.197</v>
+        <v>62.736</v>
       </c>
       <c r="L2" t="n">
-        <v>224.486</v>
+        <v>58.879</v>
       </c>
       <c r="M2" t="n">
-        <v>299.262</v>
+        <v>59.529</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.851</v>
+        <v>53.215</v>
       </c>
       <c r="C3" t="n">
-        <v>82.753</v>
+        <v>48.462</v>
       </c>
       <c r="D3" t="n">
-        <v>118.555</v>
+        <v>75.45699999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>222.981</v>
+        <v>216.43</v>
       </c>
       <c r="F3" t="n">
-        <v>75.026</v>
+        <v>75.63</v>
       </c>
       <c r="G3" t="n">
-        <v>88.104</v>
+        <v>79.178</v>
       </c>
       <c r="H3" t="n">
-        <v>139.997</v>
+        <v>29.12</v>
       </c>
       <c r="I3" t="n">
-        <v>132.312</v>
+        <v>32.289</v>
       </c>
       <c r="J3" t="n">
-        <v>119.451</v>
+        <v>17.858</v>
       </c>
       <c r="K3" t="n">
-        <v>160.115</v>
+        <v>19.38</v>
       </c>
       <c r="L3" t="n">
-        <v>125.661</v>
+        <v>24.407</v>
       </c>
       <c r="M3" t="n">
-        <v>80.411</v>
+        <v>14.292</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.88</v>
+        <v>30.296</v>
       </c>
       <c r="C4" t="n">
-        <v>29.478</v>
+        <v>22.142</v>
       </c>
       <c r="D4" t="n">
-        <v>53.194</v>
+        <v>44.219</v>
       </c>
       <c r="E4" t="n">
-        <v>203.011</v>
+        <v>197.439</v>
       </c>
       <c r="F4" t="n">
-        <v>74.467</v>
+        <v>73.593</v>
       </c>
       <c r="G4" t="n">
-        <v>67.461</v>
+        <v>61.09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.607</v>
+        <v>1.941</v>
       </c>
       <c r="I4" t="n">
-        <v>2.039</v>
+        <v>5.134</v>
       </c>
       <c r="J4" t="n">
-        <v>21.629</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>43.669</v>
+        <v>6.277</v>
       </c>
       <c r="L4" t="n">
-        <v>11.329</v>
+        <v>3.213</v>
       </c>
       <c r="M4" t="n">
-        <v>21.05</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.606</v>
+        <v>18.813</v>
       </c>
       <c r="C5" t="n">
-        <v>7.36</v>
+        <v>5.273</v>
       </c>
       <c r="D5" t="n">
-        <v>18.859</v>
+        <v>18.073</v>
       </c>
       <c r="E5" t="n">
-        <v>195.469</v>
+        <v>195.367</v>
       </c>
       <c r="F5" t="n">
-        <v>93.045</v>
+        <v>94.544</v>
       </c>
       <c r="G5" t="n">
-        <v>75.919</v>
+        <v>78.178</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.803</v>
+        <v>30.072</v>
       </c>
       <c r="C6" t="n">
-        <v>51.545</v>
+        <v>9.172000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>76.074</v>
+        <v>20.748</v>
       </c>
       <c r="E6" t="n">
-        <v>188.479</v>
+        <v>174.943</v>
       </c>
       <c r="F6" t="n">
-        <v>92.52800000000001</v>
+        <v>86.857</v>
       </c>
       <c r="G6" t="n">
-        <v>63.225</v>
+        <v>48.683</v>
       </c>
       <c r="H6" t="n">
-        <v>18.695</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>39.965</v>
+        <v>5.742</v>
       </c>
       <c r="J6" t="n">
-        <v>113.373</v>
+        <v>12.105</v>
       </c>
       <c r="K6" t="n">
-        <v>134.824</v>
+        <v>11.65</v>
       </c>
       <c r="L6" t="n">
-        <v>92.22499999999999</v>
+        <v>8.004</v>
       </c>
       <c r="M6" t="n">
-        <v>107.489</v>
+        <v>9.208</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168.635</v>
+        <v>35.768</v>
       </c>
       <c r="C7" t="n">
-        <v>193.065</v>
+        <v>17.029</v>
       </c>
       <c r="D7" t="n">
-        <v>138.086</v>
+        <v>16.804</v>
       </c>
       <c r="E7" t="n">
-        <v>129.949</v>
+        <v>83.729</v>
       </c>
       <c r="F7" t="n">
-        <v>182.741</v>
+        <v>159.108</v>
       </c>
       <c r="G7" t="n">
-        <v>92.735</v>
+        <v>42.475</v>
       </c>
       <c r="H7" t="n">
-        <v>442.342</v>
+        <v>433.7</v>
       </c>
       <c r="I7" t="n">
-        <v>320.36</v>
+        <v>327.903</v>
       </c>
       <c r="J7" t="n">
-        <v>374.811</v>
+        <v>350.872</v>
       </c>
       <c r="K7" t="n">
-        <v>362.219</v>
+        <v>367.528</v>
       </c>
       <c r="L7" t="n">
-        <v>330.656</v>
+        <v>259.606</v>
       </c>
       <c r="M7" t="n">
-        <v>417.21</v>
+        <v>263.175</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.052</v>
+        <v>8.714</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.123</v>
+        <v>75.10899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>142.34</v>
+        <v>139.739</v>
       </c>
       <c r="G8" t="n">
-        <v>27.36</v>
+        <v>25.086</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.574</v>
+        <v>1.001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>45.21</v>
+        <v>83.087</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10090,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44.97</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>25.829</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>24.985</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>59.359</v>
+        <v>38.32</v>
       </c>
       <c r="F9" t="n">
-        <v>104.804</v>
+        <v>89.896</v>
       </c>
       <c r="G9" t="n">
-        <v>20.287</v>
+        <v>4.764</v>
       </c>
       <c r="H9" t="n">
-        <v>20.83</v>
+        <v>4.508</v>
       </c>
       <c r="I9" t="n">
-        <v>89.836</v>
+        <v>11.693</v>
       </c>
       <c r="J9" t="n">
-        <v>42.446</v>
+        <v>7.54</v>
       </c>
       <c r="K9" t="n">
-        <v>162.634</v>
+        <v>13.177</v>
       </c>
       <c r="L9" t="n">
-        <v>77.07599999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>21.573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.093</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>42.028</v>
+        <v>32.784</v>
       </c>
       <c r="F10" t="n">
-        <v>75.90600000000001</v>
+        <v>70.959</v>
       </c>
       <c r="G10" t="n">
-        <v>4.057</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.029</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.542</v>
+        <v>6.068</v>
       </c>
       <c r="J10" t="n">
-        <v>6.602</v>
+        <v>2.512</v>
       </c>
       <c r="K10" t="n">
-        <v>29.861</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -10185,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>37.906</v>
+        <v>34.551</v>
       </c>
       <c r="F11" t="n">
-        <v>64.315</v>
+        <v>62.546</v>
       </c>
       <c r="G11" t="n">
-        <v>1.867</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.611</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.067</v>
+        <v>0.263</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.722</v>
+        <v>22.383</v>
       </c>
       <c r="F12" t="n">
-        <v>49.017</v>
+        <v>47.975</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10262,37 +10262,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13.059</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4.394</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>16.173</v>
+        <v>1.892</v>
       </c>
       <c r="F13" t="n">
-        <v>39.507</v>
+        <v>28.268</v>
       </c>
       <c r="G13" t="n">
-        <v>1.201</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7.612</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>15.358</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>25.682</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>43.799</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>23.107</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10323,13 +10323,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.028</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4.396</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>4.847</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>219.074</v>
+        <v>137.287</v>
       </c>
       <c r="C15" t="n">
-        <v>230.359</v>
+        <v>102.307</v>
       </c>
       <c r="D15" t="n">
-        <v>240.287</v>
+        <v>127.891</v>
       </c>
       <c r="E15" t="n">
-        <v>243.71</v>
+        <v>219.577</v>
       </c>
       <c r="F15" t="n">
-        <v>98.771</v>
+        <v>97.423</v>
       </c>
       <c r="G15" t="n">
-        <v>248.523</v>
+        <v>232.365</v>
       </c>
       <c r="H15" t="n">
-        <v>132.569</v>
+        <v>137.658</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>207.203</v>
+        <v>122.922</v>
       </c>
       <c r="K15" t="n">
-        <v>207.056</v>
+        <v>187.929</v>
       </c>
       <c r="L15" t="n">
-        <v>238.67</v>
+        <v>231.721</v>
       </c>
       <c r="M15" t="n">
-        <v>245.778</v>
+        <v>223.887</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>321.082</v>
+        <v>183.488</v>
       </c>
       <c r="C16" t="n">
-        <v>353.164</v>
+        <v>150.023</v>
       </c>
       <c r="D16" t="n">
-        <v>368.998</v>
+        <v>238.461</v>
       </c>
       <c r="E16" t="n">
-        <v>392.77</v>
+        <v>371.992</v>
       </c>
       <c r="F16" t="n">
-        <v>209.35</v>
+        <v>201.858</v>
       </c>
       <c r="G16" t="n">
-        <v>429.31</v>
+        <v>418.489</v>
       </c>
       <c r="H16" t="n">
-        <v>349.255</v>
+        <v>332.095</v>
       </c>
       <c r="I16" t="n">
-        <v>143.898</v>
+        <v>145.556</v>
       </c>
       <c r="J16" t="n">
-        <v>414.826</v>
+        <v>403.494</v>
       </c>
       <c r="K16" t="n">
-        <v>374.933</v>
+        <v>334.722</v>
       </c>
       <c r="L16" t="n">
-        <v>367.486</v>
+        <v>344.066</v>
       </c>
       <c r="M16" t="n">
-        <v>379.669</v>
+        <v>360.896</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>218.493</v>
+        <v>125.077</v>
       </c>
       <c r="C17" t="n">
-        <v>203.199</v>
+        <v>112.356</v>
       </c>
       <c r="D17" t="n">
-        <v>311.59</v>
+        <v>228.485</v>
       </c>
       <c r="E17" t="n">
-        <v>420.37</v>
+        <v>415.616</v>
       </c>
       <c r="F17" t="n">
-        <v>177.211</v>
+        <v>176.782</v>
       </c>
       <c r="G17" t="n">
-        <v>330.48</v>
+        <v>323.78</v>
       </c>
       <c r="H17" t="n">
-        <v>323.196</v>
+        <v>247.612</v>
       </c>
       <c r="I17" t="n">
-        <v>140.132</v>
+        <v>88.39100000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>409.132</v>
+        <v>391.954</v>
       </c>
       <c r="K17" t="n">
-        <v>269.857</v>
+        <v>222.787</v>
       </c>
       <c r="L17" t="n">
-        <v>374.777</v>
+        <v>285.061</v>
       </c>
       <c r="M17" t="n">
-        <v>345.761</v>
+        <v>233.434</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.431</v>
+        <v>45.091</v>
       </c>
       <c r="C18" t="n">
-        <v>30.17</v>
+        <v>23.916</v>
       </c>
       <c r="D18" t="n">
-        <v>48.344</v>
+        <v>43.104</v>
       </c>
       <c r="E18" t="n">
-        <v>398.36</v>
+        <v>394.945</v>
       </c>
       <c r="F18" t="n">
-        <v>160.957</v>
+        <v>160.31</v>
       </c>
       <c r="G18" t="n">
-        <v>141.915</v>
+        <v>139.786</v>
       </c>
       <c r="H18" t="n">
-        <v>17.359</v>
+        <v>11.161</v>
       </c>
       <c r="I18" t="n">
-        <v>5.294</v>
+        <v>7.853</v>
       </c>
       <c r="J18" t="n">
-        <v>13.452</v>
+        <v>17.997</v>
       </c>
       <c r="K18" t="n">
-        <v>22.613</v>
+        <v>15.091</v>
       </c>
       <c r="L18" t="n">
-        <v>28.373</v>
+        <v>75.95</v>
       </c>
       <c r="M18" t="n">
-        <v>18.225</v>
+        <v>31.267</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.515</v>
+        <v>20.448</v>
       </c>
       <c r="C19" t="n">
-        <v>11.697</v>
+        <v>6.977</v>
       </c>
       <c r="D19" t="n">
-        <v>29.897</v>
+        <v>26.126</v>
       </c>
       <c r="E19" t="n">
-        <v>386.918</v>
+        <v>383.979</v>
       </c>
       <c r="F19" t="n">
-        <v>153.969</v>
+        <v>154.366</v>
       </c>
       <c r="G19" t="n">
-        <v>124.163</v>
+        <v>121.046</v>
       </c>
       <c r="H19" t="n">
-        <v>0.659</v>
+        <v>0.65</v>
       </c>
       <c r="I19" t="n">
-        <v>1.381</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.539</v>
       </c>
       <c r="K19" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.373</v>
+        <v>8.343</v>
       </c>
       <c r="M19" t="n">
-        <v>1.898</v>
+        <v>3.769</v>
       </c>
     </row>
     <row r="20">
@@ -10561,37 +10561,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>115.312</v>
+        <v>129.122</v>
       </c>
       <c r="C20" t="n">
-        <v>118.863</v>
+        <v>132.856</v>
       </c>
       <c r="D20" t="n">
-        <v>30.751</v>
+        <v>42.401</v>
       </c>
       <c r="E20" t="n">
-        <v>217.542</v>
+        <v>222.514</v>
       </c>
       <c r="F20" t="n">
-        <v>93.946</v>
+        <v>98.078</v>
       </c>
       <c r="G20" t="n">
-        <v>107.506</v>
+        <v>120.385</v>
       </c>
       <c r="H20" t="n">
-        <v>51.99</v>
+        <v>15.514</v>
       </c>
       <c r="I20" t="n">
-        <v>2.44</v>
+        <v>3.692</v>
       </c>
       <c r="J20" t="n">
-        <v>3.211</v>
+        <v>3.644</v>
       </c>
       <c r="K20" t="n">
-        <v>79.911</v>
+        <v>37.744</v>
       </c>
       <c r="L20" t="n">
-        <v>1.948</v>
+        <v>6.086</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>158.751</v>
+        <v>111.631</v>
       </c>
       <c r="C21" t="n">
-        <v>161.577</v>
+        <v>115.156</v>
       </c>
       <c r="D21" t="n">
-        <v>53.392</v>
+        <v>24.665</v>
       </c>
       <c r="E21" t="n">
-        <v>214.245</v>
+        <v>206.255</v>
       </c>
       <c r="F21" t="n">
-        <v>84.553</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>87.849</v>
+        <v>85.378</v>
       </c>
       <c r="H21" t="n">
-        <v>278.821</v>
+        <v>142.754</v>
       </c>
       <c r="I21" t="n">
-        <v>68.127</v>
+        <v>6.612</v>
       </c>
       <c r="J21" t="n">
-        <v>166.365</v>
+        <v>76.325</v>
       </c>
       <c r="K21" t="n">
-        <v>209.034</v>
+        <v>177.424</v>
       </c>
       <c r="L21" t="n">
-        <v>139.418</v>
+        <v>26.604</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>321.763</v>
+        <v>186.79</v>
       </c>
       <c r="C22" t="n">
-        <v>341.681</v>
+        <v>195.41</v>
       </c>
       <c r="D22" t="n">
-        <v>296.783</v>
+        <v>92.122</v>
       </c>
       <c r="E22" t="n">
-        <v>259.053</v>
+        <v>208.171</v>
       </c>
       <c r="F22" t="n">
-        <v>104.325</v>
+        <v>78.798</v>
       </c>
       <c r="G22" t="n">
-        <v>126.244</v>
+        <v>76.247</v>
       </c>
       <c r="H22" t="n">
-        <v>328.273</v>
+        <v>348.007</v>
       </c>
       <c r="I22" t="n">
-        <v>184.461</v>
+        <v>206.965</v>
       </c>
       <c r="J22" t="n">
-        <v>421.585</v>
+        <v>422.406</v>
       </c>
       <c r="K22" t="n">
-        <v>241.759</v>
+        <v>236.359</v>
       </c>
       <c r="L22" t="n">
-        <v>352.97</v>
+        <v>337.703</v>
       </c>
       <c r="M22" t="n">
-        <v>372.582</v>
+        <v>191.242</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.268</v>
+        <v>13.768</v>
       </c>
       <c r="C23" t="n">
-        <v>30.528</v>
+        <v>19.376</v>
       </c>
       <c r="D23" t="n">
-        <v>33.844</v>
+        <v>18.182</v>
       </c>
       <c r="E23" t="n">
-        <v>25.379</v>
+        <v>22.222</v>
       </c>
       <c r="F23" t="n">
-        <v>9.701000000000001</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>129.662</v>
+        <v>104.572</v>
       </c>
       <c r="H23" t="n">
-        <v>15.243</v>
+        <v>20.744</v>
       </c>
       <c r="I23" t="n">
-        <v>20.435</v>
+        <v>25.957</v>
       </c>
       <c r="J23" t="n">
-        <v>51.615</v>
+        <v>41.032</v>
       </c>
       <c r="K23" t="n">
-        <v>14.596</v>
+        <v>20.202</v>
       </c>
       <c r="L23" t="n">
-        <v>27.396</v>
+        <v>32.652</v>
       </c>
       <c r="M23" t="n">
-        <v>29.432</v>
+        <v>35.127</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16.116</v>
+        <v>10.954</v>
       </c>
       <c r="C24" t="n">
-        <v>25.788</v>
+        <v>16.375</v>
       </c>
       <c r="D24" t="n">
-        <v>22.745</v>
+        <v>12.773</v>
       </c>
       <c r="E24" t="n">
-        <v>26.181</v>
+        <v>25.242</v>
       </c>
       <c r="F24" t="n">
-        <v>10.387</v>
+        <v>10.405</v>
       </c>
       <c r="G24" t="n">
-        <v>126.35</v>
+        <v>122.373</v>
       </c>
       <c r="H24" t="n">
-        <v>14.744</v>
+        <v>19.39</v>
       </c>
       <c r="I24" t="n">
-        <v>18.473</v>
+        <v>24.773</v>
       </c>
       <c r="J24" t="n">
-        <v>38.897</v>
+        <v>45.773</v>
       </c>
       <c r="K24" t="n">
-        <v>14.115</v>
+        <v>19.559</v>
       </c>
       <c r="L24" t="n">
-        <v>23.955</v>
+        <v>29.922</v>
       </c>
       <c r="M24" t="n">
-        <v>24.889</v>
+        <v>30.504</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.56</v>
+        <v>12.412</v>
       </c>
       <c r="C25" t="n">
-        <v>17.151</v>
+        <v>12.755</v>
       </c>
       <c r="D25" t="n">
-        <v>14.13</v>
+        <v>9.634</v>
       </c>
       <c r="E25" t="n">
-        <v>25.997</v>
+        <v>26.662</v>
       </c>
       <c r="F25" t="n">
-        <v>11.906</v>
+        <v>11.877</v>
       </c>
       <c r="G25" t="n">
-        <v>93.524</v>
+        <v>72.93600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>7.184</v>
+        <v>18.957</v>
       </c>
       <c r="I25" t="n">
-        <v>7.864</v>
+        <v>4.237</v>
       </c>
       <c r="J25" t="n">
-        <v>9.199999999999999</v>
+        <v>22.559</v>
       </c>
       <c r="K25" t="n">
-        <v>9.253</v>
+        <v>16.936</v>
       </c>
       <c r="L25" t="n">
-        <v>22.892</v>
+        <v>16.135</v>
       </c>
       <c r="M25" t="n">
-        <v>9.379</v>
+        <v>7.419</v>
       </c>
     </row>
     <row r="26">
@@ -10819,28 +10819,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.491</v>
+        <v>7.614</v>
       </c>
       <c r="C26" t="n">
-        <v>10.872</v>
+        <v>9.493</v>
       </c>
       <c r="D26" t="n">
-        <v>3.965</v>
+        <v>3.604</v>
       </c>
       <c r="E26" t="n">
-        <v>22.31</v>
+        <v>22.569</v>
       </c>
       <c r="F26" t="n">
         <v>11.251</v>
       </c>
       <c r="G26" t="n">
-        <v>96.38500000000001</v>
+        <v>94.541</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.242</v>
+        <v>0.641</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -10849,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.128</v>
+        <v>0.322</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23.037</v>
+        <v>12.649</v>
       </c>
       <c r="C27" t="n">
-        <v>39.001</v>
+        <v>13.973</v>
       </c>
       <c r="D27" t="n">
-        <v>33.84</v>
+        <v>11.88</v>
       </c>
       <c r="E27" t="n">
-        <v>25.578</v>
+        <v>22.689</v>
       </c>
       <c r="F27" t="n">
-        <v>12.639</v>
+        <v>11.417</v>
       </c>
       <c r="G27" t="n">
-        <v>123.905</v>
+        <v>89.908</v>
       </c>
       <c r="H27" t="n">
-        <v>27.211</v>
+        <v>32.159</v>
       </c>
       <c r="I27" t="n">
-        <v>11.931</v>
+        <v>15.881</v>
       </c>
       <c r="J27" t="n">
-        <v>51.501</v>
+        <v>56.969</v>
       </c>
       <c r="K27" t="n">
-        <v>31</v>
+        <v>36.332</v>
       </c>
       <c r="L27" t="n">
-        <v>34.933</v>
+        <v>43.193</v>
       </c>
       <c r="M27" t="n">
-        <v>33.009</v>
+        <v>34.777</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.287</v>
+        <v>2.543</v>
       </c>
       <c r="C28" t="n">
-        <v>0.802</v>
+        <v>0.786</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>21.981</v>
+        <v>22.17</v>
       </c>
       <c r="F28" t="n">
-        <v>11.094</v>
+        <v>10.967</v>
       </c>
       <c r="G28" t="n">
-        <v>65.71599999999999</v>
+        <v>51.413</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.498</v>
+        <v>0.536</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.402</v>
+        <v>2.112</v>
       </c>
       <c r="C29" t="n">
-        <v>5.049</v>
+        <v>1.371</v>
       </c>
       <c r="D29" t="n">
-        <v>3.277</v>
+        <v>0.36</v>
       </c>
       <c r="E29" t="n">
-        <v>22.439</v>
+        <v>21.824</v>
       </c>
       <c r="F29" t="n">
-        <v>10.922</v>
+        <v>10.523</v>
       </c>
       <c r="G29" t="n">
-        <v>74.367</v>
+        <v>65.325</v>
       </c>
       <c r="H29" t="n">
-        <v>1.195</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>4.249</v>
+        <v>1.949</v>
       </c>
       <c r="J29" t="n">
-        <v>6.333</v>
+        <v>14.104</v>
       </c>
       <c r="K29" t="n">
-        <v>3.292</v>
+        <v>6.626</v>
       </c>
       <c r="L29" t="n">
-        <v>8.693</v>
+        <v>13.898</v>
       </c>
       <c r="M29" t="n">
-        <v>1.826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.295</v>
+        <v>13.747</v>
       </c>
       <c r="F30" t="n">
-        <v>5.599</v>
+        <v>5.879</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.498707332900001e-05</v>
+        <v>6.815823364000001e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.103095872100001e-05</v>
+        <v>4.743903376000001e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>4.811398380099999e-05</v>
+        <v>1.6920286084e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.949075932099998e-05</v>
+        <v>5.431509913600001e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.23587689e-05</v>
+        <v>1.1398978756e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1267434276e-05</v>
+        <v>2.229795562499999e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7352806449e-05</v>
+        <v>6.906607236e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.936261932899999e-05</v>
+        <v>9.556822080999999e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>7.033528326399999e-05</v>
+        <v>7.583448888999999e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.207387080900001e-05</v>
+        <v>3.935805696e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>5.0393964196e-05</v>
+        <v>3.466736641e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>8.955774464400001e-05</v>
+        <v>3.543701841000001e-06</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.060778201000001e-06</v>
+        <v>2.831836225000001e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>6.848059008999999e-06</v>
+        <v>2.348565444e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4055288025e-05</v>
+        <v>5.693758849e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9720526361e-05</v>
+        <v>4.68419449e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.628900675999999e-06</v>
+        <v>5.719896899999999e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.762314816e-06</v>
+        <v>6.269155684e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9599160009e-05</v>
+        <v>8.479744e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.750646534400001e-05</v>
+        <v>1.042579521e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4268541401e-05</v>
+        <v>3.189081639999999e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5636813225e-05</v>
+        <v>3.755843999999999e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5790686921e-05</v>
+        <v>5.95701649e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>6.465928921e-06</v>
+        <v>2.04261264e-07</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.7539344e-06</v>
+        <v>9.17847616e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>8.68952484e-07</v>
+        <v>4.90268164e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.829601636000001e-06</v>
+        <v>1.955319961e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1213466121e-05</v>
+        <v>3.8982158721e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.545334089e-06</v>
+        <v>5.415929649000001e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.550986520999999e-06</v>
+        <v>3.731988100000001e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7866449e-08</v>
+        <v>3.767481e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.157521e-09</v>
+        <v>2.635795600000001e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.678136410000001e-07</v>
+        <v>1.156e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.906981561e-06</v>
+        <v>3.940072900000001e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28346241e-07</v>
+        <v>1.0323369e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.431025e-07</v>
+        <v>1.0640644e-08</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.246072360000001e-07</v>
+        <v>3.53928969e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>5.416960000000001e-08</v>
+        <v>2.7804529e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.55661881e-07</v>
+        <v>3.26633329e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8208129961e-05</v>
+        <v>3.8168264689e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.657372025000001e-06</v>
+        <v>8.938567936000002e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.763694561e-06</v>
+        <v>6.111799683999999e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.022942809000001e-06</v>
+        <v>9.043251839999999e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.656887025e-06</v>
+        <v>8.412558400000002e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.787253476000001e-06</v>
+        <v>4.304795040000001e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5524333441e-05</v>
+        <v>3.060505324900001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.561430784000001e-06</v>
+        <v>7.544138449000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.997400625e-06</v>
+        <v>2.370034489e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>3.49503025e-07</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.597201225e-06</v>
+        <v>3.297056399999999e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2853437129e-05</v>
+        <v>1.46531025e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8177510976e-05</v>
+        <v>1.357225e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>8.505450624999998e-06</v>
+        <v>6.406401599999998e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1553885121e-05</v>
+        <v>8.478726400000002e-08</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.47925440833333e-06</v>
+        <v>4.264499413333334e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2424698075e-05</v>
+        <v>9.666228033333332e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.355914465333335e-06</v>
+        <v>9.412480533333332e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.628914200333334e-06</v>
+        <v>2.336848480333333e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.113142436033334e-05</v>
+        <v>8.438451887999999e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>2.866593408333333e-06</v>
+        <v>6.013752083333332e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.522214832133332e-05</v>
+        <v>6.269856333333332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.421017653333334e-05</v>
+        <v>3.5840125803e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.6827761907e-05</v>
+        <v>4.103705346133334e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.373420132033333e-05</v>
+        <v>4.502561026133334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.644446344533334e-05</v>
+        <v>2.246509174533333e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.802139469999999e-05</v>
+        <v>2.3087026875e-05</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.193870399999999e-08</v>
+        <v>7.593379600000002e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.643465129000001e-06</v>
+        <v>5.641361881e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.02606756e-05</v>
+        <v>1.9526988121e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.485696e-07</v>
+        <v>6.293073959999999e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.477476e-09</v>
+        <v>1.002001e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0439441e-06</v>
+        <v>6.903449569000001e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11414,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.741003e-07</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.223790803333334e-07</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.080834083333333e-07</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.174496960333333e-06</v>
+        <v>4.894741333333333e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.661292805333334e-06</v>
+        <v>2.693763605333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>1.371874563333333e-07</v>
+        <v>7.565232e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>1.446296333333333e-07</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>2.690168965333333e-06</v>
+        <v>4.557541633333334e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.005543053333333e-07</v>
+        <v>1.895053333333333e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.816605985333331e-06</v>
+        <v>5.787777633333332e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.980236591999999e-06</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.55131443e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.982163333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -11466,28 +11466,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>5.887842613333331e-07</v>
+        <v>3.582635520000001e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.920573612e-06</v>
+        <v>1.678393227e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>5.486416333333336e-09</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.372280333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.426592133333333e-08</v>
+        <v>1.227354133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.452880133333333e-08</v>
+        <v>2.103381333333333e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>2.972264403333334e-07</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.821333333333334e-12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -11509,22 +11509,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.789549453333333e-07</v>
+        <v>3.979238670000001e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.378806408333333e-06</v>
+        <v>1.304000705333334e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.161896333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.244403333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.424163e-09</v>
+        <v>2.305633333333334e-11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.720964280000001e-07</v>
+        <v>1.66999563e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>8.008887630000001e-07</v>
+        <v>7.672002083333336e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11586,37 +11586,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.684582699999999e-08</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6.435745333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.718864299999999e-08</v>
+        <v>1.193221333333333e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>5.20267683e-07</v>
+        <v>2.663599413333334e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>4.808003333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.931418133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>7.862272133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.198550413333333e-07</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>6.394508003333333e-07</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.779778163333333e-07</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11647,13 +11647,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.408261333333332e-09</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>6.441605333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7.831136333333335e-09</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.7993417476e-05</v>
+        <v>1.8847720369e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>5.3065268881e-05</v>
+        <v>1.0466722249e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7737842369e-05</v>
+        <v>1.6356107881e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>5.93945641e-05</v>
+        <v>4.8214058929e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.755710440999999e-06</v>
+        <v>9.491240929e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>6.176368152899999e-05</v>
+        <v>5.399349322500001e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7574539761e-05</v>
+        <v>1.894972496399999e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>4.2933083209e-05</v>
+        <v>1.5109818084e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.287218713600001e-05</v>
+        <v>3.531730904100001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.69633689e-05</v>
+        <v>5.3694621841e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0406825284e-05</v>
+        <v>5.0125388769e-05</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.436455024133332e-05</v>
+        <v>1.122261538133334e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>4.157493696533333e-05</v>
+        <v>7.502300176333332e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>4.538650800133333e-05</v>
+        <v>1.8954549507e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>5.142275763333333e-05</v>
+        <v>4.612601602133335e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.460914083333333e-05</v>
+        <v>1.3582217388e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.143569203333335e-05</v>
+        <v>5.837768104033333e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.065968500833333e-05</v>
+        <v>3.676236300833334e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>6.902211467999999e-06</v>
+        <v>7.062183045333335e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.736020342533334e-05</v>
+        <v>5.426913601200001e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.685825149633333e-05</v>
+        <v>3.734627242799999e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.501532006533333e-05</v>
+        <v>3.946047078533333e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.804951652033333e-05</v>
+        <v>4.341530760533333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5913063683e-05</v>
+        <v>5.214751976333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3763277867e-05</v>
+        <v>4.207956912e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>3.236277603333333e-05</v>
+        <v>1.740179840833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.890364563333334e-05</v>
+        <v>5.757888648533332e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.046791284033333e-05</v>
+        <v>1.041729184133334e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.64056768e-05</v>
+        <v>3.494449613333332e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.481855147200001e-05</v>
+        <v>2.043723418133333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>6.545659141333333e-06</v>
+        <v>2.604322960333334e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.579633114133333e-05</v>
+        <v>5.120931270533334e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.427426681633334e-05</v>
+        <v>1.654468245633333e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4.681926657633332e-05</v>
+        <v>2.708659124033332e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.985022304033334e-05</v>
+        <v>1.816381078533333e-05</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.818539203333332e-07</v>
+        <v>6.777327603333333e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>3.034096333333334e-07</v>
+        <v>1.90658352e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.790474453333333e-07</v>
+        <v>6.193182719999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.289689653333333e-05</v>
+        <v>5.199385100833333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.635718616333333e-06</v>
+        <v>8.566432033333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.713289074999999e-06</v>
+        <v>6.513375265333333e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.004449603333334e-07</v>
+        <v>4.152264033333332e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>9.342145333333331e-09</v>
+        <v>2.055653633333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>6.0318768e-08</v>
+        <v>1.07964003e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>1.704492563333333e-07</v>
+        <v>7.591276033333333e-08</v>
       </c>
       <c r="L18" t="n">
-        <v>2.683423763333334e-07</v>
+        <v>1.922800833333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>1.10716875e-07</v>
+        <v>3.258750963333332e-07</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.343484083333333e-07</v>
+        <v>1.39373568e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>4.5606603e-08</v>
+        <v>1.622617633333334e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.979435363333333e-07</v>
+        <v>2.275226253333333e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.990184624133333e-05</v>
+        <v>4.914662414699999e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.902150986999999e-06</v>
+        <v>7.942953985333334e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.138816856333333e-06</v>
+        <v>4.884044705333334e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.447603333333334e-10</v>
+        <v>1.408333333333333e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>6.357203333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>7.895070000000001e-10</v>
       </c>
       <c r="K19" t="n">
-        <v>4.489633333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.877043e-09</v>
+        <v>2.3201883e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>1.200801333333333e-09</v>
+        <v>4.735120333333334e-09</v>
       </c>
     </row>
     <row r="20">
@@ -11885,37 +11885,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.432285781333333e-06</v>
+        <v>5.557496961333335e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>4.709470923e-06</v>
+        <v>5.883572245333334e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>3.152080003333333e-07</v>
+        <v>5.992816003333334e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5774840588e-05</v>
+        <v>1.650416006533334e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>2.941950305333333e-06</v>
+        <v>3.206431361333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>3.852513345333334e-06</v>
+        <v>4.830849408333334e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>9.009867e-07</v>
+        <v>8.022806533333333e-08</v>
       </c>
       <c r="I20" t="n">
-        <v>1.984533333333333e-09</v>
+        <v>4.543621333333333e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>3.436840333333333e-09</v>
+        <v>4.426245333333334e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>2.128589307e-06</v>
+        <v>4.748698453333333e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>1.264901333333333e-09</v>
+        <v>1.234646533333334e-08</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.400626667000001e-06</v>
+        <v>4.153826720333333e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.702375643e-06</v>
+        <v>4.420301445333334e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>9.502352213333334e-07</v>
+        <v>2.027874083333333e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5300306675e-05</v>
+        <v>1.418037500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.383069936333334e-06</v>
+        <v>2.367256661333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.572482267000001e-06</v>
+        <v>2.429800961333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>2.591371668033334e-05</v>
+        <v>6.792901505333333e-06</v>
       </c>
       <c r="I21" t="n">
-        <v>1.547096043e-06</v>
+        <v>1.4572848e-08</v>
       </c>
       <c r="J21" t="n">
-        <v>9.225771075000002e-06</v>
+        <v>1.941835208333333e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4565071052e-05</v>
+        <v>1.049309192533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>6.479126241333335e-06</v>
+        <v>2.35924272e-07</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.451047605633332e-05</v>
+        <v>1.163016803333333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.891530192033332e-05</v>
+        <v>1.272835603333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>2.936004969633334e-05</v>
+        <v>2.828820961333333e-06</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2369485603e-05</v>
+        <v>1.444505508033333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>3.627901875e-06</v>
+        <v>2.069708268e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>5.312515845333332e-06</v>
+        <v>1.937868336333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.592105417633334e-05</v>
+        <v>4.036962401633334e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1341953507e-05</v>
+        <v>1.427817040833333e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>5.924463740833333e-05</v>
+        <v>5.9475609612e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.948247136033333e-05</v>
+        <v>1.862185896033334e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.152927363333333e-05</v>
+        <v>3.801443873633333e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>4.627244890799999e-05</v>
+        <v>1.219116752133333e-05</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6.90007824e-06</v>
+        <v>1.89557824e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>9.31958784e-06</v>
+        <v>3.75429376e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>1.145416336e-05</v>
+        <v>3.30585124e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>6.440936410000001e-06</v>
+        <v>4.938172840000001e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.410940100000003e-07</v>
+        <v>8.184820900000002e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6812234244e-05</v>
+        <v>1.0935303184e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>2.32349049e-06</v>
+        <v>4.30313536e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.175892249999999e-06</v>
+        <v>6.737658490000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>2.664108225e-05</v>
+        <v>1.683625024e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>2.13043216e-06</v>
+        <v>4.08120804e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>7.50540816e-06</v>
+        <v>1.066153104e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>8.662426240000001e-06</v>
+        <v>1.233906129000001e-05</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.59725456e-06</v>
+        <v>1.19990116e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>6.650209440000002e-06</v>
+        <v>2.68140625e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>5.173350250000001e-06</v>
+        <v>1.63149529e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.85444761e-06</v>
+        <v>6.37158564e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.07889769e-06</v>
+        <v>1.08264025e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.59643225e-05</v>
+        <v>1.4975151129e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.17385536e-06</v>
+        <v>3.759721000000001e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>3.41251729e-06</v>
+        <v>6.13701529e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>1.512976609e-05</v>
+        <v>2.095167529e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>1.99233225e-06</v>
+        <v>3.82554481e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>5.738420249999999e-06</v>
+        <v>8.953260840000001e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>6.194623209999999e-06</v>
+        <v>9.30494016e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.838736e-06</v>
+        <v>1.54057744e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>2.94156801e-06</v>
+        <v>1.62690025e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>1.996569e-06</v>
+        <v>9.281395600000001e-07</v>
       </c>
       <c r="E25" t="n">
-        <v>6.75844009e-06</v>
+        <v>7.108622439999999e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.41752836e-06</v>
+        <v>1.41063129e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>8.746738576e-06</v>
+        <v>5.319660096e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>5.1609856e-07</v>
+        <v>3.593678490000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>6.184249599999999e-07</v>
+        <v>1.7952169e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>8.464000000000001e-07</v>
+        <v>5.089084810000001e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>8.561800900000001e-07</v>
+        <v>2.86828096e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>5.240436639999999e-06</v>
+        <v>2.60338225e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>8.7965641e-07</v>
+        <v>5.504156099999999e-07</v>
       </c>
     </row>
     <row r="26">
@@ -12143,28 +12143,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.611508099999999e-07</v>
+        <v>5.797299600000001e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.18200384e-06</v>
+        <v>9.011704899999999e-07</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5721225e-07</v>
+        <v>1.2988816e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>4.977361e-06</v>
+        <v>5.093597609999999e-06</v>
       </c>
       <c r="F26" t="n">
         <v>1.26585001e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.290068225e-06</v>
+        <v>8.938000681e-06</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.542564e-08</v>
+        <v>4.10881e-09</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -12173,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>4.528384e-08</v>
+        <v>1.03684e-09</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.307033689999999e-06</v>
+        <v>1.59997201e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.521078001e-05</v>
+        <v>1.95244729e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1451456e-05</v>
+        <v>1.411344e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>6.542340840000001e-06</v>
+        <v>5.147907210000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.59744321e-06</v>
+        <v>1.30347889e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5352449025e-05</v>
+        <v>8.083448463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>7.404385209999999e-06</v>
+        <v>1.034201281e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>1.42348761e-06</v>
+        <v>2.52206161e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>2.652353001e-05</v>
+        <v>3.245466961e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>9.609999999999999e-06</v>
+        <v>1.320014224e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.220314489e-05</v>
+        <v>1.865635249e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.089594081e-05</v>
+        <v>1.209439729e-05</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.230369e-08</v>
+        <v>6.466849e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>6.432040000000001e-09</v>
+        <v>6.17796e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.83164361e-06</v>
+        <v>4.915089000000001e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.23076836e-06</v>
+        <v>1.20275089e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>4.318592655999999e-06</v>
+        <v>2.643296568999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.48004e-09</v>
+        <v>2.87296e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9377604e-07</v>
+        <v>4.460544e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>2.5492401e-07</v>
+        <v>1.879641e-08</v>
       </c>
       <c r="D29" t="n">
-        <v>1.0738729e-07</v>
+        <v>1.296e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>5.03508721e-06</v>
+        <v>4.762869760000001e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.19290084e-06</v>
+        <v>1.10733529e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.530450689e-06</v>
+        <v>4.267355625000001e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>1.428025e-08</v>
+        <v>6.577210000000002e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>1.805400099999999e-07</v>
+        <v>3.798601e-08</v>
       </c>
       <c r="J29" t="n">
-        <v>4.0106889e-07</v>
+        <v>1.98922816e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>1.0837264e-07</v>
+        <v>4.3903876e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>7.556824899999998e-07</v>
+        <v>1.93154404e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>3.334276000000001e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.76757025e-06</v>
+        <v>1.88980009e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.1348801e-07</v>
+        <v>3.4562641e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.206944</v>
+        <v>0.041319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="I2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="K2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="M2" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="3">
@@ -12482,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.185069</v>
+        <v>0.041319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.19375</v>
+        <v>0.041319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E3" t="n">
-        <v>0.207986</v>
+        <v>0.000694</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H3" t="n">
-        <v>0.165972</v>
+        <v>0.041319</v>
       </c>
       <c r="I3" t="n">
-        <v>0.160417</v>
+        <v>0.041319</v>
       </c>
       <c r="J3" t="n">
-        <v>0.181597</v>
+        <v>0.041319</v>
       </c>
       <c r="K3" t="n">
-        <v>0.192014</v>
+        <v>0.041319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.166667</v>
+        <v>0.041319</v>
       </c>
       <c r="M3" t="n">
-        <v>0.160764</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.207639</v>
+        <v>0.038889</v>
       </c>
       <c r="G4" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H4" t="n">
-        <v>0.148264</v>
+        <v>0.041319</v>
       </c>
       <c r="I4" t="n">
-        <v>0.051042</v>
+        <v>0.040625</v>
       </c>
       <c r="J4" t="n">
-        <v>0.19375</v>
+        <v>0.041319</v>
       </c>
       <c r="K4" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.204514</v>
+        <v>0.041319</v>
       </c>
       <c r="M4" t="n">
-        <v>0.202083</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="5">
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.207986</v>
+        <v>0.001042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.196181</v>
+        <v>0.000694</v>
       </c>
       <c r="E5" t="n">
         <v>0.000694</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H6" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="J6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="K6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="L6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="M6" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="7">
@@ -12652,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H7" t="n">
-        <v>0.080556</v>
+        <v>0.039583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.045833</v>
+        <v>0.040625</v>
       </c>
       <c r="J7" t="n">
-        <v>0.047569</v>
+        <v>0.041319</v>
       </c>
       <c r="K7" t="n">
-        <v>0.061806</v>
+        <v>0.041319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08784699999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="M7" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.166667</v>
+        <v>0.038194</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12704,19 +12704,19 @@
         <v>0.003472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.111111</v>
+        <v>0.038194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.204861</v>
+        <v>0.038194</v>
       </c>
       <c r="G8" t="n">
-        <v>0.204861</v>
+        <v>0.038194</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.100694</v>
+        <v>0.038194</v>
       </c>
       <c r="J8" t="n">
         <v>0.003472</v>
@@ -12738,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="I9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="J9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="K9" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="M9" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="10">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="C10" t="n">
         <v>0.000347</v>
@@ -12790,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F10" t="n">
-        <v>0.207639</v>
+        <v>0.041319</v>
       </c>
       <c r="G10" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="H10" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08437500000000001</v>
+        <v>0.041319</v>
       </c>
       <c r="J10" t="n">
-        <v>0.127083</v>
+        <v>0.041319</v>
       </c>
       <c r="K10" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.13125</v>
+        <v>0.000347</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12833,22 +12833,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G11" t="n">
-        <v>0.207986</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.170833</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.125694</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12876,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.133681</v>
+        <v>0.000347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12910,37 +12910,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="C13" t="n">
         <v>0.000347</v>
       </c>
       <c r="D13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F13" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="H13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="I13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="K13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12971,13 +12971,13 @@
         <v>0.000347</v>
       </c>
       <c r="H14" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="I14" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="J14" t="n">
-        <v>0.207986</v>
+        <v>0.000347</v>
       </c>
       <c r="K14" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C15" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D15" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E15" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.205903</v>
+        <v>0.041319</v>
       </c>
       <c r="H15" t="n">
-        <v>0.046528</v>
+        <v>0.041319</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="K15" t="n">
-        <v>0.133333</v>
+        <v>0.041319</v>
       </c>
       <c r="L15" t="n">
-        <v>0.150347</v>
+        <v>0.041319</v>
       </c>
       <c r="M15" t="n">
-        <v>0.156597</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C16" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D16" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E16" t="n">
-        <v>0.207986</v>
+        <v>0.010764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G16" t="n">
         <v>0.021875</v>
       </c>
       <c r="H16" t="n">
-        <v>0.076389</v>
+        <v>0.035069</v>
       </c>
       <c r="I16" t="n">
-        <v>0.060764</v>
+        <v>0.041319</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07256899999999999</v>
+        <v>0.023611</v>
       </c>
       <c r="K16" t="n">
-        <v>0.154514</v>
+        <v>0.041319</v>
       </c>
       <c r="L16" t="n">
-        <v>0.139236</v>
+        <v>0.041319</v>
       </c>
       <c r="M16" t="n">
-        <v>0.132986</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="17">
@@ -13080,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C17" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D17" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.207986</v>
+        <v>0.000694</v>
       </c>
       <c r="F17" t="n">
-        <v>0.101042</v>
+        <v>0.001042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H17" t="n">
-        <v>0.130556</v>
+        <v>0.041319</v>
       </c>
       <c r="I17" t="n">
-        <v>0.205208</v>
+        <v>0.041319</v>
       </c>
       <c r="J17" t="n">
-        <v>0.100694</v>
+        <v>0.041319</v>
       </c>
       <c r="K17" t="n">
-        <v>0.144444</v>
+        <v>0.041319</v>
       </c>
       <c r="L17" t="n">
-        <v>0.174306</v>
+        <v>0.041319</v>
       </c>
       <c r="M17" t="n">
-        <v>0.198611</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="18">
@@ -13123,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.137847</v>
+        <v>0.041319</v>
       </c>
       <c r="C18" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D18" t="n">
-        <v>0.207292</v>
+        <v>0.041319</v>
       </c>
       <c r="E18" t="n">
-        <v>0.141319</v>
+        <v>0.041319</v>
       </c>
       <c r="F18" t="n">
-        <v>0.132986</v>
+        <v>0.041319</v>
       </c>
       <c r="G18" t="n">
-        <v>0.207986</v>
+        <v>0.001389</v>
       </c>
       <c r="H18" t="n">
-        <v>0.092361</v>
+        <v>0.041319</v>
       </c>
       <c r="I18" t="n">
-        <v>0.073958</v>
+        <v>0.041319</v>
       </c>
       <c r="J18" t="n">
-        <v>0.064236</v>
+        <v>0.041319</v>
       </c>
       <c r="K18" t="n">
-        <v>0.088542</v>
+        <v>0.041319</v>
       </c>
       <c r="L18" t="n">
-        <v>0.053125</v>
+        <v>0.041319</v>
       </c>
       <c r="M18" t="n">
-        <v>0.061458</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="19">
@@ -13166,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C19" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D19" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E19" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F19" t="n">
-        <v>0.044792</v>
+        <v>0.041319</v>
       </c>
       <c r="G19" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H19" t="n">
-        <v>0.092014</v>
+        <v>0.041319</v>
       </c>
       <c r="I19" t="n">
-        <v>0.100347</v>
+        <v>0.000347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1</v>
+        <v>0.041319</v>
       </c>
       <c r="K19" t="n">
-        <v>0.093056</v>
+        <v>0.000347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.052431</v>
+        <v>0.041319</v>
       </c>
       <c r="M19" t="n">
-        <v>0.067708</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="20">
@@ -13236,7 +13236,7 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="L20" t="n">
         <v>0.026736</v>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.197222</v>
+        <v>0.041319</v>
       </c>
       <c r="C21" t="n">
-        <v>0.197917</v>
+        <v>0.041319</v>
       </c>
       <c r="D21" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E21" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F21" t="n">
-        <v>0.139236</v>
+        <v>0.041319</v>
       </c>
       <c r="G21" t="n">
-        <v>0.207986</v>
+        <v>0.005903</v>
       </c>
       <c r="H21" t="n">
-        <v>0.146875</v>
+        <v>0.041319</v>
       </c>
       <c r="I21" t="n">
-        <v>0.169444</v>
+        <v>0.040972</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="K21" t="n">
-        <v>0.101042</v>
+        <v>0.041319</v>
       </c>
       <c r="L21" t="n">
-        <v>0.126736</v>
+        <v>0.041319</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="C22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H22" t="n">
-        <v>0.052431</v>
+        <v>0.041319</v>
       </c>
       <c r="I22" t="n">
         <v>0.021181</v>
       </c>
       <c r="J22" t="n">
-        <v>0.073958</v>
+        <v>0.022222</v>
       </c>
       <c r="K22" t="n">
-        <v>0.118403</v>
+        <v>0.041319</v>
       </c>
       <c r="L22" t="n">
-        <v>0.164931</v>
+        <v>0.041319</v>
       </c>
       <c r="M22" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="23">
@@ -13341,19 +13341,19 @@
         <v>0.028819</v>
       </c>
       <c r="C23" t="n">
-        <v>0.163194</v>
+        <v>0.041319</v>
       </c>
       <c r="D23" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E23" t="n">
-        <v>0.207986</v>
+        <v>0.000694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.207292</v>
+        <v>0.041319</v>
       </c>
       <c r="G23" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H23" t="n">
         <v>0.033681</v>
@@ -13362,16 +13362,16 @@
         <v>0.022222</v>
       </c>
       <c r="J23" t="n">
-        <v>0.117708</v>
+        <v>0.041319</v>
       </c>
       <c r="K23" t="n">
         <v>0.031944</v>
       </c>
       <c r="L23" t="n">
-        <v>0.042014</v>
+        <v>0.041319</v>
       </c>
       <c r="M23" t="n">
-        <v>0.045486</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="24">
@@ -13381,22 +13381,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.190625</v>
+        <v>0.041319</v>
       </c>
       <c r="C24" t="n">
-        <v>0.169097</v>
+        <v>0.041319</v>
       </c>
       <c r="D24" t="n">
-        <v>0.185764</v>
+        <v>0.041319</v>
       </c>
       <c r="E24" t="n">
-        <v>0.207292</v>
+        <v>0.041319</v>
       </c>
       <c r="F24" t="n">
-        <v>0.080208</v>
+        <v>0.000347</v>
       </c>
       <c r="G24" t="n">
-        <v>0.207986</v>
+        <v>0.000694</v>
       </c>
       <c r="H24" t="n">
         <v>0.024306</v>
@@ -13405,7 +13405,7 @@
         <v>0.017361</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09375</v>
+        <v>0.041319</v>
       </c>
       <c r="K24" t="n">
         <v>0.030556</v>
@@ -13424,40 +13424,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.164931</v>
+        <v>0.000694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.147569</v>
+        <v>0.001042</v>
       </c>
       <c r="D25" t="n">
-        <v>0.151736</v>
+        <v>0.041319</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.106597</v>
+        <v>0.000694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H25" t="n">
-        <v>0.043403</v>
+        <v>0.041319</v>
       </c>
       <c r="I25" t="n">
-        <v>0.092014</v>
+        <v>0.041319</v>
       </c>
       <c r="J25" t="n">
-        <v>0.054167</v>
+        <v>0.041319</v>
       </c>
       <c r="K25" t="n">
-        <v>0.080208</v>
+        <v>0.041319</v>
       </c>
       <c r="L25" t="n">
-        <v>0.115625</v>
+        <v>0.041319</v>
       </c>
       <c r="M25" t="n">
-        <v>0.103472</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="26">
@@ -13470,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.132292</v>
+        <v>0.010069</v>
       </c>
       <c r="D26" t="n">
-        <v>0.154167</v>
+        <v>0.000694</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13482,22 +13482,22 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.160417</v>
+        <v>0.041319</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08472200000000001</v>
+        <v>0.000347</v>
       </c>
       <c r="I26" t="n">
-        <v>0.130903</v>
+        <v>0.012153</v>
       </c>
       <c r="J26" t="n">
-        <v>0.104167</v>
+        <v>0.000347</v>
       </c>
       <c r="K26" t="n">
-        <v>0.072917</v>
+        <v>0.000347</v>
       </c>
       <c r="L26" t="n">
-        <v>0.089931</v>
+        <v>0.041319</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.202431</v>
+        <v>0.041319</v>
       </c>
       <c r="C27" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="D27" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="E27" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="F27" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="G27" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07083299999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="I27" t="n">
         <v>0.015278</v>
       </c>
       <c r="J27" t="n">
-        <v>0.067014</v>
+        <v>0.041319</v>
       </c>
       <c r="K27" t="n">
-        <v>0.057639</v>
+        <v>0.041319</v>
       </c>
       <c r="L27" t="n">
-        <v>0.043403</v>
+        <v>0.041319</v>
       </c>
       <c r="M27" t="n">
-        <v>0.057639</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.052431</v>
+        <v>0.041319</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,7 +13568,7 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
@@ -13596,40 +13596,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.157639</v>
+        <v>0.041319</v>
       </c>
       <c r="C29" t="n">
-        <v>0.144792</v>
+        <v>0.041319</v>
       </c>
       <c r="D29" t="n">
-        <v>0.139583</v>
+        <v>0.041319</v>
       </c>
       <c r="E29" t="n">
-        <v>0.203125</v>
+        <v>0.041319</v>
       </c>
       <c r="F29" t="n">
-        <v>0.199306</v>
+        <v>0.041319</v>
       </c>
       <c r="G29" t="n">
-        <v>0.207986</v>
+        <v>0.041319</v>
       </c>
       <c r="H29" t="n">
-        <v>0.092708</v>
+        <v>0.041319</v>
       </c>
       <c r="I29" t="n">
-        <v>0.093056</v>
+        <v>0.041319</v>
       </c>
       <c r="J29" t="n">
-        <v>0.058333</v>
+        <v>0.041319</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08819399999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="L29" t="n">
-        <v>0.077431</v>
+        <v>0.041319</v>
       </c>
       <c r="M29" t="n">
-        <v>0.117708</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="30">

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.037</v>
+        <v>0.007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.187</v>
+        <v>0.06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04</v>
+        <v>0.013</v>
       </c>
       <c r="G2" t="n">
-        <v>0.076</v>
+        <v>0.024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1874,28 +1874,28 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.007</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.021</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.002</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.007</v>
-      </c>
       <c r="E4" t="n">
-        <v>0.138</v>
+        <v>0.045</v>
       </c>
       <c r="F4" t="n">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.136</v>
+        <v>0.044</v>
       </c>
       <c r="F5" t="n">
-        <v>0.032</v>
+        <v>0.01</v>
       </c>
       <c r="G5" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.002</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.008</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2055,31 +2055,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.028</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.174</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.115</v>
+        <v>0.03</v>
       </c>
       <c r="J7" t="n">
-        <v>0.054</v>
+        <v>0.001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.132</v>
+        <v>0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06</v>
+        <v>0.014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.022</v>
+        <v>0.006</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.005</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>0.001</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.003</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.043</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.019</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.035</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.163</v>
+        <v>0.051</v>
       </c>
       <c r="F15" t="n">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
       <c r="G15" t="n">
-        <v>0.186</v>
+        <v>0.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.023</v>
+        <v>0.001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.058</v>
+        <v>0.003</v>
       </c>
       <c r="L15" t="n">
-        <v>0.102</v>
+        <v>0.007</v>
       </c>
       <c r="M15" t="n">
-        <v>0.067</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="C16" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="D16" t="n">
-        <v>0.045</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>0.166</v>
+        <v>0.055</v>
       </c>
       <c r="F16" t="n">
-        <v>0.047</v>
+        <v>0.015</v>
       </c>
       <c r="G16" t="n">
-        <v>0.217</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="I16" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.13</v>
+        <v>0.007</v>
       </c>
       <c r="K16" t="n">
-        <v>0.055</v>
+        <v>0.001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.092</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.066</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="C17" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="D17" t="n">
-        <v>0.052</v>
+        <v>0.015</v>
       </c>
       <c r="E17" t="n">
-        <v>0.205</v>
+        <v>0.066</v>
       </c>
       <c r="F17" t="n">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.124</v>
+        <v>0.04</v>
       </c>
       <c r="H17" t="n">
-        <v>0.047</v>
+        <v>0.002</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.054</v>
+        <v>0.003</v>
       </c>
       <c r="M17" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2519,22 +2519,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.001</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.002</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.184</v>
+        <v>0.06</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G18" t="n">
-        <v>0.023</v>
+        <v>0.008</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2568,16 +2568,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.174</v>
+        <v>0.056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.028</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.017</v>
+        <v>0.006</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,22 +2605,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="C20" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.059</v>
+        <v>0.019</v>
       </c>
       <c r="F20" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="G20" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,34 +2648,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="C21" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05</v>
+        <v>0.016</v>
       </c>
       <c r="F21" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="G21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.023</v>
+        <v>0.004</v>
       </c>
       <c r="C22" t="n">
-        <v>0.025</v>
+        <v>0.004</v>
       </c>
       <c r="D22" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.049</v>
+        <v>0.016</v>
       </c>
       <c r="F22" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="G22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.006</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.144</v>
-      </c>
       <c r="K22" t="n">
-        <v>0.042</v>
+        <v>0.002</v>
       </c>
       <c r="L22" t="n">
-        <v>0.068</v>
+        <v>0.002</v>
       </c>
       <c r="M22" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.038</v>
+        <v>0.016</v>
       </c>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.005</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.017</v>
-      </c>
       <c r="F23" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.036</v>
+        <v>0.011</v>
       </c>
       <c r="H23" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.017</v>
+        <v>0.002</v>
       </c>
       <c r="J23" t="n">
-        <v>0.029</v>
+        <v>0.001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.024</v>
+        <v>0.002</v>
       </c>
       <c r="M23" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.002</v>
       </c>
-      <c r="C24" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.017</v>
-      </c>
       <c r="J24" t="n">
-        <v>0.032</v>
+        <v>0.001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.025</v>
+        <v>0.003</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2820,37 +2820,37 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="C25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.004</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.016</v>
-      </c>
       <c r="H25" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="F26" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.031</v>
+        <v>0.01</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.002</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.022</v>
-      </c>
       <c r="I27" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.079</v>
+        <v>0.006</v>
       </c>
       <c r="K27" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.042</v>
+        <v>0.003</v>
       </c>
       <c r="M27" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="F28" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3001,14 +3001,14 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.017</v>
+        <v>0.005</v>
       </c>
       <c r="F29" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.004</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.014</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -3016,13 +3016,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82.55800000000001</v>
+        <v>52.236</v>
       </c>
       <c r="C2" t="n">
-        <v>68.876</v>
+        <v>40.848</v>
       </c>
       <c r="D2" t="n">
-        <v>130.078</v>
+        <v>89.02500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>233.056</v>
+        <v>228.123</v>
       </c>
       <c r="F2" t="n">
-        <v>106.766</v>
+        <v>105.855</v>
       </c>
       <c r="G2" t="n">
-        <v>149.325</v>
+        <v>144.529</v>
       </c>
       <c r="H2" t="n">
-        <v>83.10599999999999</v>
+        <v>13.225</v>
       </c>
       <c r="I2" t="n">
-        <v>97.759</v>
+        <v>21.667</v>
       </c>
       <c r="J2" t="n">
-        <v>87.083</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>62.736</v>
+        <v>9.362</v>
       </c>
       <c r="L2" t="n">
-        <v>58.879</v>
+        <v>6.178</v>
       </c>
       <c r="M2" t="n">
-        <v>59.529</v>
+        <v>11.703</v>
       </c>
     </row>
     <row r="3">
@@ -7186,13 +7186,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.215</v>
+        <v>42.707</v>
       </c>
       <c r="C3" t="n">
-        <v>48.462</v>
+        <v>37.339</v>
       </c>
       <c r="D3" t="n">
-        <v>75.45699999999999</v>
+        <v>62.271</v>
       </c>
       <c r="E3" t="n">
         <v>217.978</v>
@@ -7201,25 +7201,25 @@
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>79.178</v>
+        <v>76.80500000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>29.12</v>
+        <v>1.063</v>
       </c>
       <c r="I3" t="n">
-        <v>32.289</v>
+        <v>6.124</v>
       </c>
       <c r="J3" t="n">
-        <v>17.858</v>
+        <v>3.734</v>
       </c>
       <c r="K3" t="n">
-        <v>19.38</v>
+        <v>2.422</v>
       </c>
       <c r="L3" t="n">
-        <v>24.407</v>
+        <v>2.201</v>
       </c>
       <c r="M3" t="n">
-        <v>14.292</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.296</v>
+        <v>27.253</v>
       </c>
       <c r="C4" t="n">
-        <v>22.142</v>
+        <v>19.919</v>
       </c>
       <c r="D4" t="n">
-        <v>44.219</v>
+        <v>42.394</v>
       </c>
       <c r="E4" t="n">
-        <v>197.439</v>
+        <v>196.74</v>
       </c>
       <c r="F4" t="n">
-        <v>73.631</v>
+        <v>73.182</v>
       </c>
       <c r="G4" t="n">
-        <v>61.09</v>
+        <v>59.056</v>
       </c>
       <c r="H4" t="n">
-        <v>1.941</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5.146</v>
+        <v>2.159</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6.277</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.213</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.262</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="5">
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.813</v>
+        <v>18.623</v>
       </c>
       <c r="C5" t="n">
         <v>5.454</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.072</v>
+        <v>15.875</v>
       </c>
       <c r="C6" t="n">
-        <v>9.172000000000001</v>
+        <v>1.743</v>
       </c>
       <c r="D6" t="n">
-        <v>20.748</v>
+        <v>10.034</v>
       </c>
       <c r="E6" t="n">
-        <v>174.943</v>
+        <v>172.737</v>
       </c>
       <c r="F6" t="n">
-        <v>86.857</v>
+        <v>85.747</v>
       </c>
       <c r="G6" t="n">
-        <v>48.683</v>
+        <v>45.115</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5.742</v>
+        <v>1.415</v>
       </c>
       <c r="J6" t="n">
-        <v>12.105</v>
+        <v>0.293</v>
       </c>
       <c r="K6" t="n">
-        <v>11.65</v>
+        <v>0.412</v>
       </c>
       <c r="L6" t="n">
-        <v>8.004</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>9.208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.768</v>
+        <v>11.537</v>
       </c>
       <c r="C7" t="n">
-        <v>17.029</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>16.804</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>83.729</v>
+        <v>77.108</v>
       </c>
       <c r="F7" t="n">
-        <v>159.108</v>
+        <v>153.113</v>
       </c>
       <c r="G7" t="n">
-        <v>42.475</v>
+        <v>35.306</v>
       </c>
       <c r="H7" t="n">
-        <v>433.844</v>
+        <v>402.337</v>
       </c>
       <c r="I7" t="n">
-        <v>327.903</v>
+        <v>321.932</v>
       </c>
       <c r="J7" t="n">
-        <v>350.872</v>
+        <v>78.265</v>
       </c>
       <c r="K7" t="n">
-        <v>367.528</v>
+        <v>339.646</v>
       </c>
       <c r="L7" t="n">
-        <v>259.606</v>
+        <v>42.462</v>
       </c>
       <c r="M7" t="n">
-        <v>263.175</v>
+        <v>49.153</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.714</v>
+        <v>8.500999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7408,19 +7408,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.10899999999999</v>
+        <v>74.858</v>
       </c>
       <c r="F8" t="n">
-        <v>139.739</v>
+        <v>137.875</v>
       </c>
       <c r="G8" t="n">
-        <v>25.086</v>
+        <v>24.265</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.001</v>
+        <v>0.766</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7451,25 +7451,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>38.32</v>
+        <v>36.359</v>
       </c>
       <c r="F9" t="n">
-        <v>89.896</v>
+        <v>86.658</v>
       </c>
       <c r="G9" t="n">
-        <v>4.764</v>
+        <v>3.442</v>
       </c>
       <c r="H9" t="n">
-        <v>4.508</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11.693</v>
+        <v>3.667</v>
       </c>
       <c r="J9" t="n">
-        <v>7.54</v>
+        <v>2.028</v>
       </c>
       <c r="K9" t="n">
-        <v>13.177</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -7494,10 +7494,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.784</v>
+        <v>32.368</v>
       </c>
       <c r="F10" t="n">
-        <v>70.959</v>
+        <v>69.78100000000001</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -7506,10 +7506,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.068</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.512</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -7537,10 +7537,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34.551</v>
+        <v>34.141</v>
       </c>
       <c r="F11" t="n">
-        <v>62.546</v>
+        <v>61.606</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>22.546</v>
       </c>
       <c r="F12" t="n">
-        <v>47.975</v>
+        <v>47.548</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.892</v>
+        <v>0.699</v>
       </c>
       <c r="F13" t="n">
-        <v>28.268</v>
+        <v>26.62</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137.287</v>
+        <v>96.527</v>
       </c>
       <c r="C15" t="n">
-        <v>102.307</v>
+        <v>58.888</v>
       </c>
       <c r="D15" t="n">
-        <v>127.891</v>
+        <v>85.241</v>
       </c>
       <c r="E15" t="n">
-        <v>219.577</v>
+        <v>212.542</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>232.365</v>
+        <v>229.985</v>
       </c>
       <c r="H15" t="n">
-        <v>137.658</v>
+        <v>19.119</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>122.922</v>
+        <v>51.292</v>
       </c>
       <c r="K15" t="n">
-        <v>187.929</v>
+        <v>81.736</v>
       </c>
       <c r="L15" t="n">
-        <v>231.721</v>
+        <v>138.554</v>
       </c>
       <c r="M15" t="n">
-        <v>223.887</v>
+        <v>48.635</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>183.488</v>
+        <v>116.888</v>
       </c>
       <c r="C16" t="n">
-        <v>150.023</v>
+        <v>86.634</v>
       </c>
       <c r="D16" t="n">
-        <v>238.461</v>
+        <v>175.484</v>
       </c>
       <c r="E16" t="n">
         <v>377.251</v>
       </c>
       <c r="F16" t="n">
-        <v>201.858</v>
+        <v>200.497</v>
       </c>
       <c r="G16" t="n">
-        <v>437.584</v>
+        <v>436.177</v>
       </c>
       <c r="H16" t="n">
-        <v>332.719</v>
+        <v>186.378</v>
       </c>
       <c r="I16" t="n">
-        <v>145.556</v>
+        <v>67.57899999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>406.512</v>
+        <v>281.353</v>
       </c>
       <c r="K16" t="n">
-        <v>334.722</v>
+        <v>93.015</v>
       </c>
       <c r="L16" t="n">
-        <v>344.066</v>
+        <v>240.571</v>
       </c>
       <c r="M16" t="n">
-        <v>360.896</v>
+        <v>104.704</v>
       </c>
     </row>
     <row r="17">
@@ -7784,13 +7784,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125.077</v>
+        <v>96.625</v>
       </c>
       <c r="C17" t="n">
-        <v>112.356</v>
+        <v>88.55200000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>228.485</v>
+        <v>201.837</v>
       </c>
       <c r="E17" t="n">
         <v>416.187</v>
@@ -7799,25 +7799,25 @@
         <v>177.486</v>
       </c>
       <c r="G17" t="n">
-        <v>323.78</v>
+        <v>322.729</v>
       </c>
       <c r="H17" t="n">
-        <v>247.612</v>
+        <v>169.533</v>
       </c>
       <c r="I17" t="n">
-        <v>88.39100000000001</v>
+        <v>42.79</v>
       </c>
       <c r="J17" t="n">
-        <v>391.954</v>
+        <v>129.461</v>
       </c>
       <c r="K17" t="n">
-        <v>222.787</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>285.061</v>
+        <v>163.884</v>
       </c>
       <c r="M17" t="n">
-        <v>233.434</v>
+        <v>72.009</v>
       </c>
     </row>
     <row r="18">
@@ -7827,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.091</v>
+        <v>40.557</v>
       </c>
       <c r="C18" t="n">
-        <v>23.916</v>
+        <v>20.167</v>
       </c>
       <c r="D18" t="n">
-        <v>43.104</v>
+        <v>40.053</v>
       </c>
       <c r="E18" t="n">
-        <v>394.945</v>
+        <v>393.462</v>
       </c>
       <c r="F18" t="n">
-        <v>160.31</v>
+        <v>159.617</v>
       </c>
       <c r="G18" t="n">
         <v>140.235</v>
       </c>
       <c r="H18" t="n">
-        <v>11.161</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>7.853</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>17.997</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>15.091</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>75.95</v>
+        <v>5.197</v>
       </c>
       <c r="M18" t="n">
-        <v>31.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.448</v>
+        <v>17.933</v>
       </c>
       <c r="C19" t="n">
-        <v>6.977</v>
+        <v>4.508</v>
       </c>
       <c r="D19" t="n">
-        <v>26.126</v>
+        <v>23.175</v>
       </c>
       <c r="E19" t="n">
-        <v>383.979</v>
+        <v>382.84</v>
       </c>
       <c r="F19" t="n">
-        <v>154.366</v>
+        <v>152.843</v>
       </c>
       <c r="G19" t="n">
-        <v>121.046</v>
+        <v>120.932</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.539</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8.343</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -7940,10 +7940,10 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>37.744</v>
+        <v>11.559</v>
       </c>
       <c r="L20" t="n">
-        <v>7.176</v>
+        <v>5.484</v>
       </c>
       <c r="M20" t="n">
         <v>38.08</v>
@@ -7956,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111.631</v>
+        <v>96.55800000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>115.156</v>
+        <v>99.063</v>
       </c>
       <c r="D21" t="n">
-        <v>24.665</v>
+        <v>20.397</v>
       </c>
       <c r="E21" t="n">
-        <v>206.255</v>
+        <v>204.705</v>
       </c>
       <c r="F21" t="n">
-        <v>84.27200000000001</v>
+        <v>83.80200000000001</v>
       </c>
       <c r="G21" t="n">
         <v>86.164</v>
       </c>
       <c r="H21" t="n">
-        <v>142.754</v>
+        <v>14.682</v>
       </c>
       <c r="I21" t="n">
-        <v>6.613</v>
+        <v>4.609</v>
       </c>
       <c r="J21" t="n">
-        <v>76.325</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>177.424</v>
+        <v>23.807</v>
       </c>
       <c r="L21" t="n">
-        <v>26.604</v>
+        <v>15.954</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>186.79</v>
+        <v>114.327</v>
       </c>
       <c r="C22" t="n">
-        <v>195.41</v>
+        <v>120.887</v>
       </c>
       <c r="D22" t="n">
-        <v>92.122</v>
+        <v>35.922</v>
       </c>
       <c r="E22" t="n">
-        <v>208.171</v>
+        <v>201.41</v>
       </c>
       <c r="F22" t="n">
-        <v>78.798</v>
+        <v>74.88800000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>76.247</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>348.007</v>
+        <v>333.396</v>
       </c>
       <c r="I22" t="n">
-        <v>218.601</v>
+        <v>168.953</v>
       </c>
       <c r="J22" t="n">
-        <v>424.852</v>
+        <v>304.833</v>
       </c>
       <c r="K22" t="n">
-        <v>236.359</v>
+        <v>159.955</v>
       </c>
       <c r="L22" t="n">
-        <v>337.703</v>
+        <v>150.705</v>
       </c>
       <c r="M22" t="n">
-        <v>191.242</v>
+        <v>18.902</v>
       </c>
     </row>
     <row r="23">
@@ -8042,40 +8042,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>68.547</v>
+        <v>55.505</v>
       </c>
       <c r="C23" t="n">
-        <v>19.376</v>
+        <v>7.236</v>
       </c>
       <c r="D23" t="n">
-        <v>18.182</v>
+        <v>6.276</v>
       </c>
       <c r="E23" t="n">
         <v>22.371</v>
       </c>
       <c r="F23" t="n">
-        <v>9.047000000000001</v>
+        <v>8.757999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>104.572</v>
+        <v>99.06</v>
       </c>
       <c r="H23" t="n">
-        <v>21.522</v>
+        <v>11.334</v>
       </c>
       <c r="I23" t="n">
-        <v>26.488</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>41.032</v>
+        <v>21.449</v>
       </c>
       <c r="K23" t="n">
-        <v>20.712</v>
+        <v>10.535</v>
       </c>
       <c r="L23" t="n">
-        <v>32.652</v>
+        <v>24.243</v>
       </c>
       <c r="M23" t="n">
-        <v>35.127</v>
+        <v>9.904999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -8085,16 +8085,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.954</v>
+        <v>6.885</v>
       </c>
       <c r="C24" t="n">
-        <v>16.375</v>
+        <v>8.907</v>
       </c>
       <c r="D24" t="n">
-        <v>12.773</v>
+        <v>5.29</v>
       </c>
       <c r="E24" t="n">
-        <v>25.242</v>
+        <v>24.782</v>
       </c>
       <c r="F24" t="n">
         <v>10.442</v>
@@ -8103,22 +8103,22 @@
         <v>123.314</v>
       </c>
       <c r="H24" t="n">
-        <v>20.425</v>
+        <v>14.395</v>
       </c>
       <c r="I24" t="n">
-        <v>25.756</v>
+        <v>22.1</v>
       </c>
       <c r="J24" t="n">
-        <v>45.773</v>
+        <v>22.573</v>
       </c>
       <c r="K24" t="n">
-        <v>20.024</v>
+        <v>10.676</v>
       </c>
       <c r="L24" t="n">
-        <v>30.576</v>
+        <v>26.582</v>
       </c>
       <c r="M24" t="n">
-        <v>30.786</v>
+        <v>16.085</v>
       </c>
     </row>
     <row r="25">
@@ -8134,7 +8134,7 @@
         <v>12.953</v>
       </c>
       <c r="D25" t="n">
-        <v>9.634</v>
+        <v>7.988</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
@@ -8143,25 +8143,25 @@
         <v>12.001</v>
       </c>
       <c r="G25" t="n">
-        <v>72.93600000000001</v>
+        <v>63.877</v>
       </c>
       <c r="H25" t="n">
-        <v>18.957</v>
+        <v>8.564</v>
       </c>
       <c r="I25" t="n">
-        <v>4.237</v>
+        <v>1.314</v>
       </c>
       <c r="J25" t="n">
-        <v>22.559</v>
+        <v>1.225</v>
       </c>
       <c r="K25" t="n">
-        <v>16.936</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>16.135</v>
+        <v>2.614</v>
       </c>
       <c r="M25" t="n">
-        <v>7.419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -8186,7 +8186,7 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>94.541</v>
+        <v>93.23399999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -8201,7 +8201,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8214,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.649</v>
+        <v>5.819</v>
       </c>
       <c r="C27" t="n">
-        <v>13.973</v>
+        <v>6.667</v>
       </c>
       <c r="D27" t="n">
-        <v>11.88</v>
+        <v>2.961</v>
       </c>
       <c r="E27" t="n">
-        <v>22.689</v>
+        <v>22.295</v>
       </c>
       <c r="F27" t="n">
-        <v>11.417</v>
+        <v>10.996</v>
       </c>
       <c r="G27" t="n">
-        <v>89.908</v>
+        <v>81.908</v>
       </c>
       <c r="H27" t="n">
-        <v>32.159</v>
+        <v>21.933</v>
       </c>
       <c r="I27" t="n">
-        <v>18.642</v>
+        <v>16.855</v>
       </c>
       <c r="J27" t="n">
-        <v>56.969</v>
+        <v>42.51</v>
       </c>
       <c r="K27" t="n">
-        <v>36.332</v>
+        <v>11.903</v>
       </c>
       <c r="L27" t="n">
-        <v>43.193</v>
+        <v>32.756</v>
       </c>
       <c r="M27" t="n">
-        <v>34.777</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.543</v>
+        <v>2.401</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,13 +8272,13 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>51.413</v>
+        <v>43.697</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.536</v>
+        <v>0.399</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -8300,37 +8300,37 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.112</v>
+        <v>1.693</v>
       </c>
       <c r="C29" t="n">
-        <v>1.371</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>21.824</v>
+        <v>21.558</v>
       </c>
       <c r="F29" t="n">
-        <v>10.523</v>
+        <v>10.421</v>
       </c>
       <c r="G29" t="n">
-        <v>65.325</v>
+        <v>61.837</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8110000000000001</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.949</v>
+        <v>0.855</v>
       </c>
       <c r="J29" t="n">
-        <v>14.104</v>
+        <v>0.067</v>
       </c>
       <c r="K29" t="n">
-        <v>6.626</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>13.898</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.815823364000001e-06</v>
+        <v>2.728599696e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.743903376000001e-06</v>
+        <v>1.668559104e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6920286084e-05</v>
+        <v>7.925450625000001e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.431509913600001e-05</v>
+        <v>5.204010312899999e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1398978756e-05</v>
+        <v>1.1205281025e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.229795562499999e-05</v>
+        <v>2.0888631841e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>6.906607236e-06</v>
+        <v>1.74900625e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.556822080999999e-06</v>
+        <v>4.694588890000001e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.583448888999999e-06</v>
+        <v>8.613696100000003e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.935805696e-06</v>
+        <v>8.7647044e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.466736641e-06</v>
+        <v>3.816768400000001e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.543701841000001e-06</v>
+        <v>1.36960209e-07</v>
       </c>
     </row>
     <row r="3">
@@ -8510,13 +8510,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.831836225000001e-06</v>
+        <v>1.823887849e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.348565444e-06</v>
+        <v>1.394200921e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.693758849e-06</v>
+        <v>3.877677441e-06</v>
       </c>
       <c r="E3" t="n">
         <v>4.7514408484e-05</v>
@@ -8525,25 +8525,25 @@
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.269155684e-06</v>
+        <v>5.899008025000002e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.479744e-07</v>
+        <v>1.129969e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.042579521e-06</v>
+        <v>3.750337599999999e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.189081639999999e-07</v>
+        <v>1.3942756e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.755843999999999e-07</v>
+        <v>5.866084000000001e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.95701649e-07</v>
+        <v>4.844401000000001e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>2.04261264e-07</v>
+        <v>2.585664e-09</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.17847616e-07</v>
+        <v>7.427260089999999e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.90268164e-07</v>
+        <v>3.96766561e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.955319961e-06</v>
+        <v>1.797251236e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8982158721e-05</v>
+        <v>3.87066276e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.421524161e-06</v>
+        <v>5.355605124e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.731988100000001e-06</v>
+        <v>3.487611136e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>3.767481e-09</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.648131599999999e-08</v>
+        <v>4.661281e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.156e-08</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3.940072900000001e-08</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0323369e-08</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0640644e-08</v>
+        <v>4.040100000000001e-11</v>
       </c>
     </row>
     <row r="5">
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.53928969e-07</v>
+        <v>3.46816129e-07</v>
       </c>
       <c r="C5" t="n">
         <v>2.9746116e-08</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.043251839999999e-07</v>
+        <v>2.52015625e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.412558400000002e-08</v>
+        <v>3.038049000000001e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.304795040000001e-07</v>
+        <v>1.00681156e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.060505324900001e-05</v>
+        <v>2.9838071169e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.544138449000001e-06</v>
+        <v>7.352548009000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.370034489e-06</v>
+        <v>2.035363225e-06</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.297056399999999e-08</v>
+        <v>2.002225e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.46531025e-07</v>
+        <v>8.584899999999997e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357225e-07</v>
+        <v>1.69744e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.406401599999998e-08</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>8.478726400000002e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8680,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.264499413333334e-07</v>
+        <v>4.436745633333333e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>9.666228033333332e-08</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.412480533333332e-08</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2.336848480333333e-06</v>
+        <v>1.981881221333334e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.438451887999999e-06</v>
+        <v>7.814530256333334e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.013752083333332e-07</v>
+        <v>4.155045453333333e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.274020544533334e-05</v>
+        <v>5.395835385633333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5840125803e-05</v>
+        <v>3.454673754133334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.103705346133334e-05</v>
+        <v>2.041803408333333e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>4.502561026133334e-05</v>
+        <v>3.845313510533333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.246509174533333e-05</v>
+        <v>6.010071480000001e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3087026875e-05</v>
+        <v>8.053391363333332e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.593379600000002e-08</v>
+        <v>7.2267001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8732,19 +8732,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.641361881e-06</v>
+        <v>5.603720164000002e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9526988121e-05</v>
+        <v>1.9009515625e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>6.293073959999999e-07</v>
+        <v>5.887902250000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002001e-09</v>
+        <v>5.86756e-10</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8775,25 +8775,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4.894741333333333e-07</v>
+        <v>4.406589603333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.693763605333333e-06</v>
+        <v>2.503202988e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>7.565232e-09</v>
+        <v>3.949121333333334e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.557541633333334e-08</v>
+        <v>4.482296333333332e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.895053333333333e-08</v>
+        <v>1.370928e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>5.787777633333332e-08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -8818,10 +8818,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.582635520000001e-07</v>
+        <v>3.492291413333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.678393227e-06</v>
+        <v>1.623129320333334e-06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.227354133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.103381333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -8861,10 +8861,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.979238670000001e-07</v>
+        <v>3.885359603333333e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.304000705333334e-06</v>
+        <v>1.265099745333333e-06</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.305633333333334e-11</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         <v>1.694407053333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.672002083333336e-07</v>
+        <v>7.536041013333334e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193221333333333e-09</v>
+        <v>1.62867e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>2.663599413333334e-07</v>
+        <v>2.362081333333334e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8847720369e-05</v>
+        <v>9.317461729000001e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0466722249e-05</v>
+        <v>3.467796543999999e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6356107881e-05</v>
+        <v>7.266028080999999e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8214058929e-05</v>
+        <v>4.5174101764e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.399349322500001e-05</v>
+        <v>5.289310022500001e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.894972496399999e-05</v>
+        <v>3.65536161e-07</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1.5109818084e-05</v>
+        <v>2.630869264e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>3.531730904100001e-05</v>
+        <v>6.680773696000001e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3694621841e-05</v>
+        <v>1.9197210916e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>5.0125388769e-05</v>
+        <v>2.365363225e-06</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.122261538133334e-05</v>
+        <v>4.554268181333334e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>7.502300176333332e-06</v>
+        <v>2.501816652e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8954549507e-05</v>
+        <v>1.026487808533333e-05</v>
       </c>
       <c r="E16" t="n">
         <v>4.743943900033334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3582217388e-05</v>
+        <v>1.339968233633333e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.382658568533334e-05</v>
+        <v>6.341679177633334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>3.690064432033333e-05</v>
+        <v>1.1578919628e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>7.062183045333335e-06</v>
+        <v>1.522307080333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5084002048e-05</v>
+        <v>2.638650353633333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.734627242799999e-05</v>
+        <v>2.883930075e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>3.946047078533333e-05</v>
+        <v>1.929146868033334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.341530760533333e-05</v>
+        <v>3.654309205333333e-06</v>
       </c>
     </row>
     <row r="17">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.214751976333333e-06</v>
+        <v>3.112130208333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>4.207956912e-06</v>
+        <v>2.613818901333333e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>1.740179840833333e-05</v>
+        <v>1.3579391523e-05</v>
       </c>
       <c r="E17" t="n">
         <v>5.773720632300001e-05</v>
@@ -9123,25 +9123,25 @@
         <v>1.0500426732e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.494449613333332e-05</v>
+        <v>3.471800248033333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.043723418133333e-05</v>
+        <v>9.580479362999998e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.604322960333334e-06</v>
+        <v>6.103280333333334e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>5.120931270533334e-05</v>
+        <v>5.586716840333335e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>1.654468245633333e-05</v>
+        <v>1.760794133333334e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>2.708659124033332e-05</v>
+        <v>8.952655151999998e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>1.816381078533333e-05</v>
+        <v>1.728432027e-06</v>
       </c>
     </row>
     <row r="18">
@@ -9151,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.777327603333333e-07</v>
+        <v>5.48290083e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.90658352e-07</v>
+        <v>1.355692963333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>6.193182719999999e-07</v>
+        <v>5.347476029999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.199385100833333e-05</v>
+        <v>5.1604115148e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.566432033333334e-06</v>
+        <v>8.492528896333331e-06</v>
       </c>
       <c r="G18" t="n">
         <v>6.555285075000002e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>4.152264033333332e-08</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.055653633333334e-08</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.07964003e-07</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>7.591276033333333e-08</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.922800833333333e-06</v>
+        <v>9.002936333333335e-09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.258750963333332e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -9194,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.39373568e-07</v>
+        <v>1.071974963333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>1.622617633333334e-08</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>2.275226253333333e-07</v>
+        <v>1.79026875e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.914662414699999e-05</v>
+        <v>4.885548853333333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.942953985333334e-06</v>
+        <v>7.786994216333332e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.884044705333334e-06</v>
+        <v>4.874849541333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.408333333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7.895070000000001e-10</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3201883e-08</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.735120333333334e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -9264,10 +9264,10 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>4.748698453333333e-07</v>
+        <v>4.4536827e-08</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7164992e-08</v>
+        <v>1.0024752e-08</v>
       </c>
       <c r="M20" t="n">
         <v>4.833621333333333e-07</v>
@@ -9280,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.153826720333333e-06</v>
+        <v>3.107815788e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>4.420301445333334e-06</v>
+        <v>3.271159323e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>2.027874083333333e-07</v>
+        <v>1.38679203e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.418037500833333e-05</v>
+        <v>1.3968045675e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.367256661333333e-06</v>
+        <v>2.340925068e-06</v>
       </c>
       <c r="G21" t="n">
         <v>2.474744965333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>6.792901505333333e-06</v>
+        <v>7.1853708e-08</v>
       </c>
       <c r="I21" t="n">
-        <v>1.457725633333334e-08</v>
+        <v>7.080960333333333e-09</v>
       </c>
       <c r="J21" t="n">
-        <v>1.941835208333333e-06</v>
+        <v>2.881140300000001e-08</v>
       </c>
       <c r="K21" t="n">
-        <v>1.049309192533333e-05</v>
+        <v>1.889244163333333e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>2.35924272e-07</v>
+        <v>8.484337199999999e-08</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.163016803333333e-05</v>
+        <v>4.356887643e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>1.272835603333333e-05</v>
+        <v>4.871222256333332e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>2.828820961333333e-06</v>
+        <v>4.301300279999999e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.444505508033333e-05</v>
+        <v>1.352199603333333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.069708268e-06</v>
+        <v>1.869404181333334e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.937868336333333e-06</v>
+        <v>1.6666347e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.036962401633334e-05</v>
+        <v>3.705096427200001e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5928799067e-05</v>
+        <v>9.515038736333332e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>6.016640730133331e-05</v>
+        <v>3.097438596300001e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.862185896033334e-05</v>
+        <v>8.528534008333335e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>3.801443873633333e-05</v>
+        <v>7.570665675000001e-06</v>
       </c>
       <c r="M22" t="n">
-        <v>1.219116752133333e-05</v>
+        <v>1.190952013333334e-07</v>
       </c>
     </row>
     <row r="23">
@@ -9366,40 +9366,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.698691208999999e-05</v>
+        <v>3.080805025e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>3.75429376e-06</v>
+        <v>5.235969599999999e-07</v>
       </c>
       <c r="D23" t="n">
-        <v>3.30585124e-06</v>
+        <v>3.938817599999999e-07</v>
       </c>
       <c r="E23" t="n">
         <v>5.00461641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>8.184820900000002e-07</v>
+        <v>7.670256399999996e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0935303184e-05</v>
+        <v>9.812883600000002e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>4.63196484e-06</v>
+        <v>1.28459556e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>7.016141440000001e-06</v>
+        <v>4.41e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>1.683625024e-05</v>
+        <v>4.600596010000001e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>4.28986944e-06</v>
+        <v>1.10986225e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066153104e-05</v>
+        <v>5.877230489999999e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.233906129000001e-05</v>
+        <v>9.810902499999998e-07</v>
       </c>
     </row>
     <row r="24">
@@ -9409,16 +9409,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19990116e-06</v>
+        <v>4.7403225e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>2.68140625e-06</v>
+        <v>7.933464900000001e-07</v>
       </c>
       <c r="D24" t="n">
-        <v>1.63149529e-06</v>
+        <v>2.798410000000001e-07</v>
       </c>
       <c r="E24" t="n">
-        <v>6.37158564e-06</v>
+        <v>6.14147524e-06</v>
       </c>
       <c r="F24" t="n">
         <v>1.09035364e-06</v>
@@ -9427,22 +9427,22 @@
         <v>1.5206342596e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>4.171806250000001e-06</v>
+        <v>2.07216025e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>6.633715360000001e-06</v>
+        <v>4.884100000000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.095167529e-05</v>
+        <v>5.095403289999999e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>4.00960576e-06</v>
+        <v>1.13976976e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>9.34891776e-06</v>
+        <v>7.066027240000001e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>9.477777960000001e-06</v>
+        <v>2.587272250000001e-06</v>
       </c>
     </row>
     <row r="25">
@@ -9458,7 +9458,7 @@
         <v>1.67780209e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>9.281395600000001e-07</v>
+        <v>6.3808144e-07</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
@@ -9467,25 +9467,25 @@
         <v>1.44024001e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>5.319660096e-06</v>
+        <v>4.080271129e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.593678490000001e-06</v>
+        <v>7.334209600000002e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7952169e-07</v>
+        <v>1.726596e-08</v>
       </c>
       <c r="J25" t="n">
-        <v>5.089084810000001e-06</v>
+        <v>1.500625e-08</v>
       </c>
       <c r="K25" t="n">
-        <v>2.86828096e-06</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.60338225e-06</v>
+        <v>6.832996e-08</v>
       </c>
       <c r="M25" t="n">
-        <v>5.504156099999999e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -9510,7 +9510,7 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.938000681e-06</v>
+        <v>8.692578755999999e-06</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03684e-09</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9538,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.59997201e-06</v>
+        <v>3.386076099999999e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>1.95244729e-06</v>
+        <v>4.4448889e-07</v>
       </c>
       <c r="D27" t="n">
-        <v>1.411344e-06</v>
+        <v>8.767520999999998e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>5.147907210000001e-06</v>
+        <v>4.970670250000002e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.30347889e-06</v>
+        <v>1.20912016e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>8.083448463999999e-06</v>
+        <v>6.708920463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>1.034201281e-05</v>
+        <v>4.81056489e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>3.47524164e-06</v>
+        <v>2.84091025e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.245466961e-05</v>
+        <v>1.8071001e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.320014224e-05</v>
+        <v>1.41681409e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>1.865635249e-05</v>
+        <v>1.072955536e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.209439729e-05</v>
+        <v>6.953892100000002e-07</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.466849e-08</v>
+        <v>5.764801e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,13 +9596,13 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.643296568999999e-06</v>
+        <v>1.909427809e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.87296e-09</v>
+        <v>1.59201e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -9624,37 +9624,37 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.460544e-08</v>
+        <v>2.866249e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>1.879641e-08</v>
+        <v>8.723560000000001e-09</v>
       </c>
       <c r="D29" t="n">
-        <v>1.296e-09</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.762869760000001e-06</v>
+        <v>4.64747364e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.10733529e-06</v>
+        <v>1.08597241e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>4.267355625000001e-06</v>
+        <v>3.823814569e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>6.577210000000002e-09</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3.798601e-08</v>
+        <v>7.310249999999999e-09</v>
       </c>
       <c r="J29" t="n">
-        <v>1.98922816e-06</v>
+        <v>4.489000000000001e-11</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3903876e-07</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.93154404e-06</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82.55800000000001</v>
+        <v>52.236</v>
       </c>
       <c r="C2" t="n">
-        <v>68.876</v>
+        <v>40.848</v>
       </c>
       <c r="D2" t="n">
-        <v>130.078</v>
+        <v>89.02500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>233.056</v>
+        <v>228.123</v>
       </c>
       <c r="F2" t="n">
-        <v>106.766</v>
+        <v>105.855</v>
       </c>
       <c r="G2" t="n">
-        <v>149.325</v>
+        <v>144.529</v>
       </c>
       <c r="H2" t="n">
-        <v>83.10599999999999</v>
+        <v>13.225</v>
       </c>
       <c r="I2" t="n">
-        <v>97.759</v>
+        <v>21.667</v>
       </c>
       <c r="J2" t="n">
-        <v>87.083</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>62.736</v>
+        <v>9.362</v>
       </c>
       <c r="L2" t="n">
-        <v>58.879</v>
+        <v>6.178</v>
       </c>
       <c r="M2" t="n">
-        <v>59.529</v>
+        <v>11.703</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.215</v>
+        <v>42.707</v>
       </c>
       <c r="C3" t="n">
-        <v>48.462</v>
+        <v>37.339</v>
       </c>
       <c r="D3" t="n">
-        <v>75.45699999999999</v>
+        <v>62.271</v>
       </c>
       <c r="E3" t="n">
-        <v>216.43</v>
+        <v>216.724</v>
       </c>
       <c r="F3" t="n">
-        <v>75.63</v>
+        <v>76.273</v>
       </c>
       <c r="G3" t="n">
-        <v>79.178</v>
+        <v>76.80500000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>29.12</v>
+        <v>1.063</v>
       </c>
       <c r="I3" t="n">
-        <v>32.289</v>
+        <v>6.124</v>
       </c>
       <c r="J3" t="n">
-        <v>17.858</v>
+        <v>3.734</v>
       </c>
       <c r="K3" t="n">
-        <v>19.38</v>
+        <v>2.422</v>
       </c>
       <c r="L3" t="n">
-        <v>24.407</v>
+        <v>2.201</v>
       </c>
       <c r="M3" t="n">
-        <v>14.292</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.296</v>
+        <v>27.253</v>
       </c>
       <c r="C4" t="n">
-        <v>22.142</v>
+        <v>19.919</v>
       </c>
       <c r="D4" t="n">
-        <v>44.219</v>
+        <v>42.394</v>
       </c>
       <c r="E4" t="n">
-        <v>197.439</v>
+        <v>196.74</v>
       </c>
       <c r="F4" t="n">
-        <v>73.593</v>
+        <v>73.179</v>
       </c>
       <c r="G4" t="n">
-        <v>61.09</v>
+        <v>59.056</v>
       </c>
       <c r="H4" t="n">
-        <v>1.941</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5.134</v>
+        <v>2.159</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6.277</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.213</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.262</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.813</v>
+        <v>18.424</v>
       </c>
       <c r="C5" t="n">
-        <v>5.273</v>
+        <v>4.869</v>
       </c>
       <c r="D5" t="n">
-        <v>18.073</v>
+        <v>18.03</v>
       </c>
       <c r="E5" t="n">
-        <v>195.367</v>
+        <v>196.141</v>
       </c>
       <c r="F5" t="n">
-        <v>94.544</v>
+        <v>94.65900000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>78.178</v>
+        <v>78.86199999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.072</v>
+        <v>15.875</v>
       </c>
       <c r="C6" t="n">
-        <v>9.172000000000001</v>
+        <v>1.743</v>
       </c>
       <c r="D6" t="n">
-        <v>20.748</v>
+        <v>10.034</v>
       </c>
       <c r="E6" t="n">
-        <v>174.943</v>
+        <v>172.737</v>
       </c>
       <c r="F6" t="n">
-        <v>86.857</v>
+        <v>85.747</v>
       </c>
       <c r="G6" t="n">
-        <v>48.683</v>
+        <v>45.115</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5.742</v>
+        <v>1.415</v>
       </c>
       <c r="J6" t="n">
-        <v>12.105</v>
+        <v>0.293</v>
       </c>
       <c r="K6" t="n">
-        <v>11.65</v>
+        <v>0.347</v>
       </c>
       <c r="L6" t="n">
-        <v>8.004</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>9.208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.768</v>
+        <v>11.537</v>
       </c>
       <c r="C7" t="n">
-        <v>17.029</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>16.804</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>83.729</v>
+        <v>77.108</v>
       </c>
       <c r="F7" t="n">
-        <v>159.108</v>
+        <v>153.113</v>
       </c>
       <c r="G7" t="n">
-        <v>42.475</v>
+        <v>35.306</v>
       </c>
       <c r="H7" t="n">
-        <v>433.7</v>
+        <v>402.337</v>
       </c>
       <c r="I7" t="n">
-        <v>327.903</v>
+        <v>321.932</v>
       </c>
       <c r="J7" t="n">
-        <v>350.872</v>
+        <v>78.265</v>
       </c>
       <c r="K7" t="n">
-        <v>367.528</v>
+        <v>339.646</v>
       </c>
       <c r="L7" t="n">
-        <v>259.606</v>
+        <v>42.462</v>
       </c>
       <c r="M7" t="n">
-        <v>263.175</v>
+        <v>49.153</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.714</v>
+        <v>8.500999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.10899999999999</v>
+        <v>74.858</v>
       </c>
       <c r="F8" t="n">
-        <v>139.739</v>
+        <v>137.875</v>
       </c>
       <c r="G8" t="n">
-        <v>25.086</v>
+        <v>24.265</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.001</v>
+        <v>0.766</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>83.087</v>
+        <v>84.98</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10099,25 +10099,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>38.32</v>
+        <v>36.359</v>
       </c>
       <c r="F9" t="n">
-        <v>89.896</v>
+        <v>86.658</v>
       </c>
       <c r="G9" t="n">
-        <v>4.764</v>
+        <v>3.442</v>
       </c>
       <c r="H9" t="n">
-        <v>4.508</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>11.693</v>
+        <v>3.667</v>
       </c>
       <c r="J9" t="n">
-        <v>7.54</v>
+        <v>2.028</v>
       </c>
       <c r="K9" t="n">
-        <v>13.177</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -10142,10 +10142,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.784</v>
+        <v>32.017</v>
       </c>
       <c r="F10" t="n">
-        <v>70.959</v>
+        <v>69.78100000000001</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -10154,10 +10154,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.068</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.512</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -10185,10 +10185,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34.551</v>
+        <v>33.871</v>
       </c>
       <c r="F11" t="n">
-        <v>62.546</v>
+        <v>61.606</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.263</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.383</v>
+        <v>22.256</v>
       </c>
       <c r="F12" t="n">
-        <v>47.975</v>
+        <v>47.548</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10271,10 +10271,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.892</v>
+        <v>0.699</v>
       </c>
       <c r="F13" t="n">
-        <v>28.268</v>
+        <v>26.62</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137.287</v>
+        <v>96.527</v>
       </c>
       <c r="C15" t="n">
-        <v>102.307</v>
+        <v>58.888</v>
       </c>
       <c r="D15" t="n">
-        <v>127.891</v>
+        <v>85.241</v>
       </c>
       <c r="E15" t="n">
-        <v>219.577</v>
+        <v>212.542</v>
       </c>
       <c r="F15" t="n">
-        <v>97.423</v>
+        <v>96.351</v>
       </c>
       <c r="G15" t="n">
-        <v>232.365</v>
+        <v>227.132</v>
       </c>
       <c r="H15" t="n">
-        <v>137.658</v>
+        <v>17.825</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>122.922</v>
+        <v>51.292</v>
       </c>
       <c r="K15" t="n">
-        <v>187.929</v>
+        <v>68.693</v>
       </c>
       <c r="L15" t="n">
-        <v>231.721</v>
+        <v>119.495</v>
       </c>
       <c r="M15" t="n">
-        <v>223.887</v>
+        <v>48.635</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>183.488</v>
+        <v>116.888</v>
       </c>
       <c r="C16" t="n">
-        <v>150.023</v>
+        <v>86.634</v>
       </c>
       <c r="D16" t="n">
-        <v>238.461</v>
+        <v>175.484</v>
       </c>
       <c r="E16" t="n">
-        <v>371.992</v>
+        <v>375.145</v>
       </c>
       <c r="F16" t="n">
-        <v>201.858</v>
+        <v>199.537</v>
       </c>
       <c r="G16" t="n">
-        <v>418.489</v>
+        <v>435.904</v>
       </c>
       <c r="H16" t="n">
-        <v>332.095</v>
+        <v>186.378</v>
       </c>
       <c r="I16" t="n">
-        <v>145.556</v>
+        <v>67.57899999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>403.494</v>
+        <v>281.353</v>
       </c>
       <c r="K16" t="n">
-        <v>334.722</v>
+        <v>93.015</v>
       </c>
       <c r="L16" t="n">
-        <v>344.066</v>
+        <v>240.571</v>
       </c>
       <c r="M16" t="n">
-        <v>360.896</v>
+        <v>104.704</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125.077</v>
+        <v>96.625</v>
       </c>
       <c r="C17" t="n">
-        <v>112.356</v>
+        <v>88.55200000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>228.485</v>
+        <v>201.837</v>
       </c>
       <c r="E17" t="n">
-        <v>415.616</v>
+        <v>415.356</v>
       </c>
       <c r="F17" t="n">
-        <v>176.782</v>
+        <v>176.602</v>
       </c>
       <c r="G17" t="n">
-        <v>323.78</v>
+        <v>322.729</v>
       </c>
       <c r="H17" t="n">
-        <v>247.612</v>
+        <v>169.533</v>
       </c>
       <c r="I17" t="n">
-        <v>88.39100000000001</v>
+        <v>42.79</v>
       </c>
       <c r="J17" t="n">
-        <v>391.954</v>
+        <v>129.461</v>
       </c>
       <c r="K17" t="n">
-        <v>222.787</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>285.061</v>
+        <v>163.884</v>
       </c>
       <c r="M17" t="n">
-        <v>233.434</v>
+        <v>72.009</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.091</v>
+        <v>40.557</v>
       </c>
       <c r="C18" t="n">
-        <v>23.916</v>
+        <v>20.167</v>
       </c>
       <c r="D18" t="n">
-        <v>43.104</v>
+        <v>40.053</v>
       </c>
       <c r="E18" t="n">
-        <v>394.945</v>
+        <v>393.462</v>
       </c>
       <c r="F18" t="n">
-        <v>160.31</v>
+        <v>159.419</v>
       </c>
       <c r="G18" t="n">
-        <v>139.786</v>
+        <v>140.198</v>
       </c>
       <c r="H18" t="n">
-        <v>11.161</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>7.853</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>17.997</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>15.091</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>75.95</v>
+        <v>5.197</v>
       </c>
       <c r="M18" t="n">
-        <v>31.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.448</v>
+        <v>17.933</v>
       </c>
       <c r="C19" t="n">
-        <v>6.977</v>
+        <v>4.508</v>
       </c>
       <c r="D19" t="n">
-        <v>26.126</v>
+        <v>23.175</v>
       </c>
       <c r="E19" t="n">
-        <v>383.979</v>
+        <v>382.84</v>
       </c>
       <c r="F19" t="n">
-        <v>154.366</v>
+        <v>152.843</v>
       </c>
       <c r="G19" t="n">
-        <v>121.046</v>
+        <v>120.932</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.539</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>8.343</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -10561,40 +10561,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>129.122</v>
+        <v>132.136</v>
       </c>
       <c r="C20" t="n">
-        <v>132.856</v>
+        <v>136.172</v>
       </c>
       <c r="D20" t="n">
-        <v>42.401</v>
+        <v>45.395</v>
       </c>
       <c r="E20" t="n">
-        <v>222.514</v>
+        <v>224.255</v>
       </c>
       <c r="F20" t="n">
-        <v>98.078</v>
+        <v>98.873</v>
       </c>
       <c r="G20" t="n">
-        <v>120.385</v>
+        <v>124.497</v>
       </c>
       <c r="H20" t="n">
-        <v>15.514</v>
+        <v>10.995</v>
       </c>
       <c r="I20" t="n">
-        <v>3.692</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3.644</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>37.744</v>
+        <v>9.539</v>
       </c>
       <c r="L20" t="n">
-        <v>6.086</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.504</v>
       </c>
     </row>
     <row r="21">
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111.631</v>
+        <v>96.55800000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>115.156</v>
+        <v>99.063</v>
       </c>
       <c r="D21" t="n">
-        <v>24.665</v>
+        <v>20.397</v>
       </c>
       <c r="E21" t="n">
-        <v>206.255</v>
+        <v>204.705</v>
       </c>
       <c r="F21" t="n">
-        <v>84.27200000000001</v>
+        <v>83.80200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>85.378</v>
+        <v>86.005</v>
       </c>
       <c r="H21" t="n">
-        <v>142.754</v>
+        <v>14.682</v>
       </c>
       <c r="I21" t="n">
-        <v>6.612</v>
+        <v>4.609</v>
       </c>
       <c r="J21" t="n">
-        <v>76.325</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>177.424</v>
+        <v>23.807</v>
       </c>
       <c r="L21" t="n">
-        <v>26.604</v>
+        <v>15.954</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>186.79</v>
+        <v>114.327</v>
       </c>
       <c r="C22" t="n">
-        <v>195.41</v>
+        <v>120.887</v>
       </c>
       <c r="D22" t="n">
-        <v>92.122</v>
+        <v>35.922</v>
       </c>
       <c r="E22" t="n">
-        <v>208.171</v>
+        <v>201.41</v>
       </c>
       <c r="F22" t="n">
-        <v>78.798</v>
+        <v>74.88800000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>76.247</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>348.007</v>
+        <v>333.396</v>
       </c>
       <c r="I22" t="n">
-        <v>206.965</v>
+        <v>168.953</v>
       </c>
       <c r="J22" t="n">
-        <v>422.406</v>
+        <v>304.833</v>
       </c>
       <c r="K22" t="n">
-        <v>236.359</v>
+        <v>159.955</v>
       </c>
       <c r="L22" t="n">
-        <v>337.703</v>
+        <v>150.705</v>
       </c>
       <c r="M22" t="n">
-        <v>191.242</v>
+        <v>18.902</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13.768</v>
+        <v>27.053</v>
       </c>
       <c r="C23" t="n">
-        <v>19.376</v>
+        <v>7.236</v>
       </c>
       <c r="D23" t="n">
-        <v>18.182</v>
+        <v>6.276</v>
       </c>
       <c r="E23" t="n">
-        <v>22.222</v>
+        <v>21.546</v>
       </c>
       <c r="F23" t="n">
-        <v>9.047000000000001</v>
+        <v>8.757999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>104.572</v>
+        <v>99.06</v>
       </c>
       <c r="H23" t="n">
-        <v>20.744</v>
+        <v>11.334</v>
       </c>
       <c r="I23" t="n">
-        <v>25.957</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>41.032</v>
+        <v>21.449</v>
       </c>
       <c r="K23" t="n">
-        <v>20.202</v>
+        <v>10.535</v>
       </c>
       <c r="L23" t="n">
-        <v>32.652</v>
+        <v>24.243</v>
       </c>
       <c r="M23" t="n">
-        <v>35.127</v>
+        <v>9.904999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.954</v>
+        <v>6.885</v>
       </c>
       <c r="C24" t="n">
-        <v>16.375</v>
+        <v>8.907</v>
       </c>
       <c r="D24" t="n">
-        <v>12.773</v>
+        <v>5.29</v>
       </c>
       <c r="E24" t="n">
-        <v>25.242</v>
+        <v>24.782</v>
       </c>
       <c r="F24" t="n">
-        <v>10.405</v>
+        <v>10.331</v>
       </c>
       <c r="G24" t="n">
-        <v>122.373</v>
+        <v>122.325</v>
       </c>
       <c r="H24" t="n">
-        <v>19.39</v>
+        <v>14.395</v>
       </c>
       <c r="I24" t="n">
-        <v>24.773</v>
+        <v>22.1</v>
       </c>
       <c r="J24" t="n">
-        <v>45.773</v>
+        <v>22.573</v>
       </c>
       <c r="K24" t="n">
-        <v>19.559</v>
+        <v>10.676</v>
       </c>
       <c r="L24" t="n">
-        <v>29.922</v>
+        <v>26.582</v>
       </c>
       <c r="M24" t="n">
-        <v>30.504</v>
+        <v>16.085</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12.412</v>
+        <v>11.742</v>
       </c>
       <c r="C25" t="n">
-        <v>12.755</v>
+        <v>10.397</v>
       </c>
       <c r="D25" t="n">
-        <v>9.634</v>
+        <v>7.173</v>
       </c>
       <c r="E25" t="n">
-        <v>26.662</v>
+        <v>26.426</v>
       </c>
       <c r="F25" t="n">
-        <v>11.877</v>
+        <v>11.776</v>
       </c>
       <c r="G25" t="n">
-        <v>72.93600000000001</v>
+        <v>63.877</v>
       </c>
       <c r="H25" t="n">
-        <v>18.957</v>
+        <v>8.564</v>
       </c>
       <c r="I25" t="n">
-        <v>4.237</v>
+        <v>1.271</v>
       </c>
       <c r="J25" t="n">
-        <v>22.559</v>
+        <v>1.225</v>
       </c>
       <c r="K25" t="n">
-        <v>16.936</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>16.135</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>7.419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -10819,28 +10819,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.614</v>
+        <v>7.58</v>
       </c>
       <c r="C26" t="n">
-        <v>9.493</v>
+        <v>9.933999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>3.604</v>
+        <v>3.571</v>
       </c>
       <c r="E26" t="n">
-        <v>22.569</v>
+        <v>22.686</v>
       </c>
       <c r="F26" t="n">
-        <v>11.251</v>
+        <v>11.281</v>
       </c>
       <c r="G26" t="n">
-        <v>94.541</v>
+        <v>93.23399999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.641</v>
+        <v>0.705</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -10849,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.649</v>
+        <v>5.819</v>
       </c>
       <c r="C27" t="n">
-        <v>13.973</v>
+        <v>4.266</v>
       </c>
       <c r="D27" t="n">
-        <v>11.88</v>
+        <v>2.961</v>
       </c>
       <c r="E27" t="n">
-        <v>22.689</v>
+        <v>22.007</v>
       </c>
       <c r="F27" t="n">
-        <v>11.417</v>
+        <v>10.996</v>
       </c>
       <c r="G27" t="n">
-        <v>89.908</v>
+        <v>81.908</v>
       </c>
       <c r="H27" t="n">
-        <v>32.159</v>
+        <v>21.933</v>
       </c>
       <c r="I27" t="n">
-        <v>15.881</v>
+        <v>16.855</v>
       </c>
       <c r="J27" t="n">
-        <v>56.969</v>
+        <v>42.51</v>
       </c>
       <c r="K27" t="n">
-        <v>36.332</v>
+        <v>11.903</v>
       </c>
       <c r="L27" t="n">
-        <v>43.193</v>
+        <v>32.756</v>
       </c>
       <c r="M27" t="n">
-        <v>34.777</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.543</v>
+        <v>2.401</v>
       </c>
       <c r="C28" t="n">
-        <v>0.786</v>
+        <v>0.661</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.17</v>
+        <v>22.238</v>
       </c>
       <c r="F28" t="n">
-        <v>10.967</v>
+        <v>10.991</v>
       </c>
       <c r="G28" t="n">
-        <v>51.413</v>
+        <v>43.697</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.536</v>
+        <v>0.399</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,37 +10948,37 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.112</v>
+        <v>1.693</v>
       </c>
       <c r="C29" t="n">
-        <v>1.371</v>
+        <v>0.284</v>
       </c>
       <c r="D29" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>21.824</v>
+        <v>21.558</v>
       </c>
       <c r="F29" t="n">
-        <v>10.523</v>
+        <v>10.421</v>
       </c>
       <c r="G29" t="n">
-        <v>65.325</v>
+        <v>61.837</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8110000000000001</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1.949</v>
+        <v>0.828</v>
       </c>
       <c r="J29" t="n">
-        <v>14.104</v>
+        <v>0.067</v>
       </c>
       <c r="K29" t="n">
-        <v>6.626</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>13.898</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.747</v>
+        <v>13.808</v>
       </c>
       <c r="F30" t="n">
-        <v>5.879</v>
+        <v>5.919</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.815823364000001e-06</v>
+        <v>2.728599696e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>4.743903376000001e-06</v>
+        <v>1.668559104e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6920286084e-05</v>
+        <v>7.925450625000001e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.431509913600001e-05</v>
+        <v>5.204010312899999e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1398978756e-05</v>
+        <v>1.1205281025e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.229795562499999e-05</v>
+        <v>2.0888631841e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>6.906607236e-06</v>
+        <v>1.74900625e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>9.556822080999999e-06</v>
+        <v>4.694588890000001e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.583448888999999e-06</v>
+        <v>8.613696100000003e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.935805696e-06</v>
+        <v>8.7647044e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.466736641e-06</v>
+        <v>3.816768400000001e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.543701841000001e-06</v>
+        <v>1.36960209e-07</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.831836225000001e-06</v>
+        <v>1.823887849e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.348565444e-06</v>
+        <v>1.394200921e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.693758849e-06</v>
+        <v>3.877677441e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.68419449e-05</v>
+        <v>4.6969292176e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.719896899999999e-06</v>
+        <v>5.817570528999999e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.269155684e-06</v>
+        <v>5.899008025000002e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.479744e-07</v>
+        <v>1.129969e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.042579521e-06</v>
+        <v>3.750337599999999e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.189081639999999e-07</v>
+        <v>1.3942756e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.755843999999999e-07</v>
+        <v>5.866084000000001e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.95701649e-07</v>
+        <v>4.844401000000001e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>2.04261264e-07</v>
+        <v>2.585664e-09</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.17847616e-07</v>
+        <v>7.427260089999999e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.90268164e-07</v>
+        <v>3.96766561e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.955319961e-06</v>
+        <v>1.797251236e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8982158721e-05</v>
+        <v>3.87066276e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.415929649000001e-06</v>
+        <v>5.355166041000001e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.731988100000001e-06</v>
+        <v>3.487611136e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>3.767481e-09</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.635795600000001e-08</v>
+        <v>4.661281e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.156e-08</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3.940072900000001e-08</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0323369e-08</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0640644e-08</v>
+        <v>4.040100000000001e-11</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.53928969e-07</v>
+        <v>3.39443776e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7804529e-08</v>
+        <v>2.3707161e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.26633329e-07</v>
+        <v>3.250809e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8168264689e-05</v>
+        <v>3.847129188099999e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.938567936000002e-06</v>
+        <v>8.960326281000003e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>6.111799683999999e-06</v>
+        <v>6.219215044e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.043251839999999e-07</v>
+        <v>2.52015625e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>8.412558400000002e-08</v>
+        <v>3.038049000000001e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.304795040000001e-07</v>
+        <v>1.00681156e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.060505324900001e-05</v>
+        <v>2.9838071169e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.544138449000001e-06</v>
+        <v>7.352548009000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.370034489e-06</v>
+        <v>2.035363225e-06</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.297056399999999e-08</v>
+        <v>2.002225e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.46531025e-07</v>
+        <v>8.584899999999997e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357225e-07</v>
+        <v>1.20409e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>6.406401599999998e-08</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>8.478726400000002e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.264499413333334e-07</v>
+        <v>4.436745633333333e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>9.666228033333332e-08</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9.412480533333332e-08</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2.336848480333333e-06</v>
+        <v>1.981881221333334e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.438451887999999e-06</v>
+        <v>7.814530256333334e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.013752083333332e-07</v>
+        <v>4.155045453333333e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.269856333333332e-05</v>
+        <v>5.395835385633333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5840125803e-05</v>
+        <v>3.454673754133334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.103705346133334e-05</v>
+        <v>2.041803408333333e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>4.502561026133334e-05</v>
+        <v>3.845313510533333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.246509174533333e-05</v>
+        <v>6.010071480000001e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3087026875e-05</v>
+        <v>8.053391363333332e-07</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.593379600000002e-08</v>
+        <v>7.2267001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.641361881e-06</v>
+        <v>5.603720164000002e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9526988121e-05</v>
+        <v>1.9009515625e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>6.293073959999999e-07</v>
+        <v>5.887902250000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002001e-09</v>
+        <v>5.86756e-10</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.903449569000001e-06</v>
+        <v>7.2216004e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11423,25 +11423,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4.894741333333333e-07</v>
+        <v>4.406589603333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.693763605333333e-06</v>
+        <v>2.503202988e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>7.565232e-09</v>
+        <v>3.949121333333334e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.557541633333334e-08</v>
+        <v>4.482296333333332e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.895053333333333e-08</v>
+        <v>1.370928e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>5.787777633333332e-08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -11466,10 +11466,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.582635520000001e-07</v>
+        <v>3.416960963333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.678393227e-06</v>
+        <v>1.623129320333334e-06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -11478,10 +11478,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.227354133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.103381333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -11509,10 +11509,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.979238670000001e-07</v>
+        <v>3.824148803333335e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.304000705333334e-06</v>
+        <v>1.265099745333333e-06</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -11524,7 +11524,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.305633333333334e-11</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.66999563e-07</v>
+        <v>1.651098453333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.672002083333336e-07</v>
+        <v>7.536041013333334e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193221333333333e-09</v>
+        <v>1.62867e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>2.663599413333334e-07</v>
+        <v>2.362081333333334e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8847720369e-05</v>
+        <v>9.317461729000001e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0466722249e-05</v>
+        <v>3.467796543999999e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6356107881e-05</v>
+        <v>7.266028080999999e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8214058929e-05</v>
+        <v>4.5174101764e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.491240929e-06</v>
+        <v>9.283515200999998e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.399349322500001e-05</v>
+        <v>5.1588945424e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.894972496399999e-05</v>
+        <v>3.17730625e-07</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1.5109818084e-05</v>
+        <v>2.630869264e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>3.531730904100001e-05</v>
+        <v>4.718728249000001e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3694621841e-05</v>
+        <v>1.4279055025e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>5.0125388769e-05</v>
+        <v>2.365363225e-06</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.122261538133334e-05</v>
+        <v>4.554268181333334e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>7.502300176333332e-06</v>
+        <v>2.501816652e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8954549507e-05</v>
+        <v>1.026487808533333e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.612601602133335e-05</v>
+        <v>4.691125700833334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3582217388e-05</v>
+        <v>1.327167145633334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>5.837768104033333e-05</v>
+        <v>6.333743240533333e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>3.676236300833334e-05</v>
+        <v>1.1578919628e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>7.062183045333335e-06</v>
+        <v>1.522307080333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.426913601200001e-05</v>
+        <v>2.638650353633333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.734627242799999e-05</v>
+        <v>2.883930075e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>3.946047078533333e-05</v>
+        <v>1.929146868033334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.341530760533333e-05</v>
+        <v>3.654309205333333e-06</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.214751976333333e-06</v>
+        <v>3.112130208333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>4.207956912e-06</v>
+        <v>2.613818901333333e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>1.740179840833333e-05</v>
+        <v>1.3579391523e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.757888648533332e-05</v>
+        <v>5.7506868912e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.041729184133334e-05</v>
+        <v>1.039608880133333e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.494449613333332e-05</v>
+        <v>3.471800248033333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.043723418133333e-05</v>
+        <v>9.580479362999998e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>2.604322960333334e-06</v>
+        <v>6.103280333333334e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>5.120931270533334e-05</v>
+        <v>5.586716840333335e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>1.654468245633333e-05</v>
+        <v>1.760794133333334e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>2.708659124033332e-05</v>
+        <v>8.952655151999998e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>1.816381078533333e-05</v>
+        <v>1.728432027e-06</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.777327603333333e-07</v>
+        <v>5.48290083e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.90658352e-07</v>
+        <v>1.355692963333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>6.193182719999999e-07</v>
+        <v>5.347476029999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.199385100833333e-05</v>
+        <v>5.1604115148e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.566432033333334e-06</v>
+        <v>8.471472520333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.513375265333333e-06</v>
+        <v>6.551826401333335e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>4.152264033333332e-08</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.055653633333334e-08</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.07964003e-07</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>7.591276033333333e-08</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.922800833333333e-06</v>
+        <v>9.002936333333335e-09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.258750963333332e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.39373568e-07</v>
+        <v>1.071974963333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>1.622617633333334e-08</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>2.275226253333333e-07</v>
+        <v>1.79026875e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.914662414699999e-05</v>
+        <v>4.885548853333333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.942953985333334e-06</v>
+        <v>7.786994216333332e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.884044705333334e-06</v>
+        <v>4.874849541333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.408333333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7.895070000000001e-10</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3201883e-08</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.735120333333334e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -11885,40 +11885,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.557496961333335e-06</v>
+        <v>5.819974165333333e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>5.883572245333334e-06</v>
+        <v>6.180937861333332e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>5.992816003333334e-07</v>
+        <v>6.869020083333335e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.650416006533334e-05</v>
+        <v>1.676343500833333e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.206431361333333e-06</v>
+        <v>3.258623376333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>4.830849408333334e-06</v>
+        <v>5.166501003e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>8.022806533333333e-08</v>
+        <v>4.029667499999999e-08</v>
       </c>
       <c r="I20" t="n">
-        <v>4.543621333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>4.426245333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4.748698453333333e-07</v>
+        <v>3.033084033333332e-08</v>
       </c>
       <c r="L20" t="n">
-        <v>1.234646533333334e-08</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7.540053333333332e-10</v>
       </c>
     </row>
     <row r="21">
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.153826720333333e-06</v>
+        <v>3.107815788e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>4.420301445333334e-06</v>
+        <v>3.271159323e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>2.027874083333333e-07</v>
+        <v>1.38679203e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.418037500833333e-05</v>
+        <v>1.3968045675e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.367256661333333e-06</v>
+        <v>2.340925068e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.429800961333333e-06</v>
+        <v>2.465620008333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>6.792901505333333e-06</v>
+        <v>7.1853708e-08</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4572848e-08</v>
+        <v>7.080960333333333e-09</v>
       </c>
       <c r="J21" t="n">
-        <v>1.941835208333333e-06</v>
+        <v>2.881140300000001e-08</v>
       </c>
       <c r="K21" t="n">
-        <v>1.049309192533333e-05</v>
+        <v>1.889244163333333e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>2.35924272e-07</v>
+        <v>8.484337199999999e-08</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.163016803333333e-05</v>
+        <v>4.356887643e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>1.272835603333333e-05</v>
+        <v>4.871222256333332e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>2.828820961333333e-06</v>
+        <v>4.301300279999999e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.444505508033333e-05</v>
+        <v>1.352199603333333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.069708268e-06</v>
+        <v>1.869404181333334e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.937868336333333e-06</v>
+        <v>1.6666347e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.036962401633334e-05</v>
+        <v>3.705096427200001e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.427817040833333e-05</v>
+        <v>9.515038736333332e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>5.9475609612e-05</v>
+        <v>3.097438596300001e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.862185896033334e-05</v>
+        <v>8.528534008333335e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>3.801443873633333e-05</v>
+        <v>7.570665675000001e-06</v>
       </c>
       <c r="M22" t="n">
-        <v>1.219116752133333e-05</v>
+        <v>1.190952013333334e-07</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.89557824e-06</v>
+        <v>7.31864809e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>3.75429376e-06</v>
+        <v>5.235969599999999e-07</v>
       </c>
       <c r="D23" t="n">
-        <v>3.30585124e-06</v>
+        <v>3.938817599999999e-07</v>
       </c>
       <c r="E23" t="n">
-        <v>4.938172840000001e-06</v>
+        <v>4.64230116e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>8.184820900000002e-07</v>
+        <v>7.670256399999996e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0935303184e-05</v>
+        <v>9.812883600000002e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>4.30313536e-06</v>
+        <v>1.28459556e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>6.737658490000001e-06</v>
+        <v>4.41e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>1.683625024e-05</v>
+        <v>4.600596010000001e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>4.08120804e-06</v>
+        <v>1.10986225e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066153104e-05</v>
+        <v>5.877230489999999e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.233906129000001e-05</v>
+        <v>9.810902499999998e-07</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19990116e-06</v>
+        <v>4.7403225e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>2.68140625e-06</v>
+        <v>7.933464900000001e-07</v>
       </c>
       <c r="D24" t="n">
-        <v>1.63149529e-06</v>
+        <v>2.798410000000001e-07</v>
       </c>
       <c r="E24" t="n">
-        <v>6.37158564e-06</v>
+        <v>6.14147524e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.08264025e-06</v>
+        <v>1.06729561e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4975151129e-05</v>
+        <v>1.4963405625e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>3.759721000000001e-06</v>
+        <v>2.07216025e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>6.13701529e-06</v>
+        <v>4.884100000000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.095167529e-05</v>
+        <v>5.095403289999999e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>3.82554481e-06</v>
+        <v>1.13976976e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>8.953260840000001e-06</v>
+        <v>7.066027240000001e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>9.30494016e-06</v>
+        <v>2.587272250000001e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.54057744e-06</v>
+        <v>1.37874564e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.62690025e-06</v>
+        <v>1.08097609e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>9.281395600000001e-07</v>
+        <v>5.145192899999999e-07</v>
       </c>
       <c r="E25" t="n">
-        <v>7.108622439999999e-06</v>
+        <v>6.98333476e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.41063129e-06</v>
+        <v>1.38674176e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>5.319660096e-06</v>
+        <v>4.080271129e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.593678490000001e-06</v>
+        <v>7.334209600000002e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7952169e-07</v>
+        <v>1.615441e-08</v>
       </c>
       <c r="J25" t="n">
-        <v>5.089084810000001e-06</v>
+        <v>1.500625e-08</v>
       </c>
       <c r="K25" t="n">
-        <v>2.86828096e-06</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.60338225e-06</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.504156099999999e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -12143,28 +12143,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.797299600000001e-07</v>
+        <v>5.74564e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>9.011704899999999e-07</v>
+        <v>9.868435600000001e-07</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2988816e-07</v>
+        <v>1.2752041e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.093597609999999e-06</v>
+        <v>5.14654596e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.26585001e-06</v>
+        <v>1.27260961e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.938000681e-06</v>
+        <v>8.692578755999999e-06</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4.10881e-09</v>
+        <v>4.97025e-09</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -12173,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03684e-09</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.59997201e-06</v>
+        <v>3.386076099999999e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>1.95244729e-06</v>
+        <v>1.8198756e-07</v>
       </c>
       <c r="D27" t="n">
-        <v>1.411344e-06</v>
+        <v>8.767520999999998e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>5.147907210000001e-06</v>
+        <v>4.843080490000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.30347889e-06</v>
+        <v>1.20912016e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>8.083448463999999e-06</v>
+        <v>6.708920463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>1.034201281e-05</v>
+        <v>4.81056489e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>2.52206161e-06</v>
+        <v>2.84091025e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.245466961e-05</v>
+        <v>1.8071001e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.320014224e-05</v>
+        <v>1.41681409e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>1.865635249e-05</v>
+        <v>1.072955536e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.209439729e-05</v>
+        <v>6.953892100000002e-07</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.466849e-08</v>
+        <v>5.764801e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>6.17796e-09</v>
+        <v>4.369210000000001e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.915089000000001e-06</v>
+        <v>4.945286440000001e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.20275089e-06</v>
+        <v>1.20802081e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.643296568999999e-06</v>
+        <v>1.909427809e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.87296e-09</v>
+        <v>1.59201e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,37 +12272,37 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.460544e-08</v>
+        <v>2.866249e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>1.879641e-08</v>
+        <v>8.065599999999997e-10</v>
       </c>
       <c r="D29" t="n">
-        <v>1.296e-09</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.762869760000001e-06</v>
+        <v>4.64747364e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.10733529e-06</v>
+        <v>1.08597241e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>4.267355625000001e-06</v>
+        <v>3.823814569e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>6.577210000000002e-09</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3.798601e-08</v>
+        <v>6.855839999999999e-09</v>
       </c>
       <c r="J29" t="n">
-        <v>1.98922816e-06</v>
+        <v>4.489000000000001e-11</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3903876e-07</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.93154404e-06</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.88980009e-06</v>
+        <v>1.90660864e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.4562641e-07</v>
+        <v>3.5034561e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="J2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M2" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="3">
@@ -12482,13 +12482,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E3" t="n">
         <v>0.000694</v>
@@ -12497,25 +12497,25 @@
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M3" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C4" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D4" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E4" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.038889</v>
+        <v>0.013194</v>
       </c>
       <c r="G4" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H4" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.040625</v>
+        <v>0.013542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="M4" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="5">
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="C5" t="n">
         <v>0.001042</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H6" t="n">
         <v>0.000347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="J6" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K6" t="n">
-        <v>0.041319</v>
+        <v>0.013194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="M6" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="7">
@@ -12652,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C7" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="D7" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H7" t="n">
-        <v>0.039583</v>
+        <v>0.013542</v>
       </c>
       <c r="I7" t="n">
-        <v>0.040625</v>
+        <v>0.013542</v>
       </c>
       <c r="J7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M7" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.038194</v>
+        <v>0.010417</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12704,19 +12704,19 @@
         <v>0.003472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.038194</v>
+        <v>0.010417</v>
       </c>
       <c r="F8" t="n">
-        <v>0.038194</v>
+        <v>0.010417</v>
       </c>
       <c r="G8" t="n">
-        <v>0.038194</v>
+        <v>0.010417</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.038194</v>
+        <v>0.010417</v>
       </c>
       <c r="J8" t="n">
         <v>0.003472</v>
@@ -12747,25 +12747,25 @@
         <v>0.000347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F9" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G9" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H9" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="J9" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K9" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L9" t="n">
         <v>0.000347</v>
@@ -12790,10 +12790,10 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.041319</v>
+        <v>0.000694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G10" t="n">
         <v>0.000347</v>
@@ -12802,10 +12802,10 @@
         <v>0.000347</v>
       </c>
       <c r="I10" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="J10" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="K10" t="n">
         <v>0.000347</v>
@@ -12833,10 +12833,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="F11" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -12848,7 +12848,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.041319</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12879,7 +12879,7 @@
         <v>0.000347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12919,10 +12919,10 @@
         <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F13" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G13" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C15" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D15" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E15" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.041319</v>
+        <v>0.000694</v>
       </c>
       <c r="H15" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K15" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="M15" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E16" t="n">
         <v>0.010764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.041319</v>
+        <v>0.011458</v>
       </c>
       <c r="G16" t="n">
-        <v>0.021875</v>
+        <v>0.0125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.035069</v>
+        <v>0.013542</v>
       </c>
       <c r="I16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="J16" t="n">
-        <v>0.023611</v>
+        <v>0.013542</v>
       </c>
       <c r="K16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M16" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="17">
@@ -13080,13 +13080,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E17" t="n">
         <v>0.000694</v>
@@ -13095,25 +13095,25 @@
         <v>0.001042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="J17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M17" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="18">
@@ -13123,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C18" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D18" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E18" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="G18" t="n">
         <v>0.001389</v>
       </c>
       <c r="H18" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="I18" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="J18" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="K18" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L18" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M18" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="19">
@@ -13166,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C19" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D19" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E19" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G19" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H19" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="I19" t="n">
         <v>0.000347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="K19" t="n">
         <v>0.000347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="M19" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="20">
@@ -13236,10 +13236,10 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L20" t="n">
-        <v>0.026736</v>
+        <v>0.000347</v>
       </c>
       <c r="M20" t="n">
         <v>0.000347</v>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G21" t="n">
         <v>0.005903</v>
       </c>
       <c r="H21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I21" t="n">
-        <v>0.040972</v>
+        <v>0.013542</v>
       </c>
       <c r="J21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L21" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I22" t="n">
-        <v>0.021181</v>
+        <v>0.013542</v>
       </c>
       <c r="J22" t="n">
-        <v>0.022222</v>
+        <v>0.013542</v>
       </c>
       <c r="K22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M22" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="23">
@@ -13338,40 +13338,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.028819</v>
+        <v>0.0125</v>
       </c>
       <c r="C23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E23" t="n">
         <v>0.000694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H23" t="n">
-        <v>0.033681</v>
+        <v>0.013542</v>
       </c>
       <c r="I23" t="n">
-        <v>0.022222</v>
+        <v>0.013542</v>
       </c>
       <c r="J23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K23" t="n">
-        <v>0.031944</v>
+        <v>0.013542</v>
       </c>
       <c r="L23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M23" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="24">
@@ -13381,16 +13381,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C24" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="D24" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E24" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F24" t="n">
         <v>0.000347</v>
@@ -13399,22 +13399,22 @@
         <v>0.000694</v>
       </c>
       <c r="H24" t="n">
-        <v>0.024306</v>
+        <v>0.013542</v>
       </c>
       <c r="I24" t="n">
-        <v>0.017361</v>
+        <v>0.013542</v>
       </c>
       <c r="J24" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K24" t="n">
-        <v>0.030556</v>
+        <v>0.013542</v>
       </c>
       <c r="L24" t="n">
-        <v>0.025347</v>
+        <v>0.013542</v>
       </c>
       <c r="M24" t="n">
-        <v>0.036111</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="25">
@@ -13430,7 +13430,7 @@
         <v>0.001042</v>
       </c>
       <c r="D25" t="n">
-        <v>0.041319</v>
+        <v>0.001042</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
@@ -13439,25 +13439,25 @@
         <v>0.000694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H25" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I25" t="n">
-        <v>0.041319</v>
+        <v>0.011111</v>
       </c>
       <c r="J25" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K25" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L25" t="n">
-        <v>0.041319</v>
+        <v>0.001042</v>
       </c>
       <c r="M25" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="26">
@@ -13482,7 +13482,7 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H26" t="n">
         <v>0.000347</v>
@@ -13497,7 +13497,7 @@
         <v>0.000347</v>
       </c>
       <c r="L26" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C27" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="D27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="E27" t="n">
-        <v>0.041319</v>
+        <v>0.001389</v>
       </c>
       <c r="F27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="G27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="I27" t="n">
-        <v>0.015278</v>
+        <v>0.013542</v>
       </c>
       <c r="J27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="L27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="M27" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,13 +13568,13 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
       </c>
       <c r="I28" t="n">
-        <v>0.040625</v>
+        <v>0.013542</v>
       </c>
       <c r="J28" t="n">
         <v>0.000347</v>
@@ -13596,37 +13596,37 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="C29" t="n">
-        <v>0.041319</v>
+        <v>0.001042</v>
       </c>
       <c r="D29" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="E29" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="F29" t="n">
-        <v>0.041319</v>
+        <v>0.001042</v>
       </c>
       <c r="G29" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="H29" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="I29" t="n">
-        <v>0.041319</v>
+        <v>0.010069</v>
       </c>
       <c r="J29" t="n">
-        <v>0.041319</v>
+        <v>0.013542</v>
       </c>
       <c r="K29" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="L29" t="n">
-        <v>0.041319</v>
+        <v>0.000347</v>
       </c>
       <c r="M29" t="n">
         <v>0.000347</v>

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002</v>
+        <v>0.109</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001</v>
+        <v>0.096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007</v>
+        <v>0.254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>0.608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.013</v>
+        <v>0.124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.024</v>
+        <v>0.253</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002</v>
+        <v>0.039</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001</v>
+        <v>0.036</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004</v>
+        <v>0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>0.055</v>
+        <v>0.511</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007</v>
+        <v>0.062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="4">
@@ -1917,34 +1917,34 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="K4" t="n">
         <v>0.002</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.044</v>
+        <v>0.41</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01</v>
+        <v>0.096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007</v>
+        <v>0.065</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="E6" t="n">
-        <v>0.034</v>
+        <v>0.336</v>
       </c>
       <c r="F6" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.008</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002</v>
+        <v>0.029</v>
       </c>
       <c r="F7" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>0.646</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03</v>
+        <v>0.369</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001</v>
+        <v>0.416</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>0.457</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.284</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004</v>
+        <v>0.059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.014</v>
+        <v>0.203</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006</v>
+        <v>0.063</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2141,25 +2141,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.001</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.263</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003</v>
+        <v>0.177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>0.246</v>
       </c>
       <c r="E15" t="n">
-        <v>0.051</v>
+        <v>0.536</v>
       </c>
       <c r="F15" t="n">
-        <v>0.011</v>
+        <v>0.103</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06</v>
+        <v>0.594</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001</v>
+        <v>0.185</v>
       </c>
       <c r="K15" t="n">
-        <v>0.003</v>
+        <v>0.356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007</v>
+        <v>0.502</v>
       </c>
       <c r="M15" t="n">
-        <v>0.001</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.004</v>
+        <v>0.167</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002</v>
+        <v>0.136</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>0.262</v>
       </c>
       <c r="E16" t="n">
-        <v>0.055</v>
+        <v>0.502</v>
       </c>
       <c r="F16" t="n">
-        <v>0.015</v>
+        <v>0.148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.643</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002</v>
+        <v>0.373</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001</v>
+        <v>0.37</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.401</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.003</v>
+        <v>0.077</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003</v>
+        <v>0.064</v>
       </c>
       <c r="D17" t="n">
-        <v>0.015</v>
+        <v>0.218</v>
       </c>
       <c r="E17" t="n">
-        <v>0.066</v>
+        <v>0.623</v>
       </c>
       <c r="F17" t="n">
-        <v>0.012</v>
+        <v>0.113</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04</v>
+        <v>0.379</v>
       </c>
       <c r="H17" t="n">
-        <v>0.002</v>
+        <v>0.265</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001</v>
+        <v>0.475</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003</v>
+        <v>0.341</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.001</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.056</v>
+        <v>0.53</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006</v>
+        <v>0.053</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.007</v>
+        <v>0.058</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007</v>
+        <v>0.061</v>
       </c>
       <c r="D20" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E20" t="n">
-        <v>0.019</v>
+        <v>0.176</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004</v>
+        <v>0.034</v>
       </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.05</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D21" t="n">
         <v>0.004</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
       <c r="E21" t="n">
-        <v>0.016</v>
+        <v>0.155</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003</v>
+        <v>0.026</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003</v>
+        <v>0.026</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004</v>
+        <v>0.171</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004</v>
+        <v>0.194</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E22" t="n">
-        <v>0.016</v>
+        <v>0.167</v>
       </c>
       <c r="F22" t="n">
-        <v>0.002</v>
+        <v>0.025</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002</v>
+        <v>0.025</v>
       </c>
       <c r="H22" t="n">
-        <v>0.016</v>
+        <v>0.394</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002</v>
+        <v>0.137</v>
       </c>
       <c r="J22" t="n">
-        <v>0.006</v>
+        <v>0.609</v>
       </c>
       <c r="K22" t="n">
-        <v>0.002</v>
+        <v>0.183</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002</v>
+        <v>0.352</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.016</v>
+        <v>0.064</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005</v>
+        <v>0.056</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.011</v>
+        <v>0.127</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002</v>
+        <v>0.059</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001</v>
+        <v>0.231</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002</v>
+        <v>0.097</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001</v>
+        <v>0.04</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="E24" t="n">
-        <v>0.007</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.001</v>
+        <v>0.012</v>
       </c>
       <c r="G24" t="n">
-        <v>0.017</v>
+        <v>0.164</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001</v>
+        <v>0.033</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002</v>
+        <v>0.054</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001</v>
+        <v>0.191</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003</v>
+        <v>0.083</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.002</v>
+        <v>0.018</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001</v>
+        <v>0.022</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="E25" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.008</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006</v>
+        <v>0.055</v>
       </c>
       <c r="F26" t="n">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01</v>
+        <v>0.097</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006</v>
+        <v>0.057</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001</v>
+        <v>0.015</v>
       </c>
       <c r="G27" t="n">
-        <v>0.007</v>
+        <v>0.098</v>
       </c>
       <c r="H27" t="n">
-        <v>0.002</v>
+        <v>0.097</v>
       </c>
       <c r="I27" t="n">
-        <v>0.001</v>
+        <v>0.022</v>
       </c>
       <c r="J27" t="n">
-        <v>0.006</v>
+        <v>0.317</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="L27" t="n">
-        <v>0.003</v>
+        <v>0.159</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="28">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.006</v>
+        <v>0.053</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="G28" t="n">
-        <v>0.002</v>
+        <v>0.031</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.005</v>
+        <v>0.052</v>
       </c>
       <c r="F29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M29" t="n">
         <v>0.001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3333333333333333</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.236</v>
+        <v>139.289</v>
       </c>
       <c r="C2" t="n">
-        <v>40.848</v>
+        <v>144.547</v>
       </c>
       <c r="D2" t="n">
-        <v>89.02500000000001</v>
+        <v>199.349</v>
       </c>
       <c r="E2" t="n">
-        <v>228.123</v>
+        <v>250.146</v>
       </c>
       <c r="F2" t="n">
-        <v>105.855</v>
+        <v>109.167</v>
       </c>
       <c r="G2" t="n">
-        <v>144.529</v>
+        <v>164.082</v>
       </c>
       <c r="H2" t="n">
-        <v>13.225</v>
+        <v>170.619</v>
       </c>
       <c r="I2" t="n">
-        <v>21.667</v>
+        <v>196.4</v>
       </c>
       <c r="J2" t="n">
-        <v>9.281000000000001</v>
+        <v>248.485</v>
       </c>
       <c r="K2" t="n">
-        <v>9.362</v>
+        <v>186.89</v>
       </c>
       <c r="L2" t="n">
-        <v>6.178</v>
+        <v>174.557</v>
       </c>
       <c r="M2" t="n">
-        <v>11.703</v>
+        <v>230.517</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.707</v>
+        <v>74.538</v>
       </c>
       <c r="C3" t="n">
-        <v>37.339</v>
+        <v>76.78400000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>62.271</v>
+        <v>108.727</v>
       </c>
       <c r="E3" t="n">
-        <v>217.978</v>
+        <v>220.451</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>76.80500000000001</v>
+        <v>86.02</v>
       </c>
       <c r="H3" t="n">
-        <v>1.063</v>
+        <v>136.496</v>
       </c>
       <c r="I3" t="n">
-        <v>6.124</v>
+        <v>135.516</v>
       </c>
       <c r="J3" t="n">
-        <v>3.734</v>
+        <v>108.492</v>
       </c>
       <c r="K3" t="n">
-        <v>2.422</v>
+        <v>138.241</v>
       </c>
       <c r="L3" t="n">
-        <v>2.201</v>
+        <v>127.499</v>
       </c>
       <c r="M3" t="n">
-        <v>1.608</v>
+        <v>78.70699999999999</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.253</v>
+        <v>38.016</v>
       </c>
       <c r="C4" t="n">
-        <v>19.919</v>
+        <v>27.104</v>
       </c>
       <c r="D4" t="n">
-        <v>42.394</v>
+        <v>49.399</v>
       </c>
       <c r="E4" t="n">
-        <v>196.74</v>
+        <v>200.76</v>
       </c>
       <c r="F4" t="n">
-        <v>73.182</v>
+        <v>74.05</v>
       </c>
       <c r="G4" t="n">
-        <v>59.056</v>
+        <v>65.21299999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9.351000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.159</v>
+        <v>5.348</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>15.704</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>28.691</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>8.858000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.201</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.623</v>
+        <v>19.895</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454</v>
+        <v>6.652</v>
       </c>
       <c r="D5" t="n">
         <v>18.59</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.875</v>
+        <v>63.335</v>
       </c>
       <c r="C6" t="n">
-        <v>1.743</v>
+        <v>33.024</v>
       </c>
       <c r="D6" t="n">
-        <v>10.034</v>
+        <v>51.429</v>
       </c>
       <c r="E6" t="n">
-        <v>172.737</v>
+        <v>181.879</v>
       </c>
       <c r="F6" t="n">
-        <v>85.747</v>
+        <v>89.614</v>
       </c>
       <c r="G6" t="n">
-        <v>45.115</v>
+        <v>57.795</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4.262</v>
       </c>
       <c r="I6" t="n">
-        <v>1.415</v>
+        <v>22.08</v>
       </c>
       <c r="J6" t="n">
-        <v>0.293</v>
+        <v>72.655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.412</v>
+        <v>100.951</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>53.361</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>64.032</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.537</v>
+        <v>110.645</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>116.566</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>83.959</v>
       </c>
       <c r="E7" t="n">
-        <v>77.108</v>
+        <v>107.365</v>
       </c>
       <c r="F7" t="n">
-        <v>153.113</v>
+        <v>171.397</v>
       </c>
       <c r="G7" t="n">
-        <v>35.306</v>
+        <v>68.69799999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>402.337</v>
+        <v>448.705</v>
       </c>
       <c r="I7" t="n">
-        <v>321.932</v>
+        <v>328.085</v>
       </c>
       <c r="J7" t="n">
-        <v>78.265</v>
+        <v>406.981</v>
       </c>
       <c r="K7" t="n">
-        <v>339.646</v>
+        <v>369.421</v>
       </c>
       <c r="L7" t="n">
-        <v>42.462</v>
+        <v>345.876</v>
       </c>
       <c r="M7" t="n">
-        <v>49.153</v>
+        <v>409.27</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.500999999999999</v>
+        <v>8.999000000000001</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7408,19 +7408,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>74.858</v>
+        <v>75.474</v>
       </c>
       <c r="F8" t="n">
-        <v>137.875</v>
+        <v>141.702</v>
       </c>
       <c r="G8" t="n">
-        <v>24.265</v>
+        <v>26.707</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.766</v>
+        <v>2.15</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7442,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>20.174</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.285</v>
       </c>
       <c r="E9" t="n">
-        <v>36.359</v>
+        <v>49.127</v>
       </c>
       <c r="F9" t="n">
-        <v>86.658</v>
+        <v>98.14100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3.442</v>
+        <v>12.37</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="I9" t="n">
-        <v>3.667</v>
+        <v>29.345</v>
       </c>
       <c r="J9" t="n">
-        <v>2.028</v>
+        <v>19.625</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>133.562</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>21.648</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.757</v>
       </c>
     </row>
     <row r="10">
@@ -7494,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.368</v>
+        <v>38.165</v>
       </c>
       <c r="F10" t="n">
-        <v>69.78100000000001</v>
+        <v>74.45</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>11.198</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>7.096</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5.148</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34.141</v>
+        <v>36.519</v>
       </c>
       <c r="F11" t="n">
-        <v>61.606</v>
+        <v>63.697</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.891</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.736</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7580,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.546</v>
+        <v>22.796</v>
       </c>
       <c r="F12" t="n">
-        <v>47.548</v>
+        <v>48.502</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.699</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>26.62</v>
+        <v>34.177</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7635,16 +7635,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.807</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>13.525</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>16.795</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.407</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.527</v>
+        <v>198.422</v>
       </c>
       <c r="C15" t="n">
-        <v>58.888</v>
+        <v>182.077</v>
       </c>
       <c r="D15" t="n">
-        <v>85.241</v>
+        <v>205.629</v>
       </c>
       <c r="E15" t="n">
-        <v>212.542</v>
+        <v>234.016</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>229.985</v>
+        <v>242.281</v>
       </c>
       <c r="H15" t="n">
-        <v>19.119</v>
+        <v>150.226</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>51.292</v>
+        <v>168.641</v>
       </c>
       <c r="K15" t="n">
-        <v>81.736</v>
+        <v>210.788</v>
       </c>
       <c r="L15" t="n">
-        <v>138.554</v>
+        <v>240.008</v>
       </c>
       <c r="M15" t="n">
-        <v>48.635</v>
+        <v>246.087</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116.888</v>
+        <v>283.941</v>
       </c>
       <c r="C16" t="n">
-        <v>86.634</v>
+        <v>285.944</v>
       </c>
       <c r="D16" t="n">
-        <v>175.484</v>
+        <v>337.826</v>
       </c>
       <c r="E16" t="n">
-        <v>377.251</v>
+        <v>380.599</v>
       </c>
       <c r="F16" t="n">
-        <v>200.497</v>
+        <v>206.405</v>
       </c>
       <c r="G16" t="n">
-        <v>436.177</v>
+        <v>437.584</v>
       </c>
       <c r="H16" t="n">
-        <v>186.378</v>
+        <v>361.504</v>
       </c>
       <c r="I16" t="n">
-        <v>67.57899999999999</v>
+        <v>171.377</v>
       </c>
       <c r="J16" t="n">
-        <v>281.353</v>
+        <v>429.552</v>
       </c>
       <c r="K16" t="n">
-        <v>93.015</v>
+        <v>376.299</v>
       </c>
       <c r="L16" t="n">
-        <v>240.571</v>
+        <v>369.467</v>
       </c>
       <c r="M16" t="n">
-        <v>104.704</v>
+        <v>383.219</v>
       </c>
     </row>
     <row r="17">
@@ -7784,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>96.625</v>
+        <v>190.162</v>
       </c>
       <c r="C17" t="n">
-        <v>88.55200000000001</v>
+        <v>176.974</v>
       </c>
       <c r="D17" t="n">
-        <v>201.837</v>
+        <v>287.615</v>
       </c>
       <c r="E17" t="n">
-        <v>416.187</v>
+        <v>418.938</v>
       </c>
       <c r="F17" t="n">
-        <v>177.486</v>
+        <v>178.899</v>
       </c>
       <c r="G17" t="n">
-        <v>322.729</v>
+        <v>328.324</v>
       </c>
       <c r="H17" t="n">
-        <v>169.533</v>
+        <v>334.933</v>
       </c>
       <c r="I17" t="n">
-        <v>42.79</v>
+        <v>122.944</v>
       </c>
       <c r="J17" t="n">
-        <v>129.461</v>
+        <v>426.081</v>
       </c>
       <c r="K17" t="n">
-        <v>72.68000000000001</v>
+        <v>280.581</v>
       </c>
       <c r="L17" t="n">
-        <v>163.884</v>
+        <v>364.881</v>
       </c>
       <c r="M17" t="n">
-        <v>72.009</v>
+        <v>329.791</v>
       </c>
     </row>
     <row r="18">
@@ -7827,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.557</v>
+        <v>49.284</v>
       </c>
       <c r="C18" t="n">
-        <v>20.167</v>
+        <v>29.031</v>
       </c>
       <c r="D18" t="n">
-        <v>40.053</v>
+        <v>47.026</v>
       </c>
       <c r="E18" t="n">
-        <v>393.462</v>
+        <v>398.401</v>
       </c>
       <c r="F18" t="n">
-        <v>159.617</v>
+        <v>162.221</v>
       </c>
       <c r="G18" t="n">
-        <v>140.235</v>
+        <v>140.396</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>32.366</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>10.028</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>20.694</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>35.773</v>
       </c>
       <c r="L18" t="n">
-        <v>5.197</v>
+        <v>80.483</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>36.838</v>
       </c>
     </row>
     <row r="19">
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.933</v>
+        <v>23.853</v>
       </c>
       <c r="C19" t="n">
-        <v>4.508</v>
+        <v>10.437</v>
       </c>
       <c r="D19" t="n">
-        <v>23.175</v>
+        <v>29.286</v>
       </c>
       <c r="E19" t="n">
-        <v>382.84</v>
+        <v>385.916</v>
       </c>
       <c r="F19" t="n">
-        <v>152.843</v>
+        <v>154.628</v>
       </c>
       <c r="G19" t="n">
-        <v>120.932</v>
+        <v>122.902</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.267</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>7.721</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>10.242</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="20">
@@ -7940,10 +7940,10 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>11.559</v>
+        <v>70.63</v>
       </c>
       <c r="L20" t="n">
-        <v>5.484</v>
+        <v>7.176</v>
       </c>
       <c r="M20" t="n">
         <v>38.08</v>
@@ -7956,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.55800000000001</v>
+        <v>151.843</v>
       </c>
       <c r="C21" t="n">
-        <v>99.063</v>
+        <v>155.286</v>
       </c>
       <c r="D21" t="n">
-        <v>20.397</v>
+        <v>44.554</v>
       </c>
       <c r="E21" t="n">
-        <v>204.705</v>
+        <v>211.495</v>
       </c>
       <c r="F21" t="n">
-        <v>83.80200000000001</v>
+        <v>84.84699999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>86.164</v>
+        <v>86.437</v>
       </c>
       <c r="H21" t="n">
-        <v>14.682</v>
+        <v>315.454</v>
       </c>
       <c r="I21" t="n">
-        <v>4.609</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>9.297000000000001</v>
+        <v>312.499</v>
       </c>
       <c r="K21" t="n">
-        <v>23.807</v>
+        <v>218.524</v>
       </c>
       <c r="L21" t="n">
-        <v>15.954</v>
+        <v>181.643</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>114.327</v>
+        <v>285.401</v>
       </c>
       <c r="C22" t="n">
-        <v>120.887</v>
+        <v>308.21</v>
       </c>
       <c r="D22" t="n">
-        <v>35.922</v>
+        <v>213.229</v>
       </c>
       <c r="E22" t="n">
-        <v>201.41</v>
+        <v>235.775</v>
       </c>
       <c r="F22" t="n">
-        <v>74.88800000000001</v>
+        <v>93.426</v>
       </c>
       <c r="G22" t="n">
-        <v>70.70999999999999</v>
+        <v>102.116</v>
       </c>
       <c r="H22" t="n">
-        <v>333.396</v>
+        <v>351.305</v>
       </c>
       <c r="I22" t="n">
-        <v>168.953</v>
+        <v>218.601</v>
       </c>
       <c r="J22" t="n">
-        <v>304.833</v>
+        <v>447.263</v>
       </c>
       <c r="K22" t="n">
-        <v>159.955</v>
+        <v>245.673</v>
       </c>
       <c r="L22" t="n">
-        <v>150.705</v>
+        <v>351.869</v>
       </c>
       <c r="M22" t="n">
-        <v>18.902</v>
+        <v>345.778</v>
       </c>
     </row>
     <row r="23">
@@ -8042,40 +8042,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55.505</v>
+        <v>68.547</v>
       </c>
       <c r="C23" t="n">
-        <v>7.236</v>
+        <v>30.674</v>
       </c>
       <c r="D23" t="n">
-        <v>6.276</v>
+        <v>31.352</v>
       </c>
       <c r="E23" t="n">
-        <v>22.371</v>
+        <v>24.121</v>
       </c>
       <c r="F23" t="n">
-        <v>8.757999999999999</v>
+        <v>9.519</v>
       </c>
       <c r="G23" t="n">
-        <v>99.06</v>
+        <v>119.489</v>
       </c>
       <c r="H23" t="n">
-        <v>11.334</v>
+        <v>21.522</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>26.488</v>
       </c>
       <c r="J23" t="n">
-        <v>21.449</v>
+        <v>56.446</v>
       </c>
       <c r="K23" t="n">
-        <v>10.535</v>
+        <v>20.712</v>
       </c>
       <c r="L23" t="n">
-        <v>24.243</v>
+        <v>32.653</v>
       </c>
       <c r="M23" t="n">
-        <v>9.904999999999999</v>
+        <v>35.369</v>
       </c>
     </row>
     <row r="24">
@@ -8085,40 +8085,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.885</v>
+        <v>15.531</v>
       </c>
       <c r="C24" t="n">
-        <v>8.907</v>
+        <v>25.396</v>
       </c>
       <c r="D24" t="n">
-        <v>5.29</v>
+        <v>21.851</v>
       </c>
       <c r="E24" t="n">
-        <v>24.782</v>
+        <v>25.831</v>
       </c>
       <c r="F24" t="n">
-        <v>10.442</v>
+        <v>10.472</v>
       </c>
       <c r="G24" t="n">
-        <v>123.314</v>
+        <v>125.227</v>
       </c>
       <c r="H24" t="n">
-        <v>14.395</v>
+        <v>20.425</v>
       </c>
       <c r="I24" t="n">
-        <v>22.1</v>
+        <v>25.756</v>
       </c>
       <c r="J24" t="n">
-        <v>22.573</v>
+        <v>47.703</v>
       </c>
       <c r="K24" t="n">
-        <v>10.676</v>
+        <v>20.024</v>
       </c>
       <c r="L24" t="n">
-        <v>26.582</v>
+        <v>30.576</v>
       </c>
       <c r="M24" t="n">
-        <v>16.085</v>
+        <v>30.786</v>
       </c>
     </row>
     <row r="25">
@@ -8128,40 +8128,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12.981</v>
+        <v>13.563</v>
       </c>
       <c r="C25" t="n">
-        <v>12.953</v>
+        <v>17.647</v>
       </c>
       <c r="D25" t="n">
-        <v>7.988</v>
+        <v>14.358</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>12.001</v>
+        <v>12.027</v>
       </c>
       <c r="G25" t="n">
-        <v>63.877</v>
+        <v>86.818</v>
       </c>
       <c r="H25" t="n">
-        <v>8.564</v>
+        <v>19.045</v>
       </c>
       <c r="I25" t="n">
-        <v>1.314</v>
+        <v>11.804</v>
       </c>
       <c r="J25" t="n">
-        <v>1.225</v>
+        <v>25.778</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>23.603</v>
       </c>
       <c r="L25" t="n">
-        <v>2.614</v>
+        <v>27.658</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="26">
@@ -8174,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.094</v>
+        <v>11.235</v>
       </c>
       <c r="D26" t="n">
-        <v>3.837</v>
+        <v>4.172</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8186,22 +8186,22 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>93.23399999999999</v>
+        <v>96.301</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.428</v>
       </c>
       <c r="I26" t="n">
-        <v>0.706</v>
+        <v>1.551</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.274</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>6.246</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8214,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.819</v>
+        <v>21.634</v>
       </c>
       <c r="C27" t="n">
-        <v>6.667</v>
+        <v>31.771</v>
       </c>
       <c r="D27" t="n">
-        <v>2.961</v>
+        <v>27.277</v>
       </c>
       <c r="E27" t="n">
-        <v>22.295</v>
+        <v>24.271</v>
       </c>
       <c r="F27" t="n">
-        <v>10.996</v>
+        <v>12.223</v>
       </c>
       <c r="G27" t="n">
-        <v>81.908</v>
+        <v>109.659</v>
       </c>
       <c r="H27" t="n">
-        <v>21.933</v>
+        <v>33.252</v>
       </c>
       <c r="I27" t="n">
-        <v>16.855</v>
+        <v>18.642</v>
       </c>
       <c r="J27" t="n">
-        <v>42.51</v>
+        <v>58.309</v>
       </c>
       <c r="K27" t="n">
-        <v>11.903</v>
+        <v>37.326</v>
       </c>
       <c r="L27" t="n">
-        <v>32.756</v>
+        <v>43.613</v>
       </c>
       <c r="M27" t="n">
-        <v>8.339</v>
+        <v>36.754</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.401</v>
+        <v>2.559</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,13 +8272,13 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>43.697</v>
+        <v>61.175</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.399</v>
+        <v>0.536</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -8300,40 +8300,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.693</v>
+        <v>4.367</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9340000000000001</v>
+        <v>5.664</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3.613</v>
       </c>
       <c r="E29" t="n">
-        <v>21.558</v>
+        <v>22.205</v>
       </c>
       <c r="F29" t="n">
-        <v>10.421</v>
+        <v>10.799</v>
       </c>
       <c r="G29" t="n">
-        <v>61.837</v>
+        <v>71.66200000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>5.992</v>
       </c>
       <c r="I29" t="n">
-        <v>0.855</v>
+        <v>7.339</v>
       </c>
       <c r="J29" t="n">
-        <v>0.067</v>
+        <v>16.438</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>11.718</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>21.617</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="30">
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728599696e-06</v>
+        <v>1.9401425521e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.668559104e-06</v>
+        <v>2.0893835209e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.925450625000001e-06</v>
+        <v>3.9740023801e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.204010312899999e-05</v>
+        <v>6.2573021316e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1205281025e-05</v>
+        <v>1.1917433889e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0888631841e-05</v>
+        <v>2.6922902724e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.74900625e-07</v>
+        <v>2.9110843161e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>4.694588890000001e-07</v>
+        <v>3.857296000000001e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.613696100000003e-08</v>
+        <v>6.1744795225e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>8.7647044e-08</v>
+        <v>3.49278721e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.816768400000001e-08</v>
+        <v>3.0470146249e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.36960209e-07</v>
+        <v>5.3138087289e-05</v>
       </c>
     </row>
     <row r="3">
@@ -8510,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.823887849e-06</v>
+        <v>5.555913443999999e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.394200921e-06</v>
+        <v>5.895782656e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.877677441e-06</v>
+        <v>1.1821560529e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7514408484e-05</v>
+        <v>4.8598643401e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.899008025000002e-06</v>
+        <v>7.3994404e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.129969e-09</v>
+        <v>1.8631158016e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.750337599999999e-08</v>
+        <v>1.8364586256e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3942756e-08</v>
+        <v>1.1770514064e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.866084000000001e-09</v>
+        <v>1.9110574081e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>4.844401000000001e-09</v>
+        <v>1.6255995001e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.585664e-09</v>
+        <v>6.194791848999999e-06</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.427260089999999e-07</v>
+        <v>1.445216256e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>3.96766561e-07</v>
+        <v>7.346268159999999e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.797251236e-06</v>
+        <v>2.440261201e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.87066276e-05</v>
+        <v>4.030457759999999e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.355605124e-06</v>
+        <v>5.483402499999999e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.487611136e-06</v>
+        <v>4.252735369e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>8.744120100000002e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.661281e-09</v>
+        <v>2.860110399999999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.46615616e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8.231734809999998e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>7.846416400000002e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.040100000000001e-11</v>
+        <v>1.5876e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.46816129e-07</v>
+        <v>3.95811025e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9746116e-08</v>
+        <v>4.4249104e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.455880999999999e-07</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.52015625e-07</v>
+        <v>4.011322225000001e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>3.038049000000001e-09</v>
+        <v>1.090584576e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.00681156e-07</v>
+        <v>2.644942041e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9838071169e-05</v>
+        <v>3.3079970641e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.352548009000001e-06</v>
+        <v>8.030668996000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.035363225e-06</v>
+        <v>3.340262025e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.816464399999999e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.002225e-09</v>
+        <v>4.875263999999999e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>8.584899999999997e-11</v>
+        <v>5.278749024999999e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.69744e-10</v>
+        <v>1.0191104401e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.847396321e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.100097023999998e-06</v>
       </c>
     </row>
     <row r="7">
@@ -8680,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.436745633333333e-08</v>
+        <v>4.080772008333333e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4.529210785333334e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.349704560333334e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.981881221333334e-06</v>
+        <v>3.842414408333332e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.814530256333334e-06</v>
+        <v>9.792310536333332e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>4.155045453333333e-07</v>
+        <v>1.573138401333333e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>5.395835385633333e-05</v>
+        <v>6.711205900833333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.454673754133334e-05</v>
+        <v>3.587992240833332e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.041803408333333e-06</v>
+        <v>5.521117812033333e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.845313510533333e-05</v>
+        <v>4.549062508033333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.010071480000001e-07</v>
+        <v>3.987673579199999e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>8.053391363333332e-07</v>
+        <v>5.583397763333333e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.2267001e-08</v>
+        <v>8.098200100000001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8732,19 +8732,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.603720164000002e-06</v>
+        <v>5.696324676e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9009515625e-05</v>
+        <v>2.0079456804e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.887902250000001e-07</v>
+        <v>7.132638490000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5.86756e-10</v>
+        <v>4.622500000000001e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.356634253333333e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.608033333333334e-11</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6.120408333333333e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.406589603333334e-07</v>
+        <v>8.044873763333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.503202988e-06</v>
+        <v>3.210551960333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.949121333333334e-09</v>
+        <v>5.100563333333332e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.123413333333333e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.482296333333332e-09</v>
+        <v>2.870430083333333e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.370928e-09</v>
+        <v>1.283802083333333e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5.946269281333335e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56211968e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1047683e-08</v>
       </c>
     </row>
     <row r="10">
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.492291413333334e-07</v>
+        <v>4.855224083333332e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.623129320333334e-06</v>
+        <v>1.847600833333333e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.136333333333333e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>7.301333333333332e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4.179840133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.678440533333333e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8.833968e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.694216333333333e-09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8861,22 +8861,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.885359603333333e-07</v>
+        <v>4.445457869999999e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.265099745333333e-06</v>
+        <v>1.352435936333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.93548e-10</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.785960333333333e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4.652565333333334e-09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.694407053333334e-07</v>
+        <v>1.732192053333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.536041013333334e-07</v>
+        <v>7.841480013333335e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.62867e-10</v>
+        <v>2.507942533333333e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>2.362081333333334e-07</v>
+        <v>3.893557763333333e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8959,16 +8959,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.831083e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>6.097520833333334e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>9.402400833333334e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8287883e-08</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.317461729000001e-06</v>
+        <v>3.9371290084e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>3.467796543999999e-06</v>
+        <v>3.3152033929e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>7.266028080999999e-06</v>
+        <v>4.228328564099999e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5174101764e-05</v>
+        <v>5.4763488256e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.289310022500001e-05</v>
+        <v>5.8700082961e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65536161e-07</v>
+        <v>2.2567851076e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.630869264e-06</v>
+        <v>2.843978688099999e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>6.680773696000001e-06</v>
+        <v>4.4431580944e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9197210916e-05</v>
+        <v>5.7603840064e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.365363225e-06</v>
+        <v>6.0558811569e-05</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.554268181333334e-06</v>
+        <v>2.6874163827e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>2.501816652e-06</v>
+        <v>2.725465704533334e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>1.026487808533333e-05</v>
+        <v>3.804213542533334e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.743943900033334e-05</v>
+        <v>4.828519960033332e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.339968233633333e-05</v>
+        <v>1.420100800833334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.341679177633334e-05</v>
+        <v>6.382658568533334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1578919628e-05</v>
+        <v>4.356171400533333e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>1.522307080333333e-06</v>
+        <v>9.790025376333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>2.638650353633333e-05</v>
+        <v>6.150497356800002e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>2.883930075e-06</v>
+        <v>4.7200312467e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>1.929146868033334e-05</v>
+        <v>4.550195469633334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.654309205333333e-06</v>
+        <v>4.895226732033333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -9108,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.112130208333333e-06</v>
+        <v>1.205386208133333e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>2.613818901333333e-06</v>
+        <v>1.043993222533333e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3579391523e-05</v>
+        <v>2.757412940833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.773720632300001e-05</v>
+        <v>5.850301594799999e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0500426732e-05</v>
+        <v>1.0668284067e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.471800248033333e-05</v>
+        <v>3.593221632533333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>9.580479362999998e-06</v>
+        <v>3.739337149633333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>6.103280333333334e-07</v>
+        <v>5.038409045333333e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.586716840333335e-06</v>
+        <v>6.051500618700001e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>1.760794133333334e-06</v>
+        <v>2.6241899187e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>8.952655151999998e-06</v>
+        <v>4.437938138699999e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>1.728432027e-06</v>
+        <v>3.625403456033334e-05</v>
       </c>
     </row>
     <row r="18">
@@ -9151,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.48290083e-07</v>
+        <v>8.09637552e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.355692963333334e-07</v>
+        <v>2.80932987e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>5.347476029999999e-07</v>
+        <v>7.371482253333335e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.1604115148e-05</v>
+        <v>5.290778560033334e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.492528896333331e-06</v>
+        <v>8.771884280333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.555285075000002e-06</v>
+        <v>6.570345605333333e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3.491859853333333e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3.352026133333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.42747212e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.265691763333335e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>9.002936333333335e-09</v>
+        <v>2.159171096333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.523460813333334e-07</v>
       </c>
     </row>
     <row r="19">
@@ -9194,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.071974963333333e-07</v>
+        <v>1.89655203e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>3.6310323e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.79026875e-07</v>
+        <v>2.85889932e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.885548853333333e-05</v>
+        <v>4.964371968533333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.786994216333332e-06</v>
+        <v>7.969939461333333e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.874849541333333e-06</v>
+        <v>5.034967201333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4.712533333333333e-09</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.557763e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4.224533333333334e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.987128033333334e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.4966188e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.689813333333334e-08</v>
       </c>
     </row>
     <row r="20">
@@ -9264,10 +9264,10 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4536827e-08</v>
+        <v>1.662865633333333e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0024752e-08</v>
+        <v>1.7164992e-08</v>
       </c>
       <c r="M20" t="n">
         <v>4.833621333333333e-07</v>
@@ -9280,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.107815788e-06</v>
+        <v>7.685432216333331e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>3.271159323e-06</v>
+        <v>8.037913932000002e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38679203e-07</v>
+        <v>6.616863053333334e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3968045675e-05</v>
+        <v>1.491004500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.340925068e-06</v>
+        <v>2.399671136333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.474744965333333e-06</v>
+        <v>2.490451656333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>7.1853708e-08</v>
+        <v>3.317040870533334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>7.080960333333333e-09</v>
+        <v>1.536803333333333e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>2.881140300000001e-08</v>
+        <v>3.255187500033334e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>1.889244163333333e-07</v>
+        <v>1.591757952533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>8.484337199999999e-08</v>
+        <v>1.099805981633333e-05</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.356887643e-06</v>
+        <v>2.715124360033333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>4.871222256333332e-06</v>
+        <v>3.166446803333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>4.301300279999999e-07</v>
+        <v>1.515553548033333e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.352199603333333e-05</v>
+        <v>1.852995020833333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.869404181333334e-06</v>
+        <v>2.909472492e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6666347e-06</v>
+        <v>3.475892485333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.705096427200001e-05</v>
+        <v>4.113840100833334e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>9.515038736333332e-06</v>
+        <v>1.5928799067e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.097438596300001e-05</v>
+        <v>6.668139705633332e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>8.528534008333335e-06</v>
+        <v>2.0118407643e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>7.570665675000001e-06</v>
+        <v>4.127059772033335e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>1.190952013333334e-07</v>
+        <v>3.985414176133334e-05</v>
       </c>
     </row>
     <row r="23">
@@ -9366,40 +9366,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.080805025e-05</v>
+        <v>4.698691208999999e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>5.235969599999999e-07</v>
+        <v>9.408942760000001e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>3.938817599999999e-07</v>
+        <v>9.82947904e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>5.00461641e-06</v>
+        <v>5.81822641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>7.670256399999996e-07</v>
+        <v>9.0611361e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.812883600000002e-06</v>
+        <v>1.4277621121e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.28459556e-06</v>
+        <v>4.63196484e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.41e-06</v>
+        <v>7.016141440000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>4.600596010000001e-06</v>
+        <v>3.186150915999999e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>1.10986225e-06</v>
+        <v>4.28986944e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>5.877230489999999e-06</v>
+        <v>1.066218409e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>9.810902499999998e-07</v>
+        <v>1.250966161e-05</v>
       </c>
     </row>
     <row r="24">
@@ -9409,40 +9409,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.7403225e-07</v>
+        <v>2.41211961e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>7.933464900000001e-07</v>
+        <v>6.449568160000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>4.774662009999999e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.14147524e-06</v>
+        <v>6.67240561e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09035364e-06</v>
+        <v>1.09662784e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5206342596e-05</v>
+        <v>1.5681801529e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.07216025e-06</v>
+        <v>4.171806250000001e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>4.884100000000001e-06</v>
+        <v>6.633715360000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>5.095403289999999e-06</v>
+        <v>2.275576209e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>1.13976976e-06</v>
+        <v>4.00960576e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>7.066027240000001e-06</v>
+        <v>9.34891776e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>2.587272250000001e-06</v>
+        <v>9.477777960000001e-06</v>
       </c>
     </row>
     <row r="25">
@@ -9452,40 +9452,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.68506361e-06</v>
+        <v>1.83954969e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.67780209e-06</v>
+        <v>3.11416609e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>6.3808144e-07</v>
+        <v>2.06152164e-06</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44024001e-06</v>
+        <v>1.44648729e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>4.080271129e-06</v>
+        <v>7.537365123999998e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>7.334209600000002e-07</v>
+        <v>3.627120250000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.726596e-08</v>
+        <v>1.39334416e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>1.500625e-08</v>
+        <v>6.645052839999999e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>5.571016090000001e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>6.832996e-08</v>
+        <v>7.64964964e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.58572096e-06</v>
       </c>
     </row>
     <row r="26">
@@ -9498,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.23076836e-06</v>
+        <v>1.26225225e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4722569e-07</v>
+        <v>1.7405584e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9510,22 +9510,22 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.692578755999999e-06</v>
+        <v>9.273882601e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.039184e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>4.984359999999999e-09</v>
+        <v>2.405601e-08</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>9.35089e-09</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.623076e-08</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.901251600000001e-07</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9538,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.386076099999999e-07</v>
+        <v>4.680299560000001e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>4.4448889e-07</v>
+        <v>1.009396441e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>8.767520999999998e-08</v>
+        <v>7.440347290000001e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>4.970670250000002e-06</v>
+        <v>5.890814410000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.20912016e-06</v>
+        <v>1.49401729e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>6.708920463999999e-06</v>
+        <v>1.2025096281e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>4.81056489e-06</v>
+        <v>1.105695504e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>2.84091025e-06</v>
+        <v>3.47524164e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8071001e-05</v>
+        <v>3.399939481e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.41681409e-06</v>
+        <v>1.393230276e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.072955536e-05</v>
+        <v>1.902093769e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>6.953892100000002e-07</v>
+        <v>1.350856516e-05</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.764801e-08</v>
+        <v>6.548481000000001e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,13 +9596,13 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.909427809e-06</v>
+        <v>3.742380625e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.59201e-09</v>
+        <v>2.87296e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -9624,40 +9624,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.866249e-08</v>
+        <v>1.9070689e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>8.723560000000001e-09</v>
+        <v>3.2080896e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1.3053769e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.64747364e-06</v>
+        <v>4.930620249999999e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08597241e-06</v>
+        <v>1.16618401e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>3.823814569e-06</v>
+        <v>5.135442244e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3.5904064e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>7.310249999999999e-09</v>
+        <v>5.3860921e-07</v>
       </c>
       <c r="J29" t="n">
-        <v>4.489000000000001e-11</v>
+        <v>2.70207844e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1.37311524e-06</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.67294689e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.946318399999999e-07</v>
       </c>
     </row>
     <row r="30">
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.236</v>
+        <v>139.289</v>
       </c>
       <c r="C2" t="n">
-        <v>40.848</v>
+        <v>144.547</v>
       </c>
       <c r="D2" t="n">
-        <v>89.02500000000001</v>
+        <v>199.349</v>
       </c>
       <c r="E2" t="n">
-        <v>228.123</v>
+        <v>250.146</v>
       </c>
       <c r="F2" t="n">
-        <v>105.855</v>
+        <v>109.167</v>
       </c>
       <c r="G2" t="n">
-        <v>144.529</v>
+        <v>164.082</v>
       </c>
       <c r="H2" t="n">
-        <v>13.225</v>
+        <v>170.619</v>
       </c>
       <c r="I2" t="n">
-        <v>21.667</v>
+        <v>196.4</v>
       </c>
       <c r="J2" t="n">
-        <v>9.281000000000001</v>
+        <v>248.469</v>
       </c>
       <c r="K2" t="n">
-        <v>9.362</v>
+        <v>186.89</v>
       </c>
       <c r="L2" t="n">
-        <v>6.178</v>
+        <v>174.557</v>
       </c>
       <c r="M2" t="n">
-        <v>11.703</v>
+        <v>230.517</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.707</v>
+        <v>74.538</v>
       </c>
       <c r="C3" t="n">
-        <v>37.339</v>
+        <v>76.78400000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>62.271</v>
+        <v>108.727</v>
       </c>
       <c r="E3" t="n">
-        <v>216.724</v>
+        <v>220.451</v>
       </c>
       <c r="F3" t="n">
-        <v>76.273</v>
+        <v>76.491</v>
       </c>
       <c r="G3" t="n">
-        <v>76.80500000000001</v>
+        <v>86.02</v>
       </c>
       <c r="H3" t="n">
-        <v>1.063</v>
+        <v>136.496</v>
       </c>
       <c r="I3" t="n">
-        <v>6.124</v>
+        <v>135.516</v>
       </c>
       <c r="J3" t="n">
-        <v>3.734</v>
+        <v>108.463</v>
       </c>
       <c r="K3" t="n">
-        <v>2.422</v>
+        <v>138.241</v>
       </c>
       <c r="L3" t="n">
-        <v>2.201</v>
+        <v>127.499</v>
       </c>
       <c r="M3" t="n">
-        <v>1.608</v>
+        <v>78.70699999999999</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.253</v>
+        <v>38.016</v>
       </c>
       <c r="C4" t="n">
-        <v>19.919</v>
+        <v>27.104</v>
       </c>
       <c r="D4" t="n">
-        <v>42.394</v>
+        <v>49.399</v>
       </c>
       <c r="E4" t="n">
-        <v>196.74</v>
+        <v>200.76</v>
       </c>
       <c r="F4" t="n">
-        <v>73.179</v>
+        <v>74.05</v>
       </c>
       <c r="G4" t="n">
-        <v>59.056</v>
+        <v>65.21299999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9.351000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.159</v>
+        <v>3.563</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>15.704</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>28.691</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>8.858000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.201</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.424</v>
+        <v>19.895</v>
       </c>
       <c r="C5" t="n">
-        <v>4.869</v>
+        <v>6.652</v>
       </c>
       <c r="D5" t="n">
-        <v>18.03</v>
+        <v>18.554</v>
       </c>
       <c r="E5" t="n">
-        <v>196.141</v>
+        <v>195.073</v>
       </c>
       <c r="F5" t="n">
-        <v>94.65900000000001</v>
+        <v>93.86199999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>78.86199999999999</v>
+        <v>76.872</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.875</v>
+        <v>63.335</v>
       </c>
       <c r="C6" t="n">
-        <v>1.743</v>
+        <v>33.024</v>
       </c>
       <c r="D6" t="n">
-        <v>10.034</v>
+        <v>51.429</v>
       </c>
       <c r="E6" t="n">
-        <v>172.737</v>
+        <v>181.879</v>
       </c>
       <c r="F6" t="n">
-        <v>85.747</v>
+        <v>89.614</v>
       </c>
       <c r="G6" t="n">
-        <v>45.115</v>
+        <v>57.795</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4.262</v>
       </c>
       <c r="I6" t="n">
-        <v>1.415</v>
+        <v>22.08</v>
       </c>
       <c r="J6" t="n">
-        <v>0.293</v>
+        <v>72.655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.347</v>
+        <v>100.951</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>53.361</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>64.032</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.537</v>
+        <v>110.645</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>116.566</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>83.959</v>
       </c>
       <c r="E7" t="n">
-        <v>77.108</v>
+        <v>107.365</v>
       </c>
       <c r="F7" t="n">
-        <v>153.113</v>
+        <v>171.397</v>
       </c>
       <c r="G7" t="n">
-        <v>35.306</v>
+        <v>68.69799999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>402.337</v>
+        <v>444.155</v>
       </c>
       <c r="I7" t="n">
-        <v>321.932</v>
+        <v>322.767</v>
       </c>
       <c r="J7" t="n">
-        <v>78.265</v>
+        <v>374.397</v>
       </c>
       <c r="K7" t="n">
-        <v>339.646</v>
+        <v>365.191</v>
       </c>
       <c r="L7" t="n">
-        <v>42.462</v>
+        <v>341.074</v>
       </c>
       <c r="M7" t="n">
-        <v>49.153</v>
+        <v>408.096</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.500999999999999</v>
+        <v>8.999000000000001</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>74.858</v>
+        <v>75.462</v>
       </c>
       <c r="F8" t="n">
-        <v>137.875</v>
+        <v>141.702</v>
       </c>
       <c r="G8" t="n">
-        <v>24.265</v>
+        <v>26.707</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.766</v>
+        <v>1.796</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>84.98</v>
+        <v>62.415</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10090,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>20.174</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.285</v>
       </c>
       <c r="E9" t="n">
-        <v>36.359</v>
+        <v>49.127</v>
       </c>
       <c r="F9" t="n">
-        <v>86.658</v>
+        <v>98.14100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>3.442</v>
+        <v>12.37</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="I9" t="n">
-        <v>3.667</v>
+        <v>29.345</v>
       </c>
       <c r="J9" t="n">
-        <v>2.028</v>
+        <v>19.625</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>133.562</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>21.648</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.757</v>
       </c>
     </row>
     <row r="10">
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.017</v>
+        <v>38.165</v>
       </c>
       <c r="F10" t="n">
-        <v>69.78100000000001</v>
+        <v>74.45</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.476</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>10.515</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>7.096</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5.148</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -10185,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>33.871</v>
+        <v>36.519</v>
       </c>
       <c r="F11" t="n">
-        <v>61.606</v>
+        <v>63.697</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.891</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.736</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.256</v>
+        <v>22.796</v>
       </c>
       <c r="F12" t="n">
-        <v>47.548</v>
+        <v>48.502</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10271,10 +10271,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.699</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>26.62</v>
+        <v>34.177</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.807</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>13.525</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>16.795</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.407</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.527</v>
+        <v>198.422</v>
       </c>
       <c r="C15" t="n">
-        <v>58.888</v>
+        <v>182.077</v>
       </c>
       <c r="D15" t="n">
-        <v>85.241</v>
+        <v>205.629</v>
       </c>
       <c r="E15" t="n">
-        <v>212.542</v>
+        <v>234.016</v>
       </c>
       <c r="F15" t="n">
-        <v>96.351</v>
+        <v>98.13800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>227.132</v>
+        <v>242.281</v>
       </c>
       <c r="H15" t="n">
-        <v>17.825</v>
+        <v>144.372</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>51.292</v>
+        <v>168.641</v>
       </c>
       <c r="K15" t="n">
-        <v>68.693</v>
+        <v>210.788</v>
       </c>
       <c r="L15" t="n">
-        <v>119.495</v>
+        <v>240.008</v>
       </c>
       <c r="M15" t="n">
-        <v>48.635</v>
+        <v>246.087</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116.888</v>
+        <v>283.941</v>
       </c>
       <c r="C16" t="n">
-        <v>86.634</v>
+        <v>285.944</v>
       </c>
       <c r="D16" t="n">
-        <v>175.484</v>
+        <v>337.826</v>
       </c>
       <c r="E16" t="n">
-        <v>375.145</v>
+        <v>380.599</v>
       </c>
       <c r="F16" t="n">
-        <v>199.537</v>
+        <v>206.405</v>
       </c>
       <c r="G16" t="n">
-        <v>435.904</v>
+        <v>424.195</v>
       </c>
       <c r="H16" t="n">
-        <v>186.378</v>
+        <v>356.476</v>
       </c>
       <c r="I16" t="n">
-        <v>67.57899999999999</v>
+        <v>160.309</v>
       </c>
       <c r="J16" t="n">
-        <v>281.353</v>
+        <v>422.299</v>
       </c>
       <c r="K16" t="n">
-        <v>93.015</v>
+        <v>376.299</v>
       </c>
       <c r="L16" t="n">
-        <v>240.571</v>
+        <v>369.467</v>
       </c>
       <c r="M16" t="n">
-        <v>104.704</v>
+        <v>383.219</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>96.625</v>
+        <v>190.162</v>
       </c>
       <c r="C17" t="n">
-        <v>88.55200000000001</v>
+        <v>176.974</v>
       </c>
       <c r="D17" t="n">
-        <v>201.837</v>
+        <v>287.615</v>
       </c>
       <c r="E17" t="n">
-        <v>415.356</v>
+        <v>418.938</v>
       </c>
       <c r="F17" t="n">
-        <v>176.602</v>
+        <v>178.14</v>
       </c>
       <c r="G17" t="n">
-        <v>322.729</v>
+        <v>328.324</v>
       </c>
       <c r="H17" t="n">
-        <v>169.533</v>
+        <v>334.933</v>
       </c>
       <c r="I17" t="n">
-        <v>42.79</v>
+        <v>122.944</v>
       </c>
       <c r="J17" t="n">
-        <v>129.461</v>
+        <v>421.894</v>
       </c>
       <c r="K17" t="n">
-        <v>72.68000000000001</v>
+        <v>280.581</v>
       </c>
       <c r="L17" t="n">
-        <v>163.884</v>
+        <v>364.881</v>
       </c>
       <c r="M17" t="n">
-        <v>72.009</v>
+        <v>329.791</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.557</v>
+        <v>49.284</v>
       </c>
       <c r="C18" t="n">
-        <v>20.167</v>
+        <v>29.031</v>
       </c>
       <c r="D18" t="n">
-        <v>40.053</v>
+        <v>47.026</v>
       </c>
       <c r="E18" t="n">
-        <v>393.462</v>
+        <v>398.401</v>
       </c>
       <c r="F18" t="n">
-        <v>159.419</v>
+        <v>162.221</v>
       </c>
       <c r="G18" t="n">
-        <v>140.198</v>
+        <v>140.396</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>29.584</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>8.759</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>18.803</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>32.529</v>
       </c>
       <c r="L18" t="n">
-        <v>5.197</v>
+        <v>52.306</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>27.016</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.933</v>
+        <v>23.853</v>
       </c>
       <c r="C19" t="n">
-        <v>4.508</v>
+        <v>10.437</v>
       </c>
       <c r="D19" t="n">
-        <v>23.175</v>
+        <v>29.286</v>
       </c>
       <c r="E19" t="n">
-        <v>382.84</v>
+        <v>385.916</v>
       </c>
       <c r="F19" t="n">
-        <v>152.843</v>
+        <v>153.59</v>
       </c>
       <c r="G19" t="n">
-        <v>120.932</v>
+        <v>122.902</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.177</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.101</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.914</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6.987</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6.497</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.883</v>
       </c>
     </row>
     <row r="20">
@@ -10561,40 +10561,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>132.136</v>
+        <v>120.83</v>
       </c>
       <c r="C20" t="n">
-        <v>136.172</v>
+        <v>124.046</v>
       </c>
       <c r="D20" t="n">
-        <v>45.395</v>
+        <v>35.092</v>
       </c>
       <c r="E20" t="n">
-        <v>224.255</v>
+        <v>219.31</v>
       </c>
       <c r="F20" t="n">
-        <v>98.873</v>
+        <v>95.608</v>
       </c>
       <c r="G20" t="n">
-        <v>124.497</v>
+        <v>112.855</v>
       </c>
       <c r="H20" t="n">
-        <v>10.995</v>
+        <v>42.608</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.029</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.275</v>
       </c>
       <c r="K20" t="n">
-        <v>9.539</v>
+        <v>70.63</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.369</v>
       </c>
       <c r="M20" t="n">
-        <v>1.504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.55800000000001</v>
+        <v>151.843</v>
       </c>
       <c r="C21" t="n">
-        <v>99.063</v>
+        <v>155.286</v>
       </c>
       <c r="D21" t="n">
-        <v>20.397</v>
+        <v>44.554</v>
       </c>
       <c r="E21" t="n">
-        <v>204.705</v>
+        <v>211.495</v>
       </c>
       <c r="F21" t="n">
-        <v>83.80200000000001</v>
+        <v>84.84699999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>86.005</v>
+        <v>86.437</v>
       </c>
       <c r="H21" t="n">
-        <v>14.682</v>
+        <v>315.454</v>
       </c>
       <c r="I21" t="n">
-        <v>4.609</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>9.297000000000001</v>
+        <v>282.613</v>
       </c>
       <c r="K21" t="n">
-        <v>23.807</v>
+        <v>217.762</v>
       </c>
       <c r="L21" t="n">
-        <v>15.954</v>
+        <v>181.643</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>114.327</v>
+        <v>285.401</v>
       </c>
       <c r="C22" t="n">
-        <v>120.887</v>
+        <v>308.21</v>
       </c>
       <c r="D22" t="n">
-        <v>35.922</v>
+        <v>213.229</v>
       </c>
       <c r="E22" t="n">
-        <v>201.41</v>
+        <v>235.775</v>
       </c>
       <c r="F22" t="n">
-        <v>74.88800000000001</v>
+        <v>93.426</v>
       </c>
       <c r="G22" t="n">
-        <v>70.70999999999999</v>
+        <v>102.116</v>
       </c>
       <c r="H22" t="n">
-        <v>333.396</v>
+        <v>337.765</v>
       </c>
       <c r="I22" t="n">
-        <v>168.953</v>
+        <v>194.998</v>
       </c>
       <c r="J22" t="n">
-        <v>304.833</v>
+        <v>436.149</v>
       </c>
       <c r="K22" t="n">
-        <v>159.955</v>
+        <v>245.437</v>
       </c>
       <c r="L22" t="n">
-        <v>150.705</v>
+        <v>351.869</v>
       </c>
       <c r="M22" t="n">
-        <v>18.902</v>
+        <v>345.778</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.053</v>
+        <v>23.674</v>
       </c>
       <c r="C23" t="n">
-        <v>7.236</v>
+        <v>30.674</v>
       </c>
       <c r="D23" t="n">
-        <v>6.276</v>
+        <v>31.352</v>
       </c>
       <c r="E23" t="n">
-        <v>21.546</v>
+        <v>24.121</v>
       </c>
       <c r="F23" t="n">
-        <v>8.757999999999999</v>
+        <v>9.516999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>99.06</v>
+        <v>119.489</v>
       </c>
       <c r="H23" t="n">
-        <v>11.334</v>
+        <v>17.539</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>22.228</v>
       </c>
       <c r="J23" t="n">
-        <v>21.449</v>
+        <v>56.305</v>
       </c>
       <c r="K23" t="n">
-        <v>10.535</v>
+        <v>16.719</v>
       </c>
       <c r="L23" t="n">
-        <v>24.243</v>
+        <v>30.828</v>
       </c>
       <c r="M23" t="n">
-        <v>9.904999999999999</v>
+        <v>32.793</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.885</v>
+        <v>15.531</v>
       </c>
       <c r="C24" t="n">
-        <v>8.907</v>
+        <v>25.396</v>
       </c>
       <c r="D24" t="n">
-        <v>5.29</v>
+        <v>21.851</v>
       </c>
       <c r="E24" t="n">
-        <v>24.782</v>
+        <v>25.831</v>
       </c>
       <c r="F24" t="n">
-        <v>10.331</v>
+        <v>10.456</v>
       </c>
       <c r="G24" t="n">
-        <v>122.325</v>
+        <v>125.227</v>
       </c>
       <c r="H24" t="n">
-        <v>14.395</v>
+        <v>16.58</v>
       </c>
       <c r="I24" t="n">
-        <v>22.1</v>
+        <v>20.535</v>
       </c>
       <c r="J24" t="n">
-        <v>22.573</v>
+        <v>46.069</v>
       </c>
       <c r="K24" t="n">
-        <v>10.676</v>
+        <v>16.215</v>
       </c>
       <c r="L24" t="n">
-        <v>26.582</v>
+        <v>27.037</v>
       </c>
       <c r="M24" t="n">
-        <v>16.085</v>
+        <v>28.073</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.742</v>
+        <v>13.563</v>
       </c>
       <c r="C25" t="n">
-        <v>10.397</v>
+        <v>17.647</v>
       </c>
       <c r="D25" t="n">
-        <v>7.173</v>
+        <v>14.358</v>
       </c>
       <c r="E25" t="n">
-        <v>26.426</v>
+        <v>26.681</v>
       </c>
       <c r="F25" t="n">
-        <v>11.776</v>
+        <v>12.021</v>
       </c>
       <c r="G25" t="n">
-        <v>63.877</v>
+        <v>86.818</v>
       </c>
       <c r="H25" t="n">
-        <v>8.564</v>
+        <v>16.527</v>
       </c>
       <c r="I25" t="n">
-        <v>1.271</v>
+        <v>11.087</v>
       </c>
       <c r="J25" t="n">
-        <v>1.225</v>
+        <v>18.461</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>21.149</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>27.456</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>18.094</v>
       </c>
     </row>
     <row r="26">
@@ -10819,37 +10819,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.58</v>
+        <v>7.778</v>
       </c>
       <c r="C26" t="n">
-        <v>9.933999999999999</v>
+        <v>11.235</v>
       </c>
       <c r="D26" t="n">
-        <v>3.571</v>
+        <v>4.172</v>
       </c>
       <c r="E26" t="n">
-        <v>22.686</v>
+        <v>22.438</v>
       </c>
       <c r="F26" t="n">
-        <v>11.281</v>
+        <v>11.269</v>
       </c>
       <c r="G26" t="n">
-        <v>93.23399999999999</v>
+        <v>96.301</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="I26" t="n">
-        <v>0.705</v>
+        <v>1.551</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.756</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.061</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.819</v>
+        <v>21.634</v>
       </c>
       <c r="C27" t="n">
-        <v>4.266</v>
+        <v>31.771</v>
       </c>
       <c r="D27" t="n">
-        <v>2.961</v>
+        <v>27.277</v>
       </c>
       <c r="E27" t="n">
-        <v>22.007</v>
+        <v>24.271</v>
       </c>
       <c r="F27" t="n">
-        <v>10.996</v>
+        <v>12.223</v>
       </c>
       <c r="G27" t="n">
-        <v>81.908</v>
+        <v>109.659</v>
       </c>
       <c r="H27" t="n">
-        <v>21.933</v>
+        <v>30.772</v>
       </c>
       <c r="I27" t="n">
-        <v>16.855</v>
+        <v>12.796</v>
       </c>
       <c r="J27" t="n">
-        <v>42.51</v>
+        <v>55.912</v>
       </c>
       <c r="K27" t="n">
-        <v>11.903</v>
+        <v>34.4</v>
       </c>
       <c r="L27" t="n">
-        <v>32.756</v>
+        <v>38.12</v>
       </c>
       <c r="M27" t="n">
-        <v>8.339</v>
+        <v>35.866</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.401</v>
+        <v>2.447</v>
       </c>
       <c r="C28" t="n">
-        <v>0.661</v>
+        <v>0.793</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.238</v>
+        <v>22.019</v>
       </c>
       <c r="F28" t="n">
-        <v>10.991</v>
+        <v>11.078</v>
       </c>
       <c r="G28" t="n">
-        <v>43.697</v>
+        <v>61.175</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.399</v>
+        <v>0.512</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.693</v>
+        <v>4.367</v>
       </c>
       <c r="C29" t="n">
-        <v>0.284</v>
+        <v>5.664</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3.613</v>
       </c>
       <c r="E29" t="n">
-        <v>21.558</v>
+        <v>22.205</v>
       </c>
       <c r="F29" t="n">
-        <v>10.421</v>
+        <v>10.799</v>
       </c>
       <c r="G29" t="n">
-        <v>61.837</v>
+        <v>71.66200000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4.842</v>
       </c>
       <c r="I29" t="n">
-        <v>0.828</v>
+        <v>6.896</v>
       </c>
       <c r="J29" t="n">
-        <v>0.067</v>
+        <v>11.724</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>9.029</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>17.681</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="30">
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.808</v>
+        <v>13.548</v>
       </c>
       <c r="F30" t="n">
-        <v>5.919</v>
+        <v>5.748</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728599696e-06</v>
+        <v>1.9401425521e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.668559104e-06</v>
+        <v>2.0893835209e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>7.925450625000001e-06</v>
+        <v>3.9740023801e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.204010312899999e-05</v>
+        <v>6.2573021316e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1205281025e-05</v>
+        <v>1.1917433889e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0888631841e-05</v>
+        <v>2.6922902724e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.74900625e-07</v>
+        <v>2.9110843161e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>4.694588890000001e-07</v>
+        <v>3.857296000000001e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>8.613696100000003e-08</v>
+        <v>6.1736843961e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>8.7647044e-08</v>
+        <v>3.49278721e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.816768400000001e-08</v>
+        <v>3.0470146249e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.36960209e-07</v>
+        <v>5.3138087289e-05</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.823887849e-06</v>
+        <v>5.555913443999999e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.394200921e-06</v>
+        <v>5.895782656e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.877677441e-06</v>
+        <v>1.1821560529e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6969292176e-05</v>
+        <v>4.8598643401e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.817570528999999e-06</v>
+        <v>5.850873081e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.899008025000002e-06</v>
+        <v>7.3994404e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.129969e-09</v>
+        <v>1.8631158016e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.750337599999999e-08</v>
+        <v>1.8364586256e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3942756e-08</v>
+        <v>1.1764222369e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>5.866084000000001e-09</v>
+        <v>1.9110574081e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>4.844401000000001e-09</v>
+        <v>1.6255995001e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.585664e-09</v>
+        <v>6.194791848999999e-06</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.427260089999999e-07</v>
+        <v>1.445216256e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>3.96766561e-07</v>
+        <v>7.346268159999999e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.797251236e-06</v>
+        <v>2.440261201e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.87066276e-05</v>
+        <v>4.030457759999999e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.355166041000001e-06</v>
+        <v>5.483402499999999e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.487611136e-06</v>
+        <v>4.252735369e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>8.744120100000002e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.661281e-09</v>
+        <v>1.2694969e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.46615616e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8.231734809999998e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>7.846416400000002e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.040100000000001e-11</v>
+        <v>1.5876e-07</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.39443776e-07</v>
+        <v>3.95811025e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3707161e-08</v>
+        <v>4.4249104e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.250809e-07</v>
+        <v>3.442509159999999e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.847129188099999e-05</v>
+        <v>3.8053475329e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.960326281000003e-06</v>
+        <v>8.810075044000001e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>6.219215044e-06</v>
+        <v>5.909304383999999e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.52015625e-07</v>
+        <v>4.011322225000001e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>3.038049000000001e-09</v>
+        <v>1.090584576e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>1.00681156e-07</v>
+        <v>2.644942041e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9838071169e-05</v>
+        <v>3.3079970641e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.352548009000001e-06</v>
+        <v>8.030668996000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.035363225e-06</v>
+        <v>3.340262025e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.816464399999999e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.002225e-09</v>
+        <v>4.875263999999999e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>8.584899999999997e-11</v>
+        <v>5.278749024999999e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.20409e-10</v>
+        <v>1.0191104401e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.847396321e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.100097023999998e-06</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.436745633333333e-08</v>
+        <v>4.080772008333333e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4.529210785333334e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.349704560333334e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.981881221333334e-06</v>
+        <v>3.842414408333332e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.814530256333334e-06</v>
+        <v>9.792310536333332e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>4.155045453333333e-07</v>
+        <v>1.573138401333333e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>5.395835385633333e-05</v>
+        <v>6.575788800833332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.454673754133334e-05</v>
+        <v>3.472617876299999e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.041803408333333e-06</v>
+        <v>4.672437120299999e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.845313510533333e-05</v>
+        <v>4.445482216033334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.010071480000001e-07</v>
+        <v>3.877715782533333e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>8.053391363333332e-07</v>
+        <v>5.5514115072e-05</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.2267001e-08</v>
+        <v>8.098200100000001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.603720164000002e-06</v>
+        <v>5.694513444e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9009515625e-05</v>
+        <v>2.0079456804e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>5.887902250000001e-07</v>
+        <v>7.132638490000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5.86756e-10</v>
+        <v>3.225616e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2216004e-06</v>
+        <v>3.895632225e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11414,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.356634253333333e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.608033333333334e-11</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6.120408333333333e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.406589603333334e-07</v>
+        <v>8.044873763333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.503202988e-06</v>
+        <v>3.210551960333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.949121333333334e-09</v>
+        <v>5.100563333333332e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.123413333333333e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.482296333333332e-09</v>
+        <v>2.870430083333333e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.370928e-09</v>
+        <v>1.283802083333333e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5.946269281333335e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56211968e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1047683e-08</v>
       </c>
     </row>
     <row r="10">
@@ -11466,28 +11466,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.416960963333334e-07</v>
+        <v>4.855224083333332e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.623129320333334e-06</v>
+        <v>1.847600833333333e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.136333333333333e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>7.261919999999999e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3.6855075e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.678440533333333e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8.833968e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.694216333333333e-09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -11509,22 +11509,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.824148803333335e-07</v>
+        <v>4.445457869999999e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.265099745333333e-06</v>
+        <v>1.352435936333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.93548e-10</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.785960333333333e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4.652565333333334e-09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.651098453333334e-07</v>
+        <v>1.732192053333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.536041013333334e-07</v>
+        <v>7.841480013333335e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.62867e-10</v>
+        <v>2.507942533333333e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>2.362081333333334e-07</v>
+        <v>3.893557763333333e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11607,16 +11607,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.831083e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>6.097520833333334e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>9.402400833333334e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8287883e-08</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.317461729000001e-06</v>
+        <v>3.9371290084e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>3.467796543999999e-06</v>
+        <v>3.3152033929e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>7.266028080999999e-06</v>
+        <v>4.228328564099999e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5174101764e-05</v>
+        <v>5.4763488256e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.283515200999998e-06</v>
+        <v>9.631067044e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1588945424e-05</v>
+        <v>5.8700082961e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>3.17730625e-07</v>
+        <v>2.0843274384e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.630869264e-06</v>
+        <v>2.843978688099999e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.718728249000001e-06</v>
+        <v>4.4431580944e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4279055025e-05</v>
+        <v>5.7603840064e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.365363225e-06</v>
+        <v>6.0558811569e-05</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.554268181333334e-06</v>
+        <v>2.6874163827e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>2.501816652e-06</v>
+        <v>2.725465704533334e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>1.026487808533333e-05</v>
+        <v>3.804213542533334e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.691125700833334e-05</v>
+        <v>4.828519960033332e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.327167145633334e-05</v>
+        <v>1.420100800833334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.333743240533333e-05</v>
+        <v>5.998046600833333e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1578919628e-05</v>
+        <v>4.235837952533334e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>1.522307080333333e-06</v>
+        <v>8.566325160333335e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>2.638650353633333e-05</v>
+        <v>5.944548180033333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>2.883930075e-06</v>
+        <v>4.7200312467e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>1.929146868033334e-05</v>
+        <v>4.550195469633334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.654309205333333e-06</v>
+        <v>4.895226732033333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.112130208333333e-06</v>
+        <v>1.205386208133333e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>2.613818901333333e-06</v>
+        <v>1.043993222533333e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3579391523e-05</v>
+        <v>2.757412940833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7506868912e-05</v>
+        <v>5.850301594799999e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.039608880133333e-05</v>
+        <v>1.05779532e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.471800248033333e-05</v>
+        <v>3.593221632533333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>9.580479362999998e-06</v>
+        <v>3.739337149633333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>6.103280333333334e-07</v>
+        <v>5.038409045333333e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.586716840333335e-06</v>
+        <v>5.933151574533333e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>1.760794133333334e-06</v>
+        <v>2.6241899187e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>8.952655151999998e-06</v>
+        <v>4.437938138699999e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>1.728432027e-06</v>
+        <v>3.625403456033334e-05</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.48290083e-07</v>
+        <v>8.09637552e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.355692963333334e-07</v>
+        <v>2.80932987e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>5.347476029999999e-07</v>
+        <v>7.371482253333335e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.1604115148e-05</v>
+        <v>5.290778560033334e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.471472520333334e-06</v>
+        <v>8.771884280333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.551826401333335e-06</v>
+        <v>6.570345605333333e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.917376853333333e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.557336033333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.178509363333333e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>3.52711947e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>9.002936333333335e-09</v>
+        <v>9.119725453333332e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.432880853333333e-07</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.071974963333333e-07</v>
+        <v>1.89655203e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>3.6310323e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.79026875e-07</v>
+        <v>2.85889932e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.885548853333333e-05</v>
+        <v>4.964371968533333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.786994216333332e-06</v>
+        <v>7.863296033333334e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.874849541333333e-06</v>
+        <v>5.034967201333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.364443000000001e-09</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.205400333333334e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.221132e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.6272723e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.407033633333333e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7.947896333333335e-09</v>
       </c>
     </row>
     <row r="20">
@@ -11885,40 +11885,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.819974165333333e-06</v>
+        <v>4.866629633333332e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>6.180937861333332e-06</v>
+        <v>5.129136705333333e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>6.869020083333335e-07</v>
+        <v>4.104828213333333e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.676343500833333e-05</v>
+        <v>1.603229203333334e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.258623376333333e-06</v>
+        <v>3.046963221333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>5.166501003e-06</v>
+        <v>4.245417008333334e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>4.029667499999999e-08</v>
+        <v>6.051472213333333e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.058280333333333e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.725208333333333e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>3.033084033333332e-08</v>
+        <v>1.662865633333333e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.783387e-09</v>
       </c>
       <c r="M20" t="n">
-        <v>7.540053333333332e-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.107815788e-06</v>
+        <v>7.685432216333331e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>3.271159323e-06</v>
+        <v>8.037913932000002e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38679203e-07</v>
+        <v>6.616863053333334e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3968045675e-05</v>
+        <v>1.491004500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.340925068e-06</v>
+        <v>2.399671136333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.465620008333333e-06</v>
+        <v>2.490451656333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>7.1853708e-08</v>
+        <v>3.317040870533334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>7.080960333333333e-09</v>
+        <v>1.536803333333333e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>2.881140300000001e-08</v>
+        <v>2.662336925633333e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>1.889244163333333e-07</v>
+        <v>1.580676288133333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>8.484337199999999e-08</v>
+        <v>1.099805981633333e-05</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.356887643e-06</v>
+        <v>2.715124360033333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>4.871222256333332e-06</v>
+        <v>3.166446803333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>4.301300279999999e-07</v>
+        <v>1.515553548033333e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.352199603333333e-05</v>
+        <v>1.852995020833333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.869404181333334e-06</v>
+        <v>2.909472492e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6666347e-06</v>
+        <v>3.475892485333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.705096427200001e-05</v>
+        <v>3.802839840833333e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>9.515038736333332e-06</v>
+        <v>1.267474000133333e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.097438596300001e-05</v>
+        <v>6.3408650067e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>8.528534008333335e-06</v>
+        <v>2.007977365633334e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>7.570665675000001e-06</v>
+        <v>4.127059772033335e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>1.190952013333334e-07</v>
+        <v>3.985414176133334e-05</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.31864809e-06</v>
+        <v>5.60458276e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>5.235969599999999e-07</v>
+        <v>9.408942760000001e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>3.938817599999999e-07</v>
+        <v>9.82947904e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>4.64230116e-06</v>
+        <v>5.81822641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>7.670256399999996e-07</v>
+        <v>9.057328899999998e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.812883600000002e-06</v>
+        <v>1.4277621121e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.28459556e-06</v>
+        <v>3.076165210000001e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.41e-06</v>
+        <v>4.940839840000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>4.600596010000001e-06</v>
+        <v>3.170253025e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>1.10986225e-06</v>
+        <v>2.79524961e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>5.877230489999999e-06</v>
+        <v>9.503655839999998e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>9.810902499999998e-07</v>
+        <v>1.075380849e-05</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.7403225e-07</v>
+        <v>2.41211961e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>7.933464900000001e-07</v>
+        <v>6.449568160000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>4.774662009999999e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.14147524e-06</v>
+        <v>6.67240561e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.06729561e-06</v>
+        <v>1.09327936e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4963405625e-05</v>
+        <v>1.5681801529e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.07216025e-06</v>
+        <v>2.748963999999999e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>4.884100000000001e-06</v>
+        <v>4.21686225e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>5.095403289999999e-06</v>
+        <v>2.122352761e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>1.13976976e-06</v>
+        <v>2.62926225e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>7.066027240000001e-06</v>
+        <v>7.309993689999999e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>2.587272250000001e-06</v>
+        <v>7.88093329e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.37874564e-06</v>
+        <v>1.83954969e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.08097609e-06</v>
+        <v>3.11416609e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>5.145192899999999e-07</v>
+        <v>2.06152164e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>6.98333476e-06</v>
+        <v>7.118757610000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.38674176e-06</v>
+        <v>1.44504441e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>4.080271129e-06</v>
+        <v>7.537365123999998e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>7.334209600000002e-07</v>
+        <v>2.73141729e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.615441e-08</v>
+        <v>1.22921569e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>1.500625e-08</v>
+        <v>3.408085209999999e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4.472802010000001e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>7.538319360000001e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.273928360000001e-06</v>
       </c>
     </row>
     <row r="26">
@@ -12143,37 +12143,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.74564e-07</v>
+        <v>6.049728399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>9.868435600000001e-07</v>
+        <v>1.26225225e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2752041e-07</v>
+        <v>1.7405584e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.14654596e-06</v>
+        <v>5.03463844e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.27260961e-06</v>
+        <v>1.26990361e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.692578755999999e-06</v>
+        <v>9.273882601e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.012036e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>4.97025e-09</v>
+        <v>2.405601e-08</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>5.715360000000001e-09</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.53009e-09</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.5613721e-07</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.386076099999999e-07</v>
+        <v>4.680299560000001e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.8198756e-07</v>
+        <v>1.009396441e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>8.767520999999998e-08</v>
+        <v>7.440347290000001e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>4.843080490000001e-06</v>
+        <v>5.890814410000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.20912016e-06</v>
+        <v>1.49401729e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>6.708920463999999e-06</v>
+        <v>1.2025096281e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>4.81056489e-06</v>
+        <v>9.469159839999999e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>2.84091025e-06</v>
+        <v>1.63737616e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8071001e-05</v>
+        <v>3.126151743999999e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.41681409e-06</v>
+        <v>1.18336e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.072955536e-05</v>
+        <v>1.453134399999999e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>6.953892100000002e-07</v>
+        <v>1.286369956e-05</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.764801e-08</v>
+        <v>5.987809e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>4.369210000000001e-09</v>
+        <v>6.288490000000001e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.945286440000001e-06</v>
+        <v>4.848363609999998e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.20802081e-06</v>
+        <v>1.22722084e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.909427809e-06</v>
+        <v>3.742380625e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.59201e-09</v>
+        <v>2.62144e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.866249e-08</v>
+        <v>1.9070689e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>8.065599999999997e-10</v>
+        <v>3.2080896e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1.3053769e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.64747364e-06</v>
+        <v>4.930620249999999e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08597241e-06</v>
+        <v>1.16618401e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>3.823814569e-06</v>
+        <v>5.135442244e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.3444964e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>6.855839999999999e-09</v>
+        <v>4.7554816e-07</v>
       </c>
       <c r="J29" t="n">
-        <v>4.489000000000001e-11</v>
+        <v>1.37452176e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>8.152284100000001e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.126177610000001e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.798410000000001e-07</v>
       </c>
     </row>
     <row r="30">
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.90660864e-06</v>
+        <v>1.83548304e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.5034561e-07</v>
+        <v>3.303950400000001e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="I2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="J2" t="n">
-        <v>0.013542</v>
+        <v>0.123958</v>
       </c>
       <c r="K2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="M2" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="3">
@@ -12482,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="J3" t="n">
-        <v>0.013542</v>
+        <v>0.122569</v>
       </c>
       <c r="K3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="L3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="M3" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C4" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.013194</v>
+        <v>0.124653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="I4" t="n">
-        <v>0.013542</v>
+        <v>0.051042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M4" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="5">
@@ -12568,10 +12568,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001042</v>
+        <v>0.124653</v>
       </c>
       <c r="D5" t="n">
         <v>0.000694</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="J6" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="K6" t="n">
-        <v>0.013194</v>
+        <v>0.124653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="7">
@@ -12652,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F7" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G7" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.013542</v>
+        <v>0.080556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.013542</v>
+        <v>0.045833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.013542</v>
+        <v>0.047569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.013542</v>
+        <v>0.061806</v>
       </c>
       <c r="L7" t="n">
-        <v>0.013542</v>
+        <v>0.08784699999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.013542</v>
+        <v>0.103472</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.010417</v>
+        <v>0.121528</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12704,19 +12704,19 @@
         <v>0.003472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.010417</v>
+        <v>0.111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.010417</v>
+        <v>0.121528</v>
       </c>
       <c r="G8" t="n">
-        <v>0.010417</v>
+        <v>0.121528</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.010417</v>
+        <v>0.100694</v>
       </c>
       <c r="J8" t="n">
         <v>0.003472</v>
@@ -12738,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G9" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="J9" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="10">
@@ -12790,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F10" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000347</v>
+        <v>0.123958</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000347</v>
+        <v>0.08437500000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12833,22 +12833,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.124653</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.124653</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.124653</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12876,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="F12" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12919,10 +12919,10 @@
         <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F13" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G13" t="n">
         <v>0.000347</v>
@@ -12931,16 +12931,16 @@
         <v>0.000347</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C15" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D15" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000347</v>
+        <v>0.046528</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="K15" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M15" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C16" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D16" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.010764</v>
+        <v>0.124653</v>
       </c>
       <c r="F16" t="n">
-        <v>0.011458</v>
+        <v>0.124653</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0125</v>
+        <v>0.021875</v>
       </c>
       <c r="H16" t="n">
-        <v>0.013542</v>
+        <v>0.076389</v>
       </c>
       <c r="I16" t="n">
-        <v>0.013542</v>
+        <v>0.060764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.013542</v>
+        <v>0.07256899999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="L16" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="M16" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="17">
@@ -13080,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001042</v>
+        <v>0.101042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="I17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="J17" t="n">
-        <v>0.013542</v>
+        <v>0.100694</v>
       </c>
       <c r="K17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="L17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="M17" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="18">
@@ -13123,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C18" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D18" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E18" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001389</v>
+        <v>0.124653</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000347</v>
+        <v>0.092361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000347</v>
+        <v>0.073958</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000347</v>
+        <v>0.064236</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000347</v>
+        <v>0.088542</v>
       </c>
       <c r="L18" t="n">
-        <v>0.013542</v>
+        <v>0.053125</v>
       </c>
       <c r="M18" t="n">
-        <v>0.000347</v>
+        <v>0.061458</v>
       </c>
     </row>
     <row r="19">
@@ -13166,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C19" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D19" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E19" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F19" t="n">
-        <v>0.013542</v>
+        <v>0.044792</v>
       </c>
       <c r="G19" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H19" t="n">
-        <v>0.000347</v>
+        <v>0.092014</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000347</v>
+        <v>0.100347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000347</v>
+        <v>0.1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.000347</v>
+        <v>0.093056</v>
       </c>
       <c r="L19" t="n">
-        <v>0.000347</v>
+        <v>0.052431</v>
       </c>
       <c r="M19" t="n">
-        <v>0.000347</v>
+        <v>0.067708</v>
       </c>
     </row>
     <row r="20">
@@ -13236,10 +13236,10 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L20" t="n">
-        <v>0.000347</v>
+        <v>0.026736</v>
       </c>
       <c r="M20" t="n">
         <v>0.000347</v>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005903</v>
+        <v>0.124653</v>
       </c>
       <c r="H21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="I21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="J21" t="n">
-        <v>0.013542</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.013542</v>
+        <v>0.101042</v>
       </c>
       <c r="L21" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H22" t="n">
-        <v>0.013542</v>
+        <v>0.052431</v>
       </c>
       <c r="I22" t="n">
-        <v>0.013542</v>
+        <v>0.021181</v>
       </c>
       <c r="J22" t="n">
-        <v>0.013542</v>
+        <v>0.073958</v>
       </c>
       <c r="K22" t="n">
-        <v>0.013542</v>
+        <v>0.118403</v>
       </c>
       <c r="L22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="M22" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="23">
@@ -13338,40 +13338,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0125</v>
+        <v>0.028819</v>
       </c>
       <c r="C23" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D23" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F23" t="n">
-        <v>0.013542</v>
+        <v>0.123958</v>
       </c>
       <c r="G23" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H23" t="n">
-        <v>0.013542</v>
+        <v>0.033681</v>
       </c>
       <c r="I23" t="n">
-        <v>0.013542</v>
+        <v>0.022222</v>
       </c>
       <c r="J23" t="n">
-        <v>0.013542</v>
+        <v>0.117708</v>
       </c>
       <c r="K23" t="n">
-        <v>0.013542</v>
+        <v>0.031944</v>
       </c>
       <c r="L23" t="n">
-        <v>0.013542</v>
+        <v>0.042014</v>
       </c>
       <c r="M23" t="n">
-        <v>0.013542</v>
+        <v>0.045486</v>
       </c>
     </row>
     <row r="24">
@@ -13381,40 +13381,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C24" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="D24" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E24" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="F24" t="n">
-        <v>0.000347</v>
+        <v>0.080208</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="H24" t="n">
-        <v>0.013542</v>
+        <v>0.024306</v>
       </c>
       <c r="I24" t="n">
-        <v>0.013542</v>
+        <v>0.017361</v>
       </c>
       <c r="J24" t="n">
-        <v>0.013542</v>
+        <v>0.09375</v>
       </c>
       <c r="K24" t="n">
-        <v>0.013542</v>
+        <v>0.030556</v>
       </c>
       <c r="L24" t="n">
-        <v>0.013542</v>
+        <v>0.025347</v>
       </c>
       <c r="M24" t="n">
-        <v>0.013542</v>
+        <v>0.036111</v>
       </c>
     </row>
     <row r="25">
@@ -13424,40 +13424,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001042</v>
+        <v>0.124653</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001042</v>
+        <v>0.124653</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000694</v>
+        <v>0.106597</v>
       </c>
       <c r="G25" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H25" t="n">
-        <v>0.013542</v>
+        <v>0.043403</v>
       </c>
       <c r="I25" t="n">
-        <v>0.011111</v>
+        <v>0.092014</v>
       </c>
       <c r="J25" t="n">
-        <v>0.013542</v>
+        <v>0.054167</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000347</v>
+        <v>0.080208</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001042</v>
+        <v>0.115625</v>
       </c>
       <c r="M25" t="n">
-        <v>0.000347</v>
+        <v>0.103472</v>
       </c>
     </row>
     <row r="26">
@@ -13470,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.010069</v>
+        <v>0.124653</v>
       </c>
       <c r="D26" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13482,22 +13482,22 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000347</v>
+        <v>0.08472200000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.012153</v>
+        <v>0.124653</v>
       </c>
       <c r="J26" t="n">
-        <v>0.000347</v>
+        <v>0.104167</v>
       </c>
       <c r="K26" t="n">
-        <v>0.000347</v>
+        <v>0.072917</v>
       </c>
       <c r="L26" t="n">
-        <v>0.000347</v>
+        <v>0.089931</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C27" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="D27" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001389</v>
+        <v>0.124653</v>
       </c>
       <c r="F27" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="G27" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H27" t="n">
-        <v>0.013542</v>
+        <v>0.07083299999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.013542</v>
+        <v>0.015278</v>
       </c>
       <c r="J27" t="n">
-        <v>0.013542</v>
+        <v>0.067014</v>
       </c>
       <c r="K27" t="n">
-        <v>0.013542</v>
+        <v>0.057639</v>
       </c>
       <c r="L27" t="n">
-        <v>0.013542</v>
+        <v>0.043403</v>
       </c>
       <c r="M27" t="n">
-        <v>0.013542</v>
+        <v>0.057639</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.013542</v>
+        <v>0.052431</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,13 +13568,13 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
       </c>
       <c r="I28" t="n">
-        <v>0.013542</v>
+        <v>0.040625</v>
       </c>
       <c r="J28" t="n">
         <v>0.000347</v>
@@ -13596,40 +13596,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001042</v>
+        <v>0.124306</v>
       </c>
       <c r="D29" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="E29" t="n">
-        <v>0.013542</v>
+        <v>0.123958</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001042</v>
+        <v>0.124653</v>
       </c>
       <c r="G29" t="n">
-        <v>0.013542</v>
+        <v>0.124653</v>
       </c>
       <c r="H29" t="n">
-        <v>0.000347</v>
+        <v>0.092708</v>
       </c>
       <c r="I29" t="n">
-        <v>0.010069</v>
+        <v>0.093056</v>
       </c>
       <c r="J29" t="n">
-        <v>0.013542</v>
+        <v>0.058333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.000347</v>
+        <v>0.08819399999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000347</v>
+        <v>0.077431</v>
       </c>
       <c r="M29" t="n">
-        <v>0.000347</v>
+        <v>0.117708</v>
       </c>
     </row>
     <row r="30">

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.109</v>
+        <v>0.014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.096</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.254</v>
+        <v>0.037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.608</v>
+        <v>0.187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.124</v>
+        <v>0.04</v>
       </c>
       <c r="G2" t="n">
-        <v>0.253</v>
+        <v>0.076</v>
       </c>
       <c r="H2" t="n">
-        <v>0.146</v>
+        <v>0.007</v>
       </c>
       <c r="I2" t="n">
-        <v>0.185</v>
+        <v>0.012</v>
       </c>
       <c r="J2" t="n">
-        <v>0.293</v>
+        <v>0.006</v>
       </c>
       <c r="K2" t="n">
-        <v>0.151</v>
+        <v>0.003</v>
       </c>
       <c r="L2" t="n">
-        <v>0.138</v>
+        <v>0.003</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039</v>
+        <v>0.007</v>
       </c>
       <c r="C3" t="n">
-        <v>0.036</v>
+        <v>0.006</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08</v>
+        <v>0.016</v>
       </c>
       <c r="E3" t="n">
-        <v>0.511</v>
+        <v>0.168</v>
       </c>
       <c r="F3" t="n">
-        <v>0.062</v>
+        <v>0.021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="H3" t="n">
-        <v>0.059</v>
+        <v>0.001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="E4" t="n">
-        <v>0.423</v>
+        <v>0.138</v>
       </c>
       <c r="F4" t="n">
-        <v>0.058</v>
+        <v>0.019</v>
       </c>
       <c r="G4" t="n">
-        <v>0.041</v>
+        <v>0.013</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.41</v>
+        <v>0.136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.096</v>
+        <v>0.032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.065</v>
+        <v>0.022</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.336</v>
+        <v>0.107</v>
       </c>
       <c r="F6" t="n">
-        <v>0.082</v>
+        <v>0.026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.028</v>
+        <v>0.008</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.007</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.029</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.094</v>
+        <v>0.028</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>0.646</v>
+        <v>0.174</v>
       </c>
       <c r="I7" t="n">
-        <v>0.369</v>
+        <v>0.115</v>
       </c>
       <c r="J7" t="n">
-        <v>0.416</v>
+        <v>0.054</v>
       </c>
       <c r="K7" t="n">
-        <v>0.457</v>
+        <v>0.132</v>
       </c>
       <c r="L7" t="n">
-        <v>0.284</v>
+        <v>0.025</v>
       </c>
       <c r="M7" t="n">
-        <v>0.364</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.059</v>
+        <v>0.018</v>
       </c>
       <c r="F8" t="n">
-        <v>0.203</v>
+        <v>0.06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.063</v>
+        <v>0.022</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2153,13 +2153,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.263</v>
+        <v>0.043</v>
       </c>
       <c r="C15" t="n">
-        <v>0.177</v>
+        <v>0.019</v>
       </c>
       <c r="D15" t="n">
-        <v>0.246</v>
+        <v>0.035</v>
       </c>
       <c r="E15" t="n">
-        <v>0.536</v>
+        <v>0.163</v>
       </c>
       <c r="F15" t="n">
-        <v>0.103</v>
+        <v>0.033</v>
       </c>
       <c r="G15" t="n">
-        <v>0.594</v>
+        <v>0.186</v>
       </c>
       <c r="H15" t="n">
-        <v>0.174</v>
+        <v>0.022</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.185</v>
+        <v>0.023</v>
       </c>
       <c r="K15" t="n">
-        <v>0.356</v>
+        <v>0.058</v>
       </c>
       <c r="L15" t="n">
-        <v>0.502</v>
+        <v>0.102</v>
       </c>
       <c r="M15" t="n">
-        <v>0.49</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.167</v>
+        <v>0.023</v>
       </c>
       <c r="C16" t="n">
-        <v>0.136</v>
+        <v>0.014</v>
       </c>
       <c r="D16" t="n">
-        <v>0.262</v>
+        <v>0.045</v>
       </c>
       <c r="E16" t="n">
-        <v>0.502</v>
+        <v>0.166</v>
       </c>
       <c r="F16" t="n">
-        <v>0.148</v>
+        <v>0.047</v>
       </c>
       <c r="G16" t="n">
-        <v>0.643</v>
+        <v>0.217</v>
       </c>
       <c r="H16" t="n">
-        <v>0.373</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.075</v>
+        <v>0.013</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="K16" t="n">
-        <v>0.37</v>
+        <v>0.055</v>
       </c>
       <c r="L16" t="n">
-        <v>0.401</v>
+        <v>0.092</v>
       </c>
       <c r="M16" t="n">
-        <v>0.403</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.077</v>
+        <v>0.013</v>
       </c>
       <c r="C17" t="n">
-        <v>0.064</v>
+        <v>0.011</v>
       </c>
       <c r="D17" t="n">
-        <v>0.218</v>
+        <v>0.052</v>
       </c>
       <c r="E17" t="n">
-        <v>0.623</v>
+        <v>0.205</v>
       </c>
       <c r="F17" t="n">
-        <v>0.113</v>
+        <v>0.037</v>
       </c>
       <c r="G17" t="n">
-        <v>0.379</v>
+        <v>0.124</v>
       </c>
       <c r="H17" t="n">
-        <v>0.265</v>
+        <v>0.047</v>
       </c>
       <c r="I17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.029</v>
       </c>
-      <c r="J17" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.2</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.341</v>
+        <v>0.054</v>
       </c>
       <c r="M17" t="n">
-        <v>0.24</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="C18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.002</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.007</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.184</v>
       </c>
       <c r="F18" t="n">
-        <v>0.093</v>
+        <v>0.03</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.002</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.014</v>
-      </c>
       <c r="M18" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.53</v>
+        <v>0.174</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="G19" t="n">
-        <v>0.053</v>
+        <v>0.017</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.058</v>
+        <v>0.02</v>
       </c>
       <c r="C20" t="n">
-        <v>0.061</v>
+        <v>0.022</v>
       </c>
       <c r="D20" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="E20" t="n">
-        <v>0.176</v>
+        <v>0.059</v>
       </c>
       <c r="F20" t="n">
-        <v>0.034</v>
+        <v>0.012</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05</v>
+        <v>0.018</v>
       </c>
       <c r="H20" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.056</v>
+        <v>0.012</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.155</v>
+        <v>0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="G21" t="n">
-        <v>0.026</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.202</v>
+        <v>0.005</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.161</v>
+        <v>0.001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.117</v>
+        <v>0.01</v>
       </c>
       <c r="L21" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.171</v>
+        <v>0.023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.194</v>
+        <v>0.025</v>
       </c>
       <c r="D22" t="n">
-        <v>0.065</v>
+        <v>0.004</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0.049</v>
       </c>
       <c r="F22" t="n">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="G22" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="H22" t="n">
-        <v>0.394</v>
+        <v>0.108</v>
       </c>
       <c r="I22" t="n">
-        <v>0.137</v>
+        <v>0.036</v>
       </c>
       <c r="J22" t="n">
-        <v>0.609</v>
+        <v>0.144</v>
       </c>
       <c r="K22" t="n">
-        <v>0.183</v>
+        <v>0.042</v>
       </c>
       <c r="L22" t="n">
-        <v>0.352</v>
+        <v>0.068</v>
       </c>
       <c r="M22" t="n">
-        <v>0.222</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.064</v>
+        <v>0.038</v>
       </c>
       <c r="C23" t="n">
-        <v>0.058</v>
+        <v>0.005</v>
       </c>
       <c r="D23" t="n">
-        <v>0.056</v>
+        <v>0.004</v>
       </c>
       <c r="E23" t="n">
-        <v>0.056</v>
+        <v>0.017</v>
       </c>
       <c r="F23" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G23" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.033</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.097</v>
+        <v>0.024</v>
       </c>
       <c r="M23" t="n">
-        <v>0.101</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="D24" t="n">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="G24" t="n">
-        <v>0.164</v>
+        <v>0.053</v>
       </c>
       <c r="H24" t="n">
-        <v>0.033</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.054</v>
+        <v>0.017</v>
       </c>
       <c r="J24" t="n">
-        <v>0.191</v>
+        <v>0.032</v>
       </c>
       <c r="K24" t="n">
-        <v>0.032</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.083</v>
+        <v>0.025</v>
       </c>
       <c r="M24" t="n">
-        <v>0.081</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="C25" t="n">
-        <v>0.022</v>
+        <v>0.004</v>
       </c>
       <c r="D25" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.077</v>
+        <v>0.025</v>
       </c>
       <c r="F25" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="G25" t="n">
-        <v>0.063</v>
+        <v>0.016</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
       <c r="I25" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.044</v>
+        <v>0.006</v>
       </c>
       <c r="K25" t="n">
-        <v>0.038</v>
+        <v>0.002</v>
       </c>
       <c r="L25" t="n">
-        <v>0.047</v>
+        <v>0.002</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="C26" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.055</v>
+        <v>0.018</v>
       </c>
       <c r="F26" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="G26" t="n">
-        <v>0.097</v>
+        <v>0.031</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="C27" t="n">
-        <v>0.045</v>
+        <v>0.002</v>
       </c>
       <c r="D27" t="n">
-        <v>0.033</v>
+        <v>0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.057</v>
+        <v>0.018</v>
       </c>
       <c r="F27" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="G27" t="n">
-        <v>0.098</v>
+        <v>0.025</v>
       </c>
       <c r="H27" t="n">
-        <v>0.097</v>
+        <v>0.022</v>
       </c>
       <c r="I27" t="n">
-        <v>0.022</v>
+        <v>0.008</v>
       </c>
       <c r="J27" t="n">
-        <v>0.317</v>
+        <v>0.079</v>
       </c>
       <c r="K27" t="n">
-        <v>0.115</v>
+        <v>0.021</v>
       </c>
       <c r="L27" t="n">
-        <v>0.159</v>
+        <v>0.042</v>
       </c>
       <c r="M27" t="n">
-        <v>0.111</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="28">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.053</v>
+        <v>0.018</v>
       </c>
       <c r="F28" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="G28" t="n">
-        <v>0.031</v>
+        <v>0.007</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.052</v>
+        <v>0.017</v>
       </c>
       <c r="F29" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="G29" t="n">
-        <v>0.048</v>
+        <v>0.014</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.002</v>
       </c>
-      <c r="I29" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.017</v>
-      </c>
       <c r="K29" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03</v>
+        <v>0.002</v>
       </c>
       <c r="M29" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02</v>
+        <v>0.007</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.289</v>
+        <v>82.55800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>144.547</v>
+        <v>68.876</v>
       </c>
       <c r="D2" t="n">
-        <v>199.349</v>
+        <v>130.078</v>
       </c>
       <c r="E2" t="n">
-        <v>250.146</v>
+        <v>233.056</v>
       </c>
       <c r="F2" t="n">
-        <v>109.167</v>
+        <v>106.766</v>
       </c>
       <c r="G2" t="n">
-        <v>164.082</v>
+        <v>149.325</v>
       </c>
       <c r="H2" t="n">
-        <v>170.619</v>
+        <v>83.10599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4</v>
+        <v>97.759</v>
       </c>
       <c r="J2" t="n">
-        <v>248.485</v>
+        <v>87.083</v>
       </c>
       <c r="K2" t="n">
-        <v>186.89</v>
+        <v>62.736</v>
       </c>
       <c r="L2" t="n">
-        <v>174.557</v>
+        <v>58.879</v>
       </c>
       <c r="M2" t="n">
-        <v>230.517</v>
+        <v>59.529</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.538</v>
+        <v>53.215</v>
       </c>
       <c r="C3" t="n">
-        <v>76.78400000000001</v>
+        <v>48.462</v>
       </c>
       <c r="D3" t="n">
-        <v>108.727</v>
+        <v>75.45699999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>220.451</v>
+        <v>217.978</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>86.02</v>
+        <v>79.178</v>
       </c>
       <c r="H3" t="n">
-        <v>136.496</v>
+        <v>29.12</v>
       </c>
       <c r="I3" t="n">
-        <v>135.516</v>
+        <v>32.289</v>
       </c>
       <c r="J3" t="n">
-        <v>108.492</v>
+        <v>17.858</v>
       </c>
       <c r="K3" t="n">
-        <v>138.241</v>
+        <v>19.38</v>
       </c>
       <c r="L3" t="n">
-        <v>127.499</v>
+        <v>24.407</v>
       </c>
       <c r="M3" t="n">
-        <v>78.70699999999999</v>
+        <v>14.292</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.016</v>
+        <v>30.296</v>
       </c>
       <c r="C4" t="n">
-        <v>27.104</v>
+        <v>22.142</v>
       </c>
       <c r="D4" t="n">
-        <v>49.399</v>
+        <v>44.219</v>
       </c>
       <c r="E4" t="n">
-        <v>200.76</v>
+        <v>197.439</v>
       </c>
       <c r="F4" t="n">
-        <v>74.05</v>
+        <v>73.631</v>
       </c>
       <c r="G4" t="n">
-        <v>65.21299999999999</v>
+        <v>61.09</v>
       </c>
       <c r="H4" t="n">
-        <v>9.351000000000001</v>
+        <v>1.941</v>
       </c>
       <c r="I4" t="n">
-        <v>5.348</v>
+        <v>5.146</v>
       </c>
       <c r="J4" t="n">
-        <v>15.704</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>28.691</v>
+        <v>6.277</v>
       </c>
       <c r="L4" t="n">
-        <v>8.858000000000001</v>
+        <v>3.213</v>
       </c>
       <c r="M4" t="n">
-        <v>12.6</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="5">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.895</v>
+        <v>18.813</v>
       </c>
       <c r="C5" t="n">
-        <v>6.652</v>
+        <v>5.454</v>
       </c>
       <c r="D5" t="n">
         <v>18.59</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.335</v>
+        <v>30.072</v>
       </c>
       <c r="C6" t="n">
-        <v>33.024</v>
+        <v>9.172000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>51.429</v>
+        <v>20.748</v>
       </c>
       <c r="E6" t="n">
-        <v>181.879</v>
+        <v>174.943</v>
       </c>
       <c r="F6" t="n">
-        <v>89.614</v>
+        <v>86.857</v>
       </c>
       <c r="G6" t="n">
-        <v>57.795</v>
+        <v>48.683</v>
       </c>
       <c r="H6" t="n">
-        <v>4.262</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>22.08</v>
+        <v>5.742</v>
       </c>
       <c r="J6" t="n">
-        <v>72.655</v>
+        <v>12.105</v>
       </c>
       <c r="K6" t="n">
-        <v>100.951</v>
+        <v>11.65</v>
       </c>
       <c r="L6" t="n">
-        <v>53.361</v>
+        <v>8.004</v>
       </c>
       <c r="M6" t="n">
-        <v>64.032</v>
+        <v>9.208</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.645</v>
+        <v>35.768</v>
       </c>
       <c r="C7" t="n">
-        <v>116.566</v>
+        <v>17.029</v>
       </c>
       <c r="D7" t="n">
-        <v>83.959</v>
+        <v>16.804</v>
       </c>
       <c r="E7" t="n">
-        <v>107.365</v>
+        <v>83.729</v>
       </c>
       <c r="F7" t="n">
-        <v>171.397</v>
+        <v>159.108</v>
       </c>
       <c r="G7" t="n">
-        <v>68.69799999999999</v>
+        <v>42.475</v>
       </c>
       <c r="H7" t="n">
-        <v>448.705</v>
+        <v>433.844</v>
       </c>
       <c r="I7" t="n">
-        <v>328.085</v>
+        <v>327.903</v>
       </c>
       <c r="J7" t="n">
-        <v>406.981</v>
+        <v>350.872</v>
       </c>
       <c r="K7" t="n">
-        <v>369.421</v>
+        <v>367.528</v>
       </c>
       <c r="L7" t="n">
-        <v>345.876</v>
+        <v>259.606</v>
       </c>
       <c r="M7" t="n">
-        <v>409.27</v>
+        <v>263.175</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.999000000000001</v>
+        <v>8.714</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7408,19 +7408,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.474</v>
+        <v>75.10899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>141.702</v>
+        <v>139.739</v>
       </c>
       <c r="G8" t="n">
-        <v>26.707</v>
+        <v>25.086</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.15</v>
+        <v>1.001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7442,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.174</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.329</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49.127</v>
+        <v>38.32</v>
       </c>
       <c r="F9" t="n">
-        <v>98.14100000000001</v>
+        <v>89.896</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37</v>
+        <v>4.764</v>
       </c>
       <c r="H9" t="n">
-        <v>9.68</v>
+        <v>4.508</v>
       </c>
       <c r="I9" t="n">
-        <v>29.345</v>
+        <v>11.693</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625</v>
+        <v>7.54</v>
       </c>
       <c r="K9" t="n">
-        <v>133.562</v>
+        <v>13.177</v>
       </c>
       <c r="L9" t="n">
-        <v>21.648</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7494,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>38.165</v>
+        <v>32.784</v>
       </c>
       <c r="F10" t="n">
-        <v>74.45</v>
+        <v>70.959</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11.198</v>
+        <v>6.068</v>
       </c>
       <c r="J10" t="n">
-        <v>7.096</v>
+        <v>2.512</v>
       </c>
       <c r="K10" t="n">
-        <v>5.148</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.843</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36.519</v>
+        <v>34.551</v>
       </c>
       <c r="F11" t="n">
-        <v>63.697</v>
+        <v>62.546</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.891</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.736</v>
+        <v>0.263</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7580,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.796</v>
+        <v>22.546</v>
       </c>
       <c r="F12" t="n">
-        <v>48.502</v>
+        <v>47.975</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.673999999999999</v>
+        <v>1.892</v>
       </c>
       <c r="F13" t="n">
-        <v>34.177</v>
+        <v>28.268</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7635,16 +7635,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3.807</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13.525</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>16.795</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7.407</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198.422</v>
+        <v>137.287</v>
       </c>
       <c r="C15" t="n">
-        <v>182.077</v>
+        <v>102.307</v>
       </c>
       <c r="D15" t="n">
-        <v>205.629</v>
+        <v>127.891</v>
       </c>
       <c r="E15" t="n">
-        <v>234.016</v>
+        <v>219.577</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>242.281</v>
+        <v>232.365</v>
       </c>
       <c r="H15" t="n">
-        <v>150.226</v>
+        <v>137.658</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>168.641</v>
+        <v>122.922</v>
       </c>
       <c r="K15" t="n">
-        <v>210.788</v>
+        <v>187.929</v>
       </c>
       <c r="L15" t="n">
-        <v>240.008</v>
+        <v>231.721</v>
       </c>
       <c r="M15" t="n">
-        <v>246.087</v>
+        <v>223.887</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.941</v>
+        <v>183.488</v>
       </c>
       <c r="C16" t="n">
-        <v>285.944</v>
+        <v>150.023</v>
       </c>
       <c r="D16" t="n">
-        <v>337.826</v>
+        <v>238.461</v>
       </c>
       <c r="E16" t="n">
-        <v>380.599</v>
+        <v>377.251</v>
       </c>
       <c r="F16" t="n">
-        <v>206.405</v>
+        <v>201.858</v>
       </c>
       <c r="G16" t="n">
         <v>437.584</v>
       </c>
       <c r="H16" t="n">
-        <v>361.504</v>
+        <v>332.719</v>
       </c>
       <c r="I16" t="n">
-        <v>171.377</v>
+        <v>145.556</v>
       </c>
       <c r="J16" t="n">
-        <v>429.552</v>
+        <v>406.512</v>
       </c>
       <c r="K16" t="n">
-        <v>376.299</v>
+        <v>334.722</v>
       </c>
       <c r="L16" t="n">
-        <v>369.467</v>
+        <v>344.066</v>
       </c>
       <c r="M16" t="n">
-        <v>383.219</v>
+        <v>360.896</v>
       </c>
     </row>
     <row r="17">
@@ -7784,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>190.162</v>
+        <v>125.077</v>
       </c>
       <c r="C17" t="n">
-        <v>176.974</v>
+        <v>112.356</v>
       </c>
       <c r="D17" t="n">
-        <v>287.615</v>
+        <v>228.485</v>
       </c>
       <c r="E17" t="n">
-        <v>418.938</v>
+        <v>416.187</v>
       </c>
       <c r="F17" t="n">
-        <v>178.899</v>
+        <v>177.486</v>
       </c>
       <c r="G17" t="n">
-        <v>328.324</v>
+        <v>323.78</v>
       </c>
       <c r="H17" t="n">
-        <v>334.933</v>
+        <v>247.612</v>
       </c>
       <c r="I17" t="n">
-        <v>122.944</v>
+        <v>88.39100000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>426.081</v>
+        <v>391.954</v>
       </c>
       <c r="K17" t="n">
-        <v>280.581</v>
+        <v>222.787</v>
       </c>
       <c r="L17" t="n">
-        <v>364.881</v>
+        <v>285.061</v>
       </c>
       <c r="M17" t="n">
-        <v>329.791</v>
+        <v>233.434</v>
       </c>
     </row>
     <row r="18">
@@ -7827,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.284</v>
+        <v>45.091</v>
       </c>
       <c r="C18" t="n">
-        <v>29.031</v>
+        <v>23.916</v>
       </c>
       <c r="D18" t="n">
-        <v>47.026</v>
+        <v>43.104</v>
       </c>
       <c r="E18" t="n">
-        <v>398.401</v>
+        <v>394.945</v>
       </c>
       <c r="F18" t="n">
-        <v>162.221</v>
+        <v>160.31</v>
       </c>
       <c r="G18" t="n">
-        <v>140.396</v>
+        <v>140.235</v>
       </c>
       <c r="H18" t="n">
-        <v>32.366</v>
+        <v>11.161</v>
       </c>
       <c r="I18" t="n">
-        <v>10.028</v>
+        <v>7.853</v>
       </c>
       <c r="J18" t="n">
-        <v>20.694</v>
+        <v>17.997</v>
       </c>
       <c r="K18" t="n">
-        <v>35.773</v>
+        <v>15.091</v>
       </c>
       <c r="L18" t="n">
-        <v>80.483</v>
+        <v>75.95</v>
       </c>
       <c r="M18" t="n">
-        <v>36.838</v>
+        <v>31.267</v>
       </c>
     </row>
     <row r="19">
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.853</v>
+        <v>20.448</v>
       </c>
       <c r="C19" t="n">
-        <v>10.437</v>
+        <v>6.977</v>
       </c>
       <c r="D19" t="n">
-        <v>29.286</v>
+        <v>26.126</v>
       </c>
       <c r="E19" t="n">
-        <v>385.916</v>
+        <v>383.979</v>
       </c>
       <c r="F19" t="n">
-        <v>154.628</v>
+        <v>154.366</v>
       </c>
       <c r="G19" t="n">
-        <v>122.902</v>
+        <v>121.046</v>
       </c>
       <c r="H19" t="n">
-        <v>3.76</v>
+        <v>0.65</v>
       </c>
       <c r="I19" t="n">
-        <v>3.267</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.56</v>
+        <v>1.539</v>
       </c>
       <c r="K19" t="n">
-        <v>7.721</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.242</v>
+        <v>8.343</v>
       </c>
       <c r="M19" t="n">
-        <v>7.12</v>
+        <v>3.769</v>
       </c>
     </row>
     <row r="20">
@@ -7940,7 +7940,7 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>70.63</v>
+        <v>37.744</v>
       </c>
       <c r="L20" t="n">
         <v>7.176</v>
@@ -7956,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151.843</v>
+        <v>111.631</v>
       </c>
       <c r="C21" t="n">
-        <v>155.286</v>
+        <v>115.156</v>
       </c>
       <c r="D21" t="n">
-        <v>44.554</v>
+        <v>24.665</v>
       </c>
       <c r="E21" t="n">
-        <v>211.495</v>
+        <v>206.255</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84699999999999</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>86.437</v>
+        <v>86.164</v>
       </c>
       <c r="H21" t="n">
-        <v>315.454</v>
+        <v>142.754</v>
       </c>
       <c r="I21" t="n">
-        <v>67.90000000000001</v>
+        <v>6.613</v>
       </c>
       <c r="J21" t="n">
-        <v>312.499</v>
+        <v>76.325</v>
       </c>
       <c r="K21" t="n">
-        <v>218.524</v>
+        <v>177.424</v>
       </c>
       <c r="L21" t="n">
-        <v>181.643</v>
+        <v>26.604</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285.401</v>
+        <v>186.79</v>
       </c>
       <c r="C22" t="n">
-        <v>308.21</v>
+        <v>195.41</v>
       </c>
       <c r="D22" t="n">
-        <v>213.229</v>
+        <v>92.122</v>
       </c>
       <c r="E22" t="n">
-        <v>235.775</v>
+        <v>208.171</v>
       </c>
       <c r="F22" t="n">
-        <v>93.426</v>
+        <v>78.798</v>
       </c>
       <c r="G22" t="n">
-        <v>102.116</v>
+        <v>76.247</v>
       </c>
       <c r="H22" t="n">
-        <v>351.305</v>
+        <v>348.007</v>
       </c>
       <c r="I22" t="n">
         <v>218.601</v>
       </c>
       <c r="J22" t="n">
-        <v>447.263</v>
+        <v>424.852</v>
       </c>
       <c r="K22" t="n">
-        <v>245.673</v>
+        <v>236.359</v>
       </c>
       <c r="L22" t="n">
-        <v>351.869</v>
+        <v>337.703</v>
       </c>
       <c r="M22" t="n">
-        <v>345.778</v>
+        <v>191.242</v>
       </c>
     </row>
     <row r="23">
@@ -8045,19 +8045,19 @@
         <v>68.547</v>
       </c>
       <c r="C23" t="n">
-        <v>30.674</v>
+        <v>19.376</v>
       </c>
       <c r="D23" t="n">
-        <v>31.352</v>
+        <v>18.182</v>
       </c>
       <c r="E23" t="n">
-        <v>24.121</v>
+        <v>22.371</v>
       </c>
       <c r="F23" t="n">
-        <v>9.519</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>119.489</v>
+        <v>104.572</v>
       </c>
       <c r="H23" t="n">
         <v>21.522</v>
@@ -8066,16 +8066,16 @@
         <v>26.488</v>
       </c>
       <c r="J23" t="n">
-        <v>56.446</v>
+        <v>41.032</v>
       </c>
       <c r="K23" t="n">
         <v>20.712</v>
       </c>
       <c r="L23" t="n">
-        <v>32.653</v>
+        <v>32.652</v>
       </c>
       <c r="M23" t="n">
-        <v>35.369</v>
+        <v>35.127</v>
       </c>
     </row>
     <row r="24">
@@ -8085,22 +8085,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.531</v>
+        <v>10.954</v>
       </c>
       <c r="C24" t="n">
-        <v>25.396</v>
+        <v>16.375</v>
       </c>
       <c r="D24" t="n">
-        <v>21.851</v>
+        <v>12.773</v>
       </c>
       <c r="E24" t="n">
-        <v>25.831</v>
+        <v>25.242</v>
       </c>
       <c r="F24" t="n">
-        <v>10.472</v>
+        <v>10.442</v>
       </c>
       <c r="G24" t="n">
-        <v>125.227</v>
+        <v>123.314</v>
       </c>
       <c r="H24" t="n">
         <v>20.425</v>
@@ -8109,7 +8109,7 @@
         <v>25.756</v>
       </c>
       <c r="J24" t="n">
-        <v>47.703</v>
+        <v>45.773</v>
       </c>
       <c r="K24" t="n">
         <v>20.024</v>
@@ -8128,40 +8128,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.563</v>
+        <v>12.981</v>
       </c>
       <c r="C25" t="n">
-        <v>17.647</v>
+        <v>12.953</v>
       </c>
       <c r="D25" t="n">
-        <v>14.358</v>
+        <v>9.634</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>12.027</v>
+        <v>12.001</v>
       </c>
       <c r="G25" t="n">
-        <v>86.818</v>
+        <v>72.93600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>19.045</v>
+        <v>18.957</v>
       </c>
       <c r="I25" t="n">
-        <v>11.804</v>
+        <v>4.237</v>
       </c>
       <c r="J25" t="n">
-        <v>25.778</v>
+        <v>22.559</v>
       </c>
       <c r="K25" t="n">
-        <v>23.603</v>
+        <v>16.936</v>
       </c>
       <c r="L25" t="n">
-        <v>27.658</v>
+        <v>16.135</v>
       </c>
       <c r="M25" t="n">
-        <v>18.936</v>
+        <v>7.419</v>
       </c>
     </row>
     <row r="26">
@@ -8174,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.235</v>
+        <v>11.094</v>
       </c>
       <c r="D26" t="n">
-        <v>4.172</v>
+        <v>3.837</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8186,22 +8186,22 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>96.301</v>
+        <v>94.541</v>
       </c>
       <c r="H26" t="n">
-        <v>1.428</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.551</v>
+        <v>0.706</v>
       </c>
       <c r="J26" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.274</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>6.246</v>
+        <v>0.322</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8214,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.634</v>
+        <v>12.649</v>
       </c>
       <c r="C27" t="n">
-        <v>31.771</v>
+        <v>13.973</v>
       </c>
       <c r="D27" t="n">
-        <v>27.277</v>
+        <v>11.88</v>
       </c>
       <c r="E27" t="n">
-        <v>24.271</v>
+        <v>22.689</v>
       </c>
       <c r="F27" t="n">
-        <v>12.223</v>
+        <v>11.417</v>
       </c>
       <c r="G27" t="n">
-        <v>109.659</v>
+        <v>89.908</v>
       </c>
       <c r="H27" t="n">
-        <v>33.252</v>
+        <v>32.159</v>
       </c>
       <c r="I27" t="n">
         <v>18.642</v>
       </c>
       <c r="J27" t="n">
-        <v>58.309</v>
+        <v>56.969</v>
       </c>
       <c r="K27" t="n">
-        <v>37.326</v>
+        <v>36.332</v>
       </c>
       <c r="L27" t="n">
-        <v>43.613</v>
+        <v>43.193</v>
       </c>
       <c r="M27" t="n">
-        <v>36.754</v>
+        <v>34.777</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.559</v>
+        <v>2.543</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,7 +8272,7 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>61.175</v>
+        <v>51.413</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -8300,40 +8300,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.367</v>
+        <v>2.112</v>
       </c>
       <c r="C29" t="n">
-        <v>5.664</v>
+        <v>1.371</v>
       </c>
       <c r="D29" t="n">
-        <v>3.613</v>
+        <v>0.36</v>
       </c>
       <c r="E29" t="n">
-        <v>22.205</v>
+        <v>21.824</v>
       </c>
       <c r="F29" t="n">
-        <v>10.799</v>
+        <v>10.523</v>
       </c>
       <c r="G29" t="n">
-        <v>71.66200000000001</v>
+        <v>65.325</v>
       </c>
       <c r="H29" t="n">
-        <v>5.992</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>7.339</v>
+        <v>1.949</v>
       </c>
       <c r="J29" t="n">
-        <v>16.438</v>
+        <v>14.104</v>
       </c>
       <c r="K29" t="n">
-        <v>11.718</v>
+        <v>6.626</v>
       </c>
       <c r="L29" t="n">
-        <v>21.617</v>
+        <v>13.898</v>
       </c>
       <c r="M29" t="n">
-        <v>5.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9401425521e-05</v>
+        <v>6.815823364000001e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0893835209e-05</v>
+        <v>4.743903376000001e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9740023801e-05</v>
+        <v>1.6920286084e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2573021316e-05</v>
+        <v>5.431509913600001e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1917433889e-05</v>
+        <v>1.1398978756e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6922902724e-05</v>
+        <v>2.229795562499999e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9110843161e-05</v>
+        <v>6.906607236e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857296000000001e-05</v>
+        <v>9.556822080999999e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1744795225e-05</v>
+        <v>7.583448888999999e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.49278721e-05</v>
+        <v>3.935805696e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0470146249e-05</v>
+        <v>3.466736641e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3138087289e-05</v>
+        <v>3.543701841000001e-06</v>
       </c>
     </row>
     <row r="3">
@@ -8510,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.555913443999999e-06</v>
+        <v>2.831836225000001e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.895782656e-06</v>
+        <v>2.348565444e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1821560529e-05</v>
+        <v>5.693758849e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8598643401e-05</v>
+        <v>4.7514408484e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3994404e-06</v>
+        <v>6.269155684e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8631158016e-05</v>
+        <v>8.479744e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8364586256e-05</v>
+        <v>1.042579521e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1770514064e-05</v>
+        <v>3.189081639999999e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9110574081e-05</v>
+        <v>3.755843999999999e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6255995001e-05</v>
+        <v>5.95701649e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>6.194791848999999e-06</v>
+        <v>2.04261264e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.445216256e-06</v>
+        <v>9.17847616e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.346268159999999e-07</v>
+        <v>4.90268164e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.440261201e-06</v>
+        <v>1.955319961e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.030457759999999e-05</v>
+        <v>3.8982158721e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.483402499999999e-06</v>
+        <v>5.421524161e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.252735369e-06</v>
+        <v>3.731988100000001e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.744120100000002e-08</v>
+        <v>3.767481e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>2.860110399999999e-08</v>
+        <v>2.648131599999999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.46615616e-07</v>
+        <v>1.156e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.231734809999998e-07</v>
+        <v>3.940072900000001e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.846416400000002e-08</v>
+        <v>1.0323369e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5876e-07</v>
+        <v>1.0640644e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95811025e-07</v>
+        <v>3.53928969e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4249104e-08</v>
+        <v>2.9746116e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.455880999999999e-07</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011322225000001e-06</v>
+        <v>9.043251839999999e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.090584576e-06</v>
+        <v>8.412558400000002e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644942041e-06</v>
+        <v>4.304795040000001e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3079970641e-05</v>
+        <v>3.060505324900001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.030668996000001e-06</v>
+        <v>7.544138449000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.340262025e-06</v>
+        <v>2.370034489e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816464399999999e-08</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875263999999999e-07</v>
+        <v>3.297056399999999e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.278749024999999e-06</v>
+        <v>1.46531025e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0191104401e-05</v>
+        <v>1.357225e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.847396321e-06</v>
+        <v>6.406401599999998e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.100097023999998e-06</v>
+        <v>8.478726400000002e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8680,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.080772008333333e-06</v>
+        <v>4.264499413333334e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>4.529210785333334e-06</v>
+        <v>9.666228033333332e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349704560333334e-06</v>
+        <v>9.412480533333332e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.842414408333332e-06</v>
+        <v>2.336848480333333e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792310536333332e-06</v>
+        <v>8.438451887999999e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.573138401333333e-06</v>
+        <v>6.013752083333332e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.711205900833333e-05</v>
+        <v>6.274020544533334e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.587992240833332e-05</v>
+        <v>3.5840125803e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.521117812033333e-05</v>
+        <v>4.103705346133334e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.549062508033333e-05</v>
+        <v>4.502561026133334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.987673579199999e-05</v>
+        <v>2.246509174533333e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.583397763333333e-05</v>
+        <v>2.3087026875e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.098200100000001e-08</v>
+        <v>7.593379600000002e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8732,19 +8732,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.696324676e-06</v>
+        <v>5.641361881e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0079456804e-05</v>
+        <v>1.9526988121e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.132638490000001e-07</v>
+        <v>6.293073959999999e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.622500000000001e-09</v>
+        <v>1.002001e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.356634253333333e-07</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.608033333333334e-11</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6.120408333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.044873763333334e-07</v>
+        <v>4.894741333333333e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210551960333334e-06</v>
+        <v>2.693763605333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>5.100563333333332e-08</v>
+        <v>7.565232e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>3.123413333333333e-08</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>2.870430083333333e-07</v>
+        <v>4.557541633333334e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.283802083333333e-07</v>
+        <v>1.895053333333333e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.946269281333335e-06</v>
+        <v>5.787777633333332e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56211968e-07</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1047683e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.855224083333332e-07</v>
+        <v>3.582635520000001e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847600833333333e-06</v>
+        <v>1.678393227e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.136333333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.301333333333332e-10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.179840133333333e-08</v>
+        <v>1.227354133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.678440533333333e-08</v>
+        <v>2.103381333333333e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>8.833968e-09</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.694216333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8861,22 +8861,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.445457869999999e-07</v>
+        <v>3.979238670000001e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352435936333333e-06</v>
+        <v>1.304000705333334e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93548e-10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.785960333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652565333333334e-09</v>
+        <v>2.305633333333334e-11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.732192053333333e-07</v>
+        <v>1.694407053333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.841480013333335e-07</v>
+        <v>7.672002083333336e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.507942533333333e-08</v>
+        <v>1.193221333333333e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>3.893557763333333e-07</v>
+        <v>2.663599413333334e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8959,16 +8959,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.831083e-09</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6.097520833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>9.402400833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8287883e-08</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9371290084e-05</v>
+        <v>1.8847720369e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3152033929e-05</v>
+        <v>1.0466722249e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.228328564099999e-05</v>
+        <v>1.6356107881e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4763488256e-05</v>
+        <v>4.8214058929e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8700082961e-05</v>
+        <v>5.399349322500001e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2567851076e-05</v>
+        <v>1.894972496399999e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.843978688099999e-05</v>
+        <v>1.5109818084e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4431580944e-05</v>
+        <v>3.531730904100001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7603840064e-05</v>
+        <v>5.3694621841e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0558811569e-05</v>
+        <v>5.0125388769e-05</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6874163827e-05</v>
+        <v>1.122261538133334e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>2.725465704533334e-05</v>
+        <v>7.502300176333332e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>3.804213542533334e-05</v>
+        <v>1.8954549507e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.828519960033332e-05</v>
+        <v>4.743943900033334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.420100800833334e-05</v>
+        <v>1.3582217388e-05</v>
       </c>
       <c r="G16" t="n">
         <v>6.382658568533334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.356171400533333e-05</v>
+        <v>3.690064432033333e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>9.790025376333333e-06</v>
+        <v>7.062183045333335e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>6.150497356800002e-05</v>
+        <v>5.5084002048e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7200312467e-05</v>
+        <v>3.734627242799999e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.550195469633334e-05</v>
+        <v>3.946047078533333e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.895226732033333e-05</v>
+        <v>4.341530760533333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -9108,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.205386208133333e-05</v>
+        <v>5.214751976333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>1.043993222533333e-05</v>
+        <v>4.207956912e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>2.757412940833333e-05</v>
+        <v>1.740179840833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.850301594799999e-05</v>
+        <v>5.773720632300001e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0668284067e-05</v>
+        <v>1.0500426732e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.593221632533333e-05</v>
+        <v>3.494449613333332e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.739337149633333e-05</v>
+        <v>2.043723418133333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>5.038409045333333e-06</v>
+        <v>2.604322960333334e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>6.051500618700001e-05</v>
+        <v>5.120931270533334e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6241899187e-05</v>
+        <v>1.654468245633333e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4.437938138699999e-05</v>
+        <v>2.708659124033332e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.625403456033334e-05</v>
+        <v>1.816381078533333e-05</v>
       </c>
     </row>
     <row r="18">
@@ -9151,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.09637552e-07</v>
+        <v>6.777327603333333e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>2.80932987e-07</v>
+        <v>1.90658352e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.371482253333335e-07</v>
+        <v>6.193182719999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.290778560033334e-05</v>
+        <v>5.199385100833333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.771884280333334e-06</v>
+        <v>8.566432033333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.570345605333333e-06</v>
+        <v>6.555285075000002e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>3.491859853333333e-07</v>
+        <v>4.152264033333332e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>3.352026133333334e-08</v>
+        <v>2.055653633333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.42747212e-07</v>
+        <v>1.07964003e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>4.265691763333335e-07</v>
+        <v>7.591276033333333e-08</v>
       </c>
       <c r="L18" t="n">
-        <v>2.159171096333333e-06</v>
+        <v>1.922800833333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>4.523460813333334e-07</v>
+        <v>3.258750963333332e-07</v>
       </c>
     </row>
     <row r="19">
@@ -9194,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.89655203e-07</v>
+        <v>1.39373568e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6310323e-08</v>
+        <v>1.622617633333334e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85889932e-07</v>
+        <v>2.275226253333333e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.964371968533333e-05</v>
+        <v>4.914662414699999e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.969939461333333e-06</v>
+        <v>7.942953985333334e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.034967201333333e-06</v>
+        <v>4.884044705333334e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>4.712533333333333e-09</v>
+        <v>1.408333333333333e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>3.557763e-09</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.224533333333334e-09</v>
+        <v>7.895070000000001e-10</v>
       </c>
       <c r="K19" t="n">
-        <v>1.987128033333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4966188e-08</v>
+        <v>2.3201883e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>1.689813333333334e-08</v>
+        <v>4.735120333333334e-09</v>
       </c>
     </row>
     <row r="20">
@@ -9264,7 +9264,7 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>1.662865633333333e-06</v>
+        <v>4.748698453333333e-07</v>
       </c>
       <c r="L20" t="n">
         <v>1.7164992e-08</v>
@@ -9280,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.685432216333331e-06</v>
+        <v>4.153826720333333e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.037913932000002e-06</v>
+        <v>4.420301445333334e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>6.616863053333334e-07</v>
+        <v>2.027874083333333e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491004500833333e-05</v>
+        <v>1.418037500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399671136333333e-06</v>
+        <v>2.367256661333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.490451656333333e-06</v>
+        <v>2.474744965333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317040870533334e-05</v>
+        <v>6.792901505333333e-06</v>
       </c>
       <c r="I21" t="n">
-        <v>1.536803333333333e-06</v>
+        <v>1.457725633333334e-08</v>
       </c>
       <c r="J21" t="n">
-        <v>3.255187500033334e-05</v>
+        <v>1.941835208333333e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>1.591757952533333e-05</v>
+        <v>1.049309192533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.099805981633333e-05</v>
+        <v>2.35924272e-07</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.715124360033333e-05</v>
+        <v>1.163016803333333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.166446803333333e-05</v>
+        <v>1.272835603333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.515553548033333e-05</v>
+        <v>2.828820961333333e-06</v>
       </c>
       <c r="E22" t="n">
-        <v>1.852995020833333e-05</v>
+        <v>1.444505508033333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.909472492e-06</v>
+        <v>2.069708268e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>3.475892485333333e-06</v>
+        <v>1.937868336333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.113840100833334e-05</v>
+        <v>4.036962401633334e-05</v>
       </c>
       <c r="I22" t="n">
         <v>1.5928799067e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>6.668139705633332e-05</v>
+        <v>6.016640730133331e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0118407643e-05</v>
+        <v>1.862185896033334e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.127059772033335e-05</v>
+        <v>3.801443873633333e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.985414176133334e-05</v>
+        <v>1.219116752133333e-05</v>
       </c>
     </row>
     <row r="23">
@@ -9369,19 +9369,19 @@
         <v>4.698691208999999e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>9.408942760000001e-06</v>
+        <v>3.75429376e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82947904e-06</v>
+        <v>3.30585124e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>5.81822641e-06</v>
+        <v>5.00461641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.0611361e-07</v>
+        <v>8.184820900000002e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4277621121e-05</v>
+        <v>1.0935303184e-05</v>
       </c>
       <c r="H23" t="n">
         <v>4.63196484e-06</v>
@@ -9390,16 +9390,16 @@
         <v>7.016141440000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>3.186150915999999e-05</v>
+        <v>1.683625024e-05</v>
       </c>
       <c r="K23" t="n">
         <v>4.28986944e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066218409e-05</v>
+        <v>1.066153104e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>1.250966161e-05</v>
+        <v>1.233906129000001e-05</v>
       </c>
     </row>
     <row r="24">
@@ -9409,22 +9409,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.41211961e-06</v>
+        <v>1.19990116e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>6.449568160000001e-06</v>
+        <v>2.68140625e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>4.774662009999999e-06</v>
+        <v>1.63149529e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.67240561e-06</v>
+        <v>6.37158564e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09662784e-06</v>
+        <v>1.09035364e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5681801529e-05</v>
+        <v>1.5206342596e-05</v>
       </c>
       <c r="H24" t="n">
         <v>4.171806250000001e-06</v>
@@ -9433,7 +9433,7 @@
         <v>6.633715360000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.275576209e-05</v>
+        <v>2.095167529e-05</v>
       </c>
       <c r="K24" t="n">
         <v>4.00960576e-06</v>
@@ -9452,40 +9452,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.83954969e-06</v>
+        <v>1.68506361e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.11416609e-06</v>
+        <v>1.67780209e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.06152164e-06</v>
+        <v>9.281395600000001e-07</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44648729e-06</v>
+        <v>1.44024001e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>7.537365123999998e-06</v>
+        <v>5.319660096e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.627120250000001e-06</v>
+        <v>3.593678490000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.39334416e-06</v>
+        <v>1.7952169e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>6.645052839999999e-06</v>
+        <v>5.089084810000001e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>5.571016090000001e-06</v>
+        <v>2.86828096e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>7.64964964e-06</v>
+        <v>2.60338225e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>3.58572096e-06</v>
+        <v>5.504156099999999e-07</v>
       </c>
     </row>
     <row r="26">
@@ -9498,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26225225e-06</v>
+        <v>1.23076836e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7405584e-07</v>
+        <v>1.4722569e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9510,22 +9510,22 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.273882601e-06</v>
+        <v>8.938000681e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>2.039184e-08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.405601e-08</v>
+        <v>4.984359999999999e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>9.35089e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.623076e-08</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3.901251600000001e-07</v>
+        <v>1.03684e-09</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9538,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.680299560000001e-06</v>
+        <v>1.59997201e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.009396441e-05</v>
+        <v>1.95244729e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>7.440347290000001e-06</v>
+        <v>1.411344e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>5.890814410000001e-06</v>
+        <v>5.147907210000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49401729e-06</v>
+        <v>1.30347889e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2025096281e-05</v>
+        <v>8.083448463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>1.105695504e-05</v>
+        <v>1.034201281e-05</v>
       </c>
       <c r="I27" t="n">
         <v>3.47524164e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.399939481e-05</v>
+        <v>3.245466961e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.393230276e-05</v>
+        <v>1.320014224e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.902093769e-05</v>
+        <v>1.865635249e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.350856516e-05</v>
+        <v>1.209439729e-05</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.548481000000001e-08</v>
+        <v>6.466849e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,7 +9596,7 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>3.742380625e-06</v>
+        <v>2.643296568999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -9624,40 +9624,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9070689e-07</v>
+        <v>4.460544e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2080896e-07</v>
+        <v>1.879641e-08</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3053769e-07</v>
+        <v>1.296e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>4.930620249999999e-06</v>
+        <v>4.762869760000001e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16618401e-06</v>
+        <v>1.10733529e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.135442244e-06</v>
+        <v>4.267355625000001e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5904064e-07</v>
+        <v>6.577210000000002e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>5.3860921e-07</v>
+        <v>3.798601e-08</v>
       </c>
       <c r="J29" t="n">
-        <v>2.70207844e-06</v>
+        <v>1.98922816e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>1.37311524e-06</v>
+        <v>4.3903876e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>4.67294689e-06</v>
+        <v>1.93154404e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>2.946318399999999e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.289</v>
+        <v>82.55800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>144.547</v>
+        <v>68.876</v>
       </c>
       <c r="D2" t="n">
-        <v>199.349</v>
+        <v>130.078</v>
       </c>
       <c r="E2" t="n">
-        <v>250.146</v>
+        <v>233.056</v>
       </c>
       <c r="F2" t="n">
-        <v>109.167</v>
+        <v>106.766</v>
       </c>
       <c r="G2" t="n">
-        <v>164.082</v>
+        <v>149.325</v>
       </c>
       <c r="H2" t="n">
-        <v>170.619</v>
+        <v>83.10599999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4</v>
+        <v>97.759</v>
       </c>
       <c r="J2" t="n">
-        <v>248.469</v>
+        <v>87.083</v>
       </c>
       <c r="K2" t="n">
-        <v>186.89</v>
+        <v>62.736</v>
       </c>
       <c r="L2" t="n">
-        <v>174.557</v>
+        <v>58.879</v>
       </c>
       <c r="M2" t="n">
-        <v>230.517</v>
+        <v>59.529</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.538</v>
+        <v>53.215</v>
       </c>
       <c r="C3" t="n">
-        <v>76.78400000000001</v>
+        <v>48.462</v>
       </c>
       <c r="D3" t="n">
-        <v>108.727</v>
+        <v>75.45699999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>220.451</v>
+        <v>216.43</v>
       </c>
       <c r="F3" t="n">
-        <v>76.491</v>
+        <v>75.63</v>
       </c>
       <c r="G3" t="n">
-        <v>86.02</v>
+        <v>79.178</v>
       </c>
       <c r="H3" t="n">
-        <v>136.496</v>
+        <v>29.12</v>
       </c>
       <c r="I3" t="n">
-        <v>135.516</v>
+        <v>32.289</v>
       </c>
       <c r="J3" t="n">
-        <v>108.463</v>
+        <v>17.858</v>
       </c>
       <c r="K3" t="n">
-        <v>138.241</v>
+        <v>19.38</v>
       </c>
       <c r="L3" t="n">
-        <v>127.499</v>
+        <v>24.407</v>
       </c>
       <c r="M3" t="n">
-        <v>78.70699999999999</v>
+        <v>14.292</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.016</v>
+        <v>30.296</v>
       </c>
       <c r="C4" t="n">
-        <v>27.104</v>
+        <v>22.142</v>
       </c>
       <c r="D4" t="n">
-        <v>49.399</v>
+        <v>44.219</v>
       </c>
       <c r="E4" t="n">
-        <v>200.76</v>
+        <v>197.439</v>
       </c>
       <c r="F4" t="n">
-        <v>74.05</v>
+        <v>73.593</v>
       </c>
       <c r="G4" t="n">
-        <v>65.21299999999999</v>
+        <v>61.09</v>
       </c>
       <c r="H4" t="n">
-        <v>9.351000000000001</v>
+        <v>1.941</v>
       </c>
       <c r="I4" t="n">
-        <v>3.563</v>
+        <v>5.134</v>
       </c>
       <c r="J4" t="n">
-        <v>15.704</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>28.691</v>
+        <v>6.277</v>
       </c>
       <c r="L4" t="n">
-        <v>8.858000000000001</v>
+        <v>3.213</v>
       </c>
       <c r="M4" t="n">
-        <v>12.6</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.895</v>
+        <v>18.813</v>
       </c>
       <c r="C5" t="n">
-        <v>6.652</v>
+        <v>5.273</v>
       </c>
       <c r="D5" t="n">
-        <v>18.554</v>
+        <v>18.073</v>
       </c>
       <c r="E5" t="n">
-        <v>195.073</v>
+        <v>195.367</v>
       </c>
       <c r="F5" t="n">
-        <v>93.86199999999999</v>
+        <v>94.544</v>
       </c>
       <c r="G5" t="n">
-        <v>76.872</v>
+        <v>78.178</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.335</v>
+        <v>30.072</v>
       </c>
       <c r="C6" t="n">
-        <v>33.024</v>
+        <v>9.172000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>51.429</v>
+        <v>20.748</v>
       </c>
       <c r="E6" t="n">
-        <v>181.879</v>
+        <v>174.943</v>
       </c>
       <c r="F6" t="n">
-        <v>89.614</v>
+        <v>86.857</v>
       </c>
       <c r="G6" t="n">
-        <v>57.795</v>
+        <v>48.683</v>
       </c>
       <c r="H6" t="n">
-        <v>4.262</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>22.08</v>
+        <v>5.742</v>
       </c>
       <c r="J6" t="n">
-        <v>72.655</v>
+        <v>12.105</v>
       </c>
       <c r="K6" t="n">
-        <v>100.951</v>
+        <v>11.65</v>
       </c>
       <c r="L6" t="n">
-        <v>53.361</v>
+        <v>8.004</v>
       </c>
       <c r="M6" t="n">
-        <v>64.032</v>
+        <v>9.208</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.645</v>
+        <v>35.768</v>
       </c>
       <c r="C7" t="n">
-        <v>116.566</v>
+        <v>17.029</v>
       </c>
       <c r="D7" t="n">
-        <v>83.959</v>
+        <v>16.804</v>
       </c>
       <c r="E7" t="n">
-        <v>107.365</v>
+        <v>83.729</v>
       </c>
       <c r="F7" t="n">
-        <v>171.397</v>
+        <v>159.108</v>
       </c>
       <c r="G7" t="n">
-        <v>68.69799999999999</v>
+        <v>42.475</v>
       </c>
       <c r="H7" t="n">
-        <v>444.155</v>
+        <v>433.7</v>
       </c>
       <c r="I7" t="n">
-        <v>322.767</v>
+        <v>327.903</v>
       </c>
       <c r="J7" t="n">
-        <v>374.397</v>
+        <v>350.872</v>
       </c>
       <c r="K7" t="n">
-        <v>365.191</v>
+        <v>367.528</v>
       </c>
       <c r="L7" t="n">
-        <v>341.074</v>
+        <v>259.606</v>
       </c>
       <c r="M7" t="n">
-        <v>408.096</v>
+        <v>263.175</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.999000000000001</v>
+        <v>8.714</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.462</v>
+        <v>75.10899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>141.702</v>
+        <v>139.739</v>
       </c>
       <c r="G8" t="n">
-        <v>26.707</v>
+        <v>25.086</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.796</v>
+        <v>1.001</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>62.415</v>
+        <v>83.087</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10090,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.174</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.329</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49.127</v>
+        <v>38.32</v>
       </c>
       <c r="F9" t="n">
-        <v>98.14100000000001</v>
+        <v>89.896</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37</v>
+        <v>4.764</v>
       </c>
       <c r="H9" t="n">
-        <v>9.68</v>
+        <v>4.508</v>
       </c>
       <c r="I9" t="n">
-        <v>29.345</v>
+        <v>11.693</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625</v>
+        <v>7.54</v>
       </c>
       <c r="K9" t="n">
-        <v>133.562</v>
+        <v>13.177</v>
       </c>
       <c r="L9" t="n">
-        <v>21.648</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>38.165</v>
+        <v>32.784</v>
       </c>
       <c r="F10" t="n">
-        <v>74.45</v>
+        <v>70.959</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.476</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10.515</v>
+        <v>6.068</v>
       </c>
       <c r="J10" t="n">
-        <v>7.096</v>
+        <v>2.512</v>
       </c>
       <c r="K10" t="n">
-        <v>5.148</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.843</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -10185,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36.519</v>
+        <v>34.551</v>
       </c>
       <c r="F11" t="n">
-        <v>63.697</v>
+        <v>62.546</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.891</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.736</v>
+        <v>0.263</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.796</v>
+        <v>22.383</v>
       </c>
       <c r="F12" t="n">
-        <v>48.502</v>
+        <v>47.975</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10271,10 +10271,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.673999999999999</v>
+        <v>1.892</v>
       </c>
       <c r="F13" t="n">
-        <v>34.177</v>
+        <v>28.268</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3.807</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13.525</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>16.795</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7.407</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198.422</v>
+        <v>137.287</v>
       </c>
       <c r="C15" t="n">
-        <v>182.077</v>
+        <v>102.307</v>
       </c>
       <c r="D15" t="n">
-        <v>205.629</v>
+        <v>127.891</v>
       </c>
       <c r="E15" t="n">
-        <v>234.016</v>
+        <v>219.577</v>
       </c>
       <c r="F15" t="n">
-        <v>98.13800000000001</v>
+        <v>97.423</v>
       </c>
       <c r="G15" t="n">
-        <v>242.281</v>
+        <v>232.365</v>
       </c>
       <c r="H15" t="n">
-        <v>144.372</v>
+        <v>137.658</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>168.641</v>
+        <v>122.922</v>
       </c>
       <c r="K15" t="n">
-        <v>210.788</v>
+        <v>187.929</v>
       </c>
       <c r="L15" t="n">
-        <v>240.008</v>
+        <v>231.721</v>
       </c>
       <c r="M15" t="n">
-        <v>246.087</v>
+        <v>223.887</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.941</v>
+        <v>183.488</v>
       </c>
       <c r="C16" t="n">
-        <v>285.944</v>
+        <v>150.023</v>
       </c>
       <c r="D16" t="n">
-        <v>337.826</v>
+        <v>238.461</v>
       </c>
       <c r="E16" t="n">
-        <v>380.599</v>
+        <v>371.992</v>
       </c>
       <c r="F16" t="n">
-        <v>206.405</v>
+        <v>201.858</v>
       </c>
       <c r="G16" t="n">
-        <v>424.195</v>
+        <v>418.489</v>
       </c>
       <c r="H16" t="n">
-        <v>356.476</v>
+        <v>332.095</v>
       </c>
       <c r="I16" t="n">
-        <v>160.309</v>
+        <v>145.556</v>
       </c>
       <c r="J16" t="n">
-        <v>422.299</v>
+        <v>403.494</v>
       </c>
       <c r="K16" t="n">
-        <v>376.299</v>
+        <v>334.722</v>
       </c>
       <c r="L16" t="n">
-        <v>369.467</v>
+        <v>344.066</v>
       </c>
       <c r="M16" t="n">
-        <v>383.219</v>
+        <v>360.896</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>190.162</v>
+        <v>125.077</v>
       </c>
       <c r="C17" t="n">
-        <v>176.974</v>
+        <v>112.356</v>
       </c>
       <c r="D17" t="n">
-        <v>287.615</v>
+        <v>228.485</v>
       </c>
       <c r="E17" t="n">
-        <v>418.938</v>
+        <v>415.616</v>
       </c>
       <c r="F17" t="n">
-        <v>178.14</v>
+        <v>176.782</v>
       </c>
       <c r="G17" t="n">
-        <v>328.324</v>
+        <v>323.78</v>
       </c>
       <c r="H17" t="n">
-        <v>334.933</v>
+        <v>247.612</v>
       </c>
       <c r="I17" t="n">
-        <v>122.944</v>
+        <v>88.39100000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>421.894</v>
+        <v>391.954</v>
       </c>
       <c r="K17" t="n">
-        <v>280.581</v>
+        <v>222.787</v>
       </c>
       <c r="L17" t="n">
-        <v>364.881</v>
+        <v>285.061</v>
       </c>
       <c r="M17" t="n">
-        <v>329.791</v>
+        <v>233.434</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.284</v>
+        <v>45.091</v>
       </c>
       <c r="C18" t="n">
-        <v>29.031</v>
+        <v>23.916</v>
       </c>
       <c r="D18" t="n">
-        <v>47.026</v>
+        <v>43.104</v>
       </c>
       <c r="E18" t="n">
-        <v>398.401</v>
+        <v>394.945</v>
       </c>
       <c r="F18" t="n">
-        <v>162.221</v>
+        <v>160.31</v>
       </c>
       <c r="G18" t="n">
-        <v>140.396</v>
+        <v>139.786</v>
       </c>
       <c r="H18" t="n">
-        <v>29.584</v>
+        <v>11.161</v>
       </c>
       <c r="I18" t="n">
-        <v>8.759</v>
+        <v>7.853</v>
       </c>
       <c r="J18" t="n">
-        <v>18.803</v>
+        <v>17.997</v>
       </c>
       <c r="K18" t="n">
-        <v>32.529</v>
+        <v>15.091</v>
       </c>
       <c r="L18" t="n">
-        <v>52.306</v>
+        <v>75.95</v>
       </c>
       <c r="M18" t="n">
-        <v>27.016</v>
+        <v>31.267</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.853</v>
+        <v>20.448</v>
       </c>
       <c r="C19" t="n">
-        <v>10.437</v>
+        <v>6.977</v>
       </c>
       <c r="D19" t="n">
-        <v>29.286</v>
+        <v>26.126</v>
       </c>
       <c r="E19" t="n">
-        <v>385.916</v>
+        <v>383.979</v>
       </c>
       <c r="F19" t="n">
-        <v>153.59</v>
+        <v>154.366</v>
       </c>
       <c r="G19" t="n">
-        <v>122.902</v>
+        <v>121.046</v>
       </c>
       <c r="H19" t="n">
-        <v>3.177</v>
+        <v>0.65</v>
       </c>
       <c r="I19" t="n">
-        <v>3.101</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.914</v>
+        <v>1.539</v>
       </c>
       <c r="K19" t="n">
-        <v>6.987</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.497</v>
+        <v>8.343</v>
       </c>
       <c r="M19" t="n">
-        <v>4.883</v>
+        <v>3.769</v>
       </c>
     </row>
     <row r="20">
@@ -10561,37 +10561,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>120.83</v>
+        <v>129.122</v>
       </c>
       <c r="C20" t="n">
-        <v>124.046</v>
+        <v>132.856</v>
       </c>
       <c r="D20" t="n">
-        <v>35.092</v>
+        <v>42.401</v>
       </c>
       <c r="E20" t="n">
-        <v>219.31</v>
+        <v>222.514</v>
       </c>
       <c r="F20" t="n">
-        <v>95.608</v>
+        <v>98.078</v>
       </c>
       <c r="G20" t="n">
-        <v>112.855</v>
+        <v>120.385</v>
       </c>
       <c r="H20" t="n">
-        <v>42.608</v>
+        <v>15.514</v>
       </c>
       <c r="I20" t="n">
-        <v>3.029</v>
+        <v>3.692</v>
       </c>
       <c r="J20" t="n">
-        <v>2.275</v>
+        <v>3.644</v>
       </c>
       <c r="K20" t="n">
-        <v>70.63</v>
+        <v>37.744</v>
       </c>
       <c r="L20" t="n">
-        <v>3.369</v>
+        <v>6.086</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151.843</v>
+        <v>111.631</v>
       </c>
       <c r="C21" t="n">
-        <v>155.286</v>
+        <v>115.156</v>
       </c>
       <c r="D21" t="n">
-        <v>44.554</v>
+        <v>24.665</v>
       </c>
       <c r="E21" t="n">
-        <v>211.495</v>
+        <v>206.255</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84699999999999</v>
+        <v>84.27200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>86.437</v>
+        <v>85.378</v>
       </c>
       <c r="H21" t="n">
-        <v>315.454</v>
+        <v>142.754</v>
       </c>
       <c r="I21" t="n">
-        <v>67.90000000000001</v>
+        <v>6.612</v>
       </c>
       <c r="J21" t="n">
-        <v>282.613</v>
+        <v>76.325</v>
       </c>
       <c r="K21" t="n">
-        <v>217.762</v>
+        <v>177.424</v>
       </c>
       <c r="L21" t="n">
-        <v>181.643</v>
+        <v>26.604</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285.401</v>
+        <v>186.79</v>
       </c>
       <c r="C22" t="n">
-        <v>308.21</v>
+        <v>195.41</v>
       </c>
       <c r="D22" t="n">
-        <v>213.229</v>
+        <v>92.122</v>
       </c>
       <c r="E22" t="n">
-        <v>235.775</v>
+        <v>208.171</v>
       </c>
       <c r="F22" t="n">
-        <v>93.426</v>
+        <v>78.798</v>
       </c>
       <c r="G22" t="n">
-        <v>102.116</v>
+        <v>76.247</v>
       </c>
       <c r="H22" t="n">
-        <v>337.765</v>
+        <v>348.007</v>
       </c>
       <c r="I22" t="n">
-        <v>194.998</v>
+        <v>206.965</v>
       </c>
       <c r="J22" t="n">
-        <v>436.149</v>
+        <v>422.406</v>
       </c>
       <c r="K22" t="n">
-        <v>245.437</v>
+        <v>236.359</v>
       </c>
       <c r="L22" t="n">
-        <v>351.869</v>
+        <v>337.703</v>
       </c>
       <c r="M22" t="n">
-        <v>345.778</v>
+        <v>191.242</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.674</v>
+        <v>13.768</v>
       </c>
       <c r="C23" t="n">
-        <v>30.674</v>
+        <v>19.376</v>
       </c>
       <c r="D23" t="n">
-        <v>31.352</v>
+        <v>18.182</v>
       </c>
       <c r="E23" t="n">
-        <v>24.121</v>
+        <v>22.222</v>
       </c>
       <c r="F23" t="n">
-        <v>9.516999999999999</v>
+        <v>9.047000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>119.489</v>
+        <v>104.572</v>
       </c>
       <c r="H23" t="n">
-        <v>17.539</v>
+        <v>20.744</v>
       </c>
       <c r="I23" t="n">
-        <v>22.228</v>
+        <v>25.957</v>
       </c>
       <c r="J23" t="n">
-        <v>56.305</v>
+        <v>41.032</v>
       </c>
       <c r="K23" t="n">
-        <v>16.719</v>
+        <v>20.202</v>
       </c>
       <c r="L23" t="n">
-        <v>30.828</v>
+        <v>32.652</v>
       </c>
       <c r="M23" t="n">
-        <v>32.793</v>
+        <v>35.127</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.531</v>
+        <v>10.954</v>
       </c>
       <c r="C24" t="n">
-        <v>25.396</v>
+        <v>16.375</v>
       </c>
       <c r="D24" t="n">
-        <v>21.851</v>
+        <v>12.773</v>
       </c>
       <c r="E24" t="n">
-        <v>25.831</v>
+        <v>25.242</v>
       </c>
       <c r="F24" t="n">
-        <v>10.456</v>
+        <v>10.405</v>
       </c>
       <c r="G24" t="n">
-        <v>125.227</v>
+        <v>122.373</v>
       </c>
       <c r="H24" t="n">
-        <v>16.58</v>
+        <v>19.39</v>
       </c>
       <c r="I24" t="n">
-        <v>20.535</v>
+        <v>24.773</v>
       </c>
       <c r="J24" t="n">
-        <v>46.069</v>
+        <v>45.773</v>
       </c>
       <c r="K24" t="n">
-        <v>16.215</v>
+        <v>19.559</v>
       </c>
       <c r="L24" t="n">
-        <v>27.037</v>
+        <v>29.922</v>
       </c>
       <c r="M24" t="n">
-        <v>28.073</v>
+        <v>30.504</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.563</v>
+        <v>12.412</v>
       </c>
       <c r="C25" t="n">
-        <v>17.647</v>
+        <v>12.755</v>
       </c>
       <c r="D25" t="n">
-        <v>14.358</v>
+        <v>9.634</v>
       </c>
       <c r="E25" t="n">
-        <v>26.681</v>
+        <v>26.662</v>
       </c>
       <c r="F25" t="n">
-        <v>12.021</v>
+        <v>11.877</v>
       </c>
       <c r="G25" t="n">
-        <v>86.818</v>
+        <v>72.93600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>16.527</v>
+        <v>18.957</v>
       </c>
       <c r="I25" t="n">
-        <v>11.087</v>
+        <v>4.237</v>
       </c>
       <c r="J25" t="n">
-        <v>18.461</v>
+        <v>22.559</v>
       </c>
       <c r="K25" t="n">
-        <v>21.149</v>
+        <v>16.936</v>
       </c>
       <c r="L25" t="n">
-        <v>27.456</v>
+        <v>16.135</v>
       </c>
       <c r="M25" t="n">
-        <v>18.094</v>
+        <v>7.419</v>
       </c>
     </row>
     <row r="26">
@@ -10819,37 +10819,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.778</v>
+        <v>7.614</v>
       </c>
       <c r="C26" t="n">
-        <v>11.235</v>
+        <v>9.493</v>
       </c>
       <c r="D26" t="n">
-        <v>4.172</v>
+        <v>3.604</v>
       </c>
       <c r="E26" t="n">
-        <v>22.438</v>
+        <v>22.569</v>
       </c>
       <c r="F26" t="n">
-        <v>11.269</v>
+        <v>11.251</v>
       </c>
       <c r="G26" t="n">
-        <v>96.301</v>
+        <v>94.541</v>
       </c>
       <c r="H26" t="n">
-        <v>1.006</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.551</v>
+        <v>0.641</v>
       </c>
       <c r="J26" t="n">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>5.061</v>
+        <v>0.322</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.634</v>
+        <v>12.649</v>
       </c>
       <c r="C27" t="n">
-        <v>31.771</v>
+        <v>13.973</v>
       </c>
       <c r="D27" t="n">
-        <v>27.277</v>
+        <v>11.88</v>
       </c>
       <c r="E27" t="n">
-        <v>24.271</v>
+        <v>22.689</v>
       </c>
       <c r="F27" t="n">
-        <v>12.223</v>
+        <v>11.417</v>
       </c>
       <c r="G27" t="n">
-        <v>109.659</v>
+        <v>89.908</v>
       </c>
       <c r="H27" t="n">
-        <v>30.772</v>
+        <v>32.159</v>
       </c>
       <c r="I27" t="n">
-        <v>12.796</v>
+        <v>15.881</v>
       </c>
       <c r="J27" t="n">
-        <v>55.912</v>
+        <v>56.969</v>
       </c>
       <c r="K27" t="n">
-        <v>34.4</v>
+        <v>36.332</v>
       </c>
       <c r="L27" t="n">
-        <v>38.12</v>
+        <v>43.193</v>
       </c>
       <c r="M27" t="n">
-        <v>35.866</v>
+        <v>34.777</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.447</v>
+        <v>2.543</v>
       </c>
       <c r="C28" t="n">
-        <v>0.793</v>
+        <v>0.786</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.019</v>
+        <v>22.17</v>
       </c>
       <c r="F28" t="n">
-        <v>11.078</v>
+        <v>10.967</v>
       </c>
       <c r="G28" t="n">
-        <v>61.175</v>
+        <v>51.413</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.512</v>
+        <v>0.536</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.367</v>
+        <v>2.112</v>
       </c>
       <c r="C29" t="n">
-        <v>5.664</v>
+        <v>1.371</v>
       </c>
       <c r="D29" t="n">
-        <v>3.613</v>
+        <v>0.36</v>
       </c>
       <c r="E29" t="n">
-        <v>22.205</v>
+        <v>21.824</v>
       </c>
       <c r="F29" t="n">
-        <v>10.799</v>
+        <v>10.523</v>
       </c>
       <c r="G29" t="n">
-        <v>71.66200000000001</v>
+        <v>65.325</v>
       </c>
       <c r="H29" t="n">
-        <v>4.842</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>6.896</v>
+        <v>1.949</v>
       </c>
       <c r="J29" t="n">
-        <v>11.724</v>
+        <v>14.104</v>
       </c>
       <c r="K29" t="n">
-        <v>9.029</v>
+        <v>6.626</v>
       </c>
       <c r="L29" t="n">
-        <v>17.681</v>
+        <v>13.898</v>
       </c>
       <c r="M29" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.548</v>
+        <v>13.747</v>
       </c>
       <c r="F30" t="n">
-        <v>5.748</v>
+        <v>5.879</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9401425521e-05</v>
+        <v>6.815823364000001e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0893835209e-05</v>
+        <v>4.743903376000001e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9740023801e-05</v>
+        <v>1.6920286084e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2573021316e-05</v>
+        <v>5.431509913600001e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1917433889e-05</v>
+        <v>1.1398978756e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6922902724e-05</v>
+        <v>2.229795562499999e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9110843161e-05</v>
+        <v>6.906607236e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857296000000001e-05</v>
+        <v>9.556822080999999e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1736843961e-05</v>
+        <v>7.583448888999999e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.49278721e-05</v>
+        <v>3.935805696e-06</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0470146249e-05</v>
+        <v>3.466736641e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3138087289e-05</v>
+        <v>3.543701841000001e-06</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.555913443999999e-06</v>
+        <v>2.831836225000001e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.895782656e-06</v>
+        <v>2.348565444e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1821560529e-05</v>
+        <v>5.693758849e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8598643401e-05</v>
+        <v>4.68419449e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.850873081e-06</v>
+        <v>5.719896899999999e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3994404e-06</v>
+        <v>6.269155684e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8631158016e-05</v>
+        <v>8.479744e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8364586256e-05</v>
+        <v>1.042579521e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1764222369e-05</v>
+        <v>3.189081639999999e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9110574081e-05</v>
+        <v>3.755843999999999e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6255995001e-05</v>
+        <v>5.95701649e-07</v>
       </c>
       <c r="M3" t="n">
-        <v>6.194791848999999e-06</v>
+        <v>2.04261264e-07</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.445216256e-06</v>
+        <v>9.17847616e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.346268159999999e-07</v>
+        <v>4.90268164e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.440261201e-06</v>
+        <v>1.955319961e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.030457759999999e-05</v>
+        <v>3.8982158721e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.483402499999999e-06</v>
+        <v>5.415929649000001e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.252735369e-06</v>
+        <v>3.731988100000001e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.744120100000002e-08</v>
+        <v>3.767481e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2694969e-08</v>
+        <v>2.635795600000001e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.46615616e-07</v>
+        <v>1.156e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.231734809999998e-07</v>
+        <v>3.940072900000001e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.846416400000002e-08</v>
+        <v>1.0323369e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5876e-07</v>
+        <v>1.0640644e-08</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95811025e-07</v>
+        <v>3.53928969e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4249104e-08</v>
+        <v>2.7804529e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.442509159999999e-07</v>
+        <v>3.26633329e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8053475329e-05</v>
+        <v>3.8168264689e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.810075044000001e-06</v>
+        <v>8.938567936000002e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.909304383999999e-06</v>
+        <v>6.111799683999999e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011322225000001e-06</v>
+        <v>9.043251839999999e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.090584576e-06</v>
+        <v>8.412558400000002e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644942041e-06</v>
+        <v>4.304795040000001e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3079970641e-05</v>
+        <v>3.060505324900001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.030668996000001e-06</v>
+        <v>7.544138449000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.340262025e-06</v>
+        <v>2.370034489e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816464399999999e-08</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875263999999999e-07</v>
+        <v>3.297056399999999e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.278749024999999e-06</v>
+        <v>1.46531025e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0191104401e-05</v>
+        <v>1.357225e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.847396321e-06</v>
+        <v>6.406401599999998e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.100097023999998e-06</v>
+        <v>8.478726400000002e-08</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.080772008333333e-06</v>
+        <v>4.264499413333334e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>4.529210785333334e-06</v>
+        <v>9.666228033333332e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349704560333334e-06</v>
+        <v>9.412480533333332e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.842414408333332e-06</v>
+        <v>2.336848480333333e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792310536333332e-06</v>
+        <v>8.438451887999999e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.573138401333333e-06</v>
+        <v>6.013752083333332e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.575788800833332e-05</v>
+        <v>6.269856333333332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.472617876299999e-05</v>
+        <v>3.5840125803e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.672437120299999e-05</v>
+        <v>4.103705346133334e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.445482216033334e-05</v>
+        <v>4.502561026133334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.877715782533333e-05</v>
+        <v>2.246509174533333e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5514115072e-05</v>
+        <v>2.3087026875e-05</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.098200100000001e-08</v>
+        <v>7.593379600000002e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.694513444e-06</v>
+        <v>5.641361881e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0079456804e-05</v>
+        <v>1.9526988121e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.132638490000001e-07</v>
+        <v>6.293073959999999e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.225616e-09</v>
+        <v>1.002001e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.895632225e-06</v>
+        <v>6.903449569000001e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11414,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.356634253333333e-07</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.608033333333334e-11</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6.120408333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.044873763333334e-07</v>
+        <v>4.894741333333333e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210551960333334e-06</v>
+        <v>2.693763605333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>5.100563333333332e-08</v>
+        <v>7.565232e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>3.123413333333333e-08</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>2.870430083333333e-07</v>
+        <v>4.557541633333334e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.283802083333333e-07</v>
+        <v>1.895053333333333e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.946269281333335e-06</v>
+        <v>5.787777633333332e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56211968e-07</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1047683e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -11466,28 +11466,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.855224083333332e-07</v>
+        <v>3.582635520000001e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847600833333333e-06</v>
+        <v>1.678393227e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.136333333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.261919999999999e-10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6855075e-08</v>
+        <v>1.227354133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.678440533333333e-08</v>
+        <v>2.103381333333333e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>8.833968e-09</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.694216333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -11509,22 +11509,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.445457869999999e-07</v>
+        <v>3.979238670000001e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352435936333333e-06</v>
+        <v>1.304000705333334e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93548e-10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.785960333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652565333333334e-09</v>
+        <v>2.305633333333334e-11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.732192053333333e-07</v>
+        <v>1.66999563e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.841480013333335e-07</v>
+        <v>7.672002083333336e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.507942533333333e-08</v>
+        <v>1.193221333333333e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>3.893557763333333e-07</v>
+        <v>2.663599413333334e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11607,16 +11607,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.831083e-09</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6.097520833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>9.402400833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8287883e-08</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9371290084e-05</v>
+        <v>1.8847720369e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3152033929e-05</v>
+        <v>1.0466722249e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.228328564099999e-05</v>
+        <v>1.6356107881e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4763488256e-05</v>
+        <v>4.8214058929e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.631067044e-06</v>
+        <v>9.491240929e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8700082961e-05</v>
+        <v>5.399349322500001e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0843274384e-05</v>
+        <v>1.894972496399999e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.843978688099999e-05</v>
+        <v>1.5109818084e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4431580944e-05</v>
+        <v>3.531730904100001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7603840064e-05</v>
+        <v>5.3694621841e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0558811569e-05</v>
+        <v>5.0125388769e-05</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6874163827e-05</v>
+        <v>1.122261538133334e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>2.725465704533334e-05</v>
+        <v>7.502300176333332e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>3.804213542533334e-05</v>
+        <v>1.8954549507e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.828519960033332e-05</v>
+        <v>4.612601602133335e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.420100800833334e-05</v>
+        <v>1.3582217388e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>5.998046600833333e-05</v>
+        <v>5.837768104033333e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.235837952533334e-05</v>
+        <v>3.676236300833334e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>8.566325160333335e-06</v>
+        <v>7.062183045333335e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.944548180033333e-05</v>
+        <v>5.426913601200001e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7200312467e-05</v>
+        <v>3.734627242799999e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.550195469633334e-05</v>
+        <v>3.946047078533333e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.895226732033333e-05</v>
+        <v>4.341530760533333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.205386208133333e-05</v>
+        <v>5.214751976333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>1.043993222533333e-05</v>
+        <v>4.207956912e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>2.757412940833333e-05</v>
+        <v>1.740179840833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.850301594799999e-05</v>
+        <v>5.757888648533332e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.05779532e-05</v>
+        <v>1.041729184133334e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.593221632533333e-05</v>
+        <v>3.494449613333332e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.739337149633333e-05</v>
+        <v>2.043723418133333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>5.038409045333333e-06</v>
+        <v>2.604322960333334e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.933151574533333e-05</v>
+        <v>5.120931270533334e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6241899187e-05</v>
+        <v>1.654468245633333e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4.437938138699999e-05</v>
+        <v>2.708659124033332e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.625403456033334e-05</v>
+        <v>1.816381078533333e-05</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.09637552e-07</v>
+        <v>6.777327603333333e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>2.80932987e-07</v>
+        <v>1.90658352e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.371482253333335e-07</v>
+        <v>6.193182719999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.290778560033334e-05</v>
+        <v>5.199385100833333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.771884280333334e-06</v>
+        <v>8.566432033333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.570345605333333e-06</v>
+        <v>6.513375265333333e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>2.917376853333333e-07</v>
+        <v>4.152264033333332e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>2.557336033333334e-08</v>
+        <v>2.055653633333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.178509363333333e-07</v>
+        <v>1.07964003e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>3.52711947e-07</v>
+        <v>7.591276033333333e-08</v>
       </c>
       <c r="L18" t="n">
-        <v>9.119725453333332e-07</v>
+        <v>1.922800833333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>2.432880853333333e-07</v>
+        <v>3.258750963333332e-07</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.89655203e-07</v>
+        <v>1.39373568e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6310323e-08</v>
+        <v>1.622617633333334e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85889932e-07</v>
+        <v>2.275226253333333e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.964371968533333e-05</v>
+        <v>4.914662414699999e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.863296033333334e-06</v>
+        <v>7.942953985333334e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.034967201333333e-06</v>
+        <v>4.884044705333334e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>3.364443000000001e-09</v>
+        <v>1.408333333333333e-10</v>
       </c>
       <c r="I19" t="n">
-        <v>3.205400333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.221132e-09</v>
+        <v>7.895070000000001e-10</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6272723e-08</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.407033633333333e-08</v>
+        <v>2.3201883e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>7.947896333333335e-09</v>
+        <v>4.735120333333334e-09</v>
       </c>
     </row>
     <row r="20">
@@ -11885,37 +11885,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.866629633333332e-06</v>
+        <v>5.557496961333335e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>5.129136705333333e-06</v>
+        <v>5.883572245333334e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>4.104828213333333e-07</v>
+        <v>5.992816003333334e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.603229203333334e-05</v>
+        <v>1.650416006533334e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.046963221333333e-06</v>
+        <v>3.206431361333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>4.245417008333334e-06</v>
+        <v>4.830849408333334e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>6.051472213333333e-07</v>
+        <v>8.022806533333333e-08</v>
       </c>
       <c r="I20" t="n">
-        <v>3.058280333333333e-09</v>
+        <v>4.543621333333333e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>1.725208333333333e-09</v>
+        <v>4.426245333333334e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>1.662865633333333e-06</v>
+        <v>4.748698453333333e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>3.783387e-09</v>
+        <v>1.234646533333334e-08</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.685432216333331e-06</v>
+        <v>4.153826720333333e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.037913932000002e-06</v>
+        <v>4.420301445333334e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>6.616863053333334e-07</v>
+        <v>2.027874083333333e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491004500833333e-05</v>
+        <v>1.418037500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399671136333333e-06</v>
+        <v>2.367256661333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.490451656333333e-06</v>
+        <v>2.429800961333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317040870533334e-05</v>
+        <v>6.792901505333333e-06</v>
       </c>
       <c r="I21" t="n">
-        <v>1.536803333333333e-06</v>
+        <v>1.4572848e-08</v>
       </c>
       <c r="J21" t="n">
-        <v>2.662336925633333e-05</v>
+        <v>1.941835208333333e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>1.580676288133333e-05</v>
+        <v>1.049309192533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>1.099805981633333e-05</v>
+        <v>2.35924272e-07</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.715124360033333e-05</v>
+        <v>1.163016803333333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.166446803333333e-05</v>
+        <v>1.272835603333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.515553548033333e-05</v>
+        <v>2.828820961333333e-06</v>
       </c>
       <c r="E22" t="n">
-        <v>1.852995020833333e-05</v>
+        <v>1.444505508033333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.909472492e-06</v>
+        <v>2.069708268e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>3.475892485333333e-06</v>
+        <v>1.937868336333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.802839840833333e-05</v>
+        <v>4.036962401633334e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.267474000133333e-05</v>
+        <v>1.427817040833333e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>6.3408650067e-05</v>
+        <v>5.9475609612e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.007977365633334e-05</v>
+        <v>1.862185896033334e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>4.127059772033335e-05</v>
+        <v>3.801443873633333e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>3.985414176133334e-05</v>
+        <v>1.219116752133333e-05</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.60458276e-06</v>
+        <v>1.89557824e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>9.408942760000001e-06</v>
+        <v>3.75429376e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82947904e-06</v>
+        <v>3.30585124e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>5.81822641e-06</v>
+        <v>4.938172840000001e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.057328899999998e-07</v>
+        <v>8.184820900000002e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4277621121e-05</v>
+        <v>1.0935303184e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>3.076165210000001e-06</v>
+        <v>4.30313536e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.940839840000001e-06</v>
+        <v>6.737658490000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>3.170253025e-05</v>
+        <v>1.683625024e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>2.79524961e-06</v>
+        <v>4.08120804e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>9.503655839999998e-06</v>
+        <v>1.066153104e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>1.075380849e-05</v>
+        <v>1.233906129000001e-05</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.41211961e-06</v>
+        <v>1.19990116e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>6.449568160000001e-06</v>
+        <v>2.68140625e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>4.774662009999999e-06</v>
+        <v>1.63149529e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.67240561e-06</v>
+        <v>6.37158564e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09327936e-06</v>
+        <v>1.08264025e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5681801529e-05</v>
+        <v>1.4975151129e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.748963999999999e-06</v>
+        <v>3.759721000000001e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>4.21686225e-06</v>
+        <v>6.13701529e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.122352761e-05</v>
+        <v>2.095167529e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>2.62926225e-06</v>
+        <v>3.82554481e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>7.309993689999999e-06</v>
+        <v>8.953260840000001e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>7.88093329e-06</v>
+        <v>9.30494016e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.83954969e-06</v>
+        <v>1.54057744e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.11416609e-06</v>
+        <v>1.62690025e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.06152164e-06</v>
+        <v>9.281395600000001e-07</v>
       </c>
       <c r="E25" t="n">
-        <v>7.118757610000001e-06</v>
+        <v>7.108622439999999e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44504441e-06</v>
+        <v>1.41063129e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>7.537365123999998e-06</v>
+        <v>5.319660096e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>2.73141729e-06</v>
+        <v>3.593678490000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.22921569e-06</v>
+        <v>1.7952169e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>3.408085209999999e-06</v>
+        <v>5.089084810000001e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>4.472802010000001e-06</v>
+        <v>2.86828096e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>7.538319360000001e-06</v>
+        <v>2.60338225e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>3.273928360000001e-06</v>
+        <v>5.504156099999999e-07</v>
       </c>
     </row>
     <row r="26">
@@ -12143,37 +12143,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.049728399999999e-07</v>
+        <v>5.797299600000001e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26225225e-06</v>
+        <v>9.011704899999999e-07</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7405584e-07</v>
+        <v>1.2988816e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.03463844e-06</v>
+        <v>5.093597609999999e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.26990361e-06</v>
+        <v>1.26585001e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.273882601e-06</v>
+        <v>8.938000681e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>1.012036e-08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.405601e-08</v>
+        <v>4.10881e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>5.715360000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2.53009e-09</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.5613721e-07</v>
+        <v>1.03684e-09</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.680299560000001e-06</v>
+        <v>1.59997201e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.009396441e-05</v>
+        <v>1.95244729e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>7.440347290000001e-06</v>
+        <v>1.411344e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>5.890814410000001e-06</v>
+        <v>5.147907210000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49401729e-06</v>
+        <v>1.30347889e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2025096281e-05</v>
+        <v>8.083448463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>9.469159839999999e-06</v>
+        <v>1.034201281e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>1.63737616e-06</v>
+        <v>2.52206161e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.126151743999999e-05</v>
+        <v>3.245466961e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.18336e-05</v>
+        <v>1.320014224e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.453134399999999e-05</v>
+        <v>1.865635249e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.286369956e-05</v>
+        <v>1.209439729e-05</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.987809e-08</v>
+        <v>6.466849e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>6.288490000000001e-09</v>
+        <v>6.17796e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.848363609999998e-06</v>
+        <v>4.915089000000001e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.22722084e-06</v>
+        <v>1.20275089e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>3.742380625e-06</v>
+        <v>2.643296568999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.62144e-09</v>
+        <v>2.87296e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9070689e-07</v>
+        <v>4.460544e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2080896e-07</v>
+        <v>1.879641e-08</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3053769e-07</v>
+        <v>1.296e-09</v>
       </c>
       <c r="E29" t="n">
-        <v>4.930620249999999e-06</v>
+        <v>4.762869760000001e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16618401e-06</v>
+        <v>1.10733529e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.135442244e-06</v>
+        <v>4.267355625000001e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3444964e-07</v>
+        <v>6.577210000000002e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7554816e-07</v>
+        <v>3.798601e-08</v>
       </c>
       <c r="J29" t="n">
-        <v>1.37452176e-06</v>
+        <v>1.98922816e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>8.152284100000001e-07</v>
+        <v>4.3903876e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>3.126177610000001e-06</v>
+        <v>1.93154404e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.83548304e-06</v>
+        <v>1.88980009e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.303950400000001e-07</v>
+        <v>3.4562641e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="I2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.123958</v>
+        <v>0.041319</v>
       </c>
       <c r="K2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M2" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="3">
@@ -12482,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E3" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="I3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="J3" t="n">
-        <v>0.122569</v>
+        <v>0.041319</v>
       </c>
       <c r="K3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M3" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.124653</v>
+        <v>0.038889</v>
       </c>
       <c r="G4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="I4" t="n">
-        <v>0.051042</v>
+        <v>0.040625</v>
       </c>
       <c r="J4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M4" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="5">
@@ -12568,10 +12568,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.124653</v>
+        <v>0.001042</v>
       </c>
       <c r="D5" t="n">
         <v>0.000694</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H6" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="J6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M6" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="7">
@@ -12652,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C7" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D7" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E7" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F7" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G7" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H7" t="n">
-        <v>0.080556</v>
+        <v>0.039583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.045833</v>
+        <v>0.040625</v>
       </c>
       <c r="J7" t="n">
-        <v>0.047569</v>
+        <v>0.041319</v>
       </c>
       <c r="K7" t="n">
-        <v>0.061806</v>
+        <v>0.041319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08784699999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="M7" t="n">
-        <v>0.103472</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.121528</v>
+        <v>0.038194</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12704,19 +12704,19 @@
         <v>0.003472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.111111</v>
+        <v>0.038194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.121528</v>
+        <v>0.038194</v>
       </c>
       <c r="G8" t="n">
-        <v>0.121528</v>
+        <v>0.038194</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.100694</v>
+        <v>0.038194</v>
       </c>
       <c r="J8" t="n">
         <v>0.003472</v>
@@ -12738,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="I9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="J9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K9" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="10">
@@ -12790,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F10" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="H10" t="n">
-        <v>0.123958</v>
+        <v>0.000347</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08437500000000001</v>
+        <v>0.041319</v>
       </c>
       <c r="J10" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12833,22 +12833,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G11" t="n">
-        <v>0.124653</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.124653</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12876,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12919,10 +12919,10 @@
         <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F13" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G13" t="n">
         <v>0.000347</v>
@@ -12931,16 +12931,16 @@
         <v>0.000347</v>
       </c>
       <c r="I13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="K13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H15" t="n">
-        <v>0.046528</v>
+        <v>0.041319</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="K15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M15" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E16" t="n">
-        <v>0.124653</v>
+        <v>0.010764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G16" t="n">
         <v>0.021875</v>
       </c>
       <c r="H16" t="n">
-        <v>0.076389</v>
+        <v>0.035069</v>
       </c>
       <c r="I16" t="n">
-        <v>0.060764</v>
+        <v>0.041319</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07256899999999999</v>
+        <v>0.023611</v>
       </c>
       <c r="K16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M16" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="17">
@@ -13080,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F17" t="n">
-        <v>0.101042</v>
+        <v>0.001042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="I17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="J17" t="n">
-        <v>0.100694</v>
+        <v>0.041319</v>
       </c>
       <c r="K17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M17" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="18">
@@ -13123,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C18" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D18" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E18" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F18" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G18" t="n">
-        <v>0.124653</v>
+        <v>0.001389</v>
       </c>
       <c r="H18" t="n">
-        <v>0.092361</v>
+        <v>0.041319</v>
       </c>
       <c r="I18" t="n">
-        <v>0.073958</v>
+        <v>0.041319</v>
       </c>
       <c r="J18" t="n">
-        <v>0.064236</v>
+        <v>0.041319</v>
       </c>
       <c r="K18" t="n">
-        <v>0.088542</v>
+        <v>0.041319</v>
       </c>
       <c r="L18" t="n">
-        <v>0.053125</v>
+        <v>0.041319</v>
       </c>
       <c r="M18" t="n">
-        <v>0.061458</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="19">
@@ -13166,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C19" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D19" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E19" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F19" t="n">
-        <v>0.044792</v>
+        <v>0.041319</v>
       </c>
       <c r="G19" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H19" t="n">
-        <v>0.092014</v>
+        <v>0.041319</v>
       </c>
       <c r="I19" t="n">
-        <v>0.100347</v>
+        <v>0.000347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1</v>
+        <v>0.041319</v>
       </c>
       <c r="K19" t="n">
-        <v>0.093056</v>
+        <v>0.000347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.052431</v>
+        <v>0.041319</v>
       </c>
       <c r="M19" t="n">
-        <v>0.067708</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="20">
@@ -13236,7 +13236,7 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="L20" t="n">
         <v>0.026736</v>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G21" t="n">
-        <v>0.124653</v>
+        <v>0.005903</v>
       </c>
       <c r="H21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="I21" t="n">
-        <v>0.124653</v>
+        <v>0.040972</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="K21" t="n">
-        <v>0.101042</v>
+        <v>0.041319</v>
       </c>
       <c r="L21" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H22" t="n">
-        <v>0.052431</v>
+        <v>0.041319</v>
       </c>
       <c r="I22" t="n">
         <v>0.021181</v>
       </c>
       <c r="J22" t="n">
-        <v>0.073958</v>
+        <v>0.022222</v>
       </c>
       <c r="K22" t="n">
-        <v>0.118403</v>
+        <v>0.041319</v>
       </c>
       <c r="L22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="M22" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="23">
@@ -13341,19 +13341,19 @@
         <v>0.028819</v>
       </c>
       <c r="C23" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D23" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E23" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.123958</v>
+        <v>0.041319</v>
       </c>
       <c r="G23" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H23" t="n">
         <v>0.033681</v>
@@ -13362,16 +13362,16 @@
         <v>0.022222</v>
       </c>
       <c r="J23" t="n">
-        <v>0.117708</v>
+        <v>0.041319</v>
       </c>
       <c r="K23" t="n">
         <v>0.031944</v>
       </c>
       <c r="L23" t="n">
-        <v>0.042014</v>
+        <v>0.041319</v>
       </c>
       <c r="M23" t="n">
-        <v>0.045486</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="24">
@@ -13381,22 +13381,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C24" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D24" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E24" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F24" t="n">
-        <v>0.080208</v>
+        <v>0.000347</v>
       </c>
       <c r="G24" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="H24" t="n">
         <v>0.024306</v>
@@ -13405,7 +13405,7 @@
         <v>0.017361</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09375</v>
+        <v>0.041319</v>
       </c>
       <c r="K24" t="n">
         <v>0.030556</v>
@@ -13424,40 +13424,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.124653</v>
+        <v>0.001042</v>
       </c>
       <c r="D25" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.106597</v>
+        <v>0.000694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H25" t="n">
-        <v>0.043403</v>
+        <v>0.041319</v>
       </c>
       <c r="I25" t="n">
-        <v>0.092014</v>
+        <v>0.041319</v>
       </c>
       <c r="J25" t="n">
-        <v>0.054167</v>
+        <v>0.041319</v>
       </c>
       <c r="K25" t="n">
-        <v>0.080208</v>
+        <v>0.041319</v>
       </c>
       <c r="L25" t="n">
-        <v>0.115625</v>
+        <v>0.041319</v>
       </c>
       <c r="M25" t="n">
-        <v>0.103472</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="26">
@@ -13470,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.124653</v>
+        <v>0.010069</v>
       </c>
       <c r="D26" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13482,22 +13482,22 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08472200000000001</v>
+        <v>0.000347</v>
       </c>
       <c r="I26" t="n">
-        <v>0.124653</v>
+        <v>0.012153</v>
       </c>
       <c r="J26" t="n">
-        <v>0.104167</v>
+        <v>0.000347</v>
       </c>
       <c r="K26" t="n">
-        <v>0.072917</v>
+        <v>0.000347</v>
       </c>
       <c r="L26" t="n">
-        <v>0.089931</v>
+        <v>0.041319</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C27" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="D27" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E27" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="F27" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G27" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07083299999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="I27" t="n">
         <v>0.015278</v>
       </c>
       <c r="J27" t="n">
-        <v>0.067014</v>
+        <v>0.041319</v>
       </c>
       <c r="K27" t="n">
-        <v>0.057639</v>
+        <v>0.041319</v>
       </c>
       <c r="L27" t="n">
-        <v>0.043403</v>
+        <v>0.041319</v>
       </c>
       <c r="M27" t="n">
-        <v>0.057639</v>
+        <v>0.041319</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.052431</v>
+        <v>0.041319</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,7 +13568,7 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
@@ -13596,40 +13596,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="C29" t="n">
-        <v>0.124306</v>
+        <v>0.041319</v>
       </c>
       <c r="D29" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="E29" t="n">
-        <v>0.123958</v>
+        <v>0.041319</v>
       </c>
       <c r="F29" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="G29" t="n">
-        <v>0.124653</v>
+        <v>0.041319</v>
       </c>
       <c r="H29" t="n">
-        <v>0.092708</v>
+        <v>0.041319</v>
       </c>
       <c r="I29" t="n">
-        <v>0.093056</v>
+        <v>0.041319</v>
       </c>
       <c r="J29" t="n">
-        <v>0.058333</v>
+        <v>0.041319</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08819399999999999</v>
+        <v>0.041319</v>
       </c>
       <c r="L29" t="n">
-        <v>0.077431</v>
+        <v>0.041319</v>
       </c>
       <c r="M29" t="n">
-        <v>0.117708</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="30">

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.014</v>
+        <v>0.109</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.037</v>
+        <v>0.254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.187</v>
+        <v>0.608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04</v>
+        <v>0.124</v>
       </c>
       <c r="G2" t="n">
-        <v>0.076</v>
+        <v>0.253</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007</v>
+        <v>0.146</v>
       </c>
       <c r="I2" t="n">
-        <v>0.012</v>
+        <v>0.185</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006</v>
+        <v>0.293</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003</v>
+        <v>0.151</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003</v>
+        <v>0.138</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007</v>
+        <v>0.039</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006</v>
+        <v>0.036</v>
       </c>
       <c r="D3" t="n">
-        <v>0.016</v>
+        <v>0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>0.168</v>
+        <v>0.511</v>
       </c>
       <c r="F3" t="n">
-        <v>0.021</v>
+        <v>0.062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.021</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001</v>
+        <v>0.059</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="4">
@@ -1917,34 +1917,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="C4" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.002</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.136</v>
+        <v>0.41</v>
       </c>
       <c r="F5" t="n">
-        <v>0.032</v>
+        <v>0.096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.022</v>
+        <v>0.065</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002</v>
+        <v>0.019</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D6" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.001</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.008</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007</v>
+        <v>0.029</v>
       </c>
       <c r="F7" t="n">
-        <v>0.028</v>
+        <v>0.094</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.174</v>
+        <v>0.646</v>
       </c>
       <c r="I7" t="n">
-        <v>0.115</v>
+        <v>0.369</v>
       </c>
       <c r="J7" t="n">
-        <v>0.054</v>
+        <v>0.416</v>
       </c>
       <c r="K7" t="n">
-        <v>0.132</v>
+        <v>0.457</v>
       </c>
       <c r="L7" t="n">
-        <v>0.025</v>
+        <v>0.284</v>
       </c>
       <c r="M7" t="n">
-        <v>0.026</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.018</v>
+        <v>0.059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06</v>
+        <v>0.203</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.022</v>
+        <v>0.063</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2153,13 +2153,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.043</v>
+        <v>0.263</v>
       </c>
       <c r="C15" t="n">
-        <v>0.019</v>
+        <v>0.177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.035</v>
+        <v>0.246</v>
       </c>
       <c r="E15" t="n">
-        <v>0.163</v>
+        <v>0.536</v>
       </c>
       <c r="F15" t="n">
-        <v>0.033</v>
+        <v>0.103</v>
       </c>
       <c r="G15" t="n">
-        <v>0.186</v>
+        <v>0.594</v>
       </c>
       <c r="H15" t="n">
-        <v>0.022</v>
+        <v>0.174</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.023</v>
+        <v>0.185</v>
       </c>
       <c r="K15" t="n">
-        <v>0.058</v>
+        <v>0.356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.102</v>
+        <v>0.502</v>
       </c>
       <c r="M15" t="n">
-        <v>0.067</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.023</v>
+        <v>0.167</v>
       </c>
       <c r="C16" t="n">
-        <v>0.014</v>
+        <v>0.136</v>
       </c>
       <c r="D16" t="n">
-        <v>0.045</v>
+        <v>0.262</v>
       </c>
       <c r="E16" t="n">
-        <v>0.166</v>
+        <v>0.502</v>
       </c>
       <c r="F16" t="n">
-        <v>0.047</v>
+        <v>0.148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.217</v>
+        <v>0.643</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="I16" t="n">
-        <v>0.013</v>
+        <v>0.075</v>
       </c>
       <c r="J16" t="n">
-        <v>0.13</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.055</v>
+        <v>0.37</v>
       </c>
       <c r="L16" t="n">
-        <v>0.092</v>
+        <v>0.401</v>
       </c>
       <c r="M16" t="n">
-        <v>0.066</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.013</v>
+        <v>0.077</v>
       </c>
       <c r="C17" t="n">
-        <v>0.011</v>
+        <v>0.064</v>
       </c>
       <c r="D17" t="n">
-        <v>0.052</v>
+        <v>0.218</v>
       </c>
       <c r="E17" t="n">
-        <v>0.205</v>
+        <v>0.623</v>
       </c>
       <c r="F17" t="n">
-        <v>0.037</v>
+        <v>0.113</v>
       </c>
       <c r="G17" t="n">
-        <v>0.124</v>
+        <v>0.379</v>
       </c>
       <c r="H17" t="n">
-        <v>0.047</v>
+        <v>0.265</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.475</v>
       </c>
       <c r="K17" t="n">
-        <v>0.029</v>
+        <v>0.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0.054</v>
+        <v>0.341</v>
       </c>
       <c r="M17" t="n">
-        <v>0.032</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.002</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.001</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.174</v>
+        <v>0.53</v>
       </c>
       <c r="F19" t="n">
-        <v>0.028</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.017</v>
+        <v>0.053</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02</v>
+        <v>0.058</v>
       </c>
       <c r="C20" t="n">
-        <v>0.022</v>
+        <v>0.061</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="E20" t="n">
-        <v>0.059</v>
+        <v>0.176</v>
       </c>
       <c r="F20" t="n">
-        <v>0.012</v>
+        <v>0.034</v>
       </c>
       <c r="G20" t="n">
-        <v>0.018</v>
+        <v>0.05</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.012</v>
+        <v>0.056</v>
       </c>
       <c r="C21" t="n">
-        <v>0.013</v>
+        <v>0.06</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05</v>
+        <v>0.155</v>
       </c>
       <c r="F21" t="n">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="G21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005</v>
+        <v>0.202</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001</v>
+        <v>0.161</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01</v>
+        <v>0.117</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.023</v>
+        <v>0.171</v>
       </c>
       <c r="C22" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.025</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.007</v>
-      </c>
       <c r="G22" t="n">
-        <v>0.006</v>
+        <v>0.025</v>
       </c>
       <c r="H22" t="n">
-        <v>0.108</v>
+        <v>0.394</v>
       </c>
       <c r="I22" t="n">
-        <v>0.036</v>
+        <v>0.137</v>
       </c>
       <c r="J22" t="n">
-        <v>0.144</v>
+        <v>0.609</v>
       </c>
       <c r="K22" t="n">
-        <v>0.042</v>
+        <v>0.183</v>
       </c>
       <c r="L22" t="n">
-        <v>0.068</v>
+        <v>0.352</v>
       </c>
       <c r="M22" t="n">
-        <v>0.011</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.038</v>
+        <v>0.064</v>
       </c>
       <c r="C23" t="n">
-        <v>0.005</v>
+        <v>0.058</v>
       </c>
       <c r="D23" t="n">
-        <v>0.004</v>
+        <v>0.056</v>
       </c>
       <c r="E23" t="n">
-        <v>0.017</v>
+        <v>0.056</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.036</v>
+        <v>0.127</v>
       </c>
       <c r="H23" t="n">
-        <v>0.008</v>
+        <v>0.035</v>
       </c>
       <c r="I23" t="n">
-        <v>0.017</v>
+        <v>0.059</v>
       </c>
       <c r="J23" t="n">
-        <v>0.029</v>
+        <v>0.231</v>
       </c>
       <c r="K23" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="L23" t="n">
-        <v>0.024</v>
+        <v>0.097</v>
       </c>
       <c r="M23" t="n">
-        <v>0.017</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.002</v>
+        <v>0.016</v>
       </c>
       <c r="C24" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="D24" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="E24" t="n">
-        <v>0.022</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.004</v>
+        <v>0.012</v>
       </c>
       <c r="G24" t="n">
-        <v>0.053</v>
+        <v>0.164</v>
       </c>
       <c r="H24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="I24" t="n">
-        <v>0.017</v>
+        <v>0.054</v>
       </c>
       <c r="J24" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.032</v>
       </c>
-      <c r="K24" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.025</v>
+        <v>0.083</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="C25" t="n">
-        <v>0.004</v>
+        <v>0.022</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="E25" t="n">
-        <v>0.025</v>
+        <v>0.077</v>
       </c>
       <c r="F25" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="G25" t="n">
-        <v>0.016</v>
+        <v>0.063</v>
       </c>
       <c r="H25" t="n">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="J25" t="n">
-        <v>0.006</v>
+        <v>0.044</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002</v>
+        <v>0.038</v>
       </c>
       <c r="L25" t="n">
-        <v>0.002</v>
+        <v>0.047</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.002</v>
       </c>
-      <c r="C26" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
-        <v>0.018</v>
+        <v>0.055</v>
       </c>
       <c r="F26" t="n">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="G26" t="n">
-        <v>0.031</v>
+        <v>0.097</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="C27" t="n">
-        <v>0.002</v>
+        <v>0.045</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002</v>
+        <v>0.033</v>
       </c>
       <c r="E27" t="n">
-        <v>0.018</v>
+        <v>0.057</v>
       </c>
       <c r="F27" t="n">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="G27" t="n">
-        <v>0.025</v>
+        <v>0.098</v>
       </c>
       <c r="H27" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.022</v>
       </c>
-      <c r="I27" t="n">
-        <v>0.008</v>
-      </c>
       <c r="J27" t="n">
-        <v>0.079</v>
+        <v>0.317</v>
       </c>
       <c r="K27" t="n">
-        <v>0.021</v>
+        <v>0.115</v>
       </c>
       <c r="L27" t="n">
-        <v>0.042</v>
+        <v>0.159</v>
       </c>
       <c r="M27" t="n">
-        <v>0.016</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="28">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.018</v>
+        <v>0.053</v>
       </c>
       <c r="F28" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="G28" t="n">
-        <v>0.007</v>
+        <v>0.031</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="J29" t="n">
         <v>0.017</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.002</v>
-      </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L29" t="n">
-        <v>0.002</v>
+        <v>0.03</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.007</v>
+        <v>0.02</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82.55800000000001</v>
+        <v>139.289</v>
       </c>
       <c r="C2" t="n">
-        <v>68.876</v>
+        <v>144.547</v>
       </c>
       <c r="D2" t="n">
-        <v>130.078</v>
+        <v>199.349</v>
       </c>
       <c r="E2" t="n">
-        <v>233.056</v>
+        <v>250.146</v>
       </c>
       <c r="F2" t="n">
-        <v>106.766</v>
+        <v>109.167</v>
       </c>
       <c r="G2" t="n">
-        <v>149.325</v>
+        <v>164.082</v>
       </c>
       <c r="H2" t="n">
-        <v>83.10599999999999</v>
+        <v>170.619</v>
       </c>
       <c r="I2" t="n">
-        <v>97.759</v>
+        <v>196.4</v>
       </c>
       <c r="J2" t="n">
-        <v>87.083</v>
+        <v>248.485</v>
       </c>
       <c r="K2" t="n">
-        <v>62.736</v>
+        <v>186.89</v>
       </c>
       <c r="L2" t="n">
-        <v>58.879</v>
+        <v>174.557</v>
       </c>
       <c r="M2" t="n">
-        <v>59.529</v>
+        <v>230.517</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.215</v>
+        <v>74.538</v>
       </c>
       <c r="C3" t="n">
-        <v>48.462</v>
+        <v>76.78400000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>75.45699999999999</v>
+        <v>108.727</v>
       </c>
       <c r="E3" t="n">
-        <v>217.978</v>
+        <v>220.451</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>79.178</v>
+        <v>86.02</v>
       </c>
       <c r="H3" t="n">
-        <v>29.12</v>
+        <v>136.496</v>
       </c>
       <c r="I3" t="n">
-        <v>32.289</v>
+        <v>135.516</v>
       </c>
       <c r="J3" t="n">
-        <v>17.858</v>
+        <v>108.492</v>
       </c>
       <c r="K3" t="n">
-        <v>19.38</v>
+        <v>138.241</v>
       </c>
       <c r="L3" t="n">
-        <v>24.407</v>
+        <v>127.499</v>
       </c>
       <c r="M3" t="n">
-        <v>14.292</v>
+        <v>78.70699999999999</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.296</v>
+        <v>38.016</v>
       </c>
       <c r="C4" t="n">
-        <v>22.142</v>
+        <v>27.104</v>
       </c>
       <c r="D4" t="n">
-        <v>44.219</v>
+        <v>49.399</v>
       </c>
       <c r="E4" t="n">
-        <v>197.439</v>
+        <v>200.76</v>
       </c>
       <c r="F4" t="n">
-        <v>73.631</v>
+        <v>74.05</v>
       </c>
       <c r="G4" t="n">
-        <v>61.09</v>
+        <v>65.21299999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.941</v>
+        <v>9.351000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>5.146</v>
+        <v>5.348</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>15.704</v>
       </c>
       <c r="K4" t="n">
-        <v>6.277</v>
+        <v>28.691</v>
       </c>
       <c r="L4" t="n">
-        <v>3.213</v>
+        <v>8.858000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>3.262</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.813</v>
+        <v>19.895</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454</v>
+        <v>6.652</v>
       </c>
       <c r="D5" t="n">
         <v>18.59</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.072</v>
+        <v>63.335</v>
       </c>
       <c r="C6" t="n">
-        <v>9.172000000000001</v>
+        <v>33.024</v>
       </c>
       <c r="D6" t="n">
-        <v>20.748</v>
+        <v>51.429</v>
       </c>
       <c r="E6" t="n">
-        <v>174.943</v>
+        <v>181.879</v>
       </c>
       <c r="F6" t="n">
-        <v>86.857</v>
+        <v>89.614</v>
       </c>
       <c r="G6" t="n">
-        <v>48.683</v>
+        <v>57.795</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4.262</v>
       </c>
       <c r="I6" t="n">
-        <v>5.742</v>
+        <v>22.08</v>
       </c>
       <c r="J6" t="n">
-        <v>12.105</v>
+        <v>72.655</v>
       </c>
       <c r="K6" t="n">
-        <v>11.65</v>
+        <v>100.951</v>
       </c>
       <c r="L6" t="n">
-        <v>8.004</v>
+        <v>53.361</v>
       </c>
       <c r="M6" t="n">
-        <v>9.208</v>
+        <v>64.032</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.768</v>
+        <v>110.645</v>
       </c>
       <c r="C7" t="n">
-        <v>17.029</v>
+        <v>116.566</v>
       </c>
       <c r="D7" t="n">
-        <v>16.804</v>
+        <v>83.959</v>
       </c>
       <c r="E7" t="n">
-        <v>83.729</v>
+        <v>107.365</v>
       </c>
       <c r="F7" t="n">
-        <v>159.108</v>
+        <v>171.397</v>
       </c>
       <c r="G7" t="n">
-        <v>42.475</v>
+        <v>68.69799999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>433.844</v>
+        <v>448.705</v>
       </c>
       <c r="I7" t="n">
-        <v>327.903</v>
+        <v>328.085</v>
       </c>
       <c r="J7" t="n">
-        <v>350.872</v>
+        <v>406.981</v>
       </c>
       <c r="K7" t="n">
-        <v>367.528</v>
+        <v>369.421</v>
       </c>
       <c r="L7" t="n">
-        <v>259.606</v>
+        <v>345.876</v>
       </c>
       <c r="M7" t="n">
-        <v>263.175</v>
+        <v>409.27</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.714</v>
+        <v>8.999000000000001</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7408,19 +7408,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.10899999999999</v>
+        <v>75.474</v>
       </c>
       <c r="F8" t="n">
-        <v>139.739</v>
+        <v>141.702</v>
       </c>
       <c r="G8" t="n">
-        <v>25.086</v>
+        <v>26.707</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.001</v>
+        <v>2.15</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7442,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>20.174</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.285</v>
       </c>
       <c r="E9" t="n">
-        <v>38.32</v>
+        <v>49.127</v>
       </c>
       <c r="F9" t="n">
-        <v>89.896</v>
+        <v>98.14100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4.764</v>
+        <v>12.37</v>
       </c>
       <c r="H9" t="n">
-        <v>4.508</v>
+        <v>9.68</v>
       </c>
       <c r="I9" t="n">
-        <v>11.693</v>
+        <v>29.345</v>
       </c>
       <c r="J9" t="n">
-        <v>7.54</v>
+        <v>19.625</v>
       </c>
       <c r="K9" t="n">
-        <v>13.177</v>
+        <v>133.562</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>21.648</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.757</v>
       </c>
     </row>
     <row r="10">
@@ -7494,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.784</v>
+        <v>38.165</v>
       </c>
       <c r="F10" t="n">
-        <v>70.959</v>
+        <v>74.45</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="n">
-        <v>6.068</v>
+        <v>11.198</v>
       </c>
       <c r="J10" t="n">
-        <v>2.512</v>
+        <v>7.096</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5.148</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34.551</v>
+        <v>36.519</v>
       </c>
       <c r="F11" t="n">
-        <v>62.546</v>
+        <v>63.697</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.891</v>
       </c>
       <c r="J11" t="n">
-        <v>0.263</v>
+        <v>3.736</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7580,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.546</v>
+        <v>22.796</v>
       </c>
       <c r="F12" t="n">
-        <v>47.975</v>
+        <v>48.502</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.892</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>28.268</v>
+        <v>34.177</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7635,16 +7635,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.807</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>13.525</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>16.795</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.407</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137.287</v>
+        <v>198.422</v>
       </c>
       <c r="C15" t="n">
-        <v>102.307</v>
+        <v>182.077</v>
       </c>
       <c r="D15" t="n">
-        <v>127.891</v>
+        <v>205.629</v>
       </c>
       <c r="E15" t="n">
-        <v>219.577</v>
+        <v>234.016</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>232.365</v>
+        <v>242.281</v>
       </c>
       <c r="H15" t="n">
-        <v>137.658</v>
+        <v>150.226</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>122.922</v>
+        <v>168.641</v>
       </c>
       <c r="K15" t="n">
-        <v>187.929</v>
+        <v>210.788</v>
       </c>
       <c r="L15" t="n">
-        <v>231.721</v>
+        <v>240.008</v>
       </c>
       <c r="M15" t="n">
-        <v>223.887</v>
+        <v>246.087</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>183.488</v>
+        <v>283.941</v>
       </c>
       <c r="C16" t="n">
-        <v>150.023</v>
+        <v>285.944</v>
       </c>
       <c r="D16" t="n">
-        <v>238.461</v>
+        <v>337.826</v>
       </c>
       <c r="E16" t="n">
-        <v>377.251</v>
+        <v>380.599</v>
       </c>
       <c r="F16" t="n">
-        <v>201.858</v>
+        <v>206.405</v>
       </c>
       <c r="G16" t="n">
         <v>437.584</v>
       </c>
       <c r="H16" t="n">
-        <v>332.719</v>
+        <v>361.504</v>
       </c>
       <c r="I16" t="n">
-        <v>145.556</v>
+        <v>171.377</v>
       </c>
       <c r="J16" t="n">
-        <v>406.512</v>
+        <v>429.552</v>
       </c>
       <c r="K16" t="n">
-        <v>334.722</v>
+        <v>376.299</v>
       </c>
       <c r="L16" t="n">
-        <v>344.066</v>
+        <v>369.467</v>
       </c>
       <c r="M16" t="n">
-        <v>360.896</v>
+        <v>383.219</v>
       </c>
     </row>
     <row r="17">
@@ -7784,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125.077</v>
+        <v>190.162</v>
       </c>
       <c r="C17" t="n">
-        <v>112.356</v>
+        <v>176.974</v>
       </c>
       <c r="D17" t="n">
-        <v>228.485</v>
+        <v>287.615</v>
       </c>
       <c r="E17" t="n">
-        <v>416.187</v>
+        <v>418.938</v>
       </c>
       <c r="F17" t="n">
-        <v>177.486</v>
+        <v>178.899</v>
       </c>
       <c r="G17" t="n">
-        <v>323.78</v>
+        <v>328.324</v>
       </c>
       <c r="H17" t="n">
-        <v>247.612</v>
+        <v>334.933</v>
       </c>
       <c r="I17" t="n">
-        <v>88.39100000000001</v>
+        <v>122.944</v>
       </c>
       <c r="J17" t="n">
-        <v>391.954</v>
+        <v>426.081</v>
       </c>
       <c r="K17" t="n">
-        <v>222.787</v>
+        <v>280.581</v>
       </c>
       <c r="L17" t="n">
-        <v>285.061</v>
+        <v>364.881</v>
       </c>
       <c r="M17" t="n">
-        <v>233.434</v>
+        <v>329.791</v>
       </c>
     </row>
     <row r="18">
@@ -7827,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.091</v>
+        <v>49.284</v>
       </c>
       <c r="C18" t="n">
-        <v>23.916</v>
+        <v>29.031</v>
       </c>
       <c r="D18" t="n">
-        <v>43.104</v>
+        <v>47.026</v>
       </c>
       <c r="E18" t="n">
-        <v>394.945</v>
+        <v>398.401</v>
       </c>
       <c r="F18" t="n">
-        <v>160.31</v>
+        <v>162.221</v>
       </c>
       <c r="G18" t="n">
-        <v>140.235</v>
+        <v>140.396</v>
       </c>
       <c r="H18" t="n">
-        <v>11.161</v>
+        <v>32.366</v>
       </c>
       <c r="I18" t="n">
-        <v>7.853</v>
+        <v>10.028</v>
       </c>
       <c r="J18" t="n">
-        <v>17.997</v>
+        <v>20.694</v>
       </c>
       <c r="K18" t="n">
-        <v>15.091</v>
+        <v>35.773</v>
       </c>
       <c r="L18" t="n">
-        <v>75.95</v>
+        <v>80.483</v>
       </c>
       <c r="M18" t="n">
-        <v>31.267</v>
+        <v>36.838</v>
       </c>
     </row>
     <row r="19">
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.448</v>
+        <v>23.853</v>
       </c>
       <c r="C19" t="n">
-        <v>6.977</v>
+        <v>10.437</v>
       </c>
       <c r="D19" t="n">
-        <v>26.126</v>
+        <v>29.286</v>
       </c>
       <c r="E19" t="n">
-        <v>383.979</v>
+        <v>385.916</v>
       </c>
       <c r="F19" t="n">
-        <v>154.366</v>
+        <v>154.628</v>
       </c>
       <c r="G19" t="n">
-        <v>121.046</v>
+        <v>122.902</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>3.76</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.267</v>
       </c>
       <c r="J19" t="n">
-        <v>1.539</v>
+        <v>3.56</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>7.721</v>
       </c>
       <c r="L19" t="n">
-        <v>8.343</v>
+        <v>10.242</v>
       </c>
       <c r="M19" t="n">
-        <v>3.769</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="20">
@@ -7940,7 +7940,7 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>37.744</v>
+        <v>70.63</v>
       </c>
       <c r="L20" t="n">
         <v>7.176</v>
@@ -7956,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111.631</v>
+        <v>151.843</v>
       </c>
       <c r="C21" t="n">
-        <v>115.156</v>
+        <v>155.286</v>
       </c>
       <c r="D21" t="n">
-        <v>24.665</v>
+        <v>44.554</v>
       </c>
       <c r="E21" t="n">
-        <v>206.255</v>
+        <v>211.495</v>
       </c>
       <c r="F21" t="n">
-        <v>84.27200000000001</v>
+        <v>84.84699999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>86.164</v>
+        <v>86.437</v>
       </c>
       <c r="H21" t="n">
-        <v>142.754</v>
+        <v>315.454</v>
       </c>
       <c r="I21" t="n">
-        <v>6.613</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>76.325</v>
+        <v>312.499</v>
       </c>
       <c r="K21" t="n">
-        <v>177.424</v>
+        <v>218.524</v>
       </c>
       <c r="L21" t="n">
-        <v>26.604</v>
+        <v>181.643</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>186.79</v>
+        <v>285.401</v>
       </c>
       <c r="C22" t="n">
-        <v>195.41</v>
+        <v>308.21</v>
       </c>
       <c r="D22" t="n">
-        <v>92.122</v>
+        <v>213.229</v>
       </c>
       <c r="E22" t="n">
-        <v>208.171</v>
+        <v>235.775</v>
       </c>
       <c r="F22" t="n">
-        <v>78.798</v>
+        <v>93.426</v>
       </c>
       <c r="G22" t="n">
-        <v>76.247</v>
+        <v>102.116</v>
       </c>
       <c r="H22" t="n">
-        <v>348.007</v>
+        <v>351.305</v>
       </c>
       <c r="I22" t="n">
         <v>218.601</v>
       </c>
       <c r="J22" t="n">
-        <v>424.852</v>
+        <v>447.263</v>
       </c>
       <c r="K22" t="n">
-        <v>236.359</v>
+        <v>245.673</v>
       </c>
       <c r="L22" t="n">
-        <v>337.703</v>
+        <v>351.869</v>
       </c>
       <c r="M22" t="n">
-        <v>191.242</v>
+        <v>345.778</v>
       </c>
     </row>
     <row r="23">
@@ -8045,19 +8045,19 @@
         <v>68.547</v>
       </c>
       <c r="C23" t="n">
-        <v>19.376</v>
+        <v>30.674</v>
       </c>
       <c r="D23" t="n">
-        <v>18.182</v>
+        <v>31.352</v>
       </c>
       <c r="E23" t="n">
-        <v>22.371</v>
+        <v>24.121</v>
       </c>
       <c r="F23" t="n">
-        <v>9.047000000000001</v>
+        <v>9.519</v>
       </c>
       <c r="G23" t="n">
-        <v>104.572</v>
+        <v>119.489</v>
       </c>
       <c r="H23" t="n">
         <v>21.522</v>
@@ -8066,16 +8066,16 @@
         <v>26.488</v>
       </c>
       <c r="J23" t="n">
-        <v>41.032</v>
+        <v>56.446</v>
       </c>
       <c r="K23" t="n">
         <v>20.712</v>
       </c>
       <c r="L23" t="n">
-        <v>32.652</v>
+        <v>32.653</v>
       </c>
       <c r="M23" t="n">
-        <v>35.127</v>
+        <v>35.369</v>
       </c>
     </row>
     <row r="24">
@@ -8085,22 +8085,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.954</v>
+        <v>15.531</v>
       </c>
       <c r="C24" t="n">
-        <v>16.375</v>
+        <v>25.396</v>
       </c>
       <c r="D24" t="n">
-        <v>12.773</v>
+        <v>21.851</v>
       </c>
       <c r="E24" t="n">
-        <v>25.242</v>
+        <v>25.831</v>
       </c>
       <c r="F24" t="n">
-        <v>10.442</v>
+        <v>10.472</v>
       </c>
       <c r="G24" t="n">
-        <v>123.314</v>
+        <v>125.227</v>
       </c>
       <c r="H24" t="n">
         <v>20.425</v>
@@ -8109,7 +8109,7 @@
         <v>25.756</v>
       </c>
       <c r="J24" t="n">
-        <v>45.773</v>
+        <v>47.703</v>
       </c>
       <c r="K24" t="n">
         <v>20.024</v>
@@ -8128,40 +8128,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12.981</v>
+        <v>13.563</v>
       </c>
       <c r="C25" t="n">
-        <v>12.953</v>
+        <v>17.647</v>
       </c>
       <c r="D25" t="n">
-        <v>9.634</v>
+        <v>14.358</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>12.001</v>
+        <v>12.027</v>
       </c>
       <c r="G25" t="n">
-        <v>72.93600000000001</v>
+        <v>86.818</v>
       </c>
       <c r="H25" t="n">
-        <v>18.957</v>
+        <v>19.045</v>
       </c>
       <c r="I25" t="n">
-        <v>4.237</v>
+        <v>11.804</v>
       </c>
       <c r="J25" t="n">
-        <v>22.559</v>
+        <v>25.778</v>
       </c>
       <c r="K25" t="n">
-        <v>16.936</v>
+        <v>23.603</v>
       </c>
       <c r="L25" t="n">
-        <v>16.135</v>
+        <v>27.658</v>
       </c>
       <c r="M25" t="n">
-        <v>7.419</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="26">
@@ -8174,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.094</v>
+        <v>11.235</v>
       </c>
       <c r="D26" t="n">
-        <v>3.837</v>
+        <v>4.172</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8186,22 +8186,22 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>94.541</v>
+        <v>96.301</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.428</v>
       </c>
       <c r="I26" t="n">
-        <v>0.706</v>
+        <v>1.551</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.274</v>
       </c>
       <c r="L26" t="n">
-        <v>0.322</v>
+        <v>6.246</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8214,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.649</v>
+        <v>21.634</v>
       </c>
       <c r="C27" t="n">
-        <v>13.973</v>
+        <v>31.771</v>
       </c>
       <c r="D27" t="n">
-        <v>11.88</v>
+        <v>27.277</v>
       </c>
       <c r="E27" t="n">
-        <v>22.689</v>
+        <v>24.271</v>
       </c>
       <c r="F27" t="n">
-        <v>11.417</v>
+        <v>12.223</v>
       </c>
       <c r="G27" t="n">
-        <v>89.908</v>
+        <v>109.659</v>
       </c>
       <c r="H27" t="n">
-        <v>32.159</v>
+        <v>33.252</v>
       </c>
       <c r="I27" t="n">
         <v>18.642</v>
       </c>
       <c r="J27" t="n">
-        <v>56.969</v>
+        <v>58.309</v>
       </c>
       <c r="K27" t="n">
-        <v>36.332</v>
+        <v>37.326</v>
       </c>
       <c r="L27" t="n">
-        <v>43.193</v>
+        <v>43.613</v>
       </c>
       <c r="M27" t="n">
-        <v>34.777</v>
+        <v>36.754</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.543</v>
+        <v>2.559</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,7 +8272,7 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>51.413</v>
+        <v>61.175</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -8300,40 +8300,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.112</v>
+        <v>4.367</v>
       </c>
       <c r="C29" t="n">
-        <v>1.371</v>
+        <v>5.664</v>
       </c>
       <c r="D29" t="n">
-        <v>0.36</v>
+        <v>3.613</v>
       </c>
       <c r="E29" t="n">
-        <v>21.824</v>
+        <v>22.205</v>
       </c>
       <c r="F29" t="n">
-        <v>10.523</v>
+        <v>10.799</v>
       </c>
       <c r="G29" t="n">
-        <v>65.325</v>
+        <v>71.66200000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8110000000000001</v>
+        <v>5.992</v>
       </c>
       <c r="I29" t="n">
-        <v>1.949</v>
+        <v>7.339</v>
       </c>
       <c r="J29" t="n">
-        <v>14.104</v>
+        <v>16.438</v>
       </c>
       <c r="K29" t="n">
-        <v>6.626</v>
+        <v>11.718</v>
       </c>
       <c r="L29" t="n">
-        <v>13.898</v>
+        <v>21.617</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="30">
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.815823364000001e-06</v>
+        <v>1.9401425521e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>4.743903376000001e-06</v>
+        <v>2.0893835209e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6920286084e-05</v>
+        <v>3.9740023801e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.431509913600001e-05</v>
+        <v>6.2573021316e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1398978756e-05</v>
+        <v>1.1917433889e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.229795562499999e-05</v>
+        <v>2.6922902724e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>6.906607236e-06</v>
+        <v>2.9110843161e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>9.556822080999999e-06</v>
+        <v>3.857296000000001e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.583448888999999e-06</v>
+        <v>6.1744795225e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.935805696e-06</v>
+        <v>3.49278721e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.466736641e-06</v>
+        <v>3.0470146249e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.543701841000001e-06</v>
+        <v>5.3138087289e-05</v>
       </c>
     </row>
     <row r="3">
@@ -8510,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.831836225000001e-06</v>
+        <v>5.555913443999999e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.348565444e-06</v>
+        <v>5.895782656e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.693758849e-06</v>
+        <v>1.1821560529e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7514408484e-05</v>
+        <v>4.8598643401e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.269155684e-06</v>
+        <v>7.3994404e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.479744e-07</v>
+        <v>1.8631158016e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.042579521e-06</v>
+        <v>1.8364586256e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.189081639999999e-07</v>
+        <v>1.1770514064e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.755843999999999e-07</v>
+        <v>1.9110574081e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.95701649e-07</v>
+        <v>1.6255995001e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.04261264e-07</v>
+        <v>6.194791848999999e-06</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.17847616e-07</v>
+        <v>1.445216256e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.90268164e-07</v>
+        <v>7.346268159999999e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.955319961e-06</v>
+        <v>2.440261201e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8982158721e-05</v>
+        <v>4.030457759999999e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.421524161e-06</v>
+        <v>5.483402499999999e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.731988100000001e-06</v>
+        <v>4.252735369e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>3.767481e-09</v>
+        <v>8.744120100000002e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.648131599999999e-08</v>
+        <v>2.860110399999999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.156e-08</v>
+        <v>2.46615616e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.940072900000001e-08</v>
+        <v>8.231734809999998e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0323369e-08</v>
+        <v>7.846416400000002e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0640644e-08</v>
+        <v>1.5876e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.53928969e-07</v>
+        <v>3.95811025e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9746116e-08</v>
+        <v>4.4249104e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.455880999999999e-07</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.043251839999999e-07</v>
+        <v>4.011322225000001e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>8.412558400000002e-08</v>
+        <v>1.090584576e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.304795040000001e-07</v>
+        <v>2.644942041e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>3.060505324900001e-05</v>
+        <v>3.3079970641e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.544138449000001e-06</v>
+        <v>8.030668996000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.370034489e-06</v>
+        <v>3.340262025e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.816464399999999e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.297056399999999e-08</v>
+        <v>4.875263999999999e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.46531025e-07</v>
+        <v>5.278749024999999e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357225e-07</v>
+        <v>1.0191104401e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>6.406401599999998e-08</v>
+        <v>2.847396321e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>8.478726400000002e-08</v>
+        <v>4.100097023999998e-06</v>
       </c>
     </row>
     <row r="7">
@@ -8680,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.264499413333334e-07</v>
+        <v>4.080772008333333e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>9.666228033333332e-08</v>
+        <v>4.529210785333334e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.412480533333332e-08</v>
+        <v>2.349704560333334e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.336848480333333e-06</v>
+        <v>3.842414408333332e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.438451887999999e-06</v>
+        <v>9.792310536333332e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.013752083333332e-07</v>
+        <v>1.573138401333333e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>6.274020544533334e-05</v>
+        <v>6.711205900833333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5840125803e-05</v>
+        <v>3.587992240833332e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.103705346133334e-05</v>
+        <v>5.521117812033333e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.502561026133334e-05</v>
+        <v>4.549062508033333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.246509174533333e-05</v>
+        <v>3.987673579199999e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3087026875e-05</v>
+        <v>5.583397763333333e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.593379600000002e-08</v>
+        <v>8.098200100000001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8732,19 +8732,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.641361881e-06</v>
+        <v>5.696324676e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9526988121e-05</v>
+        <v>2.0079456804e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>6.293073959999999e-07</v>
+        <v>7.132638490000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002001e-09</v>
+        <v>4.622500000000001e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.356634253333333e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.608033333333334e-11</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6.120408333333333e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.894741333333333e-07</v>
+        <v>8.044873763333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.693763605333333e-06</v>
+        <v>3.210551960333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>7.565232e-09</v>
+        <v>5.100563333333332e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>3.123413333333333e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.557541633333334e-08</v>
+        <v>2.870430083333333e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.895053333333333e-08</v>
+        <v>1.283802083333333e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.787777633333332e-08</v>
+        <v>5.946269281333335e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56211968e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1047683e-08</v>
       </c>
     </row>
     <row r="10">
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.582635520000001e-07</v>
+        <v>4.855224083333332e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.678393227e-06</v>
+        <v>1.847600833333333e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.136333333333333e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>7.301333333333332e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>1.227354133333333e-08</v>
+        <v>4.179840133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.103381333333333e-09</v>
+        <v>1.678440533333333e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8.833968e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.694216333333333e-09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8861,22 +8861,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.979238670000001e-07</v>
+        <v>4.445457869999999e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.304000705333334e-06</v>
+        <v>1.352435936333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.93548e-10</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.785960333333333e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>2.305633333333334e-11</v>
+        <v>4.652565333333334e-09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.694407053333334e-07</v>
+        <v>1.732192053333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.672002083333336e-07</v>
+        <v>7.841480013333335e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193221333333333e-09</v>
+        <v>2.507942533333333e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>2.663599413333334e-07</v>
+        <v>3.893557763333333e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8959,16 +8959,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.831083e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>6.097520833333334e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>9.402400833333334e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8287883e-08</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8847720369e-05</v>
+        <v>3.9371290084e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0466722249e-05</v>
+        <v>3.3152033929e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6356107881e-05</v>
+        <v>4.228328564099999e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8214058929e-05</v>
+        <v>5.4763488256e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.399349322500001e-05</v>
+        <v>5.8700082961e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.894972496399999e-05</v>
+        <v>2.2567851076e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1.5109818084e-05</v>
+        <v>2.843978688099999e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.531730904100001e-05</v>
+        <v>4.4431580944e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3694621841e-05</v>
+        <v>5.7603840064e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>5.0125388769e-05</v>
+        <v>6.0558811569e-05</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.122261538133334e-05</v>
+        <v>2.6874163827e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>7.502300176333332e-06</v>
+        <v>2.725465704533334e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8954549507e-05</v>
+        <v>3.804213542533334e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.743943900033334e-05</v>
+        <v>4.828519960033332e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3582217388e-05</v>
+        <v>1.420100800833334e-05</v>
       </c>
       <c r="G16" t="n">
         <v>6.382658568533334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>3.690064432033333e-05</v>
+        <v>4.356171400533333e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>7.062183045333335e-06</v>
+        <v>9.790025376333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5084002048e-05</v>
+        <v>6.150497356800002e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.734627242799999e-05</v>
+        <v>4.7200312467e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>3.946047078533333e-05</v>
+        <v>4.550195469633334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.341530760533333e-05</v>
+        <v>4.895226732033333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -9108,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.214751976333333e-06</v>
+        <v>1.205386208133333e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>4.207956912e-06</v>
+        <v>1.043993222533333e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>1.740179840833333e-05</v>
+        <v>2.757412940833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.773720632300001e-05</v>
+        <v>5.850301594799999e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0500426732e-05</v>
+        <v>1.0668284067e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.494449613333332e-05</v>
+        <v>3.593221632533333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.043723418133333e-05</v>
+        <v>3.739337149633333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>2.604322960333334e-06</v>
+        <v>5.038409045333333e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.120931270533334e-05</v>
+        <v>6.051500618700001e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>1.654468245633333e-05</v>
+        <v>2.6241899187e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>2.708659124033332e-05</v>
+        <v>4.437938138699999e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>1.816381078533333e-05</v>
+        <v>3.625403456033334e-05</v>
       </c>
     </row>
     <row r="18">
@@ -9151,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.777327603333333e-07</v>
+        <v>8.09637552e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.90658352e-07</v>
+        <v>2.80932987e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>6.193182719999999e-07</v>
+        <v>7.371482253333335e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.199385100833333e-05</v>
+        <v>5.290778560033334e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.566432033333334e-06</v>
+        <v>8.771884280333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.555285075000002e-06</v>
+        <v>6.570345605333333e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>4.152264033333332e-08</v>
+        <v>3.491859853333333e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>2.055653633333334e-08</v>
+        <v>3.352026133333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.07964003e-07</v>
+        <v>1.42747212e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>7.591276033333333e-08</v>
+        <v>4.265691763333335e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>1.922800833333333e-06</v>
+        <v>2.159171096333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>3.258750963333332e-07</v>
+        <v>4.523460813333334e-07</v>
       </c>
     </row>
     <row r="19">
@@ -9194,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.39373568e-07</v>
+        <v>1.89655203e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>1.622617633333334e-08</v>
+        <v>3.6310323e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.275226253333333e-07</v>
+        <v>2.85889932e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.914662414699999e-05</v>
+        <v>4.964371968533333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.942953985333334e-06</v>
+        <v>7.969939461333333e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.884044705333334e-06</v>
+        <v>5.034967201333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.408333333333333e-10</v>
+        <v>4.712533333333333e-09</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.557763e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>7.895070000000001e-10</v>
+        <v>4.224533333333334e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.987128033333334e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3201883e-08</v>
+        <v>3.4966188e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>4.735120333333334e-09</v>
+        <v>1.689813333333334e-08</v>
       </c>
     </row>
     <row r="20">
@@ -9264,7 +9264,7 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>4.748698453333333e-07</v>
+        <v>1.662865633333333e-06</v>
       </c>
       <c r="L20" t="n">
         <v>1.7164992e-08</v>
@@ -9280,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.153826720333333e-06</v>
+        <v>7.685432216333331e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>4.420301445333334e-06</v>
+        <v>8.037913932000002e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>2.027874083333333e-07</v>
+        <v>6.616863053333334e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.418037500833333e-05</v>
+        <v>1.491004500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.367256661333333e-06</v>
+        <v>2.399671136333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.474744965333333e-06</v>
+        <v>2.490451656333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>6.792901505333333e-06</v>
+        <v>3.317040870533334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>1.457725633333334e-08</v>
+        <v>1.536803333333333e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>1.941835208333333e-06</v>
+        <v>3.255187500033334e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>1.049309192533333e-05</v>
+        <v>1.591757952533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>2.35924272e-07</v>
+        <v>1.099805981633333e-05</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.163016803333333e-05</v>
+        <v>2.715124360033333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>1.272835603333333e-05</v>
+        <v>3.166446803333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>2.828820961333333e-06</v>
+        <v>1.515553548033333e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.444505508033333e-05</v>
+        <v>1.852995020833333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.069708268e-06</v>
+        <v>2.909472492e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.937868336333333e-06</v>
+        <v>3.475892485333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.036962401633334e-05</v>
+        <v>4.113840100833334e-05</v>
       </c>
       <c r="I22" t="n">
         <v>1.5928799067e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>6.016640730133331e-05</v>
+        <v>6.668139705633332e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.862185896033334e-05</v>
+        <v>2.0118407643e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>3.801443873633333e-05</v>
+        <v>4.127059772033335e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>1.219116752133333e-05</v>
+        <v>3.985414176133334e-05</v>
       </c>
     </row>
     <row r="23">
@@ -9369,19 +9369,19 @@
         <v>4.698691208999999e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>3.75429376e-06</v>
+        <v>9.408942760000001e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>3.30585124e-06</v>
+        <v>9.82947904e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>5.00461641e-06</v>
+        <v>5.81822641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>8.184820900000002e-07</v>
+        <v>9.0611361e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0935303184e-05</v>
+        <v>1.4277621121e-05</v>
       </c>
       <c r="H23" t="n">
         <v>4.63196484e-06</v>
@@ -9390,16 +9390,16 @@
         <v>7.016141440000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>1.683625024e-05</v>
+        <v>3.186150915999999e-05</v>
       </c>
       <c r="K23" t="n">
         <v>4.28986944e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066153104e-05</v>
+        <v>1.066218409e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>1.233906129000001e-05</v>
+        <v>1.250966161e-05</v>
       </c>
     </row>
     <row r="24">
@@ -9409,22 +9409,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19990116e-06</v>
+        <v>2.41211961e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>2.68140625e-06</v>
+        <v>6.449568160000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>1.63149529e-06</v>
+        <v>4.774662009999999e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.37158564e-06</v>
+        <v>6.67240561e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09035364e-06</v>
+        <v>1.09662784e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5206342596e-05</v>
+        <v>1.5681801529e-05</v>
       </c>
       <c r="H24" t="n">
         <v>4.171806250000001e-06</v>
@@ -9433,7 +9433,7 @@
         <v>6.633715360000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.095167529e-05</v>
+        <v>2.275576209e-05</v>
       </c>
       <c r="K24" t="n">
         <v>4.00960576e-06</v>
@@ -9452,40 +9452,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.68506361e-06</v>
+        <v>1.83954969e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.67780209e-06</v>
+        <v>3.11416609e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>9.281395600000001e-07</v>
+        <v>2.06152164e-06</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44024001e-06</v>
+        <v>1.44648729e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>5.319660096e-06</v>
+        <v>7.537365123999998e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.593678490000001e-06</v>
+        <v>3.627120250000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7952169e-07</v>
+        <v>1.39334416e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>5.089084810000001e-06</v>
+        <v>6.645052839999999e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>2.86828096e-06</v>
+        <v>5.571016090000001e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>2.60338225e-06</v>
+        <v>7.64964964e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>5.504156099999999e-07</v>
+        <v>3.58572096e-06</v>
       </c>
     </row>
     <row r="26">
@@ -9498,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.23076836e-06</v>
+        <v>1.26225225e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4722569e-07</v>
+        <v>1.7405584e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9510,22 +9510,22 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.938000681e-06</v>
+        <v>9.273882601e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.039184e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>4.984359999999999e-09</v>
+        <v>2.405601e-08</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>9.35089e-09</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.623076e-08</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03684e-09</v>
+        <v>3.901251600000001e-07</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9538,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.59997201e-06</v>
+        <v>4.680299560000001e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.95244729e-06</v>
+        <v>1.009396441e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.411344e-06</v>
+        <v>7.440347290000001e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>5.147907210000001e-06</v>
+        <v>5.890814410000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.30347889e-06</v>
+        <v>1.49401729e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>8.083448463999999e-06</v>
+        <v>1.2025096281e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>1.034201281e-05</v>
+        <v>1.105695504e-05</v>
       </c>
       <c r="I27" t="n">
         <v>3.47524164e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.245466961e-05</v>
+        <v>3.399939481e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.320014224e-05</v>
+        <v>1.393230276e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.865635249e-05</v>
+        <v>1.902093769e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.209439729e-05</v>
+        <v>1.350856516e-05</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.466849e-08</v>
+        <v>6.548481000000001e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,7 +9596,7 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.643296568999999e-06</v>
+        <v>3.742380625e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -9624,40 +9624,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.460544e-08</v>
+        <v>1.9070689e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>1.879641e-08</v>
+        <v>3.2080896e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>1.296e-09</v>
+        <v>1.3053769e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.762869760000001e-06</v>
+        <v>4.930620249999999e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.10733529e-06</v>
+        <v>1.16618401e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>4.267355625000001e-06</v>
+        <v>5.135442244e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>6.577210000000002e-09</v>
+        <v>3.5904064e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>3.798601e-08</v>
+        <v>5.3860921e-07</v>
       </c>
       <c r="J29" t="n">
-        <v>1.98922816e-06</v>
+        <v>2.70207844e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3903876e-07</v>
+        <v>1.37311524e-06</v>
       </c>
       <c r="L29" t="n">
-        <v>1.93154404e-06</v>
+        <v>4.67294689e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.946318399999999e-07</v>
       </c>
     </row>
     <row r="30">
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82.55800000000001</v>
+        <v>139.289</v>
       </c>
       <c r="C2" t="n">
-        <v>68.876</v>
+        <v>144.547</v>
       </c>
       <c r="D2" t="n">
-        <v>130.078</v>
+        <v>199.349</v>
       </c>
       <c r="E2" t="n">
-        <v>233.056</v>
+        <v>250.146</v>
       </c>
       <c r="F2" t="n">
-        <v>106.766</v>
+        <v>109.167</v>
       </c>
       <c r="G2" t="n">
-        <v>149.325</v>
+        <v>164.082</v>
       </c>
       <c r="H2" t="n">
-        <v>83.10599999999999</v>
+        <v>170.619</v>
       </c>
       <c r="I2" t="n">
-        <v>97.759</v>
+        <v>196.4</v>
       </c>
       <c r="J2" t="n">
-        <v>87.083</v>
+        <v>248.469</v>
       </c>
       <c r="K2" t="n">
-        <v>62.736</v>
+        <v>186.89</v>
       </c>
       <c r="L2" t="n">
-        <v>58.879</v>
+        <v>174.557</v>
       </c>
       <c r="M2" t="n">
-        <v>59.529</v>
+        <v>230.517</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53.215</v>
+        <v>74.538</v>
       </c>
       <c r="C3" t="n">
-        <v>48.462</v>
+        <v>76.78400000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>75.45699999999999</v>
+        <v>108.727</v>
       </c>
       <c r="E3" t="n">
-        <v>216.43</v>
+        <v>220.451</v>
       </c>
       <c r="F3" t="n">
-        <v>75.63</v>
+        <v>76.491</v>
       </c>
       <c r="G3" t="n">
-        <v>79.178</v>
+        <v>86.02</v>
       </c>
       <c r="H3" t="n">
-        <v>29.12</v>
+        <v>136.496</v>
       </c>
       <c r="I3" t="n">
-        <v>32.289</v>
+        <v>135.516</v>
       </c>
       <c r="J3" t="n">
-        <v>17.858</v>
+        <v>108.463</v>
       </c>
       <c r="K3" t="n">
-        <v>19.38</v>
+        <v>138.241</v>
       </c>
       <c r="L3" t="n">
-        <v>24.407</v>
+        <v>127.499</v>
       </c>
       <c r="M3" t="n">
-        <v>14.292</v>
+        <v>78.70699999999999</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.296</v>
+        <v>38.016</v>
       </c>
       <c r="C4" t="n">
-        <v>22.142</v>
+        <v>27.104</v>
       </c>
       <c r="D4" t="n">
-        <v>44.219</v>
+        <v>49.399</v>
       </c>
       <c r="E4" t="n">
-        <v>197.439</v>
+        <v>200.76</v>
       </c>
       <c r="F4" t="n">
-        <v>73.593</v>
+        <v>74.05</v>
       </c>
       <c r="G4" t="n">
-        <v>61.09</v>
+        <v>65.21299999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.941</v>
+        <v>9.351000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>5.134</v>
+        <v>3.563</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>15.704</v>
       </c>
       <c r="K4" t="n">
-        <v>6.277</v>
+        <v>28.691</v>
       </c>
       <c r="L4" t="n">
-        <v>3.213</v>
+        <v>8.858000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>3.262</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.813</v>
+        <v>19.895</v>
       </c>
       <c r="C5" t="n">
-        <v>5.273</v>
+        <v>6.652</v>
       </c>
       <c r="D5" t="n">
-        <v>18.073</v>
+        <v>18.554</v>
       </c>
       <c r="E5" t="n">
-        <v>195.367</v>
+        <v>195.073</v>
       </c>
       <c r="F5" t="n">
-        <v>94.544</v>
+        <v>93.86199999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>78.178</v>
+        <v>76.872</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.072</v>
+        <v>63.335</v>
       </c>
       <c r="C6" t="n">
-        <v>9.172000000000001</v>
+        <v>33.024</v>
       </c>
       <c r="D6" t="n">
-        <v>20.748</v>
+        <v>51.429</v>
       </c>
       <c r="E6" t="n">
-        <v>174.943</v>
+        <v>181.879</v>
       </c>
       <c r="F6" t="n">
-        <v>86.857</v>
+        <v>89.614</v>
       </c>
       <c r="G6" t="n">
-        <v>48.683</v>
+        <v>57.795</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4.262</v>
       </c>
       <c r="I6" t="n">
-        <v>5.742</v>
+        <v>22.08</v>
       </c>
       <c r="J6" t="n">
-        <v>12.105</v>
+        <v>72.655</v>
       </c>
       <c r="K6" t="n">
-        <v>11.65</v>
+        <v>100.951</v>
       </c>
       <c r="L6" t="n">
-        <v>8.004</v>
+        <v>53.361</v>
       </c>
       <c r="M6" t="n">
-        <v>9.208</v>
+        <v>64.032</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.768</v>
+        <v>110.645</v>
       </c>
       <c r="C7" t="n">
-        <v>17.029</v>
+        <v>116.566</v>
       </c>
       <c r="D7" t="n">
-        <v>16.804</v>
+        <v>83.959</v>
       </c>
       <c r="E7" t="n">
-        <v>83.729</v>
+        <v>107.365</v>
       </c>
       <c r="F7" t="n">
-        <v>159.108</v>
+        <v>171.397</v>
       </c>
       <c r="G7" t="n">
-        <v>42.475</v>
+        <v>68.69799999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>433.7</v>
+        <v>444.155</v>
       </c>
       <c r="I7" t="n">
-        <v>327.903</v>
+        <v>322.767</v>
       </c>
       <c r="J7" t="n">
-        <v>350.872</v>
+        <v>374.397</v>
       </c>
       <c r="K7" t="n">
-        <v>367.528</v>
+        <v>365.191</v>
       </c>
       <c r="L7" t="n">
-        <v>259.606</v>
+        <v>341.074</v>
       </c>
       <c r="M7" t="n">
-        <v>263.175</v>
+        <v>408.096</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.714</v>
+        <v>8.999000000000001</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.10899999999999</v>
+        <v>75.462</v>
       </c>
       <c r="F8" t="n">
-        <v>139.739</v>
+        <v>141.702</v>
       </c>
       <c r="G8" t="n">
-        <v>25.086</v>
+        <v>26.707</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.001</v>
+        <v>1.796</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>83.087</v>
+        <v>62.415</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10090,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>20.174</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.329</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.285</v>
       </c>
       <c r="E9" t="n">
-        <v>38.32</v>
+        <v>49.127</v>
       </c>
       <c r="F9" t="n">
-        <v>89.896</v>
+        <v>98.14100000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4.764</v>
+        <v>12.37</v>
       </c>
       <c r="H9" t="n">
-        <v>4.508</v>
+        <v>9.68</v>
       </c>
       <c r="I9" t="n">
-        <v>11.693</v>
+        <v>29.345</v>
       </c>
       <c r="J9" t="n">
-        <v>7.54</v>
+        <v>19.625</v>
       </c>
       <c r="K9" t="n">
-        <v>13.177</v>
+        <v>133.562</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>21.648</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.757</v>
       </c>
     </row>
     <row r="10">
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.784</v>
+        <v>38.165</v>
       </c>
       <c r="F10" t="n">
-        <v>70.959</v>
+        <v>74.45</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.476</v>
       </c>
       <c r="I10" t="n">
-        <v>6.068</v>
+        <v>10.515</v>
       </c>
       <c r="J10" t="n">
-        <v>2.512</v>
+        <v>7.096</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5.148</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -10185,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34.551</v>
+        <v>36.519</v>
       </c>
       <c r="F11" t="n">
-        <v>62.546</v>
+        <v>63.697</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.762</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.891</v>
       </c>
       <c r="J11" t="n">
-        <v>0.263</v>
+        <v>3.736</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.383</v>
+        <v>22.796</v>
       </c>
       <c r="F12" t="n">
-        <v>47.975</v>
+        <v>48.502</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10271,10 +10271,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.892</v>
+        <v>8.673999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>28.268</v>
+        <v>34.177</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.807</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>13.525</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>16.795</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>7.407</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>137.287</v>
+        <v>198.422</v>
       </c>
       <c r="C15" t="n">
-        <v>102.307</v>
+        <v>182.077</v>
       </c>
       <c r="D15" t="n">
-        <v>127.891</v>
+        <v>205.629</v>
       </c>
       <c r="E15" t="n">
-        <v>219.577</v>
+        <v>234.016</v>
       </c>
       <c r="F15" t="n">
-        <v>97.423</v>
+        <v>98.13800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>232.365</v>
+        <v>242.281</v>
       </c>
       <c r="H15" t="n">
-        <v>137.658</v>
+        <v>144.372</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>122.922</v>
+        <v>168.641</v>
       </c>
       <c r="K15" t="n">
-        <v>187.929</v>
+        <v>210.788</v>
       </c>
       <c r="L15" t="n">
-        <v>231.721</v>
+        <v>240.008</v>
       </c>
       <c r="M15" t="n">
-        <v>223.887</v>
+        <v>246.087</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>183.488</v>
+        <v>283.941</v>
       </c>
       <c r="C16" t="n">
-        <v>150.023</v>
+        <v>285.944</v>
       </c>
       <c r="D16" t="n">
-        <v>238.461</v>
+        <v>337.826</v>
       </c>
       <c r="E16" t="n">
-        <v>371.992</v>
+        <v>380.599</v>
       </c>
       <c r="F16" t="n">
-        <v>201.858</v>
+        <v>206.405</v>
       </c>
       <c r="G16" t="n">
-        <v>418.489</v>
+        <v>424.195</v>
       </c>
       <c r="H16" t="n">
-        <v>332.095</v>
+        <v>356.476</v>
       </c>
       <c r="I16" t="n">
-        <v>145.556</v>
+        <v>160.309</v>
       </c>
       <c r="J16" t="n">
-        <v>403.494</v>
+        <v>422.299</v>
       </c>
       <c r="K16" t="n">
-        <v>334.722</v>
+        <v>376.299</v>
       </c>
       <c r="L16" t="n">
-        <v>344.066</v>
+        <v>369.467</v>
       </c>
       <c r="M16" t="n">
-        <v>360.896</v>
+        <v>383.219</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>125.077</v>
+        <v>190.162</v>
       </c>
       <c r="C17" t="n">
-        <v>112.356</v>
+        <v>176.974</v>
       </c>
       <c r="D17" t="n">
-        <v>228.485</v>
+        <v>287.615</v>
       </c>
       <c r="E17" t="n">
-        <v>415.616</v>
+        <v>418.938</v>
       </c>
       <c r="F17" t="n">
-        <v>176.782</v>
+        <v>178.14</v>
       </c>
       <c r="G17" t="n">
-        <v>323.78</v>
+        <v>328.324</v>
       </c>
       <c r="H17" t="n">
-        <v>247.612</v>
+        <v>334.933</v>
       </c>
       <c r="I17" t="n">
-        <v>88.39100000000001</v>
+        <v>122.944</v>
       </c>
       <c r="J17" t="n">
-        <v>391.954</v>
+        <v>421.894</v>
       </c>
       <c r="K17" t="n">
-        <v>222.787</v>
+        <v>280.581</v>
       </c>
       <c r="L17" t="n">
-        <v>285.061</v>
+        <v>364.881</v>
       </c>
       <c r="M17" t="n">
-        <v>233.434</v>
+        <v>329.791</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.091</v>
+        <v>49.284</v>
       </c>
       <c r="C18" t="n">
-        <v>23.916</v>
+        <v>29.031</v>
       </c>
       <c r="D18" t="n">
-        <v>43.104</v>
+        <v>47.026</v>
       </c>
       <c r="E18" t="n">
-        <v>394.945</v>
+        <v>398.401</v>
       </c>
       <c r="F18" t="n">
-        <v>160.31</v>
+        <v>162.221</v>
       </c>
       <c r="G18" t="n">
-        <v>139.786</v>
+        <v>140.396</v>
       </c>
       <c r="H18" t="n">
-        <v>11.161</v>
+        <v>29.584</v>
       </c>
       <c r="I18" t="n">
-        <v>7.853</v>
+        <v>8.759</v>
       </c>
       <c r="J18" t="n">
-        <v>17.997</v>
+        <v>18.803</v>
       </c>
       <c r="K18" t="n">
-        <v>15.091</v>
+        <v>32.529</v>
       </c>
       <c r="L18" t="n">
-        <v>75.95</v>
+        <v>52.306</v>
       </c>
       <c r="M18" t="n">
-        <v>31.267</v>
+        <v>27.016</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20.448</v>
+        <v>23.853</v>
       </c>
       <c r="C19" t="n">
-        <v>6.977</v>
+        <v>10.437</v>
       </c>
       <c r="D19" t="n">
-        <v>26.126</v>
+        <v>29.286</v>
       </c>
       <c r="E19" t="n">
-        <v>383.979</v>
+        <v>385.916</v>
       </c>
       <c r="F19" t="n">
-        <v>154.366</v>
+        <v>153.59</v>
       </c>
       <c r="G19" t="n">
-        <v>121.046</v>
+        <v>122.902</v>
       </c>
       <c r="H19" t="n">
-        <v>0.65</v>
+        <v>3.177</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.101</v>
       </c>
       <c r="J19" t="n">
-        <v>1.539</v>
+        <v>1.914</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6.987</v>
       </c>
       <c r="L19" t="n">
-        <v>8.343</v>
+        <v>6.497</v>
       </c>
       <c r="M19" t="n">
-        <v>3.769</v>
+        <v>4.883</v>
       </c>
     </row>
     <row r="20">
@@ -10561,37 +10561,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>129.122</v>
+        <v>120.83</v>
       </c>
       <c r="C20" t="n">
-        <v>132.856</v>
+        <v>124.046</v>
       </c>
       <c r="D20" t="n">
-        <v>42.401</v>
+        <v>35.092</v>
       </c>
       <c r="E20" t="n">
-        <v>222.514</v>
+        <v>219.31</v>
       </c>
       <c r="F20" t="n">
-        <v>98.078</v>
+        <v>95.608</v>
       </c>
       <c r="G20" t="n">
-        <v>120.385</v>
+        <v>112.855</v>
       </c>
       <c r="H20" t="n">
-        <v>15.514</v>
+        <v>42.608</v>
       </c>
       <c r="I20" t="n">
-        <v>3.692</v>
+        <v>3.029</v>
       </c>
       <c r="J20" t="n">
-        <v>3.644</v>
+        <v>2.275</v>
       </c>
       <c r="K20" t="n">
-        <v>37.744</v>
+        <v>70.63</v>
       </c>
       <c r="L20" t="n">
-        <v>6.086</v>
+        <v>3.369</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>111.631</v>
+        <v>151.843</v>
       </c>
       <c r="C21" t="n">
-        <v>115.156</v>
+        <v>155.286</v>
       </c>
       <c r="D21" t="n">
-        <v>24.665</v>
+        <v>44.554</v>
       </c>
       <c r="E21" t="n">
-        <v>206.255</v>
+        <v>211.495</v>
       </c>
       <c r="F21" t="n">
-        <v>84.27200000000001</v>
+        <v>84.84699999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>85.378</v>
+        <v>86.437</v>
       </c>
       <c r="H21" t="n">
-        <v>142.754</v>
+        <v>315.454</v>
       </c>
       <c r="I21" t="n">
-        <v>6.612</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>76.325</v>
+        <v>282.613</v>
       </c>
       <c r="K21" t="n">
-        <v>177.424</v>
+        <v>217.762</v>
       </c>
       <c r="L21" t="n">
-        <v>26.604</v>
+        <v>181.643</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>186.79</v>
+        <v>285.401</v>
       </c>
       <c r="C22" t="n">
-        <v>195.41</v>
+        <v>308.21</v>
       </c>
       <c r="D22" t="n">
-        <v>92.122</v>
+        <v>213.229</v>
       </c>
       <c r="E22" t="n">
-        <v>208.171</v>
+        <v>235.775</v>
       </c>
       <c r="F22" t="n">
-        <v>78.798</v>
+        <v>93.426</v>
       </c>
       <c r="G22" t="n">
-        <v>76.247</v>
+        <v>102.116</v>
       </c>
       <c r="H22" t="n">
-        <v>348.007</v>
+        <v>337.765</v>
       </c>
       <c r="I22" t="n">
-        <v>206.965</v>
+        <v>194.998</v>
       </c>
       <c r="J22" t="n">
-        <v>422.406</v>
+        <v>436.149</v>
       </c>
       <c r="K22" t="n">
-        <v>236.359</v>
+        <v>245.437</v>
       </c>
       <c r="L22" t="n">
-        <v>337.703</v>
+        <v>351.869</v>
       </c>
       <c r="M22" t="n">
-        <v>191.242</v>
+        <v>345.778</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13.768</v>
+        <v>23.674</v>
       </c>
       <c r="C23" t="n">
-        <v>19.376</v>
+        <v>30.674</v>
       </c>
       <c r="D23" t="n">
-        <v>18.182</v>
+        <v>31.352</v>
       </c>
       <c r="E23" t="n">
-        <v>22.222</v>
+        <v>24.121</v>
       </c>
       <c r="F23" t="n">
-        <v>9.047000000000001</v>
+        <v>9.516999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>104.572</v>
+        <v>119.489</v>
       </c>
       <c r="H23" t="n">
-        <v>20.744</v>
+        <v>17.539</v>
       </c>
       <c r="I23" t="n">
-        <v>25.957</v>
+        <v>22.228</v>
       </c>
       <c r="J23" t="n">
-        <v>41.032</v>
+        <v>56.305</v>
       </c>
       <c r="K23" t="n">
-        <v>20.202</v>
+        <v>16.719</v>
       </c>
       <c r="L23" t="n">
-        <v>32.652</v>
+        <v>30.828</v>
       </c>
       <c r="M23" t="n">
-        <v>35.127</v>
+        <v>32.793</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10.954</v>
+        <v>15.531</v>
       </c>
       <c r="C24" t="n">
-        <v>16.375</v>
+        <v>25.396</v>
       </c>
       <c r="D24" t="n">
-        <v>12.773</v>
+        <v>21.851</v>
       </c>
       <c r="E24" t="n">
-        <v>25.242</v>
+        <v>25.831</v>
       </c>
       <c r="F24" t="n">
-        <v>10.405</v>
+        <v>10.456</v>
       </c>
       <c r="G24" t="n">
-        <v>122.373</v>
+        <v>125.227</v>
       </c>
       <c r="H24" t="n">
-        <v>19.39</v>
+        <v>16.58</v>
       </c>
       <c r="I24" t="n">
-        <v>24.773</v>
+        <v>20.535</v>
       </c>
       <c r="J24" t="n">
-        <v>45.773</v>
+        <v>46.069</v>
       </c>
       <c r="K24" t="n">
-        <v>19.559</v>
+        <v>16.215</v>
       </c>
       <c r="L24" t="n">
-        <v>29.922</v>
+        <v>27.037</v>
       </c>
       <c r="M24" t="n">
-        <v>30.504</v>
+        <v>28.073</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12.412</v>
+        <v>13.563</v>
       </c>
       <c r="C25" t="n">
-        <v>12.755</v>
+        <v>17.647</v>
       </c>
       <c r="D25" t="n">
-        <v>9.634</v>
+        <v>14.358</v>
       </c>
       <c r="E25" t="n">
-        <v>26.662</v>
+        <v>26.681</v>
       </c>
       <c r="F25" t="n">
-        <v>11.877</v>
+        <v>12.021</v>
       </c>
       <c r="G25" t="n">
-        <v>72.93600000000001</v>
+        <v>86.818</v>
       </c>
       <c r="H25" t="n">
-        <v>18.957</v>
+        <v>16.527</v>
       </c>
       <c r="I25" t="n">
-        <v>4.237</v>
+        <v>11.087</v>
       </c>
       <c r="J25" t="n">
-        <v>22.559</v>
+        <v>18.461</v>
       </c>
       <c r="K25" t="n">
-        <v>16.936</v>
+        <v>21.149</v>
       </c>
       <c r="L25" t="n">
-        <v>16.135</v>
+        <v>27.456</v>
       </c>
       <c r="M25" t="n">
-        <v>7.419</v>
+        <v>18.094</v>
       </c>
     </row>
     <row r="26">
@@ -10819,37 +10819,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.614</v>
+        <v>7.778</v>
       </c>
       <c r="C26" t="n">
-        <v>9.493</v>
+        <v>11.235</v>
       </c>
       <c r="D26" t="n">
-        <v>3.604</v>
+        <v>4.172</v>
       </c>
       <c r="E26" t="n">
-        <v>22.569</v>
+        <v>22.438</v>
       </c>
       <c r="F26" t="n">
-        <v>11.251</v>
+        <v>11.269</v>
       </c>
       <c r="G26" t="n">
-        <v>94.541</v>
+        <v>96.301</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="I26" t="n">
-        <v>0.641</v>
+        <v>1.551</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.756</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="L26" t="n">
-        <v>0.322</v>
+        <v>5.061</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.649</v>
+        <v>21.634</v>
       </c>
       <c r="C27" t="n">
-        <v>13.973</v>
+        <v>31.771</v>
       </c>
       <c r="D27" t="n">
-        <v>11.88</v>
+        <v>27.277</v>
       </c>
       <c r="E27" t="n">
-        <v>22.689</v>
+        <v>24.271</v>
       </c>
       <c r="F27" t="n">
-        <v>11.417</v>
+        <v>12.223</v>
       </c>
       <c r="G27" t="n">
-        <v>89.908</v>
+        <v>109.659</v>
       </c>
       <c r="H27" t="n">
-        <v>32.159</v>
+        <v>30.772</v>
       </c>
       <c r="I27" t="n">
-        <v>15.881</v>
+        <v>12.796</v>
       </c>
       <c r="J27" t="n">
-        <v>56.969</v>
+        <v>55.912</v>
       </c>
       <c r="K27" t="n">
-        <v>36.332</v>
+        <v>34.4</v>
       </c>
       <c r="L27" t="n">
-        <v>43.193</v>
+        <v>38.12</v>
       </c>
       <c r="M27" t="n">
-        <v>34.777</v>
+        <v>35.866</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.543</v>
+        <v>2.447</v>
       </c>
       <c r="C28" t="n">
-        <v>0.786</v>
+        <v>0.793</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.17</v>
+        <v>22.019</v>
       </c>
       <c r="F28" t="n">
-        <v>10.967</v>
+        <v>11.078</v>
       </c>
       <c r="G28" t="n">
-        <v>51.413</v>
+        <v>61.175</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.536</v>
+        <v>0.512</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.112</v>
+        <v>4.367</v>
       </c>
       <c r="C29" t="n">
-        <v>1.371</v>
+        <v>5.664</v>
       </c>
       <c r="D29" t="n">
-        <v>0.36</v>
+        <v>3.613</v>
       </c>
       <c r="E29" t="n">
-        <v>21.824</v>
+        <v>22.205</v>
       </c>
       <c r="F29" t="n">
-        <v>10.523</v>
+        <v>10.799</v>
       </c>
       <c r="G29" t="n">
-        <v>65.325</v>
+        <v>71.66200000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8110000000000001</v>
+        <v>4.842</v>
       </c>
       <c r="I29" t="n">
-        <v>1.949</v>
+        <v>6.896</v>
       </c>
       <c r="J29" t="n">
-        <v>14.104</v>
+        <v>11.724</v>
       </c>
       <c r="K29" t="n">
-        <v>6.626</v>
+        <v>9.029</v>
       </c>
       <c r="L29" t="n">
-        <v>13.898</v>
+        <v>17.681</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="30">
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.747</v>
+        <v>13.548</v>
       </c>
       <c r="F30" t="n">
-        <v>5.879</v>
+        <v>5.748</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.815823364000001e-06</v>
+        <v>1.9401425521e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>4.743903376000001e-06</v>
+        <v>2.0893835209e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6920286084e-05</v>
+        <v>3.9740023801e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.431509913600001e-05</v>
+        <v>6.2573021316e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1398978756e-05</v>
+        <v>1.1917433889e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.229795562499999e-05</v>
+        <v>2.6922902724e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>6.906607236e-06</v>
+        <v>2.9110843161e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>9.556822080999999e-06</v>
+        <v>3.857296000000001e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>7.583448888999999e-06</v>
+        <v>6.1736843961e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.935805696e-06</v>
+        <v>3.49278721e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>3.466736641e-06</v>
+        <v>3.0470146249e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.543701841000001e-06</v>
+        <v>5.3138087289e-05</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.831836225000001e-06</v>
+        <v>5.555913443999999e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.348565444e-06</v>
+        <v>5.895782656e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>5.693758849e-06</v>
+        <v>1.1821560529e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.68419449e-05</v>
+        <v>4.8598643401e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.719896899999999e-06</v>
+        <v>5.850873081e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.269155684e-06</v>
+        <v>7.3994404e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>8.479744e-07</v>
+        <v>1.8631158016e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.042579521e-06</v>
+        <v>1.8364586256e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.189081639999999e-07</v>
+        <v>1.1764222369e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.755843999999999e-07</v>
+        <v>1.9110574081e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>5.95701649e-07</v>
+        <v>1.6255995001e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>2.04261264e-07</v>
+        <v>6.194791848999999e-06</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.17847616e-07</v>
+        <v>1.445216256e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.90268164e-07</v>
+        <v>7.346268159999999e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.955319961e-06</v>
+        <v>2.440261201e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8982158721e-05</v>
+        <v>4.030457759999999e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.415929649000001e-06</v>
+        <v>5.483402499999999e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.731988100000001e-06</v>
+        <v>4.252735369e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>3.767481e-09</v>
+        <v>8.744120100000002e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>2.635795600000001e-08</v>
+        <v>1.2694969e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.156e-08</v>
+        <v>2.46615616e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.940072900000001e-08</v>
+        <v>8.231734809999998e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0323369e-08</v>
+        <v>7.846416400000002e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0640644e-08</v>
+        <v>1.5876e-07</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.53928969e-07</v>
+        <v>3.95811025e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7804529e-08</v>
+        <v>4.4249104e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.26633329e-07</v>
+        <v>3.442509159999999e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8168264689e-05</v>
+        <v>3.8053475329e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.938567936000002e-06</v>
+        <v>8.810075044000001e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>6.111799683999999e-06</v>
+        <v>5.909304383999999e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.043251839999999e-07</v>
+        <v>4.011322225000001e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>8.412558400000002e-08</v>
+        <v>1.090584576e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>4.304795040000001e-07</v>
+        <v>2.644942041e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>3.060505324900001e-05</v>
+        <v>3.3079970641e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.544138449000001e-06</v>
+        <v>8.030668996000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.370034489e-06</v>
+        <v>3.340262025e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.816464399999999e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.297056399999999e-08</v>
+        <v>4.875263999999999e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.46531025e-07</v>
+        <v>5.278749024999999e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>1.357225e-07</v>
+        <v>1.0191104401e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>6.406401599999998e-08</v>
+        <v>2.847396321e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>8.478726400000002e-08</v>
+        <v>4.100097023999998e-06</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.264499413333334e-07</v>
+        <v>4.080772008333333e-06</v>
       </c>
       <c r="C7" t="n">
-        <v>9.666228033333332e-08</v>
+        <v>4.529210785333334e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>9.412480533333332e-08</v>
+        <v>2.349704560333334e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>2.336848480333333e-06</v>
+        <v>3.842414408333332e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>8.438451887999999e-06</v>
+        <v>9.792310536333332e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>6.013752083333332e-07</v>
+        <v>1.573138401333333e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>6.269856333333332e-05</v>
+        <v>6.575788800833332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5840125803e-05</v>
+        <v>3.472617876299999e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.103705346133334e-05</v>
+        <v>4.672437120299999e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>4.502561026133334e-05</v>
+        <v>4.445482216033334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>2.246509174533333e-05</v>
+        <v>3.877715782533333e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3087026875e-05</v>
+        <v>5.5514115072e-05</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.593379600000002e-08</v>
+        <v>8.098200100000001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.641361881e-06</v>
+        <v>5.694513444e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9526988121e-05</v>
+        <v>2.0079456804e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>6.293073959999999e-07</v>
+        <v>7.132638490000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002001e-09</v>
+        <v>3.225616e-09</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.903449569000001e-06</v>
+        <v>3.895632225e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11414,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.356634253333333e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.608033333333334e-11</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>6.120408333333333e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.894741333333333e-07</v>
+        <v>8.044873763333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.693763605333333e-06</v>
+        <v>3.210551960333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>7.565232e-09</v>
+        <v>5.100563333333332e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>3.123413333333333e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.557541633333334e-08</v>
+        <v>2.870430083333333e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.895053333333333e-08</v>
+        <v>1.283802083333333e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>5.787777633333332e-08</v>
+        <v>5.946269281333335e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56211968e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.1047683e-08</v>
       </c>
     </row>
     <row r="10">
@@ -11466,28 +11466,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.582635520000001e-07</v>
+        <v>4.855224083333332e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.678393227e-06</v>
+        <v>1.847600833333333e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.136333333333333e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>7.261919999999999e-10</v>
       </c>
       <c r="I10" t="n">
-        <v>1.227354133333333e-08</v>
+        <v>3.6855075e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.103381333333333e-09</v>
+        <v>1.678440533333333e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8.833968e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.694216333333333e-09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -11509,22 +11509,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.979238670000001e-07</v>
+        <v>4.445457869999999e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.304000705333334e-06</v>
+        <v>1.352435936333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.93548e-10</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.785960333333333e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>2.305633333333334e-11</v>
+        <v>4.652565333333334e-09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.66999563e-07</v>
+        <v>1.732192053333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.672002083333336e-07</v>
+        <v>7.841480013333335e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.193221333333333e-09</v>
+        <v>2.507942533333333e-08</v>
       </c>
       <c r="F13" t="n">
-        <v>2.663599413333334e-07</v>
+        <v>3.893557763333333e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11607,16 +11607,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>4.831083e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>6.097520833333334e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>9.402400833333334e-08</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8287883e-08</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8847720369e-05</v>
+        <v>3.9371290084e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0466722249e-05</v>
+        <v>3.3152033929e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6356107881e-05</v>
+        <v>4.228328564099999e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8214058929e-05</v>
+        <v>5.4763488256e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.491240929e-06</v>
+        <v>9.631067044e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.399349322500001e-05</v>
+        <v>5.8700082961e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.894972496399999e-05</v>
+        <v>2.0843274384e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1.5109818084e-05</v>
+        <v>2.843978688099999e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.531730904100001e-05</v>
+        <v>4.4431580944e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3694621841e-05</v>
+        <v>5.7603840064e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>5.0125388769e-05</v>
+        <v>6.0558811569e-05</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.122261538133334e-05</v>
+        <v>2.6874163827e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>7.502300176333332e-06</v>
+        <v>2.725465704533334e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8954549507e-05</v>
+        <v>3.804213542533334e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.612601602133335e-05</v>
+        <v>4.828519960033332e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3582217388e-05</v>
+        <v>1.420100800833334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>5.837768104033333e-05</v>
+        <v>5.998046600833333e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>3.676236300833334e-05</v>
+        <v>4.235837952533334e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>7.062183045333335e-06</v>
+        <v>8.566325160333335e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.426913601200001e-05</v>
+        <v>5.944548180033333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.734627242799999e-05</v>
+        <v>4.7200312467e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>3.946047078533333e-05</v>
+        <v>4.550195469633334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.341530760533333e-05</v>
+        <v>4.895226732033333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.214751976333333e-06</v>
+        <v>1.205386208133333e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>4.207956912e-06</v>
+        <v>1.043993222533333e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>1.740179840833333e-05</v>
+        <v>2.757412940833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.757888648533332e-05</v>
+        <v>5.850301594799999e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.041729184133334e-05</v>
+        <v>1.05779532e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.494449613333332e-05</v>
+        <v>3.593221632533333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.043723418133333e-05</v>
+        <v>3.739337149633333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>2.604322960333334e-06</v>
+        <v>5.038409045333333e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.120931270533334e-05</v>
+        <v>5.933151574533333e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>1.654468245633333e-05</v>
+        <v>2.6241899187e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>2.708659124033332e-05</v>
+        <v>4.437938138699999e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>1.816381078533333e-05</v>
+        <v>3.625403456033334e-05</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.777327603333333e-07</v>
+        <v>8.09637552e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.90658352e-07</v>
+        <v>2.80932987e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>6.193182719999999e-07</v>
+        <v>7.371482253333335e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.199385100833333e-05</v>
+        <v>5.290778560033334e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.566432033333334e-06</v>
+        <v>8.771884280333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.513375265333333e-06</v>
+        <v>6.570345605333333e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>4.152264033333332e-08</v>
+        <v>2.917376853333333e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>2.055653633333334e-08</v>
+        <v>2.557336033333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.07964003e-07</v>
+        <v>1.178509363333333e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>7.591276033333333e-08</v>
+        <v>3.52711947e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>1.922800833333333e-06</v>
+        <v>9.119725453333332e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.258750963333332e-07</v>
+        <v>2.432880853333333e-07</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.39373568e-07</v>
+        <v>1.89655203e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>1.622617633333334e-08</v>
+        <v>3.6310323e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>2.275226253333333e-07</v>
+        <v>2.85889932e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.914662414699999e-05</v>
+        <v>4.964371968533333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.942953985333334e-06</v>
+        <v>7.863296033333334e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.884044705333334e-06</v>
+        <v>5.034967201333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.408333333333333e-10</v>
+        <v>3.364443000000001e-09</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.205400333333334e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>7.895070000000001e-10</v>
+        <v>1.221132e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.6272723e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3201883e-08</v>
+        <v>1.407033633333333e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>4.735120333333334e-09</v>
+        <v>7.947896333333335e-09</v>
       </c>
     </row>
     <row r="20">
@@ -11885,37 +11885,37 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.557496961333335e-06</v>
+        <v>4.866629633333332e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>5.883572245333334e-06</v>
+        <v>5.129136705333333e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>5.992816003333334e-07</v>
+        <v>4.104828213333333e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.650416006533334e-05</v>
+        <v>1.603229203333334e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.206431361333333e-06</v>
+        <v>3.046963221333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>4.830849408333334e-06</v>
+        <v>4.245417008333334e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>8.022806533333333e-08</v>
+        <v>6.051472213333333e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>4.543621333333333e-09</v>
+        <v>3.058280333333333e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>4.426245333333334e-09</v>
+        <v>1.725208333333333e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>4.748698453333333e-07</v>
+        <v>1.662865633333333e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>1.234646533333334e-08</v>
+        <v>3.783387e-09</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.153826720333333e-06</v>
+        <v>7.685432216333331e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>4.420301445333334e-06</v>
+        <v>8.037913932000002e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>2.027874083333333e-07</v>
+        <v>6.616863053333334e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.418037500833333e-05</v>
+        <v>1.491004500833333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.367256661333333e-06</v>
+        <v>2.399671136333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.429800961333333e-06</v>
+        <v>2.490451656333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>6.792901505333333e-06</v>
+        <v>3.317040870533334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4572848e-08</v>
+        <v>1.536803333333333e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>1.941835208333333e-06</v>
+        <v>2.662336925633333e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>1.049309192533333e-05</v>
+        <v>1.580676288133333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>2.35924272e-07</v>
+        <v>1.099805981633333e-05</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.163016803333333e-05</v>
+        <v>2.715124360033333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>1.272835603333333e-05</v>
+        <v>3.166446803333333e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>2.828820961333333e-06</v>
+        <v>1.515553548033333e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.444505508033333e-05</v>
+        <v>1.852995020833333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.069708268e-06</v>
+        <v>2.909472492e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.937868336333333e-06</v>
+        <v>3.475892485333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.036962401633334e-05</v>
+        <v>3.802839840833333e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.427817040833333e-05</v>
+        <v>1.267474000133333e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>5.9475609612e-05</v>
+        <v>6.3408650067e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.862185896033334e-05</v>
+        <v>2.007977365633334e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>3.801443873633333e-05</v>
+        <v>4.127059772033335e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>1.219116752133333e-05</v>
+        <v>3.985414176133334e-05</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.89557824e-06</v>
+        <v>5.60458276e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>3.75429376e-06</v>
+        <v>9.408942760000001e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>3.30585124e-06</v>
+        <v>9.82947904e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>4.938172840000001e-06</v>
+        <v>5.81822641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>8.184820900000002e-07</v>
+        <v>9.057328899999998e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0935303184e-05</v>
+        <v>1.4277621121e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>4.30313536e-06</v>
+        <v>3.076165210000001e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>6.737658490000001e-06</v>
+        <v>4.940839840000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>1.683625024e-05</v>
+        <v>3.170253025e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>4.08120804e-06</v>
+        <v>2.79524961e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066153104e-05</v>
+        <v>9.503655839999998e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.233906129000001e-05</v>
+        <v>1.075380849e-05</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.19990116e-06</v>
+        <v>2.41211961e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>2.68140625e-06</v>
+        <v>6.449568160000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>1.63149529e-06</v>
+        <v>4.774662009999999e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.37158564e-06</v>
+        <v>6.67240561e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.08264025e-06</v>
+        <v>1.09327936e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4975151129e-05</v>
+        <v>1.5681801529e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>3.759721000000001e-06</v>
+        <v>2.748963999999999e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>6.13701529e-06</v>
+        <v>4.21686225e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.095167529e-05</v>
+        <v>2.122352761e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.82554481e-06</v>
+        <v>2.62926225e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>8.953260840000001e-06</v>
+        <v>7.309993689999999e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>9.30494016e-06</v>
+        <v>7.88093329e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.54057744e-06</v>
+        <v>1.83954969e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.62690025e-06</v>
+        <v>3.11416609e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>9.281395600000001e-07</v>
+        <v>2.06152164e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>7.108622439999999e-06</v>
+        <v>7.118757610000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.41063129e-06</v>
+        <v>1.44504441e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>5.319660096e-06</v>
+        <v>7.537365123999998e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.593678490000001e-06</v>
+        <v>2.73141729e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7952169e-07</v>
+        <v>1.22921569e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>5.089084810000001e-06</v>
+        <v>3.408085209999999e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>2.86828096e-06</v>
+        <v>4.472802010000001e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>2.60338225e-06</v>
+        <v>7.538319360000001e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>5.504156099999999e-07</v>
+        <v>3.273928360000001e-06</v>
       </c>
     </row>
     <row r="26">
@@ -12143,37 +12143,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.797299600000001e-07</v>
+        <v>6.049728399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>9.011704899999999e-07</v>
+        <v>1.26225225e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2988816e-07</v>
+        <v>1.7405584e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.093597609999999e-06</v>
+        <v>5.03463844e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.26585001e-06</v>
+        <v>1.26990361e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.938000681e-06</v>
+        <v>9.273882601e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.012036e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>4.10881e-09</v>
+        <v>2.405601e-08</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>5.715360000000001e-09</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.53009e-09</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03684e-09</v>
+        <v>2.5613721e-07</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.59997201e-06</v>
+        <v>4.680299560000001e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>1.95244729e-06</v>
+        <v>1.009396441e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.411344e-06</v>
+        <v>7.440347290000001e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>5.147907210000001e-06</v>
+        <v>5.890814410000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.30347889e-06</v>
+        <v>1.49401729e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>8.083448463999999e-06</v>
+        <v>1.2025096281e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>1.034201281e-05</v>
+        <v>9.469159839999999e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>2.52206161e-06</v>
+        <v>1.63737616e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.245466961e-05</v>
+        <v>3.126151743999999e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.320014224e-05</v>
+        <v>1.18336e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>1.865635249e-05</v>
+        <v>1.453134399999999e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.209439729e-05</v>
+        <v>1.286369956e-05</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.466849e-08</v>
+        <v>5.987809e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>6.17796e-09</v>
+        <v>6.288490000000001e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.915089000000001e-06</v>
+        <v>4.848363609999998e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.20275089e-06</v>
+        <v>1.22722084e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>2.643296568999999e-06</v>
+        <v>3.742380625e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.87296e-09</v>
+        <v>2.62144e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.460544e-08</v>
+        <v>1.9070689e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>1.879641e-08</v>
+        <v>3.2080896e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>1.296e-09</v>
+        <v>1.3053769e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.762869760000001e-06</v>
+        <v>4.930620249999999e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.10733529e-06</v>
+        <v>1.16618401e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>4.267355625000001e-06</v>
+        <v>5.135442244e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>6.577210000000002e-09</v>
+        <v>2.3444964e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>3.798601e-08</v>
+        <v>4.7554816e-07</v>
       </c>
       <c r="J29" t="n">
-        <v>1.98922816e-06</v>
+        <v>1.37452176e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3903876e-07</v>
+        <v>8.152284100000001e-07</v>
       </c>
       <c r="L29" t="n">
-        <v>1.93154404e-06</v>
+        <v>3.126177610000001e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.798410000000001e-07</v>
       </c>
     </row>
     <row r="30">
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.88980009e-06</v>
+        <v>1.83548304e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.4562641e-07</v>
+        <v>3.303950400000001e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="I2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="J2" t="n">
-        <v>0.041319</v>
+        <v>0.123958</v>
       </c>
       <c r="K2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M2" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="3">
@@ -12482,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="J3" t="n">
-        <v>0.041319</v>
+        <v>0.122569</v>
       </c>
       <c r="K3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M3" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.038889</v>
+        <v>0.124653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="I4" t="n">
-        <v>0.040625</v>
+        <v>0.051042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="K4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M4" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="5">
@@ -12568,10 +12568,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001042</v>
+        <v>0.124653</v>
       </c>
       <c r="D5" t="n">
         <v>0.000694</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="J6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="K6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M6" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="7">
@@ -12652,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C7" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D7" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F7" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G7" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.039583</v>
+        <v>0.080556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.040625</v>
+        <v>0.045833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.041319</v>
+        <v>0.047569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.041319</v>
+        <v>0.061806</v>
       </c>
       <c r="L7" t="n">
-        <v>0.041319</v>
+        <v>0.08784699999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.041319</v>
+        <v>0.103472</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.038194</v>
+        <v>0.121528</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12704,19 +12704,19 @@
         <v>0.003472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.038194</v>
+        <v>0.111111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.038194</v>
+        <v>0.121528</v>
       </c>
       <c r="G8" t="n">
-        <v>0.038194</v>
+        <v>0.121528</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.038194</v>
+        <v>0.100694</v>
       </c>
       <c r="J8" t="n">
         <v>0.003472</v>
@@ -12738,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="J9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="10">
@@ -12790,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F10" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000347</v>
+        <v>0.123958</v>
       </c>
       <c r="I10" t="n">
-        <v>0.041319</v>
+        <v>0.08437500000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12833,22 +12833,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.124653</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.124653</v>
       </c>
       <c r="J11" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12876,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="F12" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12919,10 +12919,10 @@
         <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F13" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G13" t="n">
         <v>0.000347</v>
@@ -12931,16 +12931,16 @@
         <v>0.000347</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000347</v>
+        <v>0.124653</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H15" t="n">
-        <v>0.041319</v>
+        <v>0.046528</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="K15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M15" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.010764</v>
+        <v>0.124653</v>
       </c>
       <c r="F16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G16" t="n">
         <v>0.021875</v>
       </c>
       <c r="H16" t="n">
-        <v>0.035069</v>
+        <v>0.076389</v>
       </c>
       <c r="I16" t="n">
-        <v>0.041319</v>
+        <v>0.060764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.023611</v>
+        <v>0.07256899999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M16" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="17">
@@ -13080,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001042</v>
+        <v>0.101042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="I17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="J17" t="n">
-        <v>0.041319</v>
+        <v>0.100694</v>
       </c>
       <c r="K17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M17" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="18">
@@ -13123,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C18" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D18" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E18" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F18" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001389</v>
+        <v>0.124653</v>
       </c>
       <c r="H18" t="n">
-        <v>0.041319</v>
+        <v>0.092361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.041319</v>
+        <v>0.073958</v>
       </c>
       <c r="J18" t="n">
-        <v>0.041319</v>
+        <v>0.064236</v>
       </c>
       <c r="K18" t="n">
-        <v>0.041319</v>
+        <v>0.088542</v>
       </c>
       <c r="L18" t="n">
-        <v>0.041319</v>
+        <v>0.053125</v>
       </c>
       <c r="M18" t="n">
-        <v>0.041319</v>
+        <v>0.061458</v>
       </c>
     </row>
     <row r="19">
@@ -13166,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C19" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D19" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E19" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F19" t="n">
-        <v>0.041319</v>
+        <v>0.044792</v>
       </c>
       <c r="G19" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H19" t="n">
-        <v>0.041319</v>
+        <v>0.092014</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000347</v>
+        <v>0.100347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.041319</v>
+        <v>0.1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.000347</v>
+        <v>0.093056</v>
       </c>
       <c r="L19" t="n">
-        <v>0.041319</v>
+        <v>0.052431</v>
       </c>
       <c r="M19" t="n">
-        <v>0.041319</v>
+        <v>0.067708</v>
       </c>
     </row>
     <row r="20">
@@ -13236,7 +13236,7 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="L20" t="n">
         <v>0.026736</v>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005903</v>
+        <v>0.124653</v>
       </c>
       <c r="H21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="I21" t="n">
-        <v>0.040972</v>
+        <v>0.124653</v>
       </c>
       <c r="J21" t="n">
-        <v>0.041319</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.041319</v>
+        <v>0.101042</v>
       </c>
       <c r="L21" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H22" t="n">
-        <v>0.041319</v>
+        <v>0.052431</v>
       </c>
       <c r="I22" t="n">
         <v>0.021181</v>
       </c>
       <c r="J22" t="n">
-        <v>0.022222</v>
+        <v>0.073958</v>
       </c>
       <c r="K22" t="n">
-        <v>0.041319</v>
+        <v>0.118403</v>
       </c>
       <c r="L22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="M22" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
     </row>
     <row r="23">
@@ -13341,19 +13341,19 @@
         <v>0.028819</v>
       </c>
       <c r="C23" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D23" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="F23" t="n">
-        <v>0.041319</v>
+        <v>0.123958</v>
       </c>
       <c r="G23" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H23" t="n">
         <v>0.033681</v>
@@ -13362,16 +13362,16 @@
         <v>0.022222</v>
       </c>
       <c r="J23" t="n">
-        <v>0.041319</v>
+        <v>0.117708</v>
       </c>
       <c r="K23" t="n">
         <v>0.031944</v>
       </c>
       <c r="L23" t="n">
-        <v>0.041319</v>
+        <v>0.042014</v>
       </c>
       <c r="M23" t="n">
-        <v>0.041319</v>
+        <v>0.045486</v>
       </c>
     </row>
     <row r="24">
@@ -13381,22 +13381,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C24" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D24" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E24" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F24" t="n">
-        <v>0.000347</v>
+        <v>0.080208</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="H24" t="n">
         <v>0.024306</v>
@@ -13405,7 +13405,7 @@
         <v>0.017361</v>
       </c>
       <c r="J24" t="n">
-        <v>0.041319</v>
+        <v>0.09375</v>
       </c>
       <c r="K24" t="n">
         <v>0.030556</v>
@@ -13424,40 +13424,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001042</v>
+        <v>0.124653</v>
       </c>
       <c r="D25" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000694</v>
+        <v>0.106597</v>
       </c>
       <c r="G25" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H25" t="n">
-        <v>0.041319</v>
+        <v>0.043403</v>
       </c>
       <c r="I25" t="n">
-        <v>0.041319</v>
+        <v>0.092014</v>
       </c>
       <c r="J25" t="n">
-        <v>0.041319</v>
+        <v>0.054167</v>
       </c>
       <c r="K25" t="n">
-        <v>0.041319</v>
+        <v>0.080208</v>
       </c>
       <c r="L25" t="n">
-        <v>0.041319</v>
+        <v>0.115625</v>
       </c>
       <c r="M25" t="n">
-        <v>0.041319</v>
+        <v>0.103472</v>
       </c>
     </row>
     <row r="26">
@@ -13470,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.010069</v>
+        <v>0.124653</v>
       </c>
       <c r="D26" t="n">
-        <v>0.000694</v>
+        <v>0.124653</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13482,22 +13482,22 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000347</v>
+        <v>0.08472200000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.012153</v>
+        <v>0.124653</v>
       </c>
       <c r="J26" t="n">
-        <v>0.000347</v>
+        <v>0.104167</v>
       </c>
       <c r="K26" t="n">
-        <v>0.000347</v>
+        <v>0.072917</v>
       </c>
       <c r="L26" t="n">
-        <v>0.041319</v>
+        <v>0.089931</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C27" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="D27" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E27" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="F27" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G27" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H27" t="n">
-        <v>0.041319</v>
+        <v>0.07083299999999999</v>
       </c>
       <c r="I27" t="n">
         <v>0.015278</v>
       </c>
       <c r="J27" t="n">
-        <v>0.041319</v>
+        <v>0.067014</v>
       </c>
       <c r="K27" t="n">
-        <v>0.041319</v>
+        <v>0.057639</v>
       </c>
       <c r="L27" t="n">
-        <v>0.041319</v>
+        <v>0.043403</v>
       </c>
       <c r="M27" t="n">
-        <v>0.041319</v>
+        <v>0.057639</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.041319</v>
+        <v>0.052431</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,7 +13568,7 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
@@ -13596,40 +13596,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="C29" t="n">
-        <v>0.041319</v>
+        <v>0.124306</v>
       </c>
       <c r="D29" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="E29" t="n">
-        <v>0.041319</v>
+        <v>0.123958</v>
       </c>
       <c r="F29" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="G29" t="n">
-        <v>0.041319</v>
+        <v>0.124653</v>
       </c>
       <c r="H29" t="n">
-        <v>0.041319</v>
+        <v>0.092708</v>
       </c>
       <c r="I29" t="n">
-        <v>0.041319</v>
+        <v>0.093056</v>
       </c>
       <c r="J29" t="n">
-        <v>0.041319</v>
+        <v>0.058333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.041319</v>
+        <v>0.08819399999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>0.041319</v>
+        <v>0.077431</v>
       </c>
       <c r="M29" t="n">
-        <v>0.000347</v>
+        <v>0.117708</v>
       </c>
     </row>
     <row r="30">

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.109</v>
+        <v>0.002</v>
       </c>
       <c r="C2" t="n">
-        <v>0.096</v>
+        <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.254</v>
+        <v>0.007</v>
       </c>
       <c r="E2" t="n">
-        <v>0.608</v>
+        <v>0.06</v>
       </c>
       <c r="F2" t="n">
-        <v>0.124</v>
+        <v>0.013</v>
       </c>
       <c r="G2" t="n">
-        <v>0.253</v>
+        <v>0.024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.138</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039</v>
+        <v>0.002</v>
       </c>
       <c r="C3" t="n">
-        <v>0.036</v>
+        <v>0.001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08</v>
+        <v>0.004</v>
       </c>
       <c r="E3" t="n">
-        <v>0.511</v>
+        <v>0.055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.062</v>
+        <v>0.007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.006</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.058</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.041</v>
+        <v>0.004</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1941,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.41</v>
+        <v>0.044</v>
       </c>
       <c r="F5" t="n">
-        <v>0.096</v>
+        <v>0.01</v>
       </c>
       <c r="G5" t="n">
-        <v>0.065</v>
+        <v>0.007</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.336</v>
+        <v>0.034</v>
       </c>
       <c r="F6" t="n">
-        <v>0.082</v>
+        <v>0.008</v>
       </c>
       <c r="G6" t="n">
-        <v>0.028</v>
+        <v>0.002</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.029</v>
+        <v>0.002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.094</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.646</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>0.369</v>
+        <v>0.03</v>
       </c>
       <c r="J7" t="n">
-        <v>0.416</v>
+        <v>0.001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.457</v>
+        <v>0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>0.284</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.059</v>
+        <v>0.004</v>
       </c>
       <c r="F8" t="n">
-        <v>0.203</v>
+        <v>0.014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.063</v>
+        <v>0.006</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2153,13 +2153,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.019</v>
+        <v>0.002</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.263</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.177</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.246</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.536</v>
+        <v>0.051</v>
       </c>
       <c r="F15" t="n">
-        <v>0.103</v>
+        <v>0.011</v>
       </c>
       <c r="G15" t="n">
-        <v>0.594</v>
+        <v>0.06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.185</v>
+        <v>0.001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.356</v>
+        <v>0.003</v>
       </c>
       <c r="L15" t="n">
-        <v>0.502</v>
+        <v>0.007</v>
       </c>
       <c r="M15" t="n">
-        <v>0.49</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.167</v>
+        <v>0.004</v>
       </c>
       <c r="C16" t="n">
-        <v>0.136</v>
+        <v>0.002</v>
       </c>
       <c r="D16" t="n">
-        <v>0.262</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>0.502</v>
+        <v>0.055</v>
       </c>
       <c r="F16" t="n">
-        <v>0.148</v>
+        <v>0.015</v>
       </c>
       <c r="G16" t="n">
-        <v>0.643</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.373</v>
+        <v>0.002</v>
       </c>
       <c r="I16" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="K16" t="n">
-        <v>0.37</v>
+        <v>0.001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.401</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.403</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.077</v>
+        <v>0.003</v>
       </c>
       <c r="C17" t="n">
-        <v>0.064</v>
+        <v>0.003</v>
       </c>
       <c r="D17" t="n">
-        <v>0.218</v>
+        <v>0.015</v>
       </c>
       <c r="E17" t="n">
-        <v>0.623</v>
+        <v>0.066</v>
       </c>
       <c r="F17" t="n">
-        <v>0.113</v>
+        <v>0.012</v>
       </c>
       <c r="G17" t="n">
-        <v>0.379</v>
+        <v>0.04</v>
       </c>
       <c r="H17" t="n">
-        <v>0.265</v>
+        <v>0.002</v>
       </c>
       <c r="I17" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.475</v>
+        <v>0.001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.341</v>
+        <v>0.003</v>
       </c>
       <c r="M17" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.008</v>
       </c>
-      <c r="C18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.093</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="H18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.53</v>
+        <v>0.056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.053</v>
+        <v>0.006</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.058</v>
+        <v>0.007</v>
       </c>
       <c r="C20" t="n">
-        <v>0.061</v>
+        <v>0.007</v>
       </c>
       <c r="D20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.006</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05</v>
-      </c>
       <c r="H20" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.056</v>
+        <v>0.004</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06</v>
+        <v>0.004</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.155</v>
+        <v>0.016</v>
       </c>
       <c r="F21" t="n">
-        <v>0.026</v>
+        <v>0.003</v>
       </c>
       <c r="G21" t="n">
-        <v>0.026</v>
+        <v>0.003</v>
       </c>
       <c r="H21" t="n">
-        <v>0.202</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.171</v>
+        <v>0.004</v>
       </c>
       <c r="C22" t="n">
-        <v>0.194</v>
+        <v>0.004</v>
       </c>
       <c r="D22" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0.016</v>
       </c>
       <c r="F22" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="G22" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="H22" t="n">
-        <v>0.394</v>
+        <v>0.016</v>
       </c>
       <c r="I22" t="n">
-        <v>0.137</v>
+        <v>0.002</v>
       </c>
       <c r="J22" t="n">
-        <v>0.609</v>
+        <v>0.006</v>
       </c>
       <c r="K22" t="n">
-        <v>0.183</v>
+        <v>0.002</v>
       </c>
       <c r="L22" t="n">
-        <v>0.352</v>
+        <v>0.002</v>
       </c>
       <c r="M22" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.064</v>
+        <v>0.016</v>
       </c>
       <c r="C23" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.056</v>
+        <v>0.005</v>
       </c>
       <c r="F23" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.127</v>
+        <v>0.011</v>
       </c>
       <c r="H23" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.059</v>
+        <v>0.002</v>
       </c>
       <c r="J23" t="n">
-        <v>0.231</v>
+        <v>0.001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.097</v>
+        <v>0.002</v>
       </c>
       <c r="M23" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04</v>
+        <v>0.001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.007</v>
       </c>
       <c r="F24" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.164</v>
+        <v>0.017</v>
       </c>
       <c r="H24" t="n">
-        <v>0.033</v>
+        <v>0.001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.054</v>
+        <v>0.002</v>
       </c>
       <c r="J24" t="n">
-        <v>0.191</v>
+        <v>0.001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.083</v>
+        <v>0.003</v>
       </c>
       <c r="M24" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="C25" t="n">
-        <v>0.022</v>
+        <v>0.001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.077</v>
+        <v>0.008</v>
       </c>
       <c r="F25" t="n">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="G25" t="n">
-        <v>0.063</v>
+        <v>0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.006</v>
       </c>
-      <c r="C26" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.055</v>
-      </c>
       <c r="F26" t="n">
-        <v>0.014</v>
+        <v>0.001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.097</v>
+        <v>0.01</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.057</v>
+        <v>0.006</v>
       </c>
       <c r="F27" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.098</v>
+        <v>0.007</v>
       </c>
       <c r="H27" t="n">
-        <v>0.097</v>
+        <v>0.002</v>
       </c>
       <c r="I27" t="n">
-        <v>0.022</v>
+        <v>0.001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.317</v>
+        <v>0.006</v>
       </c>
       <c r="K27" t="n">
-        <v>0.115</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.159</v>
+        <v>0.003</v>
       </c>
       <c r="M27" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2949,22 +2949,22 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F28" t="n">
         <v>0.001</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.013</v>
-      </c>
       <c r="G28" t="n">
-        <v>0.031</v>
+        <v>0.002</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F29" t="n">
         <v>0.001</v>
       </c>
-      <c r="C29" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.012</v>
-      </c>
       <c r="G29" t="n">
-        <v>0.048</v>
+        <v>0.004</v>
       </c>
       <c r="H29" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="F30" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.289</v>
+        <v>52.236</v>
       </c>
       <c r="C2" t="n">
-        <v>144.547</v>
+        <v>40.848</v>
       </c>
       <c r="D2" t="n">
-        <v>199.349</v>
+        <v>89.02500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>250.146</v>
+        <v>228.123</v>
       </c>
       <c r="F2" t="n">
-        <v>109.167</v>
+        <v>105.855</v>
       </c>
       <c r="G2" t="n">
-        <v>164.082</v>
+        <v>144.529</v>
       </c>
       <c r="H2" t="n">
-        <v>170.619</v>
+        <v>13.225</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4</v>
+        <v>21.667</v>
       </c>
       <c r="J2" t="n">
-        <v>248.485</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>186.89</v>
+        <v>9.362</v>
       </c>
       <c r="L2" t="n">
-        <v>174.557</v>
+        <v>6.178</v>
       </c>
       <c r="M2" t="n">
-        <v>230.517</v>
+        <v>11.703</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.538</v>
+        <v>42.707</v>
       </c>
       <c r="C3" t="n">
-        <v>76.78400000000001</v>
+        <v>37.339</v>
       </c>
       <c r="D3" t="n">
-        <v>108.727</v>
+        <v>62.271</v>
       </c>
       <c r="E3" t="n">
-        <v>220.451</v>
+        <v>217.978</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>86.02</v>
+        <v>76.80500000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>136.496</v>
+        <v>1.063</v>
       </c>
       <c r="I3" t="n">
-        <v>135.516</v>
+        <v>6.124</v>
       </c>
       <c r="J3" t="n">
-        <v>108.492</v>
+        <v>3.734</v>
       </c>
       <c r="K3" t="n">
-        <v>138.241</v>
+        <v>2.422</v>
       </c>
       <c r="L3" t="n">
-        <v>127.499</v>
+        <v>2.201</v>
       </c>
       <c r="M3" t="n">
-        <v>78.70699999999999</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.016</v>
+        <v>27.253</v>
       </c>
       <c r="C4" t="n">
-        <v>27.104</v>
+        <v>19.919</v>
       </c>
       <c r="D4" t="n">
-        <v>49.399</v>
+        <v>42.394</v>
       </c>
       <c r="E4" t="n">
-        <v>200.76</v>
+        <v>196.74</v>
       </c>
       <c r="F4" t="n">
-        <v>74.05</v>
+        <v>73.182</v>
       </c>
       <c r="G4" t="n">
-        <v>65.21299999999999</v>
+        <v>59.056</v>
       </c>
       <c r="H4" t="n">
-        <v>9.351000000000001</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>5.348</v>
+        <v>2.159</v>
       </c>
       <c r="J4" t="n">
-        <v>15.704</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>28.691</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8.858000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12.6</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="5">
@@ -7272,10 +7272,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.895</v>
+        <v>18.623</v>
       </c>
       <c r="C5" t="n">
-        <v>6.652</v>
+        <v>5.454</v>
       </c>
       <c r="D5" t="n">
         <v>18.59</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.335</v>
+        <v>15.875</v>
       </c>
       <c r="C6" t="n">
-        <v>33.024</v>
+        <v>1.743</v>
       </c>
       <c r="D6" t="n">
-        <v>51.429</v>
+        <v>10.034</v>
       </c>
       <c r="E6" t="n">
-        <v>181.879</v>
+        <v>172.737</v>
       </c>
       <c r="F6" t="n">
-        <v>89.614</v>
+        <v>85.747</v>
       </c>
       <c r="G6" t="n">
-        <v>57.795</v>
+        <v>45.115</v>
       </c>
       <c r="H6" t="n">
-        <v>4.262</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>22.08</v>
+        <v>1.415</v>
       </c>
       <c r="J6" t="n">
-        <v>72.655</v>
+        <v>0.293</v>
       </c>
       <c r="K6" t="n">
-        <v>100.951</v>
+        <v>0.412</v>
       </c>
       <c r="L6" t="n">
-        <v>53.361</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>64.032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.645</v>
+        <v>11.537</v>
       </c>
       <c r="C7" t="n">
-        <v>116.566</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>83.959</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>107.365</v>
+        <v>77.108</v>
       </c>
       <c r="F7" t="n">
-        <v>171.397</v>
+        <v>153.113</v>
       </c>
       <c r="G7" t="n">
-        <v>68.69799999999999</v>
+        <v>35.306</v>
       </c>
       <c r="H7" t="n">
-        <v>448.705</v>
+        <v>402.337</v>
       </c>
       <c r="I7" t="n">
-        <v>328.085</v>
+        <v>321.932</v>
       </c>
       <c r="J7" t="n">
-        <v>406.981</v>
+        <v>78.265</v>
       </c>
       <c r="K7" t="n">
-        <v>369.421</v>
+        <v>339.646</v>
       </c>
       <c r="L7" t="n">
-        <v>345.876</v>
+        <v>42.462</v>
       </c>
       <c r="M7" t="n">
-        <v>409.27</v>
+        <v>49.153</v>
       </c>
     </row>
     <row r="8">
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.999000000000001</v>
+        <v>8.500999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7408,19 +7408,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.474</v>
+        <v>74.858</v>
       </c>
       <c r="F8" t="n">
-        <v>141.702</v>
+        <v>137.875</v>
       </c>
       <c r="G8" t="n">
-        <v>26.707</v>
+        <v>24.265</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.15</v>
+        <v>0.766</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -7442,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.174</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.329</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49.127</v>
+        <v>36.359</v>
       </c>
       <c r="F9" t="n">
-        <v>98.14100000000001</v>
+        <v>86.658</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37</v>
+        <v>3.442</v>
       </c>
       <c r="H9" t="n">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>29.345</v>
+        <v>3.667</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625</v>
+        <v>2.028</v>
       </c>
       <c r="K9" t="n">
-        <v>133.562</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21.648</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7494,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>38.165</v>
+        <v>32.368</v>
       </c>
       <c r="F10" t="n">
-        <v>74.45</v>
+        <v>69.78100000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>11.198</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7.096</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.148</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.843</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36.519</v>
+        <v>34.141</v>
       </c>
       <c r="F11" t="n">
-        <v>63.697</v>
+        <v>61.606</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.891</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.736</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7580,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.796</v>
+        <v>22.546</v>
       </c>
       <c r="F12" t="n">
-        <v>48.502</v>
+        <v>47.548</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.673999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="F13" t="n">
-        <v>34.177</v>
+        <v>26.62</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7635,16 +7635,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3.807</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13.525</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>16.795</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7.407</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7700,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198.422</v>
+        <v>96.527</v>
       </c>
       <c r="C15" t="n">
-        <v>182.077</v>
+        <v>58.888</v>
       </c>
       <c r="D15" t="n">
-        <v>205.629</v>
+        <v>85.241</v>
       </c>
       <c r="E15" t="n">
-        <v>234.016</v>
+        <v>212.542</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>242.281</v>
+        <v>229.985</v>
       </c>
       <c r="H15" t="n">
-        <v>150.226</v>
+        <v>19.119</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>168.641</v>
+        <v>51.292</v>
       </c>
       <c r="K15" t="n">
-        <v>210.788</v>
+        <v>81.736</v>
       </c>
       <c r="L15" t="n">
-        <v>240.008</v>
+        <v>138.554</v>
       </c>
       <c r="M15" t="n">
-        <v>246.087</v>
+        <v>48.635</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.941</v>
+        <v>116.888</v>
       </c>
       <c r="C16" t="n">
-        <v>285.944</v>
+        <v>86.634</v>
       </c>
       <c r="D16" t="n">
-        <v>337.826</v>
+        <v>175.484</v>
       </c>
       <c r="E16" t="n">
-        <v>380.599</v>
+        <v>377.251</v>
       </c>
       <c r="F16" t="n">
-        <v>206.405</v>
+        <v>200.497</v>
       </c>
       <c r="G16" t="n">
-        <v>437.584</v>
+        <v>436.177</v>
       </c>
       <c r="H16" t="n">
-        <v>361.504</v>
+        <v>186.378</v>
       </c>
       <c r="I16" t="n">
-        <v>171.377</v>
+        <v>67.57899999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>429.552</v>
+        <v>281.353</v>
       </c>
       <c r="K16" t="n">
-        <v>376.299</v>
+        <v>93.015</v>
       </c>
       <c r="L16" t="n">
-        <v>369.467</v>
+        <v>240.571</v>
       </c>
       <c r="M16" t="n">
-        <v>383.219</v>
+        <v>104.704</v>
       </c>
     </row>
     <row r="17">
@@ -7784,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>190.162</v>
+        <v>96.625</v>
       </c>
       <c r="C17" t="n">
-        <v>176.974</v>
+        <v>88.55200000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>287.615</v>
+        <v>201.837</v>
       </c>
       <c r="E17" t="n">
-        <v>418.938</v>
+        <v>416.187</v>
       </c>
       <c r="F17" t="n">
-        <v>178.899</v>
+        <v>177.486</v>
       </c>
       <c r="G17" t="n">
-        <v>328.324</v>
+        <v>322.729</v>
       </c>
       <c r="H17" t="n">
-        <v>334.933</v>
+        <v>169.533</v>
       </c>
       <c r="I17" t="n">
-        <v>122.944</v>
+        <v>42.79</v>
       </c>
       <c r="J17" t="n">
-        <v>426.081</v>
+        <v>129.461</v>
       </c>
       <c r="K17" t="n">
-        <v>280.581</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>364.881</v>
+        <v>163.884</v>
       </c>
       <c r="M17" t="n">
-        <v>329.791</v>
+        <v>72.009</v>
       </c>
     </row>
     <row r="18">
@@ -7827,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.284</v>
+        <v>40.557</v>
       </c>
       <c r="C18" t="n">
-        <v>29.031</v>
+        <v>20.167</v>
       </c>
       <c r="D18" t="n">
-        <v>47.026</v>
+        <v>40.053</v>
       </c>
       <c r="E18" t="n">
-        <v>398.401</v>
+        <v>393.462</v>
       </c>
       <c r="F18" t="n">
-        <v>162.221</v>
+        <v>159.617</v>
       </c>
       <c r="G18" t="n">
-        <v>140.396</v>
+        <v>140.235</v>
       </c>
       <c r="H18" t="n">
-        <v>32.366</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>10.028</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>20.694</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>35.773</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>80.483</v>
+        <v>5.197</v>
       </c>
       <c r="M18" t="n">
-        <v>36.838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -7870,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.853</v>
+        <v>17.933</v>
       </c>
       <c r="C19" t="n">
-        <v>10.437</v>
+        <v>4.508</v>
       </c>
       <c r="D19" t="n">
-        <v>29.286</v>
+        <v>23.175</v>
       </c>
       <c r="E19" t="n">
-        <v>385.916</v>
+        <v>382.84</v>
       </c>
       <c r="F19" t="n">
-        <v>154.628</v>
+        <v>152.843</v>
       </c>
       <c r="G19" t="n">
-        <v>122.902</v>
+        <v>120.932</v>
       </c>
       <c r="H19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3.267</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7.721</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.242</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -7940,10 +7940,10 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>70.63</v>
+        <v>11.559</v>
       </c>
       <c r="L20" t="n">
-        <v>7.176</v>
+        <v>5.484</v>
       </c>
       <c r="M20" t="n">
         <v>38.08</v>
@@ -7956,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151.843</v>
+        <v>96.55800000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>155.286</v>
+        <v>99.063</v>
       </c>
       <c r="D21" t="n">
-        <v>44.554</v>
+        <v>20.397</v>
       </c>
       <c r="E21" t="n">
-        <v>211.495</v>
+        <v>204.705</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84699999999999</v>
+        <v>83.80200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>86.437</v>
+        <v>86.164</v>
       </c>
       <c r="H21" t="n">
-        <v>315.454</v>
+        <v>14.682</v>
       </c>
       <c r="I21" t="n">
-        <v>67.90000000000001</v>
+        <v>4.609</v>
       </c>
       <c r="J21" t="n">
-        <v>312.499</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>218.524</v>
+        <v>23.807</v>
       </c>
       <c r="L21" t="n">
-        <v>181.643</v>
+        <v>15.954</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285.401</v>
+        <v>114.327</v>
       </c>
       <c r="C22" t="n">
-        <v>308.21</v>
+        <v>120.887</v>
       </c>
       <c r="D22" t="n">
-        <v>213.229</v>
+        <v>35.922</v>
       </c>
       <c r="E22" t="n">
-        <v>235.775</v>
+        <v>201.41</v>
       </c>
       <c r="F22" t="n">
-        <v>93.426</v>
+        <v>74.88800000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>102.116</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>351.305</v>
+        <v>333.396</v>
       </c>
       <c r="I22" t="n">
-        <v>218.601</v>
+        <v>168.953</v>
       </c>
       <c r="J22" t="n">
-        <v>447.263</v>
+        <v>304.833</v>
       </c>
       <c r="K22" t="n">
-        <v>245.673</v>
+        <v>159.955</v>
       </c>
       <c r="L22" t="n">
-        <v>351.869</v>
+        <v>150.705</v>
       </c>
       <c r="M22" t="n">
-        <v>345.778</v>
+        <v>18.902</v>
       </c>
     </row>
     <row r="23">
@@ -8042,40 +8042,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>68.547</v>
+        <v>55.505</v>
       </c>
       <c r="C23" t="n">
-        <v>30.674</v>
+        <v>7.236</v>
       </c>
       <c r="D23" t="n">
-        <v>31.352</v>
+        <v>6.276</v>
       </c>
       <c r="E23" t="n">
-        <v>24.121</v>
+        <v>22.371</v>
       </c>
       <c r="F23" t="n">
-        <v>9.519</v>
+        <v>8.757999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>119.489</v>
+        <v>99.06</v>
       </c>
       <c r="H23" t="n">
-        <v>21.522</v>
+        <v>11.334</v>
       </c>
       <c r="I23" t="n">
-        <v>26.488</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>56.446</v>
+        <v>21.449</v>
       </c>
       <c r="K23" t="n">
-        <v>20.712</v>
+        <v>10.535</v>
       </c>
       <c r="L23" t="n">
-        <v>32.653</v>
+        <v>24.243</v>
       </c>
       <c r="M23" t="n">
-        <v>35.369</v>
+        <v>9.904999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -8085,40 +8085,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.531</v>
+        <v>6.885</v>
       </c>
       <c r="C24" t="n">
-        <v>25.396</v>
+        <v>8.907</v>
       </c>
       <c r="D24" t="n">
-        <v>21.851</v>
+        <v>5.29</v>
       </c>
       <c r="E24" t="n">
-        <v>25.831</v>
+        <v>24.782</v>
       </c>
       <c r="F24" t="n">
-        <v>10.472</v>
+        <v>10.442</v>
       </c>
       <c r="G24" t="n">
-        <v>125.227</v>
+        <v>123.314</v>
       </c>
       <c r="H24" t="n">
-        <v>20.425</v>
+        <v>14.395</v>
       </c>
       <c r="I24" t="n">
-        <v>25.756</v>
+        <v>22.1</v>
       </c>
       <c r="J24" t="n">
-        <v>47.703</v>
+        <v>22.573</v>
       </c>
       <c r="K24" t="n">
-        <v>20.024</v>
+        <v>10.676</v>
       </c>
       <c r="L24" t="n">
-        <v>30.576</v>
+        <v>26.582</v>
       </c>
       <c r="M24" t="n">
-        <v>30.786</v>
+        <v>16.085</v>
       </c>
     </row>
     <row r="25">
@@ -8128,40 +8128,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.563</v>
+        <v>12.981</v>
       </c>
       <c r="C25" t="n">
-        <v>17.647</v>
+        <v>12.953</v>
       </c>
       <c r="D25" t="n">
-        <v>14.358</v>
+        <v>7.988</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>12.027</v>
+        <v>12.001</v>
       </c>
       <c r="G25" t="n">
-        <v>86.818</v>
+        <v>63.877</v>
       </c>
       <c r="H25" t="n">
-        <v>19.045</v>
+        <v>8.564</v>
       </c>
       <c r="I25" t="n">
-        <v>11.804</v>
+        <v>1.314</v>
       </c>
       <c r="J25" t="n">
-        <v>25.778</v>
+        <v>1.225</v>
       </c>
       <c r="K25" t="n">
-        <v>23.603</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>27.658</v>
+        <v>2.614</v>
       </c>
       <c r="M25" t="n">
-        <v>18.936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -8174,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.235</v>
+        <v>11.094</v>
       </c>
       <c r="D26" t="n">
-        <v>4.172</v>
+        <v>3.837</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8186,22 +8186,22 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>96.301</v>
+        <v>93.23399999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>1.428</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.551</v>
+        <v>0.706</v>
       </c>
       <c r="J26" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.274</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>6.246</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8214,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.634</v>
+        <v>5.819</v>
       </c>
       <c r="C27" t="n">
-        <v>31.771</v>
+        <v>6.667</v>
       </c>
       <c r="D27" t="n">
-        <v>27.277</v>
+        <v>2.961</v>
       </c>
       <c r="E27" t="n">
-        <v>24.271</v>
+        <v>22.295</v>
       </c>
       <c r="F27" t="n">
-        <v>12.223</v>
+        <v>10.996</v>
       </c>
       <c r="G27" t="n">
-        <v>109.659</v>
+        <v>81.908</v>
       </c>
       <c r="H27" t="n">
-        <v>33.252</v>
+        <v>21.933</v>
       </c>
       <c r="I27" t="n">
-        <v>18.642</v>
+        <v>16.855</v>
       </c>
       <c r="J27" t="n">
-        <v>58.309</v>
+        <v>42.51</v>
       </c>
       <c r="K27" t="n">
-        <v>37.326</v>
+        <v>11.903</v>
       </c>
       <c r="L27" t="n">
-        <v>43.613</v>
+        <v>32.756</v>
       </c>
       <c r="M27" t="n">
-        <v>36.754</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.559</v>
+        <v>2.401</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,13 +8272,13 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>61.175</v>
+        <v>43.697</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.536</v>
+        <v>0.399</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -8300,40 +8300,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.367</v>
+        <v>1.693</v>
       </c>
       <c r="C29" t="n">
-        <v>5.664</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>3.613</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>22.205</v>
+        <v>21.558</v>
       </c>
       <c r="F29" t="n">
-        <v>10.799</v>
+        <v>10.421</v>
       </c>
       <c r="G29" t="n">
-        <v>71.66200000000001</v>
+        <v>61.837</v>
       </c>
       <c r="H29" t="n">
-        <v>5.992</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>7.339</v>
+        <v>0.855</v>
       </c>
       <c r="J29" t="n">
-        <v>16.438</v>
+        <v>0.067</v>
       </c>
       <c r="K29" t="n">
-        <v>11.718</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>21.617</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -8467,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9401425521e-05</v>
+        <v>2.728599696e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0893835209e-05</v>
+        <v>1.668559104e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9740023801e-05</v>
+        <v>7.925450625000001e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2573021316e-05</v>
+        <v>5.204010312899999e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1917433889e-05</v>
+        <v>1.1205281025e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6922902724e-05</v>
+        <v>2.0888631841e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9110843161e-05</v>
+        <v>1.74900625e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857296000000001e-05</v>
+        <v>4.694588890000001e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1744795225e-05</v>
+        <v>8.613696100000003e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.49278721e-05</v>
+        <v>8.7647044e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0470146249e-05</v>
+        <v>3.816768400000001e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3138087289e-05</v>
+        <v>1.36960209e-07</v>
       </c>
     </row>
     <row r="3">
@@ -8510,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.555913443999999e-06</v>
+        <v>1.823887849e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.895782656e-06</v>
+        <v>1.394200921e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1821560529e-05</v>
+        <v>3.877677441e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8598643401e-05</v>
+        <v>4.7514408484e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3994404e-06</v>
+        <v>5.899008025000002e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8631158016e-05</v>
+        <v>1.129969e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8364586256e-05</v>
+        <v>3.750337599999999e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1770514064e-05</v>
+        <v>1.3942756e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9110574081e-05</v>
+        <v>5.866084000000001e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6255995001e-05</v>
+        <v>4.844401000000001e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>6.194791848999999e-06</v>
+        <v>2.585664e-09</v>
       </c>
     </row>
     <row r="4">
@@ -8553,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.445216256e-06</v>
+        <v>7.427260089999999e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.346268159999999e-07</v>
+        <v>3.96766561e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.440261201e-06</v>
+        <v>1.797251236e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.030457759999999e-05</v>
+        <v>3.87066276e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.483402499999999e-06</v>
+        <v>5.355605124e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.252735369e-06</v>
+        <v>3.487611136e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.744120100000002e-08</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.860110399999999e-08</v>
+        <v>4.661281e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.46615616e-07</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8.231734809999998e-07</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7.846416400000002e-08</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5876e-07</v>
+        <v>4.040100000000001e-11</v>
       </c>
     </row>
     <row r="5">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95811025e-07</v>
+        <v>3.46816129e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4249104e-08</v>
+        <v>2.9746116e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.455880999999999e-07</v>
@@ -8637,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011322225000001e-06</v>
+        <v>2.52015625e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.090584576e-06</v>
+        <v>3.038049000000001e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644942041e-06</v>
+        <v>1.00681156e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3079970641e-05</v>
+        <v>2.9838071169e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.030668996000001e-06</v>
+        <v>7.352548009000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.340262025e-06</v>
+        <v>2.035363225e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816464399999999e-08</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875263999999999e-07</v>
+        <v>2.002225e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.278749024999999e-06</v>
+        <v>8.584899999999997e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0191104401e-05</v>
+        <v>1.69744e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>2.847396321e-06</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.100097023999998e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8680,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.080772008333333e-06</v>
+        <v>4.436745633333333e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.529210785333334e-06</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349704560333334e-06</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3.842414408333332e-06</v>
+        <v>1.981881221333334e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792310536333332e-06</v>
+        <v>7.814530256333334e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.573138401333333e-06</v>
+        <v>4.155045453333333e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.711205900833333e-05</v>
+        <v>5.395835385633333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.587992240833332e-05</v>
+        <v>3.454673754133334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>5.521117812033333e-05</v>
+        <v>2.041803408333333e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>4.549062508033333e-05</v>
+        <v>3.845313510533333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.987673579199999e-05</v>
+        <v>6.010071480000001e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>5.583397763333333e-05</v>
+        <v>8.053391363333332e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.098200100000001e-08</v>
+        <v>7.2267001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -8732,19 +8732,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.696324676e-06</v>
+        <v>5.603720164000002e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0079456804e-05</v>
+        <v>1.9009515625e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.132638490000001e-07</v>
+        <v>5.887902250000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.622500000000001e-09</v>
+        <v>5.86756e-10</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8766,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.356634253333333e-07</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.608033333333334e-11</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6.120408333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.044873763333334e-07</v>
+        <v>4.406589603333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210551960333334e-06</v>
+        <v>2.503202988e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>5.100563333333332e-08</v>
+        <v>3.949121333333334e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>3.123413333333333e-08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.870430083333333e-07</v>
+        <v>4.482296333333332e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.283802083333333e-07</v>
+        <v>1.370928e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>5.946269281333335e-06</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56211968e-07</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1047683e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8818,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.855224083333332e-07</v>
+        <v>3.492291413333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847600833333333e-06</v>
+        <v>1.623129320333334e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.136333333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.301333333333332e-10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.179840133333333e-08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.678440533333333e-08</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8.833968e-09</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.694216333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8861,22 +8861,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.445457869999999e-07</v>
+        <v>3.885359603333333e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352435936333333e-06</v>
+        <v>1.265099745333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93548e-10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.785960333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652565333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8904,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.732192053333333e-07</v>
+        <v>1.694407053333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.841480013333335e-07</v>
+        <v>7.536041013333334e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.507942533333333e-08</v>
+        <v>1.62867e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>3.893557763333333e-07</v>
+        <v>2.362081333333334e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8959,16 +8959,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.831083e-09</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6.097520833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>9.402400833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8287883e-08</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -9024,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9371290084e-05</v>
+        <v>9.317461729000001e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3152033929e-05</v>
+        <v>3.467796543999999e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>4.228328564099999e-05</v>
+        <v>7.266028080999999e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4763488256e-05</v>
+        <v>4.5174101764e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8700082961e-05</v>
+        <v>5.289310022500001e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2567851076e-05</v>
+        <v>3.65536161e-07</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.843978688099999e-05</v>
+        <v>2.630869264e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4431580944e-05</v>
+        <v>6.680773696000001e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7603840064e-05</v>
+        <v>1.9197210916e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0558811569e-05</v>
+        <v>2.365363225e-06</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6874163827e-05</v>
+        <v>4.554268181333334e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>2.725465704533334e-05</v>
+        <v>2.501816652e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>3.804213542533334e-05</v>
+        <v>1.026487808533333e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.828519960033332e-05</v>
+        <v>4.743943900033334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.420100800833334e-05</v>
+        <v>1.339968233633333e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.382658568533334e-05</v>
+        <v>6.341679177633334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.356171400533333e-05</v>
+        <v>1.1578919628e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>9.790025376333333e-06</v>
+        <v>1.522307080333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>6.150497356800002e-05</v>
+        <v>2.638650353633333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7200312467e-05</v>
+        <v>2.883930075e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>4.550195469633334e-05</v>
+        <v>1.929146868033334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.895226732033333e-05</v>
+        <v>3.654309205333333e-06</v>
       </c>
     </row>
     <row r="17">
@@ -9108,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.205386208133333e-05</v>
+        <v>3.112130208333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>1.043993222533333e-05</v>
+        <v>2.613818901333333e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>2.757412940833333e-05</v>
+        <v>1.3579391523e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.850301594799999e-05</v>
+        <v>5.773720632300001e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0668284067e-05</v>
+        <v>1.0500426732e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.593221632533333e-05</v>
+        <v>3.471800248033333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.739337149633333e-05</v>
+        <v>9.580479362999998e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>5.038409045333333e-06</v>
+        <v>6.103280333333334e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>6.051500618700001e-05</v>
+        <v>5.586716840333335e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6241899187e-05</v>
+        <v>1.760794133333334e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>4.437938138699999e-05</v>
+        <v>8.952655151999998e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>3.625403456033334e-05</v>
+        <v>1.728432027e-06</v>
       </c>
     </row>
     <row r="18">
@@ -9151,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.09637552e-07</v>
+        <v>5.48290083e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>2.80932987e-07</v>
+        <v>1.355692963333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.371482253333335e-07</v>
+        <v>5.347476029999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.290778560033334e-05</v>
+        <v>5.1604115148e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.771884280333334e-06</v>
+        <v>8.492528896333331e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.570345605333333e-06</v>
+        <v>6.555285075000002e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>3.491859853333333e-07</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3.352026133333334e-08</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.42747212e-07</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.265691763333335e-07</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.159171096333333e-06</v>
+        <v>9.002936333333335e-09</v>
       </c>
       <c r="M18" t="n">
-        <v>4.523460813333334e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -9194,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.89655203e-07</v>
+        <v>1.071974963333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6310323e-08</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85889932e-07</v>
+        <v>1.79026875e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.964371968533333e-05</v>
+        <v>4.885548853333333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.969939461333333e-06</v>
+        <v>7.786994216333332e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.034967201333333e-06</v>
+        <v>4.874849541333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>4.712533333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3.557763e-09</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>4.224533333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.987128033333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.4966188e-08</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.689813333333334e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -9264,10 +9264,10 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>1.662865633333333e-06</v>
+        <v>4.4536827e-08</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7164992e-08</v>
+        <v>1.0024752e-08</v>
       </c>
       <c r="M20" t="n">
         <v>4.833621333333333e-07</v>
@@ -9280,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.685432216333331e-06</v>
+        <v>3.107815788e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.037913932000002e-06</v>
+        <v>3.271159323e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>6.616863053333334e-07</v>
+        <v>1.38679203e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491004500833333e-05</v>
+        <v>1.3968045675e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399671136333333e-06</v>
+        <v>2.340925068e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.490451656333333e-06</v>
+        <v>2.474744965333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317040870533334e-05</v>
+        <v>7.1853708e-08</v>
       </c>
       <c r="I21" t="n">
-        <v>1.536803333333333e-06</v>
+        <v>7.080960333333333e-09</v>
       </c>
       <c r="J21" t="n">
-        <v>3.255187500033334e-05</v>
+        <v>2.881140300000001e-08</v>
       </c>
       <c r="K21" t="n">
-        <v>1.591757952533333e-05</v>
+        <v>1.889244163333333e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>1.099805981633333e-05</v>
+        <v>8.484337199999999e-08</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.715124360033333e-05</v>
+        <v>4.356887643e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>3.166446803333333e-05</v>
+        <v>4.871222256333332e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>1.515553548033333e-05</v>
+        <v>4.301300279999999e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.852995020833333e-05</v>
+        <v>1.352199603333333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.909472492e-06</v>
+        <v>1.869404181333334e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>3.475892485333333e-06</v>
+        <v>1.6666347e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.113840100833334e-05</v>
+        <v>3.705096427200001e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5928799067e-05</v>
+        <v>9.515038736333332e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>6.668139705633332e-05</v>
+        <v>3.097438596300001e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0118407643e-05</v>
+        <v>8.528534008333335e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>4.127059772033335e-05</v>
+        <v>7.570665675000001e-06</v>
       </c>
       <c r="M22" t="n">
-        <v>3.985414176133334e-05</v>
+        <v>1.190952013333334e-07</v>
       </c>
     </row>
     <row r="23">
@@ -9366,40 +9366,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.698691208999999e-05</v>
+        <v>3.080805025e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>9.408942760000001e-06</v>
+        <v>5.235969599999999e-07</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82947904e-06</v>
+        <v>3.938817599999999e-07</v>
       </c>
       <c r="E23" t="n">
-        <v>5.81822641e-06</v>
+        <v>5.00461641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.0611361e-07</v>
+        <v>7.670256399999996e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4277621121e-05</v>
+        <v>9.812883600000002e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>4.63196484e-06</v>
+        <v>1.28459556e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>7.016141440000001e-06</v>
+        <v>4.41e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>3.186150915999999e-05</v>
+        <v>4.600596010000001e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>4.28986944e-06</v>
+        <v>1.10986225e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>1.066218409e-05</v>
+        <v>5.877230489999999e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.250966161e-05</v>
+        <v>9.810902499999998e-07</v>
       </c>
     </row>
     <row r="24">
@@ -9409,40 +9409,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.41211961e-06</v>
+        <v>4.7403225e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>6.449568160000001e-06</v>
+        <v>7.933464900000001e-07</v>
       </c>
       <c r="D24" t="n">
-        <v>4.774662009999999e-06</v>
+        <v>2.798410000000001e-07</v>
       </c>
       <c r="E24" t="n">
-        <v>6.67240561e-06</v>
+        <v>6.14147524e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09662784e-06</v>
+        <v>1.09035364e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5681801529e-05</v>
+        <v>1.5206342596e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>4.171806250000001e-06</v>
+        <v>2.07216025e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>6.633715360000001e-06</v>
+        <v>4.884100000000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.275576209e-05</v>
+        <v>5.095403289999999e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>4.00960576e-06</v>
+        <v>1.13976976e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>9.34891776e-06</v>
+        <v>7.066027240000001e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>9.477777960000001e-06</v>
+        <v>2.587272250000001e-06</v>
       </c>
     </row>
     <row r="25">
@@ -9452,40 +9452,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.83954969e-06</v>
+        <v>1.68506361e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.11416609e-06</v>
+        <v>1.67780209e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.06152164e-06</v>
+        <v>6.3808144e-07</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44648729e-06</v>
+        <v>1.44024001e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>7.537365123999998e-06</v>
+        <v>4.080271129e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>3.627120250000001e-06</v>
+        <v>7.334209600000002e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>1.39334416e-06</v>
+        <v>1.726596e-08</v>
       </c>
       <c r="J25" t="n">
-        <v>6.645052839999999e-06</v>
+        <v>1.500625e-08</v>
       </c>
       <c r="K25" t="n">
-        <v>5.571016090000001e-06</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7.64964964e-06</v>
+        <v>6.832996e-08</v>
       </c>
       <c r="M25" t="n">
-        <v>3.58572096e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -9498,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26225225e-06</v>
+        <v>1.23076836e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7405584e-07</v>
+        <v>1.4722569e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9510,22 +9510,22 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.273882601e-06</v>
+        <v>8.692578755999999e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>2.039184e-08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.405601e-08</v>
+        <v>4.984359999999999e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>9.35089e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.623076e-08</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3.901251600000001e-07</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9538,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.680299560000001e-06</v>
+        <v>3.386076099999999e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>1.009396441e-05</v>
+        <v>4.4448889e-07</v>
       </c>
       <c r="D27" t="n">
-        <v>7.440347290000001e-06</v>
+        <v>8.767520999999998e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>5.890814410000001e-06</v>
+        <v>4.970670250000002e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49401729e-06</v>
+        <v>1.20912016e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2025096281e-05</v>
+        <v>6.708920463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>1.105695504e-05</v>
+        <v>4.81056489e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>3.47524164e-06</v>
+        <v>2.84091025e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.399939481e-05</v>
+        <v>1.8071001e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.393230276e-05</v>
+        <v>1.41681409e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>1.902093769e-05</v>
+        <v>1.072955536e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.350856516e-05</v>
+        <v>6.953892100000002e-07</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.548481000000001e-08</v>
+        <v>5.764801e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,13 +9596,13 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>3.742380625e-06</v>
+        <v>1.909427809e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.87296e-09</v>
+        <v>1.59201e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -9624,40 +9624,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9070689e-07</v>
+        <v>2.866249e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2080896e-07</v>
+        <v>8.723560000000001e-09</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3053769e-07</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.930620249999999e-06</v>
+        <v>4.64747364e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16618401e-06</v>
+        <v>1.08597241e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.135442244e-06</v>
+        <v>3.823814569e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5904064e-07</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>5.3860921e-07</v>
+        <v>7.310249999999999e-09</v>
       </c>
       <c r="J29" t="n">
-        <v>2.70207844e-06</v>
+        <v>4.489000000000001e-11</v>
       </c>
       <c r="K29" t="n">
-        <v>1.37311524e-06</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>4.67294689e-06</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.946318399999999e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -9791,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139.289</v>
+        <v>52.236</v>
       </c>
       <c r="C2" t="n">
-        <v>144.547</v>
+        <v>40.848</v>
       </c>
       <c r="D2" t="n">
-        <v>199.349</v>
+        <v>89.02500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>250.146</v>
+        <v>228.123</v>
       </c>
       <c r="F2" t="n">
-        <v>109.167</v>
+        <v>105.855</v>
       </c>
       <c r="G2" t="n">
-        <v>164.082</v>
+        <v>144.529</v>
       </c>
       <c r="H2" t="n">
-        <v>170.619</v>
+        <v>13.225</v>
       </c>
       <c r="I2" t="n">
-        <v>196.4</v>
+        <v>21.667</v>
       </c>
       <c r="J2" t="n">
-        <v>248.469</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>186.89</v>
+        <v>9.362</v>
       </c>
       <c r="L2" t="n">
-        <v>174.557</v>
+        <v>6.178</v>
       </c>
       <c r="M2" t="n">
-        <v>230.517</v>
+        <v>11.703</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.538</v>
+        <v>42.707</v>
       </c>
       <c r="C3" t="n">
-        <v>76.78400000000001</v>
+        <v>37.339</v>
       </c>
       <c r="D3" t="n">
-        <v>108.727</v>
+        <v>62.271</v>
       </c>
       <c r="E3" t="n">
-        <v>220.451</v>
+        <v>216.724</v>
       </c>
       <c r="F3" t="n">
-        <v>76.491</v>
+        <v>76.273</v>
       </c>
       <c r="G3" t="n">
-        <v>86.02</v>
+        <v>76.80500000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>136.496</v>
+        <v>1.063</v>
       </c>
       <c r="I3" t="n">
-        <v>135.516</v>
+        <v>6.124</v>
       </c>
       <c r="J3" t="n">
-        <v>108.463</v>
+        <v>3.734</v>
       </c>
       <c r="K3" t="n">
-        <v>138.241</v>
+        <v>2.422</v>
       </c>
       <c r="L3" t="n">
-        <v>127.499</v>
+        <v>2.201</v>
       </c>
       <c r="M3" t="n">
-        <v>78.70699999999999</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="4">
@@ -9877,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.016</v>
+        <v>27.253</v>
       </c>
       <c r="C4" t="n">
-        <v>27.104</v>
+        <v>19.919</v>
       </c>
       <c r="D4" t="n">
-        <v>49.399</v>
+        <v>42.394</v>
       </c>
       <c r="E4" t="n">
-        <v>200.76</v>
+        <v>196.74</v>
       </c>
       <c r="F4" t="n">
-        <v>74.05</v>
+        <v>73.179</v>
       </c>
       <c r="G4" t="n">
-        <v>65.21299999999999</v>
+        <v>59.056</v>
       </c>
       <c r="H4" t="n">
-        <v>9.351000000000001</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3.563</v>
+        <v>2.159</v>
       </c>
       <c r="J4" t="n">
-        <v>15.704</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>28.691</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8.858000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>12.6</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.895</v>
+        <v>18.424</v>
       </c>
       <c r="C5" t="n">
-        <v>6.652</v>
+        <v>4.869</v>
       </c>
       <c r="D5" t="n">
-        <v>18.554</v>
+        <v>18.03</v>
       </c>
       <c r="E5" t="n">
-        <v>195.073</v>
+        <v>196.141</v>
       </c>
       <c r="F5" t="n">
-        <v>93.86199999999999</v>
+        <v>94.65900000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>76.872</v>
+        <v>78.86199999999999</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63.335</v>
+        <v>15.875</v>
       </c>
       <c r="C6" t="n">
-        <v>33.024</v>
+        <v>1.743</v>
       </c>
       <c r="D6" t="n">
-        <v>51.429</v>
+        <v>10.034</v>
       </c>
       <c r="E6" t="n">
-        <v>181.879</v>
+        <v>172.737</v>
       </c>
       <c r="F6" t="n">
-        <v>89.614</v>
+        <v>85.747</v>
       </c>
       <c r="G6" t="n">
-        <v>57.795</v>
+        <v>45.115</v>
       </c>
       <c r="H6" t="n">
-        <v>4.262</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>22.08</v>
+        <v>1.415</v>
       </c>
       <c r="J6" t="n">
-        <v>72.655</v>
+        <v>0.293</v>
       </c>
       <c r="K6" t="n">
-        <v>100.951</v>
+        <v>0.347</v>
       </c>
       <c r="L6" t="n">
-        <v>53.361</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>64.032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -10004,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>110.645</v>
+        <v>11.537</v>
       </c>
       <c r="C7" t="n">
-        <v>116.566</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>83.959</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>107.365</v>
+        <v>77.108</v>
       </c>
       <c r="F7" t="n">
-        <v>171.397</v>
+        <v>153.113</v>
       </c>
       <c r="G7" t="n">
-        <v>68.69799999999999</v>
+        <v>35.306</v>
       </c>
       <c r="H7" t="n">
-        <v>444.155</v>
+        <v>402.337</v>
       </c>
       <c r="I7" t="n">
-        <v>322.767</v>
+        <v>321.932</v>
       </c>
       <c r="J7" t="n">
-        <v>374.397</v>
+        <v>78.265</v>
       </c>
       <c r="K7" t="n">
-        <v>365.191</v>
+        <v>339.646</v>
       </c>
       <c r="L7" t="n">
-        <v>341.074</v>
+        <v>42.462</v>
       </c>
       <c r="M7" t="n">
-        <v>408.096</v>
+        <v>49.153</v>
       </c>
     </row>
     <row r="8">
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.999000000000001</v>
+        <v>8.500999999999999</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -10056,25 +10056,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>75.462</v>
+        <v>74.858</v>
       </c>
       <c r="F8" t="n">
-        <v>141.702</v>
+        <v>137.875</v>
       </c>
       <c r="G8" t="n">
-        <v>26.707</v>
+        <v>24.265</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1.796</v>
+        <v>0.766</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>62.415</v>
+        <v>84.98</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -10090,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.174</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.329</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4.285</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49.127</v>
+        <v>36.359</v>
       </c>
       <c r="F9" t="n">
-        <v>98.14100000000001</v>
+        <v>86.658</v>
       </c>
       <c r="G9" t="n">
-        <v>12.37</v>
+        <v>3.442</v>
       </c>
       <c r="H9" t="n">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>29.345</v>
+        <v>3.667</v>
       </c>
       <c r="J9" t="n">
-        <v>19.625</v>
+        <v>2.028</v>
       </c>
       <c r="K9" t="n">
-        <v>133.562</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21.648</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>5.757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>38.165</v>
+        <v>32.017</v>
       </c>
       <c r="F10" t="n">
-        <v>74.45</v>
+        <v>69.78100000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.476</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10.515</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7.096</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.148</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.843</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -10185,22 +10185,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>36.519</v>
+        <v>33.871</v>
       </c>
       <c r="F11" t="n">
-        <v>63.697</v>
+        <v>61.606</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.891</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3.736</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10228,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.796</v>
+        <v>22.256</v>
       </c>
       <c r="F12" t="n">
-        <v>48.502</v>
+        <v>47.548</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10271,10 +10271,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.673999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="F13" t="n">
-        <v>34.177</v>
+        <v>26.62</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3.807</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>13.525</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>16.795</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>7.407</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10348,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198.422</v>
+        <v>96.527</v>
       </c>
       <c r="C15" t="n">
-        <v>182.077</v>
+        <v>58.888</v>
       </c>
       <c r="D15" t="n">
-        <v>205.629</v>
+        <v>85.241</v>
       </c>
       <c r="E15" t="n">
-        <v>234.016</v>
+        <v>212.542</v>
       </c>
       <c r="F15" t="n">
-        <v>98.13800000000001</v>
+        <v>96.351</v>
       </c>
       <c r="G15" t="n">
-        <v>242.281</v>
+        <v>227.132</v>
       </c>
       <c r="H15" t="n">
-        <v>144.372</v>
+        <v>17.825</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>168.641</v>
+        <v>51.292</v>
       </c>
       <c r="K15" t="n">
-        <v>210.788</v>
+        <v>68.693</v>
       </c>
       <c r="L15" t="n">
-        <v>240.008</v>
+        <v>119.495</v>
       </c>
       <c r="M15" t="n">
-        <v>246.087</v>
+        <v>48.635</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>283.941</v>
+        <v>116.888</v>
       </c>
       <c r="C16" t="n">
-        <v>285.944</v>
+        <v>86.634</v>
       </c>
       <c r="D16" t="n">
-        <v>337.826</v>
+        <v>175.484</v>
       </c>
       <c r="E16" t="n">
-        <v>380.599</v>
+        <v>375.145</v>
       </c>
       <c r="F16" t="n">
-        <v>206.405</v>
+        <v>199.537</v>
       </c>
       <c r="G16" t="n">
-        <v>424.195</v>
+        <v>435.904</v>
       </c>
       <c r="H16" t="n">
-        <v>356.476</v>
+        <v>186.378</v>
       </c>
       <c r="I16" t="n">
-        <v>160.309</v>
+        <v>67.57899999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>422.299</v>
+        <v>281.353</v>
       </c>
       <c r="K16" t="n">
-        <v>376.299</v>
+        <v>93.015</v>
       </c>
       <c r="L16" t="n">
-        <v>369.467</v>
+        <v>240.571</v>
       </c>
       <c r="M16" t="n">
-        <v>383.219</v>
+        <v>104.704</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>190.162</v>
+        <v>96.625</v>
       </c>
       <c r="C17" t="n">
-        <v>176.974</v>
+        <v>88.55200000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>287.615</v>
+        <v>201.837</v>
       </c>
       <c r="E17" t="n">
-        <v>418.938</v>
+        <v>415.356</v>
       </c>
       <c r="F17" t="n">
-        <v>178.14</v>
+        <v>176.602</v>
       </c>
       <c r="G17" t="n">
-        <v>328.324</v>
+        <v>322.729</v>
       </c>
       <c r="H17" t="n">
-        <v>334.933</v>
+        <v>169.533</v>
       </c>
       <c r="I17" t="n">
-        <v>122.944</v>
+        <v>42.79</v>
       </c>
       <c r="J17" t="n">
-        <v>421.894</v>
+        <v>129.461</v>
       </c>
       <c r="K17" t="n">
-        <v>280.581</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>364.881</v>
+        <v>163.884</v>
       </c>
       <c r="M17" t="n">
-        <v>329.791</v>
+        <v>72.009</v>
       </c>
     </row>
     <row r="18">
@@ -10475,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.284</v>
+        <v>40.557</v>
       </c>
       <c r="C18" t="n">
-        <v>29.031</v>
+        <v>20.167</v>
       </c>
       <c r="D18" t="n">
-        <v>47.026</v>
+        <v>40.053</v>
       </c>
       <c r="E18" t="n">
-        <v>398.401</v>
+        <v>393.462</v>
       </c>
       <c r="F18" t="n">
-        <v>162.221</v>
+        <v>159.419</v>
       </c>
       <c r="G18" t="n">
-        <v>140.396</v>
+        <v>140.198</v>
       </c>
       <c r="H18" t="n">
-        <v>29.584</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>8.759</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>18.803</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>32.529</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>52.306</v>
+        <v>5.197</v>
       </c>
       <c r="M18" t="n">
-        <v>27.016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10518,40 +10518,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.853</v>
+        <v>17.933</v>
       </c>
       <c r="C19" t="n">
-        <v>10.437</v>
+        <v>4.508</v>
       </c>
       <c r="D19" t="n">
-        <v>29.286</v>
+        <v>23.175</v>
       </c>
       <c r="E19" t="n">
-        <v>385.916</v>
+        <v>382.84</v>
       </c>
       <c r="F19" t="n">
-        <v>153.59</v>
+        <v>152.843</v>
       </c>
       <c r="G19" t="n">
-        <v>122.902</v>
+        <v>120.932</v>
       </c>
       <c r="H19" t="n">
-        <v>3.177</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3.101</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.914</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6.987</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.497</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -10561,40 +10561,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>120.83</v>
+        <v>132.136</v>
       </c>
       <c r="C20" t="n">
-        <v>124.046</v>
+        <v>136.172</v>
       </c>
       <c r="D20" t="n">
-        <v>35.092</v>
+        <v>45.395</v>
       </c>
       <c r="E20" t="n">
-        <v>219.31</v>
+        <v>224.255</v>
       </c>
       <c r="F20" t="n">
-        <v>95.608</v>
+        <v>98.873</v>
       </c>
       <c r="G20" t="n">
-        <v>112.855</v>
+        <v>124.497</v>
       </c>
       <c r="H20" t="n">
-        <v>42.608</v>
+        <v>10.995</v>
       </c>
       <c r="I20" t="n">
-        <v>3.029</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.275</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>70.63</v>
+        <v>9.539</v>
       </c>
       <c r="L20" t="n">
-        <v>3.369</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.504</v>
       </c>
     </row>
     <row r="21">
@@ -10604,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151.843</v>
+        <v>96.55800000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>155.286</v>
+        <v>99.063</v>
       </c>
       <c r="D21" t="n">
-        <v>44.554</v>
+        <v>20.397</v>
       </c>
       <c r="E21" t="n">
-        <v>211.495</v>
+        <v>204.705</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84699999999999</v>
+        <v>83.80200000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>86.437</v>
+        <v>86.005</v>
       </c>
       <c r="H21" t="n">
-        <v>315.454</v>
+        <v>14.682</v>
       </c>
       <c r="I21" t="n">
-        <v>67.90000000000001</v>
+        <v>4.609</v>
       </c>
       <c r="J21" t="n">
-        <v>282.613</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>217.762</v>
+        <v>23.807</v>
       </c>
       <c r="L21" t="n">
-        <v>181.643</v>
+        <v>15.954</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>285.401</v>
+        <v>114.327</v>
       </c>
       <c r="C22" t="n">
-        <v>308.21</v>
+        <v>120.887</v>
       </c>
       <c r="D22" t="n">
-        <v>213.229</v>
+        <v>35.922</v>
       </c>
       <c r="E22" t="n">
-        <v>235.775</v>
+        <v>201.41</v>
       </c>
       <c r="F22" t="n">
-        <v>93.426</v>
+        <v>74.88800000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>102.116</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>337.765</v>
+        <v>333.396</v>
       </c>
       <c r="I22" t="n">
-        <v>194.998</v>
+        <v>168.953</v>
       </c>
       <c r="J22" t="n">
-        <v>436.149</v>
+        <v>304.833</v>
       </c>
       <c r="K22" t="n">
-        <v>245.437</v>
+        <v>159.955</v>
       </c>
       <c r="L22" t="n">
-        <v>351.869</v>
+        <v>150.705</v>
       </c>
       <c r="M22" t="n">
-        <v>345.778</v>
+        <v>18.902</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.674</v>
+        <v>27.053</v>
       </c>
       <c r="C23" t="n">
-        <v>30.674</v>
+        <v>7.236</v>
       </c>
       <c r="D23" t="n">
-        <v>31.352</v>
+        <v>6.276</v>
       </c>
       <c r="E23" t="n">
-        <v>24.121</v>
+        <v>21.546</v>
       </c>
       <c r="F23" t="n">
-        <v>9.516999999999999</v>
+        <v>8.757999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>119.489</v>
+        <v>99.06</v>
       </c>
       <c r="H23" t="n">
-        <v>17.539</v>
+        <v>11.334</v>
       </c>
       <c r="I23" t="n">
-        <v>22.228</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>56.305</v>
+        <v>21.449</v>
       </c>
       <c r="K23" t="n">
-        <v>16.719</v>
+        <v>10.535</v>
       </c>
       <c r="L23" t="n">
-        <v>30.828</v>
+        <v>24.243</v>
       </c>
       <c r="M23" t="n">
-        <v>32.793</v>
+        <v>9.904999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15.531</v>
+        <v>6.885</v>
       </c>
       <c r="C24" t="n">
-        <v>25.396</v>
+        <v>8.907</v>
       </c>
       <c r="D24" t="n">
-        <v>21.851</v>
+        <v>5.29</v>
       </c>
       <c r="E24" t="n">
-        <v>25.831</v>
+        <v>24.782</v>
       </c>
       <c r="F24" t="n">
-        <v>10.456</v>
+        <v>10.331</v>
       </c>
       <c r="G24" t="n">
-        <v>125.227</v>
+        <v>122.325</v>
       </c>
       <c r="H24" t="n">
-        <v>16.58</v>
+        <v>14.395</v>
       </c>
       <c r="I24" t="n">
-        <v>20.535</v>
+        <v>22.1</v>
       </c>
       <c r="J24" t="n">
-        <v>46.069</v>
+        <v>22.573</v>
       </c>
       <c r="K24" t="n">
-        <v>16.215</v>
+        <v>10.676</v>
       </c>
       <c r="L24" t="n">
-        <v>27.037</v>
+        <v>26.582</v>
       </c>
       <c r="M24" t="n">
-        <v>28.073</v>
+        <v>16.085</v>
       </c>
     </row>
     <row r="25">
@@ -10776,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.563</v>
+        <v>11.742</v>
       </c>
       <c r="C25" t="n">
-        <v>17.647</v>
+        <v>10.397</v>
       </c>
       <c r="D25" t="n">
-        <v>14.358</v>
+        <v>7.173</v>
       </c>
       <c r="E25" t="n">
-        <v>26.681</v>
+        <v>26.426</v>
       </c>
       <c r="F25" t="n">
-        <v>12.021</v>
+        <v>11.776</v>
       </c>
       <c r="G25" t="n">
-        <v>86.818</v>
+        <v>63.877</v>
       </c>
       <c r="H25" t="n">
-        <v>16.527</v>
+        <v>8.564</v>
       </c>
       <c r="I25" t="n">
-        <v>11.087</v>
+        <v>1.271</v>
       </c>
       <c r="J25" t="n">
-        <v>18.461</v>
+        <v>1.225</v>
       </c>
       <c r="K25" t="n">
-        <v>21.149</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>27.456</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>18.094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -10819,37 +10819,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.778</v>
+        <v>7.58</v>
       </c>
       <c r="C26" t="n">
-        <v>11.235</v>
+        <v>9.933999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>4.172</v>
+        <v>3.571</v>
       </c>
       <c r="E26" t="n">
-        <v>22.438</v>
+        <v>22.686</v>
       </c>
       <c r="F26" t="n">
-        <v>11.269</v>
+        <v>11.281</v>
       </c>
       <c r="G26" t="n">
-        <v>96.301</v>
+        <v>93.23399999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>1.006</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1.551</v>
+        <v>0.705</v>
       </c>
       <c r="J26" t="n">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>5.061</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.634</v>
+        <v>5.819</v>
       </c>
       <c r="C27" t="n">
-        <v>31.771</v>
+        <v>4.266</v>
       </c>
       <c r="D27" t="n">
-        <v>27.277</v>
+        <v>2.961</v>
       </c>
       <c r="E27" t="n">
-        <v>24.271</v>
+        <v>22.007</v>
       </c>
       <c r="F27" t="n">
-        <v>12.223</v>
+        <v>10.996</v>
       </c>
       <c r="G27" t="n">
-        <v>109.659</v>
+        <v>81.908</v>
       </c>
       <c r="H27" t="n">
-        <v>30.772</v>
+        <v>21.933</v>
       </c>
       <c r="I27" t="n">
-        <v>12.796</v>
+        <v>16.855</v>
       </c>
       <c r="J27" t="n">
-        <v>55.912</v>
+        <v>42.51</v>
       </c>
       <c r="K27" t="n">
-        <v>34.4</v>
+        <v>11.903</v>
       </c>
       <c r="L27" t="n">
-        <v>38.12</v>
+        <v>32.756</v>
       </c>
       <c r="M27" t="n">
-        <v>35.866</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.447</v>
+        <v>2.401</v>
       </c>
       <c r="C28" t="n">
-        <v>0.793</v>
+        <v>0.661</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.019</v>
+        <v>22.238</v>
       </c>
       <c r="F28" t="n">
-        <v>11.078</v>
+        <v>10.991</v>
       </c>
       <c r="G28" t="n">
-        <v>61.175</v>
+        <v>43.697</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.512</v>
+        <v>0.399</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.367</v>
+        <v>1.693</v>
       </c>
       <c r="C29" t="n">
-        <v>5.664</v>
+        <v>0.284</v>
       </c>
       <c r="D29" t="n">
-        <v>3.613</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>22.205</v>
+        <v>21.558</v>
       </c>
       <c r="F29" t="n">
-        <v>10.799</v>
+        <v>10.421</v>
       </c>
       <c r="G29" t="n">
-        <v>71.66200000000001</v>
+        <v>61.837</v>
       </c>
       <c r="H29" t="n">
-        <v>4.842</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>6.896</v>
+        <v>0.828</v>
       </c>
       <c r="J29" t="n">
-        <v>11.724</v>
+        <v>0.067</v>
       </c>
       <c r="K29" t="n">
-        <v>9.029</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>17.681</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -11000,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.548</v>
+        <v>13.808</v>
       </c>
       <c r="F30" t="n">
-        <v>5.748</v>
+        <v>5.919</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.9401425521e-05</v>
+        <v>2.728599696e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0893835209e-05</v>
+        <v>1.668559104e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9740023801e-05</v>
+        <v>7.925450625000001e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2573021316e-05</v>
+        <v>5.204010312899999e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1917433889e-05</v>
+        <v>1.1205281025e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6922902724e-05</v>
+        <v>2.0888631841e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9110843161e-05</v>
+        <v>1.74900625e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>3.857296000000001e-05</v>
+        <v>4.694588890000001e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1736843961e-05</v>
+        <v>8.613696100000003e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.49278721e-05</v>
+        <v>8.7647044e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0470146249e-05</v>
+        <v>3.816768400000001e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3138087289e-05</v>
+        <v>1.36960209e-07</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.555913443999999e-06</v>
+        <v>1.823887849e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>5.895782656e-06</v>
+        <v>1.394200921e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1821560529e-05</v>
+        <v>3.877677441e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8598643401e-05</v>
+        <v>4.6969292176e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.850873081e-06</v>
+        <v>5.817570528999999e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3994404e-06</v>
+        <v>5.899008025000002e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8631158016e-05</v>
+        <v>1.129969e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8364586256e-05</v>
+        <v>3.750337599999999e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1764222369e-05</v>
+        <v>1.3942756e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9110574081e-05</v>
+        <v>5.866084000000001e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6255995001e-05</v>
+        <v>4.844401000000001e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>6.194791848999999e-06</v>
+        <v>2.585664e-09</v>
       </c>
     </row>
     <row r="4">
@@ -11201,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.445216256e-06</v>
+        <v>7.427260089999999e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>7.346268159999999e-07</v>
+        <v>3.96766561e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.440261201e-06</v>
+        <v>1.797251236e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.030457759999999e-05</v>
+        <v>3.87066276e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.483402499999999e-06</v>
+        <v>5.355166041000001e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>4.252735369e-06</v>
+        <v>3.487611136e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>8.744120100000002e-08</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2694969e-08</v>
+        <v>4.661281e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.46615616e-07</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8.231734809999998e-07</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7.846416400000002e-08</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5876e-07</v>
+        <v>4.040100000000001e-11</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.95811025e-07</v>
+        <v>3.39443776e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4249104e-08</v>
+        <v>2.3707161e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.442509159999999e-07</v>
+        <v>3.250809e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8053475329e-05</v>
+        <v>3.847129188099999e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.810075044000001e-06</v>
+        <v>8.960326281000003e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>5.909304383999999e-06</v>
+        <v>6.219215044e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.011322225000001e-06</v>
+        <v>2.52015625e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.090584576e-06</v>
+        <v>3.038049000000001e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.644942041e-06</v>
+        <v>1.00681156e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3079970641e-05</v>
+        <v>2.9838071169e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>8.030668996000001e-06</v>
+        <v>7.352548009000001e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>3.340262025e-06</v>
+        <v>2.035363225e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816464399999999e-08</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4.875263999999999e-07</v>
+        <v>2.002225e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>5.278749024999999e-06</v>
+        <v>8.584899999999997e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0191104401e-05</v>
+        <v>1.20409e-10</v>
       </c>
       <c r="L6" t="n">
-        <v>2.847396321e-06</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.100097023999998e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -11328,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.080772008333333e-06</v>
+        <v>4.436745633333333e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.529210785333334e-06</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2.349704560333334e-06</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3.842414408333332e-06</v>
+        <v>1.981881221333334e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792310536333332e-06</v>
+        <v>7.814530256333334e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>1.573138401333333e-06</v>
+        <v>4.155045453333333e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>6.575788800833332e-05</v>
+        <v>5.395835385633333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.472617876299999e-05</v>
+        <v>3.454673754133334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.672437120299999e-05</v>
+        <v>2.041803408333333e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>4.445482216033334e-05</v>
+        <v>3.845313510533333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>3.877715782533333e-05</v>
+        <v>6.010071480000001e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5514115072e-05</v>
+        <v>8.053391363333332e-07</v>
       </c>
     </row>
     <row r="8">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.098200100000001e-08</v>
+        <v>7.2267001e-08</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -11380,25 +11380,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.694513444e-06</v>
+        <v>5.603720164000002e-06</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0079456804e-05</v>
+        <v>1.9009515625e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.132638490000001e-07</v>
+        <v>5.887902250000001e-07</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.225616e-09</v>
+        <v>5.86756e-10</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.895632225e-06</v>
+        <v>7.2216004e-06</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -11414,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.356634253333333e-07</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3.608033333333334e-11</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6.120408333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.044873763333334e-07</v>
+        <v>4.406589603333334e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>3.210551960333334e-06</v>
+        <v>2.503202988e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>5.100563333333332e-08</v>
+        <v>3.949121333333334e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>3.123413333333333e-08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.870430083333333e-07</v>
+        <v>4.482296333333332e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>1.283802083333333e-07</v>
+        <v>1.370928e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>5.946269281333335e-06</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.56211968e-07</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1047683e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -11466,28 +11466,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.855224083333332e-07</v>
+        <v>3.416960963333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.847600833333333e-06</v>
+        <v>1.623129320333334e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>3.136333333333333e-10</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.261919999999999e-10</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6855075e-08</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.678440533333333e-08</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8.833968e-09</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2.694216333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -11509,22 +11509,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.445457869999999e-07</v>
+        <v>3.824148803333335e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.352435936333333e-06</v>
+        <v>1.265099745333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93548e-10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.785960333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.652565333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11552,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.732192053333333e-07</v>
+        <v>1.651098453333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.841480013333335e-07</v>
+        <v>7.536041013333334e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>2.507942533333333e-08</v>
+        <v>1.62867e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>3.893557763333333e-07</v>
+        <v>2.362081333333334e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11607,16 +11607,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.831083e-09</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6.097520833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>9.402400833333334e-08</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8287883e-08</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11672,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.9371290084e-05</v>
+        <v>9.317461729000001e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3152033929e-05</v>
+        <v>3.467796543999999e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>4.228328564099999e-05</v>
+        <v>7.266028080999999e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4763488256e-05</v>
+        <v>4.5174101764e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.631067044e-06</v>
+        <v>9.283515200999998e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.8700082961e-05</v>
+        <v>5.1588945424e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0843274384e-05</v>
+        <v>3.17730625e-07</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.843978688099999e-05</v>
+        <v>2.630869264e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4431580944e-05</v>
+        <v>4.718728249000001e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7603840064e-05</v>
+        <v>1.4279055025e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>6.0558811569e-05</v>
+        <v>2.365363225e-06</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6874163827e-05</v>
+        <v>4.554268181333334e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>2.725465704533334e-05</v>
+        <v>2.501816652e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>3.804213542533334e-05</v>
+        <v>1.026487808533333e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.828519960033332e-05</v>
+        <v>4.691125700833334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.420100800833334e-05</v>
+        <v>1.327167145633334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>5.998046600833333e-05</v>
+        <v>6.333743240533333e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>4.235837952533334e-05</v>
+        <v>1.1578919628e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>8.566325160333335e-06</v>
+        <v>1.522307080333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>5.944548180033333e-05</v>
+        <v>2.638650353633333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7200312467e-05</v>
+        <v>2.883930075e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>4.550195469633334e-05</v>
+        <v>1.929146868033334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.895226732033333e-05</v>
+        <v>3.654309205333333e-06</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.205386208133333e-05</v>
+        <v>3.112130208333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>1.043993222533333e-05</v>
+        <v>2.613818901333333e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>2.757412940833333e-05</v>
+        <v>1.3579391523e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.850301594799999e-05</v>
+        <v>5.7506868912e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.05779532e-05</v>
+        <v>1.039608880133333e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.593221632533333e-05</v>
+        <v>3.471800248033333e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>3.739337149633333e-05</v>
+        <v>9.580479362999998e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>5.038409045333333e-06</v>
+        <v>6.103280333333334e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>5.933151574533333e-05</v>
+        <v>5.586716840333335e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6241899187e-05</v>
+        <v>1.760794133333334e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>4.437938138699999e-05</v>
+        <v>8.952655151999998e-06</v>
       </c>
       <c r="M17" t="n">
-        <v>3.625403456033334e-05</v>
+        <v>1.728432027e-06</v>
       </c>
     </row>
     <row r="18">
@@ -11799,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.09637552e-07</v>
+        <v>5.48290083e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>2.80932987e-07</v>
+        <v>1.355692963333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>7.371482253333335e-07</v>
+        <v>5.347476029999999e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.290778560033334e-05</v>
+        <v>5.1604115148e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.771884280333334e-06</v>
+        <v>8.471472520333334e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.570345605333333e-06</v>
+        <v>6.551826401333335e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>2.917376853333333e-07</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2.557336033333334e-08</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.178509363333333e-07</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>3.52711947e-07</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9.119725453333332e-07</v>
+        <v>9.002936333333335e-09</v>
       </c>
       <c r="M18" t="n">
-        <v>2.432880853333333e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -11842,40 +11842,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.89655203e-07</v>
+        <v>1.071974963333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6310323e-08</v>
+        <v>6.774021333333332e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>2.85889932e-07</v>
+        <v>1.79026875e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.964371968533333e-05</v>
+        <v>4.885548853333333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.863296033333334e-06</v>
+        <v>7.786994216333332e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>5.034967201333333e-06</v>
+        <v>4.874849541333333e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>3.364443000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3.205400333333334e-09</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.221132e-09</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6272723e-08</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.407033633333333e-08</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7.947896333333335e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -11885,40 +11885,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.866629633333332e-06</v>
+        <v>5.819974165333333e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>5.129136705333333e-06</v>
+        <v>6.180937861333332e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>4.104828213333333e-07</v>
+        <v>6.869020083333335e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.603229203333334e-05</v>
+        <v>1.676343500833333e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.046963221333333e-06</v>
+        <v>3.258623376333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>4.245417008333334e-06</v>
+        <v>5.166501003e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>6.051472213333333e-07</v>
+        <v>4.029667499999999e-08</v>
       </c>
       <c r="I20" t="n">
-        <v>3.058280333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.725208333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.662865633333333e-06</v>
+        <v>3.033084033333332e-08</v>
       </c>
       <c r="L20" t="n">
-        <v>3.783387e-09</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>7.540053333333332e-10</v>
       </c>
     </row>
     <row r="21">
@@ -11928,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.685432216333331e-06</v>
+        <v>3.107815788e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>8.037913932000002e-06</v>
+        <v>3.271159323e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>6.616863053333334e-07</v>
+        <v>1.38679203e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.491004500833333e-05</v>
+        <v>1.3968045675e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.399671136333333e-06</v>
+        <v>2.340925068e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.490451656333333e-06</v>
+        <v>2.465620008333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317040870533334e-05</v>
+        <v>7.1853708e-08</v>
       </c>
       <c r="I21" t="n">
-        <v>1.536803333333333e-06</v>
+        <v>7.080960333333333e-09</v>
       </c>
       <c r="J21" t="n">
-        <v>2.662336925633333e-05</v>
+        <v>2.881140300000001e-08</v>
       </c>
       <c r="K21" t="n">
-        <v>1.580676288133333e-05</v>
+        <v>1.889244163333333e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>1.099805981633333e-05</v>
+        <v>8.484337199999999e-08</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.715124360033333e-05</v>
+        <v>4.356887643e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>3.166446803333333e-05</v>
+        <v>4.871222256333332e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>1.515553548033333e-05</v>
+        <v>4.301300279999999e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.852995020833333e-05</v>
+        <v>1.352199603333333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>2.909472492e-06</v>
+        <v>1.869404181333334e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>3.475892485333333e-06</v>
+        <v>1.6666347e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.802839840833333e-05</v>
+        <v>3.705096427200001e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.267474000133333e-05</v>
+        <v>9.515038736333332e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>6.3408650067e-05</v>
+        <v>3.097438596300001e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.007977365633334e-05</v>
+        <v>8.528534008333335e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>4.127059772033335e-05</v>
+        <v>7.570665675000001e-06</v>
       </c>
       <c r="M22" t="n">
-        <v>3.985414176133334e-05</v>
+        <v>1.190952013333334e-07</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5.60458276e-06</v>
+        <v>7.31864809e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>9.408942760000001e-06</v>
+        <v>5.235969599999999e-07</v>
       </c>
       <c r="D23" t="n">
-        <v>9.82947904e-06</v>
+        <v>3.938817599999999e-07</v>
       </c>
       <c r="E23" t="n">
-        <v>5.81822641e-06</v>
+        <v>4.64230116e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>9.057328899999998e-07</v>
+        <v>7.670256399999996e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4277621121e-05</v>
+        <v>9.812883600000002e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>3.076165210000001e-06</v>
+        <v>1.28459556e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>4.940839840000001e-06</v>
+        <v>4.41e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>3.170253025e-05</v>
+        <v>4.600596010000001e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>2.79524961e-06</v>
+        <v>1.10986225e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>9.503655839999998e-06</v>
+        <v>5.877230489999999e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>1.075380849e-05</v>
+        <v>9.810902499999998e-07</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.41211961e-06</v>
+        <v>4.7403225e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>6.449568160000001e-06</v>
+        <v>7.933464900000001e-07</v>
       </c>
       <c r="D24" t="n">
-        <v>4.774662009999999e-06</v>
+        <v>2.798410000000001e-07</v>
       </c>
       <c r="E24" t="n">
-        <v>6.67240561e-06</v>
+        <v>6.14147524e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09327936e-06</v>
+        <v>1.06729561e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5681801529e-05</v>
+        <v>1.4963405625e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.748963999999999e-06</v>
+        <v>2.07216025e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>4.21686225e-06</v>
+        <v>4.884100000000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>2.122352761e-05</v>
+        <v>5.095403289999999e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>2.62926225e-06</v>
+        <v>1.13976976e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>7.309993689999999e-06</v>
+        <v>7.066027240000001e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>7.88093329e-06</v>
+        <v>2.587272250000001e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12100,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.83954969e-06</v>
+        <v>1.37874564e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>3.11416609e-06</v>
+        <v>1.08097609e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>2.06152164e-06</v>
+        <v>5.145192899999999e-07</v>
       </c>
       <c r="E25" t="n">
-        <v>7.118757610000001e-06</v>
+        <v>6.98333476e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44504441e-06</v>
+        <v>1.38674176e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>7.537365123999998e-06</v>
+        <v>4.080271129e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>2.73141729e-06</v>
+        <v>7.334209600000002e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>1.22921569e-06</v>
+        <v>1.615441e-08</v>
       </c>
       <c r="J25" t="n">
-        <v>3.408085209999999e-06</v>
+        <v>1.500625e-08</v>
       </c>
       <c r="K25" t="n">
-        <v>4.472802010000001e-06</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7.538319360000001e-06</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.273928360000001e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -12143,37 +12143,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.049728399999999e-07</v>
+        <v>5.74564e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.26225225e-06</v>
+        <v>9.868435600000001e-07</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7405584e-07</v>
+        <v>1.2752041e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.03463844e-06</v>
+        <v>5.14654596e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.26990361e-06</v>
+        <v>1.27260961e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>9.273882601e-06</v>
+        <v>8.692578755999999e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>1.012036e-08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.405601e-08</v>
+        <v>4.97025e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>5.715360000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>2.53009e-09</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.5613721e-07</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12186,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.680299560000001e-06</v>
+        <v>3.386076099999999e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>1.009396441e-05</v>
+        <v>1.8198756e-07</v>
       </c>
       <c r="D27" t="n">
-        <v>7.440347290000001e-06</v>
+        <v>8.767520999999998e-08</v>
       </c>
       <c r="E27" t="n">
-        <v>5.890814410000001e-06</v>
+        <v>4.843080490000001e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.49401729e-06</v>
+        <v>1.20912016e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2025096281e-05</v>
+        <v>6.708920463999999e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>9.469159839999999e-06</v>
+        <v>4.81056489e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>1.63737616e-06</v>
+        <v>2.84091025e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>3.126151743999999e-05</v>
+        <v>1.8071001e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>1.18336e-05</v>
+        <v>1.41681409e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>1.453134399999999e-05</v>
+        <v>1.072955536e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>1.286369956e-05</v>
+        <v>6.953892100000002e-07</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.987809e-08</v>
+        <v>5.764801e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>6.288490000000001e-09</v>
+        <v>4.369210000000001e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.848363609999998e-06</v>
+        <v>4.945286440000001e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.22722084e-06</v>
+        <v>1.20802081e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>3.742380625e-06</v>
+        <v>1.909427809e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.62144e-09</v>
+        <v>1.59201e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9070689e-07</v>
+        <v>2.866249e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>3.2080896e-07</v>
+        <v>8.065599999999997e-10</v>
       </c>
       <c r="D29" t="n">
-        <v>1.3053769e-07</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.930620249999999e-06</v>
+        <v>4.64747364e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.16618401e-06</v>
+        <v>1.08597241e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>5.135442244e-06</v>
+        <v>3.823814569e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3444964e-07</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4.7554816e-07</v>
+        <v>6.855839999999999e-09</v>
       </c>
       <c r="J29" t="n">
-        <v>1.37452176e-06</v>
+        <v>4.489000000000001e-11</v>
       </c>
       <c r="K29" t="n">
-        <v>8.152284100000001e-07</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>3.126177610000001e-06</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.83548304e-06</v>
+        <v>1.90660864e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.303950400000001e-07</v>
+        <v>3.5034561e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="I2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="J2" t="n">
-        <v>0.123958</v>
+        <v>0.013542</v>
       </c>
       <c r="K2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="L2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="M2" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="3">
@@ -12482,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E3" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.122569</v>
+        <v>0.013542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="L3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="M3" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="4">
@@ -12525,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C4" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D4" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E4" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.124653</v>
+        <v>0.013194</v>
       </c>
       <c r="G4" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H4" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.051042</v>
+        <v>0.013542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M4" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="5">
@@ -12568,10 +12568,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="C5" t="n">
-        <v>0.124653</v>
+        <v>0.001042</v>
       </c>
       <c r="D5" t="n">
         <v>0.000694</v>
@@ -12609,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H6" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="J6" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="K6" t="n">
-        <v>0.124653</v>
+        <v>0.013194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M6" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="7">
@@ -12652,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C7" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="D7" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F7" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G7" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H7" t="n">
-        <v>0.080556</v>
+        <v>0.013542</v>
       </c>
       <c r="I7" t="n">
-        <v>0.045833</v>
+        <v>0.013542</v>
       </c>
       <c r="J7" t="n">
-        <v>0.047569</v>
+        <v>0.013542</v>
       </c>
       <c r="K7" t="n">
-        <v>0.061806</v>
+        <v>0.013542</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08784699999999999</v>
+        <v>0.013542</v>
       </c>
       <c r="M7" t="n">
-        <v>0.103472</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="8">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.121528</v>
+        <v>0.010417</v>
       </c>
       <c r="C8" t="n">
         <v>0.003472</v>
@@ -12704,19 +12704,19 @@
         <v>0.003472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.111111</v>
+        <v>0.010417</v>
       </c>
       <c r="F8" t="n">
-        <v>0.121528</v>
+        <v>0.010417</v>
       </c>
       <c r="G8" t="n">
-        <v>0.121528</v>
+        <v>0.010417</v>
       </c>
       <c r="H8" t="n">
         <v>0.003472</v>
       </c>
       <c r="I8" t="n">
-        <v>0.100694</v>
+        <v>0.010417</v>
       </c>
       <c r="J8" t="n">
         <v>0.003472</v>
@@ -12738,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="D9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F9" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G9" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="J9" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="K9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M9" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="10">
@@ -12790,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="H10" t="n">
-        <v>0.123958</v>
+        <v>0.000347</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08437500000000001</v>
+        <v>0.000347</v>
       </c>
       <c r="J10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="K10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L10" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12833,22 +12833,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="F11" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G11" t="n">
-        <v>0.124653</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.124653</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.124653</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12876,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12919,10 +12919,10 @@
         <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F13" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G13" t="n">
         <v>0.000347</v>
@@ -12931,16 +12931,16 @@
         <v>0.000347</v>
       </c>
       <c r="I13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="J13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="K13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12996,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C15" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D15" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E15" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="H15" t="n">
-        <v>0.046528</v>
+        <v>0.000347</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="K15" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="M15" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C16" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D16" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E16" t="n">
-        <v>0.124653</v>
+        <v>0.010764</v>
       </c>
       <c r="F16" t="n">
-        <v>0.124653</v>
+        <v>0.011458</v>
       </c>
       <c r="G16" t="n">
-        <v>0.021875</v>
+        <v>0.0125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.076389</v>
+        <v>0.013542</v>
       </c>
       <c r="I16" t="n">
-        <v>0.060764</v>
+        <v>0.013542</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07256899999999999</v>
+        <v>0.013542</v>
       </c>
       <c r="K16" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="L16" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="M16" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="17">
@@ -13080,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E17" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F17" t="n">
-        <v>0.101042</v>
+        <v>0.001042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="I17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="J17" t="n">
-        <v>0.100694</v>
+        <v>0.013542</v>
       </c>
       <c r="K17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="L17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="M17" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="18">
@@ -13123,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C18" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D18" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E18" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="G18" t="n">
-        <v>0.124653</v>
+        <v>0.001389</v>
       </c>
       <c r="H18" t="n">
-        <v>0.092361</v>
+        <v>0.000347</v>
       </c>
       <c r="I18" t="n">
-        <v>0.073958</v>
+        <v>0.000347</v>
       </c>
       <c r="J18" t="n">
-        <v>0.064236</v>
+        <v>0.000347</v>
       </c>
       <c r="K18" t="n">
-        <v>0.088542</v>
+        <v>0.000347</v>
       </c>
       <c r="L18" t="n">
-        <v>0.053125</v>
+        <v>0.013542</v>
       </c>
       <c r="M18" t="n">
-        <v>0.061458</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="19">
@@ -13166,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C19" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D19" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E19" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.044792</v>
+        <v>0.013542</v>
       </c>
       <c r="G19" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H19" t="n">
-        <v>0.092014</v>
+        <v>0.000347</v>
       </c>
       <c r="I19" t="n">
-        <v>0.100347</v>
+        <v>0.000347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1</v>
+        <v>0.000347</v>
       </c>
       <c r="K19" t="n">
-        <v>0.093056</v>
+        <v>0.000347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.052431</v>
+        <v>0.000347</v>
       </c>
       <c r="M19" t="n">
-        <v>0.067708</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="20">
@@ -13236,10 +13236,10 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="L20" t="n">
-        <v>0.026736</v>
+        <v>0.000347</v>
       </c>
       <c r="M20" t="n">
         <v>0.000347</v>
@@ -13252,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G21" t="n">
-        <v>0.124653</v>
+        <v>0.005903</v>
       </c>
       <c r="H21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="I21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.013542</v>
       </c>
       <c r="K21" t="n">
-        <v>0.101042</v>
+        <v>0.013542</v>
       </c>
       <c r="L21" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H22" t="n">
-        <v>0.052431</v>
+        <v>0.013542</v>
       </c>
       <c r="I22" t="n">
-        <v>0.021181</v>
+        <v>0.013542</v>
       </c>
       <c r="J22" t="n">
-        <v>0.073958</v>
+        <v>0.013542</v>
       </c>
       <c r="K22" t="n">
-        <v>0.118403</v>
+        <v>0.013542</v>
       </c>
       <c r="L22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="M22" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="23">
@@ -13338,40 +13338,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.028819</v>
+        <v>0.0125</v>
       </c>
       <c r="C23" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D23" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E23" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.123958</v>
+        <v>0.013542</v>
       </c>
       <c r="G23" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H23" t="n">
-        <v>0.033681</v>
+        <v>0.013542</v>
       </c>
       <c r="I23" t="n">
-        <v>0.022222</v>
+        <v>0.013542</v>
       </c>
       <c r="J23" t="n">
-        <v>0.117708</v>
+        <v>0.013542</v>
       </c>
       <c r="K23" t="n">
-        <v>0.031944</v>
+        <v>0.013542</v>
       </c>
       <c r="L23" t="n">
-        <v>0.042014</v>
+        <v>0.013542</v>
       </c>
       <c r="M23" t="n">
-        <v>0.045486</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="24">
@@ -13381,40 +13381,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C24" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="D24" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E24" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="F24" t="n">
-        <v>0.080208</v>
+        <v>0.000347</v>
       </c>
       <c r="G24" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="H24" t="n">
-        <v>0.024306</v>
+        <v>0.013542</v>
       </c>
       <c r="I24" t="n">
-        <v>0.017361</v>
+        <v>0.013542</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09375</v>
+        <v>0.013542</v>
       </c>
       <c r="K24" t="n">
-        <v>0.030556</v>
+        <v>0.013542</v>
       </c>
       <c r="L24" t="n">
-        <v>0.025347</v>
+        <v>0.013542</v>
       </c>
       <c r="M24" t="n">
-        <v>0.036111</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="25">
@@ -13424,40 +13424,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.124653</v>
+        <v>0.001042</v>
       </c>
       <c r="D25" t="n">
-        <v>0.124653</v>
+        <v>0.001042</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.106597</v>
+        <v>0.000694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H25" t="n">
-        <v>0.043403</v>
+        <v>0.013542</v>
       </c>
       <c r="I25" t="n">
-        <v>0.092014</v>
+        <v>0.011111</v>
       </c>
       <c r="J25" t="n">
-        <v>0.054167</v>
+        <v>0.013542</v>
       </c>
       <c r="K25" t="n">
-        <v>0.080208</v>
+        <v>0.000347</v>
       </c>
       <c r="L25" t="n">
-        <v>0.115625</v>
+        <v>0.001042</v>
       </c>
       <c r="M25" t="n">
-        <v>0.103472</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="26">
@@ -13470,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.124653</v>
+        <v>0.010069</v>
       </c>
       <c r="D26" t="n">
-        <v>0.124653</v>
+        <v>0.000694</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13482,22 +13482,22 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08472200000000001</v>
+        <v>0.000347</v>
       </c>
       <c r="I26" t="n">
-        <v>0.124653</v>
+        <v>0.012153</v>
       </c>
       <c r="J26" t="n">
-        <v>0.104167</v>
+        <v>0.000347</v>
       </c>
       <c r="K26" t="n">
-        <v>0.072917</v>
+        <v>0.000347</v>
       </c>
       <c r="L26" t="n">
-        <v>0.089931</v>
+        <v>0.000347</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C27" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="D27" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="E27" t="n">
-        <v>0.124653</v>
+        <v>0.001389</v>
       </c>
       <c r="F27" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="G27" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07083299999999999</v>
+        <v>0.013542</v>
       </c>
       <c r="I27" t="n">
-        <v>0.015278</v>
+        <v>0.013542</v>
       </c>
       <c r="J27" t="n">
-        <v>0.067014</v>
+        <v>0.013542</v>
       </c>
       <c r="K27" t="n">
-        <v>0.057639</v>
+        <v>0.013542</v>
       </c>
       <c r="L27" t="n">
-        <v>0.043403</v>
+        <v>0.013542</v>
       </c>
       <c r="M27" t="n">
-        <v>0.057639</v>
+        <v>0.013542</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.052431</v>
+        <v>0.013542</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,13 +13568,13 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
       </c>
       <c r="I28" t="n">
-        <v>0.040625</v>
+        <v>0.013542</v>
       </c>
       <c r="J28" t="n">
         <v>0.000347</v>
@@ -13596,40 +13596,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="C29" t="n">
-        <v>0.124306</v>
+        <v>0.001042</v>
       </c>
       <c r="D29" t="n">
-        <v>0.124653</v>
+        <v>0.000347</v>
       </c>
       <c r="E29" t="n">
-        <v>0.123958</v>
+        <v>0.013542</v>
       </c>
       <c r="F29" t="n">
-        <v>0.124653</v>
+        <v>0.001042</v>
       </c>
       <c r="G29" t="n">
-        <v>0.124653</v>
+        <v>0.013542</v>
       </c>
       <c r="H29" t="n">
-        <v>0.092708</v>
+        <v>0.000347</v>
       </c>
       <c r="I29" t="n">
-        <v>0.093056</v>
+        <v>0.010069</v>
       </c>
       <c r="J29" t="n">
-        <v>0.058333</v>
+        <v>0.013542</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08819399999999999</v>
+        <v>0.000347</v>
       </c>
       <c r="L29" t="n">
-        <v>0.077431</v>
+        <v>0.000347</v>
       </c>
       <c r="M29" t="n">
-        <v>0.117708</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="30">

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,22 +1831,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.001</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.007</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="G2" t="n">
-        <v>0.024</v>
+        <v>0.005</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1874,22 +1874,22 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.002</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.007</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.006</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.044</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.034</v>
+        <v>0.008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -2055,25 +2055,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.002</v>
       </c>
-      <c r="F7" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>0.002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2098,10 +2098,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.001</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.003</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2390,22 +2390,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.051</v>
+        <v>0.011</v>
       </c>
       <c r="F15" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2414,16 +2414,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.001</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.003</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="M15" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.002</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.01</v>
-      </c>
       <c r="E16" t="n">
-        <v>0.055</v>
+        <v>0.012</v>
       </c>
       <c r="F16" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.016</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.001</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="M16" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2476,37 +2476,37 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.003</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F17" t="n">
         <v>0.003</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.012</v>
-      </c>
       <c r="G17" t="n">
-        <v>0.04</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2519,22 +2519,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.056</v>
+        <v>0.012</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,22 +2605,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.001</v>
       </c>
-      <c r="E20" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.004</v>
-      </c>
       <c r="G20" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2648,22 +2648,22 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.004</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.016</v>
-      </c>
       <c r="F21" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="F22" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.016</v>
+        <v>0.002</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2743,28 +2743,28 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2780,34 +2780,34 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="F24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2820,22 +2820,22 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.002</v>
       </c>
-      <c r="C25" t="n">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.001</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.004</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.001</v>
       </c>
-      <c r="C26" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.006</v>
-      </c>
       <c r="F26" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.001</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.007</v>
-      </c>
       <c r="H27" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3001,13 +3001,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.004</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.08333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.236</v>
+        <v>42.491</v>
       </c>
       <c r="C2" t="n">
-        <v>40.848</v>
+        <v>33.013</v>
       </c>
       <c r="D2" t="n">
-        <v>89.02500000000001</v>
+        <v>74.485</v>
       </c>
       <c r="E2" t="n">
-        <v>228.123</v>
+        <v>227.211</v>
       </c>
       <c r="F2" t="n">
-        <v>105.855</v>
+        <v>105.694</v>
       </c>
       <c r="G2" t="n">
-        <v>144.529</v>
+        <v>142.874</v>
       </c>
       <c r="H2" t="n">
-        <v>13.225</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>21.667</v>
+        <v>1.394</v>
       </c>
       <c r="J2" t="n">
-        <v>9.281000000000001</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9.362</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6.178</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>11.703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7186,13 +7186,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.707</v>
+        <v>40.778</v>
       </c>
       <c r="C3" t="n">
-        <v>37.339</v>
+        <v>34.942</v>
       </c>
       <c r="D3" t="n">
-        <v>62.271</v>
+        <v>59.212</v>
       </c>
       <c r="E3" t="n">
         <v>217.978</v>
@@ -7201,25 +7201,25 @@
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>76.80500000000001</v>
+        <v>76.501</v>
       </c>
       <c r="H3" t="n">
-        <v>1.063</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>6.124</v>
+        <v>1.561</v>
       </c>
       <c r="J3" t="n">
-        <v>3.734</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.422</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.201</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7229,28 +7229,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.253</v>
+        <v>25.982</v>
       </c>
       <c r="C4" t="n">
-        <v>19.919</v>
+        <v>19.544</v>
       </c>
       <c r="D4" t="n">
-        <v>42.394</v>
+        <v>41.82</v>
       </c>
       <c r="E4" t="n">
-        <v>196.74</v>
+        <v>196.131</v>
       </c>
       <c r="F4" t="n">
-        <v>73.182</v>
+        <v>72.789</v>
       </c>
       <c r="G4" t="n">
-        <v>59.056</v>
+        <v>58.103</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.159</v>
+        <v>1.131</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -7262,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7313,34 +7313,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.875</v>
+        <v>12.732</v>
       </c>
       <c r="C6" t="n">
-        <v>1.743</v>
+        <v>1.601</v>
       </c>
       <c r="D6" t="n">
-        <v>10.034</v>
+        <v>8.722</v>
       </c>
       <c r="E6" t="n">
-        <v>172.737</v>
+        <v>172.055</v>
       </c>
       <c r="F6" t="n">
-        <v>85.747</v>
+        <v>85.541</v>
       </c>
       <c r="G6" t="n">
-        <v>45.115</v>
+        <v>44.255</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.415</v>
+        <v>0.899</v>
       </c>
       <c r="J6" t="n">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.537</v>
+        <v>7.628</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -7365,31 +7365,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>77.108</v>
+        <v>76.08</v>
       </c>
       <c r="F7" t="n">
-        <v>153.113</v>
+        <v>150.504</v>
       </c>
       <c r="G7" t="n">
-        <v>35.306</v>
+        <v>34.369</v>
       </c>
       <c r="H7" t="n">
-        <v>402.337</v>
+        <v>214.948</v>
       </c>
       <c r="I7" t="n">
-        <v>321.932</v>
+        <v>275.053</v>
       </c>
       <c r="J7" t="n">
-        <v>78.265</v>
+        <v>4.675</v>
       </c>
       <c r="K7" t="n">
-        <v>339.646</v>
+        <v>254.836</v>
       </c>
       <c r="L7" t="n">
-        <v>42.462</v>
+        <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>49.153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7398,42 +7398,18 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>8.500999999999999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>74.858</v>
-      </c>
-      <c r="F8" t="n">
-        <v>137.875</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24.265</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>88.336</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7451,22 +7427,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>36.359</v>
+        <v>36.049</v>
       </c>
       <c r="F9" t="n">
-        <v>86.658</v>
+        <v>85.033</v>
       </c>
       <c r="G9" t="n">
-        <v>3.442</v>
+        <v>3.236</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3.667</v>
+        <v>1.442</v>
       </c>
       <c r="J9" t="n">
-        <v>2.028</v>
+        <v>0.442</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -7497,7 +7473,7 @@
         <v>32.368</v>
       </c>
       <c r="F10" t="n">
-        <v>69.78100000000001</v>
+        <v>69.432</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -7540,7 +7516,7 @@
         <v>34.141</v>
       </c>
       <c r="F11" t="n">
-        <v>61.606</v>
+        <v>61.315</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -7583,7 +7559,7 @@
         <v>22.546</v>
       </c>
       <c r="F12" t="n">
-        <v>47.548</v>
+        <v>47.514</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7623,10 +7599,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.699</v>
+        <v>0.643</v>
       </c>
       <c r="F13" t="n">
-        <v>26.62</v>
+        <v>26.56</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7700,16 +7676,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.527</v>
+        <v>82.124</v>
       </c>
       <c r="C15" t="n">
-        <v>58.888</v>
+        <v>46.643</v>
       </c>
       <c r="D15" t="n">
-        <v>85.241</v>
+        <v>71.619</v>
       </c>
       <c r="E15" t="n">
-        <v>212.542</v>
+        <v>208.792</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
@@ -7722,7 +7698,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>51.292</v>
+        <v>13.238</v>
       </c>
       <c r="K15" t="n">
         <v>81.736</v>
@@ -7731,7 +7707,7 @@
         <v>138.554</v>
       </c>
       <c r="M15" t="n">
-        <v>48.635</v>
+        <v>17.575</v>
       </c>
     </row>
     <row r="16">
@@ -7741,40 +7717,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116.888</v>
+        <v>96.947</v>
       </c>
       <c r="C16" t="n">
-        <v>86.634</v>
+        <v>71.104</v>
       </c>
       <c r="D16" t="n">
-        <v>175.484</v>
+        <v>155.105</v>
       </c>
       <c r="E16" t="n">
-        <v>377.251</v>
+        <v>377.207</v>
       </c>
       <c r="F16" t="n">
-        <v>200.497</v>
+        <v>199.136</v>
       </c>
       <c r="G16" t="n">
-        <v>436.177</v>
+        <v>435.996</v>
       </c>
       <c r="H16" t="n">
-        <v>186.378</v>
+        <v>59.522</v>
       </c>
       <c r="I16" t="n">
-        <v>67.57899999999999</v>
+        <v>0.443</v>
       </c>
       <c r="J16" t="n">
-        <v>281.353</v>
+        <v>38.478</v>
       </c>
       <c r="K16" t="n">
-        <v>93.015</v>
+        <v>61.709</v>
       </c>
       <c r="L16" t="n">
-        <v>240.571</v>
+        <v>109.779</v>
       </c>
       <c r="M16" t="n">
-        <v>104.704</v>
+        <v>11.038</v>
       </c>
     </row>
     <row r="17">
@@ -7784,13 +7760,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>96.625</v>
+        <v>92.18300000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>88.55200000000001</v>
+        <v>86.048</v>
       </c>
       <c r="D17" t="n">
-        <v>201.837</v>
+        <v>201.537</v>
       </c>
       <c r="E17" t="n">
         <v>416.187</v>
@@ -7799,25 +7775,25 @@
         <v>177.486</v>
       </c>
       <c r="G17" t="n">
-        <v>322.729</v>
+        <v>322.479</v>
       </c>
       <c r="H17" t="n">
-        <v>169.533</v>
+        <v>6.425</v>
       </c>
       <c r="I17" t="n">
-        <v>42.79</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>129.461</v>
+        <v>4.222</v>
       </c>
       <c r="K17" t="n">
-        <v>72.68000000000001</v>
+        <v>14.504</v>
       </c>
       <c r="L17" t="n">
-        <v>163.884</v>
+        <v>48.374</v>
       </c>
       <c r="M17" t="n">
-        <v>72.009</v>
+        <v>3.567</v>
       </c>
     </row>
     <row r="18">
@@ -7827,16 +7803,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.557</v>
+        <v>39.234</v>
       </c>
       <c r="C18" t="n">
-        <v>20.167</v>
+        <v>18.643</v>
       </c>
       <c r="D18" t="n">
-        <v>40.053</v>
+        <v>39.319</v>
       </c>
       <c r="E18" t="n">
-        <v>393.462</v>
+        <v>393.227</v>
       </c>
       <c r="F18" t="n">
         <v>159.617</v>
@@ -7857,7 +7833,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5.197</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -7870,22 +7846,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.933</v>
+        <v>17.301</v>
       </c>
       <c r="C19" t="n">
-        <v>4.508</v>
+        <v>3.241</v>
       </c>
       <c r="D19" t="n">
-        <v>23.175</v>
+        <v>22.803</v>
       </c>
       <c r="E19" t="n">
-        <v>382.84</v>
+        <v>382.753</v>
       </c>
       <c r="F19" t="n">
-        <v>152.843</v>
+        <v>152.154</v>
       </c>
       <c r="G19" t="n">
-        <v>120.932</v>
+        <v>120.812</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -7928,7 +7904,7 @@
         <v>99.241</v>
       </c>
       <c r="G20" t="n">
-        <v>125.58</v>
+        <v>125.406</v>
       </c>
       <c r="H20" t="n">
         <v>101.544</v>
@@ -7956,37 +7932,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.55800000000001</v>
+        <v>96.51600000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>99.063</v>
+        <v>98.995</v>
       </c>
       <c r="D21" t="n">
-        <v>20.397</v>
+        <v>18.796</v>
       </c>
       <c r="E21" t="n">
-        <v>204.705</v>
+        <v>204.369</v>
       </c>
       <c r="F21" t="n">
-        <v>83.80200000000001</v>
+        <v>83.34399999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>86.164</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>14.682</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4.609</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>9.297000000000001</v>
+        <v>0.534</v>
       </c>
       <c r="K21" t="n">
-        <v>23.807</v>
+        <v>0.082</v>
       </c>
       <c r="L21" t="n">
-        <v>15.954</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7999,40 +7975,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>114.327</v>
+        <v>96.35899999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>120.887</v>
+        <v>95.316</v>
       </c>
       <c r="D22" t="n">
-        <v>35.922</v>
+        <v>22.094</v>
       </c>
       <c r="E22" t="n">
-        <v>201.41</v>
+        <v>201.306</v>
       </c>
       <c r="F22" t="n">
-        <v>74.88800000000001</v>
+        <v>74.621</v>
       </c>
       <c r="G22" t="n">
-        <v>70.70999999999999</v>
+        <v>70.05800000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>333.396</v>
+        <v>19.641</v>
       </c>
       <c r="I22" t="n">
-        <v>168.953</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>304.833</v>
+        <v>1.117</v>
       </c>
       <c r="K22" t="n">
-        <v>159.955</v>
+        <v>58.242</v>
       </c>
       <c r="L22" t="n">
-        <v>150.705</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>18.902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8042,40 +8018,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55.505</v>
+        <v>27.521</v>
       </c>
       <c r="C23" t="n">
-        <v>7.236</v>
+        <v>1.717</v>
       </c>
       <c r="D23" t="n">
-        <v>6.276</v>
+        <v>0.17</v>
       </c>
       <c r="E23" t="n">
         <v>22.371</v>
       </c>
       <c r="F23" t="n">
-        <v>8.757999999999999</v>
+        <v>8.746</v>
       </c>
       <c r="G23" t="n">
-        <v>99.06</v>
+        <v>97.43600000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>11.334</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>1.751</v>
       </c>
       <c r="J23" t="n">
-        <v>21.449</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>10.535</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>24.243</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9.904999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -8085,16 +8061,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.885</v>
+        <v>5.95</v>
       </c>
       <c r="C24" t="n">
-        <v>8.907</v>
+        <v>6.083</v>
       </c>
       <c r="D24" t="n">
-        <v>5.29</v>
+        <v>1.636</v>
       </c>
       <c r="E24" t="n">
-        <v>24.782</v>
+        <v>24.681</v>
       </c>
       <c r="F24" t="n">
         <v>10.442</v>
@@ -8103,22 +8079,22 @@
         <v>123.314</v>
       </c>
       <c r="H24" t="n">
-        <v>14.395</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>22.1</v>
+        <v>1.238</v>
       </c>
       <c r="J24" t="n">
-        <v>22.573</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>10.676</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>26.582</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>16.085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -8143,16 +8119,16 @@
         <v>12.001</v>
       </c>
       <c r="G25" t="n">
-        <v>63.877</v>
+        <v>57.234</v>
       </c>
       <c r="H25" t="n">
-        <v>8.564</v>
+        <v>0.49</v>
       </c>
       <c r="I25" t="n">
-        <v>1.314</v>
+        <v>0.486</v>
       </c>
       <c r="J25" t="n">
-        <v>1.225</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -8174,7 +8150,7 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>11.094</v>
+        <v>7.148</v>
       </c>
       <c r="D26" t="n">
         <v>3.837</v>
@@ -8186,13 +8162,13 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>93.23399999999999</v>
+        <v>91.337</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.706</v>
+        <v>0.28</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -8214,40 +8190,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.819</v>
+        <v>3.977</v>
       </c>
       <c r="C27" t="n">
         <v>6.667</v>
       </c>
       <c r="D27" t="n">
-        <v>2.961</v>
+        <v>0.124</v>
       </c>
       <c r="E27" t="n">
         <v>22.295</v>
       </c>
       <c r="F27" t="n">
-        <v>10.996</v>
+        <v>10.847</v>
       </c>
       <c r="G27" t="n">
-        <v>81.908</v>
+        <v>78.401</v>
       </c>
       <c r="H27" t="n">
-        <v>21.933</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>16.855</v>
+        <v>0.874</v>
       </c>
       <c r="J27" t="n">
-        <v>42.51</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>11.903</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>32.756</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>8.339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -8257,7 +8233,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.401</v>
+        <v>2.174</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8272,13 +8248,13 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>43.697</v>
+        <v>38.04</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.399</v>
+        <v>0.184</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -8300,7 +8276,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.693</v>
+        <v>1.367</v>
       </c>
       <c r="C29" t="n">
         <v>0.9340000000000001</v>
@@ -8309,22 +8285,22 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>21.558</v>
+        <v>21.446</v>
       </c>
       <c r="F29" t="n">
         <v>10.421</v>
       </c>
       <c r="G29" t="n">
-        <v>61.837</v>
+        <v>59.63</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.855</v>
+        <v>0.09</v>
       </c>
       <c r="J29" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -8467,40 +8443,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728599696e-06</v>
+        <v>1.805485081e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.668559104e-06</v>
+        <v>1.089858169e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.925450625000001e-06</v>
+        <v>5.548015225e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.204010312899999e-05</v>
+        <v>5.162483852100002e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1205281025e-05</v>
+        <v>1.1171221636e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0888631841e-05</v>
+        <v>2.0412979876e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.74900625e-07</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4.694588890000001e-07</v>
+        <v>1.943236e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>8.613696100000003e-08</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8.7647044e-08</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3.816768400000001e-08</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.36960209e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -8510,13 +8486,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.823887849e-06</v>
+        <v>1.662845284e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.394200921e-06</v>
+        <v>1.220943364e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.877677441e-06</v>
+        <v>3.506060944e-06</v>
       </c>
       <c r="E3" t="n">
         <v>4.7514408484e-05</v>
@@ -8525,25 +8501,25 @@
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.899008025000002e-06</v>
+        <v>5.852403000999999e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.129969e-09</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3.750337599999999e-08</v>
+        <v>2.436721e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3942756e-08</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5.866084000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.844401000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.585664e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -8553,28 +8529,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.427260089999999e-07</v>
+        <v>6.750643239999999e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.96766561e-07</v>
+        <v>3.819679359999999e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.797251236e-06</v>
+        <v>1.7489124e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.87066276e-05</v>
+        <v>3.8467369161e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.355605124e-06</v>
+        <v>5.298238521000002e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.487611136e-06</v>
+        <v>3.375958609e-06</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4.661281e-09</v>
+        <v>1.279161e-09</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -8586,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.040100000000001e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8637,34 +8613,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.52015625e-07</v>
+        <v>1.62103824e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>3.038049000000001e-09</v>
+        <v>2.563201e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.00681156e-07</v>
+        <v>7.607328399999998e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9838071169e-05</v>
+        <v>2.960292302500001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.352548009000001e-06</v>
+        <v>7.317262680999998e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.035363225e-06</v>
+        <v>1.958505025e-06</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.002225e-09</v>
+        <v>8.082010000000001e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.584899999999997e-11</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.69744e-10</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -8680,7 +8656,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.436745633333333e-08</v>
+        <v>1.939546133333334e-08</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -8689,31 +8665,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.981881221333334e-06</v>
+        <v>1.9293888e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.814530256333334e-06</v>
+        <v>7.550484672e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>4.155045453333333e-07</v>
+        <v>3.937427203333333e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>5.395835385633333e-05</v>
+        <v>1.540088090133333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>3.454673754133334e-05</v>
+        <v>2.521805093633333e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.041803408333333e-06</v>
+        <v>7.285208333333332e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.845313510533333e-05</v>
+        <v>2.164712896533333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.010071480000001e-07</v>
+        <v>1.008333333333333e-10</v>
       </c>
       <c r="M7" t="n">
-        <v>8.053391363333332e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8722,42 +8698,18 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7.2267001e-08</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5.603720164000002e-06</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.9009515625e-05</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5.887902250000001e-07</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.86756e-10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.803248896e-06</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8775,22 +8727,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4.406589603333334e-07</v>
+        <v>4.331768003333333e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.503202988e-06</v>
+        <v>2.410203696333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.949121333333334e-09</v>
+        <v>3.490565333333334e-09</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.482296333333332e-09</v>
+        <v>6.931213333333333e-10</v>
       </c>
       <c r="J9" t="n">
-        <v>1.370928e-09</v>
+        <v>6.512133333333333e-11</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -8821,7 +8773,7 @@
         <v>3.492291413333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.623129320333334e-06</v>
+        <v>1.606934208e-06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8864,7 +8816,7 @@
         <v>3.885359603333333e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.265099745333333e-06</v>
+        <v>1.253176408333333e-06</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8907,7 +8859,7 @@
         <v>1.694407053333334e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.536041013333334e-07</v>
+        <v>7.52526732e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8947,10 +8899,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.62867e-10</v>
+        <v>1.378163333333333e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>2.362081333333334e-07</v>
+        <v>2.351445333333333e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -9024,16 +8976,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.317461729000001e-06</v>
+        <v>6.744351375999998e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>3.467796543999999e-06</v>
+        <v>2.175569449e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>7.266028080999999e-06</v>
+        <v>5.129281161e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5174101764e-05</v>
+        <v>4.3594099264e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
@@ -9046,7 +8998,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.630869264e-06</v>
+        <v>1.75244644e-07</v>
       </c>
       <c r="K15" t="n">
         <v>6.680773696000001e-06</v>
@@ -9055,7 +9007,7 @@
         <v>1.9197210916e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.365363225e-06</v>
+        <v>3.08880625e-07</v>
       </c>
     </row>
     <row r="16">
@@ -9065,40 +9017,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.554268181333334e-06</v>
+        <v>3.132906936333334e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>2.501816652e-06</v>
+        <v>1.685259605333333e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.026487808533333e-05</v>
+        <v>8.019187008333333e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>4.743943900033334e-05</v>
+        <v>4.742837361633334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.339968233633333e-05</v>
+        <v>1.321838216533333e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.341679177633334e-05</v>
+        <v>6.3364170672e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1578919628e-05</v>
+        <v>1.180956161333333e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>1.522307080333333e-06</v>
+        <v>6.541633333333333e-11</v>
       </c>
       <c r="J16" t="n">
-        <v>2.638650353633333e-05</v>
+        <v>4.935188279999999e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>2.883930075e-06</v>
+        <v>1.269333560333333e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>1.929146868033334e-05</v>
+        <v>4.017142947e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.654309205333333e-06</v>
+        <v>4.061248133333334e-08</v>
       </c>
     </row>
     <row r="17">
@@ -9108,13 +9060,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.112130208333333e-06</v>
+        <v>2.832568496333333e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>2.613818901333333e-06</v>
+        <v>2.468086101333333e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3579391523e-05</v>
+        <v>1.3539054123e-05</v>
       </c>
       <c r="E17" t="n">
         <v>5.773720632300001e-05</v>
@@ -9123,25 +9075,25 @@
         <v>1.0500426732e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.471800248033333e-05</v>
+        <v>3.466423514699999e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>9.580479362999998e-06</v>
+        <v>1.376020833333333e-08</v>
       </c>
       <c r="I17" t="n">
-        <v>6.103280333333334e-07</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5.586716840333335e-06</v>
+        <v>5.941761333333333e-09</v>
       </c>
       <c r="K17" t="n">
-        <v>1.760794133333334e-06</v>
+        <v>7.012200533333333e-08</v>
       </c>
       <c r="L17" t="n">
-        <v>8.952655151999998e-06</v>
+        <v>7.800146253333334e-07</v>
       </c>
       <c r="M17" t="n">
-        <v>1.728432027e-06</v>
+        <v>4.241163000000001e-09</v>
       </c>
     </row>
     <row r="18">
@@ -9151,16 +9103,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.48290083e-07</v>
+        <v>5.131022520000001e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.355692963333334e-07</v>
+        <v>1.158538163333333e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>5.347476029999999e-07</v>
+        <v>5.153279203333333e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.1604115148e-05</v>
+        <v>5.154249117633333e-05</v>
       </c>
       <c r="F18" t="n">
         <v>8.492528896333331e-06</v>
@@ -9181,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9.002936333333335e-09</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9194,22 +9146,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.071974963333333e-07</v>
+        <v>9.977486699999996e-08</v>
       </c>
       <c r="C19" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>3.501360333333333e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.79026875e-07</v>
+        <v>1.73325603e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.885548853333333e-05</v>
+        <v>4.883328633633334e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.786994216333332e-06</v>
+        <v>7.716946571999999e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.874849541333333e-06</v>
+        <v>4.865179781333334e-06</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -9252,7 +9204,7 @@
         <v>3.282925360333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>5.2567788e-06</v>
+        <v>5.242221612000001e-06</v>
       </c>
       <c r="H20" t="n">
         <v>3.437061312e-06</v>
@@ -9280,37 +9232,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.107815788e-06</v>
+        <v>3.105112752e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>3.271159323e-06</v>
+        <v>3.266670008333333e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38679203e-07</v>
+        <v>1.177632053333333e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3968045675e-05</v>
+        <v>1.3922229387e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.340925068e-06</v>
+        <v>2.315407445333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.474744965333333e-06</v>
+        <v>2.4659067e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>7.1853708e-08</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>7.080960333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.881140300000001e-08</v>
+        <v>9.505200000000003e-11</v>
       </c>
       <c r="K21" t="n">
-        <v>1.889244163333333e-07</v>
+        <v>2.241333333333333e-12</v>
       </c>
       <c r="L21" t="n">
-        <v>8.484337199999999e-08</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9323,40 +9275,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.356887643e-06</v>
+        <v>3.095018960333333e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>4.871222256333332e-06</v>
+        <v>3.028379952e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>4.301300279999999e-07</v>
+        <v>1.627149453333334e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.352199603333333e-05</v>
+        <v>1.3508035212e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.869404181333334e-06</v>
+        <v>1.856097880333333e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6666347e-06</v>
+        <v>1.636041121333334e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.705096427200001e-05</v>
+        <v>1.28589627e-07</v>
       </c>
       <c r="I22" t="n">
-        <v>9.515038736333332e-06</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.097438596300001e-05</v>
+        <v>4.158963333333333e-10</v>
       </c>
       <c r="K22" t="n">
-        <v>8.528534008333335e-06</v>
+        <v>1.130710188e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>7.570665675000001e-06</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.190952013333334e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -9366,40 +9318,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.080805025e-05</v>
+        <v>7.57405441e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>5.235969599999999e-07</v>
+        <v>2.948089e-08</v>
       </c>
       <c r="D23" t="n">
-        <v>3.938817599999999e-07</v>
+        <v>2.89e-10</v>
       </c>
       <c r="E23" t="n">
         <v>5.00461641e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>7.670256399999996e-07</v>
+        <v>7.649251600000001e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.812883600000002e-06</v>
+        <v>9.493774096000001e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>1.28459556e-06</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4.41e-06</v>
+        <v>3.066000999999999e-08</v>
       </c>
       <c r="J23" t="n">
-        <v>4.600596010000001e-06</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.10986225e-06</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>5.877230489999999e-06</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9.810902499999998e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -9409,16 +9361,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.7403225e-07</v>
+        <v>3.540250000000001e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>7.933464900000001e-07</v>
+        <v>3.7002889e-07</v>
       </c>
       <c r="D24" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>2.676496e-08</v>
       </c>
       <c r="E24" t="n">
-        <v>6.14147524e-06</v>
+        <v>6.09151761e-06</v>
       </c>
       <c r="F24" t="n">
         <v>1.09035364e-06</v>
@@ -9427,22 +9379,22 @@
         <v>1.5206342596e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.07216025e-06</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4.884100000000001e-06</v>
+        <v>1.532644e-08</v>
       </c>
       <c r="J24" t="n">
-        <v>5.095403289999999e-06</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.13976976e-06</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>7.066027240000001e-06</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.587272250000001e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -9467,16 +9419,16 @@
         <v>1.44024001e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>4.080271129e-06</v>
+        <v>3.275730756e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>7.334209600000002e-07</v>
+        <v>2.401e-09</v>
       </c>
       <c r="I25" t="n">
-        <v>1.726596e-08</v>
+        <v>2.36196e-09</v>
       </c>
       <c r="J25" t="n">
-        <v>1.500625e-08</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -9498,7 +9450,7 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>1.23076836e-06</v>
+        <v>5.1093904e-07</v>
       </c>
       <c r="D26" t="n">
         <v>1.4722569e-07</v>
@@ -9510,13 +9462,13 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.692578755999999e-06</v>
+        <v>8.342447569000002e-06</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4.984359999999999e-09</v>
+        <v>7.840000000000002e-10</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -9538,40 +9490,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.386076099999999e-07</v>
+        <v>1.5816529e-07</v>
       </c>
       <c r="C27" t="n">
         <v>4.4448889e-07</v>
       </c>
       <c r="D27" t="n">
-        <v>8.767520999999998e-08</v>
+        <v>1.5376e-10</v>
       </c>
       <c r="E27" t="n">
         <v>4.970670250000002e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.20912016e-06</v>
+        <v>1.17657409e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>6.708920463999999e-06</v>
+        <v>6.146716801e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>4.81056489e-06</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2.84091025e-06</v>
+        <v>7.638759999999999e-09</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8071001e-05</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.41681409e-06</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.072955536e-05</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6.953892100000002e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -9581,7 +9533,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.764801e-08</v>
+        <v>4.726275999999999e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9596,13 +9548,13 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.909427809e-06</v>
+        <v>1.4470416e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.59201e-09</v>
+        <v>3.3856e-10</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -9624,7 +9576,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.866249e-08</v>
+        <v>1.868689e-08</v>
       </c>
       <c r="C29" t="n">
         <v>8.723560000000001e-09</v>
@@ -9633,22 +9585,22 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.64747364e-06</v>
+        <v>4.59930916e-06</v>
       </c>
       <c r="F29" t="n">
         <v>1.08597241e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>3.823814569e-06</v>
+        <v>3.5557369e-06</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>7.310249999999999e-09</v>
+        <v>8.099999999999998e-11</v>
       </c>
       <c r="J29" t="n">
-        <v>4.489000000000001e-11</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -9791,40 +9743,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.236</v>
+        <v>41.655</v>
       </c>
       <c r="C2" t="n">
-        <v>40.848</v>
+        <v>33.013</v>
       </c>
       <c r="D2" t="n">
-        <v>89.02500000000001</v>
+        <v>74.485</v>
       </c>
       <c r="E2" t="n">
-        <v>228.123</v>
+        <v>226.953</v>
       </c>
       <c r="F2" t="n">
-        <v>105.855</v>
+        <v>105.694</v>
       </c>
       <c r="G2" t="n">
-        <v>144.529</v>
+        <v>142.874</v>
       </c>
       <c r="H2" t="n">
-        <v>13.225</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>21.667</v>
+        <v>1.115</v>
       </c>
       <c r="J2" t="n">
-        <v>9.281000000000001</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>9.362</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6.178</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>11.703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -9834,40 +9786,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.707</v>
+        <v>40.098</v>
       </c>
       <c r="C3" t="n">
-        <v>37.339</v>
+        <v>34.545</v>
       </c>
       <c r="D3" t="n">
-        <v>62.271</v>
+        <v>58.052</v>
       </c>
       <c r="E3" t="n">
-        <v>216.724</v>
+        <v>217.489</v>
       </c>
       <c r="F3" t="n">
-        <v>76.273</v>
+        <v>76.753</v>
       </c>
       <c r="G3" t="n">
-        <v>76.80500000000001</v>
+        <v>76.501</v>
       </c>
       <c r="H3" t="n">
-        <v>1.063</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>6.124</v>
+        <v>1.127</v>
       </c>
       <c r="J3" t="n">
-        <v>3.734</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.422</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2.201</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -9877,28 +9829,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.253</v>
+        <v>25.982</v>
       </c>
       <c r="C4" t="n">
-        <v>19.919</v>
+        <v>19.197</v>
       </c>
       <c r="D4" t="n">
-        <v>42.394</v>
+        <v>41.357</v>
       </c>
       <c r="E4" t="n">
-        <v>196.74</v>
+        <v>196.131</v>
       </c>
       <c r="F4" t="n">
-        <v>73.179</v>
+        <v>72.789</v>
       </c>
       <c r="G4" t="n">
-        <v>59.056</v>
+        <v>58.103</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.159</v>
+        <v>0.805</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -9910,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -9920,22 +9872,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.424</v>
+        <v>18.334</v>
       </c>
       <c r="C5" t="n">
-        <v>4.869</v>
+        <v>5.148</v>
       </c>
       <c r="D5" t="n">
-        <v>18.03</v>
+        <v>18.238</v>
       </c>
       <c r="E5" t="n">
-        <v>196.141</v>
+        <v>195.511</v>
       </c>
       <c r="F5" t="n">
-        <v>94.65900000000001</v>
+        <v>94.895</v>
       </c>
       <c r="G5" t="n">
-        <v>78.86199999999999</v>
+        <v>79.226</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9961,34 +9913,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.875</v>
+        <v>12.542</v>
       </c>
       <c r="C6" t="n">
-        <v>1.743</v>
+        <v>1.053</v>
       </c>
       <c r="D6" t="n">
-        <v>10.034</v>
+        <v>8.552</v>
       </c>
       <c r="E6" t="n">
-        <v>172.737</v>
+        <v>172.055</v>
       </c>
       <c r="F6" t="n">
-        <v>85.747</v>
+        <v>85.48</v>
       </c>
       <c r="G6" t="n">
-        <v>45.115</v>
+        <v>44.255</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.415</v>
+        <v>0.794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.347</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -10004,7 +9956,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.537</v>
+        <v>7.595</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -10013,31 +9965,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>77.108</v>
+        <v>76.08</v>
       </c>
       <c r="F7" t="n">
-        <v>153.113</v>
+        <v>150.272</v>
       </c>
       <c r="G7" t="n">
-        <v>35.306</v>
+        <v>34.208</v>
       </c>
       <c r="H7" t="n">
-        <v>402.337</v>
+        <v>143.924</v>
       </c>
       <c r="I7" t="n">
-        <v>321.932</v>
+        <v>192.448</v>
       </c>
       <c r="J7" t="n">
-        <v>78.265</v>
+        <v>4.675</v>
       </c>
       <c r="K7" t="n">
-        <v>339.646</v>
+        <v>224.924</v>
       </c>
       <c r="L7" t="n">
-        <v>42.462</v>
+        <v>0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>49.153</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -10046,42 +9998,18 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>8.500999999999999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>74.858</v>
-      </c>
-      <c r="F8" t="n">
-        <v>137.875</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24.265</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>84.98</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10099,22 +10027,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>36.359</v>
+        <v>35.994</v>
       </c>
       <c r="F9" t="n">
-        <v>86.658</v>
+        <v>84.928</v>
       </c>
       <c r="G9" t="n">
-        <v>3.442</v>
+        <v>3.223</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3.667</v>
+        <v>1.442</v>
       </c>
       <c r="J9" t="n">
-        <v>2.028</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -10142,10 +10070,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.017</v>
+        <v>32.17</v>
       </c>
       <c r="F10" t="n">
-        <v>69.78100000000001</v>
+        <v>69.276</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -10185,10 +10113,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>33.871</v>
+        <v>33.989</v>
       </c>
       <c r="F11" t="n">
-        <v>61.606</v>
+        <v>61.171</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -10228,10 +10156,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.256</v>
+        <v>22.445</v>
       </c>
       <c r="F12" t="n">
-        <v>47.548</v>
+        <v>47.431</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10271,10 +10199,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.699</v>
+        <v>0.593</v>
       </c>
       <c r="F13" t="n">
-        <v>26.62</v>
+        <v>26.159</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -10348,38 +10276,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.527</v>
+        <v>80.235</v>
       </c>
       <c r="C15" t="n">
-        <v>58.888</v>
+        <v>45.415</v>
       </c>
       <c r="D15" t="n">
-        <v>85.241</v>
+        <v>69.904</v>
       </c>
       <c r="E15" t="n">
-        <v>212.542</v>
+        <v>208.792</v>
       </c>
       <c r="F15" t="n">
-        <v>96.351</v>
+        <v>96.212</v>
       </c>
       <c r="G15" t="n">
-        <v>227.132</v>
+        <v>227.015</v>
       </c>
       <c r="H15" t="n">
-        <v>17.825</v>
+        <v>2.681</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>51.292</v>
+        <v>2.775</v>
       </c>
       <c r="K15" t="n">
-        <v>68.693</v>
+        <v>45.67</v>
       </c>
       <c r="L15" t="n">
-        <v>119.495</v>
+        <v>46.579</v>
       </c>
       <c r="M15" t="n">
-        <v>48.635</v>
+        <v>10.018</v>
       </c>
     </row>
     <row r="16">
@@ -10389,40 +10317,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>116.888</v>
+        <v>95.76600000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>86.634</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>175.484</v>
+        <v>153.779</v>
       </c>
       <c r="E16" t="n">
-        <v>375.145</v>
+        <v>377.098</v>
       </c>
       <c r="F16" t="n">
-        <v>199.537</v>
+        <v>197.952</v>
       </c>
       <c r="G16" t="n">
-        <v>435.904</v>
+        <v>435.996</v>
       </c>
       <c r="H16" t="n">
-        <v>186.378</v>
+        <v>10.418</v>
       </c>
       <c r="I16" t="n">
-        <v>67.57899999999999</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>281.353</v>
+        <v>10.048</v>
       </c>
       <c r="K16" t="n">
-        <v>93.015</v>
+        <v>38.655</v>
       </c>
       <c r="L16" t="n">
-        <v>240.571</v>
+        <v>85.613</v>
       </c>
       <c r="M16" t="n">
-        <v>104.704</v>
+        <v>8.475</v>
       </c>
     </row>
     <row r="17">
@@ -10432,40 +10360,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>96.625</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>88.55200000000001</v>
+        <v>85.08499999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>201.837</v>
+        <v>196.673</v>
       </c>
       <c r="E17" t="n">
-        <v>415.356</v>
+        <v>415.737</v>
       </c>
       <c r="F17" t="n">
-        <v>176.602</v>
+        <v>177.048</v>
       </c>
       <c r="G17" t="n">
-        <v>322.729</v>
+        <v>322.329</v>
       </c>
       <c r="H17" t="n">
-        <v>169.533</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>42.79</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>129.461</v>
+        <v>0.075</v>
       </c>
       <c r="K17" t="n">
-        <v>72.68000000000001</v>
+        <v>10.614</v>
       </c>
       <c r="L17" t="n">
-        <v>163.884</v>
+        <v>38.936</v>
       </c>
       <c r="M17" t="n">
-        <v>72.009</v>
+        <v>3.173</v>
       </c>
     </row>
     <row r="18">
@@ -10475,19 +10403,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.557</v>
+        <v>38.885</v>
       </c>
       <c r="C18" t="n">
-        <v>20.167</v>
+        <v>18.22</v>
       </c>
       <c r="D18" t="n">
-        <v>40.053</v>
+        <v>38.09</v>
       </c>
       <c r="E18" t="n">
-        <v>393.462</v>
+        <v>393.227</v>
       </c>
       <c r="F18" t="n">
-        <v>159.419</v>
+        <v>159.022</v>
       </c>
       <c r="G18" t="n">
         <v>140.198</v>
@@ -10505,7 +10433,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>5.197</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -10518,22 +10446,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.933</v>
+        <v>16.939</v>
       </c>
       <c r="C19" t="n">
-        <v>4.508</v>
+        <v>2.914</v>
       </c>
       <c r="D19" t="n">
-        <v>23.175</v>
+        <v>21.791</v>
       </c>
       <c r="E19" t="n">
-        <v>382.84</v>
+        <v>382.328</v>
       </c>
       <c r="F19" t="n">
-        <v>152.843</v>
+        <v>152.154</v>
       </c>
       <c r="G19" t="n">
-        <v>120.932</v>
+        <v>120.812</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10561,25 +10489,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>132.136</v>
+        <v>132.625</v>
       </c>
       <c r="C20" t="n">
-        <v>136.172</v>
+        <v>138.198</v>
       </c>
       <c r="D20" t="n">
-        <v>45.395</v>
+        <v>45.368</v>
       </c>
       <c r="E20" t="n">
-        <v>224.255</v>
+        <v>224.826</v>
       </c>
       <c r="F20" t="n">
-        <v>98.873</v>
+        <v>99.00700000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>124.497</v>
+        <v>125.406</v>
       </c>
       <c r="H20" t="n">
-        <v>10.995</v>
+        <v>17.737</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -10588,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>9.539</v>
+        <v>4.986</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.504</v>
+        <v>12.607</v>
       </c>
     </row>
     <row r="21">
@@ -10604,37 +10532,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.55800000000001</v>
+        <v>95.017</v>
       </c>
       <c r="C21" t="n">
-        <v>99.063</v>
+        <v>97.836</v>
       </c>
       <c r="D21" t="n">
-        <v>20.397</v>
+        <v>18.113</v>
       </c>
       <c r="E21" t="n">
-        <v>204.705</v>
+        <v>204.369</v>
       </c>
       <c r="F21" t="n">
-        <v>83.80200000000001</v>
+        <v>83.313</v>
       </c>
       <c r="G21" t="n">
-        <v>86.005</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>14.682</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4.609</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>9.297000000000001</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>23.807</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15.954</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10647,40 +10575,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>114.327</v>
+        <v>95.029</v>
       </c>
       <c r="C22" t="n">
-        <v>120.887</v>
+        <v>94.398</v>
       </c>
       <c r="D22" t="n">
-        <v>35.922</v>
+        <v>22.094</v>
       </c>
       <c r="E22" t="n">
-        <v>201.41</v>
+        <v>200.965</v>
       </c>
       <c r="F22" t="n">
-        <v>74.88800000000001</v>
+        <v>74.34699999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>70.70999999999999</v>
+        <v>70.051</v>
       </c>
       <c r="H22" t="n">
-        <v>333.396</v>
+        <v>19.518</v>
       </c>
       <c r="I22" t="n">
-        <v>168.953</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>304.833</v>
+        <v>1.048</v>
       </c>
       <c r="K22" t="n">
-        <v>159.955</v>
+        <v>34.998</v>
       </c>
       <c r="L22" t="n">
-        <v>150.705</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>18.902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -10690,40 +10618,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.053</v>
+        <v>27.521</v>
       </c>
       <c r="C23" t="n">
-        <v>7.236</v>
+        <v>1.433</v>
       </c>
       <c r="D23" t="n">
-        <v>6.276</v>
+        <v>0.09</v>
       </c>
       <c r="E23" t="n">
-        <v>21.546</v>
+        <v>21.579</v>
       </c>
       <c r="F23" t="n">
-        <v>8.757999999999999</v>
+        <v>8.698</v>
       </c>
       <c r="G23" t="n">
-        <v>99.06</v>
+        <v>97.333</v>
       </c>
       <c r="H23" t="n">
-        <v>11.334</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>1.751</v>
       </c>
       <c r="J23" t="n">
-        <v>21.449</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>10.535</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>24.243</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9.904999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -10733,40 +10661,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.885</v>
+        <v>5.551</v>
       </c>
       <c r="C24" t="n">
-        <v>8.907</v>
+        <v>5.93</v>
       </c>
       <c r="D24" t="n">
-        <v>5.29</v>
+        <v>1.38</v>
       </c>
       <c r="E24" t="n">
-        <v>24.782</v>
+        <v>24.548</v>
       </c>
       <c r="F24" t="n">
-        <v>10.331</v>
+        <v>10.275</v>
       </c>
       <c r="G24" t="n">
-        <v>122.325</v>
+        <v>122.502</v>
       </c>
       <c r="H24" t="n">
-        <v>14.395</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>22.1</v>
+        <v>1.238</v>
       </c>
       <c r="J24" t="n">
-        <v>22.573</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>10.676</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>26.582</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>16.085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -10776,31 +10704,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.742</v>
+        <v>11.665</v>
       </c>
       <c r="C25" t="n">
-        <v>10.397</v>
+        <v>10.307</v>
       </c>
       <c r="D25" t="n">
-        <v>7.173</v>
+        <v>7.096</v>
       </c>
       <c r="E25" t="n">
-        <v>26.426</v>
+        <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>11.776</v>
+        <v>11.755</v>
       </c>
       <c r="G25" t="n">
-        <v>63.877</v>
+        <v>57.234</v>
       </c>
       <c r="H25" t="n">
-        <v>8.564</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1.271</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.225</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -10819,28 +10747,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.58</v>
+        <v>7.487</v>
       </c>
       <c r="C26" t="n">
-        <v>9.933999999999999</v>
+        <v>5.694</v>
       </c>
       <c r="D26" t="n">
-        <v>3.571</v>
+        <v>3.318</v>
       </c>
       <c r="E26" t="n">
-        <v>22.686</v>
+        <v>22.679</v>
       </c>
       <c r="F26" t="n">
-        <v>11.281</v>
+        <v>11.332</v>
       </c>
       <c r="G26" t="n">
-        <v>93.23399999999999</v>
+        <v>91.337</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -10862,40 +10790,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.819</v>
+        <v>3.708</v>
       </c>
       <c r="C27" t="n">
-        <v>4.266</v>
+        <v>2.249</v>
       </c>
       <c r="D27" t="n">
-        <v>2.961</v>
+        <v>0.006</v>
       </c>
       <c r="E27" t="n">
-        <v>22.007</v>
+        <v>21.705</v>
       </c>
       <c r="F27" t="n">
-        <v>10.996</v>
+        <v>10.837</v>
       </c>
       <c r="G27" t="n">
-        <v>81.908</v>
+        <v>78.401</v>
       </c>
       <c r="H27" t="n">
-        <v>21.933</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>16.855</v>
+        <v>0.874</v>
       </c>
       <c r="J27" t="n">
-        <v>42.51</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>11.903</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>32.756</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>8.339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -10905,28 +10833,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.401</v>
+        <v>2.147</v>
       </c>
       <c r="C28" t="n">
-        <v>0.661</v>
+        <v>0.541</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.238</v>
+        <v>22.316</v>
       </c>
       <c r="F28" t="n">
-        <v>10.991</v>
+        <v>11.046</v>
       </c>
       <c r="G28" t="n">
-        <v>43.697</v>
+        <v>38.04</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.399</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10948,31 +10876,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.693</v>
+        <v>1.293</v>
       </c>
       <c r="C29" t="n">
-        <v>0.284</v>
+        <v>0.126</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>21.558</v>
+        <v>21.435</v>
       </c>
       <c r="F29" t="n">
-        <v>10.421</v>
+        <v>10.391</v>
       </c>
       <c r="G29" t="n">
-        <v>61.837</v>
+        <v>59.63</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.828</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -11000,10 +10928,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.808</v>
+        <v>13.836</v>
       </c>
       <c r="F30" t="n">
-        <v>5.919</v>
+        <v>5.937</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11115,40 +11043,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.728599696e-06</v>
+        <v>1.735139025000001e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.668559104e-06</v>
+        <v>1.089858169e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>7.925450625000001e-06</v>
+        <v>5.548015225e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>5.204010312899999e-05</v>
+        <v>5.150766420900001e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1205281025e-05</v>
+        <v>1.1171221636e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0888631841e-05</v>
+        <v>2.0412979876e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.74900625e-07</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4.694588890000001e-07</v>
+        <v>1.243225e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>8.613696100000003e-08</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>8.7647044e-08</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3.816768400000001e-08</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.36960209e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -11158,40 +11086,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.823887849e-06</v>
+        <v>1.607849604e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.394200921e-06</v>
+        <v>1.193357025e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.877677441e-06</v>
+        <v>3.370034704e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6969292176e-05</v>
+        <v>4.730146512100001e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.817570528999999e-06</v>
+        <v>5.891023009e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.899008025000002e-06</v>
+        <v>5.852403000999999e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.129969e-09</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3.750337599999999e-08</v>
+        <v>1.270129e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3942756e-08</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5.866084000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4.844401000000001e-09</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.585664e-09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -11201,28 +11129,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.427260089999999e-07</v>
+        <v>6.750643239999999e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.96766561e-07</v>
+        <v>3.68524809e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.797251236e-06</v>
+        <v>1.710401449e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.87066276e-05</v>
+        <v>3.8467369161e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.355166041000001e-06</v>
+        <v>5.298238521000002e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.487611136e-06</v>
+        <v>3.375958609e-06</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>4.661281e-09</v>
+        <v>6.48025e-10</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -11234,7 +11162,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.040100000000001e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -11244,22 +11172,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.39443776e-07</v>
+        <v>3.36135556e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3707161e-08</v>
+        <v>2.6501904e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.250809e-07</v>
+        <v>3.32624644e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.847129188099999e-05</v>
+        <v>3.8224551121e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>8.960326281000003e-06</v>
+        <v>9.005061024999999e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>6.219215044e-06</v>
+        <v>6.276759076e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11285,34 +11213,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.52015625e-07</v>
+        <v>1.57301764e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>3.038049000000001e-09</v>
+        <v>1.108809e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.00681156e-07</v>
+        <v>7.313670399999997e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9838071169e-05</v>
+        <v>2.960292302500001e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.352548009000001e-06</v>
+        <v>7.3068304e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>2.035363225e-06</v>
+        <v>1.958505025e-06</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2.002225e-09</v>
+        <v>6.30436e-10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.584899999999997e-11</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.20409e-10</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -11328,7 +11256,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.436745633333333e-08</v>
+        <v>1.922800833333333e-08</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -11337,31 +11265,31 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.981881221333334e-06</v>
+        <v>1.9293888e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.814530256333334e-06</v>
+        <v>7.527224661333332e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>4.155045453333333e-07</v>
+        <v>3.900624213333332e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>5.395835385633333e-05</v>
+        <v>6.904705925333332e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>3.454673754133334e-05</v>
+        <v>1.234541090133334e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>2.041803408333333e-06</v>
+        <v>7.285208333333332e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>3.845313510533333e-05</v>
+        <v>1.686360192533334e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>6.010071480000001e-07</v>
+        <v>1.008333333333333e-10</v>
       </c>
       <c r="M7" t="n">
-        <v>8.053391363333332e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -11370,42 +11298,18 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7.2267001e-08</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5.603720164000002e-06</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.9009515625e-05</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5.887902250000001e-07</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.86756e-10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.2216004e-06</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11423,22 +11327,22 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4.406589603333334e-07</v>
+        <v>4.318560119999999e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>2.503202988e-06</v>
+        <v>2.404255061333334e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.949121333333334e-09</v>
+        <v>3.462576333333333e-09</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.482296333333332e-09</v>
+        <v>6.931213333333333e-10</v>
       </c>
       <c r="J9" t="n">
-        <v>1.370928e-09</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -11466,10 +11370,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.416960963333334e-07</v>
+        <v>3.449696333333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.623129320333334e-06</v>
+        <v>1.599721391999999e-06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -11509,10 +11413,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.824148803333335e-07</v>
+        <v>3.850840403333332e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.265099745333333e-06</v>
+        <v>1.247297080333333e-06</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -11552,10 +11456,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.651098453333334e-07</v>
+        <v>1.679260083333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.536041013333334e-07</v>
+        <v>7.498999203333331e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11595,10 +11499,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.62867e-10</v>
+        <v>1.172163333333333e-10</v>
       </c>
       <c r="F13" t="n">
-        <v>2.362081333333334e-07</v>
+        <v>2.280977603333333e-07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11672,38 +11576,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.317461729000001e-06</v>
+        <v>6.437655225e-06</v>
       </c>
       <c r="C15" t="n">
-        <v>3.467796543999999e-06</v>
+        <v>2.062522225e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>7.266028080999999e-06</v>
+        <v>4.886569215999999e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5174101764e-05</v>
+        <v>4.3594099264e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.283515200999998e-06</v>
+        <v>9.256748944000002e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1588945424e-05</v>
+        <v>5.1535810225e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>3.17730625e-07</v>
+        <v>7.187761000000001e-09</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.630869264e-06</v>
+        <v>7.700625e-09</v>
       </c>
       <c r="K15" t="n">
-        <v>4.718728249000001e-06</v>
+        <v>2.085748900000001e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4279055025e-05</v>
+        <v>2.169603241e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>2.365363225e-06</v>
+        <v>1.00360324e-07</v>
       </c>
     </row>
     <row r="16">
@@ -11713,40 +11617,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.554268181333334e-06</v>
+        <v>3.057042252e-06</v>
       </c>
       <c r="C16" t="n">
-        <v>2.501816652e-06</v>
+        <v>1.6300683e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.026487808533333e-05</v>
+        <v>7.882660280333334e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>4.691125700833334e-05</v>
+        <v>4.740096720133333e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.327167145633334e-05</v>
+        <v>1.3061664768e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.333743240533333e-05</v>
+        <v>6.3364170672e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1578919628e-05</v>
+        <v>3.617824133333332e-08</v>
       </c>
       <c r="I16" t="n">
-        <v>1.522307080333333e-06</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.638650353633333e-05</v>
+        <v>3.365410133333333e-08</v>
       </c>
       <c r="K16" t="n">
-        <v>2.883930075e-06</v>
+        <v>4.980696750000001e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>1.929146868033334e-05</v>
+        <v>2.443195256333333e-06</v>
       </c>
       <c r="M16" t="n">
-        <v>3.654309205333333e-06</v>
+        <v>2.3941875e-08</v>
       </c>
     </row>
     <row r="17">
@@ -11756,40 +11660,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.112130208333333e-06</v>
+        <v>2.754270000000001e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>2.613818901333333e-06</v>
+        <v>2.413152408333333e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3579391523e-05</v>
+        <v>1.289342297633334e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.7506868912e-05</v>
+        <v>5.761241772300001e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.039608880133333e-05</v>
+        <v>1.0448664768e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.471800248033333e-05</v>
+        <v>3.463199474700001e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>9.580479362999998e-06</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>6.103280333333334e-07</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5.586716840333335e-06</v>
+        <v>1.875e-12</v>
       </c>
       <c r="K17" t="n">
-        <v>1.760794133333334e-06</v>
+        <v>3.7552332e-08</v>
       </c>
       <c r="L17" t="n">
-        <v>8.952655151999998e-06</v>
+        <v>5.053373653333333e-07</v>
       </c>
       <c r="M17" t="n">
-        <v>1.728432027e-06</v>
+        <v>3.355976333333333e-09</v>
       </c>
     </row>
     <row r="18">
@@ -11799,19 +11703,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.48290083e-07</v>
+        <v>5.040144083333332e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.355692963333334e-07</v>
+        <v>1.106561333333333e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>5.347476029999999e-07</v>
+        <v>4.836160333333335e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.1604115148e-05</v>
+        <v>5.154249117633333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.471472520333334e-06</v>
+        <v>8.429332161333334e-06</v>
       </c>
       <c r="G18" t="n">
         <v>6.551826401333335e-06</v>
@@ -11829,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9.002936333333335e-09</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -11842,22 +11746,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.071974963333333e-07</v>
+        <v>9.564324033333333e-08</v>
       </c>
       <c r="C19" t="n">
-        <v>6.774021333333332e-09</v>
+        <v>2.830465333333334e-09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.79026875e-07</v>
+        <v>1.582825603333334e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.885548853333333e-05</v>
+        <v>4.872489986133333e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.786994216333332e-06</v>
+        <v>7.716946571999999e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.874849541333333e-06</v>
+        <v>4.865179781333334e-06</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -11885,25 +11789,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.819974165333333e-06</v>
+        <v>5.863130208333333e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>6.180937861333332e-06</v>
+        <v>6.366229068000001e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>6.869020083333335e-07</v>
+        <v>6.860851413333336e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.676343500833333e-05</v>
+        <v>1.6848910092e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.258623376333333e-06</v>
+        <v>3.267462016333334e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>5.166501003e-06</v>
+        <v>5.242221612000001e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>4.029667499999999e-08</v>
+        <v>1.048670563333333e-07</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -11912,13 +11816,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3.033084033333332e-08</v>
+        <v>8.286731999999999e-09</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.540053333333332e-10</v>
+        <v>5.297881633333333e-08</v>
       </c>
     </row>
     <row r="21">
@@ -11928,37 +11832,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.107815788e-06</v>
+        <v>3.009410096333333e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>3.271159323e-06</v>
+        <v>3.190627631999999e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>1.38679203e-07</v>
+        <v>1.093602563333333e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3968045675e-05</v>
+        <v>1.3922229387e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.340925068e-06</v>
+        <v>2.313685323e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.465620008333333e-06</v>
+        <v>2.4659067e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>7.1853708e-08</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>7.080960333333333e-09</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.881140300000001e-08</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.889244163333333e-07</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>8.484337199999999e-08</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11971,40 +11875,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.356887643e-06</v>
+        <v>3.010170280333333e-06</v>
       </c>
       <c r="C22" t="n">
-        <v>4.871222256333332e-06</v>
+        <v>2.970327468e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>4.301300279999999e-07</v>
+        <v>1.627149453333334e-07</v>
       </c>
       <c r="E22" t="n">
-        <v>1.352199603333333e-05</v>
+        <v>1.346231040833333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.869404181333334e-06</v>
+        <v>1.842492136333333e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6666347e-06</v>
+        <v>1.635714200333333e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.705096427200001e-05</v>
+        <v>1.26984108e-07</v>
       </c>
       <c r="I22" t="n">
-        <v>9.515038736333332e-06</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.097438596300001e-05</v>
+        <v>3.661013333333334e-10</v>
       </c>
       <c r="K22" t="n">
-        <v>8.528534008333335e-06</v>
+        <v>4.082866679999999e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>7.570665675000001e-06</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.190952013333334e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -12014,40 +11918,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.31864809e-06</v>
+        <v>7.57405441e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>5.235969599999999e-07</v>
+        <v>2.053489e-08</v>
       </c>
       <c r="D23" t="n">
-        <v>3.938817599999999e-07</v>
+        <v>8.099999999999998e-11</v>
       </c>
       <c r="E23" t="n">
-        <v>4.64230116e-06</v>
+        <v>4.65653241e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>7.670256399999996e-07</v>
+        <v>7.565520400000002e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.812883600000002e-06</v>
+        <v>9.473712889000001e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>1.28459556e-06</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4.41e-06</v>
+        <v>3.066000999999999e-08</v>
       </c>
       <c r="J23" t="n">
-        <v>4.600596010000001e-06</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.10986225e-06</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>5.877230489999999e-06</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>9.810902499999998e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -12057,40 +11961,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.7403225e-07</v>
+        <v>3.0813601e-07</v>
       </c>
       <c r="C24" t="n">
-        <v>7.933464900000001e-07</v>
+        <v>3.516489999999999e-07</v>
       </c>
       <c r="D24" t="n">
-        <v>2.798410000000001e-07</v>
+        <v>1.9044e-08</v>
       </c>
       <c r="E24" t="n">
-        <v>6.14147524e-06</v>
+        <v>6.026043039999998e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.06729561e-06</v>
+        <v>1.05575625e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4963405625e-05</v>
+        <v>1.5006740004e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.07216025e-06</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4.884100000000001e-06</v>
+        <v>1.532644e-08</v>
       </c>
       <c r="J24" t="n">
-        <v>5.095403289999999e-06</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.13976976e-06</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>7.066027240000001e-06</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.587272250000001e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -12100,31 +12004,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.37874564e-06</v>
+        <v>1.36072225e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.08097609e-06</v>
+        <v>1.06234249e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>5.145192899999999e-07</v>
+        <v>5.0353216e-07</v>
       </c>
       <c r="E25" t="n">
-        <v>6.98333476e-06</v>
+        <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.38674176e-06</v>
+        <v>1.381800250000001e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>4.080271129e-06</v>
+        <v>3.275730756e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>7.334209600000002e-07</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1.615441e-08</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.500625e-08</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -12143,28 +12047,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.74564e-07</v>
+        <v>5.6055169e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>9.868435600000001e-07</v>
+        <v>3.2421636e-07</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2752041e-07</v>
+        <v>1.1009124e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.14654596e-06</v>
+        <v>5.143370409999999e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.27260961e-06</v>
+        <v>1.28414224e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.692578755999999e-06</v>
+        <v>8.342447569000002e-06</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4.97025e-09</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -12186,40 +12090,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.386076099999999e-07</v>
+        <v>1.3749264e-07</v>
       </c>
       <c r="C27" t="n">
-        <v>1.8198756e-07</v>
+        <v>5.058001000000001e-08</v>
       </c>
       <c r="D27" t="n">
-        <v>8.767520999999998e-08</v>
+        <v>3.6e-13</v>
       </c>
       <c r="E27" t="n">
-        <v>4.843080490000001e-06</v>
+        <v>4.711070249999999e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.20912016e-06</v>
+        <v>1.17440569e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>6.708920463999999e-06</v>
+        <v>6.146716801e-06</v>
       </c>
       <c r="H27" t="n">
-        <v>4.81056489e-06</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2.84091025e-06</v>
+        <v>7.638759999999999e-09</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8071001e-05</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.41681409e-06</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.072955536e-05</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>6.953892100000002e-07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -12229,28 +12133,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5.764801e-08</v>
+        <v>4.609608999999999e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>4.369210000000001e-09</v>
+        <v>2.92681e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.945286440000001e-06</v>
+        <v>4.98003856e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.20802081e-06</v>
+        <v>1.22014116e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.909427809e-06</v>
+        <v>1.4470416e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1.59201e-09</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12272,31 +12176,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.866249e-08</v>
+        <v>1.671849e-08</v>
       </c>
       <c r="C29" t="n">
-        <v>8.065599999999997e-10</v>
+        <v>1.5876e-10</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>4.64747364e-06</v>
+        <v>4.59459225e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08597241e-06</v>
+        <v>1.07972881e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>3.823814569e-06</v>
+        <v>3.5557369e-06</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>6.855839999999999e-09</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>4.489000000000001e-11</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -12324,10 +12228,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.90660864e-06</v>
+        <v>1.91434896e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.5034561e-07</v>
+        <v>3.524796900000001e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12439,40 +12343,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C2" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="D2" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="E2" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="F2" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I2" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J2" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K2" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M2" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="3">
@@ -12482,13 +12386,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C3" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="D3" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="E3" t="n">
         <v>0.000694</v>
@@ -12497,25 +12401,25 @@
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.013542</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="J3" t="n">
-        <v>0.013542</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.013542</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.013542</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.013542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -12525,28 +12429,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="C4" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="D4" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.013194</v>
+        <v>0.003125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H4" t="n">
         <v>0.000347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="J4" t="n">
         <v>0.000347</v>
@@ -12558,7 +12462,7 @@
         <v>0.000347</v>
       </c>
       <c r="M4" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="5">
@@ -12609,34 +12513,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="C6" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="D6" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E6" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.013542</v>
+        <v>0.001389</v>
       </c>
       <c r="G6" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H6" t="n">
         <v>0.000347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="J6" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K6" t="n">
-        <v>0.013194</v>
+        <v>0.000347</v>
       </c>
       <c r="L6" t="n">
         <v>0.000347</v>
@@ -12652,7 +12556,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="C7" t="n">
         <v>0.000347</v>
@@ -12661,31 +12565,31 @@
         <v>0.000347</v>
       </c>
       <c r="E7" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="F7" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="G7" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="H7" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I7" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J7" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="K7" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L7" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="M7" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="8">
@@ -12694,42 +12598,18 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.010417</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.003472</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.003472</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.010417</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.010417</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.010417</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.003472</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.010417</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.003472</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.003472</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.003472</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.003472</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12747,22 +12627,22 @@
         <v>0.000347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="F9" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="G9" t="n">
-        <v>0.013542</v>
+        <v>0.001389</v>
       </c>
       <c r="H9" t="n">
         <v>0.000347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="J9" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="K9" t="n">
         <v>0.000347</v>
@@ -12793,7 +12673,7 @@
         <v>0.000694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="G10" t="n">
         <v>0.000347</v>
@@ -12836,7 +12716,7 @@
         <v>0.000347</v>
       </c>
       <c r="F11" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -12879,7 +12759,7 @@
         <v>0.000347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12919,10 +12799,10 @@
         <v>0.000347</v>
       </c>
       <c r="E13" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="F13" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="G13" t="n">
         <v>0.000347</v>
@@ -12996,16 +12876,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="C15" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="D15" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E15" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
@@ -13018,7 +12898,7 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K15" t="n">
         <v>0.000347</v>
@@ -13027,7 +12907,7 @@
         <v>0.000347</v>
       </c>
       <c r="M15" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="16">
@@ -13037,40 +12917,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="D16" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E16" t="n">
-        <v>0.010764</v>
+        <v>0.000694</v>
       </c>
       <c r="F16" t="n">
-        <v>0.011458</v>
+        <v>0.000347</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0125</v>
+        <v>0.003125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M16" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="17">
@@ -13080,13 +12960,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C17" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="D17" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="E17" t="n">
         <v>0.000694</v>
@@ -13095,25 +12975,25 @@
         <v>0.001042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="H17" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I17" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J17" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K17" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L17" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M17" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
     </row>
     <row r="18">
@@ -13123,16 +13003,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C18" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="D18" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E18" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="F18" t="n">
         <v>0.000347</v>
@@ -13153,7 +13033,7 @@
         <v>0.000347</v>
       </c>
       <c r="L18" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M18" t="n">
         <v>0.000347</v>
@@ -13166,22 +13046,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="C19" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="D19" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E19" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="F19" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="G19" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H19" t="n">
         <v>0.000347</v>
@@ -13224,7 +13104,7 @@
         <v>0.000347</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005903</v>
+        <v>0.003125</v>
       </c>
       <c r="H20" t="n">
         <v>0.000347</v>
@@ -13252,37 +13132,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="C21" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="D21" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E21" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.013542</v>
+        <v>0.001389</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005903</v>
+        <v>0.003125</v>
       </c>
       <c r="H21" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I21" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J21" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K21" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L21" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13295,40 +13175,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="C22" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="D22" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="E22" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="F22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="G22" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="H22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M22" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="23">
@@ -13338,40 +13218,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0125</v>
+        <v>0.003125</v>
       </c>
       <c r="C23" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="D23" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="E23" t="n">
         <v>0.000694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="G23" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="H23" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I23" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="J23" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K23" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L23" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M23" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="24">
@@ -13381,16 +13261,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C24" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="D24" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="E24" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="F24" t="n">
         <v>0.000347</v>
@@ -13399,22 +13279,22 @@
         <v>0.000694</v>
       </c>
       <c r="H24" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I24" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="J24" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K24" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L24" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M24" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="25">
@@ -13439,16 +13319,16 @@
         <v>0.000694</v>
       </c>
       <c r="G25" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H25" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="I25" t="n">
-        <v>0.011111</v>
+        <v>0.000347</v>
       </c>
       <c r="J25" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K25" t="n">
         <v>0.000347</v>
@@ -13470,7 +13350,7 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.010069</v>
+        <v>0.000694</v>
       </c>
       <c r="D26" t="n">
         <v>0.000694</v>
@@ -13482,13 +13362,13 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H26" t="n">
         <v>0.000347</v>
       </c>
       <c r="I26" t="n">
-        <v>0.012153</v>
+        <v>0.000347</v>
       </c>
       <c r="J26" t="n">
         <v>0.000347</v>
@@ -13510,40 +13390,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.013542</v>
+        <v>0.000694</v>
       </c>
       <c r="C27" t="n">
         <v>0.000347</v>
       </c>
       <c r="D27" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="E27" t="n">
         <v>0.001389</v>
       </c>
       <c r="F27" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="G27" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H27" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="I27" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="J27" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K27" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="L27" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="M27" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
     </row>
     <row r="28">
@@ -13553,7 +13433,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13568,13 +13448,13 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
       </c>
       <c r="I28" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="J28" t="n">
         <v>0.000347</v>
@@ -13596,7 +13476,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.013542</v>
+        <v>0.001042</v>
       </c>
       <c r="C29" t="n">
         <v>0.001042</v>
@@ -13605,22 +13485,22 @@
         <v>0.000347</v>
       </c>
       <c r="E29" t="n">
-        <v>0.013542</v>
+        <v>0.001389</v>
       </c>
       <c r="F29" t="n">
         <v>0.001042</v>
       </c>
       <c r="G29" t="n">
-        <v>0.013542</v>
+        <v>0.003125</v>
       </c>
       <c r="H29" t="n">
         <v>0.000347</v>
       </c>
       <c r="I29" t="n">
-        <v>0.010069</v>
+        <v>0.000347</v>
       </c>
       <c r="J29" t="n">
-        <v>0.013542</v>
+        <v>0.000347</v>
       </c>
       <c r="K29" t="n">
         <v>0.000347</v>

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -1831,40 +1831,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001</v>
+        <v>0.755</v>
       </c>
       <c r="E2" t="n">
-        <v>0.013</v>
+        <v>1.339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003</v>
+        <v>0.256</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005</v>
+        <v>0.578</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.711</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.008</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="3">
@@ -1874,40 +1874,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001</v>
+        <v>0.226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.013</v>
+        <v>1.045</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002</v>
+        <v>0.124</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002</v>
+        <v>0.154</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.259</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1917,40 +1917,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.866</v>
       </c>
       <c r="F4" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.001</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="L4" t="n">
         <v>0.001</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="5">
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01</v>
+        <v>0.823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002</v>
+        <v>0.19</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002</v>
+        <v>0.128</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008</v>
+        <v>0.713</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002</v>
+        <v>0.174</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="7">
@@ -2046,40 +2046,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002</v>
+        <v>0.211</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002</v>
+        <v>1.353</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003</v>
+        <v>0.74</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.918</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004</v>
+        <v>0.931</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="8">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -2098,13 +2098,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.422</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2132,40 +2132,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="F9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.001</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2227,10 +2227,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2313,10 +2313,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2325,16 +2325,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -2390,40 +2390,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002</v>
+        <v>0.762</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001</v>
+        <v>0.703</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001</v>
+        <v>0.825</v>
       </c>
       <c r="E15" t="n">
-        <v>0.011</v>
+        <v>1.165</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002</v>
+        <v>0.208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.013</v>
+        <v>1.253</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.373</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.621</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001</v>
+        <v>0.824</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002</v>
+        <v>1.121</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.147</v>
       </c>
     </row>
     <row r="16">
@@ -2433,40 +2433,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.001</v>
+        <v>0.517</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.544</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002</v>
+        <v>0.736</v>
       </c>
       <c r="E16" t="n">
-        <v>0.012</v>
+        <v>1.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0.003</v>
+        <v>0.304</v>
       </c>
       <c r="G16" t="n">
-        <v>0.016</v>
+        <v>1.303</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.186</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.878</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001</v>
+        <v>0.889</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="17">
@@ -2476,40 +2476,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.001</v>
+        <v>0.238</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001</v>
+        <v>0.204</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003</v>
+        <v>0.554</v>
       </c>
       <c r="E17" t="n">
-        <v>0.015</v>
+        <v>1.257</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003</v>
+        <v>0.226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.771</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.648</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.843</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.659</v>
       </c>
     </row>
     <row r="18">
@@ -2519,40 +2519,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="E18" t="n">
-        <v>0.013</v>
+        <v>1.134</v>
       </c>
       <c r="F18" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.002</v>
       </c>
-      <c r="G18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="19">
@@ -2562,22 +2562,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.012</v>
+        <v>1.068</v>
       </c>
       <c r="F19" t="n">
-        <v>0.002</v>
+        <v>0.17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001</v>
+        <v>0.108</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2605,25 +2605,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.002</v>
+        <v>0.107</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002</v>
+        <v>0.113</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>0.004</v>
+        <v>0.347</v>
       </c>
       <c r="F20" t="n">
-        <v>0.001</v>
+        <v>0.066</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001</v>
+        <v>0.093</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2648,37 +2648,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001</v>
+        <v>0.146</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001</v>
+        <v>0.152</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E21" t="n">
-        <v>0.004</v>
+        <v>0.319</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001</v>
+        <v>0.051</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001</v>
+        <v>0.054</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.507</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2691,40 +2691,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001</v>
+        <v>0.525</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001</v>
+        <v>0.596</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="E22" t="n">
-        <v>0.003</v>
+        <v>0.399</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.788</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="23">
@@ -2734,40 +2734,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.002</v>
+        <v>0.136</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001</v>
+        <v>0.124</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="G23" t="n">
-        <v>0.002</v>
+        <v>0.302</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="24">
@@ -2777,40 +2777,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002</v>
+        <v>0.143</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="G24" t="n">
-        <v>0.004</v>
+        <v>0.335</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.149</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="25">
@@ -2820,40 +2820,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="E25" t="n">
-        <v>0.002</v>
+        <v>0.151</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="G25" t="n">
-        <v>0.001</v>
+        <v>0.154</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="26">
@@ -2863,22 +2863,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="G26" t="n">
-        <v>0.002</v>
+        <v>0.197</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001</v>
+        <v>0.126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001</v>
+        <v>0.254</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="28">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001</v>
+        <v>0.105</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -2992,40 +2992,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001</v>
+        <v>0.106</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001</v>
+        <v>0.107</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="30">
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3159,40 +3159,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3245,40 +3245,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3288,40 +3288,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3331,40 +3331,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3374,40 +3374,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -3417,40 +3417,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -3460,40 +3460,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -3503,40 +3503,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -3546,40 +3546,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3589,40 +3589,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3632,40 +3632,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -3718,40 +3718,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -3761,40 +3761,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -3847,40 +3847,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -3890,40 +3890,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -3933,40 +3933,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -3976,40 +3976,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -4019,40 +4019,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -4062,40 +4062,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -4105,40 +4105,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -4148,40 +4148,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -4191,40 +4191,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -4234,40 +4234,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -4277,40 +4277,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -4320,40 +4320,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -4363,40 +4363,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>0.08333333333333333</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7143,40 +7143,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.491</v>
+        <v>161.233</v>
       </c>
       <c r="C2" t="n">
-        <v>33.013</v>
+        <v>216.073</v>
       </c>
       <c r="D2" t="n">
-        <v>74.485</v>
+        <v>220.892</v>
       </c>
       <c r="E2" t="n">
-        <v>227.211</v>
+        <v>268.166</v>
       </c>
       <c r="F2" t="n">
-        <v>105.694</v>
+        <v>111.783</v>
       </c>
       <c r="G2" t="n">
-        <v>142.874</v>
+        <v>181.375</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>240.642</v>
       </c>
       <c r="I2" t="n">
-        <v>1.394</v>
+        <v>227.852</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>265.541</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>237.901</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>231.776</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>316.715</v>
       </c>
     </row>
     <row r="3">
@@ -7186,40 +7186,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.778</v>
+        <v>78.113</v>
       </c>
       <c r="C3" t="n">
-        <v>34.942</v>
+        <v>82.932</v>
       </c>
       <c r="D3" t="n">
-        <v>59.212</v>
+        <v>118.894</v>
       </c>
       <c r="E3" t="n">
-        <v>217.978</v>
+        <v>223.433</v>
       </c>
       <c r="F3" t="n">
         <v>77.004</v>
       </c>
       <c r="G3" t="n">
-        <v>76.501</v>
+        <v>88.36499999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>154.766</v>
       </c>
       <c r="I3" t="n">
-        <v>1.561</v>
+        <v>143.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>124.705</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>161.81</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>132.332</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>95.678</v>
       </c>
     </row>
     <row r="4">
@@ -7229,40 +7229,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.982</v>
+        <v>42.702</v>
       </c>
       <c r="C4" t="n">
-        <v>19.544</v>
+        <v>30.117</v>
       </c>
       <c r="D4" t="n">
-        <v>41.82</v>
+        <v>53.854</v>
       </c>
       <c r="E4" t="n">
-        <v>196.131</v>
+        <v>203.603</v>
       </c>
       <c r="F4" t="n">
-        <v>72.789</v>
+        <v>74.575</v>
       </c>
       <c r="G4" t="n">
-        <v>58.103</v>
+        <v>68.42</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>10.24</v>
       </c>
       <c r="I4" t="n">
-        <v>1.131</v>
+        <v>5.348</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>21.785</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>43.685</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>11.359</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>21.458</v>
       </c>
     </row>
     <row r="5">
@@ -7272,13 +7272,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.623</v>
+        <v>20.817</v>
       </c>
       <c r="C5" t="n">
-        <v>5.454</v>
+        <v>7.574</v>
       </c>
       <c r="D5" t="n">
-        <v>18.59</v>
+        <v>18.92</v>
       </c>
       <c r="E5" t="n">
         <v>196.449</v>
@@ -7313,40 +7313,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.732</v>
+        <v>91.312</v>
       </c>
       <c r="C6" t="n">
-        <v>1.601</v>
+        <v>57.975</v>
       </c>
       <c r="D6" t="n">
-        <v>8.722</v>
+        <v>83.872</v>
       </c>
       <c r="E6" t="n">
-        <v>172.055</v>
+        <v>191.719</v>
       </c>
       <c r="F6" t="n">
-        <v>85.541</v>
+        <v>94.40600000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>44.255</v>
+        <v>64.727</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>25.738</v>
       </c>
       <c r="I6" t="n">
-        <v>0.899</v>
+        <v>45.242</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>122.182</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>150.31</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>105.877</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>126.398</v>
       </c>
     </row>
     <row r="7">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.628</v>
+        <v>193.339</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>225.704</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>162.901</v>
       </c>
       <c r="E7" t="n">
-        <v>76.08</v>
+        <v>140.334</v>
       </c>
       <c r="F7" t="n">
-        <v>150.504</v>
+        <v>188.116</v>
       </c>
       <c r="G7" t="n">
-        <v>34.369</v>
+        <v>103.174</v>
       </c>
       <c r="H7" t="n">
-        <v>214.948</v>
+        <v>448.705</v>
       </c>
       <c r="I7" t="n">
-        <v>275.053</v>
+        <v>328.085</v>
       </c>
       <c r="J7" t="n">
-        <v>4.675</v>
+        <v>406.981</v>
       </c>
       <c r="K7" t="n">
-        <v>254.836</v>
+        <v>369.421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.55</v>
+        <v>345.876</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>420.143</v>
       </c>
     </row>
     <row r="8">
@@ -7398,18 +7398,42 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>75.474</v>
+      </c>
+      <c r="F8" t="n">
+        <v>142.348</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.537</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.336</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7418,40 +7442,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>57.199</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>36.387</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>36.557</v>
       </c>
       <c r="E9" t="n">
-        <v>36.049</v>
+        <v>63.457</v>
       </c>
       <c r="F9" t="n">
-        <v>85.033</v>
+        <v>107.617</v>
       </c>
       <c r="G9" t="n">
-        <v>3.236</v>
+        <v>23.683</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>45.131</v>
       </c>
       <c r="I9" t="n">
-        <v>1.442</v>
+        <v>119.799</v>
       </c>
       <c r="J9" t="n">
-        <v>0.442</v>
+        <v>55.725</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>167.675</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>100.236</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>42.872</v>
       </c>
     </row>
     <row r="10">
@@ -7461,7 +7485,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -7470,28 +7494,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.368</v>
+        <v>43.144</v>
       </c>
       <c r="F10" t="n">
-        <v>69.432</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2.111</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>11.198</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>7.128</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>30.626</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.333</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7513,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34.141</v>
+        <v>38.294</v>
       </c>
       <c r="F11" t="n">
-        <v>61.315</v>
+        <v>64.364</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.306</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.904</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.736</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -7556,10 +7580,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.546</v>
+        <v>22.804</v>
       </c>
       <c r="F12" t="n">
-        <v>47.514</v>
+        <v>49.233</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7590,37 +7614,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>20.313</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.957</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>10.678</v>
       </c>
       <c r="E13" t="n">
-        <v>0.643</v>
+        <v>19.446</v>
       </c>
       <c r="F13" t="n">
-        <v>26.56</v>
+        <v>41.545</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.915</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>12.684</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>23.007</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>30.013</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>58.546</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>29.613</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7651,13 +7675,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.988</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.248</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>5.774</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7676,38 +7700,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82.124</v>
+        <v>224.64</v>
       </c>
       <c r="C15" t="n">
-        <v>46.643</v>
+        <v>245.145</v>
       </c>
       <c r="D15" t="n">
-        <v>71.619</v>
+        <v>250.231</v>
       </c>
       <c r="E15" t="n">
-        <v>208.792</v>
+        <v>247.101</v>
       </c>
       <c r="F15" t="n">
         <v>101.735</v>
       </c>
       <c r="G15" t="n">
-        <v>229.985</v>
+        <v>250.235</v>
       </c>
       <c r="H15" t="n">
-        <v>19.119</v>
+        <v>150.226</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>13.238</v>
+        <v>210.285</v>
       </c>
       <c r="K15" t="n">
-        <v>81.736</v>
+        <v>211.01</v>
       </c>
       <c r="L15" t="n">
-        <v>138.554</v>
+        <v>242.19</v>
       </c>
       <c r="M15" t="n">
-        <v>17.575</v>
+        <v>249.169</v>
       </c>
     </row>
     <row r="16">
@@ -7717,40 +7741,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>96.947</v>
+        <v>325.836</v>
       </c>
       <c r="C16" t="n">
-        <v>71.104</v>
+        <v>368.285</v>
       </c>
       <c r="D16" t="n">
-        <v>155.105</v>
+        <v>371.084</v>
       </c>
       <c r="E16" t="n">
-        <v>377.207</v>
+        <v>395.72</v>
       </c>
       <c r="F16" t="n">
-        <v>199.136</v>
+        <v>209.767</v>
       </c>
       <c r="G16" t="n">
-        <v>435.996</v>
+        <v>437.584</v>
       </c>
       <c r="H16" t="n">
-        <v>59.522</v>
+        <v>361.504</v>
       </c>
       <c r="I16" t="n">
-        <v>0.443</v>
+        <v>171.377</v>
       </c>
       <c r="J16" t="n">
-        <v>38.478</v>
+        <v>429.552</v>
       </c>
       <c r="K16" t="n">
-        <v>61.709</v>
+        <v>377.352</v>
       </c>
       <c r="L16" t="n">
-        <v>109.779</v>
+        <v>369.762</v>
       </c>
       <c r="M16" t="n">
-        <v>11.038</v>
+        <v>383.425</v>
       </c>
     </row>
     <row r="17">
@@ -7760,40 +7784,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92.18300000000001</v>
+        <v>223.45</v>
       </c>
       <c r="C17" t="n">
-        <v>86.048</v>
+        <v>205.63</v>
       </c>
       <c r="D17" t="n">
-        <v>201.537</v>
+        <v>316.265</v>
       </c>
       <c r="E17" t="n">
-        <v>416.187</v>
+        <v>420.762</v>
       </c>
       <c r="F17" t="n">
-        <v>177.486</v>
+        <v>178.899</v>
       </c>
       <c r="G17" t="n">
-        <v>322.479</v>
+        <v>331</v>
       </c>
       <c r="H17" t="n">
-        <v>6.425</v>
+        <v>335.315</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>140.185</v>
       </c>
       <c r="J17" t="n">
-        <v>4.222</v>
+        <v>426.081</v>
       </c>
       <c r="K17" t="n">
-        <v>14.504</v>
+        <v>282.23</v>
       </c>
       <c r="L17" t="n">
-        <v>48.374</v>
+        <v>376.867</v>
       </c>
       <c r="M17" t="n">
-        <v>3.567</v>
+        <v>346.912</v>
       </c>
     </row>
     <row r="18">
@@ -7803,40 +7827,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.234</v>
+        <v>49.49</v>
       </c>
       <c r="C18" t="n">
-        <v>18.643</v>
+        <v>30.201</v>
       </c>
       <c r="D18" t="n">
-        <v>39.319</v>
+        <v>48.346</v>
       </c>
       <c r="E18" t="n">
-        <v>393.227</v>
+        <v>398.884</v>
       </c>
       <c r="F18" t="n">
-        <v>159.617</v>
+        <v>162.699</v>
       </c>
       <c r="G18" t="n">
-        <v>140.235</v>
+        <v>142.583</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>32.366</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>10.028</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>20.694</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>35.773</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>80.483</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>36.838</v>
       </c>
     </row>
     <row r="19">
@@ -7846,40 +7870,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.301</v>
+        <v>27.131</v>
       </c>
       <c r="C19" t="n">
-        <v>3.241</v>
+        <v>12.025</v>
       </c>
       <c r="D19" t="n">
-        <v>22.803</v>
+        <v>29.92</v>
       </c>
       <c r="E19" t="n">
-        <v>382.753</v>
+        <v>386.949</v>
       </c>
       <c r="F19" t="n">
-        <v>152.154</v>
+        <v>154.628</v>
       </c>
       <c r="G19" t="n">
-        <v>120.812</v>
+        <v>124.252</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.267</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>7.721</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>10.242</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="20">
@@ -7904,7 +7928,7 @@
         <v>99.241</v>
       </c>
       <c r="G20" t="n">
-        <v>125.406</v>
+        <v>125.58</v>
       </c>
       <c r="H20" t="n">
         <v>101.544</v>
@@ -7916,10 +7940,10 @@
         <v>18.955</v>
       </c>
       <c r="K20" t="n">
-        <v>11.559</v>
+        <v>90.012</v>
       </c>
       <c r="L20" t="n">
-        <v>5.484</v>
+        <v>7.176</v>
       </c>
       <c r="M20" t="n">
         <v>38.08</v>
@@ -7932,37 +7956,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.51600000000001</v>
+        <v>158.906</v>
       </c>
       <c r="C21" t="n">
-        <v>98.995</v>
+        <v>161.693</v>
       </c>
       <c r="D21" t="n">
-        <v>18.796</v>
+        <v>54.315</v>
       </c>
       <c r="E21" t="n">
-        <v>204.369</v>
+        <v>214.901</v>
       </c>
       <c r="F21" t="n">
-        <v>83.34399999999999</v>
+        <v>84.849</v>
       </c>
       <c r="G21" t="n">
-        <v>86.01000000000001</v>
+        <v>87.883</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>315.967</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>84.494</v>
       </c>
       <c r="J21" t="n">
-        <v>0.534</v>
+        <v>312.499</v>
       </c>
       <c r="K21" t="n">
-        <v>0.082</v>
+        <v>218.524</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>181.771</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -7975,40 +7999,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>96.35899999999999</v>
+        <v>326.683</v>
       </c>
       <c r="C22" t="n">
-        <v>95.316</v>
+        <v>344.862</v>
       </c>
       <c r="D22" t="n">
-        <v>22.094</v>
+        <v>322.188</v>
       </c>
       <c r="E22" t="n">
-        <v>201.306</v>
+        <v>268.403</v>
       </c>
       <c r="F22" t="n">
-        <v>74.621</v>
+        <v>108.069</v>
       </c>
       <c r="G22" t="n">
-        <v>70.05800000000001</v>
+        <v>135.468</v>
       </c>
       <c r="H22" t="n">
-        <v>19.641</v>
+        <v>351.305</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>218.601</v>
       </c>
       <c r="J22" t="n">
-        <v>1.117</v>
+        <v>447.263</v>
       </c>
       <c r="K22" t="n">
-        <v>58.242</v>
+        <v>245.673</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>356.592</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>378.77</v>
       </c>
     </row>
     <row r="23">
@@ -8018,40 +8042,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.521</v>
+        <v>68.547</v>
       </c>
       <c r="C23" t="n">
-        <v>1.717</v>
+        <v>31.235</v>
       </c>
       <c r="D23" t="n">
-        <v>0.17</v>
+        <v>33.852</v>
       </c>
       <c r="E23" t="n">
-        <v>22.371</v>
+        <v>25.809</v>
       </c>
       <c r="F23" t="n">
-        <v>8.746</v>
+        <v>9.757999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>97.43600000000001</v>
+        <v>133.035</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>21.522</v>
       </c>
       <c r="I23" t="n">
-        <v>1.751</v>
+        <v>26.488</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>56.446</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>20.712</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>32.653</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>35.369</v>
       </c>
     </row>
     <row r="24">
@@ -8061,40 +8085,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.95</v>
+        <v>16.163</v>
       </c>
       <c r="C24" t="n">
-        <v>6.083</v>
+        <v>26.155</v>
       </c>
       <c r="D24" t="n">
-        <v>1.636</v>
+        <v>22.878</v>
       </c>
       <c r="E24" t="n">
-        <v>24.681</v>
+        <v>26.239</v>
       </c>
       <c r="F24" t="n">
-        <v>10.442</v>
+        <v>10.472</v>
       </c>
       <c r="G24" t="n">
-        <v>123.314</v>
+        <v>126.464</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>20.425</v>
       </c>
       <c r="I24" t="n">
-        <v>1.238</v>
+        <v>25.756</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>47.703</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>20.024</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>30.576</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>30.786</v>
       </c>
     </row>
     <row r="25">
@@ -8104,40 +8128,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12.981</v>
+        <v>13.675</v>
       </c>
       <c r="C25" t="n">
-        <v>12.953</v>
+        <v>17.848</v>
       </c>
       <c r="D25" t="n">
-        <v>7.988</v>
+        <v>14.61</v>
       </c>
       <c r="E25" t="n">
         <v>27.029</v>
       </c>
       <c r="F25" t="n">
-        <v>12.001</v>
+        <v>12.027</v>
       </c>
       <c r="G25" t="n">
-        <v>57.234</v>
+        <v>95.349</v>
       </c>
       <c r="H25" t="n">
-        <v>0.49</v>
+        <v>19.045</v>
       </c>
       <c r="I25" t="n">
-        <v>0.486</v>
+        <v>11.804</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>25.778</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>23.603</v>
       </c>
       <c r="L25" t="n">
-        <v>2.614</v>
+        <v>27.658</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>18.936</v>
       </c>
     </row>
     <row r="26">
@@ -8150,10 +8174,10 @@
         <v>8.202</v>
       </c>
       <c r="C26" t="n">
-        <v>7.148</v>
+        <v>11.272</v>
       </c>
       <c r="D26" t="n">
-        <v>3.837</v>
+        <v>4.246</v>
       </c>
       <c r="E26" t="n">
         <v>23.438</v>
@@ -8162,22 +8186,22 @@
         <v>11.379</v>
       </c>
       <c r="G26" t="n">
-        <v>91.337</v>
+        <v>96.486</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.428</v>
       </c>
       <c r="I26" t="n">
-        <v>0.28</v>
+        <v>1.559</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.967</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.274</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>6.246</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -8190,40 +8214,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.977</v>
+        <v>23.043</v>
       </c>
       <c r="C27" t="n">
-        <v>6.667</v>
+        <v>39.777</v>
       </c>
       <c r="D27" t="n">
-        <v>0.124</v>
+        <v>34.864</v>
       </c>
       <c r="E27" t="n">
-        <v>22.295</v>
+        <v>26.099</v>
       </c>
       <c r="F27" t="n">
-        <v>10.847</v>
+        <v>12.826</v>
       </c>
       <c r="G27" t="n">
-        <v>78.401</v>
+        <v>129.351</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>33.252</v>
       </c>
       <c r="I27" t="n">
-        <v>0.874</v>
+        <v>18.642</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>58.309</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>37.326</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>43.613</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>36.754</v>
       </c>
     </row>
     <row r="28">
@@ -8233,7 +8257,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.174</v>
+        <v>2.559</v>
       </c>
       <c r="C28" t="n">
         <v>1.408</v>
@@ -8248,13 +8272,13 @@
         <v>11.133</v>
       </c>
       <c r="G28" t="n">
-        <v>38.04</v>
+        <v>67.018</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.184</v>
+        <v>0.536</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -8276,40 +8300,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.367</v>
+        <v>4.509</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9340000000000001</v>
+        <v>5.785</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3.696</v>
       </c>
       <c r="E29" t="n">
-        <v>21.446</v>
+        <v>22.459</v>
       </c>
       <c r="F29" t="n">
-        <v>10.421</v>
+        <v>10.927</v>
       </c>
       <c r="G29" t="n">
-        <v>59.63</v>
+        <v>74.959</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>5.992</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09</v>
+        <v>7.339</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>16.438</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>11.718</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>21.617</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="30">
@@ -8443,40 +8467,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.805485081e-06</v>
+        <v>2.599608028900001e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.089858169e-06</v>
+        <v>4.668754132900001e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>5.548015225e-06</v>
+        <v>4.879327566400001e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.162483852100002e-05</v>
+        <v>7.191300355600002e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1171221636e-05</v>
+        <v>1.2495439089e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0412979876e-05</v>
+        <v>3.2896890625e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5.7908572164e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.943236e-09</v>
+        <v>5.1916533904e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7.051202268099999e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5.6596885801e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5.372011417600001e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.000100308391225</v>
       </c>
     </row>
     <row r="3">
@@ -8486,40 +8510,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.662845284e-06</v>
+        <v>6.101640769e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.220943364e-06</v>
+        <v>6.877716624000001e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.506060944e-06</v>
+        <v>1.4135783236e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7514408484e-05</v>
+        <v>4.9922305489e-05</v>
       </c>
       <c r="F3" t="n">
         <v>5.929616016e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.852403000999999e-06</v>
+        <v>7.808373225e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2.3952514756e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>2.436721e-09</v>
+        <v>2.04919225e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.5551337025e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2.61824761e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.7511758224e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9.154279684e-06</v>
       </c>
     </row>
     <row r="4">
@@ -8529,40 +8553,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.750643239999999e-07</v>
+        <v>1.823460804e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>3.819679359999999e-07</v>
+        <v>9.070336890000001e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7489124e-06</v>
+        <v>2.900253316e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8467369161e-05</v>
+        <v>4.1454181609e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.298238521000002e-06</v>
+        <v>5.561430625e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.375958609e-06</v>
+        <v>4.681296400000002e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1.048576e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.279161e-09</v>
+        <v>2.860110399999999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4.745862249999999e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.908379225e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.29026881e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.604457639999999e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8572,13 +8596,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.46816129e-07</v>
+        <v>4.333474889999999e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9746116e-08</v>
+        <v>5.7365476e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.455880999999999e-07</v>
+        <v>3.579664000000001e-07</v>
       </c>
       <c r="E5" t="n">
         <v>3.8592209601e-05</v>
@@ -8613,40 +8637,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.62103824e-07</v>
+        <v>8.337881344e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>2.563201e-09</v>
+        <v>3.361100625e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.607328399999998e-08</v>
+        <v>7.034512384000001e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>2.960292302500001e-05</v>
+        <v>3.6756174961e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.317262680999998e-06</v>
+        <v>8.912492836e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.958505025e-06</v>
+        <v>4.189584529000001e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6.624446440000001e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>8.082010000000001e-10</v>
+        <v>2.046838564e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.4928441124e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.25930961e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.1209939129e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.597645440399999e-05</v>
       </c>
     </row>
     <row r="7">
@@ -8656,40 +8680,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.939546133333334e-08</v>
+        <v>1.245998964033333e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.698076520533334e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8.845578600333335e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9293888e-06</v>
+        <v>6.564543852000001e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.550484672e-06</v>
+        <v>1.179587648533334e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.937427203333333e-07</v>
+        <v>3.548291425333334e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>1.540088090133333e-05</v>
+        <v>6.711205900833333e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>2.521805093633333e-05</v>
+        <v>3.587992240833332e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>7.285208333333332e-09</v>
+        <v>5.521117812033333e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>2.164712896533333e-05</v>
+        <v>4.549062508033333e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.008333333333333e-10</v>
+        <v>3.987673579199999e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.884004681633333e-05</v>
       </c>
     </row>
     <row r="8">
@@ -8698,18 +8722,42 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>8.3814025e-08</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.696324676e-06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.0262953104e-05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.58286369e-07</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.622500000000001e-09</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.803248896e-06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8718,40 +8766,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.090575200333333e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4.41337923e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.454714163333333e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>4.331768003333333e-07</v>
+        <v>1.342263616333334e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.410203696333333e-06</v>
+        <v>3.860472896333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.490565333333334e-09</v>
+        <v>1.869614963333333e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6.789357203333332e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>6.931213333333333e-10</v>
+        <v>4.783933467e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>6.512133333333333e-11</v>
+        <v>1.035091875e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>9.371635208333335e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.349085232e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.126694613333333e-07</v>
       </c>
     </row>
     <row r="10">
@@ -8761,7 +8809,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2.5392e-09</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -8770,28 +8818,28 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.492291413333334e-07</v>
+        <v>6.204682453333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.606934208e-06</v>
+        <v>1.9400547e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>9.2928e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.485440333333333e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4.179840133333333e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.6936128e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.126506253333333e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.702963e-09</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8813,22 +8861,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.885359603333333e-07</v>
+        <v>4.888101453333332e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.253176408333333e-06</v>
+        <v>1.380908165333333e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.772545333333333e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5.125333333333334e-12</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.811072e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4.652565333333334e-09</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8856,10 +8904,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.694407053333334e-07</v>
+        <v>1.733408053333333e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.52526732e-07</v>
+        <v>8.079627630000001e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8890,37 +8938,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1.37539323e-07</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3.05283e-10</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3.800656133333333e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>1.378163333333333e-10</v>
+        <v>1.26048972e-07</v>
       </c>
       <c r="F13" t="n">
-        <v>2.351445333333333e-07</v>
+        <v>5.753290083333333e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.109075e-09</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5.362795199999999e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.764406830000001e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.002600563333334e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.142544705333333e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.92309923e-07</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -8951,13 +8999,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8.293381333333335e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>9.180501333333333e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.111302533333333e-08</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8976,38 +9024,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.744351375999998e-06</v>
+        <v>5.046312959999999e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>2.175569449e-06</v>
+        <v>6.0096071025e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>5.129281161e-06</v>
+        <v>6.261555336099999e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3594099264e-05</v>
+        <v>6.105890420099999e-05</v>
       </c>
       <c r="F15" t="n">
         <v>1.0350010225e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>5.289310022500001e-05</v>
+        <v>6.261755522500002e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65536161e-07</v>
+        <v>2.2567851076e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1.75244644e-07</v>
+        <v>4.4219781225e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>6.680773696000001e-06</v>
+        <v>4.45252201e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9197210916e-05</v>
+        <v>5.86559961e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08880625e-07</v>
+        <v>6.2085190561e-05</v>
       </c>
     </row>
     <row r="16">
@@ -9017,40 +9065,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.132906936333334e-06</v>
+        <v>3.5389699632e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>1.685259605333333e-06</v>
+        <v>4.521128040833334e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>8.019187008333333e-06</v>
+        <v>4.590111168533334e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.742837361633334e-05</v>
+        <v>5.219810613333334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.321838216533333e-05</v>
+        <v>1.466739809633334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3364170672e-05</v>
+        <v>6.382658568533334e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.180956161333333e-06</v>
+        <v>4.356171400533333e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>6.541633333333333e-11</v>
+        <v>9.790025376333333e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>4.935188279999999e-07</v>
+        <v>6.150497356800002e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>1.269333560333333e-06</v>
+        <v>4.746484396799999e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>4.017142947e-06</v>
+        <v>4.557464554799999e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.061248133333334e-08</v>
+        <v>4.900491020833333e-05</v>
       </c>
     </row>
     <row r="17">
@@ -9060,40 +9108,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.832568496333333e-06</v>
+        <v>1.664330083333333e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>2.468086101333333e-06</v>
+        <v>1.409456563333333e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3539054123e-05</v>
+        <v>3.334118340833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.773720632300001e-05</v>
+        <v>5.9013553548e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0500426732e-05</v>
+        <v>1.0668284067e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.466423514699999e-05</v>
+        <v>3.652033333333334e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.376020833333333e-08</v>
+        <v>3.747871640833333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>6.550611408333334e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>5.941761333333333e-09</v>
+        <v>6.051500618700001e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>7.012200533333333e-08</v>
+        <v>2.655125763333334e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>7.800146253333334e-07</v>
+        <v>4.734291189633333e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.241163000000001e-09</v>
+        <v>4.011597858133333e-05</v>
       </c>
     </row>
     <row r="18">
@@ -9103,40 +9151,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.131022520000001e-07</v>
+        <v>8.164200333333334e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.158538163333333e-07</v>
+        <v>3.04033467e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>5.153279203333333e-07</v>
+        <v>7.791119053333331e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.154249117633333e-05</v>
+        <v>5.303614848533333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.492528896333331e-06</v>
+        <v>8.823654867000001e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.555285075000002e-06</v>
+        <v>6.776637296333332e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>3.491859853333333e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3.352026133333334e-08</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.42747212e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.265691763333335e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.159171096333333e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.523460813333334e-07</v>
       </c>
     </row>
     <row r="19">
@@ -9146,40 +9194,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.977486699999996e-08</v>
+        <v>2.453637203333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>3.501360333333333e-09</v>
+        <v>4.820020833333334e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.73325603e-07</v>
+        <v>2.984021333333334e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.883328633633334e-05</v>
+        <v>4.9909842867e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.716946571999999e-06</v>
+        <v>7.969939461333333e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.865179781333334e-06</v>
+        <v>5.146186501333334e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>4.712533333333333e-09</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.557763e-09</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4.224533333333334e-09</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.987128033333334e-08</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.4966188e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.689813333333334e-08</v>
       </c>
     </row>
     <row r="20">
@@ -9204,7 +9252,7 @@
         <v>3.282925360333333e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>5.242221612000001e-06</v>
+        <v>5.2567788e-06</v>
       </c>
       <c r="H20" t="n">
         <v>3.437061312e-06</v>
@@ -9216,10 +9264,10 @@
         <v>1.197640083333333e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4536827e-08</v>
+        <v>2.700720047999999e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0024752e-08</v>
+        <v>1.7164992e-08</v>
       </c>
       <c r="M20" t="n">
         <v>4.833621333333333e-07</v>
@@ -9232,37 +9280,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.105112752e-06</v>
+        <v>8.417038945333335e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>3.266670008333333e-06</v>
+        <v>8.714875416333335e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>1.177632053333333e-07</v>
+        <v>9.833730749999998e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3922229387e-05</v>
+        <v>1.539414660033333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.315407445333333e-06</v>
+        <v>2.399784267000001e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4659067e-06</v>
+        <v>2.574473896333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3.327838169633334e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.379745345333333e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>9.505200000000003e-11</v>
+        <v>3.255187500033334e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>2.241333333333333e-12</v>
+        <v>1.591757952533333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.101356548033333e-05</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9275,40 +9323,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.095018960333333e-06</v>
+        <v>3.557392749633333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>3.028379952e-06</v>
+        <v>3.9643266348e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.627149453333334e-07</v>
+        <v>3.4601702448e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3508035212e-05</v>
+        <v>2.401339013633333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.856097880333333e-06</v>
+        <v>3.892969587e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.636041121333334e-06</v>
+        <v>6.117193007999998e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>1.28589627e-07</v>
+        <v>4.113840100833334e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1.5928799067e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>4.158963333333333e-10</v>
+        <v>6.668139705633332e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>1.130710188e-06</v>
+        <v>2.0118407643e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.238595148799999e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.782223763333333e-05</v>
       </c>
     </row>
     <row r="23">
@@ -9318,40 +9366,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.57405441e-06</v>
+        <v>4.698691208999999e-05</v>
       </c>
       <c r="C23" t="n">
-        <v>2.948089e-08</v>
+        <v>9.756252249999999e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>2.89e-10</v>
+        <v>1.145957904e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>5.00461641e-06</v>
+        <v>6.661044810000001e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>7.649251600000001e-07</v>
+        <v>9.5218564e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.493774096000001e-06</v>
+        <v>1.769831122499999e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4.63196484e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>3.066000999999999e-08</v>
+        <v>7.016141440000001e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3.186150915999999e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4.28986944e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.066218409e-05</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.250966161e-05</v>
       </c>
     </row>
     <row r="24">
@@ -9361,40 +9409,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.540250000000001e-07</v>
+        <v>2.61242569e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>3.7002889e-07</v>
+        <v>6.840840250000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>2.676496e-08</v>
+        <v>5.23402884e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.09151761e-06</v>
+        <v>6.884851210000001e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.09035364e-06</v>
+        <v>1.09662784e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5206342596e-05</v>
+        <v>1.5993143296e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4.171806250000001e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>1.532644e-08</v>
+        <v>6.633715360000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.275576209e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4.00960576e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9.34891776e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>9.477777960000001e-06</v>
       </c>
     </row>
     <row r="25">
@@ -9404,40 +9452,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.68506361e-06</v>
+        <v>1.87005625e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.67780209e-06</v>
+        <v>3.18551104e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>6.3808144e-07</v>
+        <v>2.134521e-06</v>
       </c>
       <c r="E25" t="n">
         <v>7.305668410000001e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44024001e-06</v>
+        <v>1.44648729e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>3.275730756e-06</v>
+        <v>9.091431801e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>2.401e-09</v>
+        <v>3.627120250000001e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>2.36196e-09</v>
+        <v>1.39334416e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>6.645052839999999e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>5.571016090000001e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>6.832996e-08</v>
+        <v>7.64964964e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.58572096e-06</v>
       </c>
     </row>
     <row r="26">
@@ -9450,10 +9498,10 @@
         <v>6.727280399999999e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>5.1093904e-07</v>
+        <v>1.27057984e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4722569e-07</v>
+        <v>1.802851600000001e-07</v>
       </c>
       <c r="E26" t="n">
         <v>5.49339844e-06</v>
@@ -9462,22 +9510,22 @@
         <v>1.29481641e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.342447569000002e-06</v>
+        <v>9.309548195999999e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.039184e-08</v>
       </c>
       <c r="I26" t="n">
-        <v>7.840000000000002e-10</v>
+        <v>2.430480999999999e-08</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>9.35089e-09</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.623076e-08</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.901251600000001e-07</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -9490,40 +9538,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5816529e-07</v>
+        <v>5.309798490000001e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>4.4448889e-07</v>
+        <v>1.582209729e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5376e-10</v>
+        <v>1.215498496e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>4.970670250000002e-06</v>
+        <v>6.81157801e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.17657409e-06</v>
+        <v>1.64506276e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>6.146716801e-06</v>
+        <v>1.6731681201e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.105695504e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>7.638759999999999e-09</v>
+        <v>3.47524164e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.399939481e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.393230276e-05</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.902093769e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.350856516e-05</v>
       </c>
     </row>
     <row r="28">
@@ -9533,7 +9581,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.726275999999999e-08</v>
+        <v>6.548481000000001e-08</v>
       </c>
       <c r="C28" t="n">
         <v>1.982464e-08</v>
@@ -9548,13 +9596,13 @@
         <v>1.23943689e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4470416e-06</v>
+        <v>4.491412323999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3.3856e-10</v>
+        <v>2.87296e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -9576,40 +9624,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.868689e-08</v>
+        <v>2.0331081e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>8.723560000000001e-09</v>
+        <v>3.3466225e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1.3660416e-07</v>
       </c>
       <c r="E29" t="n">
-        <v>4.59930916e-06</v>
+        <v>5.04406681e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08597241e-06</v>
+        <v>1.19399329e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5557369e-06</v>
+        <v>5.618851681e-06</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3.5904064e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>8.099999999999998e-11</v>
+        <v>5.3860921e-07</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.70207844e-06</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1.37311524e-06</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.67294689e-06</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.946318399999999e-07</v>
       </c>
     </row>
     <row r="30">
@@ -9743,40 +9791,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.655</v>
+        <v>161.233</v>
       </c>
       <c r="C2" t="n">
-        <v>33.013</v>
+        <v>216.073</v>
       </c>
       <c r="D2" t="n">
-        <v>74.485</v>
+        <v>220.892</v>
       </c>
       <c r="E2" t="n">
-        <v>226.953</v>
+        <v>268.166</v>
       </c>
       <c r="F2" t="n">
-        <v>105.694</v>
+        <v>111.778</v>
       </c>
       <c r="G2" t="n">
-        <v>142.874</v>
+        <v>181.375</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>240.642</v>
       </c>
       <c r="I2" t="n">
-        <v>1.115</v>
+        <v>227.167</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>264.575</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>237.901</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>231.776</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>316.715</v>
       </c>
     </row>
     <row r="3">
@@ -9786,40 +9834,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.098</v>
+        <v>75.821</v>
       </c>
       <c r="C3" t="n">
-        <v>34.545</v>
+        <v>80.58</v>
       </c>
       <c r="D3" t="n">
-        <v>58.052</v>
+        <v>118.596</v>
       </c>
       <c r="E3" t="n">
-        <v>217.489</v>
+        <v>223.433</v>
       </c>
       <c r="F3" t="n">
-        <v>76.753</v>
+        <v>74.52</v>
       </c>
       <c r="G3" t="n">
-        <v>76.501</v>
+        <v>88.364</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>119.713</v>
       </c>
       <c r="I3" t="n">
-        <v>1.127</v>
+        <v>102.502</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>96.276</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>144.078</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>108.406</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>50.981</v>
       </c>
     </row>
     <row r="4">
@@ -9829,40 +9877,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.982</v>
+        <v>42.702</v>
       </c>
       <c r="C4" t="n">
-        <v>19.197</v>
+        <v>30.117</v>
       </c>
       <c r="D4" t="n">
-        <v>41.357</v>
+        <v>53.854</v>
       </c>
       <c r="E4" t="n">
-        <v>196.131</v>
+        <v>203.603</v>
       </c>
       <c r="F4" t="n">
-        <v>72.789</v>
+        <v>74.374</v>
       </c>
       <c r="G4" t="n">
-        <v>58.103</v>
+        <v>68.42</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I4" t="n">
-        <v>0.805</v>
+        <v>1.544</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>18.632</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>40.521</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>9.944000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9.659000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -9872,22 +9920,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.334</v>
+        <v>20.817</v>
       </c>
       <c r="C5" t="n">
-        <v>5.148</v>
+        <v>7.574</v>
       </c>
       <c r="D5" t="n">
-        <v>18.238</v>
+        <v>18.92</v>
       </c>
       <c r="E5" t="n">
-        <v>195.511</v>
+        <v>195.726</v>
       </c>
       <c r="F5" t="n">
-        <v>94.895</v>
+        <v>92.437</v>
       </c>
       <c r="G5" t="n">
-        <v>79.226</v>
+        <v>75.208</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9913,40 +9961,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.542</v>
+        <v>91.312</v>
       </c>
       <c r="C6" t="n">
-        <v>1.053</v>
+        <v>57.975</v>
       </c>
       <c r="D6" t="n">
-        <v>8.552</v>
+        <v>83.872</v>
       </c>
       <c r="E6" t="n">
-        <v>172.055</v>
+        <v>191.719</v>
       </c>
       <c r="F6" t="n">
-        <v>85.48</v>
+        <v>94.40600000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>44.255</v>
+        <v>64.727</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>25.738</v>
       </c>
       <c r="I6" t="n">
-        <v>0.794</v>
+        <v>45.242</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>122.169</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>150.31</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>105.877</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>126.398</v>
       </c>
     </row>
     <row r="7">
@@ -9956,40 +10004,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.595</v>
+        <v>193.339</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>225.704</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>162.901</v>
       </c>
       <c r="E7" t="n">
-        <v>76.08</v>
+        <v>140.334</v>
       </c>
       <c r="F7" t="n">
-        <v>150.272</v>
+        <v>188.116</v>
       </c>
       <c r="G7" t="n">
-        <v>34.208</v>
+        <v>103.174</v>
       </c>
       <c r="H7" t="n">
-        <v>143.924</v>
+        <v>441.032</v>
       </c>
       <c r="I7" t="n">
-        <v>192.448</v>
+        <v>320.07</v>
       </c>
       <c r="J7" t="n">
-        <v>4.675</v>
+        <v>384.712</v>
       </c>
       <c r="K7" t="n">
-        <v>224.924</v>
+        <v>361.383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.55</v>
+        <v>334.404</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>419.628</v>
       </c>
     </row>
     <row r="8">
@@ -9998,18 +10046,42 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>9.028</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>74.908</v>
+      </c>
+      <c r="F8" t="n">
+        <v>142.316</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.537</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>44.975</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10018,40 +10090,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>57.199</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>36.387</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>36.557</v>
       </c>
       <c r="E9" t="n">
-        <v>35.994</v>
+        <v>63.457</v>
       </c>
       <c r="F9" t="n">
-        <v>84.928</v>
+        <v>107.617</v>
       </c>
       <c r="G9" t="n">
-        <v>3.223</v>
+        <v>23.683</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>45.131</v>
       </c>
       <c r="I9" t="n">
-        <v>1.442</v>
+        <v>119.799</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>55.725</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>167.675</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>100.236</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>42.872</v>
       </c>
     </row>
     <row r="10">
@@ -10061,7 +10133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -10070,25 +10142,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>32.17</v>
+        <v>43.144</v>
       </c>
       <c r="F10" t="n">
-        <v>69.276</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.837</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5.353</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>5.856</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>28.251</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -10113,13 +10185,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>33.989</v>
+        <v>38.294</v>
       </c>
       <c r="F11" t="n">
-        <v>61.171</v>
+        <v>64.337</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2.306</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10128,7 +10200,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.028</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10156,10 +10228,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>22.445</v>
+        <v>22.59</v>
       </c>
       <c r="F12" t="n">
-        <v>47.431</v>
+        <v>49.233</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -10190,37 +10262,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>20.313</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.957</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>10.678</v>
       </c>
       <c r="E13" t="n">
-        <v>0.593</v>
+        <v>19.446</v>
       </c>
       <c r="F13" t="n">
-        <v>26.159</v>
+        <v>41.545</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.915</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>12.684</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>23.007</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>30.013</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>58.546</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>29.613</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -10251,13 +10323,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.988</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.248</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>5.774</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -10276,38 +10348,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80.235</v>
+        <v>224.64</v>
       </c>
       <c r="C15" t="n">
-        <v>45.415</v>
+        <v>245.145</v>
       </c>
       <c r="D15" t="n">
-        <v>69.904</v>
+        <v>250.231</v>
       </c>
       <c r="E15" t="n">
-        <v>208.792</v>
+        <v>247.101</v>
       </c>
       <c r="F15" t="n">
-        <v>96.212</v>
+        <v>98.852</v>
       </c>
       <c r="G15" t="n">
-        <v>227.015</v>
+        <v>250.235</v>
       </c>
       <c r="H15" t="n">
-        <v>2.681</v>
+        <v>128.108</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2.775</v>
+        <v>210.285</v>
       </c>
       <c r="K15" t="n">
-        <v>45.67</v>
+        <v>203.986</v>
       </c>
       <c r="L15" t="n">
-        <v>46.579</v>
+        <v>235.001</v>
       </c>
       <c r="M15" t="n">
-        <v>10.018</v>
+        <v>241.826</v>
       </c>
     </row>
     <row r="16">
@@ -10317,40 +10389,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>95.76600000000001</v>
+        <v>325.836</v>
       </c>
       <c r="C16" t="n">
-        <v>69.93000000000001</v>
+        <v>368.285</v>
       </c>
       <c r="D16" t="n">
-        <v>153.779</v>
+        <v>371.084</v>
       </c>
       <c r="E16" t="n">
-        <v>377.098</v>
+        <v>395.72</v>
       </c>
       <c r="F16" t="n">
-        <v>197.952</v>
+        <v>209.767</v>
       </c>
       <c r="G16" t="n">
-        <v>435.996</v>
+        <v>431.02</v>
       </c>
       <c r="H16" t="n">
-        <v>10.418</v>
+        <v>346.599</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>138.968</v>
       </c>
       <c r="J16" t="n">
-        <v>10.048</v>
+        <v>412.076</v>
       </c>
       <c r="K16" t="n">
-        <v>38.655</v>
+        <v>371.881</v>
       </c>
       <c r="L16" t="n">
-        <v>85.613</v>
+        <v>366.119</v>
       </c>
       <c r="M16" t="n">
-        <v>8.475</v>
+        <v>377.194</v>
       </c>
     </row>
     <row r="17">
@@ -10360,40 +10432,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>90.90000000000001</v>
+        <v>223.45</v>
       </c>
       <c r="C17" t="n">
-        <v>85.08499999999999</v>
+        <v>205.63</v>
       </c>
       <c r="D17" t="n">
-        <v>196.673</v>
+        <v>316.265</v>
       </c>
       <c r="E17" t="n">
-        <v>415.737</v>
+        <v>420.762</v>
       </c>
       <c r="F17" t="n">
-        <v>177.048</v>
+        <v>176.464</v>
       </c>
       <c r="G17" t="n">
-        <v>322.329</v>
+        <v>331</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>316.352</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>134.345</v>
       </c>
       <c r="J17" t="n">
-        <v>0.075</v>
+        <v>404.721</v>
       </c>
       <c r="K17" t="n">
-        <v>10.614</v>
+        <v>259.465</v>
       </c>
       <c r="L17" t="n">
-        <v>38.936</v>
+        <v>369.953</v>
       </c>
       <c r="M17" t="n">
-        <v>3.173</v>
+        <v>338.536</v>
       </c>
     </row>
     <row r="18">
@@ -10403,40 +10475,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.885</v>
+        <v>47.977</v>
       </c>
       <c r="C18" t="n">
-        <v>18.22</v>
+        <v>30.19</v>
       </c>
       <c r="D18" t="n">
-        <v>38.09</v>
+        <v>48.176</v>
       </c>
       <c r="E18" t="n">
-        <v>393.227</v>
+        <v>397.988</v>
       </c>
       <c r="F18" t="n">
-        <v>159.022</v>
+        <v>160.925</v>
       </c>
       <c r="G18" t="n">
-        <v>140.198</v>
+        <v>142.583</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>13.448</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>4.414</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>10.413</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>19.201</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>22.69</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>15.043</v>
       </c>
     </row>
     <row r="19">
@@ -10446,25 +10518,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16.939</v>
+        <v>27.131</v>
       </c>
       <c r="C19" t="n">
-        <v>2.914</v>
+        <v>12.025</v>
       </c>
       <c r="D19" t="n">
-        <v>21.791</v>
+        <v>29.892</v>
       </c>
       <c r="E19" t="n">
-        <v>382.328</v>
+        <v>386.888</v>
       </c>
       <c r="F19" t="n">
-        <v>152.154</v>
+        <v>153.23</v>
       </c>
       <c r="G19" t="n">
-        <v>120.812</v>
+        <v>124.225</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -10473,13 +10545,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.166</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.147</v>
       </c>
     </row>
     <row r="20">
@@ -10489,40 +10561,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>132.625</v>
+        <v>113.469</v>
       </c>
       <c r="C20" t="n">
-        <v>138.198</v>
+        <v>116.56</v>
       </c>
       <c r="D20" t="n">
-        <v>45.368</v>
+        <v>29.101</v>
       </c>
       <c r="E20" t="n">
-        <v>224.826</v>
+        <v>216.417</v>
       </c>
       <c r="F20" t="n">
-        <v>99.00700000000001</v>
+        <v>92.682</v>
       </c>
       <c r="G20" t="n">
-        <v>125.406</v>
+        <v>105.669</v>
       </c>
       <c r="H20" t="n">
-        <v>17.737</v>
+        <v>52.923</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.011</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.824</v>
       </c>
       <c r="K20" t="n">
-        <v>4.986</v>
+        <v>90.012</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.914</v>
       </c>
       <c r="M20" t="n">
-        <v>12.607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -10532,37 +10604,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>95.017</v>
+        <v>157.15</v>
       </c>
       <c r="C21" t="n">
-        <v>97.836</v>
+        <v>159.675</v>
       </c>
       <c r="D21" t="n">
-        <v>18.113</v>
+        <v>54.315</v>
       </c>
       <c r="E21" t="n">
-        <v>204.369</v>
+        <v>214.901</v>
       </c>
       <c r="F21" t="n">
-        <v>83.313</v>
+        <v>84.149</v>
       </c>
       <c r="G21" t="n">
-        <v>86.01000000000001</v>
+        <v>87.82599999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>241.388</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>48.644</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>123.311</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>200.545</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>109.822</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -10575,40 +10647,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>95.029</v>
+        <v>326.683</v>
       </c>
       <c r="C22" t="n">
-        <v>94.398</v>
+        <v>344.862</v>
       </c>
       <c r="D22" t="n">
-        <v>22.094</v>
+        <v>322.188</v>
       </c>
       <c r="E22" t="n">
-        <v>200.965</v>
+        <v>268.403</v>
       </c>
       <c r="F22" t="n">
-        <v>74.34699999999999</v>
+        <v>108.069</v>
       </c>
       <c r="G22" t="n">
-        <v>70.051</v>
+        <v>135.468</v>
       </c>
       <c r="H22" t="n">
-        <v>19.518</v>
+        <v>325.062</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>181.375</v>
       </c>
       <c r="J22" t="n">
-        <v>1.048</v>
+        <v>416.89</v>
       </c>
       <c r="K22" t="n">
-        <v>34.998</v>
+        <v>240.758</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>349.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>378.486</v>
       </c>
     </row>
     <row r="23">
@@ -10618,40 +10690,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.521</v>
+        <v>26.26</v>
       </c>
       <c r="C23" t="n">
-        <v>1.433</v>
+        <v>29.465</v>
       </c>
       <c r="D23" t="n">
-        <v>0.09</v>
+        <v>33.676</v>
       </c>
       <c r="E23" t="n">
-        <v>21.579</v>
+        <v>25.809</v>
       </c>
       <c r="F23" t="n">
-        <v>8.698</v>
+        <v>9.756</v>
       </c>
       <c r="G23" t="n">
-        <v>97.333</v>
+        <v>133.035</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>14.617</v>
       </c>
       <c r="I23" t="n">
-        <v>1.751</v>
+        <v>19.879</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>49.387</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>14.131</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>26.176</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>27.895</v>
       </c>
     </row>
     <row r="24">
@@ -10661,40 +10733,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.551</v>
+        <v>15.743</v>
       </c>
       <c r="C24" t="n">
-        <v>5.93</v>
+        <v>25.341</v>
       </c>
       <c r="D24" t="n">
-        <v>1.38</v>
+        <v>22.074</v>
       </c>
       <c r="E24" t="n">
-        <v>24.548</v>
+        <v>26.233</v>
       </c>
       <c r="F24" t="n">
-        <v>10.275</v>
+        <v>10.356</v>
       </c>
       <c r="G24" t="n">
-        <v>122.502</v>
+        <v>126.337</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>13.927</v>
       </c>
       <c r="I24" t="n">
-        <v>1.238</v>
+        <v>17.763</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>30.107</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>13.458</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>22.641</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>22.984</v>
       </c>
     </row>
     <row r="25">
@@ -10704,40 +10776,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.665</v>
+        <v>13.274</v>
       </c>
       <c r="C25" t="n">
-        <v>10.307</v>
+        <v>15.955</v>
       </c>
       <c r="D25" t="n">
-        <v>7.096</v>
+        <v>13.262</v>
       </c>
       <c r="E25" t="n">
-        <v>27.029</v>
+        <v>25.6</v>
       </c>
       <c r="F25" t="n">
-        <v>11.755</v>
+        <v>11.743</v>
       </c>
       <c r="G25" t="n">
-        <v>57.234</v>
+        <v>95.349</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5.195</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>6.166</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>15.879</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.342</v>
       </c>
     </row>
     <row r="26">
@@ -10747,28 +10819,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>7.487</v>
+        <v>7.286</v>
       </c>
       <c r="C26" t="n">
-        <v>5.694</v>
+        <v>10.559</v>
       </c>
       <c r="D26" t="n">
-        <v>3.318</v>
+        <v>3.729</v>
       </c>
       <c r="E26" t="n">
-        <v>22.679</v>
+        <v>22.331</v>
       </c>
       <c r="F26" t="n">
-        <v>11.332</v>
+        <v>11.266</v>
       </c>
       <c r="G26" t="n">
-        <v>91.337</v>
+        <v>96.249</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1.046</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -10777,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.396</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -10790,40 +10862,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.708</v>
+        <v>22.841</v>
       </c>
       <c r="C27" t="n">
-        <v>2.249</v>
+        <v>39.777</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006</v>
+        <v>34.864</v>
       </c>
       <c r="E27" t="n">
-        <v>21.705</v>
+        <v>26.099</v>
       </c>
       <c r="F27" t="n">
-        <v>10.837</v>
+        <v>12.826</v>
       </c>
       <c r="G27" t="n">
-        <v>78.401</v>
+        <v>129.351</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>25.845</v>
       </c>
       <c r="I27" t="n">
-        <v>0.874</v>
+        <v>11.634</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>49.373</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>29.243</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>33.368</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>31.691</v>
       </c>
     </row>
     <row r="28">
@@ -10833,28 +10905,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.147</v>
+        <v>2.191</v>
       </c>
       <c r="C28" t="n">
-        <v>0.541</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>22.316</v>
+        <v>21.923</v>
       </c>
       <c r="F28" t="n">
-        <v>11.046</v>
+        <v>11.082</v>
       </c>
       <c r="G28" t="n">
-        <v>38.04</v>
+        <v>67.018</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -10876,40 +10948,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.293</v>
+        <v>4.155</v>
       </c>
       <c r="C29" t="n">
-        <v>0.126</v>
+        <v>4.579</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.796</v>
       </c>
       <c r="E29" t="n">
-        <v>21.435</v>
+        <v>22.449</v>
       </c>
       <c r="F29" t="n">
-        <v>10.391</v>
+        <v>10.91</v>
       </c>
       <c r="G29" t="n">
-        <v>59.63</v>
+        <v>74.959</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.054</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1.567</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>5.698</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="30">
@@ -10928,10 +11000,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>13.836</v>
+        <v>13.128</v>
       </c>
       <c r="F30" t="n">
-        <v>5.937</v>
+        <v>5.505</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -11043,40 +11115,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.735139025000001e-06</v>
+        <v>2.599608028900001e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.089858169e-06</v>
+        <v>4.668754132900001e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>5.548015225e-06</v>
+        <v>4.879327566400001e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>5.150766420900001e-05</v>
+        <v>7.191300355600002e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1171221636e-05</v>
+        <v>1.2494321284e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0412979876e-05</v>
+        <v>3.2896890625e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5.7908572164e-05</v>
       </c>
       <c r="I2" t="n">
-        <v>1.243225e-09</v>
+        <v>5.1604845889e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6.9999930625e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>5.6596885801e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5.372011417600001e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.000100308391225</v>
       </c>
     </row>
     <row r="3">
@@ -11086,40 +11158,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.607849604e-06</v>
+        <v>5.748824041e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.193357025e-06</v>
+        <v>6.4931364e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>3.370034704e-06</v>
+        <v>1.4065011216e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>4.730146512100001e-05</v>
+        <v>4.9922305489e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>5.891023009e-06</v>
+        <v>5.553230400000001e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>5.852403000999999e-06</v>
+        <v>7.808196496e-06</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1.4331202369e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.270129e-09</v>
+        <v>1.0506660004e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9.269068175999999e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2.0758470084e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.1751860836e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.599062361e-06</v>
       </c>
     </row>
     <row r="4">
@@ -11129,40 +11201,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.750643239999999e-07</v>
+        <v>1.823460804e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>3.68524809e-07</v>
+        <v>9.070336890000001e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.710401449e-06</v>
+        <v>2.900253316e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8467369161e-05</v>
+        <v>4.1454181609e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>5.298238521000002e-06</v>
+        <v>5.531491875999999e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.375958609e-06</v>
+        <v>4.681296400000002e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3.481000000000001e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.48025e-10</v>
+        <v>2.383936e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3.471514240000001e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.641951441e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>9.888313600000003e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9.329628100000002e-08</v>
       </c>
     </row>
     <row r="5">
@@ -11172,22 +11244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.36135556e-07</v>
+        <v>4.333474889999999e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.6501904e-08</v>
+        <v>5.7365476e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.32624644e-07</v>
+        <v>3.579664000000001e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8224551121e-05</v>
+        <v>3.8308667076e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>9.005061024999999e-06</v>
+        <v>8.544598968999999e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>6.276759076e-06</v>
+        <v>5.656243264e-06</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11213,40 +11285,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.57301764e-07</v>
+        <v>8.337881344e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.108809e-09</v>
+        <v>3.361100625e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>7.313670399999997e-08</v>
+        <v>7.034512384000001e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>2.960292302500001e-05</v>
+        <v>3.6756174961e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>7.3068304e-06</v>
+        <v>8.912492836e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>1.958505025e-06</v>
+        <v>4.189584529000001e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6.624446440000001e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>6.30436e-10</v>
+        <v>2.046838564e-06</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.4925264561e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.25930961e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.1209939129e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.597645440399999e-05</v>
       </c>
     </row>
     <row r="7">
@@ -11256,40 +11328,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.922800833333333e-08</v>
+        <v>1.245998964033333e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.698076520533334e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8.845578600333335e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9293888e-06</v>
+        <v>6.564543852000001e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>7.527224661333332e-06</v>
+        <v>1.179587648533334e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>3.900624213333332e-07</v>
+        <v>3.548291425333334e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>6.904705925333332e-06</v>
+        <v>6.483640834133332e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>1.234541090133334e-05</v>
+        <v>3.414826829999999e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>7.285208333333332e-09</v>
+        <v>4.933444098133334e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.686360192533334e-05</v>
+        <v>4.353255756299999e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>1.008333333333333e-10</v>
+        <v>3.7275345072e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.8695886128e-05</v>
       </c>
     </row>
     <row r="8">
@@ -11298,18 +11370,42 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>8.150478400000002e-08</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.611208464e-06</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.0253843856e-05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.58286369e-07</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.022084e-09</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.022750625e-06</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11318,40 +11414,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1.090575200333333e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4.41337923e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4.454714163333333e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>4.318560119999999e-07</v>
+        <v>1.342263616333334e-06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.404255061333334e-06</v>
+        <v>3.860472896333333e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>3.462576333333333e-09</v>
+        <v>1.869614963333333e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6.789357203333332e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>6.931213333333333e-10</v>
+        <v>4.783933467e-06</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.035091875e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>9.371635208333335e-06</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.349085232e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>6.126694613333333e-07</v>
       </c>
     </row>
     <row r="10">
@@ -11361,7 +11457,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2.5392e-09</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -11370,25 +11466,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3.449696333333334e-07</v>
+        <v>6.204682453333334e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>1.599721391999999e-06</v>
+        <v>1.9400547e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>9.2928e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.124856333333333e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>9.551536333333333e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.1430912e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2.66039667e-07</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -11413,13 +11509,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.850840403333332e-07</v>
+        <v>4.888101453333332e-07</v>
       </c>
       <c r="F11" t="n">
-        <v>1.247297080333333e-06</v>
+        <v>1.379749856333334e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.772545333333333e-09</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -11428,7 +11524,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3.522613333333334e-10</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -11456,10 +11552,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1.679260083333333e-07</v>
+        <v>1.701027e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>7.498999203333331e-07</v>
+        <v>8.079627630000001e-07</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -11490,37 +11586,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1.37539323e-07</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3.05283e-10</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3.800656133333333e-08</v>
       </c>
       <c r="E13" t="n">
-        <v>1.172163333333333e-10</v>
+        <v>1.26048972e-07</v>
       </c>
       <c r="F13" t="n">
-        <v>2.280977603333333e-07</v>
+        <v>5.753290083333333e-07</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.109075e-09</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>5.362795199999999e-08</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.764406830000001e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.002600563333334e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1.142544705333333e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.92309923e-07</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -11551,13 +11647,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8.293381333333335e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>9.180501333333333e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1.111302533333333e-08</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -11576,38 +11672,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.437655225e-06</v>
+        <v>5.046312959999999e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>2.062522225e-06</v>
+        <v>6.0096071025e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>4.886569215999999e-06</v>
+        <v>6.261555336099999e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3594099264e-05</v>
+        <v>6.105890420099999e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>9.256748944000002e-06</v>
+        <v>9.771717904000002e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>5.1535810225e-05</v>
+        <v>6.261755522500002e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>7.187761000000001e-09</v>
+        <v>1.6411659664e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>7.700625e-09</v>
+        <v>4.4219781225e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>2.085748900000001e-06</v>
+        <v>4.161028819600001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>2.169603241e-06</v>
+        <v>5.522547000100001e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>1.00360324e-07</v>
+        <v>5.847981427599999e-05</v>
       </c>
     </row>
     <row r="16">
@@ -11617,40 +11713,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.057042252e-06</v>
+        <v>3.5389699632e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6300683e-06</v>
+        <v>4.521128040833334e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>7.882660280333334e-06</v>
+        <v>4.590111168533334e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>4.740096720133333e-05</v>
+        <v>5.219810613333334e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3061664768e-05</v>
+        <v>1.466739809633334e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3364170672e-05</v>
+        <v>6.192608013333332e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>3.617824133333332e-08</v>
+        <v>4.0043622267e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6.437368341333332e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>3.365410133333333e-08</v>
+        <v>5.660220992533333e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>4.980696750000001e-07</v>
+        <v>4.609849272033332e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>2.443195256333333e-06</v>
+        <v>4.468104072033334e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3941875e-08</v>
+        <v>4.742510454533334e-05</v>
       </c>
     </row>
     <row r="17">
@@ -11660,40 +11756,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.754270000000001e-06</v>
+        <v>1.664330083333333e-05</v>
       </c>
       <c r="C17" t="n">
-        <v>2.413152408333333e-06</v>
+        <v>1.409456563333333e-05</v>
       </c>
       <c r="D17" t="n">
-        <v>1.289342297633334e-05</v>
+        <v>3.334118340833333e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>5.761241772300001e-05</v>
+        <v>5.9013553548e-05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0448664768e-05</v>
+        <v>1.037984776533334e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>3.463199474700001e-05</v>
+        <v>3.652033333333334e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3.335952930133333e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>6.016193008333332e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>1.875e-12</v>
+        <v>5.4599695947e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7552332e-08</v>
+        <v>2.244069540833333e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>5.053373653333333e-07</v>
+        <v>4.562174073633333e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.355976333333333e-09</v>
+        <v>3.820220776533334e-05</v>
       </c>
     </row>
     <row r="18">
@@ -11703,40 +11799,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.040144083333332e-07</v>
+        <v>7.672641763333333e-07</v>
       </c>
       <c r="C18" t="n">
-        <v>1.106561333333333e-07</v>
+        <v>3.038120333333334e-07</v>
       </c>
       <c r="D18" t="n">
-        <v>4.836160333333335e-07</v>
+        <v>7.736423253333335e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>5.154249117633333e-05</v>
+        <v>5.279814938133333e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>8.429332161333334e-06</v>
+        <v>8.632285208333335e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>6.551826401333335e-06</v>
+        <v>6.776637296333332e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>6.028290133333334e-08</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>6.494465333333332e-09</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3.6143523e-08</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1.228928003333333e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.716120333333334e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7.543061633333332e-08</v>
       </c>
     </row>
     <row r="19">
@@ -11746,25 +11842,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.564324033333333e-08</v>
+        <v>2.453637203333333e-07</v>
       </c>
       <c r="C19" t="n">
-        <v>2.830465333333334e-09</v>
+        <v>4.820020833333334e-08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.582825603333334e-07</v>
+        <v>2.978438879999999e-07</v>
       </c>
       <c r="E19" t="n">
-        <v>4.872489986133333e-05</v>
+        <v>4.989410818133332e-05</v>
       </c>
       <c r="F19" t="n">
-        <v>7.716946571999999e-06</v>
+        <v>7.82647763333333e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>4.865179781333334e-06</v>
+        <v>5.143950208333332e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>7.680000000000001e-13</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -11773,13 +11869,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>6.979363333333335e-10</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.531853333333333e-10</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.385363333333333e-10</v>
       </c>
     </row>
     <row r="20">
@@ -11789,40 +11885,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.863130208333333e-06</v>
+        <v>4.291737987e-06</v>
       </c>
       <c r="C20" t="n">
-        <v>6.366229068000001e-06</v>
+        <v>4.528744533333333e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>6.860851413333336e-07</v>
+        <v>2.822894003333333e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6848910092e-05</v>
+        <v>1.5612105963e-05</v>
       </c>
       <c r="F20" t="n">
-        <v>3.267462016333334e-06</v>
+        <v>2.863317708e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>5.242221612000001e-06</v>
+        <v>3.721979187e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.048670563333333e-07</v>
+        <v>9.336146430000002e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.348040333333334e-09</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.658325333333333e-09</v>
       </c>
       <c r="K20" t="n">
-        <v>8.286731999999999e-09</v>
+        <v>2.700720047999999e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.784653333333333e-10</v>
       </c>
       <c r="M20" t="n">
-        <v>5.297881633333333e-08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -11832,37 +11928,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.009410096333333e-06</v>
+        <v>8.232040833333334e-06</v>
       </c>
       <c r="C21" t="n">
-        <v>3.190627631999999e-06</v>
+        <v>8.498701875000001e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>1.093602563333333e-07</v>
+        <v>9.833730749999998e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3922229387e-05</v>
+        <v>1.539414660033333e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>2.313685323e-06</v>
+        <v>2.360351400333333e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4659067e-06</v>
+        <v>2.571135425333333e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.942272218133333e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7.887462453333333e-07</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.068534240333334e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.340609900833333e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.020290561333333e-06</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -11875,40 +11971,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.010170280333333e-06</v>
+        <v>3.557392749633333e-05</v>
       </c>
       <c r="C22" t="n">
-        <v>2.970327468e-06</v>
+        <v>3.9643266348e-05</v>
       </c>
       <c r="D22" t="n">
-        <v>1.627149453333334e-07</v>
+        <v>3.4601702448e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>1.346231040833333e-05</v>
+        <v>2.401339013633333e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>1.842492136333333e-06</v>
+        <v>3.892969587e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>1.635714200333333e-06</v>
+        <v>6.117193007999998e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>1.26984108e-07</v>
+        <v>3.5221767948e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1.096563020833333e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>3.661013333333334e-10</v>
+        <v>5.793242403333333e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>4.082866679999999e-07</v>
+        <v>1.932147152133333e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.079834083333334e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.7750550732e-05</v>
       </c>
     </row>
     <row r="23">
@@ -11918,40 +12014,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.57405441e-06</v>
+        <v>6.895876000000001e-06</v>
       </c>
       <c r="C23" t="n">
-        <v>2.053489e-08</v>
+        <v>8.681862249999999e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>8.099999999999998e-11</v>
+        <v>1.134072976e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>4.65653241e-06</v>
+        <v>6.661044810000001e-06</v>
       </c>
       <c r="F23" t="n">
-        <v>7.565520400000002e-07</v>
+        <v>9.517953600000001e-07</v>
       </c>
       <c r="G23" t="n">
-        <v>9.473712889000001e-06</v>
+        <v>1.769831122499999e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.13656689e-06</v>
       </c>
       <c r="I23" t="n">
-        <v>3.066000999999999e-08</v>
+        <v>3.95174641e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2.439075769e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1.99685161e-06</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6.851829759999999e-06</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>7.781310249999999e-06</v>
       </c>
     </row>
     <row r="24">
@@ -11961,40 +12057,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.0813601e-07</v>
+        <v>2.47842049e-06</v>
       </c>
       <c r="C24" t="n">
-        <v>3.516489999999999e-07</v>
+        <v>6.421662810000001e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>1.9044e-08</v>
+        <v>4.872614760000002e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>6.026043039999998e-06</v>
+        <v>6.881702889999999e-06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.05575625e-06</v>
+        <v>1.07246736e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>1.5006740004e-05</v>
+        <v>1.5961037569e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.93961329e-06</v>
       </c>
       <c r="I24" t="n">
-        <v>1.532644e-08</v>
+        <v>3.155241690000001e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>9.064314489999999e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1.81117764e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.12614881e-06</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.28264256e-06</v>
       </c>
     </row>
     <row r="25">
@@ -12004,40 +12100,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.36072225e-06</v>
+        <v>1.76199076e-06</v>
       </c>
       <c r="C25" t="n">
-        <v>1.06234249e-06</v>
+        <v>2.54562025e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>5.0353216e-07</v>
+        <v>1.75880644e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>7.305668410000001e-06</v>
+        <v>6.5536e-06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.381800250000001e-06</v>
+        <v>1.37898049e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>3.275730756e-06</v>
+        <v>9.091431801e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.6988025e-07</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>4.199040000000001e-07</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.8019556e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4.27716e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.52142641e-06</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8536964e-07</v>
       </c>
     </row>
     <row r="26">
@@ -12047,28 +12143,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.6055169e-07</v>
+        <v>5.3085796e-07</v>
       </c>
       <c r="C26" t="n">
-        <v>3.2421636e-07</v>
+        <v>1.11492481e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1009124e-07</v>
+        <v>1.3905441e-07</v>
       </c>
       <c r="E26" t="n">
-        <v>5.143370409999999e-06</v>
+        <v>4.986735609999999e-06</v>
       </c>
       <c r="F26" t="n">
-        <v>1.28414224e-06</v>
+        <v>1.26922756e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>8.342447569000002e-06</v>
+        <v>9.263870001000001e-06</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1.094116e-08</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -12077,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.948816e-08</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -12090,40 +12186,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3749264e-07</v>
+        <v>5.21711281e-06</v>
       </c>
       <c r="C27" t="n">
-        <v>5.058001000000001e-08</v>
+        <v>1.582209729e-05</v>
       </c>
       <c r="D27" t="n">
-        <v>3.6e-13</v>
+        <v>1.215498496e-05</v>
       </c>
       <c r="E27" t="n">
-        <v>4.711070249999999e-06</v>
+        <v>6.81157801e-06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.17440569e-06</v>
+        <v>1.64506276e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>6.146716801e-06</v>
+        <v>1.6731681201e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>6.67964025e-06</v>
       </c>
       <c r="I27" t="n">
-        <v>7.638759999999999e-09</v>
+        <v>1.35349956e-06</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.437693129e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>8.55153049e-06</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.113423424e-05</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.004319481e-05</v>
       </c>
     </row>
     <row r="28">
@@ -12133,28 +12229,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.609608999999999e-08</v>
+        <v>4.800480999999999e-08</v>
       </c>
       <c r="C28" t="n">
-        <v>2.92681e-09</v>
+        <v>4.651240000000001e-09</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.98003856e-06</v>
+        <v>4.806179289999999e-06</v>
       </c>
       <c r="F28" t="n">
-        <v>1.22014116e-06</v>
+        <v>1.22810724e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4470416e-06</v>
+        <v>4.491412323999999e-06</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.94481e-09</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -12176,40 +12272,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.671849e-08</v>
+        <v>1.7264025e-07</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5876e-10</v>
+        <v>2.0967241e-07</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>7.817616e-08</v>
       </c>
       <c r="E29" t="n">
-        <v>4.59459225e-06</v>
+        <v>5.039576009999999e-06</v>
       </c>
       <c r="F29" t="n">
-        <v>1.07972881e-06</v>
+        <v>1.190281e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>3.5557369e-06</v>
+        <v>5.618851681e-06</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>9.326916e-08</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.15296e-07</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2.455489e-08</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>3.246720400000001e-07</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.368099999999999e-10</v>
       </c>
     </row>
     <row r="30">
@@ -12228,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.91434896e-06</v>
+        <v>1.72344384e-06</v>
       </c>
       <c r="F30" t="n">
-        <v>3.524796900000001e-07</v>
+        <v>3.0305025e-07</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -12343,40 +12439,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003125</v>
+        <v>0.246181</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000347</v>
+        <v>0.236458</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000347</v>
+        <v>0.21875</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
     </row>
     <row r="3">
@@ -12386,40 +12482,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000694</v>
+        <v>0.185069</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000347</v>
+        <v>0.19375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000347</v>
+        <v>0.232639</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F3" t="n">
         <v>0.001736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003125</v>
+        <v>0.249306</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.165972</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000694</v>
+        <v>0.160417</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.181597</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.192014</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.166667</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.160764</v>
       </c>
     </row>
     <row r="4">
@@ -12429,40 +12525,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003125</v>
+        <v>0.236806</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000347</v>
+        <v>0.148264</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000694</v>
+        <v>0.051042</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000347</v>
+        <v>0.19375</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000347</v>
+        <v>0.210417</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000347</v>
+        <v>0.204514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.000347</v>
+        <v>0.202083</v>
       </c>
     </row>
     <row r="5">
@@ -12472,13 +12568,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001042</v>
+        <v>0.249653</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000694</v>
+        <v>0.249306</v>
       </c>
       <c r="E5" t="n">
         <v>0.000694</v>
@@ -12513,40 +12609,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001389</v>
+        <v>0.249653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000347</v>
+        <v>0.249306</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
     </row>
     <row r="7">
@@ -12556,40 +12652,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000347</v>
+        <v>0.080556</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000347</v>
+        <v>0.045833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003125</v>
+        <v>0.047569</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000347</v>
+        <v>0.061806</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003125</v>
+        <v>0.08784699999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000347</v>
+        <v>0.233681</v>
       </c>
     </row>
     <row r="8">
@@ -12598,18 +12694,42 @@
           <t>24/09/2024</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0.166667</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.111111</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.208333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.246528</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.100694</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.003472</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.003472</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12618,40 +12738,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001389</v>
+        <v>0.249653</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
     </row>
     <row r="10">
@@ -12661,7 +12781,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C10" t="n">
         <v>0.000347</v>
@@ -12670,28 +12790,28 @@
         <v>0.000347</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F10" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000347</v>
+        <v>0.214583</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000347</v>
+        <v>0.08437500000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.000347</v>
+        <v>0.127083</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000347</v>
+        <v>0.219792</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000347</v>
+        <v>0.13125</v>
       </c>
       <c r="M10" t="n">
         <v>0.000347</v>
@@ -12713,22 +12833,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="F11" t="n">
-        <v>0.000347</v>
+        <v>0.224653</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.249653</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.170833</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.125694</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.124653</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -12756,10 +12876,10 @@
         <v>0.000347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000347</v>
+        <v>0.133681</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="G12" t="n">
         <v>0.000347</v>
@@ -12790,37 +12910,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="E13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="H13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="K13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="M13" t="n">
         <v>0.000347</v>
@@ -12851,13 +12971,13 @@
         <v>0.000347</v>
       </c>
       <c r="H14" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="K14" t="n">
         <v>0.000347</v>
@@ -12876,38 +12996,38 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="C15" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="F15" t="n">
         <v>0.000347</v>
       </c>
       <c r="G15" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000347</v>
+        <v>0.046528</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="K15" t="n">
-        <v>0.000347</v>
+        <v>0.133333</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000347</v>
+        <v>0.150347</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000347</v>
+        <v>0.156597</v>
       </c>
     </row>
     <row r="16">
@@ -12917,40 +13037,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D16" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="G16" t="n">
-        <v>0.003125</v>
+        <v>0.021875</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000347</v>
+        <v>0.076389</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000347</v>
+        <v>0.060764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000347</v>
+        <v>0.07256899999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.000347</v>
+        <v>0.154514</v>
       </c>
       <c r="L16" t="n">
-        <v>0.000347</v>
+        <v>0.139236</v>
       </c>
       <c r="M16" t="n">
-        <v>0.000347</v>
+        <v>0.132986</v>
       </c>
     </row>
     <row r="17">
@@ -12960,40 +13080,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="C17" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001042</v>
+        <v>0.101042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000347</v>
+        <v>0.130556</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000347</v>
+        <v>0.205208</v>
       </c>
       <c r="J17" t="n">
-        <v>0.000347</v>
+        <v>0.100694</v>
       </c>
       <c r="K17" t="n">
-        <v>0.000347</v>
+        <v>0.144444</v>
       </c>
       <c r="L17" t="n">
-        <v>0.000347</v>
+        <v>0.174306</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001042</v>
+        <v>0.198611</v>
       </c>
     </row>
     <row r="18">
@@ -13003,40 +13123,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.000694</v>
+        <v>0.137847</v>
       </c>
       <c r="C18" t="n">
-        <v>0.000347</v>
+        <v>0.238889</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000694</v>
+        <v>0.210069</v>
       </c>
       <c r="E18" t="n">
-        <v>0.003125</v>
+        <v>0.141319</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000347</v>
+        <v>0.132986</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001389</v>
+        <v>0.249653</v>
       </c>
       <c r="H18" t="n">
-        <v>0.000347</v>
+        <v>0.092361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000347</v>
+        <v>0.073958</v>
       </c>
       <c r="J18" t="n">
-        <v>0.000347</v>
+        <v>0.064236</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000347</v>
+        <v>0.088542</v>
       </c>
       <c r="L18" t="n">
-        <v>0.000347</v>
+        <v>0.053125</v>
       </c>
       <c r="M18" t="n">
-        <v>0.000347</v>
+        <v>0.061458</v>
       </c>
     </row>
     <row r="19">
@@ -13046,40 +13166,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.001042</v>
+        <v>0.249653</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D19" t="n">
-        <v>0.000694</v>
+        <v>0.219444</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000347</v>
+        <v>0.226736</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003125</v>
+        <v>0.044792</v>
       </c>
       <c r="G19" t="n">
-        <v>0.003125</v>
+        <v>0.219444</v>
       </c>
       <c r="H19" t="n">
-        <v>0.000347</v>
+        <v>0.092014</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000347</v>
+        <v>0.100347</v>
       </c>
       <c r="J19" t="n">
-        <v>0.000347</v>
+        <v>0.1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.000347</v>
+        <v>0.093056</v>
       </c>
       <c r="L19" t="n">
-        <v>0.000347</v>
+        <v>0.052431</v>
       </c>
       <c r="M19" t="n">
-        <v>0.000347</v>
+        <v>0.067708</v>
       </c>
     </row>
     <row r="20">
@@ -13104,7 +13224,7 @@
         <v>0.000347</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003125</v>
+        <v>0.005903</v>
       </c>
       <c r="H20" t="n">
         <v>0.000347</v>
@@ -13116,10 +13236,10 @@
         <v>0.000347</v>
       </c>
       <c r="K20" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="L20" t="n">
-        <v>0.000347</v>
+        <v>0.026736</v>
       </c>
       <c r="M20" t="n">
         <v>0.000347</v>
@@ -13132,37 +13252,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.000347</v>
+        <v>0.197222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.000694</v>
+        <v>0.197917</v>
       </c>
       <c r="D21" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001389</v>
+        <v>0.139236</v>
       </c>
       <c r="G21" t="n">
-        <v>0.003125</v>
+        <v>0.221181</v>
       </c>
       <c r="H21" t="n">
-        <v>0.000347</v>
+        <v>0.146875</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000347</v>
+        <v>0.169444</v>
       </c>
       <c r="J21" t="n">
-        <v>0.000347</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.000347</v>
+        <v>0.101042</v>
       </c>
       <c r="L21" t="n">
-        <v>0.000347</v>
+        <v>0.126736</v>
       </c>
       <c r="M21" t="n">
         <v>0.000347</v>
@@ -13175,40 +13295,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.001042</v>
+        <v>0.249653</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001042</v>
+        <v>0.249653</v>
       </c>
       <c r="D22" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="E22" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F22" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001042</v>
+        <v>0.249653</v>
       </c>
       <c r="H22" t="n">
-        <v>0.000347</v>
+        <v>0.052431</v>
       </c>
       <c r="I22" t="n">
-        <v>0.000347</v>
+        <v>0.021181</v>
       </c>
       <c r="J22" t="n">
-        <v>0.000347</v>
+        <v>0.073958</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000347</v>
+        <v>0.118403</v>
       </c>
       <c r="L22" t="n">
-        <v>0.000347</v>
+        <v>0.164931</v>
       </c>
       <c r="M22" t="n">
-        <v>0.000347</v>
+        <v>0.238542</v>
       </c>
     </row>
     <row r="23">
@@ -13218,40 +13338,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003125</v>
+        <v>0.028819</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001042</v>
+        <v>0.163194</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000694</v>
+        <v>0.210764</v>
       </c>
       <c r="E23" t="n">
-        <v>0.000694</v>
+        <v>0.249653</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001042</v>
+        <v>0.248264</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001042</v>
+        <v>0.249653</v>
       </c>
       <c r="H23" t="n">
-        <v>0.000347</v>
+        <v>0.033681</v>
       </c>
       <c r="I23" t="n">
-        <v>0.003125</v>
+        <v>0.022222</v>
       </c>
       <c r="J23" t="n">
-        <v>0.000347</v>
+        <v>0.117708</v>
       </c>
       <c r="K23" t="n">
-        <v>0.000347</v>
+        <v>0.031944</v>
       </c>
       <c r="L23" t="n">
-        <v>0.000347</v>
+        <v>0.042014</v>
       </c>
       <c r="M23" t="n">
-        <v>0.000347</v>
+        <v>0.045486</v>
       </c>
     </row>
     <row r="24">
@@ -13261,40 +13381,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.000694</v>
+        <v>0.190625</v>
       </c>
       <c r="C24" t="n">
-        <v>0.000694</v>
+        <v>0.169097</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000347</v>
+        <v>0.185764</v>
       </c>
       <c r="E24" t="n">
-        <v>0.001042</v>
+        <v>0.246181</v>
       </c>
       <c r="F24" t="n">
-        <v>0.000347</v>
+        <v>0.080208</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000694</v>
+        <v>0.21875</v>
       </c>
       <c r="H24" t="n">
-        <v>0.000347</v>
+        <v>0.024306</v>
       </c>
       <c r="I24" t="n">
-        <v>0.003125</v>
+        <v>0.017361</v>
       </c>
       <c r="J24" t="n">
-        <v>0.000347</v>
+        <v>0.09375</v>
       </c>
       <c r="K24" t="n">
-        <v>0.000347</v>
+        <v>0.030556</v>
       </c>
       <c r="L24" t="n">
-        <v>0.000347</v>
+        <v>0.025347</v>
       </c>
       <c r="M24" t="n">
-        <v>0.000347</v>
+        <v>0.036111</v>
       </c>
     </row>
     <row r="25">
@@ -13304,40 +13424,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.000694</v>
+        <v>0.164931</v>
       </c>
       <c r="C25" t="n">
-        <v>0.001042</v>
+        <v>0.147569</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001042</v>
+        <v>0.151736</v>
       </c>
       <c r="E25" t="n">
         <v>0.003125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000694</v>
+        <v>0.106597</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H25" t="n">
-        <v>0.000694</v>
+        <v>0.043403</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000347</v>
+        <v>0.092014</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000347</v>
+        <v>0.054167</v>
       </c>
       <c r="K25" t="n">
-        <v>0.000347</v>
+        <v>0.080208</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001042</v>
+        <v>0.115625</v>
       </c>
       <c r="M25" t="n">
-        <v>0.000347</v>
+        <v>0.103472</v>
       </c>
     </row>
     <row r="26">
@@ -13350,10 +13470,10 @@
         <v>0.001042</v>
       </c>
       <c r="C26" t="n">
-        <v>0.000694</v>
+        <v>0.132292</v>
       </c>
       <c r="D26" t="n">
-        <v>0.000694</v>
+        <v>0.154167</v>
       </c>
       <c r="E26" t="n">
         <v>0.001042</v>
@@ -13362,22 +13482,22 @@
         <v>0.001389</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003125</v>
+        <v>0.160417</v>
       </c>
       <c r="H26" t="n">
-        <v>0.000347</v>
+        <v>0.08472200000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.000347</v>
+        <v>0.130903</v>
       </c>
       <c r="J26" t="n">
-        <v>0.000347</v>
+        <v>0.104167</v>
       </c>
       <c r="K26" t="n">
-        <v>0.000347</v>
+        <v>0.072917</v>
       </c>
       <c r="L26" t="n">
-        <v>0.000347</v>
+        <v>0.089931</v>
       </c>
       <c r="M26" t="n">
         <v>0.000347</v>
@@ -13390,40 +13510,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.000694</v>
+        <v>0.202431</v>
       </c>
       <c r="C27" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="D27" t="n">
-        <v>0.000347</v>
+        <v>0.249653</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001389</v>
+        <v>0.249653</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001042</v>
+        <v>0.249306</v>
       </c>
       <c r="G27" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H27" t="n">
-        <v>0.000347</v>
+        <v>0.07083299999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.003125</v>
+        <v>0.015278</v>
       </c>
       <c r="J27" t="n">
-        <v>0.000347</v>
+        <v>0.067014</v>
       </c>
       <c r="K27" t="n">
-        <v>0.000347</v>
+        <v>0.057639</v>
       </c>
       <c r="L27" t="n">
-        <v>0.000347</v>
+        <v>0.043403</v>
       </c>
       <c r="M27" t="n">
-        <v>0.000347</v>
+        <v>0.057639</v>
       </c>
     </row>
     <row r="28">
@@ -13433,7 +13553,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.000347</v>
+        <v>0.052431</v>
       </c>
       <c r="C28" t="n">
         <v>0.000347</v>
@@ -13448,13 +13568,13 @@
         <v>0.000347</v>
       </c>
       <c r="G28" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H28" t="n">
         <v>0.000347</v>
       </c>
       <c r="I28" t="n">
-        <v>0.000347</v>
+        <v>0.040625</v>
       </c>
       <c r="J28" t="n">
         <v>0.000347</v>
@@ -13476,40 +13596,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001042</v>
+        <v>0.157639</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001042</v>
+        <v>0.144792</v>
       </c>
       <c r="D29" t="n">
-        <v>0.000347</v>
+        <v>0.139583</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001389</v>
+        <v>0.227083</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001042</v>
+        <v>0.212153</v>
       </c>
       <c r="G29" t="n">
-        <v>0.003125</v>
+        <v>0.249653</v>
       </c>
       <c r="H29" t="n">
-        <v>0.000347</v>
+        <v>0.092708</v>
       </c>
       <c r="I29" t="n">
-        <v>0.000347</v>
+        <v>0.093056</v>
       </c>
       <c r="J29" t="n">
-        <v>0.000347</v>
+        <v>0.058333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.000347</v>
+        <v>0.08819399999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>0.000347</v>
+        <v>0.077431</v>
       </c>
       <c r="M29" t="n">
-        <v>0.000347</v>
+        <v>0.117708</v>
       </c>
     </row>
     <row r="30">

--- a/mfc_features.xlsx
+++ b/mfc_features.xlsx
@@ -7292,7 +7292,9 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -7720,7 +7722,9 @@
       <c r="H15" t="n">
         <v>150.226</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="n">
         <v>210.285</v>
       </c>
@@ -8616,7 +8620,9 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -9044,7 +9050,9 @@
       <c r="H15" t="n">
         <v>2.2567851076e-05</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="n">
         <v>4.4219781225e-05</v>
       </c>
@@ -9940,7 +9948,9 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -10368,7 +10378,9 @@
       <c r="H15" t="n">
         <v>128.108</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="n">
         <v>210.285</v>
       </c>
@@ -11264,7 +11276,9 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -11692,7 +11706,9 @@
       <c r="H15" t="n">
         <v>1.6411659664e-05</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="n">
         <v>4.4219781225e-05</v>
       </c>
@@ -12586,20 +12602,22 @@
         <v>0.000347</v>
       </c>
       <c r="H5" t="n">
-        <v>0.000347</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
       <c r="J5" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -12698,10 +12716,10 @@
         <v>0.166667</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003472</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003472</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0.111111</v>
@@ -12713,22 +12731,22 @@
         <v>0.246528</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003472</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0.100694</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003472</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0.003472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003472</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -12784,10 +12802,10 @@
         <v>0.249653</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0.249653</v>
@@ -12814,7 +12832,7 @@
         <v>0.13125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -12867,13 +12885,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0.133681</v>
@@ -12882,25 +12900,25 @@
         <v>0.249653</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -12943,7 +12961,7 @@
         <v>0.249653</v>
       </c>
       <c r="M13" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -12953,22 +12971,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0.249653</v>
@@ -12980,13 +12998,13 @@
         <v>0.249653</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13016,7 +13034,9 @@
       <c r="H15" t="n">
         <v>0.046528</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="n">
         <v>0.249653</v>
       </c>
@@ -13285,7 +13305,7 @@
         <v>0.126736</v>
       </c>
       <c r="M21" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -13500,7 +13520,7 @@
         <v>0.089931</v>
       </c>
       <c r="M26" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -13559,7 +13579,7 @@
         <v>0.000347</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0.001389</v>
@@ -13571,22 +13591,22 @@
         <v>0.249653</v>
       </c>
       <c r="H28" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0.040625</v>
       </c>
       <c r="J28" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.000347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
